--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -3397,7 +3397,7 @@
 Call log:
   - login error must be friendly text, not a raw exception class with timeout 10000ms
   - waiting for locator('[role="alert"]').first()
-    21 × locator resolved to &lt;div role="alert" class="bg-d</t>
+    23 × locator resolved to &lt;div role="alert" class="bg-d</t>
         </is>
       </c>
       <c r="P33" s="8" t="inlineStr">
@@ -3477,7 +3477,7 @@
 Call log:
   - login error must be friendly text, not a raw exception class with timeout 10000ms
   - waiting for locator('[role="alert"]').first()
-    21 × locator resolved to &lt;div role="alert" class="bg-d</t>
+    23 × locator resolved to &lt;div role="alert" class="bg-d</t>
         </is>
       </c>
       <c r="P34" s="8" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="O55" s="7" t="inlineStr">
         <is>
-          <t>Asterisk on 'Enterprenur Name *' is taupe rgb(107,99,89) (inherits label ink-soft), NOT terracotta #C26849 (rgb 194,104,73). Marker present but wrong colour.</t>
+          <t>Asterisk on the name label is taupe rgb(107,99,89) (inherits label ink-soft), NOT terracotta #C26849. Marker present but wrong colour.</t>
         </is>
       </c>
       <c r="P55" s="8" t="inlineStr">
@@ -4996,9 +4996,9 @@
       </c>
       <c r="L58" s="7" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
-      <c r="N58" s="13" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+      <c r="N58" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O58" s="7" t="inlineStr">
@@ -5198,9 +5198,9 @@
       </c>
       <c r="L61" s="7" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
-      <c r="N61" s="13" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+      <c r="N61" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O61" s="7" t="inlineStr">
@@ -5266,8 +5266,16 @@
       </c>
       <c r="L62" s="7" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr"/>
-      <c r="N62" s="8" t="inlineStr"/>
-      <c r="O62" s="7" t="inlineStr"/>
+      <c r="N62" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O62" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P62" s="8" t="inlineStr"/>
       <c r="Q62" s="7" t="inlineStr"/>
     </row>
@@ -5327,8 +5335,16 @@
       </c>
       <c r="L63" s="7" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
-      <c r="N63" s="8" t="inlineStr"/>
-      <c r="O63" s="7" t="inlineStr"/>
+      <c r="N63" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O63" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P63" s="8" t="inlineStr"/>
       <c r="Q63" s="7" t="inlineStr"/>
     </row>
@@ -5386,9 +5402,36 @@
       </c>
       <c r="L64" s="7" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
-      <c r="N64" s="8" t="inlineStr"/>
-      <c r="O64" s="7" t="inlineStr"/>
-      <c r="P64" s="8" t="inlineStr"/>
+      <c r="N64" s="12" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O64" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Error: label violations: [{"id":"label","n":6}]
+expect(received).toEqual(expected) // deep equality
+- Expected  -   1
++ Received  + 457
+- Array []
++ Array [
++   Object {
++     "description": "Ensure every form element has a label",
++     "help": "Form elements must have labels",
++     "helpUrl": "https://dequeuniversity.com/rules/axe/4.11/label?application=playwright",
++     "id": "label",
++     "impact": "critical",
++     "nodes": Array [
++       Object {
++         "all": Array [],
++        </t>
+        </is>
+      </c>
+      <c r="P64" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="Q64" s="7" t="inlineStr"/>
     </row>
     <row r="65">
@@ -5445,9 +5488,32 @@
       </c>
       <c r="L65" s="7" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
-      <c r="N65" s="8" t="inlineStr"/>
-      <c r="O65" s="7" t="inlineStr"/>
-      <c r="P65" s="8" t="inlineStr"/>
+      <c r="N65" s="12" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O65" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Error: contrast violations: [10]
+expect(received).toEqual(expected) // deep equality
+- Expected  -   1
++ Received  + 373
+- Array []
++ Array [
++   Object {
++     "description": "Ensure the contrast between foreground and background colors meets WCAG 2 AA minimum contrast ratio thresholds",
++     "help": "Elements must meet minimum color contrast ratio thresholds",
++     "helpUrl": "https://dequeuniversity.com/rules/axe/4.11/color-contrast?application=playwright",
++     "id": "color-contrast",
+</t>
+        </is>
+      </c>
+      <c r="P65" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="Q65" s="7" t="inlineStr"/>
     </row>
     <row r="66">
@@ -5504,8 +5570,16 @@
       </c>
       <c r="L66" s="7" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
-      <c r="N66" s="8" t="inlineStr"/>
-      <c r="O66" s="7" t="inlineStr"/>
+      <c r="N66" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O66" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P66" s="8" t="inlineStr"/>
       <c r="Q66" s="7" t="inlineStr"/>
     </row>
@@ -5564,8 +5638,16 @@
       </c>
       <c r="L67" s="7" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr"/>
-      <c r="N67" s="8" t="inlineStr"/>
-      <c r="O67" s="7" t="inlineStr"/>
+      <c r="N67" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O67" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P67" s="8" t="inlineStr"/>
       <c r="Q67" s="7" t="inlineStr"/>
     </row>
@@ -5624,8 +5706,16 @@
       </c>
       <c r="L68" s="7" t="inlineStr"/>
       <c r="M68" s="7" t="inlineStr"/>
-      <c r="N68" s="8" t="inlineStr"/>
-      <c r="O68" s="7" t="inlineStr"/>
+      <c r="N68" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O68" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P68" s="8" t="inlineStr"/>
       <c r="Q68" s="7" t="inlineStr"/>
     </row>
@@ -5683,8 +5773,16 @@
       </c>
       <c r="L69" s="7" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr"/>
-      <c r="N69" s="8" t="inlineStr"/>
-      <c r="O69" s="7" t="inlineStr"/>
+      <c r="N69" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O69" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P69" s="8" t="inlineStr"/>
       <c r="Q69" s="7" t="inlineStr"/>
     </row>
@@ -6838,14 +6936,14 @@
       </c>
       <c r="L87" s="7" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr"/>
-      <c r="N87" s="12" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="N87" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O87" s="7" t="inlineStr">
         <is>
-          <t>Error: worker process exited unexpectedly (code=3221226505, signal=null)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="P87" s="8" t="inlineStr">
@@ -18686,8 +18784,16 @@
       </c>
       <c r="L270" s="7" t="inlineStr"/>
       <c r="M270" s="7" t="inlineStr"/>
-      <c r="N270" s="8" t="inlineStr"/>
-      <c r="O270" s="7" t="inlineStr"/>
+      <c r="N270" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O270" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P270" s="8" t="inlineStr"/>
       <c r="Q270" s="7" t="inlineStr"/>
     </row>
@@ -18755,8 +18861,16 @@
           <t>BRD: EP Status Monitor cascading + independent filters.</t>
         </is>
       </c>
-      <c r="N271" s="8" t="inlineStr"/>
-      <c r="O271" s="7" t="inlineStr"/>
+      <c r="N271" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O271" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P271" s="8" t="inlineStr"/>
       <c r="Q271" s="7" t="inlineStr"/>
     </row>
@@ -18814,8 +18928,16 @@
       </c>
       <c r="L272" s="7" t="inlineStr"/>
       <c r="M272" s="7" t="inlineStr"/>
-      <c r="N272" s="8" t="inlineStr"/>
-      <c r="O272" s="7" t="inlineStr"/>
+      <c r="N272" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O272" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P272" s="8" t="inlineStr"/>
       <c r="Q272" s="7" t="inlineStr"/>
     </row>
@@ -18873,8 +18995,16 @@
       </c>
       <c r="L273" s="7" t="inlineStr"/>
       <c r="M273" s="7" t="inlineStr"/>
-      <c r="N273" s="8" t="inlineStr"/>
-      <c r="O273" s="7" t="inlineStr"/>
+      <c r="N273" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O273" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P273" s="8" t="inlineStr"/>
       <c r="Q273" s="7" t="inlineStr"/>
     </row>
@@ -18932,8 +19062,16 @@
       </c>
       <c r="L274" s="7" t="inlineStr"/>
       <c r="M274" s="7" t="inlineStr"/>
-      <c r="N274" s="8" t="inlineStr"/>
-      <c r="O274" s="7" t="inlineStr"/>
+      <c r="N274" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O274" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P274" s="8" t="inlineStr"/>
       <c r="Q274" s="7" t="inlineStr"/>
     </row>
@@ -18991,8 +19129,16 @@
       </c>
       <c r="L275" s="7" t="inlineStr"/>
       <c r="M275" s="7" t="inlineStr"/>
-      <c r="N275" s="8" t="inlineStr"/>
-      <c r="O275" s="7" t="inlineStr"/>
+      <c r="N275" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O275" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P275" s="8" t="inlineStr"/>
       <c r="Q275" s="7" t="inlineStr"/>
     </row>
@@ -19050,8 +19196,16 @@
       </c>
       <c r="L276" s="7" t="inlineStr"/>
       <c r="M276" s="7" t="inlineStr"/>
-      <c r="N276" s="8" t="inlineStr"/>
-      <c r="O276" s="7" t="inlineStr"/>
+      <c r="N276" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O276" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P276" s="8" t="inlineStr"/>
       <c r="Q276" s="7" t="inlineStr"/>
     </row>
@@ -19109,8 +19263,16 @@
       </c>
       <c r="L277" s="7" t="inlineStr"/>
       <c r="M277" s="7" t="inlineStr"/>
-      <c r="N277" s="8" t="inlineStr"/>
-      <c r="O277" s="7" t="inlineStr"/>
+      <c r="N277" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O277" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P277" s="8" t="inlineStr"/>
       <c r="Q277" s="7" t="inlineStr"/>
     </row>
@@ -19168,8 +19330,16 @@
       </c>
       <c r="L278" s="7" t="inlineStr"/>
       <c r="M278" s="7" t="inlineStr"/>
-      <c r="N278" s="8" t="inlineStr"/>
-      <c r="O278" s="7" t="inlineStr"/>
+      <c r="N278" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O278" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P278" s="8" t="inlineStr"/>
       <c r="Q278" s="7" t="inlineStr"/>
     </row>
@@ -19227,8 +19397,16 @@
       </c>
       <c r="L279" s="7" t="inlineStr"/>
       <c r="M279" s="7" t="inlineStr"/>
-      <c r="N279" s="8" t="inlineStr"/>
-      <c r="O279" s="7" t="inlineStr"/>
+      <c r="N279" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O279" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P279" s="8" t="inlineStr"/>
       <c r="Q279" s="7" t="inlineStr"/>
     </row>
@@ -19286,8 +19464,16 @@
       </c>
       <c r="L280" s="7" t="inlineStr"/>
       <c r="M280" s="7" t="inlineStr"/>
-      <c r="N280" s="8" t="inlineStr"/>
-      <c r="O280" s="7" t="inlineStr"/>
+      <c r="N280" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O280" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P280" s="8" t="inlineStr"/>
       <c r="Q280" s="7" t="inlineStr"/>
     </row>
@@ -19345,8 +19531,16 @@
       </c>
       <c r="L281" s="7" t="inlineStr"/>
       <c r="M281" s="7" t="inlineStr"/>
-      <c r="N281" s="8" t="inlineStr"/>
-      <c r="O281" s="7" t="inlineStr"/>
+      <c r="N281" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O281" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P281" s="8" t="inlineStr"/>
       <c r="Q281" s="7" t="inlineStr"/>
     </row>
@@ -21993,7 +22187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N34"/>
+  <dimension ref="A1:N36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -23702,7 +23896,7 @@
 Call log:
   - login error must be friendly text, not a raw exception class with timeout 10000ms
   - waiting for locator('[role="alert"]').first()
-    21 × locator resolved to &lt;div role="alert" class="bg-d</t>
+    23 × locator resolved to &lt;div role="alert" class="bg-d</t>
         </is>
       </c>
       <c r="J30" s="7" t="inlineStr">
@@ -23771,7 +23965,7 @@
 Call log:
   - login error must be friendly text, not a raw exception class with timeout 10000ms
   - waiting for locator('[role="alert"]').first()
-    21 × locator resolved to &lt;div role="alert" class="bg-d</t>
+    23 × locator resolved to &lt;div role="alert" class="bg-d</t>
         </is>
       </c>
       <c r="J31" s="7" t="inlineStr">
@@ -23892,7 +24086,7 @@
       <c r="H33" s="7" t="inlineStr"/>
       <c r="I33" s="7" t="inlineStr">
         <is>
-          <t>Asterisk on 'Enterprenur Name *' is taupe rgb(107,99,89) (inherits label ink-soft), NOT terracotta #C26849 (rgb 194,104,73). Marker present but wrong colour.</t>
+          <t>Asterisk on the name label is taupe rgb(107,99,89) (inherits label ink-soft), NOT terracotta #C26849. Marker present but wrong colour.</t>
         </is>
       </c>
       <c r="J33" s="7" t="inlineStr"/>
@@ -23913,17 +24107,17 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-XC-086</t>
+          <t>PR-TC-XC-063</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>12. Locale, Number, Date &amp; Currency</t>
+          <t>9. Accessibility — WCAG 2.2 AA</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Phone numbers accept +91 with 10 digits, reject anything else</t>
+          <t>Form fields have associated labels (axe-core "label" rule passes)</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
@@ -23938,16 +24132,35 @@
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>• EP phone: enter 9876543210, +919876543210, 98765 43210, 123, 98765432101 (11), abc.</t>
+          <t>• Run axe-core on the EP form (via Playwright).</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr"/>
       <c r="I34" s="7" t="inlineStr">
         <is>
-          <t>Error: worker process exited unexpectedly (code=3221226505, signal=null)</t>
-        </is>
-      </c>
-      <c r="J34" s="7" t="inlineStr"/>
+          <t xml:space="preserve">Error: label violations: [{"id":"label","n":6}]
+expect(received).toEqual(expected) // deep equality
+- Expected  -   1
++ Received  + 457
+- Array []
++ Array [
++   Object {
++     "description": "Ensure every form element has a label",
++     "help": "Form elements must have labels",
++     "helpUrl": "https://dequeuniversity.com/rules/axe/4.11/label?application=playwright",
++     "id": "label",
++     "impact": "critical",
++     "nodes": Array [
++       Object {
++         "all": Array [],
++        </t>
+        </is>
+      </c>
+      <c r="J34" s="7" t="inlineStr">
+        <is>
+          <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\09-a11y-PR-TC-XC-063-·-for-17d03-ssociated-labels-axe-label--sm\test-failed-1.png</t>
+        </is>
+      </c>
       <c r="K34" s="7" t="inlineStr"/>
       <c r="L34" s="7" t="inlineStr">
         <is>
@@ -23956,6 +24169,131 @@
       </c>
       <c r="M34" s="7" t="inlineStr"/>
       <c r="N34" s="7" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>BUG-033</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-XC-064</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>9. Accessibility — WCAG 2.2 AA</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>Colour contrast meets WCAG AA</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>P1 — High</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>• Run axe-core's contrast check on EP detail, dashboard, framework form.</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr"/>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Error: contrast violations: [10]
+expect(received).toEqual(expected) // deep equality
+- Expected  -   1
++ Received  + 373
+- Array []
++ Array [
++   Object {
++     "description": "Ensure the contrast between foreground and background colors meets WCAG 2 AA minimum contrast ratio thresholds",
++     "help": "Elements must meet minimum color contrast ratio thresholds",
++     "helpUrl": "https://dequeuniversity.com/rules/axe/4.11/color-contrast?application=playwright",
++     "id": "color-contrast",
+</t>
+        </is>
+      </c>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\09-a11y-PR-TC-XC-064-·-col-8baa1-WCAG-AA-axe-color-contrast--sm\test-failed-1.png</t>
+        </is>
+      </c>
+      <c r="K35" s="7" t="inlineStr"/>
+      <c r="L35" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M35" s="7" t="inlineStr"/>
+      <c r="N35" s="7" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>BUG-034</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-XC-064b</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>(not in master — add as test case)</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-XC-064b · landscape colour contrast (WCAG AA)</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr"/>
+      <c r="G36" s="7" t="inlineStr"/>
+      <c r="H36" s="7" t="inlineStr"/>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>Error: landscape contrast nodes: 4
+expect(received).toEqual(expected) // deep equality
+- Expected  -   1
++ Received  + 163
+- Array []
++ Array [
++   Object {
++     "description": "Ensure the contrast between foreground and background colors meets WCAG 2 AA minimum contrast ratio thresholds",
++     "help": "Elements must meet minimum color contrast ratio thresholds",
++     "helpUrl": "https://dequeuniversity.com/rules/axe/4.11/color-contrast?application=playwright",
++     "id": "color-contrast"</t>
+        </is>
+      </c>
+      <c r="J36" s="7" t="inlineStr">
+        <is>
+          <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\09-a11y-PR-TC-XC-064b-·-landscape-colour-contrast-WCAG-AA--sm\test-failed-1.png</t>
+        </is>
+      </c>
+      <c r="K36" s="7" t="inlineStr"/>
+      <c r="L36" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M36" s="7" t="inlineStr"/>
+      <c r="N36" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -19531,9 +19531,9 @@
       </c>
       <c r="L281" s="7" t="inlineStr"/>
       <c r="M281" s="7" t="inlineStr"/>
-      <c r="N281" s="9" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="N281" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O281" s="7" t="inlineStr">
@@ -22187,7 +22187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N36"/>
+  <dimension ref="A1:N37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22293,7 +22293,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-FWC-BPC-002</t>
+          <t>PR-TC-DB-EPS-005</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -22303,7 +22303,7 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-FWC-BPC-002 · Business Plan Canvas header has no raw doctype / UUID</t>
+          <t>PR-TC-DB-EPS-005 · Sector→Business Basket dropdown cascades (basket filtered by sector)</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
@@ -22315,6 +22315,64 @@
       <c r="G3" s="7" t="inlineStr"/>
       <c r="H3" s="7" t="inlineStr"/>
       <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>Error: Basket dropdown for Sector="Food Processing" should list only its baskets (Agri-Food Products, Beverage, Tea), but also showed: Bamboo Crafts, Dairy &amp; Livestock, Handloom &amp; Textiles, Spices &amp; Herbs
+expect(received).toEqual(expected) // deep equality
+- Expected  - 1
++ Received  + 6
+- Array []
++ Array [
++   "Bamboo Crafts",
++   "Dairy &amp; Livestock",
++   "Handloom &amp; Textiles",
++   "Spices &amp; Herbs",
++ ]</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\19-dashboard-filters-PR-TC-78c23--basket-filtered-by-sector--sm\test-failed-1.png</t>
+        </is>
+      </c>
+      <c r="K3" s="7" t="inlineStr"/>
+      <c r="L3" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M3" s="7" t="inlineStr"/>
+      <c r="N3" s="7" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>BUG-002</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-FWC-BPC-002</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>(not in master — add as test case)</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-FWC-BPC-002 · Business Plan Canvas header has no raw doctype / UUID</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr"/>
+      <c r="G4" s="7" t="inlineStr"/>
+      <c r="H4" s="7" t="inlineStr"/>
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Business Plan Canvas: {"doctype-df-prefix":["DF BUSINESS"]}
 expect.toEqual // deep equality
@@ -22328,50 +22386,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J3" s="7" t="inlineStr">
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Bu-a8fd3-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K3" s="7" t="inlineStr"/>
-      <c r="L3" s="7" t="inlineStr">
+      <c r="K4" s="7" t="inlineStr"/>
+      <c r="L4" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M3" s="7" t="inlineStr"/>
-      <c r="N3" s="7" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>BUG-002</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="M4" s="7" t="inlineStr"/>
+      <c r="N4" s="7" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>BUG-003</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-BREG-002</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-BREG-002 · Business Registration header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr"/>
-      <c r="G4" s="7" t="inlineStr"/>
-      <c r="H4" s="7" t="inlineStr"/>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr"/>
+      <c r="G5" s="7" t="inlineStr"/>
+      <c r="H5" s="7" t="inlineStr"/>
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Business Registration: {"doctype-df-prefix":["DF BUSINESS"]}
 expect.toEqual // deep equality
@@ -22385,50 +22443,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J4" s="7" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Bu-6c730-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K4" s="7" t="inlineStr"/>
-      <c r="L4" s="7" t="inlineStr">
+      <c r="K5" s="7" t="inlineStr"/>
+      <c r="L5" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M4" s="7" t="inlineStr"/>
-      <c r="N4" s="7" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>BUG-003</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="M5" s="7" t="inlineStr"/>
+      <c r="N5" s="7" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>BUG-004</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-CA-002</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-CA-002 · Customer Analysis header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr"/>
-      <c r="G5" s="7" t="inlineStr"/>
-      <c r="H5" s="7" t="inlineStr"/>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr"/>
+      <c r="G6" s="7" t="inlineStr"/>
+      <c r="H6" s="7" t="inlineStr"/>
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Customer Analysis: {"doctype-df-prefix":["DF CUSTOMER"]}
 expect.toEqual // deep equality
@@ -22442,50 +22500,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J5" s="7" t="inlineStr">
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Cu-6ed58-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K5" s="7" t="inlineStr"/>
-      <c r="L5" s="7" t="inlineStr">
+      <c r="K6" s="7" t="inlineStr"/>
+      <c r="L6" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M5" s="7" t="inlineStr"/>
-      <c r="N5" s="7" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>BUG-004</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="M6" s="7" t="inlineStr"/>
+      <c r="N6" s="7" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>BUG-005</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-CB-002</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-CB-002 · Capacity Building header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr"/>
-      <c r="G6" s="7" t="inlineStr"/>
-      <c r="H6" s="7" t="inlineStr"/>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr"/>
+      <c r="G7" s="7" t="inlineStr"/>
+      <c r="H7" s="7" t="inlineStr"/>
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Capacity Building: {"doctype-df-prefix":["DF CAPACITY"]}
 expect.toEqual // deep equality
@@ -22499,50 +22557,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J6" s="7" t="inlineStr">
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Ca-83199-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K6" s="7" t="inlineStr"/>
-      <c r="L6" s="7" t="inlineStr">
+      <c r="K7" s="7" t="inlineStr"/>
+      <c r="L7" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M6" s="7" t="inlineStr"/>
-      <c r="N6" s="7" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>BUG-005</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="M7" s="7" t="inlineStr"/>
+      <c r="N7" s="7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>BUG-006</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-DL-002</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-DL-002 · Digital Literacy header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr"/>
-      <c r="G7" s="7" t="inlineStr"/>
-      <c r="H7" s="7" t="inlineStr"/>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr"/>
+      <c r="G8" s="7" t="inlineStr"/>
+      <c r="H8" s="7" t="inlineStr"/>
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Digital Literacy: {"doctype-df-prefix":["DF DIGITAL"]}
 expect.toEqual // deep equality
@@ -22556,50 +22614,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J7" s="7" t="inlineStr">
+      <c r="J8" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Di-845ef-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K7" s="7" t="inlineStr"/>
-      <c r="L7" s="7" t="inlineStr">
+      <c r="K8" s="7" t="inlineStr"/>
+      <c r="L8" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M7" s="7" t="inlineStr"/>
-      <c r="N7" s="7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>BUG-006</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="M8" s="7" t="inlineStr"/>
+      <c r="N8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>BUG-007</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-INFR-002</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-INFR-002 · Infrastructure (BE/EE/CE) header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr"/>
-      <c r="G8" s="7" t="inlineStr"/>
-      <c r="H8" s="7" t="inlineStr"/>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr"/>
+      <c r="G9" s="7" t="inlineStr"/>
+      <c r="H9" s="7" t="inlineStr"/>
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Infrastructure: {"doctype-df-prefix":["DF INFRASTRUCTURE"]}
 expect.toEqual // deep equality
@@ -22613,50 +22671,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J8" s="7" t="inlineStr">
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-In-3328d-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K8" s="7" t="inlineStr"/>
-      <c r="L8" s="7" t="inlineStr">
+      <c r="K9" s="7" t="inlineStr"/>
+      <c r="L9" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M8" s="7" t="inlineStr"/>
-      <c r="N8" s="7" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>BUG-007</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="M9" s="7" t="inlineStr"/>
+      <c r="N9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>BUG-008</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-LABL-002</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-LABL-002 · Marketing Label header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr"/>
-      <c r="G9" s="7" t="inlineStr"/>
-      <c r="H9" s="7" t="inlineStr"/>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr"/>
+      <c r="G10" s="7" t="inlineStr"/>
+      <c r="H10" s="7" t="inlineStr"/>
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Marketing Label: {"doctype-df-prefix":["DF MARKETING"]}
 expect.toEqual // deep equality
@@ -22670,50 +22728,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J9" s="7" t="inlineStr">
+      <c r="J10" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Ma-11834-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K9" s="7" t="inlineStr"/>
-      <c r="L9" s="7" t="inlineStr">
+      <c r="K10" s="7" t="inlineStr"/>
+      <c r="L10" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M9" s="7" t="inlineStr"/>
-      <c r="N9" s="7" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>BUG-008</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="M10" s="7" t="inlineStr"/>
+      <c r="N10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>BUG-009</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-ML-002</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-ML-002 · Market Linkage header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr"/>
-      <c r="G10" s="7" t="inlineStr"/>
-      <c r="H10" s="7" t="inlineStr"/>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr"/>
+      <c r="G11" s="7" t="inlineStr"/>
+      <c r="H11" s="7" t="inlineStr"/>
+      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Market Linkage: {"doctype-df-prefix":["DF MARKET"]}
 expect.toEqual // deep equality
@@ -22727,50 +22785,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J10" s="7" t="inlineStr">
+      <c r="J11" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Ma-22f69-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K10" s="7" t="inlineStr"/>
-      <c r="L10" s="7" t="inlineStr">
+      <c r="K11" s="7" t="inlineStr"/>
+      <c r="L11" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M10" s="7" t="inlineStr"/>
-      <c r="N10" s="7" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>BUG-009</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="M11" s="7" t="inlineStr"/>
+      <c r="N11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>BUG-010</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-MR-002</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-MR-002 · Market Research header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr"/>
-      <c r="G11" s="7" t="inlineStr"/>
-      <c r="H11" s="7" t="inlineStr"/>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr"/>
+      <c r="G12" s="7" t="inlineStr"/>
+      <c r="H12" s="7" t="inlineStr"/>
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Market Research: {"doctype-df-prefix":["DF MARKET"]}
 expect.toEqual // deep equality
@@ -22784,50 +22842,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J11" s="7" t="inlineStr">
+      <c r="J12" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Ma-6eb23-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K11" s="7" t="inlineStr"/>
-      <c r="L11" s="7" t="inlineStr">
+      <c r="K12" s="7" t="inlineStr"/>
+      <c r="L12" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M11" s="7" t="inlineStr"/>
-      <c r="N11" s="7" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>BUG-010</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="M12" s="7" t="inlineStr"/>
+      <c r="N12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>BUG-011</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PCMP-002</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PCMP-002 · Product Compliance header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr"/>
-      <c r="G12" s="7" t="inlineStr"/>
-      <c r="H12" s="7" t="inlineStr"/>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="F13" s="7" t="inlineStr"/>
+      <c r="G13" s="7" t="inlineStr"/>
+      <c r="H13" s="7" t="inlineStr"/>
+      <c r="I13" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Product Compliance: {"doctype-df-prefix":["DF PRODUCT"]}
 expect.toEqual // deep equality
@@ -22841,50 +22899,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J12" s="7" t="inlineStr">
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Pr-be46f-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K12" s="7" t="inlineStr"/>
-      <c r="L12" s="7" t="inlineStr">
+      <c r="K13" s="7" t="inlineStr"/>
+      <c r="L13" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M12" s="7" t="inlineStr"/>
-      <c r="N12" s="7" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>BUG-011</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="M13" s="7" t="inlineStr"/>
+      <c r="N13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>BUG-012</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PROM-002</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PROM-002 · Promotional Marketing header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr"/>
-      <c r="G13" s="7" t="inlineStr"/>
-      <c r="H13" s="7" t="inlineStr"/>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr"/>
+      <c r="G14" s="7" t="inlineStr"/>
+      <c r="H14" s="7" t="inlineStr"/>
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Promotional Marketing: {"doctype-df-prefix":["DF PROMOTIONAL"]}
 expect.toEqual // deep equality
@@ -22898,50 +22956,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J13" s="7" t="inlineStr">
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Pr-d8d12-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K13" s="7" t="inlineStr"/>
-      <c r="L13" s="7" t="inlineStr">
+      <c r="K14" s="7" t="inlineStr"/>
+      <c r="L14" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M13" s="7" t="inlineStr"/>
-      <c r="N13" s="7" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>BUG-012</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="M14" s="7" t="inlineStr"/>
+      <c r="N14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>BUG-013</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PROT-002</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PROT-002 · Product Prototyping header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr"/>
-      <c r="G14" s="7" t="inlineStr"/>
-      <c r="H14" s="7" t="inlineStr"/>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr"/>
+      <c r="G15" s="7" t="inlineStr"/>
+      <c r="H15" s="7" t="inlineStr"/>
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Product Prototyping: {"doctype-df-prefix":["DF PRODUCT"]}
 expect.toEqual // deep equality
@@ -22955,50 +23013,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J14" s="7" t="inlineStr">
+      <c r="J15" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Pr-1120e-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K14" s="7" t="inlineStr"/>
-      <c r="L14" s="7" t="inlineStr">
+      <c r="K15" s="7" t="inlineStr"/>
+      <c r="L15" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M14" s="7" t="inlineStr"/>
-      <c r="N14" s="7" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>BUG-013</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="M15" s="7" t="inlineStr"/>
+      <c r="N15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>BUG-014</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PTCH-002</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PTCH-002 · Pitch Deck header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr"/>
-      <c r="G15" s="7" t="inlineStr"/>
-      <c r="H15" s="7" t="inlineStr"/>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="F16" s="7" t="inlineStr"/>
+      <c r="G16" s="7" t="inlineStr"/>
+      <c r="H16" s="7" t="inlineStr"/>
+      <c r="I16" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Pitch Deck: {"doctype-df-prefix":["DF PITCH"]}
 expect.toEqual // deep equality
@@ -23012,50 +23070,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J15" s="7" t="inlineStr">
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Pi-fefd5-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K15" s="7" t="inlineStr"/>
-      <c r="L15" s="7" t="inlineStr">
+      <c r="K16" s="7" t="inlineStr"/>
+      <c r="L16" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M15" s="7" t="inlineStr"/>
-      <c r="N15" s="7" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>BUG-014</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="M16" s="7" t="inlineStr"/>
+      <c r="N16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>BUG-015</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PTST-002</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PTST-002 · Product Testing header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr"/>
-      <c r="G16" s="7" t="inlineStr"/>
-      <c r="H16" s="7" t="inlineStr"/>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="F17" s="7" t="inlineStr"/>
+      <c r="G17" s="7" t="inlineStr"/>
+      <c r="H17" s="7" t="inlineStr"/>
+      <c r="I17" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Product Testing: {"doctype-df-prefix":["DF PRODUCT"]}
 expect.toEqual // deep equality
@@ -23069,50 +23127,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J16" s="7" t="inlineStr">
+      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Pr-3e912-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K16" s="7" t="inlineStr"/>
-      <c r="L16" s="7" t="inlineStr">
+      <c r="K17" s="7" t="inlineStr"/>
+      <c r="L17" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M16" s="7" t="inlineStr"/>
-      <c r="N16" s="7" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>BUG-015</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="M17" s="7" t="inlineStr"/>
+      <c r="N17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>BUG-016</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-QC-002</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-QC-002 · Quality Control header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E18" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr"/>
-      <c r="G17" s="7" t="inlineStr"/>
-      <c r="H17" s="7" t="inlineStr"/>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="F18" s="7" t="inlineStr"/>
+      <c r="G18" s="7" t="inlineStr"/>
+      <c r="H18" s="7" t="inlineStr"/>
+      <c r="I18" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Quality Control: {"doctype-df-prefix":["DF QUALITY"]}
 expect.toEqual // deep equality
@@ -23126,50 +23184,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J17" s="7" t="inlineStr">
+      <c r="J18" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Qu-ae31c-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K17" s="7" t="inlineStr"/>
-      <c r="L17" s="7" t="inlineStr">
+      <c r="K18" s="7" t="inlineStr"/>
+      <c r="L18" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M17" s="7" t="inlineStr"/>
-      <c r="N17" s="7" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>BUG-016</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="M18" s="7" t="inlineStr"/>
+      <c r="N18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>BUG-017</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-SCHM-002</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-SCHM-002 · Schemes &amp; Funding header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr"/>
-      <c r="G18" s="7" t="inlineStr"/>
-      <c r="H18" s="7" t="inlineStr"/>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr"/>
+      <c r="G19" s="7" t="inlineStr"/>
+      <c r="H19" s="7" t="inlineStr"/>
+      <c r="I19" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Schemes &amp; Funding: {"doctype-df-prefix":["DF SCHEMES"]}
 expect.toEqual // deep equality
@@ -23183,50 +23241,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J18" s="7" t="inlineStr">
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Sc-67cb2-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K18" s="7" t="inlineStr"/>
-      <c r="L18" s="7" t="inlineStr">
+      <c r="K19" s="7" t="inlineStr"/>
+      <c r="L19" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M18" s="7" t="inlineStr"/>
-      <c r="N18" s="7" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>BUG-017</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="M19" s="7" t="inlineStr"/>
+      <c r="N19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>BUG-018</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-STD-002</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-STD-002 · Standardization header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr"/>
-      <c r="G19" s="7" t="inlineStr"/>
-      <c r="H19" s="7" t="inlineStr"/>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="F20" s="7" t="inlineStr"/>
+      <c r="G20" s="7" t="inlineStr"/>
+      <c r="H20" s="7" t="inlineStr"/>
+      <c r="I20" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Standardization: {"doctype-df-prefix":["DF STANDARDIZATION"]}
 expect.toEqual // deep equality
@@ -23240,50 +23298,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J19" s="7" t="inlineStr">
+      <c r="J20" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-St-b8b93-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K19" s="7" t="inlineStr"/>
-      <c r="L19" s="7" t="inlineStr">
+      <c r="K20" s="7" t="inlineStr"/>
+      <c r="L20" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M19" s="7" t="inlineStr"/>
-      <c r="N19" s="7" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>BUG-018</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="M20" s="7" t="inlineStr"/>
+      <c r="N20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>BUG-019</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-UP-002</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-UP-002 · Unit Pricing header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr"/>
-      <c r="G20" s="7" t="inlineStr"/>
-      <c r="H20" s="7" t="inlineStr"/>
-      <c r="I20" s="7" t="inlineStr">
+      <c r="F21" s="7" t="inlineStr"/>
+      <c r="G21" s="7" t="inlineStr"/>
+      <c r="H21" s="7" t="inlineStr"/>
+      <c r="I21" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Unit Pricing: {"doctype-df-prefix":["DF UNIT"]}
 expect.toEqual // deep equality
@@ -23297,58 +23355,58 @@
 + }</t>
         </is>
       </c>
-      <c r="J20" s="7" t="inlineStr">
+      <c r="J21" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Un-0c652-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K20" s="7" t="inlineStr"/>
-      <c r="L20" s="7" t="inlineStr">
+      <c r="K21" s="7" t="inlineStr"/>
+      <c r="L21" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M20" s="7" t="inlineStr"/>
-      <c r="N20" s="7" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>BUG-019</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="M21" s="7" t="inlineStr"/>
+      <c r="N21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>BUG-020</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>PR-TC-MS-008</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>14. Masters &amp; Reference Data</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>Cohort end date must be after start date</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr">
+      <c r="F22" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G21" s="7" t="inlineStr">
+      <c r="G22" s="7" t="inlineStr">
         <is>
           <t>• Start = 01-Apr-2026, End = 31-Mar-2025.</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr"/>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="H22" s="7" t="inlineStr"/>
+      <c r="I22" s="7" t="inlineStr">
         <is>
           <t>Error: end-before-start cohort should be rejected
 expect(received).toBeGreaterThanOrEqual(expected)
@@ -23356,59 +23414,59 @@
 Received:    200</t>
         </is>
       </c>
-      <c r="J21" s="7" t="inlineStr"/>
-      <c r="K21" s="7" t="inlineStr"/>
-      <c r="L21" s="7" t="inlineStr">
+      <c r="J22" s="7" t="inlineStr"/>
+      <c r="K22" s="7" t="inlineStr"/>
+      <c r="L22" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M21" s="7" t="inlineStr"/>
-      <c r="N21" s="7" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>BUG-020</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="M22" s="7" t="inlineStr"/>
+      <c r="N22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>BUG-021</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>PR-TC-MS-011</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>14. Masters &amp; Reference Data</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>Seed import: 351 rows from "Final PRIME Rural Task Dropdowns Master.xlsx"</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr">
+      <c r="F23" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G22" s="7" t="inlineStr">
+      <c r="G23" s="7" t="inlineStr">
         <is>
           <t>• Run the seed migration script (or use bulk import) using the canonical xlsx.
 • Verify count = 351.</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="H23" s="7" t="inlineStr">
         <is>
           <t>351 Framework Task Master records exist. Each has: module, framework, task_no, task_name, description, phase. Em-dash phase rows have phase = "Other". Logistic Service has its "Other" row added (was missing in the xlsx).</t>
         </is>
       </c>
-      <c r="I22" s="7" t="inlineStr">
+      <c r="I23" s="7" t="inlineStr">
         <is>
           <t>Error: Framework Task Master doctype should exist
 expect(received).toBe(expected) // Object.is equality
@@ -23416,58 +23474,58 @@
 Received: 404</t>
         </is>
       </c>
-      <c r="J22" s="7" t="inlineStr"/>
-      <c r="K22" s="7" t="inlineStr">
+      <c r="J23" s="7" t="inlineStr"/>
+      <c r="K23" s="7" t="inlineStr">
         <is>
           <t>BRD PR-XC-002b.</t>
         </is>
       </c>
-      <c r="L22" s="7" t="inlineStr">
+      <c r="L23" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M22" s="7" t="inlineStr"/>
-      <c r="N22" s="7" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>BUG-021</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="M23" s="7" t="inlineStr"/>
+      <c r="N23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>BUG-022</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>PR-TC-MS-015</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>14. Masters &amp; Reference Data</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>Document types: Aadhaar, PAN, EPIC, Bank Passbook, Photo, Other</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F23" s="7" t="inlineStr">
+      <c r="F24" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G23" s="7" t="inlineStr">
+      <c r="G24" s="7" t="inlineStr">
         <is>
           <t>• Masters → Document Master → list.</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr"/>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="H24" s="7" t="inlineStr"/>
+      <c r="I24" s="7" t="inlineStr">
         <is>
           <t>Error: expected the standard document types (Aadhaar/PAN/EPIC/Bank/Photo/...)
 expect(received).toBeGreaterThanOrEqual(expected)
@@ -23475,58 +23533,58 @@
 Received:    5</t>
         </is>
       </c>
-      <c r="J23" s="7" t="inlineStr"/>
-      <c r="K23" s="7" t="inlineStr"/>
-      <c r="L23" s="7" t="inlineStr">
+      <c r="J24" s="7" t="inlineStr"/>
+      <c r="K24" s="7" t="inlineStr"/>
+      <c r="L24" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M23" s="7" t="inlineStr"/>
-      <c r="N23" s="7" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>BUG-022</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="M24" s="7" t="inlineStr"/>
+      <c r="N24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>BUG-023</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>PR-TC-MS-020</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>14. Masters &amp; Reference Data</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>19 schemes pre-seeded (MOVCDNER, CGTMSE, NEHHDC, PGS-India Organic, etc.)</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr">
+      <c r="F25" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G24" s="7" t="inlineStr">
+      <c r="G25" s="7" t="inlineStr">
         <is>
           <t>• Open Scheme Master list. Count rows.</t>
         </is>
       </c>
-      <c r="H24" s="7" t="inlineStr">
+      <c r="H25" s="7" t="inlineStr">
         <is>
           <t>19 schemes present per BRD m-schemes. Each has: name, type (Grant / Loan / Subsidy / Certification), eligibility, min/max amount, applicable sectors, interest rate (if loan).</t>
         </is>
       </c>
-      <c r="I24" s="7" t="inlineStr">
+      <c r="I25" s="7" t="inlineStr">
         <is>
           <t>Error: BRD m-schemes expects 19 pre-seeded schemes
 expect(received).toBeGreaterThanOrEqual(expected)
@@ -23534,104 +23592,104 @@
 Received:    3</t>
         </is>
       </c>
-      <c r="J24" s="7" t="inlineStr"/>
-      <c r="K24" s="7" t="inlineStr">
+      <c r="J25" s="7" t="inlineStr"/>
+      <c r="K25" s="7" t="inlineStr">
         <is>
           <t>BRD m-schemes.</t>
         </is>
       </c>
-      <c r="L24" s="7" t="inlineStr">
+      <c r="L25" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M24" s="7" t="inlineStr"/>
-      <c r="N24" s="7" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>BUG-023</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="M25" s="7" t="inlineStr"/>
+      <c r="N25" s="7" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>BUG-024</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>PR-TC-SEC-005</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>23. Security — OWASP &amp; Beyond</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>Content-Security-Policy header set, restricts inline scripts</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="E26" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F25" s="7" t="inlineStr">
+      <c r="F26" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G25" s="7" t="inlineStr">
+      <c r="G26" s="7" t="inlineStr">
         <is>
           <t>• Inspect response headers on /app/.</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr"/>
-      <c r="I25" s="7" t="inlineStr">
+      <c r="H26" s="7" t="inlineStr"/>
+      <c r="I26" s="7" t="inlineStr">
         <is>
           <t>Error: CSP header should be set
 expect(received).toBeTruthy()
 Received: undefined</t>
         </is>
       </c>
-      <c r="J25" s="7" t="inlineStr"/>
-      <c r="K25" s="7" t="inlineStr"/>
-      <c r="L25" s="7" t="inlineStr">
+      <c r="J26" s="7" t="inlineStr"/>
+      <c r="K26" s="7" t="inlineStr"/>
+      <c r="L26" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M25" s="7" t="inlineStr"/>
-      <c r="N25" s="7" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>BUG-024</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="M26" s="7" t="inlineStr"/>
+      <c r="N26" s="7" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>BUG-025</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>PR-TC-UI-LEAK-001</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>PR-TC-UI-LEAK-001 · EP profile shows no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F26" s="7" t="inlineStr"/>
-      <c r="G26" s="7" t="inlineStr"/>
-      <c r="H26" s="7" t="inlineStr"/>
-      <c r="I26" s="7" t="inlineStr">
+      <c r="F27" s="7" t="inlineStr"/>
+      <c r="G27" s="7" t="inlineStr"/>
+      <c r="H27" s="7" t="inlineStr"/>
+      <c r="I27" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on EP profile: {"doctype-df-prefix":["DF PROGRESS"]}
 expect.toEqual // deep equality
@@ -23645,50 +23703,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J26" s="7" t="inlineStr">
+      <c r="J27" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\08-ui-no-backend-leak-PR-T-d694f-e-shows-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K26" s="7" t="inlineStr"/>
-      <c r="L26" s="7" t="inlineStr">
+      <c r="K27" s="7" t="inlineStr"/>
+      <c r="L27" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M26" s="7" t="inlineStr"/>
-      <c r="N26" s="7" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>BUG-025</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="M27" s="7" t="inlineStr"/>
+      <c r="N27" s="7" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>BUG-026</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>PR-TC-UI-LEAK-002</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>PR-TC-UI-LEAK-002 · new EP form header is a friendly label, not the raw doctype</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr"/>
-      <c r="G27" s="7" t="inlineStr"/>
-      <c r="H27" s="7" t="inlineStr"/>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="F28" s="7" t="inlineStr"/>
+      <c r="G28" s="7" t="inlineStr"/>
+      <c r="H28" s="7" t="inlineStr"/>
+      <c r="I28" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on new EP form: {"enterprenur-internal":["Enterprenur"]}
 expect.toEqual // deep equality
@@ -23702,126 +23760,126 @@
 + }</t>
         </is>
       </c>
-      <c r="J27" s="7" t="inlineStr">
+      <c r="J28" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\08-ui-no-backend-leak-PR-T-215c4-y-label-not-the-raw-doctype-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K27" s="7" t="inlineStr"/>
-      <c r="L27" s="7" t="inlineStr">
+      <c r="K28" s="7" t="inlineStr"/>
+      <c r="L28" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M27" s="7" t="inlineStr"/>
-      <c r="N27" s="7" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>BUG-026</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="M28" s="7" t="inlineStr"/>
+      <c r="N28" s="7" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>BUG-027</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-003</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>4. Application Entry &amp; Routing</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>Deep link to a protected page while logged out preserves the intent</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr">
+      <c r="F29" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G28" s="7" t="inlineStr">
+      <c r="G29" s="7" t="inlineStr">
         <is>
           <t>• Open https://stgprime-rural.dhwaniris.in/app/enterprenur-profile/EP-001 directly.
 • Login redirect fires.
 • Complete login as a user permitted to see that record.</t>
         </is>
       </c>
-      <c r="H28" s="7" t="inlineStr">
+      <c r="H29" s="7" t="inlineStr">
         <is>
           <t>After successful login, user is redirected to the originally requested URL (the EP detail page), not the default landing page. URL parameter (typically redirect-to or next) is preserved through the auth flow.</t>
         </is>
       </c>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="I29" s="7" t="inlineStr">
         <is>
           <t>Error: expect(received).toMatch(expected)
 Expected pattern: /redirect|next|to=/i
 Received string:  "https://stgprime-rural.dhwaniris.in/primerural/login"</t>
         </is>
       </c>
-      <c r="J28" s="7" t="inlineStr">
+      <c r="J29" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\04-entry-PR-TC-XC-ENTRY-·--e9661-t-preserves-redirect-intent-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K28" s="7" t="inlineStr">
+      <c r="K29" s="7" t="inlineStr">
         <is>
           <t>BRD: PR-OV-001 (Auth)</t>
         </is>
       </c>
-      <c r="L28" s="7" t="inlineStr">
+      <c r="L29" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M28" s="7" t="inlineStr"/>
-      <c r="N28" s="7" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>BUG-027</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="M29" s="7" t="inlineStr"/>
+      <c r="N29" s="7" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>BUG-028</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-023</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>6. Responsive Layout &amp; Screen Sizes</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>1024×768 (tablet landscape / iPad / Surface): sidebar collapses to icon rail</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="E30" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr">
+      <c r="F30" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G29" s="7" t="inlineStr">
+      <c r="G30" s="7" t="inlineStr">
         <is>
           <t>• Resize to 1024×768.</t>
         </is>
       </c>
-      <c r="H29" s="7" t="inlineStr"/>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="H30" s="7" t="inlineStr"/>
+      <c r="I30" s="7" t="inlineStr">
         <is>
           <t>Error: at 1024px the sidebar should collapse to an icon rail; width=240
 expect(received).toBeLessThanOrEqual(expected)
@@ -23829,63 +23887,63 @@
 Received:    240</t>
         </is>
       </c>
-      <c r="J29" s="7" t="inlineStr">
+      <c r="J30" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\06-08-10-nonfunctional-PR--f1c18-ollapses-to-icon-rail-64px--sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K29" s="7" t="inlineStr"/>
-      <c r="L29" s="7" t="inlineStr">
+      <c r="K30" s="7" t="inlineStr"/>
+      <c r="L30" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M29" s="7" t="inlineStr"/>
-      <c r="N29" s="7" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>BUG-028</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="M30" s="7" t="inlineStr"/>
+      <c r="N30" s="7" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>BUG-029</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-032</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>7. Login &amp; Session</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>Wrong password shows a clear error and does NOT reveal whether the email exists</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="E31" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr">
+      <c r="F31" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G30" s="7" t="inlineStr">
+      <c r="G31" s="7" t="inlineStr">
         <is>
           <t>• Login form: enter a valid email but wrong password.
 • Submit.</t>
         </is>
       </c>
-      <c r="H30" s="7" t="inlineStr">
+      <c r="H31" s="7" t="inlineStr">
         <is>
           <t>Error displays inline above the form: "Invalid email or password." — generic enough that an attacker cannot enumerate valid emails. The password field is cleared; the email field is preserved. No 500. No password ever echoed back into the field.</t>
         </is>
       </c>
-      <c r="I30" s="7" t="inlineStr">
+      <c r="I31" s="7" t="inlineStr">
         <is>
           <t>Error: login error must be friendly text, not a raw exception class
 expect(locator).not.toContainText(expected) failed
@@ -23899,62 +23957,62 @@
     23 × locator resolved to &lt;div role="alert" class="bg-d</t>
         </is>
       </c>
-      <c r="J30" s="7" t="inlineStr">
+      <c r="J31" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\07-auth-PR-TC-XC-AUTH-·-Em-429a0-neric-error-no-enumeration--sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K30" s="7" t="inlineStr">
+      <c r="K31" s="7" t="inlineStr">
         <is>
           <t>OWASP A07 Auth Failures (do not leak account existence).</t>
         </is>
       </c>
-      <c r="L30" s="7" t="inlineStr">
+      <c r="L31" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M30" s="7" t="inlineStr"/>
-      <c r="N30" s="7" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>BUG-029</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="M31" s="7" t="inlineStr"/>
+      <c r="N31" s="7" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>BUG-030</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-033</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>7. Login &amp; Session</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>Non-existent email shows the same generic error as wrong password</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="E32" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr">
+      <c r="F32" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G31" s="7" t="inlineStr">
+      <c r="G32" s="7" t="inlineStr">
         <is>
           <t>• Submit with email not-a-real-user@example.com and any password.</t>
         </is>
       </c>
-      <c r="H31" s="7" t="inlineStr"/>
-      <c r="I31" s="7" t="inlineStr">
+      <c r="H32" s="7" t="inlineStr"/>
+      <c r="I32" s="7" t="inlineStr">
         <is>
           <t>Error: login error must be friendly text, not a raw exception class
 expect(locator).not.toContainText(expected) failed
@@ -23968,129 +24026,77 @@
     23 × locator resolved to &lt;div role="alert" class="bg-d</t>
         </is>
       </c>
-      <c r="J31" s="7" t="inlineStr">
+      <c r="J32" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\07-auth-PR-TC-XC-AUTH-·-Em-a7adf-ows-identical-generic-error-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K31" s="7" t="inlineStr"/>
-      <c r="L31" s="7" t="inlineStr">
+      <c r="K32" s="7" t="inlineStr"/>
+      <c r="L32" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M31" s="7" t="inlineStr"/>
-      <c r="N31" s="7" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>BUG-030</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="M32" s="7" t="inlineStr"/>
+      <c r="N32" s="7" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>BUG-031</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-052</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>8. UI / UX Rules — Monsoon Court Compliance</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D33" s="7" t="inlineStr">
         <is>
           <t>No green and no yellow appear anywhere in the UI</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
+      <c r="E33" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F32" s="7" t="inlineStr">
+      <c r="F33" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G32" s="7" t="inlineStr">
+      <c r="G33" s="7" t="inlineStr">
         <is>
           <t>• Visually scan every page for green / yellow elements.
 • Search the rendered CSS for any colour matching green, yellow, #2ecc71, #f1c40f, similar hexes.</t>
         </is>
       </c>
-      <c r="H32" s="7" t="inlineStr">
+      <c r="H33" s="7" t="inlineStr">
         <is>
           <t>Zero green elements. Success states use teal #0E4D4E. Zero yellow elements. Warning states use terracotta #C26849.</t>
         </is>
       </c>
-      <c r="I32" s="7" t="inlineStr">
+      <c r="I33" s="7" t="inlineStr">
         <is>
           <t>Active Entrepreneurs KPI shows a GREEN check rgb(63,107,58) (hue 114). Monsoon Court forbids green — success must be teal #0E4D4E.</t>
         </is>
       </c>
-      <c r="J32" s="7" t="inlineStr">
+      <c r="J33" s="7" t="inlineStr">
         <is>
           <t>.playwright-mcp/bug-xc052-green-kpi.png</t>
         </is>
       </c>
-      <c r="K32" s="7" t="inlineStr">
+      <c r="K33" s="7" t="inlineStr">
         <is>
           <t>Monsoon Court §2.7 (brand non-negotiables).</t>
         </is>
       </c>
-      <c r="L32" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="M32" s="7" t="inlineStr"/>
-      <c r="N32" s="7" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>BUG-031</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>PR-TC-XC-054</t>
-        </is>
-      </c>
-      <c r="C33" s="7" t="inlineStr">
-        <is>
-          <t>8. UI / UX Rules — Monsoon Court Compliance</t>
-        </is>
-      </c>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>Required-field marker is a terracotta asterisk, not "(required)" text</t>
-        </is>
-      </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F33" s="7" t="inlineStr">
-        <is>
-          <t>P1 — High</t>
-        </is>
-      </c>
-      <c r="G33" s="7" t="inlineStr">
-        <is>
-          <t>• Open the EP form. Find a required field (e.g. Entrepreneur Name).</t>
-        </is>
-      </c>
-      <c r="H33" s="7" t="inlineStr"/>
-      <c r="I33" s="7" t="inlineStr">
-        <is>
-          <t>Asterisk on the name label is taupe rgb(107,99,89) (inherits label ink-soft), NOT terracotta #C26849. Marker present but wrong colour.</t>
-        </is>
-      </c>
-      <c r="J33" s="7" t="inlineStr"/>
-      <c r="K33" s="7" t="inlineStr"/>
       <c r="L33" s="7" t="inlineStr">
         <is>
           <t>Open</t>
@@ -24107,17 +24113,17 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-XC-063</t>
+          <t>PR-TC-XC-054</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>9. Accessibility — WCAG 2.2 AA</t>
+          <t>8. UI / UX Rules — Monsoon Court Compliance</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Form fields have associated labels (axe-core "label" rule passes)</t>
+          <t>Required-field marker is a terracotta asterisk, not "(required)" text</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
@@ -24132,11 +24138,63 @@
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>• Run axe-core on the EP form (via Playwright).</t>
+          <t>• Open the EP form. Find a required field (e.g. Entrepreneur Name).</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr"/>
       <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>Asterisk on the name label is taupe rgb(107,99,89) (inherits label ink-soft), NOT terracotta #C26849. Marker present but wrong colour.</t>
+        </is>
+      </c>
+      <c r="J34" s="7" t="inlineStr"/>
+      <c r="K34" s="7" t="inlineStr"/>
+      <c r="L34" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M34" s="7" t="inlineStr"/>
+      <c r="N34" s="7" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>BUG-033</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-XC-063</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>9. Accessibility — WCAG 2.2 AA</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>Form fields have associated labels (axe-core "label" rule passes)</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>P1 — High</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>• Run axe-core on the EP form (via Playwright).</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr"/>
+      <c r="I35" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: label violations: [{"id":"label","n":6}]
 expect(received).toEqual(expected) // deep equality
@@ -24156,58 +24214,58 @@
 +        </t>
         </is>
       </c>
-      <c r="J34" s="7" t="inlineStr">
+      <c r="J35" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\09-a11y-PR-TC-XC-063-·-for-17d03-ssociated-labels-axe-label--sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K34" s="7" t="inlineStr"/>
-      <c r="L34" s="7" t="inlineStr">
+      <c r="K35" s="7" t="inlineStr"/>
+      <c r="L35" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M34" s="7" t="inlineStr"/>
-      <c r="N34" s="7" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>BUG-033</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="M35" s="7" t="inlineStr"/>
+      <c r="N35" s="7" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>BUG-034</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-064</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>9. Accessibility — WCAG 2.2 AA</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>Colour contrast meets WCAG AA</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F35" s="7" t="inlineStr">
+      <c r="F36" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G35" s="7" t="inlineStr">
+      <c r="G36" s="7" t="inlineStr">
         <is>
           <t>• Run axe-core's contrast check on EP detail, dashboard, framework form.</t>
         </is>
       </c>
-      <c r="H35" s="7" t="inlineStr"/>
-      <c r="I35" s="7" t="inlineStr">
+      <c r="H36" s="7" t="inlineStr"/>
+      <c r="I36" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: contrast violations: [10]
 expect(received).toEqual(expected) // deep equality
@@ -24223,50 +24281,50 @@
 </t>
         </is>
       </c>
-      <c r="J35" s="7" t="inlineStr">
+      <c r="J36" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\09-a11y-PR-TC-XC-064-·-col-8baa1-WCAG-AA-axe-color-contrast--sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K35" s="7" t="inlineStr"/>
-      <c r="L35" s="7" t="inlineStr">
+      <c r="K36" s="7" t="inlineStr"/>
+      <c r="L36" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M35" s="7" t="inlineStr"/>
-      <c r="N35" s="7" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>BUG-034</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="M36" s="7" t="inlineStr"/>
+      <c r="N36" s="7" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>BUG-035</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-064b</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-064b · landscape colour contrast (WCAG AA)</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F36" s="7" t="inlineStr"/>
-      <c r="G36" s="7" t="inlineStr"/>
-      <c r="H36" s="7" t="inlineStr"/>
-      <c r="I36" s="7" t="inlineStr">
+      <c r="F37" s="7" t="inlineStr"/>
+      <c r="G37" s="7" t="inlineStr"/>
+      <c r="H37" s="7" t="inlineStr"/>
+      <c r="I37" s="7" t="inlineStr">
         <is>
           <t>Error: landscape contrast nodes: 4
 expect(received).toEqual(expected) // deep equality
@@ -24281,19 +24339,19 @@
 +     "id": "color-contrast"</t>
         </is>
       </c>
-      <c r="J36" s="7" t="inlineStr">
+      <c r="J37" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\09-a11y-PR-TC-XC-064b-·-landscape-colour-contrast-WCAG-AA--sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K36" s="7" t="inlineStr"/>
-      <c r="L36" s="7" t="inlineStr">
+      <c r="K37" s="7" t="inlineStr"/>
+      <c r="L37" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M36" s="7" t="inlineStr"/>
-      <c r="N36" s="7" t="inlineStr"/>
+      <c r="M37" s="7" t="inlineStr"/>
+      <c r="N37" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -13313,17 +13313,23 @@
       </c>
       <c r="L185" s="7" t="inlineStr"/>
       <c r="M185" s="7" t="inlineStr"/>
-      <c r="N185" s="9" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="N185" s="12" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
       <c r="O185" s="7" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="P185" s="8" t="inlineStr"/>
+          <t>Error: page.goto: net::ERR_NO_BUFFER_SPACE at https://stgprime-rural.dhwaniris.in/app/enterprenur-profile/EP-00006
+Call log:
+  - navigating to "https://stgprime-rural.dhwaniris.in/app/enterprenur-profile/EP-00006", waiting until "load"</t>
+        </is>
+      </c>
+      <c r="P185" s="8" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
       <c r="Q185" s="7" t="inlineStr"/>
     </row>
     <row r="186">
@@ -22187,7 +22193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N37"/>
+  <dimension ref="A1:N41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22351,7 +22357,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-FWC-BPC-002</t>
+          <t>PR-TC-DB-EPS-006</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -22361,7 +22367,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-FWC-BPC-002 · Business Plan Canvas header has no raw doctype / UUID</t>
+          <t>PR-TC-DB-EPS-006 · District→Block cascade filter is available on the dashboard</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -22373,6 +22379,210 @@
       <c r="G4" s="7" t="inlineStr"/>
       <c r="H4" s="7" t="inlineStr"/>
       <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>Error: dashboard should expose a District (and cascading Block) filter
+expect(received).toBe(expected) // Object.is equality
+Expected: true
+Received: false</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\19-dashboard-filters-PR-TC-dcc9e--available-on-the-dashboard-sm\test-failed-1.png</t>
+        </is>
+      </c>
+      <c r="K4" s="7" t="inlineStr"/>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M4" s="7" t="inlineStr"/>
+      <c r="N4" s="7" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>BUG-003</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-DB-NAV-001</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>(not in master — add as test case)</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Status Monitor nav link routes to the EP status view</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr"/>
+      <c r="G5" s="7" t="inlineStr"/>
+      <c r="H5" s="7" t="inlineStr"/>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>Sidebar 'Status Monitor' link has href=null and clicking it does not navigate (dead/placeholder link). The District/Block-filtered status-monitor view appears not to be wired in the /primerural SPA.</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr"/>
+      <c r="K5" s="7" t="inlineStr"/>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M5" s="7" t="inlineStr"/>
+      <c r="N5" s="7" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>BUG-004</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-DB-VIS-001</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>(not in master — add as test case)</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-DB-VIS-001 · Village Visits mode updates KPIs to village-visit context (GPS pin count)</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr"/>
+      <c r="G6" s="7" t="inlineStr"/>
+      <c r="H6" s="7" t="inlineStr"/>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>Error: Village Visits mode should re-scope KPIs (entrepreneurs: label="Total Entrepreneurs",gps=6; village: label="Total Entrepreneurs",gps=6)
+expect(received).toBe(expected) // Object.is equality
+Expected: true
+Received: false</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\19-dashboard-filters-PR-TC-1d640-isit-context-GPS-pin-count--sm\test-failed-1.png</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="inlineStr"/>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M6" s="7" t="inlineStr"/>
+      <c r="N6" s="7" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>BUG-005</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-EP-039</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>15. Entrepreneur Profile — Full Lifecycle</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>FA cannot edit an EP that is not in their assigned block</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>P0 — Blocker</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>• FA assigned to Block A tries to PATCH an EP in Block B via API.</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr"/>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Error: page.goto: net::ERR_NO_BUFFER_SPACE at https://stgprime-rural.dhwaniris.in/app/enterprenur-profile/EP-00006
+Call log:
+  - navigating to "https://stgprime-rural.dhwaniris.in/app/enterprenur-profile/EP-00006", waiting until "load"</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\15-ep-profile-PR-TC-EP-·-E-436b9--their-block-via-direct-URL-sm\test-failed-1.png</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr"/>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="inlineStr"/>
+      <c r="N7" s="7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>BUG-006</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-FWC-BPC-002</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>(not in master — add as test case)</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-FWC-BPC-002 · Business Plan Canvas header has no raw doctype / UUID</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr"/>
+      <c r="G8" s="7" t="inlineStr"/>
+      <c r="H8" s="7" t="inlineStr"/>
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Business Plan Canvas: {"doctype-df-prefix":["DF BUSINESS"]}
 expect.toEqual // deep equality
@@ -22386,50 +22596,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J4" s="7" t="inlineStr">
+      <c r="J8" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Bu-a8fd3-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K4" s="7" t="inlineStr"/>
-      <c r="L4" s="7" t="inlineStr">
+      <c r="K8" s="7" t="inlineStr"/>
+      <c r="L8" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M4" s="7" t="inlineStr"/>
-      <c r="N4" s="7" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>BUG-003</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="M8" s="7" t="inlineStr"/>
+      <c r="N8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>BUG-007</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-BREG-002</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-BREG-002 · Business Registration header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr"/>
-      <c r="G5" s="7" t="inlineStr"/>
-      <c r="H5" s="7" t="inlineStr"/>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr"/>
+      <c r="G9" s="7" t="inlineStr"/>
+      <c r="H9" s="7" t="inlineStr"/>
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Business Registration: {"doctype-df-prefix":["DF BUSINESS"]}
 expect.toEqual // deep equality
@@ -22443,50 +22653,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J5" s="7" t="inlineStr">
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Bu-6c730-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K5" s="7" t="inlineStr"/>
-      <c r="L5" s="7" t="inlineStr">
+      <c r="K9" s="7" t="inlineStr"/>
+      <c r="L9" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M5" s="7" t="inlineStr"/>
-      <c r="N5" s="7" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>BUG-004</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="M9" s="7" t="inlineStr"/>
+      <c r="N9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>BUG-008</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-CA-002</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-CA-002 · Customer Analysis header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr"/>
-      <c r="G6" s="7" t="inlineStr"/>
-      <c r="H6" s="7" t="inlineStr"/>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr"/>
+      <c r="G10" s="7" t="inlineStr"/>
+      <c r="H10" s="7" t="inlineStr"/>
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Customer Analysis: {"doctype-df-prefix":["DF CUSTOMER"]}
 expect.toEqual // deep equality
@@ -22500,50 +22710,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J6" s="7" t="inlineStr">
+      <c r="J10" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Cu-6ed58-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K6" s="7" t="inlineStr"/>
-      <c r="L6" s="7" t="inlineStr">
+      <c r="K10" s="7" t="inlineStr"/>
+      <c r="L10" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M6" s="7" t="inlineStr"/>
-      <c r="N6" s="7" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>BUG-005</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="M10" s="7" t="inlineStr"/>
+      <c r="N10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>BUG-009</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-CB-002</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-CB-002 · Capacity Building header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr"/>
-      <c r="G7" s="7" t="inlineStr"/>
-      <c r="H7" s="7" t="inlineStr"/>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr"/>
+      <c r="G11" s="7" t="inlineStr"/>
+      <c r="H11" s="7" t="inlineStr"/>
+      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Capacity Building: {"doctype-df-prefix":["DF CAPACITY"]}
 expect.toEqual // deep equality
@@ -22557,50 +22767,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J7" s="7" t="inlineStr">
+      <c r="J11" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Ca-83199-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K7" s="7" t="inlineStr"/>
-      <c r="L7" s="7" t="inlineStr">
+      <c r="K11" s="7" t="inlineStr"/>
+      <c r="L11" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M7" s="7" t="inlineStr"/>
-      <c r="N7" s="7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>BUG-006</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="M11" s="7" t="inlineStr"/>
+      <c r="N11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>BUG-010</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-DL-002</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-DL-002 · Digital Literacy header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr"/>
-      <c r="G8" s="7" t="inlineStr"/>
-      <c r="H8" s="7" t="inlineStr"/>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr"/>
+      <c r="G12" s="7" t="inlineStr"/>
+      <c r="H12" s="7" t="inlineStr"/>
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Digital Literacy: {"doctype-df-prefix":["DF DIGITAL"]}
 expect.toEqual // deep equality
@@ -22614,50 +22824,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J8" s="7" t="inlineStr">
+      <c r="J12" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Di-845ef-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K8" s="7" t="inlineStr"/>
-      <c r="L8" s="7" t="inlineStr">
+      <c r="K12" s="7" t="inlineStr"/>
+      <c r="L12" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M8" s="7" t="inlineStr"/>
-      <c r="N8" s="7" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>BUG-007</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="M12" s="7" t="inlineStr"/>
+      <c r="N12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>BUG-011</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-INFR-002</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-INFR-002 · Infrastructure (BE/EE/CE) header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr"/>
-      <c r="G9" s="7" t="inlineStr"/>
-      <c r="H9" s="7" t="inlineStr"/>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="F13" s="7" t="inlineStr"/>
+      <c r="G13" s="7" t="inlineStr"/>
+      <c r="H13" s="7" t="inlineStr"/>
+      <c r="I13" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Infrastructure: {"doctype-df-prefix":["DF INFRASTRUCTURE"]}
 expect.toEqual // deep equality
@@ -22671,50 +22881,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J9" s="7" t="inlineStr">
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-In-3328d-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K9" s="7" t="inlineStr"/>
-      <c r="L9" s="7" t="inlineStr">
+      <c r="K13" s="7" t="inlineStr"/>
+      <c r="L13" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M9" s="7" t="inlineStr"/>
-      <c r="N9" s="7" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>BUG-008</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="M13" s="7" t="inlineStr"/>
+      <c r="N13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>BUG-012</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-LABL-002</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-LABL-002 · Marketing Label header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr"/>
-      <c r="G10" s="7" t="inlineStr"/>
-      <c r="H10" s="7" t="inlineStr"/>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr"/>
+      <c r="G14" s="7" t="inlineStr"/>
+      <c r="H14" s="7" t="inlineStr"/>
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Marketing Label: {"doctype-df-prefix":["DF MARKETING"]}
 expect.toEqual // deep equality
@@ -22728,50 +22938,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J10" s="7" t="inlineStr">
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Ma-11834-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K10" s="7" t="inlineStr"/>
-      <c r="L10" s="7" t="inlineStr">
+      <c r="K14" s="7" t="inlineStr"/>
+      <c r="L14" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M10" s="7" t="inlineStr"/>
-      <c r="N10" s="7" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>BUG-009</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="M14" s="7" t="inlineStr"/>
+      <c r="N14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>BUG-013</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-ML-002</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-ML-002 · Market Linkage header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr"/>
-      <c r="G11" s="7" t="inlineStr"/>
-      <c r="H11" s="7" t="inlineStr"/>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr"/>
+      <c r="G15" s="7" t="inlineStr"/>
+      <c r="H15" s="7" t="inlineStr"/>
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Market Linkage: {"doctype-df-prefix":["DF MARKET"]}
 expect.toEqual // deep equality
@@ -22785,50 +22995,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J11" s="7" t="inlineStr">
+      <c r="J15" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Ma-22f69-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K11" s="7" t="inlineStr"/>
-      <c r="L11" s="7" t="inlineStr">
+      <c r="K15" s="7" t="inlineStr"/>
+      <c r="L15" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M11" s="7" t="inlineStr"/>
-      <c r="N11" s="7" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>BUG-010</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="M15" s="7" t="inlineStr"/>
+      <c r="N15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>BUG-014</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-MR-002</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-MR-002 · Market Research header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr"/>
-      <c r="G12" s="7" t="inlineStr"/>
-      <c r="H12" s="7" t="inlineStr"/>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="F16" s="7" t="inlineStr"/>
+      <c r="G16" s="7" t="inlineStr"/>
+      <c r="H16" s="7" t="inlineStr"/>
+      <c r="I16" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Market Research: {"doctype-df-prefix":["DF MARKET"]}
 expect.toEqual // deep equality
@@ -22842,50 +23052,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J12" s="7" t="inlineStr">
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Ma-6eb23-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K12" s="7" t="inlineStr"/>
-      <c r="L12" s="7" t="inlineStr">
+      <c r="K16" s="7" t="inlineStr"/>
+      <c r="L16" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M12" s="7" t="inlineStr"/>
-      <c r="N12" s="7" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>BUG-011</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="M16" s="7" t="inlineStr"/>
+      <c r="N16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>BUG-015</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PCMP-002</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PCMP-002 · Product Compliance header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr"/>
-      <c r="G13" s="7" t="inlineStr"/>
-      <c r="H13" s="7" t="inlineStr"/>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="F17" s="7" t="inlineStr"/>
+      <c r="G17" s="7" t="inlineStr"/>
+      <c r="H17" s="7" t="inlineStr"/>
+      <c r="I17" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Product Compliance: {"doctype-df-prefix":["DF PRODUCT"]}
 expect.toEqual // deep equality
@@ -22899,50 +23109,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J13" s="7" t="inlineStr">
+      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Pr-be46f-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K13" s="7" t="inlineStr"/>
-      <c r="L13" s="7" t="inlineStr">
+      <c r="K17" s="7" t="inlineStr"/>
+      <c r="L17" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M13" s="7" t="inlineStr"/>
-      <c r="N13" s="7" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>BUG-012</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="M17" s="7" t="inlineStr"/>
+      <c r="N17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>BUG-016</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PROM-002</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PROM-002 · Promotional Marketing header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E18" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr"/>
-      <c r="G14" s="7" t="inlineStr"/>
-      <c r="H14" s="7" t="inlineStr"/>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="F18" s="7" t="inlineStr"/>
+      <c r="G18" s="7" t="inlineStr"/>
+      <c r="H18" s="7" t="inlineStr"/>
+      <c r="I18" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Promotional Marketing: {"doctype-df-prefix":["DF PROMOTIONAL"]}
 expect.toEqual // deep equality
@@ -22956,50 +23166,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J14" s="7" t="inlineStr">
+      <c r="J18" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Pr-d8d12-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K14" s="7" t="inlineStr"/>
-      <c r="L14" s="7" t="inlineStr">
+      <c r="K18" s="7" t="inlineStr"/>
+      <c r="L18" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M14" s="7" t="inlineStr"/>
-      <c r="N14" s="7" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>BUG-013</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="M18" s="7" t="inlineStr"/>
+      <c r="N18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>BUG-017</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PROT-002</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PROT-002 · Product Prototyping header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr"/>
-      <c r="G15" s="7" t="inlineStr"/>
-      <c r="H15" s="7" t="inlineStr"/>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr"/>
+      <c r="G19" s="7" t="inlineStr"/>
+      <c r="H19" s="7" t="inlineStr"/>
+      <c r="I19" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Product Prototyping: {"doctype-df-prefix":["DF PRODUCT"]}
 expect.toEqual // deep equality
@@ -23013,50 +23223,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J15" s="7" t="inlineStr">
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Pr-1120e-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K15" s="7" t="inlineStr"/>
-      <c r="L15" s="7" t="inlineStr">
+      <c r="K19" s="7" t="inlineStr"/>
+      <c r="L19" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M15" s="7" t="inlineStr"/>
-      <c r="N15" s="7" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>BUG-014</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="M19" s="7" t="inlineStr"/>
+      <c r="N19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>BUG-018</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PTCH-002</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PTCH-002 · Pitch Deck header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr"/>
-      <c r="G16" s="7" t="inlineStr"/>
-      <c r="H16" s="7" t="inlineStr"/>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="F20" s="7" t="inlineStr"/>
+      <c r="G20" s="7" t="inlineStr"/>
+      <c r="H20" s="7" t="inlineStr"/>
+      <c r="I20" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Pitch Deck: {"doctype-df-prefix":["DF PITCH"]}
 expect.toEqual // deep equality
@@ -23070,50 +23280,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J16" s="7" t="inlineStr">
+      <c r="J20" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Pi-fefd5-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K16" s="7" t="inlineStr"/>
-      <c r="L16" s="7" t="inlineStr">
+      <c r="K20" s="7" t="inlineStr"/>
+      <c r="L20" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M16" s="7" t="inlineStr"/>
-      <c r="N16" s="7" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>BUG-015</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="M20" s="7" t="inlineStr"/>
+      <c r="N20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>BUG-019</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PTST-002</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PTST-002 · Product Testing header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr"/>
-      <c r="G17" s="7" t="inlineStr"/>
-      <c r="H17" s="7" t="inlineStr"/>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="F21" s="7" t="inlineStr"/>
+      <c r="G21" s="7" t="inlineStr"/>
+      <c r="H21" s="7" t="inlineStr"/>
+      <c r="I21" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Product Testing: {"doctype-df-prefix":["DF PRODUCT"]}
 expect.toEqual // deep equality
@@ -23127,50 +23337,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J17" s="7" t="inlineStr">
+      <c r="J21" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Pr-3e912-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K17" s="7" t="inlineStr"/>
-      <c r="L17" s="7" t="inlineStr">
+      <c r="K21" s="7" t="inlineStr"/>
+      <c r="L21" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M17" s="7" t="inlineStr"/>
-      <c r="N17" s="7" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>BUG-016</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="M21" s="7" t="inlineStr"/>
+      <c r="N21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>BUG-020</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-QC-002</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-QC-002 · Quality Control header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr"/>
-      <c r="G18" s="7" t="inlineStr"/>
-      <c r="H18" s="7" t="inlineStr"/>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="F22" s="7" t="inlineStr"/>
+      <c r="G22" s="7" t="inlineStr"/>
+      <c r="H22" s="7" t="inlineStr"/>
+      <c r="I22" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Quality Control: {"doctype-df-prefix":["DF QUALITY"]}
 expect.toEqual // deep equality
@@ -23184,50 +23394,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J18" s="7" t="inlineStr">
+      <c r="J22" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Qu-ae31c-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K18" s="7" t="inlineStr"/>
-      <c r="L18" s="7" t="inlineStr">
+      <c r="K22" s="7" t="inlineStr"/>
+      <c r="L22" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M18" s="7" t="inlineStr"/>
-      <c r="N18" s="7" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>BUG-017</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="M22" s="7" t="inlineStr"/>
+      <c r="N22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>BUG-021</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-SCHM-002</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-SCHM-002 · Schemes &amp; Funding header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr"/>
-      <c r="G19" s="7" t="inlineStr"/>
-      <c r="H19" s="7" t="inlineStr"/>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="F23" s="7" t="inlineStr"/>
+      <c r="G23" s="7" t="inlineStr"/>
+      <c r="H23" s="7" t="inlineStr"/>
+      <c r="I23" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Schemes &amp; Funding: {"doctype-df-prefix":["DF SCHEMES"]}
 expect.toEqual // deep equality
@@ -23241,50 +23451,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J19" s="7" t="inlineStr">
+      <c r="J23" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Sc-67cb2-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K19" s="7" t="inlineStr"/>
-      <c r="L19" s="7" t="inlineStr">
+      <c r="K23" s="7" t="inlineStr"/>
+      <c r="L23" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M19" s="7" t="inlineStr"/>
-      <c r="N19" s="7" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>BUG-018</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="M23" s="7" t="inlineStr"/>
+      <c r="N23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>BUG-022</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-STD-002</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-STD-002 · Standardization header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr"/>
-      <c r="G20" s="7" t="inlineStr"/>
-      <c r="H20" s="7" t="inlineStr"/>
-      <c r="I20" s="7" t="inlineStr">
+      <c r="F24" s="7" t="inlineStr"/>
+      <c r="G24" s="7" t="inlineStr"/>
+      <c r="H24" s="7" t="inlineStr"/>
+      <c r="I24" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Standardization: {"doctype-df-prefix":["DF STANDARDIZATION"]}
 expect.toEqual // deep equality
@@ -23298,50 +23508,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J20" s="7" t="inlineStr">
+      <c r="J24" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-St-b8b93-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K20" s="7" t="inlineStr"/>
-      <c r="L20" s="7" t="inlineStr">
+      <c r="K24" s="7" t="inlineStr"/>
+      <c r="L24" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M20" s="7" t="inlineStr"/>
-      <c r="N20" s="7" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>BUG-019</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="M24" s="7" t="inlineStr"/>
+      <c r="N24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>BUG-023</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-UP-002</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-UP-002 · Unit Pricing header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr"/>
-      <c r="G21" s="7" t="inlineStr"/>
-      <c r="H21" s="7" t="inlineStr"/>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="F25" s="7" t="inlineStr"/>
+      <c r="G25" s="7" t="inlineStr"/>
+      <c r="H25" s="7" t="inlineStr"/>
+      <c r="I25" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Unit Pricing: {"doctype-df-prefix":["DF UNIT"]}
 expect.toEqual // deep equality
@@ -23355,58 +23565,58 @@
 + }</t>
         </is>
       </c>
-      <c r="J21" s="7" t="inlineStr">
+      <c r="J25" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Un-0c652-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K21" s="7" t="inlineStr"/>
-      <c r="L21" s="7" t="inlineStr">
+      <c r="K25" s="7" t="inlineStr"/>
+      <c r="L25" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M21" s="7" t="inlineStr"/>
-      <c r="N21" s="7" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>BUG-020</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="M25" s="7" t="inlineStr"/>
+      <c r="N25" s="7" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>BUG-024</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>PR-TC-MS-008</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>14. Masters &amp; Reference Data</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>Cohort end date must be after start date</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E26" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr">
+      <c r="F26" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G22" s="7" t="inlineStr">
+      <c r="G26" s="7" t="inlineStr">
         <is>
           <t>• Start = 01-Apr-2026, End = 31-Mar-2025.</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr"/>
-      <c r="I22" s="7" t="inlineStr">
+      <c r="H26" s="7" t="inlineStr"/>
+      <c r="I26" s="7" t="inlineStr">
         <is>
           <t>Error: end-before-start cohort should be rejected
 expect(received).toBeGreaterThanOrEqual(expected)
@@ -23414,59 +23624,59 @@
 Received:    200</t>
         </is>
       </c>
-      <c r="J22" s="7" t="inlineStr"/>
-      <c r="K22" s="7" t="inlineStr"/>
-      <c r="L22" s="7" t="inlineStr">
+      <c r="J26" s="7" t="inlineStr"/>
+      <c r="K26" s="7" t="inlineStr"/>
+      <c r="L26" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M22" s="7" t="inlineStr"/>
-      <c r="N22" s="7" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>BUG-021</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="M26" s="7" t="inlineStr"/>
+      <c r="N26" s="7" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>BUG-025</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>PR-TC-MS-011</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>14. Masters &amp; Reference Data</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>Seed import: 351 rows from "Final PRIME Rural Task Dropdowns Master.xlsx"</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F23" s="7" t="inlineStr">
+      <c r="F27" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G23" s="7" t="inlineStr">
+      <c r="G27" s="7" t="inlineStr">
         <is>
           <t>• Run the seed migration script (or use bulk import) using the canonical xlsx.
 • Verify count = 351.</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
+      <c r="H27" s="7" t="inlineStr">
         <is>
           <t>351 Framework Task Master records exist. Each has: module, framework, task_no, task_name, description, phase. Em-dash phase rows have phase = "Other". Logistic Service has its "Other" row added (was missing in the xlsx).</t>
         </is>
       </c>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="I27" s="7" t="inlineStr">
         <is>
           <t>Error: Framework Task Master doctype should exist
 expect(received).toBe(expected) // Object.is equality
@@ -23474,58 +23684,58 @@
 Received: 404</t>
         </is>
       </c>
-      <c r="J23" s="7" t="inlineStr"/>
-      <c r="K23" s="7" t="inlineStr">
+      <c r="J27" s="7" t="inlineStr"/>
+      <c r="K27" s="7" t="inlineStr">
         <is>
           <t>BRD PR-XC-002b.</t>
         </is>
       </c>
-      <c r="L23" s="7" t="inlineStr">
+      <c r="L27" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M23" s="7" t="inlineStr"/>
-      <c r="N23" s="7" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>BUG-022</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="M27" s="7" t="inlineStr"/>
+      <c r="N27" s="7" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>BUG-026</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>PR-TC-MS-015</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>14. Masters &amp; Reference Data</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>Document types: Aadhaar, PAN, EPIC, Bank Passbook, Photo, Other</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr">
+      <c r="F28" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G24" s="7" t="inlineStr">
+      <c r="G28" s="7" t="inlineStr">
         <is>
           <t>• Masters → Document Master → list.</t>
         </is>
       </c>
-      <c r="H24" s="7" t="inlineStr"/>
-      <c r="I24" s="7" t="inlineStr">
+      <c r="H28" s="7" t="inlineStr"/>
+      <c r="I28" s="7" t="inlineStr">
         <is>
           <t>Error: expected the standard document types (Aadhaar/PAN/EPIC/Bank/Photo/...)
 expect(received).toBeGreaterThanOrEqual(expected)
@@ -23533,58 +23743,58 @@
 Received:    5</t>
         </is>
       </c>
-      <c r="J24" s="7" t="inlineStr"/>
-      <c r="K24" s="7" t="inlineStr"/>
-      <c r="L24" s="7" t="inlineStr">
+      <c r="J28" s="7" t="inlineStr"/>
+      <c r="K28" s="7" t="inlineStr"/>
+      <c r="L28" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M24" s="7" t="inlineStr"/>
-      <c r="N24" s="7" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>BUG-023</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="M28" s="7" t="inlineStr"/>
+      <c r="N28" s="7" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>BUG-027</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>PR-TC-MS-020</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>14. Masters &amp; Reference Data</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>19 schemes pre-seeded (MOVCDNER, CGTMSE, NEHHDC, PGS-India Organic, etc.)</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F25" s="7" t="inlineStr">
+      <c r="F29" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G25" s="7" t="inlineStr">
+      <c r="G29" s="7" t="inlineStr">
         <is>
           <t>• Open Scheme Master list. Count rows.</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr">
+      <c r="H29" s="7" t="inlineStr">
         <is>
           <t>19 schemes present per BRD m-schemes. Each has: name, type (Grant / Loan / Subsidy / Certification), eligibility, min/max amount, applicable sectors, interest rate (if loan).</t>
         </is>
       </c>
-      <c r="I25" s="7" t="inlineStr">
+      <c r="I29" s="7" t="inlineStr">
         <is>
           <t>Error: BRD m-schemes expects 19 pre-seeded schemes
 expect(received).toBeGreaterThanOrEqual(expected)
@@ -23592,104 +23802,104 @@
 Received:    3</t>
         </is>
       </c>
-      <c r="J25" s="7" t="inlineStr"/>
-      <c r="K25" s="7" t="inlineStr">
+      <c r="J29" s="7" t="inlineStr"/>
+      <c r="K29" s="7" t="inlineStr">
         <is>
           <t>BRD m-schemes.</t>
         </is>
       </c>
-      <c r="L25" s="7" t="inlineStr">
+      <c r="L29" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M25" s="7" t="inlineStr"/>
-      <c r="N25" s="7" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>BUG-024</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="M29" s="7" t="inlineStr"/>
+      <c r="N29" s="7" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>BUG-028</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>PR-TC-SEC-005</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>23. Security — OWASP &amp; Beyond</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>Content-Security-Policy header set, restricts inline scripts</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="E30" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F26" s="7" t="inlineStr">
+      <c r="F30" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G26" s="7" t="inlineStr">
+      <c r="G30" s="7" t="inlineStr">
         <is>
           <t>• Inspect response headers on /app/.</t>
         </is>
       </c>
-      <c r="H26" s="7" t="inlineStr"/>
-      <c r="I26" s="7" t="inlineStr">
+      <c r="H30" s="7" t="inlineStr"/>
+      <c r="I30" s="7" t="inlineStr">
         <is>
           <t>Error: CSP header should be set
 expect(received).toBeTruthy()
 Received: undefined</t>
         </is>
       </c>
-      <c r="J26" s="7" t="inlineStr"/>
-      <c r="K26" s="7" t="inlineStr"/>
-      <c r="L26" s="7" t="inlineStr">
+      <c r="J30" s="7" t="inlineStr"/>
+      <c r="K30" s="7" t="inlineStr"/>
+      <c r="L30" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M26" s="7" t="inlineStr"/>
-      <c r="N26" s="7" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>BUG-025</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="M30" s="7" t="inlineStr"/>
+      <c r="N30" s="7" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>BUG-029</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>PR-TC-UI-LEAK-001</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>PR-TC-UI-LEAK-001 · EP profile shows no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E31" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr"/>
-      <c r="G27" s="7" t="inlineStr"/>
-      <c r="H27" s="7" t="inlineStr"/>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="F31" s="7" t="inlineStr"/>
+      <c r="G31" s="7" t="inlineStr"/>
+      <c r="H31" s="7" t="inlineStr"/>
+      <c r="I31" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on EP profile: {"doctype-df-prefix":["DF PROGRESS"]}
 expect.toEqual // deep equality
@@ -23703,50 +23913,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J27" s="7" t="inlineStr">
+      <c r="J31" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\08-ui-no-backend-leak-PR-T-d694f-e-shows-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K27" s="7" t="inlineStr"/>
-      <c r="L27" s="7" t="inlineStr">
+      <c r="K31" s="7" t="inlineStr"/>
+      <c r="L31" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M27" s="7" t="inlineStr"/>
-      <c r="N27" s="7" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>BUG-026</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="M31" s="7" t="inlineStr"/>
+      <c r="N31" s="7" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>BUG-030</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>PR-TC-UI-LEAK-002</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>PR-TC-UI-LEAK-002 · new EP form header is a friendly label, not the raw doctype</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E32" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr"/>
-      <c r="G28" s="7" t="inlineStr"/>
-      <c r="H28" s="7" t="inlineStr"/>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="F32" s="7" t="inlineStr"/>
+      <c r="G32" s="7" t="inlineStr"/>
+      <c r="H32" s="7" t="inlineStr"/>
+      <c r="I32" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on new EP form: {"enterprenur-internal":["Enterprenur"]}
 expect.toEqual // deep equality
@@ -23760,126 +23970,126 @@
 + }</t>
         </is>
       </c>
-      <c r="J28" s="7" t="inlineStr">
+      <c r="J32" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\08-ui-no-backend-leak-PR-T-215c4-y-label-not-the-raw-doctype-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K28" s="7" t="inlineStr"/>
-      <c r="L28" s="7" t="inlineStr">
+      <c r="K32" s="7" t="inlineStr"/>
+      <c r="L32" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M28" s="7" t="inlineStr"/>
-      <c r="N28" s="7" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>BUG-027</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="M32" s="7" t="inlineStr"/>
+      <c r="N32" s="7" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>BUG-031</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-003</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>4. Application Entry &amp; Routing</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D33" s="7" t="inlineStr">
         <is>
           <t>Deep link to a protected page while logged out preserves the intent</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="E33" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr">
+      <c r="F33" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G29" s="7" t="inlineStr">
+      <c r="G33" s="7" t="inlineStr">
         <is>
           <t>• Open https://stgprime-rural.dhwaniris.in/app/enterprenur-profile/EP-001 directly.
 • Login redirect fires.
 • Complete login as a user permitted to see that record.</t>
         </is>
       </c>
-      <c r="H29" s="7" t="inlineStr">
+      <c r="H33" s="7" t="inlineStr">
         <is>
           <t>After successful login, user is redirected to the originally requested URL (the EP detail page), not the default landing page. URL parameter (typically redirect-to or next) is preserved through the auth flow.</t>
         </is>
       </c>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="I33" s="7" t="inlineStr">
         <is>
           <t>Error: expect(received).toMatch(expected)
 Expected pattern: /redirect|next|to=/i
 Received string:  "https://stgprime-rural.dhwaniris.in/primerural/login"</t>
         </is>
       </c>
-      <c r="J29" s="7" t="inlineStr">
+      <c r="J33" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\04-entry-PR-TC-XC-ENTRY-·--e9661-t-preserves-redirect-intent-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K29" s="7" t="inlineStr">
+      <c r="K33" s="7" t="inlineStr">
         <is>
           <t>BRD: PR-OV-001 (Auth)</t>
         </is>
       </c>
-      <c r="L29" s="7" t="inlineStr">
+      <c r="L33" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M29" s="7" t="inlineStr"/>
-      <c r="N29" s="7" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>BUG-028</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="M33" s="7" t="inlineStr"/>
+      <c r="N33" s="7" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>BUG-032</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-023</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>6. Responsive Layout &amp; Screen Sizes</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>1024×768 (tablet landscape / iPad / Surface): sidebar collapses to icon rail</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="E34" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr">
+      <c r="F34" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G30" s="7" t="inlineStr">
+      <c r="G34" s="7" t="inlineStr">
         <is>
           <t>• Resize to 1024×768.</t>
         </is>
       </c>
-      <c r="H30" s="7" t="inlineStr"/>
-      <c r="I30" s="7" t="inlineStr">
+      <c r="H34" s="7" t="inlineStr"/>
+      <c r="I34" s="7" t="inlineStr">
         <is>
           <t>Error: at 1024px the sidebar should collapse to an icon rail; width=240
 expect(received).toBeLessThanOrEqual(expected)
@@ -23887,63 +24097,63 @@
 Received:    240</t>
         </is>
       </c>
-      <c r="J30" s="7" t="inlineStr">
+      <c r="J34" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\06-08-10-nonfunctional-PR--f1c18-ollapses-to-icon-rail-64px--sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K30" s="7" t="inlineStr"/>
-      <c r="L30" s="7" t="inlineStr">
+      <c r="K34" s="7" t="inlineStr"/>
+      <c r="L34" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M30" s="7" t="inlineStr"/>
-      <c r="N30" s="7" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>BUG-029</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="M34" s="7" t="inlineStr"/>
+      <c r="N34" s="7" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>BUG-033</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-032</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>7. Login &amp; Session</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t>Wrong password shows a clear error and does NOT reveal whether the email exists</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="E35" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr">
+      <c r="F35" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G31" s="7" t="inlineStr">
+      <c r="G35" s="7" t="inlineStr">
         <is>
           <t>• Login form: enter a valid email but wrong password.
 • Submit.</t>
         </is>
       </c>
-      <c r="H31" s="7" t="inlineStr">
+      <c r="H35" s="7" t="inlineStr">
         <is>
           <t>Error displays inline above the form: "Invalid email or password." — generic enough that an attacker cannot enumerate valid emails. The password field is cleared; the email field is preserved. No 500. No password ever echoed back into the field.</t>
         </is>
       </c>
-      <c r="I31" s="7" t="inlineStr">
+      <c r="I35" s="7" t="inlineStr">
         <is>
           <t>Error: login error must be friendly text, not a raw exception class
 expect(locator).not.toContainText(expected) failed
@@ -23957,62 +24167,62 @@
     23 × locator resolved to &lt;div role="alert" class="bg-d</t>
         </is>
       </c>
-      <c r="J31" s="7" t="inlineStr">
+      <c r="J35" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\07-auth-PR-TC-XC-AUTH-·-Em-429a0-neric-error-no-enumeration--sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K31" s="7" t="inlineStr">
+      <c r="K35" s="7" t="inlineStr">
         <is>
           <t>OWASP A07 Auth Failures (do not leak account existence).</t>
         </is>
       </c>
-      <c r="L31" s="7" t="inlineStr">
+      <c r="L35" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M31" s="7" t="inlineStr"/>
-      <c r="N31" s="7" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>BUG-030</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="M35" s="7" t="inlineStr"/>
+      <c r="N35" s="7" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>BUG-034</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-033</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>7. Login &amp; Session</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>Non-existent email shows the same generic error as wrong password</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F32" s="7" t="inlineStr">
+      <c r="F36" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G32" s="7" t="inlineStr">
+      <c r="G36" s="7" t="inlineStr">
         <is>
           <t>• Submit with email not-a-real-user@example.com and any password.</t>
         </is>
       </c>
-      <c r="H32" s="7" t="inlineStr"/>
-      <c r="I32" s="7" t="inlineStr">
+      <c r="H36" s="7" t="inlineStr"/>
+      <c r="I36" s="7" t="inlineStr">
         <is>
           <t>Error: login error must be friendly text, not a raw exception class
 expect(locator).not.toContainText(expected) failed
@@ -24026,175 +24236,175 @@
     23 × locator resolved to &lt;div role="alert" class="bg-d</t>
         </is>
       </c>
-      <c r="J32" s="7" t="inlineStr">
+      <c r="J36" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\07-auth-PR-TC-XC-AUTH-·-Em-a7adf-ows-identical-generic-error-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K32" s="7" t="inlineStr"/>
-      <c r="L32" s="7" t="inlineStr">
+      <c r="K36" s="7" t="inlineStr"/>
+      <c r="L36" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M32" s="7" t="inlineStr"/>
-      <c r="N32" s="7" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>BUG-031</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="M36" s="7" t="inlineStr"/>
+      <c r="N36" s="7" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>BUG-035</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-052</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>8. UI / UX Rules — Monsoon Court Compliance</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t>No green and no yellow appear anywhere in the UI</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F33" s="7" t="inlineStr">
+      <c r="F37" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G33" s="7" t="inlineStr">
+      <c r="G37" s="7" t="inlineStr">
         <is>
           <t>• Visually scan every page for green / yellow elements.
 • Search the rendered CSS for any colour matching green, yellow, #2ecc71, #f1c40f, similar hexes.</t>
         </is>
       </c>
-      <c r="H33" s="7" t="inlineStr">
+      <c r="H37" s="7" t="inlineStr">
         <is>
           <t>Zero green elements. Success states use teal #0E4D4E. Zero yellow elements. Warning states use terracotta #C26849.</t>
         </is>
       </c>
-      <c r="I33" s="7" t="inlineStr">
+      <c r="I37" s="7" t="inlineStr">
         <is>
           <t>Active Entrepreneurs KPI shows a GREEN check rgb(63,107,58) (hue 114). Monsoon Court forbids green — success must be teal #0E4D4E.</t>
         </is>
       </c>
-      <c r="J33" s="7" t="inlineStr">
+      <c r="J37" s="7" t="inlineStr">
         <is>
           <t>.playwright-mcp/bug-xc052-green-kpi.png</t>
         </is>
       </c>
-      <c r="K33" s="7" t="inlineStr">
+      <c r="K37" s="7" t="inlineStr">
         <is>
           <t>Monsoon Court §2.7 (brand non-negotiables).</t>
         </is>
       </c>
-      <c r="L33" s="7" t="inlineStr">
+      <c r="L37" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M33" s="7" t="inlineStr"/>
-      <c r="N33" s="7" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>BUG-032</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="M37" s="7" t="inlineStr"/>
+      <c r="N37" s="7" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>BUG-036</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-054</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>8. UI / UX Rules — Monsoon Court Compliance</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
         <is>
           <t>Required-field marker is a terracotta asterisk, not "(required)" text</t>
         </is>
       </c>
-      <c r="E34" s="7" t="inlineStr">
+      <c r="E38" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F34" s="7" t="inlineStr">
+      <c r="F38" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G34" s="7" t="inlineStr">
+      <c r="G38" s="7" t="inlineStr">
         <is>
           <t>• Open the EP form. Find a required field (e.g. Entrepreneur Name).</t>
         </is>
       </c>
-      <c r="H34" s="7" t="inlineStr"/>
-      <c r="I34" s="7" t="inlineStr">
+      <c r="H38" s="7" t="inlineStr"/>
+      <c r="I38" s="7" t="inlineStr">
         <is>
           <t>Asterisk on the name label is taupe rgb(107,99,89) (inherits label ink-soft), NOT terracotta #C26849. Marker present but wrong colour.</t>
         </is>
       </c>
-      <c r="J34" s="7" t="inlineStr"/>
-      <c r="K34" s="7" t="inlineStr"/>
-      <c r="L34" s="7" t="inlineStr">
+      <c r="J38" s="7" t="inlineStr"/>
+      <c r="K38" s="7" t="inlineStr"/>
+      <c r="L38" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M34" s="7" t="inlineStr"/>
-      <c r="N34" s="7" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>BUG-033</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="M38" s="7" t="inlineStr"/>
+      <c r="N38" s="7" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>BUG-037</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-063</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C39" s="7" t="inlineStr">
         <is>
           <t>9. Accessibility — WCAG 2.2 AA</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="D39" s="7" t="inlineStr">
         <is>
           <t>Form fields have associated labels (axe-core "label" rule passes)</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="E39" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F35" s="7" t="inlineStr">
+      <c r="F39" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G35" s="7" t="inlineStr">
+      <c r="G39" s="7" t="inlineStr">
         <is>
           <t>• Run axe-core on the EP form (via Playwright).</t>
         </is>
       </c>
-      <c r="H35" s="7" t="inlineStr"/>
-      <c r="I35" s="7" t="inlineStr">
+      <c r="H39" s="7" t="inlineStr"/>
+      <c r="I39" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: label violations: [{"id":"label","n":6}]
 expect(received).toEqual(expected) // deep equality
@@ -24214,58 +24424,58 @@
 +        </t>
         </is>
       </c>
-      <c r="J35" s="7" t="inlineStr">
+      <c r="J39" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\09-a11y-PR-TC-XC-063-·-for-17d03-ssociated-labels-axe-label--sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K35" s="7" t="inlineStr"/>
-      <c r="L35" s="7" t="inlineStr">
+      <c r="K39" s="7" t="inlineStr"/>
+      <c r="L39" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M35" s="7" t="inlineStr"/>
-      <c r="N35" s="7" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>BUG-034</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="M39" s="7" t="inlineStr"/>
+      <c r="N39" s="7" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>BUG-038</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-064</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>9. Accessibility — WCAG 2.2 AA</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="D40" s="7" t="inlineStr">
         <is>
           <t>Colour contrast meets WCAG AA</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="E40" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F36" s="7" t="inlineStr">
+      <c r="F40" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G36" s="7" t="inlineStr">
+      <c r="G40" s="7" t="inlineStr">
         <is>
           <t>• Run axe-core's contrast check on EP detail, dashboard, framework form.</t>
         </is>
       </c>
-      <c r="H36" s="7" t="inlineStr"/>
-      <c r="I36" s="7" t="inlineStr">
+      <c r="H40" s="7" t="inlineStr"/>
+      <c r="I40" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: contrast violations: [10]
 expect(received).toEqual(expected) // deep equality
@@ -24281,50 +24491,50 @@
 </t>
         </is>
       </c>
-      <c r="J36" s="7" t="inlineStr">
+      <c r="J40" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\09-a11y-PR-TC-XC-064-·-col-8baa1-WCAG-AA-axe-color-contrast--sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K36" s="7" t="inlineStr"/>
-      <c r="L36" s="7" t="inlineStr">
+      <c r="K40" s="7" t="inlineStr"/>
+      <c r="L40" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M36" s="7" t="inlineStr"/>
-      <c r="N36" s="7" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>BUG-035</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="M40" s="7" t="inlineStr"/>
+      <c r="N40" s="7" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>BUG-039</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-064b</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="D41" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-064b · landscape colour contrast (WCAG AA)</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
+      <c r="E41" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F37" s="7" t="inlineStr"/>
-      <c r="G37" s="7" t="inlineStr"/>
-      <c r="H37" s="7" t="inlineStr"/>
-      <c r="I37" s="7" t="inlineStr">
+      <c r="F41" s="7" t="inlineStr"/>
+      <c r="G41" s="7" t="inlineStr"/>
+      <c r="H41" s="7" t="inlineStr"/>
+      <c r="I41" s="7" t="inlineStr">
         <is>
           <t>Error: landscape contrast nodes: 4
 expect(received).toEqual(expected) // deep equality
@@ -24339,19 +24549,19 @@
 +     "id": "color-contrast"</t>
         </is>
       </c>
-      <c r="J37" s="7" t="inlineStr">
+      <c r="J41" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\09-a11y-PR-TC-XC-064b-·-landscape-colour-contrast-WCAG-AA--sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K37" s="7" t="inlineStr"/>
-      <c r="L37" s="7" t="inlineStr">
+      <c r="K41" s="7" t="inlineStr"/>
+      <c r="L41" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M37" s="7" t="inlineStr"/>
-      <c r="N37" s="7" t="inlineStr"/>
+      <c r="M41" s="7" t="inlineStr"/>
+      <c r="N41" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -13313,16 +13313,14 @@
       </c>
       <c r="L185" s="7" t="inlineStr"/>
       <c r="M185" s="7" t="inlineStr"/>
-      <c r="N185" s="12" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="N185" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O185" s="7" t="inlineStr">
         <is>
-          <t>Error: page.goto: net::ERR_NO_BUFFER_SPACE at https://stgprime-rural.dhwaniris.in/app/enterprenur-profile/EP-00006
-Call log:
-  - navigating to "https://stgprime-rural.dhwaniris.in/app/enterprenur-profile/EP-00006", waiting until "load"</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="P185" s="8" t="inlineStr">
@@ -22408,7 +22406,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-DB-NAV-001</t>
+          <t>PR-TC-DB-MAP-005</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -22418,7 +22416,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Status Monitor nav link routes to the EP status view</t>
+          <t>PR-TC-DB-MAP-005 · captured coordinates fall within Meghalaya bounds (geo validation)</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -22431,7 +22429,8 @@
       <c r="H5" s="7" t="inlineStr"/>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>Sidebar 'Status Monitor' link has href=null and clicking it does not navigate (dead/placeholder link). The District/Block-filtered status-monitor view appears not to be wired in the /primerural SPA.</t>
+          <t>Error: coordinates must be valid Meghalaya geo-tags; offenders: Abhi: 37.422,-122.084 outside Meghalaya | Banshan Marak: 28.452,77.072 outside Meghalaya | Damru: malformed GeoJSON | Damru Devi: 37.422,-122.084 outside Meghalaya | Donbok Lyngkhoi: 28.623,77.218 outside Meghalaya | Dummy: malformed GeoJSON | ENtrpreneur: malformed GeoJSON | Harsh: malformed GeoJSON | Harsh test 2: malformed GeoJSON | Harsh test 3: malformed GeoJSON | Prime: 37.422,-122.084 outside Meghalaya
+expect(received).toEqu</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr"/>
@@ -22452,7 +22451,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-DB-VIS-001</t>
+          <t>PR-TC-DB-NAV-001</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -22462,7 +22461,7 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-DB-VIS-001 · Village Visits mode updates KPIs to village-visit context (GPS pin count)</t>
+          <t>Status Monitor nav link routes to the EP status view</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -22475,73 +22474,59 @@
       <c r="H6" s="7" t="inlineStr"/>
       <c r="I6" s="7" t="inlineStr">
         <is>
+          <t>Sidebar 'Status Monitor' link has href=null and clicking it does not navigate (dead/placeholder link). The District/Block-filtered status-monitor view appears not to be wired in the /primerural SPA.</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr"/>
+      <c r="K6" s="7" t="inlineStr"/>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M6" s="7" t="inlineStr"/>
+      <c r="N6" s="7" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>BUG-005</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-DB-VIS-001</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>(not in master — add as test case)</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-DB-VIS-001 · Village Visits mode updates KPIs to village-visit context (GPS pin count)</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr"/>
+      <c r="G7" s="7" t="inlineStr"/>
+      <c r="H7" s="7" t="inlineStr"/>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
           <t>Error: Village Visits mode should re-scope KPIs (entrepreneurs: label="Total Entrepreneurs",gps=6; village: label="Total Entrepreneurs",gps=6)
 expect(received).toBe(expected) // Object.is equality
 Expected: true
 Received: false</t>
         </is>
       </c>
-      <c r="J6" s="7" t="inlineStr">
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\19-dashboard-filters-PR-TC-1d640-isit-context-GPS-pin-count--sm\test-failed-1.png</t>
-        </is>
-      </c>
-      <c r="K6" s="7" t="inlineStr"/>
-      <c r="L6" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="M6" s="7" t="inlineStr"/>
-      <c r="N6" s="7" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>BUG-005</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>PR-TC-EP-039</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>15. Entrepreneur Profile — Full Lifecycle</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>FA cannot edit an EP that is not in their assigned block</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>P0 — Blocker</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>• FA assigned to Block A tries to PATCH an EP in Block B via API.</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr"/>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>Error: page.goto: net::ERR_NO_BUFFER_SPACE at https://stgprime-rural.dhwaniris.in/app/enterprenur-profile/EP-00006
-Call log:
-  - navigating to "https://stgprime-rural.dhwaniris.in/app/enterprenur-profile/EP-00006", waiting until "load"</t>
-        </is>
-      </c>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\15-ep-profile-PR-TC-EP-·-E-436b9--their-block-via-direct-URL-sm\test-failed-1.png</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr"/>

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -3397,7 +3397,7 @@
 Call log:
   - login error must be friendly text, not a raw exception class with timeout 10000ms
   - waiting for locator('[role="alert"]').first()
-    23 × locator resolved to &lt;div role="alert" class="bg-d</t>
+    22 × locator resolved to &lt;div role="alert" class="bg-d</t>
         </is>
       </c>
       <c r="P33" s="8" t="inlineStr">
@@ -3477,7 +3477,7 @@
 Call log:
   - login error must be friendly text, not a raw exception class with timeout 10000ms
   - waiting for locator('[role="alert"]').first()
-    23 × locator resolved to &lt;div role="alert" class="bg-d</t>
+    22 × locator resolved to &lt;div role="alert" class="bg-d</t>
         </is>
       </c>
       <c r="P34" s="8" t="inlineStr">
@@ -7309,9 +7309,21 @@
           <t>BRD: PR-UJ-CTI §User Management.</t>
         </is>
       </c>
-      <c r="N92" s="8" t="inlineStr"/>
-      <c r="O92" s="7" t="inlineStr"/>
-      <c r="P92" s="8" t="inlineStr"/>
+      <c r="N92" s="12" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O92" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Error: INSERT User → 417: {"exception":"frappe.exceptions.ValidationError: Error syncing User to User Manager: ('User Manager', 'uat-umc-79v3ss@dhwaniris.com', IntegrityError(1062, \"Duplicate entry '[uat]_crud_user' for key 'username'\"))","exc_type":"ValidationError","_exc_source":"dhwani_frappe_base (app)","exc":"[\"Traceback (most recent call last):\\n  File \\\"apps/frappe/frappe/model/base_document.py\\\", line 755, in db_insert\\n    name = frappe.db.sql(\\n    \\t\\\"\\\"\\\"INSERT INTO </t>
+        </is>
+      </c>
+      <c r="P92" s="8" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
       <c r="Q92" s="7" t="inlineStr"/>
     </row>
     <row r="93">
@@ -7375,8 +7387,16 @@
       </c>
       <c r="L93" s="7" t="inlineStr"/>
       <c r="M93" s="7" t="inlineStr"/>
-      <c r="N93" s="8" t="inlineStr"/>
-      <c r="O93" s="7" t="inlineStr"/>
+      <c r="N93" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O93" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P93" s="8" t="inlineStr"/>
       <c r="Q93" s="7" t="inlineStr"/>
     </row>
@@ -7444,8 +7464,16 @@
           <t>Setup step for the rest of UAT. Documented separately in §3.</t>
         </is>
       </c>
-      <c r="N94" s="8" t="inlineStr"/>
-      <c r="O94" s="7" t="inlineStr"/>
+      <c r="N94" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O94" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P94" s="8" t="inlineStr"/>
       <c r="Q94" s="7" t="inlineStr"/>
     </row>
@@ -7503,8 +7531,16 @@
       </c>
       <c r="L95" s="7" t="inlineStr"/>
       <c r="M95" s="7" t="inlineStr"/>
-      <c r="N95" s="8" t="inlineStr"/>
-      <c r="O95" s="7" t="inlineStr"/>
+      <c r="N95" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O95" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P95" s="8" t="inlineStr"/>
       <c r="Q95" s="7" t="inlineStr"/>
     </row>
@@ -7564,8 +7600,16 @@
       </c>
       <c r="L96" s="7" t="inlineStr"/>
       <c r="M96" s="7" t="inlineStr"/>
-      <c r="N96" s="8" t="inlineStr"/>
-      <c r="O96" s="7" t="inlineStr"/>
+      <c r="N96" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O96" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P96" s="8" t="inlineStr"/>
       <c r="Q96" s="7" t="inlineStr"/>
     </row>
@@ -7631,8 +7675,16 @@
           <t>BRD: PR-UJ-FA — Fessociates are block-bound.</t>
         </is>
       </c>
-      <c r="N97" s="8" t="inlineStr"/>
-      <c r="O97" s="7" t="inlineStr"/>
+      <c r="N97" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O97" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P97" s="8" t="inlineStr"/>
       <c r="Q97" s="7" t="inlineStr"/>
     </row>
@@ -7759,8 +7811,16 @@
           <t>OWASP A01 Broken Access Control.</t>
         </is>
       </c>
-      <c r="N99" s="8" t="inlineStr"/>
-      <c r="O99" s="7" t="inlineStr"/>
+      <c r="N99" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O99" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P99" s="8" t="inlineStr"/>
       <c r="Q99" s="7" t="inlineStr"/>
     </row>
@@ -7818,9 +7878,21 @@
       </c>
       <c r="L100" s="7" t="inlineStr"/>
       <c r="M100" s="7" t="inlineStr"/>
-      <c r="N100" s="8" t="inlineStr"/>
-      <c r="O100" s="7" t="inlineStr"/>
-      <c r="P100" s="8" t="inlineStr"/>
+      <c r="N100" s="12" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O100" s="7" t="inlineStr">
+        <is>
+          <t>Error: INSERT User → 417: {"exception":"frappe.exceptions.ValidationError: Error syncing User to User Manager: ('User Manager', 'uat-umn-ztbfos@dhwaniris.com', IntegrityError(1062, \"Duplicate entry '[uat]_norm' for key 'username'\"))","exc_type":"ValidationError","_exc_source":"dhwani_frappe_base (app)","exc":"[\"Traceback (most recent call last):\\n  File \\\"apps/frappe/frappe/model/base_document.py\\\", line 755, in db_insert\\n    name = frappe.db.sql(\\n    \\t\\\"\\\"\\\"INSERT INTO `tab{</t>
+        </is>
+      </c>
+      <c r="P100" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="Q100" s="7" t="inlineStr"/>
     </row>
     <row r="101">
@@ -7881,9 +7953,21 @@
       </c>
       <c r="L101" s="7" t="inlineStr"/>
       <c r="M101" s="7" t="inlineStr"/>
-      <c r="N101" s="8" t="inlineStr"/>
-      <c r="O101" s="7" t="inlineStr"/>
-      <c r="P101" s="8" t="inlineStr"/>
+      <c r="N101" s="12" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O101" s="7" t="inlineStr">
+        <is>
+          <t>Error: INSERT User → 417: {"exception":"frappe.exceptions.ValidationError: Error syncing User to User Manager: ('User Manager', 'uat-ume-1c8bs5@dhwaniris.com', IntegrityError(1062, \"Duplicate entry '[uat]_before' for key 'username'\"))","exc_type":"ValidationError","_exc_source":"dhwani_frappe_base (app)","exc":"[\"Traceback (most recent call last):\\n  File \\\"apps/frappe/frappe/model/base_document.py\\\", line 755, in db_insert\\n    name = frappe.db.sql(\\n    \\t\\\"\\\"\\\"INSERT INTO `ta</t>
+        </is>
+      </c>
+      <c r="P101" s="8" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
       <c r="Q101" s="7" t="inlineStr"/>
     </row>
     <row r="102">
@@ -7941,9 +8025,21 @@
       </c>
       <c r="L102" s="7" t="inlineStr"/>
       <c r="M102" s="7" t="inlineStr"/>
-      <c r="N102" s="8" t="inlineStr"/>
-      <c r="O102" s="7" t="inlineStr"/>
-      <c r="P102" s="8" t="inlineStr"/>
+      <c r="N102" s="12" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O102" s="7" t="inlineStr">
+        <is>
+          <t>Error: INSERT User → 417: {"exception":"frappe.exceptions.ValidationError: Error syncing User to User Manager: ('User Manager', 'uat-umd-0pc24h@dhwaniris.com', IntegrityError(1062, \"Duplicate entry '[uat]_disabled' for key 'username'\"))","exc_type":"ValidationError","_exc_source":"dhwani_frappe_base (app)","exc":"[\"Traceback (most recent call last):\\n  File \\\"apps/frappe/frappe/model/base_document.py\\\", line 755, in db_insert\\n    name = frappe.db.sql(\\n    \\t\\\"\\\"\\\"INSERT INTO `</t>
+        </is>
+      </c>
+      <c r="P102" s="8" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
       <c r="Q102" s="7" t="inlineStr"/>
     </row>
     <row r="103">
@@ -8061,8 +8157,16 @@
       </c>
       <c r="L104" s="7" t="inlineStr"/>
       <c r="M104" s="7" t="inlineStr"/>
-      <c r="N104" s="8" t="inlineStr"/>
-      <c r="O104" s="7" t="inlineStr"/>
+      <c r="N104" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O104" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P104" s="8" t="inlineStr"/>
       <c r="Q104" s="7" t="inlineStr"/>
     </row>
@@ -8120,8 +8224,16 @@
       </c>
       <c r="L105" s="7" t="inlineStr"/>
       <c r="M105" s="7" t="inlineStr"/>
-      <c r="N105" s="8" t="inlineStr"/>
-      <c r="O105" s="7" t="inlineStr"/>
+      <c r="N105" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O105" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P105" s="8" t="inlineStr"/>
       <c r="Q105" s="7" t="inlineStr"/>
     </row>
@@ -8187,8 +8299,16 @@
           <t>Recommend zxcvbn or similar; verify policy in Frappe System Settings.</t>
         </is>
       </c>
-      <c r="N106" s="8" t="inlineStr"/>
-      <c r="O106" s="7" t="inlineStr"/>
+      <c r="N106" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O106" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P106" s="8" t="inlineStr"/>
       <c r="Q106" s="7" t="inlineStr"/>
     </row>
@@ -8246,8 +8366,16 @@
       </c>
       <c r="L107" s="7" t="inlineStr"/>
       <c r="M107" s="7" t="inlineStr"/>
-      <c r="N107" s="8" t="inlineStr"/>
-      <c r="O107" s="7" t="inlineStr"/>
+      <c r="N107" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O107" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P107" s="8" t="inlineStr"/>
       <c r="Q107" s="7" t="inlineStr"/>
     </row>
@@ -8305,8 +8433,16 @@
       </c>
       <c r="L108" s="7" t="inlineStr"/>
       <c r="M108" s="7" t="inlineStr"/>
-      <c r="N108" s="8" t="inlineStr"/>
-      <c r="O108" s="7" t="inlineStr"/>
+      <c r="N108" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O108" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P108" s="8" t="inlineStr"/>
       <c r="Q108" s="7" t="inlineStr"/>
     </row>
@@ -8431,8 +8567,16 @@
       </c>
       <c r="L110" s="7" t="inlineStr"/>
       <c r="M110" s="7" t="inlineStr"/>
-      <c r="N110" s="8" t="inlineStr"/>
-      <c r="O110" s="7" t="inlineStr"/>
+      <c r="N110" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O110" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P110" s="8" t="inlineStr"/>
       <c r="Q110" s="7" t="inlineStr"/>
     </row>
@@ -8611,8 +8755,16 @@
       </c>
       <c r="L113" s="7" t="inlineStr"/>
       <c r="M113" s="7" t="inlineStr"/>
-      <c r="N113" s="8" t="inlineStr"/>
-      <c r="O113" s="7" t="inlineStr"/>
+      <c r="N113" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O113" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P113" s="8" t="inlineStr"/>
       <c r="Q113" s="7" t="inlineStr"/>
     </row>
@@ -8671,8 +8823,16 @@
       </c>
       <c r="L114" s="7" t="inlineStr"/>
       <c r="M114" s="7" t="inlineStr"/>
-      <c r="N114" s="8" t="inlineStr"/>
-      <c r="O114" s="7" t="inlineStr"/>
+      <c r="N114" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O114" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P114" s="8" t="inlineStr"/>
       <c r="Q114" s="7" t="inlineStr"/>
     </row>
@@ -8731,8 +8891,16 @@
       </c>
       <c r="L115" s="7" t="inlineStr"/>
       <c r="M115" s="7" t="inlineStr"/>
-      <c r="N115" s="8" t="inlineStr"/>
-      <c r="O115" s="7" t="inlineStr"/>
+      <c r="N115" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O115" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P115" s="8" t="inlineStr"/>
       <c r="Q115" s="7" t="inlineStr"/>
     </row>
@@ -8792,8 +8960,16 @@
       </c>
       <c r="L116" s="7" t="inlineStr"/>
       <c r="M116" s="7" t="inlineStr"/>
-      <c r="N116" s="8" t="inlineStr"/>
-      <c r="O116" s="7" t="inlineStr"/>
+      <c r="N116" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O116" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P116" s="8" t="inlineStr"/>
       <c r="Q116" s="7" t="inlineStr"/>
     </row>
@@ -8918,8 +9094,16 @@
       </c>
       <c r="L118" s="7" t="inlineStr"/>
       <c r="M118" s="7" t="inlineStr"/>
-      <c r="N118" s="8" t="inlineStr"/>
-      <c r="O118" s="7" t="inlineStr"/>
+      <c r="N118" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O118" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P118" s="8" t="inlineStr"/>
       <c r="Q118" s="7" t="inlineStr"/>
     </row>
@@ -8978,8 +9162,16 @@
       </c>
       <c r="L119" s="7" t="inlineStr"/>
       <c r="M119" s="7" t="inlineStr"/>
-      <c r="N119" s="8" t="inlineStr"/>
-      <c r="O119" s="7" t="inlineStr"/>
+      <c r="N119" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O119" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P119" s="8" t="inlineStr"/>
       <c r="Q119" s="7" t="inlineStr"/>
     </row>
@@ -9037,8 +9229,16 @@
       </c>
       <c r="L120" s="7" t="inlineStr"/>
       <c r="M120" s="7" t="inlineStr"/>
-      <c r="N120" s="8" t="inlineStr"/>
-      <c r="O120" s="7" t="inlineStr"/>
+      <c r="N120" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O120" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P120" s="8" t="inlineStr"/>
       <c r="Q120" s="7" t="inlineStr"/>
     </row>
@@ -9096,8 +9296,16 @@
       </c>
       <c r="L121" s="7" t="inlineStr"/>
       <c r="M121" s="7" t="inlineStr"/>
-      <c r="N121" s="8" t="inlineStr"/>
-      <c r="O121" s="7" t="inlineStr"/>
+      <c r="N121" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O121" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P121" s="8" t="inlineStr"/>
       <c r="Q121" s="7" t="inlineStr"/>
     </row>
@@ -10945,17 +11153,30 @@
           <t>BRD: PR-EP-001.</t>
         </is>
       </c>
-      <c r="N147" s="9" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="N147" s="12" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
       <c r="O147" s="7" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="P147" s="8" t="inlineStr"/>
+          <t>Error: expect(locator).toContainText(expected) failed
+Locator: getByRole('heading', { level: 1 })
+Expected pattern: /New Enterprenur Profile/i
+Received string:  "Welcome back"
+Timeout: 10000ms
+Call log:
+  - Expect "toContainText" with timeout 10000ms
+  - waiting for getByRole('heading', { level: 1 })
+    19 × locator resolved to &lt;h1 class="text-2xl text-ink font-semibold mb-1"&gt;Welcome back&lt;/h1&gt;
+       - unexpected value "Welcome back"</t>
+        </is>
+      </c>
+      <c r="P147" s="8" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
       <c r="Q147" s="7" t="inlineStr"/>
     </row>
     <row r="148">
@@ -12802,17 +13023,28 @@
       </c>
       <c r="L177" s="7" t="inlineStr"/>
       <c r="M177" s="7" t="inlineStr"/>
-      <c r="N177" s="9" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="N177" s="12" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
       <c r="O177" s="7" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="P177" s="8" t="inlineStr"/>
+          <t>Error: expect(locator).toBeVisible() failed
+Locator: getByRole('navigation').getByRole('link', { name: 'Entrepreneur List' })
+Expected: visible
+Timeout: 10000ms
+Error: element(s) not found
+Call log:
+  - Expect "toBeVisible" with timeout 10000ms
+  - waiting for getByRole('navigation').getByRole('link', { name: 'Entrepreneur List' })</t>
+        </is>
+      </c>
+      <c r="P177" s="8" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
       <c r="Q177" s="7" t="inlineStr"/>
     </row>
     <row r="178">
@@ -19200,9 +19432,9 @@
       </c>
       <c r="L276" s="7" t="inlineStr"/>
       <c r="M276" s="7" t="inlineStr"/>
-      <c r="N276" s="13" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+      <c r="N276" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O276" s="7" t="inlineStr">
@@ -20494,17 +20726,23 @@
       </c>
       <c r="L296" s="7" t="inlineStr"/>
       <c r="M296" s="7" t="inlineStr"/>
-      <c r="N296" s="9" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="N296" s="12" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
       <c r="O296" s="7" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="P296" s="8" t="inlineStr"/>
+          <t>Error: expect(received).toMatch(expected)
+Expected pattern: /CSRF/i
+Received string:  "{\"session_expired\":1,\"exc_type\":\"PermissionError\",\"_server_messages\":\"[\\\"{\\\\\\\"message\\\\\\\":\\\\\\\"You are not permitted to access this resource. Login to accessFunction &lt;strong&gt;frappe.client.insert&lt;/strong&gt; is not whitelisted.\\\\\\\",\\\\\\\"as_table\\\\\\\":false,\\\\\\\"title\\\\\\\":\\\\\\\"Method Not Allowed\\\\\\\",\\\\\\\"indicator\\\\\\\":\\\\\\\"red\\\\\\\",\\\\\\\"raise_exception\</t>
+        </is>
+      </c>
+      <c r="P296" s="8" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
       <c r="Q296" s="7" t="inlineStr"/>
     </row>
     <row r="297">
@@ -22191,7 +22429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N41"/>
+  <dimension ref="A1:N51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22297,47 +22535,43 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-DB-EPS-005</t>
+          <t>PR-TC-API-008</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>(not in master — add as test case)</t>
+          <t>21. API Layer</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-DB-EPS-005 · Sector→Business Basket dropdown cascades (basket filtered by sector)</t>
+          <t>Cookie-auth POST without X-Frappe-CSRF-Token is rejected</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F3" s="7" t="inlineStr"/>
-      <c r="G3" s="7" t="inlineStr"/>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>P0 — Blocker</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>• From a cross-origin page, POST /api/method/frappe.client.set_value using the user's cookie.</t>
+        </is>
+      </c>
       <c r="H3" s="7" t="inlineStr"/>
       <c r="I3" s="7" t="inlineStr">
         <is>
-          <t>Error: Basket dropdown for Sector="Food Processing" should list only its baskets (Agri-Food Products, Beverage, Tea), but also showed: Bamboo Crafts, Dairy &amp; Livestock, Handloom &amp; Textiles, Spices &amp; Herbs
-expect(received).toEqual(expected) // deep equality
-- Expected  - 1
-+ Received  + 6
-- Array []
-+ Array [
-+   "Bamboo Crafts",
-+   "Dairy &amp; Livestock",
-+   "Handloom &amp; Textiles",
-+   "Spices &amp; Herbs",
-+ ]</t>
-        </is>
-      </c>
-      <c r="J3" s="7" t="inlineStr">
-        <is>
-          <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\19-dashboard-filters-PR-TC-78c23--basket-filtered-by-sector--sm\test-failed-1.png</t>
-        </is>
-      </c>
+          <t>Error: expect(received).toMatch(expected)
+Expected pattern: /CSRF/i
+Received string:  "{\"session_expired\":1,\"exc_type\":\"PermissionError\",\"_server_messages\":\"[\\\"{\\\\\\\"message\\\\\\\":\\\\\\\"You are not permitted to access this resource. Login to accessFunction &lt;strong&gt;frappe.client.insert&lt;/strong&gt; is not whitelisted.\\\\\\\",\\\\\\\"as_table\\\\\\\":false,\\\\\\\"title\\\\\\\":\\\\\\\"Method Not Allowed\\\\\\\",\\\\\\\"indicator\\\\\\\":\\\\\\\"red\\\\\\\",\\\\\\\"raise_exception\</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr"/>
       <c r="K3" s="7" t="inlineStr"/>
       <c r="L3" s="7" t="inlineStr">
         <is>
@@ -22406,7 +22640,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-DB-MAP-005</t>
+          <t>PR-TC-DB-EPS-007</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -22416,7 +22650,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-DB-MAP-005 · captured coordinates fall within Meghalaya bounds (geo validation)</t>
+          <t>PR-TC-DB-EPS-007 · selecting a filter recomputes the KPI counts</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -22429,11 +22663,17 @@
       <c r="H5" s="7" t="inlineStr"/>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>Error: coordinates must be valid Meghalaya geo-tags; offenders: Abhi: 37.422,-122.084 outside Meghalaya | Banshan Marak: 28.452,77.072 outside Meghalaya | Damru: malformed GeoJSON | Damru Devi: 37.422,-122.084 outside Meghalaya | Donbok Lyngkhoi: 28.623,77.218 outside Meghalaya | Dummy: malformed GeoJSON | ENtrpreneur: malformed GeoJSON | Harsh: malformed GeoJSON | Harsh test 2: malformed GeoJSON | Harsh test 3: malformed GeoJSON | Prime: 37.422,-122.084 outside Meghalaya
-expect(received).toEqu</t>
-        </is>
-      </c>
-      <c r="J5" s="7" t="inlineStr"/>
+          <t>Error: KPI should recompute on Sector filter (before=-1, after=-1)
+expect(received).toBeLessThan(expected)
+Expected: &lt; -1
+Received:   -1</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\19-dashboard-filters-PR-TC-7a839-r-recomputes-the-KPI-counts-sm\test-failed-1.png</t>
+        </is>
+      </c>
       <c r="K5" s="7" t="inlineStr"/>
       <c r="L5" s="7" t="inlineStr">
         <is>
@@ -22451,7 +22691,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-DB-NAV-001</t>
+          <t>PR-TC-DB-MAP-001</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -22461,7 +22701,7 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>Status Monitor nav link routes to the EP status view</t>
+          <t>PR-TC-DB-MAP-001 · geo coordinates are captured; count cross-checks the GPS-Verified KPI</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -22474,10 +22714,17 @@
       <c r="H6" s="7" t="inlineStr"/>
       <c r="I6" s="7" t="inlineStr">
         <is>
-          <t>Sidebar 'Status Monitor' link has href=null and clicking it does not navigate (dead/placeholder link). The District/Block-filtered status-monitor view appears not to be wired in the /primerural SPA.</t>
-        </is>
-      </c>
-      <c r="J6" s="7" t="inlineStr"/>
+          <t>Error: GPS-Verified KPI should be a positive count
+expect(received).toBeGreaterThan(expected)
+Expected: &gt; 0
+Received:   -1</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\19-dashboard-maps-PR-TC-DB-c738a-checks-the-GPS-Verified-KPI-sm\test-failed-1.png</t>
+        </is>
+      </c>
       <c r="K6" s="7" t="inlineStr"/>
       <c r="L6" s="7" t="inlineStr">
         <is>
@@ -22495,7 +22742,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-DB-VIS-001</t>
+          <t>PR-TC-DB-MAP-002</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -22505,7 +22752,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-DB-VIS-001 · Village Visits mode updates KPIs to village-visit context (GPS pin count)</t>
+          <t>PR-TC-DB-MAP-002 · Landscape map renders (Leaflet canvas + tiles)</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -22518,7 +22765,7 @@
       <c r="H7" s="7" t="inlineStr"/>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>Error: Village Visits mode should re-scope KPIs (entrepreneurs: label="Total Entrepreneurs",gps=6; village: label="Total Entrepreneurs",gps=6)
+          <t>Error: Leaflet map container present
 expect(received).toBe(expected) // Object.is equality
 Expected: true
 Received: false</t>
@@ -22526,7 +22773,7 @@
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\19-dashboard-filters-PR-TC-1d640-isit-context-GPS-pin-count--sm\test-failed-1.png</t>
+          <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\19-dashboard-maps-PR-TC-DB-b4e39-nders-Leaflet-canvas-tiles--sm\test-failed-1.png</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr"/>
@@ -22546,7 +22793,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-FWC-BPC-002</t>
+          <t>PR-TC-DB-MAP-003</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -22556,7 +22803,7 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-FWC-BPC-002 · Business Plan Canvas header has no raw doctype / UUID</t>
+          <t>PR-TC-DB-MAP-003 · Meghalaya boundary overlay is rendered</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -22568,6 +22815,341 @@
       <c r="G8" s="7" t="inlineStr"/>
       <c r="H8" s="7" t="inlineStr"/>
       <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>Error: state boundary overlay (svg path or canvas) should render
+expect(received).toBe(expected) // Object.is equality
+Expected: true
+Received: false</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\19-dashboard-maps-PR-TC-DB-14a33-oundary-overlay-is-rendered-sm\test-failed-1.png</t>
+        </is>
+      </c>
+      <c r="K8" s="7" t="inlineStr"/>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M8" s="7" t="inlineStr"/>
+      <c r="N8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>BUG-007</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-DB-MAP-005</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>(not in master — add as test case)</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-DB-MAP-005 · captured coordinates fall within Meghalaya bounds (geo validation)</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr"/>
+      <c r="G9" s="7" t="inlineStr"/>
+      <c r="H9" s="7" t="inlineStr"/>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Error: all geo-tags must be valid Meghalaya coords; 5 out-of-bounds (37.422,-122.084 ; 28.452,77.072 ; 28.623,77.218) + 6 malformed GeoJSON
+expect(received).toBe(expected) // Object.is equality
+Expected: 0
+Received: 11</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr"/>
+      <c r="K9" s="7" t="inlineStr"/>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M9" s="7" t="inlineStr"/>
+      <c r="N9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>BUG-008</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-DB-NAV-001</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>(not in master — add as test case)</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>Status Monitor nav link routes to the EP status view</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr"/>
+      <c r="G10" s="7" t="inlineStr"/>
+      <c r="H10" s="7" t="inlineStr"/>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>Sidebar 'Status Monitor' link has href=null and clicking it does not navigate (dead/placeholder link). The District/Block-filtered status-monitor view appears not to be wired in the /primerural SPA.</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr"/>
+      <c r="K10" s="7" t="inlineStr"/>
+      <c r="L10" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M10" s="7" t="inlineStr"/>
+      <c r="N10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>BUG-009</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-DB-VIS-001</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>(not in master — add as test case)</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-DB-VIS-001 · Village Visits mode updates KPIs to village-visit context (GPS pin count)</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr"/>
+      <c r="G11" s="7" t="inlineStr"/>
+      <c r="H11" s="7" t="inlineStr"/>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>TimeoutError: locator.click: Timeout 15000ms exceeded.
+Call log:
+  - waiting for locator('main button:has-text("Village Visits")')</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\19-dashboard-filters-PR-TC-1d640-isit-context-GPS-pin-count--sm\test-failed-1.png</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr"/>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M11" s="7" t="inlineStr"/>
+      <c r="N11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>BUG-010</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-EP-001</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>15. Entrepreneur Profile — Full Lifecycle</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Create a new EP with all required fields filled</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>P0 — Blocker</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>• EP list → +New Entrepreneur.
+• About Entrepreneur: Name = "[UAT] Honey Farmer One", DOB = 15-Apr-1985, Gender = Female, Education = 10th, Marital = Married, Family Size = 5-10, Language = Khasi.
+• Status &amp; Cohort: Activity Status = Active, Cohort = "[UAT] Cohort 2026-29", Visit Date = today, Intervention Date = today.
+• About Enterprise: Enterprise Name = "Hilltop Honey", Business Start Date = 01-Jan-2020, Position = Founder, Enterprise Stage = Startup, Sector = Apiculture, Business Basket = "Raw honey", Market Accessibility = Local.
+• Contact: Phone = +91 9876543210, Email = honeyfarm@example.com.
+• Location: District = East Khasi Hills, Block = Laitkroh, Village = Mawphlang (or first in list), GPS captured (or manual lat/lon).
+• Documents: Upload Profile Photo, Aadhaar (12-digit valid), PAN (valid pattern).
+• Click Save.</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>Saved. EP-name like EP-[UAT] Honey Farmer One-00001 auto-generated. Toast: "Saved." Profile Dashboard tab loads with hero card, basic info, and an empty Diagnostic Framework block (no priorities set yet). Activity Status = "MET". Final Selection = blank (will be set by CTIT later).</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>Error: expect(locator).toContainText(expected) failed
+Locator: getByRole('heading', { level: 1 })
+Expected pattern: /New Enterprenur Profile/i
+Received string:  "Welcome back"
+Timeout: 10000ms
+Call log:
+  - Expect "toContainText" with timeout 10000ms
+  - waiting for getByRole('heading', { level: 1 })
+    19 × locator resolved to &lt;h1 class="text-2xl text-ink font-semibold mb-1"&gt;Welcome back&lt;/h1&gt;
+       - unexpected value "Welcome back"</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\15-ep-profile-PR-TC-EP-·-E-9e8a3-t-required-field-gates-Save-sm\test-failed-1.png</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>BRD: PR-EP-001.</t>
+        </is>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M12" s="7" t="inlineStr"/>
+      <c r="N12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>BUG-011</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-EP-031</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>15. Entrepreneur Profile — Full Lifecycle</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>EP list columns: Avatar, Name, Sector, Block, Status, Cohort, Last activity, Actions</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>P0 — Blocker</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>• Open EP list.</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr"/>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Error: expect(locator).toBeVisible() failed
+Locator: getByRole('navigation').getByRole('link', { name: 'Entrepreneur List' })
+Expected: visible
+Timeout: 10000ms
+Error: element(s) not found
+Call log:
+  - Expect "toBeVisible" with timeout 10000ms
+  - waiting for getByRole('navigation').getByRole('link', { name: 'Entrepreneur List' })</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\15-ep-profile-PR-TC-EP-·-E-77dc1--031-·-EP-list-page-renders-sm\test-failed-1.png</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr"/>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M13" s="7" t="inlineStr"/>
+      <c r="N13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>BUG-012</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-FWC-BPC-002</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>(not in master — add as test case)</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-FWC-BPC-002 · Business Plan Canvas header has no raw doctype / UUID</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr"/>
+      <c r="G14" s="7" t="inlineStr"/>
+      <c r="H14" s="7" t="inlineStr"/>
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Business Plan Canvas: {"doctype-df-prefix":["DF BUSINESS"]}
 expect.toEqual // deep equality
@@ -22581,50 +23163,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J8" s="7" t="inlineStr">
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Bu-a8fd3-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K8" s="7" t="inlineStr"/>
-      <c r="L8" s="7" t="inlineStr">
+      <c r="K14" s="7" t="inlineStr"/>
+      <c r="L14" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M8" s="7" t="inlineStr"/>
-      <c r="N8" s="7" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>BUG-007</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="M14" s="7" t="inlineStr"/>
+      <c r="N14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>BUG-013</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-BREG-002</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-BREG-002 · Business Registration header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr"/>
-      <c r="G9" s="7" t="inlineStr"/>
-      <c r="H9" s="7" t="inlineStr"/>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr"/>
+      <c r="G15" s="7" t="inlineStr"/>
+      <c r="H15" s="7" t="inlineStr"/>
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Business Registration: {"doctype-df-prefix":["DF BUSINESS"]}
 expect.toEqual // deep equality
@@ -22638,50 +23220,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J9" s="7" t="inlineStr">
+      <c r="J15" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Bu-6c730-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K9" s="7" t="inlineStr"/>
-      <c r="L9" s="7" t="inlineStr">
+      <c r="K15" s="7" t="inlineStr"/>
+      <c r="L15" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M9" s="7" t="inlineStr"/>
-      <c r="N9" s="7" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>BUG-008</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="M15" s="7" t="inlineStr"/>
+      <c r="N15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>BUG-014</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-CA-002</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-CA-002 · Customer Analysis header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr"/>
-      <c r="G10" s="7" t="inlineStr"/>
-      <c r="H10" s="7" t="inlineStr"/>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="F16" s="7" t="inlineStr"/>
+      <c r="G16" s="7" t="inlineStr"/>
+      <c r="H16" s="7" t="inlineStr"/>
+      <c r="I16" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Customer Analysis: {"doctype-df-prefix":["DF CUSTOMER"]}
 expect.toEqual // deep equality
@@ -22695,50 +23277,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J10" s="7" t="inlineStr">
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Cu-6ed58-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K10" s="7" t="inlineStr"/>
-      <c r="L10" s="7" t="inlineStr">
+      <c r="K16" s="7" t="inlineStr"/>
+      <c r="L16" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M10" s="7" t="inlineStr"/>
-      <c r="N10" s="7" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>BUG-009</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="M16" s="7" t="inlineStr"/>
+      <c r="N16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>BUG-015</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-CB-002</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-CB-002 · Capacity Building header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr"/>
-      <c r="G11" s="7" t="inlineStr"/>
-      <c r="H11" s="7" t="inlineStr"/>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="F17" s="7" t="inlineStr"/>
+      <c r="G17" s="7" t="inlineStr"/>
+      <c r="H17" s="7" t="inlineStr"/>
+      <c r="I17" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Capacity Building: {"doctype-df-prefix":["DF CAPACITY"]}
 expect.toEqual // deep equality
@@ -22752,50 +23334,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J11" s="7" t="inlineStr">
+      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Ca-83199-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K11" s="7" t="inlineStr"/>
-      <c r="L11" s="7" t="inlineStr">
+      <c r="K17" s="7" t="inlineStr"/>
+      <c r="L17" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M11" s="7" t="inlineStr"/>
-      <c r="N11" s="7" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>BUG-010</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="M17" s="7" t="inlineStr"/>
+      <c r="N17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>BUG-016</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-DL-002</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-DL-002 · Digital Literacy header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E18" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr"/>
-      <c r="G12" s="7" t="inlineStr"/>
-      <c r="H12" s="7" t="inlineStr"/>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="F18" s="7" t="inlineStr"/>
+      <c r="G18" s="7" t="inlineStr"/>
+      <c r="H18" s="7" t="inlineStr"/>
+      <c r="I18" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Digital Literacy: {"doctype-df-prefix":["DF DIGITAL"]}
 expect.toEqual // deep equality
@@ -22809,50 +23391,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J12" s="7" t="inlineStr">
+      <c r="J18" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Di-845ef-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K12" s="7" t="inlineStr"/>
-      <c r="L12" s="7" t="inlineStr">
+      <c r="K18" s="7" t="inlineStr"/>
+      <c r="L18" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M12" s="7" t="inlineStr"/>
-      <c r="N12" s="7" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>BUG-011</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="M18" s="7" t="inlineStr"/>
+      <c r="N18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>BUG-017</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-INFR-002</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-INFR-002 · Infrastructure (BE/EE/CE) header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr"/>
-      <c r="G13" s="7" t="inlineStr"/>
-      <c r="H13" s="7" t="inlineStr"/>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr"/>
+      <c r="G19" s="7" t="inlineStr"/>
+      <c r="H19" s="7" t="inlineStr"/>
+      <c r="I19" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Infrastructure: {"doctype-df-prefix":["DF INFRASTRUCTURE"]}
 expect.toEqual // deep equality
@@ -22866,50 +23448,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J13" s="7" t="inlineStr">
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-In-3328d-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K13" s="7" t="inlineStr"/>
-      <c r="L13" s="7" t="inlineStr">
+      <c r="K19" s="7" t="inlineStr"/>
+      <c r="L19" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M13" s="7" t="inlineStr"/>
-      <c r="N13" s="7" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>BUG-012</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="M19" s="7" t="inlineStr"/>
+      <c r="N19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>BUG-018</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-LABL-002</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-LABL-002 · Marketing Label header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr"/>
-      <c r="G14" s="7" t="inlineStr"/>
-      <c r="H14" s="7" t="inlineStr"/>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="F20" s="7" t="inlineStr"/>
+      <c r="G20" s="7" t="inlineStr"/>
+      <c r="H20" s="7" t="inlineStr"/>
+      <c r="I20" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Marketing Label: {"doctype-df-prefix":["DF MARKETING"]}
 expect.toEqual // deep equality
@@ -22923,50 +23505,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J14" s="7" t="inlineStr">
+      <c r="J20" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Ma-11834-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K14" s="7" t="inlineStr"/>
-      <c r="L14" s="7" t="inlineStr">
+      <c r="K20" s="7" t="inlineStr"/>
+      <c r="L20" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M14" s="7" t="inlineStr"/>
-      <c r="N14" s="7" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>BUG-013</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="M20" s="7" t="inlineStr"/>
+      <c r="N20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>BUG-019</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-ML-002</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-ML-002 · Market Linkage header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr"/>
-      <c r="G15" s="7" t="inlineStr"/>
-      <c r="H15" s="7" t="inlineStr"/>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="F21" s="7" t="inlineStr"/>
+      <c r="G21" s="7" t="inlineStr"/>
+      <c r="H21" s="7" t="inlineStr"/>
+      <c r="I21" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Market Linkage: {"doctype-df-prefix":["DF MARKET"]}
 expect.toEqual // deep equality
@@ -22980,50 +23562,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J15" s="7" t="inlineStr">
+      <c r="J21" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Ma-22f69-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K15" s="7" t="inlineStr"/>
-      <c r="L15" s="7" t="inlineStr">
+      <c r="K21" s="7" t="inlineStr"/>
+      <c r="L21" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M15" s="7" t="inlineStr"/>
-      <c r="N15" s="7" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>BUG-014</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="M21" s="7" t="inlineStr"/>
+      <c r="N21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>BUG-020</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-MR-002</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-MR-002 · Market Research header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr"/>
-      <c r="G16" s="7" t="inlineStr"/>
-      <c r="H16" s="7" t="inlineStr"/>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="F22" s="7" t="inlineStr"/>
+      <c r="G22" s="7" t="inlineStr"/>
+      <c r="H22" s="7" t="inlineStr"/>
+      <c r="I22" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Market Research: {"doctype-df-prefix":["DF MARKET"]}
 expect.toEqual // deep equality
@@ -23037,50 +23619,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J16" s="7" t="inlineStr">
+      <c r="J22" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Ma-6eb23-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K16" s="7" t="inlineStr"/>
-      <c r="L16" s="7" t="inlineStr">
+      <c r="K22" s="7" t="inlineStr"/>
+      <c r="L22" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M16" s="7" t="inlineStr"/>
-      <c r="N16" s="7" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>BUG-015</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="M22" s="7" t="inlineStr"/>
+      <c r="N22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>BUG-021</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PCMP-002</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PCMP-002 · Product Compliance header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr"/>
-      <c r="G17" s="7" t="inlineStr"/>
-      <c r="H17" s="7" t="inlineStr"/>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="F23" s="7" t="inlineStr"/>
+      <c r="G23" s="7" t="inlineStr"/>
+      <c r="H23" s="7" t="inlineStr"/>
+      <c r="I23" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Product Compliance: {"doctype-df-prefix":["DF PRODUCT"]}
 expect.toEqual // deep equality
@@ -23094,50 +23676,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J17" s="7" t="inlineStr">
+      <c r="J23" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Pr-be46f-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K17" s="7" t="inlineStr"/>
-      <c r="L17" s="7" t="inlineStr">
+      <c r="K23" s="7" t="inlineStr"/>
+      <c r="L23" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M17" s="7" t="inlineStr"/>
-      <c r="N17" s="7" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>BUG-016</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="M23" s="7" t="inlineStr"/>
+      <c r="N23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>BUG-022</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PROM-002</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PROM-002 · Promotional Marketing header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr"/>
-      <c r="G18" s="7" t="inlineStr"/>
-      <c r="H18" s="7" t="inlineStr"/>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="F24" s="7" t="inlineStr"/>
+      <c r="G24" s="7" t="inlineStr"/>
+      <c r="H24" s="7" t="inlineStr"/>
+      <c r="I24" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Promotional Marketing: {"doctype-df-prefix":["DF PROMOTIONAL"]}
 expect.toEqual // deep equality
@@ -23151,50 +23733,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J18" s="7" t="inlineStr">
+      <c r="J24" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Pr-d8d12-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K18" s="7" t="inlineStr"/>
-      <c r="L18" s="7" t="inlineStr">
+      <c r="K24" s="7" t="inlineStr"/>
+      <c r="L24" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M18" s="7" t="inlineStr"/>
-      <c r="N18" s="7" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>BUG-017</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="M24" s="7" t="inlineStr"/>
+      <c r="N24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>BUG-023</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PROT-002</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PROT-002 · Product Prototyping header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr"/>
-      <c r="G19" s="7" t="inlineStr"/>
-      <c r="H19" s="7" t="inlineStr"/>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="F25" s="7" t="inlineStr"/>
+      <c r="G25" s="7" t="inlineStr"/>
+      <c r="H25" s="7" t="inlineStr"/>
+      <c r="I25" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Product Prototyping: {"doctype-df-prefix":["DF PRODUCT"]}
 expect.toEqual // deep equality
@@ -23208,50 +23790,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J19" s="7" t="inlineStr">
+      <c r="J25" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Pr-1120e-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K19" s="7" t="inlineStr"/>
-      <c r="L19" s="7" t="inlineStr">
+      <c r="K25" s="7" t="inlineStr"/>
+      <c r="L25" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M19" s="7" t="inlineStr"/>
-      <c r="N19" s="7" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>BUG-018</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="M25" s="7" t="inlineStr"/>
+      <c r="N25" s="7" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>BUG-024</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PTCH-002</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PTCH-002 · Pitch Deck header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E26" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr"/>
-      <c r="G20" s="7" t="inlineStr"/>
-      <c r="H20" s="7" t="inlineStr"/>
-      <c r="I20" s="7" t="inlineStr">
+      <c r="F26" s="7" t="inlineStr"/>
+      <c r="G26" s="7" t="inlineStr"/>
+      <c r="H26" s="7" t="inlineStr"/>
+      <c r="I26" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Pitch Deck: {"doctype-df-prefix":["DF PITCH"]}
 expect.toEqual // deep equality
@@ -23265,50 +23847,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J20" s="7" t="inlineStr">
+      <c r="J26" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Pi-fefd5-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K20" s="7" t="inlineStr"/>
-      <c r="L20" s="7" t="inlineStr">
+      <c r="K26" s="7" t="inlineStr"/>
+      <c r="L26" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M20" s="7" t="inlineStr"/>
-      <c r="N20" s="7" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>BUG-019</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="M26" s="7" t="inlineStr"/>
+      <c r="N26" s="7" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>BUG-025</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PTST-002</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PTST-002 · Product Testing header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr"/>
-      <c r="G21" s="7" t="inlineStr"/>
-      <c r="H21" s="7" t="inlineStr"/>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="F27" s="7" t="inlineStr"/>
+      <c r="G27" s="7" t="inlineStr"/>
+      <c r="H27" s="7" t="inlineStr"/>
+      <c r="I27" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Product Testing: {"doctype-df-prefix":["DF PRODUCT"]}
 expect.toEqual // deep equality
@@ -23322,50 +23904,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J21" s="7" t="inlineStr">
+      <c r="J27" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Pr-3e912-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K21" s="7" t="inlineStr"/>
-      <c r="L21" s="7" t="inlineStr">
+      <c r="K27" s="7" t="inlineStr"/>
+      <c r="L27" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M21" s="7" t="inlineStr"/>
-      <c r="N21" s="7" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>BUG-020</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="M27" s="7" t="inlineStr"/>
+      <c r="N27" s="7" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>BUG-026</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-QC-002</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-QC-002 · Quality Control header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr"/>
-      <c r="G22" s="7" t="inlineStr"/>
-      <c r="H22" s="7" t="inlineStr"/>
-      <c r="I22" s="7" t="inlineStr">
+      <c r="F28" s="7" t="inlineStr"/>
+      <c r="G28" s="7" t="inlineStr"/>
+      <c r="H28" s="7" t="inlineStr"/>
+      <c r="I28" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Quality Control: {"doctype-df-prefix":["DF QUALITY"]}
 expect.toEqual // deep equality
@@ -23379,50 +23961,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J22" s="7" t="inlineStr">
+      <c r="J28" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Qu-ae31c-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K22" s="7" t="inlineStr"/>
-      <c r="L22" s="7" t="inlineStr">
+      <c r="K28" s="7" t="inlineStr"/>
+      <c r="L28" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M22" s="7" t="inlineStr"/>
-      <c r="N22" s="7" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>BUG-021</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="M28" s="7" t="inlineStr"/>
+      <c r="N28" s="7" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>BUG-027</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-SCHM-002</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-SCHM-002 · Schemes &amp; Funding header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F23" s="7" t="inlineStr"/>
-      <c r="G23" s="7" t="inlineStr"/>
-      <c r="H23" s="7" t="inlineStr"/>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="F29" s="7" t="inlineStr"/>
+      <c r="G29" s="7" t="inlineStr"/>
+      <c r="H29" s="7" t="inlineStr"/>
+      <c r="I29" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Schemes &amp; Funding: {"doctype-df-prefix":["DF SCHEMES"]}
 expect.toEqual // deep equality
@@ -23436,50 +24018,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J23" s="7" t="inlineStr">
+      <c r="J29" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Sc-67cb2-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K23" s="7" t="inlineStr"/>
-      <c r="L23" s="7" t="inlineStr">
+      <c r="K29" s="7" t="inlineStr"/>
+      <c r="L29" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M23" s="7" t="inlineStr"/>
-      <c r="N23" s="7" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>BUG-022</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="M29" s="7" t="inlineStr"/>
+      <c r="N29" s="7" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>BUG-028</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-STD-002</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-STD-002 · Standardization header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E30" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr"/>
-      <c r="G24" s="7" t="inlineStr"/>
-      <c r="H24" s="7" t="inlineStr"/>
-      <c r="I24" s="7" t="inlineStr">
+      <c r="F30" s="7" t="inlineStr"/>
+      <c r="G30" s="7" t="inlineStr"/>
+      <c r="H30" s="7" t="inlineStr"/>
+      <c r="I30" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Standardization: {"doctype-df-prefix":["DF STANDARDIZATION"]}
 expect.toEqual // deep equality
@@ -23493,50 +24075,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J24" s="7" t="inlineStr">
+      <c r="J30" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-St-b8b93-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K24" s="7" t="inlineStr"/>
-      <c r="L24" s="7" t="inlineStr">
+      <c r="K30" s="7" t="inlineStr"/>
+      <c r="L30" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M24" s="7" t="inlineStr"/>
-      <c r="N24" s="7" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>BUG-023</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="M30" s="7" t="inlineStr"/>
+      <c r="N30" s="7" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>BUG-029</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-UP-002</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-UP-002 · Unit Pricing header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="E31" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F25" s="7" t="inlineStr"/>
-      <c r="G25" s="7" t="inlineStr"/>
-      <c r="H25" s="7" t="inlineStr"/>
-      <c r="I25" s="7" t="inlineStr">
+      <c r="F31" s="7" t="inlineStr"/>
+      <c r="G31" s="7" t="inlineStr"/>
+      <c r="H31" s="7" t="inlineStr"/>
+      <c r="I31" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Unit Pricing: {"doctype-df-prefix":["DF UNIT"]}
 expect.toEqual // deep equality
@@ -23550,58 +24132,58 @@
 + }</t>
         </is>
       </c>
-      <c r="J25" s="7" t="inlineStr">
+      <c r="J31" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Un-0c652-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K25" s="7" t="inlineStr"/>
-      <c r="L25" s="7" t="inlineStr">
+      <c r="K31" s="7" t="inlineStr"/>
+      <c r="L31" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M25" s="7" t="inlineStr"/>
-      <c r="N25" s="7" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>BUG-024</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="M31" s="7" t="inlineStr"/>
+      <c r="N31" s="7" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>BUG-030</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>PR-TC-MS-008</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>14. Masters &amp; Reference Data</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>Cohort end date must be after start date</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="E32" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F26" s="7" t="inlineStr">
+      <c r="F32" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G26" s="7" t="inlineStr">
+      <c r="G32" s="7" t="inlineStr">
         <is>
           <t>• Start = 01-Apr-2026, End = 31-Mar-2025.</t>
         </is>
       </c>
-      <c r="H26" s="7" t="inlineStr"/>
-      <c r="I26" s="7" t="inlineStr">
+      <c r="H32" s="7" t="inlineStr"/>
+      <c r="I32" s="7" t="inlineStr">
         <is>
           <t>Error: end-before-start cohort should be rejected
 expect(received).toBeGreaterThanOrEqual(expected)
@@ -23609,59 +24191,59 @@
 Received:    200</t>
         </is>
       </c>
-      <c r="J26" s="7" t="inlineStr"/>
-      <c r="K26" s="7" t="inlineStr"/>
-      <c r="L26" s="7" t="inlineStr">
+      <c r="J32" s="7" t="inlineStr"/>
+      <c r="K32" s="7" t="inlineStr"/>
+      <c r="L32" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M26" s="7" t="inlineStr"/>
-      <c r="N26" s="7" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>BUG-025</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="M32" s="7" t="inlineStr"/>
+      <c r="N32" s="7" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>BUG-031</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>PR-TC-MS-011</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>14. Masters &amp; Reference Data</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D33" s="7" t="inlineStr">
         <is>
           <t>Seed import: 351 rows from "Final PRIME Rural Task Dropdowns Master.xlsx"</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E33" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr">
+      <c r="F33" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G27" s="7" t="inlineStr">
+      <c r="G33" s="7" t="inlineStr">
         <is>
           <t>• Run the seed migration script (or use bulk import) using the canonical xlsx.
 • Verify count = 351.</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr">
+      <c r="H33" s="7" t="inlineStr">
         <is>
           <t>351 Framework Task Master records exist. Each has: module, framework, task_no, task_name, description, phase. Em-dash phase rows have phase = "Other". Logistic Service has its "Other" row added (was missing in the xlsx).</t>
         </is>
       </c>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="I33" s="7" t="inlineStr">
         <is>
           <t>Error: Framework Task Master doctype should exist
 expect(received).toBe(expected) // Object.is equality
@@ -23669,58 +24251,58 @@
 Received: 404</t>
         </is>
       </c>
-      <c r="J27" s="7" t="inlineStr"/>
-      <c r="K27" s="7" t="inlineStr">
+      <c r="J33" s="7" t="inlineStr"/>
+      <c r="K33" s="7" t="inlineStr">
         <is>
           <t>BRD PR-XC-002b.</t>
         </is>
       </c>
-      <c r="L27" s="7" t="inlineStr">
+      <c r="L33" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M27" s="7" t="inlineStr"/>
-      <c r="N27" s="7" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>BUG-026</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="M33" s="7" t="inlineStr"/>
+      <c r="N33" s="7" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>BUG-032</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>PR-TC-MS-015</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>14. Masters &amp; Reference Data</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>Document types: Aadhaar, PAN, EPIC, Bank Passbook, Photo, Other</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E34" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr">
+      <c r="F34" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G28" s="7" t="inlineStr">
+      <c r="G34" s="7" t="inlineStr">
         <is>
           <t>• Masters → Document Master → list.</t>
         </is>
       </c>
-      <c r="H28" s="7" t="inlineStr"/>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="H34" s="7" t="inlineStr"/>
+      <c r="I34" s="7" t="inlineStr">
         <is>
           <t>Error: expected the standard document types (Aadhaar/PAN/EPIC/Bank/Photo/...)
 expect(received).toBeGreaterThanOrEqual(expected)
@@ -23728,58 +24310,58 @@
 Received:    5</t>
         </is>
       </c>
-      <c r="J28" s="7" t="inlineStr"/>
-      <c r="K28" s="7" t="inlineStr"/>
-      <c r="L28" s="7" t="inlineStr">
+      <c r="J34" s="7" t="inlineStr"/>
+      <c r="K34" s="7" t="inlineStr"/>
+      <c r="L34" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M28" s="7" t="inlineStr"/>
-      <c r="N28" s="7" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>BUG-027</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="M34" s="7" t="inlineStr"/>
+      <c r="N34" s="7" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>BUG-033</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>PR-TC-MS-020</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>14. Masters &amp; Reference Data</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t>19 schemes pre-seeded (MOVCDNER, CGTMSE, NEHHDC, PGS-India Organic, etc.)</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="E35" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr">
+      <c r="F35" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G29" s="7" t="inlineStr">
+      <c r="G35" s="7" t="inlineStr">
         <is>
           <t>• Open Scheme Master list. Count rows.</t>
         </is>
       </c>
-      <c r="H29" s="7" t="inlineStr">
+      <c r="H35" s="7" t="inlineStr">
         <is>
           <t>19 schemes present per BRD m-schemes. Each has: name, type (Grant / Loan / Subsidy / Certification), eligibility, min/max amount, applicable sectors, interest rate (if loan).</t>
         </is>
       </c>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="I35" s="7" t="inlineStr">
         <is>
           <t>Error: BRD m-schemes expects 19 pre-seeded schemes
 expect(received).toBeGreaterThanOrEqual(expected)
@@ -23787,104 +24369,104 @@
 Received:    3</t>
         </is>
       </c>
-      <c r="J29" s="7" t="inlineStr"/>
-      <c r="K29" s="7" t="inlineStr">
+      <c r="J35" s="7" t="inlineStr"/>
+      <c r="K35" s="7" t="inlineStr">
         <is>
           <t>BRD m-schemes.</t>
         </is>
       </c>
-      <c r="L29" s="7" t="inlineStr">
+      <c r="L35" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M29" s="7" t="inlineStr"/>
-      <c r="N29" s="7" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>BUG-028</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="M35" s="7" t="inlineStr"/>
+      <c r="N35" s="7" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>BUG-034</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>PR-TC-SEC-005</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>23. Security — OWASP &amp; Beyond</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>Content-Security-Policy header set, restricts inline scripts</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr">
+      <c r="F36" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G30" s="7" t="inlineStr">
+      <c r="G36" s="7" t="inlineStr">
         <is>
           <t>• Inspect response headers on /app/.</t>
         </is>
       </c>
-      <c r="H30" s="7" t="inlineStr"/>
-      <c r="I30" s="7" t="inlineStr">
+      <c r="H36" s="7" t="inlineStr"/>
+      <c r="I36" s="7" t="inlineStr">
         <is>
           <t>Error: CSP header should be set
 expect(received).toBeTruthy()
 Received: undefined</t>
         </is>
       </c>
-      <c r="J30" s="7" t="inlineStr"/>
-      <c r="K30" s="7" t="inlineStr"/>
-      <c r="L30" s="7" t="inlineStr">
+      <c r="J36" s="7" t="inlineStr"/>
+      <c r="K36" s="7" t="inlineStr"/>
+      <c r="L36" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M30" s="7" t="inlineStr"/>
-      <c r="N30" s="7" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>BUG-029</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="M36" s="7" t="inlineStr"/>
+      <c r="N36" s="7" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>BUG-035</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>PR-TC-UI-LEAK-001</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t>PR-TC-UI-LEAK-001 · EP profile shows no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr"/>
-      <c r="G31" s="7" t="inlineStr"/>
-      <c r="H31" s="7" t="inlineStr"/>
-      <c r="I31" s="7" t="inlineStr">
+      <c r="F37" s="7" t="inlineStr"/>
+      <c r="G37" s="7" t="inlineStr"/>
+      <c r="H37" s="7" t="inlineStr"/>
+      <c r="I37" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on EP profile: {"doctype-df-prefix":["DF PROGRESS"]}
 expect.toEqual // deep equality
@@ -23898,50 +24480,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J31" s="7" t="inlineStr">
+      <c r="J37" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\08-ui-no-backend-leak-PR-T-d694f-e-shows-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K31" s="7" t="inlineStr"/>
-      <c r="L31" s="7" t="inlineStr">
+      <c r="K37" s="7" t="inlineStr"/>
+      <c r="L37" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M31" s="7" t="inlineStr"/>
-      <c r="N31" s="7" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>BUG-030</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="M37" s="7" t="inlineStr"/>
+      <c r="N37" s="7" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>BUG-036</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>PR-TC-UI-LEAK-002</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
         <is>
           <t>PR-TC-UI-LEAK-002 · new EP form header is a friendly label, not the raw doctype</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
+      <c r="E38" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F32" s="7" t="inlineStr"/>
-      <c r="G32" s="7" t="inlineStr"/>
-      <c r="H32" s="7" t="inlineStr"/>
-      <c r="I32" s="7" t="inlineStr">
+      <c r="F38" s="7" t="inlineStr"/>
+      <c r="G38" s="7" t="inlineStr"/>
+      <c r="H38" s="7" t="inlineStr"/>
+      <c r="I38" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on new EP form: {"enterprenur-internal":["Enterprenur"]}
 expect.toEqual // deep equality
@@ -23955,126 +24537,352 @@
 + }</t>
         </is>
       </c>
-      <c r="J32" s="7" t="inlineStr">
+      <c r="J38" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\08-ui-no-backend-leak-PR-T-215c4-y-label-not-the-raw-doctype-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K32" s="7" t="inlineStr"/>
-      <c r="L32" s="7" t="inlineStr">
+      <c r="K38" s="7" t="inlineStr"/>
+      <c r="L38" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M32" s="7" t="inlineStr"/>
-      <c r="N32" s="7" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>BUG-031</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="M38" s="7" t="inlineStr"/>
+      <c r="N38" s="7" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>BUG-037</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-UM-001</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>13. User Management</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>Create a new Field Associate user with all required fields</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>P0 — Blocker</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>• Navigate to User Management workspace → "+ New User".
+• Fill: Email = uat-fa-test01@dhwaniris.com, First Name = UAT, Last Name = FA-Test01, Phone = +91 9876543210.
+• Set Roles: check "Field Associate" only.
+• Set Block restriction = "Laskein" (block-bound).
+• Set Send welcome email = Yes.
+• Click Save.</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>Toast: "User created successfully." User row appears in list with status "Active" and "Welcome email sent". Email arrives at the address within 2 min containing a one-time password-set link. Audit log records the creation with timestamp + creator.</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Error: INSERT User → 417: {"exception":"frappe.exceptions.ValidationError: Error syncing User to User Manager: ('User Manager', 'uat-umc-79v3ss@dhwaniris.com', IntegrityError(1062, \"Duplicate entry '[uat]_crud_user' for key 'username'\"))","exc_type":"ValidationError","_exc_source":"dhwani_frappe_base (app)","exc":"[\"Traceback (most recent call last):\\n  File \\\"apps/frappe/frappe/model/base_document.py\\\", line 755, in db_insert\\n    name = frappe.db.sql(\\n    \\t\\\"\\\"\\\"INSERT INTO </t>
+        </is>
+      </c>
+      <c r="J39" s="7" t="inlineStr"/>
+      <c r="K39" s="7" t="inlineStr">
+        <is>
+          <t>BRD: PR-UJ-CTI §User Management.</t>
+        </is>
+      </c>
+      <c r="L39" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M39" s="7" t="inlineStr"/>
+      <c r="N39" s="7" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>BUG-038</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-UM-009</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>13. User Management</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>Email must be lowercase and trimmed before save</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>P1 — High</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>• Enter email Test@Dhwaniris.COM (leading/trailing spaces, mixed case).</t>
+        </is>
+      </c>
+      <c r="H40" s="7" t="inlineStr"/>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>Error: INSERT User → 417: {"exception":"frappe.exceptions.ValidationError: Error syncing User to User Manager: ('User Manager', 'uat-umn-ztbfos@dhwaniris.com', IntegrityError(1062, \"Duplicate entry '[uat]_norm' for key 'username'\"))","exc_type":"ValidationError","_exc_source":"dhwani_frappe_base (app)","exc":"[\"Traceback (most recent call last):\\n  File \\\"apps/frappe/frappe/model/base_document.py\\\", line 755, in db_insert\\n    name = frappe.db.sql(\\n    \\t\\\"\\\"\\\"INSERT INTO `tab{</t>
+        </is>
+      </c>
+      <c r="J40" s="7" t="inlineStr"/>
+      <c r="K40" s="7" t="inlineStr"/>
+      <c r="L40" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M40" s="7" t="inlineStr"/>
+      <c r="N40" s="7" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>BUG-039</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-UM-010</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>13. User Management</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>Edit user phone, name, block — changes persist</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>P0 — Blocker</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>• Open user uat-fa-test01.
+• Change First Name to "UAT-Updated".
+• Change Block from Laskein to Khliehriat.
+• Save.
+• Log out / log in as that user.</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="inlineStr"/>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>Error: INSERT User → 417: {"exception":"frappe.exceptions.ValidationError: Error syncing User to User Manager: ('User Manager', 'uat-ume-1c8bs5@dhwaniris.com', IntegrityError(1062, \"Duplicate entry '[uat]_before' for key 'username'\"))","exc_type":"ValidationError","_exc_source":"dhwani_frappe_base (app)","exc":"[\"Traceback (most recent call last):\\n  File \\\"apps/frappe/frappe/model/base_document.py\\\", line 755, in db_insert\\n    name = frappe.db.sql(\\n    \\t\\\"\\\"\\\"INSERT INTO `ta</t>
+        </is>
+      </c>
+      <c r="J41" s="7" t="inlineStr"/>
+      <c r="K41" s="7" t="inlineStr"/>
+      <c r="L41" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M41" s="7" t="inlineStr"/>
+      <c r="N41" s="7" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>BUG-040</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-UM-011</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>13. User Management</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Deactivate a user — they cannot log in until reactivated</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>P0 — Blocker</t>
+        </is>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>• Open uat-fa-test01. Set Enabled = No. Save.
+• Sign out, attempt to log in as uat-fa-test01.</t>
+        </is>
+      </c>
+      <c r="H42" s="7" t="inlineStr"/>
+      <c r="I42" s="7" t="inlineStr">
+        <is>
+          <t>Error: INSERT User → 417: {"exception":"frappe.exceptions.ValidationError: Error syncing User to User Manager: ('User Manager', 'uat-umd-0pc24h@dhwaniris.com', IntegrityError(1062, \"Duplicate entry '[uat]_disabled' for key 'username'\"))","exc_type":"ValidationError","_exc_source":"dhwani_frappe_base (app)","exc":"[\"Traceback (most recent call last):\\n  File \\\"apps/frappe/frappe/model/base_document.py\\\", line 755, in db_insert\\n    name = frappe.db.sql(\\n    \\t\\\"\\\"\\\"INSERT INTO `</t>
+        </is>
+      </c>
+      <c r="J42" s="7" t="inlineStr"/>
+      <c r="K42" s="7" t="inlineStr"/>
+      <c r="L42" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M42" s="7" t="inlineStr"/>
+      <c r="N42" s="7" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>BUG-041</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-003</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C43" s="7" t="inlineStr">
         <is>
           <t>4. Application Entry &amp; Routing</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D43" s="7" t="inlineStr">
         <is>
           <t>Deep link to a protected page while logged out preserves the intent</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
+      <c r="E43" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F33" s="7" t="inlineStr">
+      <c r="F43" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G33" s="7" t="inlineStr">
+      <c r="G43" s="7" t="inlineStr">
         <is>
           <t>• Open https://stgprime-rural.dhwaniris.in/app/enterprenur-profile/EP-001 directly.
 • Login redirect fires.
 • Complete login as a user permitted to see that record.</t>
         </is>
       </c>
-      <c r="H33" s="7" t="inlineStr">
+      <c r="H43" s="7" t="inlineStr">
         <is>
           <t>After successful login, user is redirected to the originally requested URL (the EP detail page), not the default landing page. URL parameter (typically redirect-to or next) is preserved through the auth flow.</t>
         </is>
       </c>
-      <c r="I33" s="7" t="inlineStr">
+      <c r="I43" s="7" t="inlineStr">
         <is>
           <t>Error: expect(received).toMatch(expected)
 Expected pattern: /redirect|next|to=/i
 Received string:  "https://stgprime-rural.dhwaniris.in/primerural/login"</t>
         </is>
       </c>
-      <c r="J33" s="7" t="inlineStr">
+      <c r="J43" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\04-entry-PR-TC-XC-ENTRY-·--e9661-t-preserves-redirect-intent-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K33" s="7" t="inlineStr">
+      <c r="K43" s="7" t="inlineStr">
         <is>
           <t>BRD: PR-OV-001 (Auth)</t>
         </is>
       </c>
-      <c r="L33" s="7" t="inlineStr">
+      <c r="L43" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M33" s="7" t="inlineStr"/>
-      <c r="N33" s="7" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>BUG-032</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="M43" s="7" t="inlineStr"/>
+      <c r="N43" s="7" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>BUG-042</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-023</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C44" s="7" t="inlineStr">
         <is>
           <t>6. Responsive Layout &amp; Screen Sizes</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
         <is>
           <t>1024×768 (tablet landscape / iPad / Surface): sidebar collapses to icon rail</t>
         </is>
       </c>
-      <c r="E34" s="7" t="inlineStr">
+      <c r="E44" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F34" s="7" t="inlineStr">
+      <c r="F44" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G34" s="7" t="inlineStr">
+      <c r="G44" s="7" t="inlineStr">
         <is>
           <t>• Resize to 1024×768.</t>
         </is>
       </c>
-      <c r="H34" s="7" t="inlineStr"/>
-      <c r="I34" s="7" t="inlineStr">
+      <c r="H44" s="7" t="inlineStr"/>
+      <c r="I44" s="7" t="inlineStr">
         <is>
           <t>Error: at 1024px the sidebar should collapse to an icon rail; width=240
 expect(received).toBeLessThanOrEqual(expected)
@@ -24082,63 +24890,63 @@
 Received:    240</t>
         </is>
       </c>
-      <c r="J34" s="7" t="inlineStr">
+      <c r="J44" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\06-08-10-nonfunctional-PR--f1c18-ollapses-to-icon-rail-64px--sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K34" s="7" t="inlineStr"/>
-      <c r="L34" s="7" t="inlineStr">
+      <c r="K44" s="7" t="inlineStr"/>
+      <c r="L44" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M34" s="7" t="inlineStr"/>
-      <c r="N34" s="7" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>BUG-033</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="M44" s="7" t="inlineStr"/>
+      <c r="N44" s="7" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>BUG-043</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-032</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>7. Login &amp; Session</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="D45" s="7" t="inlineStr">
         <is>
           <t>Wrong password shows a clear error and does NOT reveal whether the email exists</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="E45" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F35" s="7" t="inlineStr">
+      <c r="F45" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G35" s="7" t="inlineStr">
+      <c r="G45" s="7" t="inlineStr">
         <is>
           <t>• Login form: enter a valid email but wrong password.
 • Submit.</t>
         </is>
       </c>
-      <c r="H35" s="7" t="inlineStr">
+      <c r="H45" s="7" t="inlineStr">
         <is>
           <t>Error displays inline above the form: "Invalid email or password." — generic enough that an attacker cannot enumerate valid emails. The password field is cleared; the email field is preserved. No 500. No password ever echoed back into the field.</t>
         </is>
       </c>
-      <c r="I35" s="7" t="inlineStr">
+      <c r="I45" s="7" t="inlineStr">
         <is>
           <t>Error: login error must be friendly text, not a raw exception class
 expect(locator).not.toContainText(expected) failed
@@ -24149,65 +24957,65 @@
 Call log:
   - login error must be friendly text, not a raw exception class with timeout 10000ms
   - waiting for locator('[role="alert"]').first()
-    23 × locator resolved to &lt;div role="alert" class="bg-d</t>
-        </is>
-      </c>
-      <c r="J35" s="7" t="inlineStr">
+    22 × locator resolved to &lt;div role="alert" class="bg-d</t>
+        </is>
+      </c>
+      <c r="J45" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\07-auth-PR-TC-XC-AUTH-·-Em-429a0-neric-error-no-enumeration--sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K35" s="7" t="inlineStr">
+      <c r="K45" s="7" t="inlineStr">
         <is>
           <t>OWASP A07 Auth Failures (do not leak account existence).</t>
         </is>
       </c>
-      <c r="L35" s="7" t="inlineStr">
+      <c r="L45" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M35" s="7" t="inlineStr"/>
-      <c r="N35" s="7" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>BUG-034</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="M45" s="7" t="inlineStr"/>
+      <c r="N45" s="7" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>BUG-044</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-033</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C46" s="7" t="inlineStr">
         <is>
           <t>7. Login &amp; Session</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
         <is>
           <t>Non-existent email shows the same generic error as wrong password</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="E46" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F36" s="7" t="inlineStr">
+      <c r="F46" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G36" s="7" t="inlineStr">
+      <c r="G46" s="7" t="inlineStr">
         <is>
           <t>• Submit with email not-a-real-user@example.com and any password.</t>
         </is>
       </c>
-      <c r="H36" s="7" t="inlineStr"/>
-      <c r="I36" s="7" t="inlineStr">
+      <c r="H46" s="7" t="inlineStr"/>
+      <c r="I46" s="7" t="inlineStr">
         <is>
           <t>Error: login error must be friendly text, not a raw exception class
 expect(locator).not.toContainText(expected) failed
@@ -24218,178 +25026,178 @@
 Call log:
   - login error must be friendly text, not a raw exception class with timeout 10000ms
   - waiting for locator('[role="alert"]').first()
-    23 × locator resolved to &lt;div role="alert" class="bg-d</t>
-        </is>
-      </c>
-      <c r="J36" s="7" t="inlineStr">
+    22 × locator resolved to &lt;div role="alert" class="bg-d</t>
+        </is>
+      </c>
+      <c r="J46" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\07-auth-PR-TC-XC-AUTH-·-Em-a7adf-ows-identical-generic-error-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K36" s="7" t="inlineStr"/>
-      <c r="L36" s="7" t="inlineStr">
+      <c r="K46" s="7" t="inlineStr"/>
+      <c r="L46" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M36" s="7" t="inlineStr"/>
-      <c r="N36" s="7" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>BUG-035</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="M46" s="7" t="inlineStr"/>
+      <c r="N46" s="7" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>BUG-045</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-052</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="C47" s="7" t="inlineStr">
         <is>
           <t>8. UI / UX Rules — Monsoon Court Compliance</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="D47" s="7" t="inlineStr">
         <is>
           <t>No green and no yellow appear anywhere in the UI</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
+      <c r="E47" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F37" s="7" t="inlineStr">
+      <c r="F47" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G37" s="7" t="inlineStr">
+      <c r="G47" s="7" t="inlineStr">
         <is>
           <t>• Visually scan every page for green / yellow elements.
 • Search the rendered CSS for any colour matching green, yellow, #2ecc71, #f1c40f, similar hexes.</t>
         </is>
       </c>
-      <c r="H37" s="7" t="inlineStr">
+      <c r="H47" s="7" t="inlineStr">
         <is>
           <t>Zero green elements. Success states use teal #0E4D4E. Zero yellow elements. Warning states use terracotta #C26849.</t>
         </is>
       </c>
-      <c r="I37" s="7" t="inlineStr">
+      <c r="I47" s="7" t="inlineStr">
         <is>
           <t>Active Entrepreneurs KPI shows a GREEN check rgb(63,107,58) (hue 114). Monsoon Court forbids green — success must be teal #0E4D4E.</t>
         </is>
       </c>
-      <c r="J37" s="7" t="inlineStr">
+      <c r="J47" s="7" t="inlineStr">
         <is>
           <t>.playwright-mcp/bug-xc052-green-kpi.png</t>
         </is>
       </c>
-      <c r="K37" s="7" t="inlineStr">
+      <c r="K47" s="7" t="inlineStr">
         <is>
           <t>Monsoon Court §2.7 (brand non-negotiables).</t>
         </is>
       </c>
-      <c r="L37" s="7" t="inlineStr">
+      <c r="L47" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M37" s="7" t="inlineStr"/>
-      <c r="N37" s="7" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>BUG-036</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="M47" s="7" t="inlineStr"/>
+      <c r="N47" s="7" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>BUG-046</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-054</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
+      <c r="C48" s="7" t="inlineStr">
         <is>
           <t>8. UI / UX Rules — Monsoon Court Compliance</t>
         </is>
       </c>
-      <c r="D38" s="7" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr">
         <is>
           <t>Required-field marker is a terracotta asterisk, not "(required)" text</t>
         </is>
       </c>
-      <c r="E38" s="7" t="inlineStr">
+      <c r="E48" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F38" s="7" t="inlineStr">
+      <c r="F48" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G38" s="7" t="inlineStr">
+      <c r="G48" s="7" t="inlineStr">
         <is>
           <t>• Open the EP form. Find a required field (e.g. Entrepreneur Name).</t>
         </is>
       </c>
-      <c r="H38" s="7" t="inlineStr"/>
-      <c r="I38" s="7" t="inlineStr">
+      <c r="H48" s="7" t="inlineStr"/>
+      <c r="I48" s="7" t="inlineStr">
         <is>
           <t>Asterisk on the name label is taupe rgb(107,99,89) (inherits label ink-soft), NOT terracotta #C26849. Marker present but wrong colour.</t>
         </is>
       </c>
-      <c r="J38" s="7" t="inlineStr"/>
-      <c r="K38" s="7" t="inlineStr"/>
-      <c r="L38" s="7" t="inlineStr">
+      <c r="J48" s="7" t="inlineStr"/>
+      <c r="K48" s="7" t="inlineStr"/>
+      <c r="L48" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M38" s="7" t="inlineStr"/>
-      <c r="N38" s="7" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>BUG-037</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="M48" s="7" t="inlineStr"/>
+      <c r="N48" s="7" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>BUG-047</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-063</t>
         </is>
       </c>
-      <c r="C39" s="7" t="inlineStr">
+      <c r="C49" s="7" t="inlineStr">
         <is>
           <t>9. Accessibility — WCAG 2.2 AA</t>
         </is>
       </c>
-      <c r="D39" s="7" t="inlineStr">
+      <c r="D49" s="7" t="inlineStr">
         <is>
           <t>Form fields have associated labels (axe-core "label" rule passes)</t>
         </is>
       </c>
-      <c r="E39" s="7" t="inlineStr">
+      <c r="E49" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F39" s="7" t="inlineStr">
+      <c r="F49" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G39" s="7" t="inlineStr">
+      <c r="G49" s="7" t="inlineStr">
         <is>
           <t>• Run axe-core on the EP form (via Playwright).</t>
         </is>
       </c>
-      <c r="H39" s="7" t="inlineStr"/>
-      <c r="I39" s="7" t="inlineStr">
+      <c r="H49" s="7" t="inlineStr"/>
+      <c r="I49" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: label violations: [{"id":"label","n":6}]
 expect(received).toEqual(expected) // deep equality
@@ -24409,58 +25217,58 @@
 +        </t>
         </is>
       </c>
-      <c r="J39" s="7" t="inlineStr">
+      <c r="J49" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\09-a11y-PR-TC-XC-063-·-for-17d03-ssociated-labels-axe-label--sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K39" s="7" t="inlineStr"/>
-      <c r="L39" s="7" t="inlineStr">
+      <c r="K49" s="7" t="inlineStr"/>
+      <c r="L49" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M39" s="7" t="inlineStr"/>
-      <c r="N39" s="7" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>BUG-038</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="M49" s="7" t="inlineStr"/>
+      <c r="N49" s="7" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>BUG-048</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-064</t>
         </is>
       </c>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="C50" s="7" t="inlineStr">
         <is>
           <t>9. Accessibility — WCAG 2.2 AA</t>
         </is>
       </c>
-      <c r="D40" s="7" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
         <is>
           <t>Colour contrast meets WCAG AA</t>
         </is>
       </c>
-      <c r="E40" s="7" t="inlineStr">
+      <c r="E50" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F40" s="7" t="inlineStr">
+      <c r="F50" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G40" s="7" t="inlineStr">
+      <c r="G50" s="7" t="inlineStr">
         <is>
           <t>• Run axe-core's contrast check on EP detail, dashboard, framework form.</t>
         </is>
       </c>
-      <c r="H40" s="7" t="inlineStr"/>
-      <c r="I40" s="7" t="inlineStr">
+      <c r="H50" s="7" t="inlineStr"/>
+      <c r="I50" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: contrast violations: [10]
 expect(received).toEqual(expected) // deep equality
@@ -24476,50 +25284,50 @@
 </t>
         </is>
       </c>
-      <c r="J40" s="7" t="inlineStr">
+      <c r="J50" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\09-a11y-PR-TC-XC-064-·-col-8baa1-WCAG-AA-axe-color-contrast--sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K40" s="7" t="inlineStr"/>
-      <c r="L40" s="7" t="inlineStr">
+      <c r="K50" s="7" t="inlineStr"/>
+      <c r="L50" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M40" s="7" t="inlineStr"/>
-      <c r="N40" s="7" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>BUG-039</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
+      <c r="M50" s="7" t="inlineStr"/>
+      <c r="N50" s="7" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>BUG-049</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-064b</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="C51" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D41" s="7" t="inlineStr">
+      <c r="D51" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-064b · landscape colour contrast (WCAG AA)</t>
         </is>
       </c>
-      <c r="E41" s="7" t="inlineStr">
+      <c r="E51" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F41" s="7" t="inlineStr"/>
-      <c r="G41" s="7" t="inlineStr"/>
-      <c r="H41" s="7" t="inlineStr"/>
-      <c r="I41" s="7" t="inlineStr">
+      <c r="F51" s="7" t="inlineStr"/>
+      <c r="G51" s="7" t="inlineStr"/>
+      <c r="H51" s="7" t="inlineStr"/>
+      <c r="I51" s="7" t="inlineStr">
         <is>
           <t>Error: landscape contrast nodes: 4
 expect(received).toEqual(expected) // deep equality
@@ -24534,19 +25342,19 @@
 +     "id": "color-contrast"</t>
         </is>
       </c>
-      <c r="J41" s="7" t="inlineStr">
+      <c r="J51" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\09-a11y-PR-TC-XC-064b-·-landscape-colour-contrast-WCAG-AA--sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K41" s="7" t="inlineStr"/>
-      <c r="L41" s="7" t="inlineStr">
+      <c r="K51" s="7" t="inlineStr"/>
+      <c r="L51" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M41" s="7" t="inlineStr"/>
-      <c r="N41" s="7" t="inlineStr"/>
+      <c r="M51" s="7" t="inlineStr"/>
+      <c r="N51" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -11235,8 +11235,16 @@
       </c>
       <c r="L148" s="7" t="inlineStr"/>
       <c r="M148" s="7" t="inlineStr"/>
-      <c r="N148" s="8" t="inlineStr"/>
-      <c r="O148" s="7" t="inlineStr"/>
+      <c r="N148" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O148" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P148" s="8" t="inlineStr"/>
       <c r="Q148" s="7" t="inlineStr"/>
     </row>
@@ -11295,8 +11303,16 @@
       </c>
       <c r="L149" s="7" t="inlineStr"/>
       <c r="M149" s="7" t="inlineStr"/>
-      <c r="N149" s="8" t="inlineStr"/>
-      <c r="O149" s="7" t="inlineStr"/>
+      <c r="N149" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O149" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P149" s="8" t="inlineStr"/>
       <c r="Q149" s="7" t="inlineStr"/>
     </row>
@@ -11354,8 +11370,16 @@
       </c>
       <c r="L150" s="7" t="inlineStr"/>
       <c r="M150" s="7" t="inlineStr"/>
-      <c r="N150" s="8" t="inlineStr"/>
-      <c r="O150" s="7" t="inlineStr"/>
+      <c r="N150" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O150" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P150" s="8" t="inlineStr"/>
       <c r="Q150" s="7" t="inlineStr"/>
     </row>
@@ -11416,9 +11440,24 @@
       </c>
       <c r="L151" s="7" t="inlineStr"/>
       <c r="M151" s="7" t="inlineStr"/>
-      <c r="N151" s="8" t="inlineStr"/>
-      <c r="O151" s="7" t="inlineStr"/>
-      <c r="P151" s="8" t="inlineStr"/>
+      <c r="N151" s="12" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O151" s="7" t="inlineStr">
+        <is>
+          <t>Error: EP without Sector/District should be rejected (BRD requires them)
+expect(received).toBeGreaterThanOrEqual(expected)
+Expected: &gt;= 400
+Received:    200</t>
+        </is>
+      </c>
+      <c r="P151" s="8" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
       <c r="Q151" s="7" t="inlineStr"/>
     </row>
     <row r="152">
@@ -11476,8 +11515,16 @@
       </c>
       <c r="L152" s="7" t="inlineStr"/>
       <c r="M152" s="7" t="inlineStr"/>
-      <c r="N152" s="8" t="inlineStr"/>
-      <c r="O152" s="7" t="inlineStr"/>
+      <c r="N152" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O152" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P152" s="8" t="inlineStr"/>
       <c r="Q152" s="7" t="inlineStr"/>
     </row>
@@ -11537,9 +11584,24 @@
       </c>
       <c r="L153" s="7" t="inlineStr"/>
       <c r="M153" s="7" t="inlineStr"/>
-      <c r="N153" s="8" t="inlineStr"/>
-      <c r="O153" s="7" t="inlineStr"/>
-      <c r="P153" s="8" t="inlineStr"/>
+      <c r="N153" s="12" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O153" s="7" t="inlineStr">
+        <is>
+          <t>Error: future date of birth should be rejected
+expect(received).toBeGreaterThanOrEqual(expected)
+Expected: &gt;= 400
+Received:    200</t>
+        </is>
+      </c>
+      <c r="P153" s="8" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
       <c r="Q153" s="7" t="inlineStr"/>
     </row>
     <row r="154">
@@ -11596,8 +11658,16 @@
       </c>
       <c r="L154" s="7" t="inlineStr"/>
       <c r="M154" s="7" t="inlineStr"/>
-      <c r="N154" s="8" t="inlineStr"/>
-      <c r="O154" s="7" t="inlineStr"/>
+      <c r="N154" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O154" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P154" s="8" t="inlineStr"/>
       <c r="Q154" s="7" t="inlineStr"/>
     </row>
@@ -11655,8 +11725,16 @@
       </c>
       <c r="L155" s="7" t="inlineStr"/>
       <c r="M155" s="7" t="inlineStr"/>
-      <c r="N155" s="8" t="inlineStr"/>
-      <c r="O155" s="7" t="inlineStr"/>
+      <c r="N155" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O155" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P155" s="8" t="inlineStr"/>
       <c r="Q155" s="7" t="inlineStr"/>
     </row>
@@ -11714,8 +11792,16 @@
       </c>
       <c r="L156" s="7" t="inlineStr"/>
       <c r="M156" s="7" t="inlineStr"/>
-      <c r="N156" s="8" t="inlineStr"/>
-      <c r="O156" s="7" t="inlineStr"/>
+      <c r="N156" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O156" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P156" s="8" t="inlineStr"/>
       <c r="Q156" s="7" t="inlineStr"/>
     </row>
@@ -11774,8 +11860,16 @@
       </c>
       <c r="L157" s="7" t="inlineStr"/>
       <c r="M157" s="7" t="inlineStr"/>
-      <c r="N157" s="8" t="inlineStr"/>
-      <c r="O157" s="7" t="inlineStr"/>
+      <c r="N157" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O157" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P157" s="8" t="inlineStr"/>
       <c r="Q157" s="7" t="inlineStr"/>
     </row>
@@ -11833,8 +11927,16 @@
       </c>
       <c r="L158" s="7" t="inlineStr"/>
       <c r="M158" s="7" t="inlineStr"/>
-      <c r="N158" s="8" t="inlineStr"/>
-      <c r="O158" s="7" t="inlineStr"/>
+      <c r="N158" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O158" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P158" s="8" t="inlineStr"/>
       <c r="Q158" s="7" t="inlineStr"/>
     </row>
@@ -11900,8 +12002,16 @@
           <t>OWASP A03 Injection / A05 Security Misconfig (file upload).</t>
         </is>
       </c>
-      <c r="N159" s="8" t="inlineStr"/>
-      <c r="O159" s="7" t="inlineStr"/>
+      <c r="N159" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O159" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P159" s="8" t="inlineStr"/>
       <c r="Q159" s="7" t="inlineStr"/>
     </row>
@@ -11961,8 +12071,16 @@
       </c>
       <c r="L160" s="7" t="inlineStr"/>
       <c r="M160" s="7" t="inlineStr"/>
-      <c r="N160" s="8" t="inlineStr"/>
-      <c r="O160" s="7" t="inlineStr"/>
+      <c r="N160" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O160" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P160" s="8" t="inlineStr"/>
       <c r="Q160" s="7" t="inlineStr"/>
     </row>
@@ -12021,8 +12139,16 @@
       </c>
       <c r="L161" s="7" t="inlineStr"/>
       <c r="M161" s="7" t="inlineStr"/>
-      <c r="N161" s="8" t="inlineStr"/>
-      <c r="O161" s="7" t="inlineStr"/>
+      <c r="N161" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O161" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P161" s="8" t="inlineStr"/>
       <c r="Q161" s="7" t="inlineStr"/>
     </row>
@@ -12090,9 +12216,27 @@
           <t>BRD Decision: Fellow fills 10Q + Rural E-Champ during profiling.</t>
         </is>
       </c>
-      <c r="N162" s="8" t="inlineStr"/>
-      <c r="O162" s="7" t="inlineStr"/>
-      <c r="P162" s="8" t="inlineStr"/>
+      <c r="N162" s="12" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O162" s="7" t="inlineStr">
+        <is>
+          <t>Error: avg_rating should compute to ~0.7 (got 3.5)
+expect(received).toBeCloseTo(expected, precision)
+Expected: 0.7
+Received: 3.5
+Expected precision:    1
+Expected difference: &lt; 0.05
+Received difference:   2.8</t>
+        </is>
+      </c>
+      <c r="P162" s="8" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
       <c r="Q162" s="7" t="inlineStr"/>
     </row>
     <row r="163">
@@ -12149,8 +12293,16 @@
       </c>
       <c r="L163" s="7" t="inlineStr"/>
       <c r="M163" s="7" t="inlineStr"/>
-      <c r="N163" s="8" t="inlineStr"/>
-      <c r="O163" s="7" t="inlineStr"/>
+      <c r="N163" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O163" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P163" s="8" t="inlineStr"/>
       <c r="Q163" s="7" t="inlineStr"/>
     </row>
@@ -12209,8 +12361,16 @@
       </c>
       <c r="L164" s="7" t="inlineStr"/>
       <c r="M164" s="7" t="inlineStr"/>
-      <c r="N164" s="8" t="inlineStr"/>
-      <c r="O164" s="7" t="inlineStr"/>
+      <c r="N164" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O164" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P164" s="8" t="inlineStr"/>
       <c r="Q164" s="7" t="inlineStr"/>
     </row>
@@ -12276,8 +12436,16 @@
           <t>BRD: Final Incubated/Supported is CTIT-only.</t>
         </is>
       </c>
-      <c r="N165" s="8" t="inlineStr"/>
-      <c r="O165" s="7" t="inlineStr"/>
+      <c r="N165" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O165" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P165" s="8" t="inlineStr"/>
       <c r="Q165" s="7" t="inlineStr"/>
     </row>
@@ -12344,8 +12512,16 @@
           <t>BRD: 3-state model (MET / Incubated / Supported).</t>
         </is>
       </c>
-      <c r="N166" s="8" t="inlineStr"/>
-      <c r="O166" s="7" t="inlineStr"/>
+      <c r="N166" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O166" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P166" s="8" t="inlineStr"/>
       <c r="Q166" s="7" t="inlineStr"/>
     </row>
@@ -12403,8 +12579,16 @@
       </c>
       <c r="L167" s="7" t="inlineStr"/>
       <c r="M167" s="7" t="inlineStr"/>
-      <c r="N167" s="8" t="inlineStr"/>
-      <c r="O167" s="7" t="inlineStr"/>
+      <c r="N167" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O167" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P167" s="8" t="inlineStr"/>
       <c r="Q167" s="7" t="inlineStr"/>
     </row>
@@ -12474,8 +12658,16 @@
           <t>BRD: Decision — Framework Prioritisation by CTIT or Fellow.</t>
         </is>
       </c>
-      <c r="N168" s="8" t="inlineStr"/>
-      <c r="O168" s="7" t="inlineStr"/>
+      <c r="N168" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O168" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P168" s="8" t="inlineStr"/>
       <c r="Q168" s="7" t="inlineStr"/>
     </row>
@@ -12533,8 +12725,16 @@
       </c>
       <c r="L169" s="7" t="inlineStr"/>
       <c r="M169" s="7" t="inlineStr"/>
-      <c r="N169" s="8" t="inlineStr"/>
-      <c r="O169" s="7" t="inlineStr"/>
+      <c r="N169" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O169" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P169" s="8" t="inlineStr"/>
       <c r="Q169" s="7" t="inlineStr"/>
     </row>
@@ -12592,8 +12792,16 @@
       </c>
       <c r="L170" s="7" t="inlineStr"/>
       <c r="M170" s="7" t="inlineStr"/>
-      <c r="N170" s="8" t="inlineStr"/>
-      <c r="O170" s="7" t="inlineStr"/>
+      <c r="N170" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O170" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P170" s="8" t="inlineStr"/>
       <c r="Q170" s="7" t="inlineStr"/>
     </row>
@@ -12659,8 +12867,16 @@
           <t>BRD: PR-EP-001 (EP Profile Dashboard).</t>
         </is>
       </c>
-      <c r="N171" s="8" t="inlineStr"/>
-      <c r="O171" s="7" t="inlineStr"/>
+      <c r="N171" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O171" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P171" s="8" t="inlineStr"/>
       <c r="Q171" s="7" t="inlineStr"/>
     </row>
@@ -12727,8 +12943,16 @@
           <t>BRD: EP Profile Dashboard — "+ Add New Product" tile decision.</t>
         </is>
       </c>
-      <c r="N172" s="8" t="inlineStr"/>
-      <c r="O172" s="7" t="inlineStr"/>
+      <c r="N172" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O172" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P172" s="8" t="inlineStr"/>
       <c r="Q172" s="7" t="inlineStr"/>
     </row>
@@ -12786,8 +13010,16 @@
       </c>
       <c r="L173" s="7" t="inlineStr"/>
       <c r="M173" s="7" t="inlineStr"/>
-      <c r="N173" s="8" t="inlineStr"/>
-      <c r="O173" s="7" t="inlineStr"/>
+      <c r="N173" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O173" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P173" s="8" t="inlineStr"/>
       <c r="Q173" s="7" t="inlineStr"/>
     </row>
@@ -12846,8 +13078,16 @@
       </c>
       <c r="L174" s="7" t="inlineStr"/>
       <c r="M174" s="7" t="inlineStr"/>
-      <c r="N174" s="8" t="inlineStr"/>
-      <c r="O174" s="7" t="inlineStr"/>
+      <c r="N174" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O174" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P174" s="8" t="inlineStr"/>
       <c r="Q174" s="7" t="inlineStr"/>
     </row>
@@ -12905,8 +13145,16 @@
       </c>
       <c r="L175" s="7" t="inlineStr"/>
       <c r="M175" s="7" t="inlineStr"/>
-      <c r="N175" s="8" t="inlineStr"/>
-      <c r="O175" s="7" t="inlineStr"/>
+      <c r="N175" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O175" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P175" s="8" t="inlineStr"/>
       <c r="Q175" s="7" t="inlineStr"/>
     </row>
@@ -12964,8 +13212,16 @@
       </c>
       <c r="L176" s="7" t="inlineStr"/>
       <c r="M176" s="7" t="inlineStr"/>
-      <c r="N176" s="8" t="inlineStr"/>
-      <c r="O176" s="7" t="inlineStr"/>
+      <c r="N176" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O176" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P176" s="8" t="inlineStr"/>
       <c r="Q176" s="7" t="inlineStr"/>
     </row>
@@ -13110,8 +13366,16 @@
           <t>BRD: EP Status Monitor + List filters (Cohort / Sector / Basket added).</t>
         </is>
       </c>
-      <c r="N178" s="8" t="inlineStr"/>
-      <c r="O178" s="7" t="inlineStr"/>
+      <c r="N178" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O178" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P178" s="8" t="inlineStr"/>
       <c r="Q178" s="7" t="inlineStr"/>
     </row>
@@ -13170,8 +13434,16 @@
       </c>
       <c r="L179" s="7" t="inlineStr"/>
       <c r="M179" s="7" t="inlineStr"/>
-      <c r="N179" s="8" t="inlineStr"/>
-      <c r="O179" s="7" t="inlineStr"/>
+      <c r="N179" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O179" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P179" s="8" t="inlineStr"/>
       <c r="Q179" s="7" t="inlineStr"/>
     </row>
@@ -13229,8 +13501,16 @@
       </c>
       <c r="L180" s="7" t="inlineStr"/>
       <c r="M180" s="7" t="inlineStr"/>
-      <c r="N180" s="8" t="inlineStr"/>
-      <c r="O180" s="7" t="inlineStr"/>
+      <c r="N180" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O180" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P180" s="8" t="inlineStr"/>
       <c r="Q180" s="7" t="inlineStr"/>
     </row>
@@ -13298,8 +13578,16 @@
           <t>BRD: Networking &amp; Mentoring module.</t>
         </is>
       </c>
-      <c r="N181" s="8" t="inlineStr"/>
-      <c r="O181" s="7" t="inlineStr"/>
+      <c r="N181" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O181" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P181" s="8" t="inlineStr"/>
       <c r="Q181" s="7" t="inlineStr"/>
     </row>
@@ -13359,8 +13647,16 @@
       </c>
       <c r="L182" s="7" t="inlineStr"/>
       <c r="M182" s="7" t="inlineStr"/>
-      <c r="N182" s="8" t="inlineStr"/>
-      <c r="O182" s="7" t="inlineStr"/>
+      <c r="N182" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O182" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P182" s="8" t="inlineStr"/>
       <c r="Q182" s="7" t="inlineStr"/>
     </row>
@@ -13418,8 +13714,16 @@
       </c>
       <c r="L183" s="7" t="inlineStr"/>
       <c r="M183" s="7" t="inlineStr"/>
-      <c r="N183" s="8" t="inlineStr"/>
-      <c r="O183" s="7" t="inlineStr"/>
+      <c r="N183" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O183" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P183" s="8" t="inlineStr"/>
       <c r="Q183" s="7" t="inlineStr"/>
     </row>
@@ -13486,8 +13790,16 @@
           <t>BRD Rule 8: Log Book is per-framework but EP-level aggregate is the EP's Log Book.</t>
         </is>
       </c>
-      <c r="N184" s="8" t="inlineStr"/>
-      <c r="O184" s="7" t="inlineStr"/>
+      <c r="N184" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O184" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P184" s="8" t="inlineStr"/>
       <c r="Q184" s="7" t="inlineStr"/>
     </row>
@@ -13617,8 +13929,16 @@
       </c>
       <c r="L186" s="7" t="inlineStr"/>
       <c r="M186" s="7" t="inlineStr"/>
-      <c r="N186" s="8" t="inlineStr"/>
-      <c r="O186" s="7" t="inlineStr"/>
+      <c r="N186" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O186" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P186" s="8" t="inlineStr"/>
       <c r="Q186" s="7" t="inlineStr"/>
     </row>
@@ -13676,8 +13996,16 @@
       </c>
       <c r="L187" s="7" t="inlineStr"/>
       <c r="M187" s="7" t="inlineStr"/>
-      <c r="N187" s="8" t="inlineStr"/>
-      <c r="O187" s="7" t="inlineStr"/>
+      <c r="N187" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O187" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P187" s="8" t="inlineStr"/>
       <c r="Q187" s="7" t="inlineStr"/>
     </row>
@@ -13735,8 +14063,16 @@
       </c>
       <c r="L188" s="7" t="inlineStr"/>
       <c r="M188" s="7" t="inlineStr"/>
-      <c r="N188" s="8" t="inlineStr"/>
-      <c r="O188" s="7" t="inlineStr"/>
+      <c r="N188" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O188" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P188" s="8" t="inlineStr"/>
       <c r="Q188" s="7" t="inlineStr"/>
     </row>
@@ -13795,8 +14131,16 @@
       </c>
       <c r="L189" s="7" t="inlineStr"/>
       <c r="M189" s="7" t="inlineStr"/>
-      <c r="N189" s="8" t="inlineStr"/>
-      <c r="O189" s="7" t="inlineStr"/>
+      <c r="N189" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O189" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P189" s="8" t="inlineStr"/>
       <c r="Q189" s="7" t="inlineStr"/>
     </row>
@@ -13854,8 +14198,16 @@
       </c>
       <c r="L190" s="7" t="inlineStr"/>
       <c r="M190" s="7" t="inlineStr"/>
-      <c r="N190" s="8" t="inlineStr"/>
-      <c r="O190" s="7" t="inlineStr"/>
+      <c r="N190" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O190" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P190" s="8" t="inlineStr"/>
       <c r="Q190" s="7" t="inlineStr"/>
     </row>
@@ -13913,8 +14265,16 @@
       </c>
       <c r="L191" s="7" t="inlineStr"/>
       <c r="M191" s="7" t="inlineStr"/>
-      <c r="N191" s="8" t="inlineStr"/>
-      <c r="O191" s="7" t="inlineStr"/>
+      <c r="N191" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O191" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P191" s="8" t="inlineStr"/>
       <c r="Q191" s="7" t="inlineStr"/>
     </row>
@@ -22429,7 +22789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N51"/>
+  <dimension ref="A1:N54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -23065,7 +23425,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-EP-031</t>
+          <t>PR-TC-EP-005</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -23075,7 +23435,7 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>EP list columns: Avatar, Name, Sector, Block, Status, Cohort, Last activity, Actions</t>
+          <t>Required fields enforced: Name, Sector, District, Block, Village</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -23090,11 +23450,194 @@
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>• Open EP list.</t>
+          <t>• Save with all fields blank.
+• Fill only Name; save.
+• Fill Name + Sector; save.
+• Continue progressively.</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr"/>
       <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Error: EP without Sector/District should be rejected (BRD requires them)
+expect(received).toBeGreaterThanOrEqual(expected)
+Expected: &gt;= 400
+Received:    200</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr"/>
+      <c r="K13" s="7" t="inlineStr"/>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M13" s="7" t="inlineStr"/>
+      <c r="N13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>BUG-012</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-EP-007</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>15. Entrepreneur Profile — Full Lifecycle</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>DOB validation: not future, not &amp;gt; 100 years old, not &amp;lt; 14 years old</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>P0 — Blocker</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>• DOB = tomorrow. Save.
+• DOB = 31-Dec-1899 (&gt; 100 years).
+• DOB = today - 10 years.</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr"/>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>Error: future date of birth should be rejected
+expect(received).toBeGreaterThanOrEqual(expected)
+Expected: &gt;= 400
+Received:    200</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr"/>
+      <c r="K14" s="7" t="inlineStr"/>
+      <c r="L14" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M14" s="7" t="inlineStr"/>
+      <c r="N14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>BUG-013</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-EP-016</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>15. Entrepreneur Profile — Full Lifecycle</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>FA fills all 10 ratings (0-1 scale) during profiling — avg_rating auto-computes</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>P0 — Blocker</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>• Open EP → Selection tab → Field Evaluation section.
+• Set all 10 ratings to 0.7.
+• Save.</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>avg_rating shows 0.70 (auto-computed). Save succeeds. Recomputes immediately on any rating change.</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>Error: avg_rating should compute to ~0.7 (got 3.5)
+expect(received).toBeCloseTo(expected, precision)
+Expected: 0.7
+Received: 3.5
+Expected precision:    1
+Expected difference: &lt; 0.05
+Received difference:   2.8</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr"/>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>BRD Decision: Fellow fills 10Q + Rural E-Champ during profiling.</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M15" s="7" t="inlineStr"/>
+      <c r="N15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>BUG-014</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-EP-031</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>15. Entrepreneur Profile — Full Lifecycle</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>EP list columns: Avatar, Name, Sector, Block, Status, Cohort, Last activity, Actions</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>P0 — Blocker</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>• Open EP list.</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr"/>
+      <c r="I16" s="7" t="inlineStr">
         <is>
           <t>Error: expect(locator).toBeVisible() failed
 Locator: getByRole('navigation').getByRole('link', { name: 'Entrepreneur List' })
@@ -23106,50 +23649,50 @@
   - waiting for getByRole('navigation').getByRole('link', { name: 'Entrepreneur List' })</t>
         </is>
       </c>
-      <c r="J13" s="7" t="inlineStr">
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\15-ep-profile-PR-TC-EP-·-E-77dc1--031-·-EP-list-page-renders-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K13" s="7" t="inlineStr"/>
-      <c r="L13" s="7" t="inlineStr">
+      <c r="K16" s="7" t="inlineStr"/>
+      <c r="L16" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M13" s="7" t="inlineStr"/>
-      <c r="N13" s="7" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>BUG-012</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="M16" s="7" t="inlineStr"/>
+      <c r="N16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>BUG-015</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-BPC-002</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-BPC-002 · Business Plan Canvas header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr"/>
-      <c r="G14" s="7" t="inlineStr"/>
-      <c r="H14" s="7" t="inlineStr"/>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="F17" s="7" t="inlineStr"/>
+      <c r="G17" s="7" t="inlineStr"/>
+      <c r="H17" s="7" t="inlineStr"/>
+      <c r="I17" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Business Plan Canvas: {"doctype-df-prefix":["DF BUSINESS"]}
 expect.toEqual // deep equality
@@ -23163,50 +23706,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J14" s="7" t="inlineStr">
+      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Bu-a8fd3-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K14" s="7" t="inlineStr"/>
-      <c r="L14" s="7" t="inlineStr">
+      <c r="K17" s="7" t="inlineStr"/>
+      <c r="L17" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M14" s="7" t="inlineStr"/>
-      <c r="N14" s="7" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>BUG-013</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="M17" s="7" t="inlineStr"/>
+      <c r="N17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>BUG-016</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-BREG-002</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-BREG-002 · Business Registration header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E18" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr"/>
-      <c r="G15" s="7" t="inlineStr"/>
-      <c r="H15" s="7" t="inlineStr"/>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="F18" s="7" t="inlineStr"/>
+      <c r="G18" s="7" t="inlineStr"/>
+      <c r="H18" s="7" t="inlineStr"/>
+      <c r="I18" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Business Registration: {"doctype-df-prefix":["DF BUSINESS"]}
 expect.toEqual // deep equality
@@ -23220,50 +23763,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J15" s="7" t="inlineStr">
+      <c r="J18" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Bu-6c730-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K15" s="7" t="inlineStr"/>
-      <c r="L15" s="7" t="inlineStr">
+      <c r="K18" s="7" t="inlineStr"/>
+      <c r="L18" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M15" s="7" t="inlineStr"/>
-      <c r="N15" s="7" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>BUG-014</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="M18" s="7" t="inlineStr"/>
+      <c r="N18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>BUG-017</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-CA-002</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-CA-002 · Customer Analysis header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr"/>
-      <c r="G16" s="7" t="inlineStr"/>
-      <c r="H16" s="7" t="inlineStr"/>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr"/>
+      <c r="G19" s="7" t="inlineStr"/>
+      <c r="H19" s="7" t="inlineStr"/>
+      <c r="I19" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Customer Analysis: {"doctype-df-prefix":["DF CUSTOMER"]}
 expect.toEqual // deep equality
@@ -23277,50 +23820,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J16" s="7" t="inlineStr">
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Cu-6ed58-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K16" s="7" t="inlineStr"/>
-      <c r="L16" s="7" t="inlineStr">
+      <c r="K19" s="7" t="inlineStr"/>
+      <c r="L19" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M16" s="7" t="inlineStr"/>
-      <c r="N16" s="7" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>BUG-015</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="M19" s="7" t="inlineStr"/>
+      <c r="N19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>BUG-018</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-CB-002</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-CB-002 · Capacity Building header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr"/>
-      <c r="G17" s="7" t="inlineStr"/>
-      <c r="H17" s="7" t="inlineStr"/>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="F20" s="7" t="inlineStr"/>
+      <c r="G20" s="7" t="inlineStr"/>
+      <c r="H20" s="7" t="inlineStr"/>
+      <c r="I20" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Capacity Building: {"doctype-df-prefix":["DF CAPACITY"]}
 expect.toEqual // deep equality
@@ -23334,50 +23877,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J17" s="7" t="inlineStr">
+      <c r="J20" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Ca-83199-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K17" s="7" t="inlineStr"/>
-      <c r="L17" s="7" t="inlineStr">
+      <c r="K20" s="7" t="inlineStr"/>
+      <c r="L20" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M17" s="7" t="inlineStr"/>
-      <c r="N17" s="7" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>BUG-016</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="M20" s="7" t="inlineStr"/>
+      <c r="N20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>BUG-019</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-DL-002</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-DL-002 · Digital Literacy header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr"/>
-      <c r="G18" s="7" t="inlineStr"/>
-      <c r="H18" s="7" t="inlineStr"/>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="F21" s="7" t="inlineStr"/>
+      <c r="G21" s="7" t="inlineStr"/>
+      <c r="H21" s="7" t="inlineStr"/>
+      <c r="I21" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Digital Literacy: {"doctype-df-prefix":["DF DIGITAL"]}
 expect.toEqual // deep equality
@@ -23391,50 +23934,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J18" s="7" t="inlineStr">
+      <c r="J21" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Di-845ef-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K18" s="7" t="inlineStr"/>
-      <c r="L18" s="7" t="inlineStr">
+      <c r="K21" s="7" t="inlineStr"/>
+      <c r="L21" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M18" s="7" t="inlineStr"/>
-      <c r="N18" s="7" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>BUG-017</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="M21" s="7" t="inlineStr"/>
+      <c r="N21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>BUG-020</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-INFR-002</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-INFR-002 · Infrastructure (BE/EE/CE) header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr"/>
-      <c r="G19" s="7" t="inlineStr"/>
-      <c r="H19" s="7" t="inlineStr"/>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="F22" s="7" t="inlineStr"/>
+      <c r="G22" s="7" t="inlineStr"/>
+      <c r="H22" s="7" t="inlineStr"/>
+      <c r="I22" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Infrastructure: {"doctype-df-prefix":["DF INFRASTRUCTURE"]}
 expect.toEqual // deep equality
@@ -23448,50 +23991,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J19" s="7" t="inlineStr">
+      <c r="J22" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-In-3328d-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K19" s="7" t="inlineStr"/>
-      <c r="L19" s="7" t="inlineStr">
+      <c r="K22" s="7" t="inlineStr"/>
+      <c r="L22" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M19" s="7" t="inlineStr"/>
-      <c r="N19" s="7" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>BUG-018</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="M22" s="7" t="inlineStr"/>
+      <c r="N22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>BUG-021</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-LABL-002</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-LABL-002 · Marketing Label header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr"/>
-      <c r="G20" s="7" t="inlineStr"/>
-      <c r="H20" s="7" t="inlineStr"/>
-      <c r="I20" s="7" t="inlineStr">
+      <c r="F23" s="7" t="inlineStr"/>
+      <c r="G23" s="7" t="inlineStr"/>
+      <c r="H23" s="7" t="inlineStr"/>
+      <c r="I23" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Marketing Label: {"doctype-df-prefix":["DF MARKETING"]}
 expect.toEqual // deep equality
@@ -23505,50 +24048,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J20" s="7" t="inlineStr">
+      <c r="J23" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Ma-11834-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K20" s="7" t="inlineStr"/>
-      <c r="L20" s="7" t="inlineStr">
+      <c r="K23" s="7" t="inlineStr"/>
+      <c r="L23" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M20" s="7" t="inlineStr"/>
-      <c r="N20" s="7" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>BUG-019</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="M23" s="7" t="inlineStr"/>
+      <c r="N23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>BUG-022</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-ML-002</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-ML-002 · Market Linkage header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr"/>
-      <c r="G21" s="7" t="inlineStr"/>
-      <c r="H21" s="7" t="inlineStr"/>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="F24" s="7" t="inlineStr"/>
+      <c r="G24" s="7" t="inlineStr"/>
+      <c r="H24" s="7" t="inlineStr"/>
+      <c r="I24" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Market Linkage: {"doctype-df-prefix":["DF MARKET"]}
 expect.toEqual // deep equality
@@ -23562,50 +24105,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J21" s="7" t="inlineStr">
+      <c r="J24" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Ma-22f69-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K21" s="7" t="inlineStr"/>
-      <c r="L21" s="7" t="inlineStr">
+      <c r="K24" s="7" t="inlineStr"/>
+      <c r="L24" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M21" s="7" t="inlineStr"/>
-      <c r="N21" s="7" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>BUG-020</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="M24" s="7" t="inlineStr"/>
+      <c r="N24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>BUG-023</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-MR-002</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-MR-002 · Market Research header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr"/>
-      <c r="G22" s="7" t="inlineStr"/>
-      <c r="H22" s="7" t="inlineStr"/>
-      <c r="I22" s="7" t="inlineStr">
+      <c r="F25" s="7" t="inlineStr"/>
+      <c r="G25" s="7" t="inlineStr"/>
+      <c r="H25" s="7" t="inlineStr"/>
+      <c r="I25" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Market Research: {"doctype-df-prefix":["DF MARKET"]}
 expect.toEqual // deep equality
@@ -23619,50 +24162,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J22" s="7" t="inlineStr">
+      <c r="J25" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Ma-6eb23-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K22" s="7" t="inlineStr"/>
-      <c r="L22" s="7" t="inlineStr">
+      <c r="K25" s="7" t="inlineStr"/>
+      <c r="L25" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M22" s="7" t="inlineStr"/>
-      <c r="N22" s="7" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>BUG-021</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="M25" s="7" t="inlineStr"/>
+      <c r="N25" s="7" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>BUG-024</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PCMP-002</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PCMP-002 · Product Compliance header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E26" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F23" s="7" t="inlineStr"/>
-      <c r="G23" s="7" t="inlineStr"/>
-      <c r="H23" s="7" t="inlineStr"/>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="F26" s="7" t="inlineStr"/>
+      <c r="G26" s="7" t="inlineStr"/>
+      <c r="H26" s="7" t="inlineStr"/>
+      <c r="I26" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Product Compliance: {"doctype-df-prefix":["DF PRODUCT"]}
 expect.toEqual // deep equality
@@ -23676,50 +24219,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J23" s="7" t="inlineStr">
+      <c r="J26" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Pr-be46f-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K23" s="7" t="inlineStr"/>
-      <c r="L23" s="7" t="inlineStr">
+      <c r="K26" s="7" t="inlineStr"/>
+      <c r="L26" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M23" s="7" t="inlineStr"/>
-      <c r="N23" s="7" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>BUG-022</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="M26" s="7" t="inlineStr"/>
+      <c r="N26" s="7" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>BUG-025</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PROM-002</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PROM-002 · Promotional Marketing header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr"/>
-      <c r="G24" s="7" t="inlineStr"/>
-      <c r="H24" s="7" t="inlineStr"/>
-      <c r="I24" s="7" t="inlineStr">
+      <c r="F27" s="7" t="inlineStr"/>
+      <c r="G27" s="7" t="inlineStr"/>
+      <c r="H27" s="7" t="inlineStr"/>
+      <c r="I27" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Promotional Marketing: {"doctype-df-prefix":["DF PROMOTIONAL"]}
 expect.toEqual // deep equality
@@ -23733,50 +24276,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J24" s="7" t="inlineStr">
+      <c r="J27" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Pr-d8d12-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K24" s="7" t="inlineStr"/>
-      <c r="L24" s="7" t="inlineStr">
+      <c r="K27" s="7" t="inlineStr"/>
+      <c r="L27" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M24" s="7" t="inlineStr"/>
-      <c r="N24" s="7" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>BUG-023</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="M27" s="7" t="inlineStr"/>
+      <c r="N27" s="7" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>BUG-026</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PROT-002</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PROT-002 · Product Prototyping header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F25" s="7" t="inlineStr"/>
-      <c r="G25" s="7" t="inlineStr"/>
-      <c r="H25" s="7" t="inlineStr"/>
-      <c r="I25" s="7" t="inlineStr">
+      <c r="F28" s="7" t="inlineStr"/>
+      <c r="G28" s="7" t="inlineStr"/>
+      <c r="H28" s="7" t="inlineStr"/>
+      <c r="I28" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Product Prototyping: {"doctype-df-prefix":["DF PRODUCT"]}
 expect.toEqual // deep equality
@@ -23790,50 +24333,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J25" s="7" t="inlineStr">
+      <c r="J28" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Pr-1120e-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K25" s="7" t="inlineStr"/>
-      <c r="L25" s="7" t="inlineStr">
+      <c r="K28" s="7" t="inlineStr"/>
+      <c r="L28" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M25" s="7" t="inlineStr"/>
-      <c r="N25" s="7" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>BUG-024</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="M28" s="7" t="inlineStr"/>
+      <c r="N28" s="7" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>BUG-027</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PTCH-002</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PTCH-002 · Pitch Deck header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F26" s="7" t="inlineStr"/>
-      <c r="G26" s="7" t="inlineStr"/>
-      <c r="H26" s="7" t="inlineStr"/>
-      <c r="I26" s="7" t="inlineStr">
+      <c r="F29" s="7" t="inlineStr"/>
+      <c r="G29" s="7" t="inlineStr"/>
+      <c r="H29" s="7" t="inlineStr"/>
+      <c r="I29" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Pitch Deck: {"doctype-df-prefix":["DF PITCH"]}
 expect.toEqual // deep equality
@@ -23847,50 +24390,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J26" s="7" t="inlineStr">
+      <c r="J29" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Pi-fefd5-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K26" s="7" t="inlineStr"/>
-      <c r="L26" s="7" t="inlineStr">
+      <c r="K29" s="7" t="inlineStr"/>
+      <c r="L29" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M26" s="7" t="inlineStr"/>
-      <c r="N26" s="7" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>BUG-025</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="M29" s="7" t="inlineStr"/>
+      <c r="N29" s="7" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>BUG-028</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PTST-002</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PTST-002 · Product Testing header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E30" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr"/>
-      <c r="G27" s="7" t="inlineStr"/>
-      <c r="H27" s="7" t="inlineStr"/>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="F30" s="7" t="inlineStr"/>
+      <c r="G30" s="7" t="inlineStr"/>
+      <c r="H30" s="7" t="inlineStr"/>
+      <c r="I30" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Product Testing: {"doctype-df-prefix":["DF PRODUCT"]}
 expect.toEqual // deep equality
@@ -23904,50 +24447,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J27" s="7" t="inlineStr">
+      <c r="J30" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Pr-3e912-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K27" s="7" t="inlineStr"/>
-      <c r="L27" s="7" t="inlineStr">
+      <c r="K30" s="7" t="inlineStr"/>
+      <c r="L30" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M27" s="7" t="inlineStr"/>
-      <c r="N27" s="7" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>BUG-026</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="M30" s="7" t="inlineStr"/>
+      <c r="N30" s="7" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>BUG-029</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-QC-002</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-QC-002 · Quality Control header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E31" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr"/>
-      <c r="G28" s="7" t="inlineStr"/>
-      <c r="H28" s="7" t="inlineStr"/>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="F31" s="7" t="inlineStr"/>
+      <c r="G31" s="7" t="inlineStr"/>
+      <c r="H31" s="7" t="inlineStr"/>
+      <c r="I31" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Quality Control: {"doctype-df-prefix":["DF QUALITY"]}
 expect.toEqual // deep equality
@@ -23961,50 +24504,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J28" s="7" t="inlineStr">
+      <c r="J31" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Qu-ae31c-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K28" s="7" t="inlineStr"/>
-      <c r="L28" s="7" t="inlineStr">
+      <c r="K31" s="7" t="inlineStr"/>
+      <c r="L31" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M28" s="7" t="inlineStr"/>
-      <c r="N28" s="7" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>BUG-027</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="M31" s="7" t="inlineStr"/>
+      <c r="N31" s="7" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>BUG-030</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-SCHM-002</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-SCHM-002 · Schemes &amp; Funding header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="E32" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr"/>
-      <c r="G29" s="7" t="inlineStr"/>
-      <c r="H29" s="7" t="inlineStr"/>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="F32" s="7" t="inlineStr"/>
+      <c r="G32" s="7" t="inlineStr"/>
+      <c r="H32" s="7" t="inlineStr"/>
+      <c r="I32" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Schemes &amp; Funding: {"doctype-df-prefix":["DF SCHEMES"]}
 expect.toEqual // deep equality
@@ -24018,50 +24561,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J29" s="7" t="inlineStr">
+      <c r="J32" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Sc-67cb2-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K29" s="7" t="inlineStr"/>
-      <c r="L29" s="7" t="inlineStr">
+      <c r="K32" s="7" t="inlineStr"/>
+      <c r="L32" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M29" s="7" t="inlineStr"/>
-      <c r="N29" s="7" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>BUG-028</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="M32" s="7" t="inlineStr"/>
+      <c r="N32" s="7" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>BUG-031</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-STD-002</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D33" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-STD-002 · Standardization header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="E33" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr"/>
-      <c r="G30" s="7" t="inlineStr"/>
-      <c r="H30" s="7" t="inlineStr"/>
-      <c r="I30" s="7" t="inlineStr">
+      <c r="F33" s="7" t="inlineStr"/>
+      <c r="G33" s="7" t="inlineStr"/>
+      <c r="H33" s="7" t="inlineStr"/>
+      <c r="I33" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Standardization: {"doctype-df-prefix":["DF STANDARDIZATION"]}
 expect.toEqual // deep equality
@@ -24075,50 +24618,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J30" s="7" t="inlineStr">
+      <c r="J33" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-St-b8b93-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K30" s="7" t="inlineStr"/>
-      <c r="L30" s="7" t="inlineStr">
+      <c r="K33" s="7" t="inlineStr"/>
+      <c r="L33" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M30" s="7" t="inlineStr"/>
-      <c r="N30" s="7" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>BUG-029</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="M33" s="7" t="inlineStr"/>
+      <c r="N33" s="7" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>BUG-032</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-UP-002</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-UP-002 · Unit Pricing header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="E34" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr"/>
-      <c r="G31" s="7" t="inlineStr"/>
-      <c r="H31" s="7" t="inlineStr"/>
-      <c r="I31" s="7" t="inlineStr">
+      <c r="F34" s="7" t="inlineStr"/>
+      <c r="G34" s="7" t="inlineStr"/>
+      <c r="H34" s="7" t="inlineStr"/>
+      <c r="I34" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Unit Pricing: {"doctype-df-prefix":["DF UNIT"]}
 expect.toEqual // deep equality
@@ -24132,58 +24675,58 @@
 + }</t>
         </is>
       </c>
-      <c r="J31" s="7" t="inlineStr">
+      <c r="J34" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Un-0c652-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K31" s="7" t="inlineStr"/>
-      <c r="L31" s="7" t="inlineStr">
+      <c r="K34" s="7" t="inlineStr"/>
+      <c r="L34" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M31" s="7" t="inlineStr"/>
-      <c r="N31" s="7" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>BUG-030</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="M34" s="7" t="inlineStr"/>
+      <c r="N34" s="7" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>BUG-033</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>PR-TC-MS-008</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>14. Masters &amp; Reference Data</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t>Cohort end date must be after start date</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
+      <c r="E35" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F32" s="7" t="inlineStr">
+      <c r="F35" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G32" s="7" t="inlineStr">
+      <c r="G35" s="7" t="inlineStr">
         <is>
           <t>• Start = 01-Apr-2026, End = 31-Mar-2025.</t>
         </is>
       </c>
-      <c r="H32" s="7" t="inlineStr"/>
-      <c r="I32" s="7" t="inlineStr">
+      <c r="H35" s="7" t="inlineStr"/>
+      <c r="I35" s="7" t="inlineStr">
         <is>
           <t>Error: end-before-start cohort should be rejected
 expect(received).toBeGreaterThanOrEqual(expected)
@@ -24191,59 +24734,59 @@
 Received:    200</t>
         </is>
       </c>
-      <c r="J32" s="7" t="inlineStr"/>
-      <c r="K32" s="7" t="inlineStr"/>
-      <c r="L32" s="7" t="inlineStr">
+      <c r="J35" s="7" t="inlineStr"/>
+      <c r="K35" s="7" t="inlineStr"/>
+      <c r="L35" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M32" s="7" t="inlineStr"/>
-      <c r="N32" s="7" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>BUG-031</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="M35" s="7" t="inlineStr"/>
+      <c r="N35" s="7" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>BUG-034</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>PR-TC-MS-011</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>14. Masters &amp; Reference Data</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>Seed import: 351 rows from "Final PRIME Rural Task Dropdowns Master.xlsx"</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F33" s="7" t="inlineStr">
+      <c r="F36" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G33" s="7" t="inlineStr">
+      <c r="G36" s="7" t="inlineStr">
         <is>
           <t>• Run the seed migration script (or use bulk import) using the canonical xlsx.
 • Verify count = 351.</t>
         </is>
       </c>
-      <c r="H33" s="7" t="inlineStr">
+      <c r="H36" s="7" t="inlineStr">
         <is>
           <t>351 Framework Task Master records exist. Each has: module, framework, task_no, task_name, description, phase. Em-dash phase rows have phase = "Other". Logistic Service has its "Other" row added (was missing in the xlsx).</t>
         </is>
       </c>
-      <c r="I33" s="7" t="inlineStr">
+      <c r="I36" s="7" t="inlineStr">
         <is>
           <t>Error: Framework Task Master doctype should exist
 expect(received).toBe(expected) // Object.is equality
@@ -24251,58 +24794,58 @@
 Received: 404</t>
         </is>
       </c>
-      <c r="J33" s="7" t="inlineStr"/>
-      <c r="K33" s="7" t="inlineStr">
+      <c r="J36" s="7" t="inlineStr"/>
+      <c r="K36" s="7" t="inlineStr">
         <is>
           <t>BRD PR-XC-002b.</t>
         </is>
       </c>
-      <c r="L33" s="7" t="inlineStr">
+      <c r="L36" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M33" s="7" t="inlineStr"/>
-      <c r="N33" s="7" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>BUG-032</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="M36" s="7" t="inlineStr"/>
+      <c r="N36" s="7" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>BUG-035</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>PR-TC-MS-015</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>14. Masters &amp; Reference Data</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t>Document types: Aadhaar, PAN, EPIC, Bank Passbook, Photo, Other</t>
         </is>
       </c>
-      <c r="E34" s="7" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F34" s="7" t="inlineStr">
+      <c r="F37" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G34" s="7" t="inlineStr">
+      <c r="G37" s="7" t="inlineStr">
         <is>
           <t>• Masters → Document Master → list.</t>
         </is>
       </c>
-      <c r="H34" s="7" t="inlineStr"/>
-      <c r="I34" s="7" t="inlineStr">
+      <c r="H37" s="7" t="inlineStr"/>
+      <c r="I37" s="7" t="inlineStr">
         <is>
           <t>Error: expected the standard document types (Aadhaar/PAN/EPIC/Bank/Photo/...)
 expect(received).toBeGreaterThanOrEqual(expected)
@@ -24310,58 +24853,58 @@
 Received:    5</t>
         </is>
       </c>
-      <c r="J34" s="7" t="inlineStr"/>
-      <c r="K34" s="7" t="inlineStr"/>
-      <c r="L34" s="7" t="inlineStr">
+      <c r="J37" s="7" t="inlineStr"/>
+      <c r="K37" s="7" t="inlineStr"/>
+      <c r="L37" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M34" s="7" t="inlineStr"/>
-      <c r="N34" s="7" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>BUG-033</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="M37" s="7" t="inlineStr"/>
+      <c r="N37" s="7" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>BUG-036</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>PR-TC-MS-020</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>14. Masters &amp; Reference Data</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
         <is>
           <t>19 schemes pre-seeded (MOVCDNER, CGTMSE, NEHHDC, PGS-India Organic, etc.)</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="E38" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F35" s="7" t="inlineStr">
+      <c r="F38" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G35" s="7" t="inlineStr">
+      <c r="G38" s="7" t="inlineStr">
         <is>
           <t>• Open Scheme Master list. Count rows.</t>
         </is>
       </c>
-      <c r="H35" s="7" t="inlineStr">
+      <c r="H38" s="7" t="inlineStr">
         <is>
           <t>19 schemes present per BRD m-schemes. Each has: name, type (Grant / Loan / Subsidy / Certification), eligibility, min/max amount, applicable sectors, interest rate (if loan).</t>
         </is>
       </c>
-      <c r="I35" s="7" t="inlineStr">
+      <c r="I38" s="7" t="inlineStr">
         <is>
           <t>Error: BRD m-schemes expects 19 pre-seeded schemes
 expect(received).toBeGreaterThanOrEqual(expected)
@@ -24369,104 +24912,104 @@
 Received:    3</t>
         </is>
       </c>
-      <c r="J35" s="7" t="inlineStr"/>
-      <c r="K35" s="7" t="inlineStr">
+      <c r="J38" s="7" t="inlineStr"/>
+      <c r="K38" s="7" t="inlineStr">
         <is>
           <t>BRD m-schemes.</t>
         </is>
       </c>
-      <c r="L35" s="7" t="inlineStr">
+      <c r="L38" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M35" s="7" t="inlineStr"/>
-      <c r="N35" s="7" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>BUG-034</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="M38" s="7" t="inlineStr"/>
+      <c r="N38" s="7" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>BUG-037</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>PR-TC-SEC-005</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C39" s="7" t="inlineStr">
         <is>
           <t>23. Security — OWASP &amp; Beyond</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="D39" s="7" t="inlineStr">
         <is>
           <t>Content-Security-Policy header set, restricts inline scripts</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="E39" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F36" s="7" t="inlineStr">
+      <c r="F39" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G36" s="7" t="inlineStr">
+      <c r="G39" s="7" t="inlineStr">
         <is>
           <t>• Inspect response headers on /app/.</t>
         </is>
       </c>
-      <c r="H36" s="7" t="inlineStr"/>
-      <c r="I36" s="7" t="inlineStr">
+      <c r="H39" s="7" t="inlineStr"/>
+      <c r="I39" s="7" t="inlineStr">
         <is>
           <t>Error: CSP header should be set
 expect(received).toBeTruthy()
 Received: undefined</t>
         </is>
       </c>
-      <c r="J36" s="7" t="inlineStr"/>
-      <c r="K36" s="7" t="inlineStr"/>
-      <c r="L36" s="7" t="inlineStr">
+      <c r="J39" s="7" t="inlineStr"/>
+      <c r="K39" s="7" t="inlineStr"/>
+      <c r="L39" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M36" s="7" t="inlineStr"/>
-      <c r="N36" s="7" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>BUG-035</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="M39" s="7" t="inlineStr"/>
+      <c r="N39" s="7" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>BUG-038</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t>PR-TC-UI-LEAK-001</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="D40" s="7" t="inlineStr">
         <is>
           <t>PR-TC-UI-LEAK-001 · EP profile shows no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
+      <c r="E40" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F37" s="7" t="inlineStr"/>
-      <c r="G37" s="7" t="inlineStr"/>
-      <c r="H37" s="7" t="inlineStr"/>
-      <c r="I37" s="7" t="inlineStr">
+      <c r="F40" s="7" t="inlineStr"/>
+      <c r="G40" s="7" t="inlineStr"/>
+      <c r="H40" s="7" t="inlineStr"/>
+      <c r="I40" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on EP profile: {"doctype-df-prefix":["DF PROGRESS"]}
 expect.toEqual // deep equality
@@ -24480,50 +25023,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J37" s="7" t="inlineStr">
+      <c r="J40" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\08-ui-no-backend-leak-PR-T-d694f-e-shows-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K37" s="7" t="inlineStr"/>
-      <c r="L37" s="7" t="inlineStr">
+      <c r="K40" s="7" t="inlineStr"/>
+      <c r="L40" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M37" s="7" t="inlineStr"/>
-      <c r="N37" s="7" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>BUG-036</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="M40" s="7" t="inlineStr"/>
+      <c r="N40" s="7" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>BUG-039</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>PR-TC-UI-LEAK-002</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D38" s="7" t="inlineStr">
+      <c r="D41" s="7" t="inlineStr">
         <is>
           <t>PR-TC-UI-LEAK-002 · new EP form header is a friendly label, not the raw doctype</t>
         </is>
       </c>
-      <c r="E38" s="7" t="inlineStr">
+      <c r="E41" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F38" s="7" t="inlineStr"/>
-      <c r="G38" s="7" t="inlineStr"/>
-      <c r="H38" s="7" t="inlineStr"/>
-      <c r="I38" s="7" t="inlineStr">
+      <c r="F41" s="7" t="inlineStr"/>
+      <c r="G41" s="7" t="inlineStr"/>
+      <c r="H41" s="7" t="inlineStr"/>
+      <c r="I41" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on new EP form: {"enterprenur-internal":["Enterprenur"]}
 expect.toEqual // deep equality
@@ -24537,52 +25080,52 @@
 + }</t>
         </is>
       </c>
-      <c r="J38" s="7" t="inlineStr">
+      <c r="J41" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\08-ui-no-backend-leak-PR-T-215c4-y-label-not-the-raw-doctype-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K38" s="7" t="inlineStr"/>
-      <c r="L38" s="7" t="inlineStr">
+      <c r="K41" s="7" t="inlineStr"/>
+      <c r="L41" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M38" s="7" t="inlineStr"/>
-      <c r="N38" s="7" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>BUG-037</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="M41" s="7" t="inlineStr"/>
+      <c r="N41" s="7" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>BUG-040</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>PR-TC-UM-001</t>
         </is>
       </c>
-      <c r="C39" s="7" t="inlineStr">
+      <c r="C42" s="7" t="inlineStr">
         <is>
           <t>13. User Management</t>
         </is>
       </c>
-      <c r="D39" s="7" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
         <is>
           <t>Create a new Field Associate user with all required fields</t>
         </is>
       </c>
-      <c r="E39" s="7" t="inlineStr">
+      <c r="E42" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F39" s="7" t="inlineStr">
+      <c r="F42" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G39" s="7" t="inlineStr">
+      <c r="G42" s="7" t="inlineStr">
         <is>
           <t>• Navigate to User Management workspace → "+ New User".
 • Fill: Email = uat-fa-test01@dhwaniris.com, First Name = UAT, Last Name = FA-Test01, Phone = +91 9876543210.
@@ -24592,114 +25135,114 @@
 • Click Save.</t>
         </is>
       </c>
-      <c r="H39" s="7" t="inlineStr">
+      <c r="H42" s="7" t="inlineStr">
         <is>
           <t>Toast: "User created successfully." User row appears in list with status "Active" and "Welcome email sent". Email arrives at the address within 2 min containing a one-time password-set link. Audit log records the creation with timestamp + creator.</t>
         </is>
       </c>
-      <c r="I39" s="7" t="inlineStr">
+      <c r="I42" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: INSERT User → 417: {"exception":"frappe.exceptions.ValidationError: Error syncing User to User Manager: ('User Manager', 'uat-umc-79v3ss@dhwaniris.com', IntegrityError(1062, \"Duplicate entry '[uat]_crud_user' for key 'username'\"))","exc_type":"ValidationError","_exc_source":"dhwani_frappe_base (app)","exc":"[\"Traceback (most recent call last):\\n  File \\\"apps/frappe/frappe/model/base_document.py\\\", line 755, in db_insert\\n    name = frappe.db.sql(\\n    \\t\\\"\\\"\\\"INSERT INTO </t>
         </is>
       </c>
-      <c r="J39" s="7" t="inlineStr"/>
-      <c r="K39" s="7" t="inlineStr">
+      <c r="J42" s="7" t="inlineStr"/>
+      <c r="K42" s="7" t="inlineStr">
         <is>
           <t>BRD: PR-UJ-CTI §User Management.</t>
         </is>
       </c>
-      <c r="L39" s="7" t="inlineStr">
+      <c r="L42" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M39" s="7" t="inlineStr"/>
-      <c r="N39" s="7" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>BUG-038</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="M42" s="7" t="inlineStr"/>
+      <c r="N42" s="7" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>BUG-041</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>PR-TC-UM-009</t>
         </is>
       </c>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="C43" s="7" t="inlineStr">
         <is>
           <t>13. User Management</t>
         </is>
       </c>
-      <c r="D40" s="7" t="inlineStr">
+      <c r="D43" s="7" t="inlineStr">
         <is>
           <t>Email must be lowercase and trimmed before save</t>
         </is>
       </c>
-      <c r="E40" s="7" t="inlineStr">
+      <c r="E43" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F40" s="7" t="inlineStr">
+      <c r="F43" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G40" s="7" t="inlineStr">
+      <c r="G43" s="7" t="inlineStr">
         <is>
           <t>• Enter email Test@Dhwaniris.COM (leading/trailing spaces, mixed case).</t>
         </is>
       </c>
-      <c r="H40" s="7" t="inlineStr"/>
-      <c r="I40" s="7" t="inlineStr">
+      <c r="H43" s="7" t="inlineStr"/>
+      <c r="I43" s="7" t="inlineStr">
         <is>
           <t>Error: INSERT User → 417: {"exception":"frappe.exceptions.ValidationError: Error syncing User to User Manager: ('User Manager', 'uat-umn-ztbfos@dhwaniris.com', IntegrityError(1062, \"Duplicate entry '[uat]_norm' for key 'username'\"))","exc_type":"ValidationError","_exc_source":"dhwani_frappe_base (app)","exc":"[\"Traceback (most recent call last):\\n  File \\\"apps/frappe/frappe/model/base_document.py\\\", line 755, in db_insert\\n    name = frappe.db.sql(\\n    \\t\\\"\\\"\\\"INSERT INTO `tab{</t>
         </is>
       </c>
-      <c r="J40" s="7" t="inlineStr"/>
-      <c r="K40" s="7" t="inlineStr"/>
-      <c r="L40" s="7" t="inlineStr">
+      <c r="J43" s="7" t="inlineStr"/>
+      <c r="K43" s="7" t="inlineStr"/>
+      <c r="L43" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M40" s="7" t="inlineStr"/>
-      <c r="N40" s="7" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>BUG-039</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
+      <c r="M43" s="7" t="inlineStr"/>
+      <c r="N43" s="7" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>BUG-042</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>PR-TC-UM-010</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="C44" s="7" t="inlineStr">
         <is>
           <t>13. User Management</t>
         </is>
       </c>
-      <c r="D41" s="7" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
         <is>
           <t>Edit user phone, name, block — changes persist</t>
         </is>
       </c>
-      <c r="E41" s="7" t="inlineStr">
+      <c r="E44" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F41" s="7" t="inlineStr">
+      <c r="F44" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G41" s="7" t="inlineStr">
+      <c r="G44" s="7" t="inlineStr">
         <is>
           <t>• Open user uat-fa-test01.
 • Change First Name to "UAT-Updated".
@@ -24708,181 +25251,181 @@
 • Log out / log in as that user.</t>
         </is>
       </c>
-      <c r="H41" s="7" t="inlineStr"/>
-      <c r="I41" s="7" t="inlineStr">
+      <c r="H44" s="7" t="inlineStr"/>
+      <c r="I44" s="7" t="inlineStr">
         <is>
           <t>Error: INSERT User → 417: {"exception":"frappe.exceptions.ValidationError: Error syncing User to User Manager: ('User Manager', 'uat-ume-1c8bs5@dhwaniris.com', IntegrityError(1062, \"Duplicate entry '[uat]_before' for key 'username'\"))","exc_type":"ValidationError","_exc_source":"dhwani_frappe_base (app)","exc":"[\"Traceback (most recent call last):\\n  File \\\"apps/frappe/frappe/model/base_document.py\\\", line 755, in db_insert\\n    name = frappe.db.sql(\\n    \\t\\\"\\\"\\\"INSERT INTO `ta</t>
         </is>
       </c>
-      <c r="J41" s="7" t="inlineStr"/>
-      <c r="K41" s="7" t="inlineStr"/>
-      <c r="L41" s="7" t="inlineStr">
+      <c r="J44" s="7" t="inlineStr"/>
+      <c r="K44" s="7" t="inlineStr"/>
+      <c r="L44" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M41" s="7" t="inlineStr"/>
-      <c r="N41" s="7" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>BUG-040</t>
-        </is>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="M44" s="7" t="inlineStr"/>
+      <c r="N44" s="7" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>BUG-043</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>PR-TC-UM-011</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>13. User Management</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D45" s="7" t="inlineStr">
         <is>
           <t>Deactivate a user — they cannot log in until reactivated</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="E45" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F42" s="7" t="inlineStr">
+      <c r="F45" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G42" s="7" t="inlineStr">
+      <c r="G45" s="7" t="inlineStr">
         <is>
           <t>• Open uat-fa-test01. Set Enabled = No. Save.
 • Sign out, attempt to log in as uat-fa-test01.</t>
         </is>
       </c>
-      <c r="H42" s="7" t="inlineStr"/>
-      <c r="I42" s="7" t="inlineStr">
+      <c r="H45" s="7" t="inlineStr"/>
+      <c r="I45" s="7" t="inlineStr">
         <is>
           <t>Error: INSERT User → 417: {"exception":"frappe.exceptions.ValidationError: Error syncing User to User Manager: ('User Manager', 'uat-umd-0pc24h@dhwaniris.com', IntegrityError(1062, \"Duplicate entry '[uat]_disabled' for key 'username'\"))","exc_type":"ValidationError","_exc_source":"dhwani_frappe_base (app)","exc":"[\"Traceback (most recent call last):\\n  File \\\"apps/frappe/frappe/model/base_document.py\\\", line 755, in db_insert\\n    name = frappe.db.sql(\\n    \\t\\\"\\\"\\\"INSERT INTO `</t>
         </is>
       </c>
-      <c r="J42" s="7" t="inlineStr"/>
-      <c r="K42" s="7" t="inlineStr"/>
-      <c r="L42" s="7" t="inlineStr">
+      <c r="J45" s="7" t="inlineStr"/>
+      <c r="K45" s="7" t="inlineStr"/>
+      <c r="L45" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M42" s="7" t="inlineStr"/>
-      <c r="N42" s="7" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="7" t="inlineStr">
-        <is>
-          <t>BUG-041</t>
-        </is>
-      </c>
-      <c r="B43" s="7" t="inlineStr">
+      <c r="M45" s="7" t="inlineStr"/>
+      <c r="N45" s="7" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>BUG-044</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-003</t>
         </is>
       </c>
-      <c r="C43" s="7" t="inlineStr">
+      <c r="C46" s="7" t="inlineStr">
         <is>
           <t>4. Application Entry &amp; Routing</t>
         </is>
       </c>
-      <c r="D43" s="7" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
         <is>
           <t>Deep link to a protected page while logged out preserves the intent</t>
         </is>
       </c>
-      <c r="E43" s="7" t="inlineStr">
+      <c r="E46" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F43" s="7" t="inlineStr">
+      <c r="F46" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G43" s="7" t="inlineStr">
+      <c r="G46" s="7" t="inlineStr">
         <is>
           <t>• Open https://stgprime-rural.dhwaniris.in/app/enterprenur-profile/EP-001 directly.
 • Login redirect fires.
 • Complete login as a user permitted to see that record.</t>
         </is>
       </c>
-      <c r="H43" s="7" t="inlineStr">
+      <c r="H46" s="7" t="inlineStr">
         <is>
           <t>After successful login, user is redirected to the originally requested URL (the EP detail page), not the default landing page. URL parameter (typically redirect-to or next) is preserved through the auth flow.</t>
         </is>
       </c>
-      <c r="I43" s="7" t="inlineStr">
+      <c r="I46" s="7" t="inlineStr">
         <is>
           <t>Error: expect(received).toMatch(expected)
 Expected pattern: /redirect|next|to=/i
 Received string:  "https://stgprime-rural.dhwaniris.in/primerural/login"</t>
         </is>
       </c>
-      <c r="J43" s="7" t="inlineStr">
+      <c r="J46" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\04-entry-PR-TC-XC-ENTRY-·--e9661-t-preserves-redirect-intent-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K43" s="7" t="inlineStr">
+      <c r="K46" s="7" t="inlineStr">
         <is>
           <t>BRD: PR-OV-001 (Auth)</t>
         </is>
       </c>
-      <c r="L43" s="7" t="inlineStr">
+      <c r="L46" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M43" s="7" t="inlineStr"/>
-      <c r="N43" s="7" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>BUG-042</t>
-        </is>
-      </c>
-      <c r="B44" s="7" t="inlineStr">
+      <c r="M46" s="7" t="inlineStr"/>
+      <c r="N46" s="7" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>BUG-045</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-023</t>
         </is>
       </c>
-      <c r="C44" s="7" t="inlineStr">
+      <c r="C47" s="7" t="inlineStr">
         <is>
           <t>6. Responsive Layout &amp; Screen Sizes</t>
         </is>
       </c>
-      <c r="D44" s="7" t="inlineStr">
+      <c r="D47" s="7" t="inlineStr">
         <is>
           <t>1024×768 (tablet landscape / iPad / Surface): sidebar collapses to icon rail</t>
         </is>
       </c>
-      <c r="E44" s="7" t="inlineStr">
+      <c r="E47" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F44" s="7" t="inlineStr">
+      <c r="F47" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G44" s="7" t="inlineStr">
+      <c r="G47" s="7" t="inlineStr">
         <is>
           <t>• Resize to 1024×768.</t>
         </is>
       </c>
-      <c r="H44" s="7" t="inlineStr"/>
-      <c r="I44" s="7" t="inlineStr">
+      <c r="H47" s="7" t="inlineStr"/>
+      <c r="I47" s="7" t="inlineStr">
         <is>
           <t>Error: at 1024px the sidebar should collapse to an icon rail; width=240
 expect(received).toBeLessThanOrEqual(expected)
@@ -24890,63 +25433,63 @@
 Received:    240</t>
         </is>
       </c>
-      <c r="J44" s="7" t="inlineStr">
+      <c r="J47" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\06-08-10-nonfunctional-PR--f1c18-ollapses-to-icon-rail-64px--sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K44" s="7" t="inlineStr"/>
-      <c r="L44" s="7" t="inlineStr">
+      <c r="K47" s="7" t="inlineStr"/>
+      <c r="L47" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M44" s="7" t="inlineStr"/>
-      <c r="N44" s="7" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="7" t="inlineStr">
-        <is>
-          <t>BUG-043</t>
-        </is>
-      </c>
-      <c r="B45" s="7" t="inlineStr">
+      <c r="M47" s="7" t="inlineStr"/>
+      <c r="N47" s="7" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>BUG-046</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-032</t>
         </is>
       </c>
-      <c r="C45" s="7" t="inlineStr">
+      <c r="C48" s="7" t="inlineStr">
         <is>
           <t>7. Login &amp; Session</t>
         </is>
       </c>
-      <c r="D45" s="7" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr">
         <is>
           <t>Wrong password shows a clear error and does NOT reveal whether the email exists</t>
         </is>
       </c>
-      <c r="E45" s="7" t="inlineStr">
+      <c r="E48" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F45" s="7" t="inlineStr">
+      <c r="F48" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G45" s="7" t="inlineStr">
+      <c r="G48" s="7" t="inlineStr">
         <is>
           <t>• Login form: enter a valid email but wrong password.
 • Submit.</t>
         </is>
       </c>
-      <c r="H45" s="7" t="inlineStr">
+      <c r="H48" s="7" t="inlineStr">
         <is>
           <t>Error displays inline above the form: "Invalid email or password." — generic enough that an attacker cannot enumerate valid emails. The password field is cleared; the email field is preserved. No 500. No password ever echoed back into the field.</t>
         </is>
       </c>
-      <c r="I45" s="7" t="inlineStr">
+      <c r="I48" s="7" t="inlineStr">
         <is>
           <t>Error: login error must be friendly text, not a raw exception class
 expect(locator).not.toContainText(expected) failed
@@ -24960,62 +25503,62 @@
     22 × locator resolved to &lt;div role="alert" class="bg-d</t>
         </is>
       </c>
-      <c r="J45" s="7" t="inlineStr">
+      <c r="J48" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\07-auth-PR-TC-XC-AUTH-·-Em-429a0-neric-error-no-enumeration--sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K45" s="7" t="inlineStr">
+      <c r="K48" s="7" t="inlineStr">
         <is>
           <t>OWASP A07 Auth Failures (do not leak account existence).</t>
         </is>
       </c>
-      <c r="L45" s="7" t="inlineStr">
+      <c r="L48" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M45" s="7" t="inlineStr"/>
-      <c r="N45" s="7" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="7" t="inlineStr">
-        <is>
-          <t>BUG-044</t>
-        </is>
-      </c>
-      <c r="B46" s="7" t="inlineStr">
+      <c r="M48" s="7" t="inlineStr"/>
+      <c r="N48" s="7" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>BUG-047</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-033</t>
         </is>
       </c>
-      <c r="C46" s="7" t="inlineStr">
+      <c r="C49" s="7" t="inlineStr">
         <is>
           <t>7. Login &amp; Session</t>
         </is>
       </c>
-      <c r="D46" s="7" t="inlineStr">
+      <c r="D49" s="7" t="inlineStr">
         <is>
           <t>Non-existent email shows the same generic error as wrong password</t>
         </is>
       </c>
-      <c r="E46" s="7" t="inlineStr">
+      <c r="E49" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F46" s="7" t="inlineStr">
+      <c r="F49" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G46" s="7" t="inlineStr">
+      <c r="G49" s="7" t="inlineStr">
         <is>
           <t>• Submit with email not-a-real-user@example.com and any password.</t>
         </is>
       </c>
-      <c r="H46" s="7" t="inlineStr"/>
-      <c r="I46" s="7" t="inlineStr">
+      <c r="H49" s="7" t="inlineStr"/>
+      <c r="I49" s="7" t="inlineStr">
         <is>
           <t>Error: login error must be friendly text, not a raw exception class
 expect(locator).not.toContainText(expected) failed
@@ -25029,175 +25572,175 @@
     22 × locator resolved to &lt;div role="alert" class="bg-d</t>
         </is>
       </c>
-      <c r="J46" s="7" t="inlineStr">
+      <c r="J49" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\07-auth-PR-TC-XC-AUTH-·-Em-a7adf-ows-identical-generic-error-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K46" s="7" t="inlineStr"/>
-      <c r="L46" s="7" t="inlineStr">
+      <c r="K49" s="7" t="inlineStr"/>
+      <c r="L49" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M46" s="7" t="inlineStr"/>
-      <c r="N46" s="7" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="7" t="inlineStr">
-        <is>
-          <t>BUG-045</t>
-        </is>
-      </c>
-      <c r="B47" s="7" t="inlineStr">
+      <c r="M49" s="7" t="inlineStr"/>
+      <c r="N49" s="7" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>BUG-048</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-052</t>
         </is>
       </c>
-      <c r="C47" s="7" t="inlineStr">
+      <c r="C50" s="7" t="inlineStr">
         <is>
           <t>8. UI / UX Rules — Monsoon Court Compliance</t>
         </is>
       </c>
-      <c r="D47" s="7" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
         <is>
           <t>No green and no yellow appear anywhere in the UI</t>
         </is>
       </c>
-      <c r="E47" s="7" t="inlineStr">
+      <c r="E50" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F47" s="7" t="inlineStr">
+      <c r="F50" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G47" s="7" t="inlineStr">
+      <c r="G50" s="7" t="inlineStr">
         <is>
           <t>• Visually scan every page for green / yellow elements.
 • Search the rendered CSS for any colour matching green, yellow, #2ecc71, #f1c40f, similar hexes.</t>
         </is>
       </c>
-      <c r="H47" s="7" t="inlineStr">
+      <c r="H50" s="7" t="inlineStr">
         <is>
           <t>Zero green elements. Success states use teal #0E4D4E. Zero yellow elements. Warning states use terracotta #C26849.</t>
         </is>
       </c>
-      <c r="I47" s="7" t="inlineStr">
+      <c r="I50" s="7" t="inlineStr">
         <is>
           <t>Active Entrepreneurs KPI shows a GREEN check rgb(63,107,58) (hue 114). Monsoon Court forbids green — success must be teal #0E4D4E.</t>
         </is>
       </c>
-      <c r="J47" s="7" t="inlineStr">
+      <c r="J50" s="7" t="inlineStr">
         <is>
           <t>.playwright-mcp/bug-xc052-green-kpi.png</t>
         </is>
       </c>
-      <c r="K47" s="7" t="inlineStr">
+      <c r="K50" s="7" t="inlineStr">
         <is>
           <t>Monsoon Court §2.7 (brand non-negotiables).</t>
         </is>
       </c>
-      <c r="L47" s="7" t="inlineStr">
+      <c r="L50" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M47" s="7" t="inlineStr"/>
-      <c r="N47" s="7" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="7" t="inlineStr">
-        <is>
-          <t>BUG-046</t>
-        </is>
-      </c>
-      <c r="B48" s="7" t="inlineStr">
+      <c r="M50" s="7" t="inlineStr"/>
+      <c r="N50" s="7" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>BUG-049</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-054</t>
         </is>
       </c>
-      <c r="C48" s="7" t="inlineStr">
+      <c r="C51" s="7" t="inlineStr">
         <is>
           <t>8. UI / UX Rules — Monsoon Court Compliance</t>
         </is>
       </c>
-      <c r="D48" s="7" t="inlineStr">
+      <c r="D51" s="7" t="inlineStr">
         <is>
           <t>Required-field marker is a terracotta asterisk, not "(required)" text</t>
         </is>
       </c>
-      <c r="E48" s="7" t="inlineStr">
+      <c r="E51" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F48" s="7" t="inlineStr">
+      <c r="F51" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G48" s="7" t="inlineStr">
+      <c r="G51" s="7" t="inlineStr">
         <is>
           <t>• Open the EP form. Find a required field (e.g. Entrepreneur Name).</t>
         </is>
       </c>
-      <c r="H48" s="7" t="inlineStr"/>
-      <c r="I48" s="7" t="inlineStr">
+      <c r="H51" s="7" t="inlineStr"/>
+      <c r="I51" s="7" t="inlineStr">
         <is>
           <t>Asterisk on the name label is taupe rgb(107,99,89) (inherits label ink-soft), NOT terracotta #C26849. Marker present but wrong colour.</t>
         </is>
       </c>
-      <c r="J48" s="7" t="inlineStr"/>
-      <c r="K48" s="7" t="inlineStr"/>
-      <c r="L48" s="7" t="inlineStr">
+      <c r="J51" s="7" t="inlineStr"/>
+      <c r="K51" s="7" t="inlineStr"/>
+      <c r="L51" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M48" s="7" t="inlineStr"/>
-      <c r="N48" s="7" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="7" t="inlineStr">
-        <is>
-          <t>BUG-047</t>
-        </is>
-      </c>
-      <c r="B49" s="7" t="inlineStr">
+      <c r="M51" s="7" t="inlineStr"/>
+      <c r="N51" s="7" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>BUG-050</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-063</t>
         </is>
       </c>
-      <c r="C49" s="7" t="inlineStr">
+      <c r="C52" s="7" t="inlineStr">
         <is>
           <t>9. Accessibility — WCAG 2.2 AA</t>
         </is>
       </c>
-      <c r="D49" s="7" t="inlineStr">
+      <c r="D52" s="7" t="inlineStr">
         <is>
           <t>Form fields have associated labels (axe-core "label" rule passes)</t>
         </is>
       </c>
-      <c r="E49" s="7" t="inlineStr">
+      <c r="E52" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F49" s="7" t="inlineStr">
+      <c r="F52" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G49" s="7" t="inlineStr">
+      <c r="G52" s="7" t="inlineStr">
         <is>
           <t>• Run axe-core on the EP form (via Playwright).</t>
         </is>
       </c>
-      <c r="H49" s="7" t="inlineStr"/>
-      <c r="I49" s="7" t="inlineStr">
+      <c r="H52" s="7" t="inlineStr"/>
+      <c r="I52" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: label violations: [{"id":"label","n":6}]
 expect(received).toEqual(expected) // deep equality
@@ -25217,58 +25760,58 @@
 +        </t>
         </is>
       </c>
-      <c r="J49" s="7" t="inlineStr">
+      <c r="J52" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\09-a11y-PR-TC-XC-063-·-for-17d03-ssociated-labels-axe-label--sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K49" s="7" t="inlineStr"/>
-      <c r="L49" s="7" t="inlineStr">
+      <c r="K52" s="7" t="inlineStr"/>
+      <c r="L52" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M49" s="7" t="inlineStr"/>
-      <c r="N49" s="7" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="7" t="inlineStr">
-        <is>
-          <t>BUG-048</t>
-        </is>
-      </c>
-      <c r="B50" s="7" t="inlineStr">
+      <c r="M52" s="7" t="inlineStr"/>
+      <c r="N52" s="7" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>BUG-051</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-064</t>
         </is>
       </c>
-      <c r="C50" s="7" t="inlineStr">
+      <c r="C53" s="7" t="inlineStr">
         <is>
           <t>9. Accessibility — WCAG 2.2 AA</t>
         </is>
       </c>
-      <c r="D50" s="7" t="inlineStr">
+      <c r="D53" s="7" t="inlineStr">
         <is>
           <t>Colour contrast meets WCAG AA</t>
         </is>
       </c>
-      <c r="E50" s="7" t="inlineStr">
+      <c r="E53" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F50" s="7" t="inlineStr">
+      <c r="F53" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G50" s="7" t="inlineStr">
+      <c r="G53" s="7" t="inlineStr">
         <is>
           <t>• Run axe-core's contrast check on EP detail, dashboard, framework form.</t>
         </is>
       </c>
-      <c r="H50" s="7" t="inlineStr"/>
-      <c r="I50" s="7" t="inlineStr">
+      <c r="H53" s="7" t="inlineStr"/>
+      <c r="I53" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: contrast violations: [10]
 expect(received).toEqual(expected) // deep equality
@@ -25284,50 +25827,50 @@
 </t>
         </is>
       </c>
-      <c r="J50" s="7" t="inlineStr">
+      <c r="J53" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\09-a11y-PR-TC-XC-064-·-col-8baa1-WCAG-AA-axe-color-contrast--sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K50" s="7" t="inlineStr"/>
-      <c r="L50" s="7" t="inlineStr">
+      <c r="K53" s="7" t="inlineStr"/>
+      <c r="L53" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M50" s="7" t="inlineStr"/>
-      <c r="N50" s="7" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="7" t="inlineStr">
-        <is>
-          <t>BUG-049</t>
-        </is>
-      </c>
-      <c r="B51" s="7" t="inlineStr">
+      <c r="M53" s="7" t="inlineStr"/>
+      <c r="N53" s="7" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>BUG-052</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-064b</t>
         </is>
       </c>
-      <c r="C51" s="7" t="inlineStr">
+      <c r="C54" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D51" s="7" t="inlineStr">
+      <c r="D54" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-064b · landscape colour contrast (WCAG AA)</t>
         </is>
       </c>
-      <c r="E51" s="7" t="inlineStr">
+      <c r="E54" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F51" s="7" t="inlineStr"/>
-      <c r="G51" s="7" t="inlineStr"/>
-      <c r="H51" s="7" t="inlineStr"/>
-      <c r="I51" s="7" t="inlineStr">
+      <c r="F54" s="7" t="inlineStr"/>
+      <c r="G54" s="7" t="inlineStr"/>
+      <c r="H54" s="7" t="inlineStr"/>
+      <c r="I54" s="7" t="inlineStr">
         <is>
           <t>Error: landscape contrast nodes: 4
 expect(received).toEqual(expected) // deep equality
@@ -25342,19 +25885,19 @@
 +     "id": "color-contrast"</t>
         </is>
       </c>
-      <c r="J51" s="7" t="inlineStr">
+      <c r="J54" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\09-a11y-PR-TC-XC-064b-·-landscape-colour-contrast-WCAG-AA--sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K51" s="7" t="inlineStr"/>
-      <c r="L51" s="7" t="inlineStr">
+      <c r="K54" s="7" t="inlineStr"/>
+      <c r="L54" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M51" s="7" t="inlineStr"/>
-      <c r="N51" s="7" t="inlineStr"/>
+      <c r="M54" s="7" t="inlineStr"/>
+      <c r="N54" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -15614,8 +15614,16 @@
       </c>
       <c r="L210" s="7" t="inlineStr"/>
       <c r="M210" s="7" t="inlineStr"/>
-      <c r="N210" s="8" t="inlineStr"/>
-      <c r="O210" s="7" t="inlineStr"/>
+      <c r="N210" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O210" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P210" s="8" t="inlineStr"/>
       <c r="Q210" s="7" t="inlineStr"/>
     </row>
@@ -15682,8 +15690,16 @@
 BRD Rule 8: Log Book per-framework, only this framework's activities.</t>
         </is>
       </c>
-      <c r="N211" s="8" t="inlineStr"/>
-      <c r="O211" s="7" t="inlineStr"/>
+      <c r="N211" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O211" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P211" s="8" t="inlineStr"/>
       <c r="Q211" s="7" t="inlineStr"/>
     </row>
@@ -15743,8 +15759,16 @@
       </c>
       <c r="L212" s="7" t="inlineStr"/>
       <c r="M212" s="7" t="inlineStr"/>
-      <c r="N212" s="8" t="inlineStr"/>
-      <c r="O212" s="7" t="inlineStr"/>
+      <c r="N212" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O212" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P212" s="8" t="inlineStr"/>
       <c r="Q212" s="7" t="inlineStr"/>
     </row>
@@ -15802,8 +15826,16 @@
       </c>
       <c r="L213" s="7" t="inlineStr"/>
       <c r="M213" s="7" t="inlineStr"/>
-      <c r="N213" s="8" t="inlineStr"/>
-      <c r="O213" s="7" t="inlineStr"/>
+      <c r="N213" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O213" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P213" s="8" t="inlineStr"/>
       <c r="Q213" s="7" t="inlineStr"/>
     </row>
@@ -15862,8 +15894,16 @@
       </c>
       <c r="L214" s="7" t="inlineStr"/>
       <c r="M214" s="7" t="inlineStr"/>
-      <c r="N214" s="8" t="inlineStr"/>
-      <c r="O214" s="7" t="inlineStr"/>
+      <c r="N214" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O214" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P214" s="8" t="inlineStr"/>
       <c r="Q214" s="7" t="inlineStr"/>
     </row>
@@ -15922,8 +15962,16 @@
       </c>
       <c r="L215" s="7" t="inlineStr"/>
       <c r="M215" s="7" t="inlineStr"/>
-      <c r="N215" s="8" t="inlineStr"/>
-      <c r="O215" s="7" t="inlineStr"/>
+      <c r="N215" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O215" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P215" s="8" t="inlineStr"/>
       <c r="Q215" s="7" t="inlineStr"/>
     </row>
@@ -15982,8 +16030,16 @@
       </c>
       <c r="L216" s="7" t="inlineStr"/>
       <c r="M216" s="7" t="inlineStr"/>
-      <c r="N216" s="8" t="inlineStr"/>
-      <c r="O216" s="7" t="inlineStr"/>
+      <c r="N216" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O216" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P216" s="8" t="inlineStr"/>
       <c r="Q216" s="7" t="inlineStr"/>
     </row>
@@ -16042,8 +16098,16 @@
       </c>
       <c r="L217" s="7" t="inlineStr"/>
       <c r="M217" s="7" t="inlineStr"/>
-      <c r="N217" s="8" t="inlineStr"/>
-      <c r="O217" s="7" t="inlineStr"/>
+      <c r="N217" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O217" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P217" s="8" t="inlineStr"/>
       <c r="Q217" s="7" t="inlineStr"/>
     </row>
@@ -16101,8 +16165,16 @@
       </c>
       <c r="L218" s="7" t="inlineStr"/>
       <c r="M218" s="7" t="inlineStr"/>
-      <c r="N218" s="8" t="inlineStr"/>
-      <c r="O218" s="7" t="inlineStr"/>
+      <c r="N218" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O218" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P218" s="8" t="inlineStr"/>
       <c r="Q218" s="7" t="inlineStr"/>
     </row>
@@ -16161,8 +16233,16 @@
       </c>
       <c r="L219" s="7" t="inlineStr"/>
       <c r="M219" s="7" t="inlineStr"/>
-      <c r="N219" s="8" t="inlineStr"/>
-      <c r="O219" s="7" t="inlineStr"/>
+      <c r="N219" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O219" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P219" s="8" t="inlineStr"/>
       <c r="Q219" s="7" t="inlineStr"/>
     </row>
@@ -16221,8 +16301,16 @@
       </c>
       <c r="L220" s="7" t="inlineStr"/>
       <c r="M220" s="7" t="inlineStr"/>
-      <c r="N220" s="8" t="inlineStr"/>
-      <c r="O220" s="7" t="inlineStr"/>
+      <c r="N220" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O220" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P220" s="8" t="inlineStr"/>
       <c r="Q220" s="7" t="inlineStr"/>
     </row>
@@ -16280,8 +16368,16 @@
       </c>
       <c r="L221" s="7" t="inlineStr"/>
       <c r="M221" s="7" t="inlineStr"/>
-      <c r="N221" s="8" t="inlineStr"/>
-      <c r="O221" s="7" t="inlineStr"/>
+      <c r="N221" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O221" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P221" s="8" t="inlineStr"/>
       <c r="Q221" s="7" t="inlineStr"/>
     </row>
@@ -16341,9 +16437,9 @@
       </c>
       <c r="L222" s="7" t="inlineStr"/>
       <c r="M222" s="7" t="inlineStr"/>
-      <c r="N222" s="9" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="N222" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O222" s="7" t="inlineStr">
@@ -16408,9 +16504,9 @@
       </c>
       <c r="L223" s="7" t="inlineStr"/>
       <c r="M223" s="7" t="inlineStr"/>
-      <c r="N223" s="9" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="N223" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O223" s="7" t="inlineStr">
@@ -16475,8 +16571,16 @@
       </c>
       <c r="L224" s="7" t="inlineStr"/>
       <c r="M224" s="7" t="inlineStr"/>
-      <c r="N224" s="8" t="inlineStr"/>
-      <c r="O224" s="7" t="inlineStr"/>
+      <c r="N224" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O224" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P224" s="8" t="inlineStr"/>
       <c r="Q224" s="7" t="inlineStr"/>
     </row>
@@ -16534,8 +16638,16 @@
       </c>
       <c r="L225" s="7" t="inlineStr"/>
       <c r="M225" s="7" t="inlineStr"/>
-      <c r="N225" s="8" t="inlineStr"/>
-      <c r="O225" s="7" t="inlineStr"/>
+      <c r="N225" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O225" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P225" s="8" t="inlineStr"/>
       <c r="Q225" s="7" t="inlineStr"/>
     </row>
@@ -16593,8 +16705,16 @@
       </c>
       <c r="L226" s="7" t="inlineStr"/>
       <c r="M226" s="7" t="inlineStr"/>
-      <c r="N226" s="8" t="inlineStr"/>
-      <c r="O226" s="7" t="inlineStr"/>
+      <c r="N226" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O226" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P226" s="8" t="inlineStr"/>
       <c r="Q226" s="7" t="inlineStr"/>
     </row>
@@ -16652,9 +16772,9 @@
       </c>
       <c r="L227" s="7" t="inlineStr"/>
       <c r="M227" s="7" t="inlineStr"/>
-      <c r="N227" s="9" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="N227" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O227" s="7" t="inlineStr">
@@ -16728,9 +16848,9 @@
           <t>BRD Decision: Machinery Required → Infra EE: dropdown selection.</t>
         </is>
       </c>
-      <c r="N228" s="9" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="N228" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O228" s="7" t="inlineStr">
@@ -16795,9 +16915,9 @@
       </c>
       <c r="L229" s="7" t="inlineStr"/>
       <c r="M229" s="7" t="inlineStr"/>
-      <c r="N229" s="9" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="N229" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O229" s="7" t="inlineStr">
@@ -16870,8 +16990,16 @@
           <t>BRD: m-infra consolidated structure.</t>
         </is>
       </c>
-      <c r="N230" s="8" t="inlineStr"/>
-      <c r="O230" s="7" t="inlineStr"/>
+      <c r="N230" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O230" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P230" s="8" t="inlineStr"/>
       <c r="Q230" s="7" t="inlineStr"/>
     </row>
@@ -16938,8 +17066,16 @@
           <t>BRD: SELCO sees full, edits SELCO fields only.</t>
         </is>
       </c>
-      <c r="N231" s="8" t="inlineStr"/>
-      <c r="O231" s="7" t="inlineStr"/>
+      <c r="N231" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O231" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P231" s="8" t="inlineStr"/>
       <c r="Q231" s="7" t="inlineStr"/>
     </row>
@@ -16998,8 +17134,16 @@
       </c>
       <c r="L232" s="7" t="inlineStr"/>
       <c r="M232" s="7" t="inlineStr"/>
-      <c r="N232" s="8" t="inlineStr"/>
-      <c r="O232" s="7" t="inlineStr"/>
+      <c r="N232" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O232" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P232" s="8" t="inlineStr"/>
       <c r="Q232" s="7" t="inlineStr"/>
     </row>
@@ -17057,8 +17201,16 @@
       </c>
       <c r="L233" s="7" t="inlineStr"/>
       <c r="M233" s="7" t="inlineStr"/>
-      <c r="N233" s="8" t="inlineStr"/>
-      <c r="O233" s="7" t="inlineStr"/>
+      <c r="N233" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O233" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P233" s="8" t="inlineStr"/>
       <c r="Q233" s="7" t="inlineStr"/>
     </row>
@@ -17116,9 +17268,9 @@
       </c>
       <c r="L234" s="7" t="inlineStr"/>
       <c r="M234" s="7" t="inlineStr"/>
-      <c r="N234" s="9" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="N234" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O234" s="7" t="inlineStr">
@@ -17183,23 +17335,14 @@
       </c>
       <c r="L235" s="7" t="inlineStr"/>
       <c r="M235" s="7" t="inlineStr"/>
-      <c r="N235" s="12" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="N235" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O235" s="7" t="inlineStr">
         <is>
-          <t>Error: Backend identifiers visible on Unit Pricing: {"doctype-df-prefix":["DF UNIT"]}
-expect.toEqual // deep equality
-- Expected - 1
-+ Received + 5
-- Object {}
-+ Object {
-+  "doctype-df-prefix": Array [
-+   "DF UNIT",
-+  ],
-+ }</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="P235" s="8" t="inlineStr">
@@ -17331,9 +17474,9 @@
       </c>
       <c r="L237" s="7" t="inlineStr"/>
       <c r="M237" s="7" t="inlineStr"/>
-      <c r="N237" s="9" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="N237" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O237" s="7" t="inlineStr">
@@ -17398,9 +17541,9 @@
       </c>
       <c r="L238" s="7" t="inlineStr"/>
       <c r="M238" s="7" t="inlineStr"/>
-      <c r="N238" s="9" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="N238" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O238" s="7" t="inlineStr">
@@ -17465,8 +17608,16 @@
       </c>
       <c r="L239" s="7" t="inlineStr"/>
       <c r="M239" s="7" t="inlineStr"/>
-      <c r="N239" s="8" t="inlineStr"/>
-      <c r="O239" s="7" t="inlineStr"/>
+      <c r="N239" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O239" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P239" s="8" t="inlineStr"/>
       <c r="Q239" s="7" t="inlineStr"/>
     </row>
@@ -17525,8 +17676,16 @@
       </c>
       <c r="L240" s="7" t="inlineStr"/>
       <c r="M240" s="7" t="inlineStr"/>
-      <c r="N240" s="8" t="inlineStr"/>
-      <c r="O240" s="7" t="inlineStr"/>
+      <c r="N240" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O240" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P240" s="8" t="inlineStr"/>
       <c r="Q240" s="7" t="inlineStr"/>
     </row>
@@ -17584,8 +17743,16 @@
       </c>
       <c r="L241" s="7" t="inlineStr"/>
       <c r="M241" s="7" t="inlineStr"/>
-      <c r="N241" s="8" t="inlineStr"/>
-      <c r="O241" s="7" t="inlineStr"/>
+      <c r="N241" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O241" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P241" s="8" t="inlineStr"/>
       <c r="Q241" s="7" t="inlineStr"/>
     </row>
@@ -17643,9 +17810,9 @@
       </c>
       <c r="L242" s="7" t="inlineStr"/>
       <c r="M242" s="7" t="inlineStr"/>
-      <c r="N242" s="9" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="N242" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O242" s="7" t="inlineStr">
@@ -17710,9 +17877,9 @@
       </c>
       <c r="L243" s="7" t="inlineStr"/>
       <c r="M243" s="7" t="inlineStr"/>
-      <c r="N243" s="9" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="N243" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O243" s="7" t="inlineStr">
@@ -17844,9 +18011,9 @@
       </c>
       <c r="L245" s="7" t="inlineStr"/>
       <c r="M245" s="7" t="inlineStr"/>
-      <c r="N245" s="9" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="N245" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O245" s="7" t="inlineStr">
@@ -17911,9 +18078,9 @@
       </c>
       <c r="L246" s="7" t="inlineStr"/>
       <c r="M246" s="7" t="inlineStr"/>
-      <c r="N246" s="9" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="N246" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O246" s="7" t="inlineStr">
@@ -17978,9 +18145,9 @@
       </c>
       <c r="L247" s="7" t="inlineStr"/>
       <c r="M247" s="7" t="inlineStr"/>
-      <c r="N247" s="9" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="N247" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O247" s="7" t="inlineStr">
@@ -18045,8 +18212,16 @@
       </c>
       <c r="L248" s="7" t="inlineStr"/>
       <c r="M248" s="7" t="inlineStr"/>
-      <c r="N248" s="8" t="inlineStr"/>
-      <c r="O248" s="7" t="inlineStr"/>
+      <c r="N248" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O248" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P248" s="8" t="inlineStr"/>
       <c r="Q248" s="7" t="inlineStr"/>
     </row>
@@ -18105,8 +18280,16 @@
       </c>
       <c r="L249" s="7" t="inlineStr"/>
       <c r="M249" s="7" t="inlineStr"/>
-      <c r="N249" s="8" t="inlineStr"/>
-      <c r="O249" s="7" t="inlineStr"/>
+      <c r="N249" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O249" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P249" s="8" t="inlineStr"/>
       <c r="Q249" s="7" t="inlineStr"/>
     </row>
@@ -18165,8 +18348,16 @@
       </c>
       <c r="L250" s="7" t="inlineStr"/>
       <c r="M250" s="7" t="inlineStr"/>
-      <c r="N250" s="8" t="inlineStr"/>
-      <c r="O250" s="7" t="inlineStr"/>
+      <c r="N250" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O250" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P250" s="8" t="inlineStr"/>
       <c r="Q250" s="7" t="inlineStr"/>
     </row>
@@ -18225,8 +18416,16 @@
       </c>
       <c r="L251" s="7" t="inlineStr"/>
       <c r="M251" s="7" t="inlineStr"/>
-      <c r="N251" s="8" t="inlineStr"/>
-      <c r="O251" s="7" t="inlineStr"/>
+      <c r="N251" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O251" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P251" s="8" t="inlineStr"/>
       <c r="Q251" s="7" t="inlineStr"/>
     </row>
@@ -18284,8 +18483,16 @@
       </c>
       <c r="L252" s="7" t="inlineStr"/>
       <c r="M252" s="7" t="inlineStr"/>
-      <c r="N252" s="8" t="inlineStr"/>
-      <c r="O252" s="7" t="inlineStr"/>
+      <c r="N252" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O252" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P252" s="8" t="inlineStr"/>
       <c r="Q252" s="7" t="inlineStr"/>
     </row>
@@ -18343,8 +18550,16 @@
       </c>
       <c r="L253" s="7" t="inlineStr"/>
       <c r="M253" s="7" t="inlineStr"/>
-      <c r="N253" s="8" t="inlineStr"/>
-      <c r="O253" s="7" t="inlineStr"/>
+      <c r="N253" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O253" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P253" s="8" t="inlineStr"/>
       <c r="Q253" s="7" t="inlineStr"/>
     </row>
@@ -18402,8 +18617,16 @@
       </c>
       <c r="L254" s="7" t="inlineStr"/>
       <c r="M254" s="7" t="inlineStr"/>
-      <c r="N254" s="8" t="inlineStr"/>
-      <c r="O254" s="7" t="inlineStr"/>
+      <c r="N254" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O254" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P254" s="8" t="inlineStr"/>
       <c r="Q254" s="7" t="inlineStr"/>
     </row>
@@ -18461,8 +18684,16 @@
       </c>
       <c r="L255" s="7" t="inlineStr"/>
       <c r="M255" s="7" t="inlineStr"/>
-      <c r="N255" s="8" t="inlineStr"/>
-      <c r="O255" s="7" t="inlineStr"/>
+      <c r="N255" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O255" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P255" s="8" t="inlineStr"/>
       <c r="Q255" s="7" t="inlineStr"/>
     </row>
@@ -18520,8 +18751,16 @@
       </c>
       <c r="L256" s="7" t="inlineStr"/>
       <c r="M256" s="7" t="inlineStr"/>
-      <c r="N256" s="8" t="inlineStr"/>
-      <c r="O256" s="7" t="inlineStr"/>
+      <c r="N256" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O256" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P256" s="8" t="inlineStr"/>
       <c r="Q256" s="7" t="inlineStr"/>
     </row>
@@ -18579,8 +18818,16 @@
       </c>
       <c r="L257" s="7" t="inlineStr"/>
       <c r="M257" s="7" t="inlineStr"/>
-      <c r="N257" s="8" t="inlineStr"/>
-      <c r="O257" s="7" t="inlineStr"/>
+      <c r="N257" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O257" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P257" s="8" t="inlineStr"/>
       <c r="Q257" s="7" t="inlineStr"/>
     </row>
@@ -18638,8 +18885,16 @@
       </c>
       <c r="L258" s="7" t="inlineStr"/>
       <c r="M258" s="7" t="inlineStr"/>
-      <c r="N258" s="8" t="inlineStr"/>
-      <c r="O258" s="7" t="inlineStr"/>
+      <c r="N258" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O258" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P258" s="8" t="inlineStr"/>
       <c r="Q258" s="7" t="inlineStr"/>
     </row>

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -16638,9 +16638,9 @@
       </c>
       <c r="L225" s="7" t="inlineStr"/>
       <c r="M225" s="7" t="inlineStr"/>
-      <c r="N225" s="13" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+      <c r="N225" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O225" s="7" t="inlineStr">
@@ -16772,17 +16772,21 @@
       </c>
       <c r="L227" s="7" t="inlineStr"/>
       <c r="M227" s="7" t="inlineStr"/>
-      <c r="N227" s="13" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+      <c r="N227" s="12" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
       <c r="O227" s="7" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="P227" s="8" t="inlineStr"/>
+          <t>UI form-fill: Cost Rs50,000, Useful Life 10y -&gt; MONTHLY DEPRECIATION Rs416.67 (= Rs5,000/yr, straight-line cost/life). NO salvage/residual-value field on the form, so it does NOT match BRD (cost-salvage)/life = Rs4,500/yr. Salvage not captured; depreciation overstated vs spec.</t>
+        </is>
+      </c>
+      <c r="P227" s="8" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
       <c r="Q227" s="7" t="inlineStr"/>
     </row>
     <row r="228">
@@ -23044,7 +23048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N54"/>
+  <dimension ref="A1:N55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -23926,28 +23930,80 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-FWC-BPC-002</t>
+          <t>PR-TC-FW-MACH-001</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>(not in master — add as test case)</t>
+          <t>17. The 27 Diagnostic Frameworks</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-FWC-BPC-002 · Business Plan Canvas header has no raw doctype / UUID</t>
+          <t>Add machine — depreciation auto-calculated per straight-line method</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr"/>
-      <c r="G17" s="7" t="inlineStr"/>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>P0 — Blocker</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>• Cost = 50,000, Useful Life = 10 years, Residual = 5,000.</t>
+        </is>
+      </c>
       <c r="H17" s="7" t="inlineStr"/>
       <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>UI form-fill: Cost Rs50,000, Useful Life 10y -&gt; MONTHLY DEPRECIATION Rs416.67 (= Rs5,000/yr, straight-line cost/life). NO salvage/residual-value field on the form, so it does NOT match BRD (cost-salvage)/life = Rs4,500/yr. Salvage not captured; depreciation overstated vs spec.</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr"/>
+      <c r="K17" s="7" t="inlineStr"/>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M17" s="7" t="inlineStr"/>
+      <c r="N17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>BUG-016</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-FWC-BPC-002</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>(not in master — add as test case)</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-FWC-BPC-002 · Business Plan Canvas header has no raw doctype / UUID</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr"/>
+      <c r="G18" s="7" t="inlineStr"/>
+      <c r="H18" s="7" t="inlineStr"/>
+      <c r="I18" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Business Plan Canvas: {"doctype-df-prefix":["DF BUSINESS"]}
 expect.toEqual // deep equality
@@ -23961,50 +24017,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J17" s="7" t="inlineStr">
+      <c r="J18" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Bu-a8fd3-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K17" s="7" t="inlineStr"/>
-      <c r="L17" s="7" t="inlineStr">
+      <c r="K18" s="7" t="inlineStr"/>
+      <c r="L18" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M17" s="7" t="inlineStr"/>
-      <c r="N17" s="7" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>BUG-016</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="M18" s="7" t="inlineStr"/>
+      <c r="N18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>BUG-017</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-BREG-002</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-BREG-002 · Business Registration header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr"/>
-      <c r="G18" s="7" t="inlineStr"/>
-      <c r="H18" s="7" t="inlineStr"/>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr"/>
+      <c r="G19" s="7" t="inlineStr"/>
+      <c r="H19" s="7" t="inlineStr"/>
+      <c r="I19" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Business Registration: {"doctype-df-prefix":["DF BUSINESS"]}
 expect.toEqual // deep equality
@@ -24018,50 +24074,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J18" s="7" t="inlineStr">
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Bu-6c730-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K18" s="7" t="inlineStr"/>
-      <c r="L18" s="7" t="inlineStr">
+      <c r="K19" s="7" t="inlineStr"/>
+      <c r="L19" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M18" s="7" t="inlineStr"/>
-      <c r="N18" s="7" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>BUG-017</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="M19" s="7" t="inlineStr"/>
+      <c r="N19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>BUG-018</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-CA-002</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-CA-002 · Customer Analysis header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr"/>
-      <c r="G19" s="7" t="inlineStr"/>
-      <c r="H19" s="7" t="inlineStr"/>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="F20" s="7" t="inlineStr"/>
+      <c r="G20" s="7" t="inlineStr"/>
+      <c r="H20" s="7" t="inlineStr"/>
+      <c r="I20" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Customer Analysis: {"doctype-df-prefix":["DF CUSTOMER"]}
 expect.toEqual // deep equality
@@ -24075,50 +24131,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J19" s="7" t="inlineStr">
+      <c r="J20" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Cu-6ed58-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K19" s="7" t="inlineStr"/>
-      <c r="L19" s="7" t="inlineStr">
+      <c r="K20" s="7" t="inlineStr"/>
+      <c r="L20" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M19" s="7" t="inlineStr"/>
-      <c r="N19" s="7" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>BUG-018</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="M20" s="7" t="inlineStr"/>
+      <c r="N20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>BUG-019</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-CB-002</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-CB-002 · Capacity Building header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr"/>
-      <c r="G20" s="7" t="inlineStr"/>
-      <c r="H20" s="7" t="inlineStr"/>
-      <c r="I20" s="7" t="inlineStr">
+      <c r="F21" s="7" t="inlineStr"/>
+      <c r="G21" s="7" t="inlineStr"/>
+      <c r="H21" s="7" t="inlineStr"/>
+      <c r="I21" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Capacity Building: {"doctype-df-prefix":["DF CAPACITY"]}
 expect.toEqual // deep equality
@@ -24132,50 +24188,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J20" s="7" t="inlineStr">
+      <c r="J21" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Ca-83199-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K20" s="7" t="inlineStr"/>
-      <c r="L20" s="7" t="inlineStr">
+      <c r="K21" s="7" t="inlineStr"/>
+      <c r="L21" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M20" s="7" t="inlineStr"/>
-      <c r="N20" s="7" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>BUG-019</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="M21" s="7" t="inlineStr"/>
+      <c r="N21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>BUG-020</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-DL-002</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-DL-002 · Digital Literacy header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr"/>
-      <c r="G21" s="7" t="inlineStr"/>
-      <c r="H21" s="7" t="inlineStr"/>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="F22" s="7" t="inlineStr"/>
+      <c r="G22" s="7" t="inlineStr"/>
+      <c r="H22" s="7" t="inlineStr"/>
+      <c r="I22" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Digital Literacy: {"doctype-df-prefix":["DF DIGITAL"]}
 expect.toEqual // deep equality
@@ -24189,50 +24245,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J21" s="7" t="inlineStr">
+      <c r="J22" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Di-845ef-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K21" s="7" t="inlineStr"/>
-      <c r="L21" s="7" t="inlineStr">
+      <c r="K22" s="7" t="inlineStr"/>
+      <c r="L22" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M21" s="7" t="inlineStr"/>
-      <c r="N21" s="7" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>BUG-020</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="M22" s="7" t="inlineStr"/>
+      <c r="N22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>BUG-021</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-INFR-002</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-INFR-002 · Infrastructure (BE/EE/CE) header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr"/>
-      <c r="G22" s="7" t="inlineStr"/>
-      <c r="H22" s="7" t="inlineStr"/>
-      <c r="I22" s="7" t="inlineStr">
+      <c r="F23" s="7" t="inlineStr"/>
+      <c r="G23" s="7" t="inlineStr"/>
+      <c r="H23" s="7" t="inlineStr"/>
+      <c r="I23" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Infrastructure: {"doctype-df-prefix":["DF INFRASTRUCTURE"]}
 expect.toEqual // deep equality
@@ -24246,50 +24302,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J22" s="7" t="inlineStr">
+      <c r="J23" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-In-3328d-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K22" s="7" t="inlineStr"/>
-      <c r="L22" s="7" t="inlineStr">
+      <c r="K23" s="7" t="inlineStr"/>
+      <c r="L23" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M22" s="7" t="inlineStr"/>
-      <c r="N22" s="7" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>BUG-021</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="M23" s="7" t="inlineStr"/>
+      <c r="N23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>BUG-022</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-LABL-002</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-LABL-002 · Marketing Label header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F23" s="7" t="inlineStr"/>
-      <c r="G23" s="7" t="inlineStr"/>
-      <c r="H23" s="7" t="inlineStr"/>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="F24" s="7" t="inlineStr"/>
+      <c r="G24" s="7" t="inlineStr"/>
+      <c r="H24" s="7" t="inlineStr"/>
+      <c r="I24" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Marketing Label: {"doctype-df-prefix":["DF MARKETING"]}
 expect.toEqual // deep equality
@@ -24303,50 +24359,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J23" s="7" t="inlineStr">
+      <c r="J24" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Ma-11834-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K23" s="7" t="inlineStr"/>
-      <c r="L23" s="7" t="inlineStr">
+      <c r="K24" s="7" t="inlineStr"/>
+      <c r="L24" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M23" s="7" t="inlineStr"/>
-      <c r="N23" s="7" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>BUG-022</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="M24" s="7" t="inlineStr"/>
+      <c r="N24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>BUG-023</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-ML-002</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-ML-002 · Market Linkage header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr"/>
-      <c r="G24" s="7" t="inlineStr"/>
-      <c r="H24" s="7" t="inlineStr"/>
-      <c r="I24" s="7" t="inlineStr">
+      <c r="F25" s="7" t="inlineStr"/>
+      <c r="G25" s="7" t="inlineStr"/>
+      <c r="H25" s="7" t="inlineStr"/>
+      <c r="I25" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Market Linkage: {"doctype-df-prefix":["DF MARKET"]}
 expect.toEqual // deep equality
@@ -24360,50 +24416,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J24" s="7" t="inlineStr">
+      <c r="J25" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Ma-22f69-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K24" s="7" t="inlineStr"/>
-      <c r="L24" s="7" t="inlineStr">
+      <c r="K25" s="7" t="inlineStr"/>
+      <c r="L25" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M24" s="7" t="inlineStr"/>
-      <c r="N24" s="7" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>BUG-023</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="M25" s="7" t="inlineStr"/>
+      <c r="N25" s="7" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>BUG-024</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-MR-002</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-MR-002 · Market Research header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="E26" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F25" s="7" t="inlineStr"/>
-      <c r="G25" s="7" t="inlineStr"/>
-      <c r="H25" s="7" t="inlineStr"/>
-      <c r="I25" s="7" t="inlineStr">
+      <c r="F26" s="7" t="inlineStr"/>
+      <c r="G26" s="7" t="inlineStr"/>
+      <c r="H26" s="7" t="inlineStr"/>
+      <c r="I26" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Market Research: {"doctype-df-prefix":["DF MARKET"]}
 expect.toEqual // deep equality
@@ -24417,50 +24473,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J25" s="7" t="inlineStr">
+      <c r="J26" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Ma-6eb23-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K25" s="7" t="inlineStr"/>
-      <c r="L25" s="7" t="inlineStr">
+      <c r="K26" s="7" t="inlineStr"/>
+      <c r="L26" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M25" s="7" t="inlineStr"/>
-      <c r="N25" s="7" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>BUG-024</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="M26" s="7" t="inlineStr"/>
+      <c r="N26" s="7" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>BUG-025</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PCMP-002</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PCMP-002 · Product Compliance header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F26" s="7" t="inlineStr"/>
-      <c r="G26" s="7" t="inlineStr"/>
-      <c r="H26" s="7" t="inlineStr"/>
-      <c r="I26" s="7" t="inlineStr">
+      <c r="F27" s="7" t="inlineStr"/>
+      <c r="G27" s="7" t="inlineStr"/>
+      <c r="H27" s="7" t="inlineStr"/>
+      <c r="I27" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Product Compliance: {"doctype-df-prefix":["DF PRODUCT"]}
 expect.toEqual // deep equality
@@ -24474,50 +24530,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J26" s="7" t="inlineStr">
+      <c r="J27" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Pr-be46f-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K26" s="7" t="inlineStr"/>
-      <c r="L26" s="7" t="inlineStr">
+      <c r="K27" s="7" t="inlineStr"/>
+      <c r="L27" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M26" s="7" t="inlineStr"/>
-      <c r="N26" s="7" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>BUG-025</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="M27" s="7" t="inlineStr"/>
+      <c r="N27" s="7" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>BUG-026</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PROM-002</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PROM-002 · Promotional Marketing header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr"/>
-      <c r="G27" s="7" t="inlineStr"/>
-      <c r="H27" s="7" t="inlineStr"/>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="F28" s="7" t="inlineStr"/>
+      <c r="G28" s="7" t="inlineStr"/>
+      <c r="H28" s="7" t="inlineStr"/>
+      <c r="I28" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Promotional Marketing: {"doctype-df-prefix":["DF PROMOTIONAL"]}
 expect.toEqual // deep equality
@@ -24531,50 +24587,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J27" s="7" t="inlineStr">
+      <c r="J28" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Pr-d8d12-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K27" s="7" t="inlineStr"/>
-      <c r="L27" s="7" t="inlineStr">
+      <c r="K28" s="7" t="inlineStr"/>
+      <c r="L28" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M27" s="7" t="inlineStr"/>
-      <c r="N27" s="7" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>BUG-026</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="M28" s="7" t="inlineStr"/>
+      <c r="N28" s="7" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>BUG-027</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PROT-002</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PROT-002 · Product Prototyping header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr"/>
-      <c r="G28" s="7" t="inlineStr"/>
-      <c r="H28" s="7" t="inlineStr"/>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="F29" s="7" t="inlineStr"/>
+      <c r="G29" s="7" t="inlineStr"/>
+      <c r="H29" s="7" t="inlineStr"/>
+      <c r="I29" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Product Prototyping: {"doctype-df-prefix":["DF PRODUCT"]}
 expect.toEqual // deep equality
@@ -24588,50 +24644,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J28" s="7" t="inlineStr">
+      <c r="J29" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Pr-1120e-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K28" s="7" t="inlineStr"/>
-      <c r="L28" s="7" t="inlineStr">
+      <c r="K29" s="7" t="inlineStr"/>
+      <c r="L29" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M28" s="7" t="inlineStr"/>
-      <c r="N28" s="7" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>BUG-027</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="M29" s="7" t="inlineStr"/>
+      <c r="N29" s="7" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>BUG-028</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PTCH-002</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PTCH-002 · Pitch Deck header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="E30" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr"/>
-      <c r="G29" s="7" t="inlineStr"/>
-      <c r="H29" s="7" t="inlineStr"/>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="F30" s="7" t="inlineStr"/>
+      <c r="G30" s="7" t="inlineStr"/>
+      <c r="H30" s="7" t="inlineStr"/>
+      <c r="I30" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Pitch Deck: {"doctype-df-prefix":["DF PITCH"]}
 expect.toEqual // deep equality
@@ -24645,50 +24701,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J29" s="7" t="inlineStr">
+      <c r="J30" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Pi-fefd5-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K29" s="7" t="inlineStr"/>
-      <c r="L29" s="7" t="inlineStr">
+      <c r="K30" s="7" t="inlineStr"/>
+      <c r="L30" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M29" s="7" t="inlineStr"/>
-      <c r="N29" s="7" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>BUG-028</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="M30" s="7" t="inlineStr"/>
+      <c r="N30" s="7" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>BUG-029</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PTST-002</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PTST-002 · Product Testing header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="E31" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr"/>
-      <c r="G30" s="7" t="inlineStr"/>
-      <c r="H30" s="7" t="inlineStr"/>
-      <c r="I30" s="7" t="inlineStr">
+      <c r="F31" s="7" t="inlineStr"/>
+      <c r="G31" s="7" t="inlineStr"/>
+      <c r="H31" s="7" t="inlineStr"/>
+      <c r="I31" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Product Testing: {"doctype-df-prefix":["DF PRODUCT"]}
 expect.toEqual // deep equality
@@ -24702,50 +24758,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J30" s="7" t="inlineStr">
+      <c r="J31" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Pr-3e912-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K30" s="7" t="inlineStr"/>
-      <c r="L30" s="7" t="inlineStr">
+      <c r="K31" s="7" t="inlineStr"/>
+      <c r="L31" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M30" s="7" t="inlineStr"/>
-      <c r="N30" s="7" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>BUG-029</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="M31" s="7" t="inlineStr"/>
+      <c r="N31" s="7" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>BUG-030</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-QC-002</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-QC-002 · Quality Control header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="E32" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr"/>
-      <c r="G31" s="7" t="inlineStr"/>
-      <c r="H31" s="7" t="inlineStr"/>
-      <c r="I31" s="7" t="inlineStr">
+      <c r="F32" s="7" t="inlineStr"/>
+      <c r="G32" s="7" t="inlineStr"/>
+      <c r="H32" s="7" t="inlineStr"/>
+      <c r="I32" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Quality Control: {"doctype-df-prefix":["DF QUALITY"]}
 expect.toEqual // deep equality
@@ -24759,50 +24815,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J31" s="7" t="inlineStr">
+      <c r="J32" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Qu-ae31c-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K31" s="7" t="inlineStr"/>
-      <c r="L31" s="7" t="inlineStr">
+      <c r="K32" s="7" t="inlineStr"/>
+      <c r="L32" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M31" s="7" t="inlineStr"/>
-      <c r="N31" s="7" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>BUG-030</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="M32" s="7" t="inlineStr"/>
+      <c r="N32" s="7" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>BUG-031</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-SCHM-002</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D33" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-SCHM-002 · Schemes &amp; Funding header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
+      <c r="E33" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F32" s="7" t="inlineStr"/>
-      <c r="G32" s="7" t="inlineStr"/>
-      <c r="H32" s="7" t="inlineStr"/>
-      <c r="I32" s="7" t="inlineStr">
+      <c r="F33" s="7" t="inlineStr"/>
+      <c r="G33" s="7" t="inlineStr"/>
+      <c r="H33" s="7" t="inlineStr"/>
+      <c r="I33" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Schemes &amp; Funding: {"doctype-df-prefix":["DF SCHEMES"]}
 expect.toEqual // deep equality
@@ -24816,50 +24872,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J32" s="7" t="inlineStr">
+      <c r="J33" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Sc-67cb2-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K32" s="7" t="inlineStr"/>
-      <c r="L32" s="7" t="inlineStr">
+      <c r="K33" s="7" t="inlineStr"/>
+      <c r="L33" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M32" s="7" t="inlineStr"/>
-      <c r="N32" s="7" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>BUG-031</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="M33" s="7" t="inlineStr"/>
+      <c r="N33" s="7" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>BUG-032</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-STD-002</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-STD-002 · Standardization header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
+      <c r="E34" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F33" s="7" t="inlineStr"/>
-      <c r="G33" s="7" t="inlineStr"/>
-      <c r="H33" s="7" t="inlineStr"/>
-      <c r="I33" s="7" t="inlineStr">
+      <c r="F34" s="7" t="inlineStr"/>
+      <c r="G34" s="7" t="inlineStr"/>
+      <c r="H34" s="7" t="inlineStr"/>
+      <c r="I34" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Standardization: {"doctype-df-prefix":["DF STANDARDIZATION"]}
 expect.toEqual // deep equality
@@ -24873,50 +24929,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J33" s="7" t="inlineStr">
+      <c r="J34" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-St-b8b93-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K33" s="7" t="inlineStr"/>
-      <c r="L33" s="7" t="inlineStr">
+      <c r="K34" s="7" t="inlineStr"/>
+      <c r="L34" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M33" s="7" t="inlineStr"/>
-      <c r="N33" s="7" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>BUG-032</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="M34" s="7" t="inlineStr"/>
+      <c r="N34" s="7" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>BUG-033</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-UP-002</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-UP-002 · Unit Pricing header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E34" s="7" t="inlineStr">
+      <c r="E35" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F34" s="7" t="inlineStr"/>
-      <c r="G34" s="7" t="inlineStr"/>
-      <c r="H34" s="7" t="inlineStr"/>
-      <c r="I34" s="7" t="inlineStr">
+      <c r="F35" s="7" t="inlineStr"/>
+      <c r="G35" s="7" t="inlineStr"/>
+      <c r="H35" s="7" t="inlineStr"/>
+      <c r="I35" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Unit Pricing: {"doctype-df-prefix":["DF UNIT"]}
 expect.toEqual // deep equality
@@ -24930,58 +24986,58 @@
 + }</t>
         </is>
       </c>
-      <c r="J34" s="7" t="inlineStr">
+      <c r="J35" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Un-0c652-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K34" s="7" t="inlineStr"/>
-      <c r="L34" s="7" t="inlineStr">
+      <c r="K35" s="7" t="inlineStr"/>
+      <c r="L35" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M34" s="7" t="inlineStr"/>
-      <c r="N34" s="7" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>BUG-033</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="M35" s="7" t="inlineStr"/>
+      <c r="N35" s="7" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>BUG-034</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>PR-TC-MS-008</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>14. Masters &amp; Reference Data</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>Cohort end date must be after start date</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F35" s="7" t="inlineStr">
+      <c r="F36" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G35" s="7" t="inlineStr">
+      <c r="G36" s="7" t="inlineStr">
         <is>
           <t>• Start = 01-Apr-2026, End = 31-Mar-2025.</t>
         </is>
       </c>
-      <c r="H35" s="7" t="inlineStr"/>
-      <c r="I35" s="7" t="inlineStr">
+      <c r="H36" s="7" t="inlineStr"/>
+      <c r="I36" s="7" t="inlineStr">
         <is>
           <t>Error: end-before-start cohort should be rejected
 expect(received).toBeGreaterThanOrEqual(expected)
@@ -24989,59 +25045,59 @@
 Received:    200</t>
         </is>
       </c>
-      <c r="J35" s="7" t="inlineStr"/>
-      <c r="K35" s="7" t="inlineStr"/>
-      <c r="L35" s="7" t="inlineStr">
+      <c r="J36" s="7" t="inlineStr"/>
+      <c r="K36" s="7" t="inlineStr"/>
+      <c r="L36" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M35" s="7" t="inlineStr"/>
-      <c r="N35" s="7" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>BUG-034</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="M36" s="7" t="inlineStr"/>
+      <c r="N36" s="7" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>BUG-035</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>PR-TC-MS-011</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>14. Masters &amp; Reference Data</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t>Seed import: 351 rows from "Final PRIME Rural Task Dropdowns Master.xlsx"</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F36" s="7" t="inlineStr">
+      <c r="F37" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G36" s="7" t="inlineStr">
+      <c r="G37" s="7" t="inlineStr">
         <is>
           <t>• Run the seed migration script (or use bulk import) using the canonical xlsx.
 • Verify count = 351.</t>
         </is>
       </c>
-      <c r="H36" s="7" t="inlineStr">
+      <c r="H37" s="7" t="inlineStr">
         <is>
           <t>351 Framework Task Master records exist. Each has: module, framework, task_no, task_name, description, phase. Em-dash phase rows have phase = "Other". Logistic Service has its "Other" row added (was missing in the xlsx).</t>
         </is>
       </c>
-      <c r="I36" s="7" t="inlineStr">
+      <c r="I37" s="7" t="inlineStr">
         <is>
           <t>Error: Framework Task Master doctype should exist
 expect(received).toBe(expected) // Object.is equality
@@ -25049,58 +25105,58 @@
 Received: 404</t>
         </is>
       </c>
-      <c r="J36" s="7" t="inlineStr"/>
-      <c r="K36" s="7" t="inlineStr">
+      <c r="J37" s="7" t="inlineStr"/>
+      <c r="K37" s="7" t="inlineStr">
         <is>
           <t>BRD PR-XC-002b.</t>
         </is>
       </c>
-      <c r="L36" s="7" t="inlineStr">
+      <c r="L37" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M36" s="7" t="inlineStr"/>
-      <c r="N36" s="7" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>BUG-035</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="M37" s="7" t="inlineStr"/>
+      <c r="N37" s="7" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>BUG-036</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>PR-TC-MS-015</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>14. Masters &amp; Reference Data</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
         <is>
           <t>Document types: Aadhaar, PAN, EPIC, Bank Passbook, Photo, Other</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
+      <c r="E38" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F37" s="7" t="inlineStr">
+      <c r="F38" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G37" s="7" t="inlineStr">
+      <c r="G38" s="7" t="inlineStr">
         <is>
           <t>• Masters → Document Master → list.</t>
         </is>
       </c>
-      <c r="H37" s="7" t="inlineStr"/>
-      <c r="I37" s="7" t="inlineStr">
+      <c r="H38" s="7" t="inlineStr"/>
+      <c r="I38" s="7" t="inlineStr">
         <is>
           <t>Error: expected the standard document types (Aadhaar/PAN/EPIC/Bank/Photo/...)
 expect(received).toBeGreaterThanOrEqual(expected)
@@ -25108,58 +25164,58 @@
 Received:    5</t>
         </is>
       </c>
-      <c r="J37" s="7" t="inlineStr"/>
-      <c r="K37" s="7" t="inlineStr"/>
-      <c r="L37" s="7" t="inlineStr">
+      <c r="J38" s="7" t="inlineStr"/>
+      <c r="K38" s="7" t="inlineStr"/>
+      <c r="L38" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M37" s="7" t="inlineStr"/>
-      <c r="N37" s="7" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>BUG-036</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="M38" s="7" t="inlineStr"/>
+      <c r="N38" s="7" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>BUG-037</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>PR-TC-MS-020</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
+      <c r="C39" s="7" t="inlineStr">
         <is>
           <t>14. Masters &amp; Reference Data</t>
         </is>
       </c>
-      <c r="D38" s="7" t="inlineStr">
+      <c r="D39" s="7" t="inlineStr">
         <is>
           <t>19 schemes pre-seeded (MOVCDNER, CGTMSE, NEHHDC, PGS-India Organic, etc.)</t>
         </is>
       </c>
-      <c r="E38" s="7" t="inlineStr">
+      <c r="E39" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F38" s="7" t="inlineStr">
+      <c r="F39" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G38" s="7" t="inlineStr">
+      <c r="G39" s="7" t="inlineStr">
         <is>
           <t>• Open Scheme Master list. Count rows.</t>
         </is>
       </c>
-      <c r="H38" s="7" t="inlineStr">
+      <c r="H39" s="7" t="inlineStr">
         <is>
           <t>19 schemes present per BRD m-schemes. Each has: name, type (Grant / Loan / Subsidy / Certification), eligibility, min/max amount, applicable sectors, interest rate (if loan).</t>
         </is>
       </c>
-      <c r="I38" s="7" t="inlineStr">
+      <c r="I39" s="7" t="inlineStr">
         <is>
           <t>Error: BRD m-schemes expects 19 pre-seeded schemes
 expect(received).toBeGreaterThanOrEqual(expected)
@@ -25167,104 +25223,104 @@
 Received:    3</t>
         </is>
       </c>
-      <c r="J38" s="7" t="inlineStr"/>
-      <c r="K38" s="7" t="inlineStr">
+      <c r="J39" s="7" t="inlineStr"/>
+      <c r="K39" s="7" t="inlineStr">
         <is>
           <t>BRD m-schemes.</t>
         </is>
       </c>
-      <c r="L38" s="7" t="inlineStr">
+      <c r="L39" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M38" s="7" t="inlineStr"/>
-      <c r="N38" s="7" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>BUG-037</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="M39" s="7" t="inlineStr"/>
+      <c r="N39" s="7" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>BUG-038</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t>PR-TC-SEC-005</t>
         </is>
       </c>
-      <c r="C39" s="7" t="inlineStr">
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>23. Security — OWASP &amp; Beyond</t>
         </is>
       </c>
-      <c r="D39" s="7" t="inlineStr">
+      <c r="D40" s="7" t="inlineStr">
         <is>
           <t>Content-Security-Policy header set, restricts inline scripts</t>
         </is>
       </c>
-      <c r="E39" s="7" t="inlineStr">
+      <c r="E40" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F39" s="7" t="inlineStr">
+      <c r="F40" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G39" s="7" t="inlineStr">
+      <c r="G40" s="7" t="inlineStr">
         <is>
           <t>• Inspect response headers on /app/.</t>
         </is>
       </c>
-      <c r="H39" s="7" t="inlineStr"/>
-      <c r="I39" s="7" t="inlineStr">
+      <c r="H40" s="7" t="inlineStr"/>
+      <c r="I40" s="7" t="inlineStr">
         <is>
           <t>Error: CSP header should be set
 expect(received).toBeTruthy()
 Received: undefined</t>
         </is>
       </c>
-      <c r="J39" s="7" t="inlineStr"/>
-      <c r="K39" s="7" t="inlineStr"/>
-      <c r="L39" s="7" t="inlineStr">
+      <c r="J40" s="7" t="inlineStr"/>
+      <c r="K40" s="7" t="inlineStr"/>
+      <c r="L40" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M39" s="7" t="inlineStr"/>
-      <c r="N39" s="7" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>BUG-038</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="M40" s="7" t="inlineStr"/>
+      <c r="N40" s="7" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>BUG-039</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>PR-TC-UI-LEAK-001</t>
         </is>
       </c>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D40" s="7" t="inlineStr">
+      <c r="D41" s="7" t="inlineStr">
         <is>
           <t>PR-TC-UI-LEAK-001 · EP profile shows no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E40" s="7" t="inlineStr">
+      <c r="E41" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F40" s="7" t="inlineStr"/>
-      <c r="G40" s="7" t="inlineStr"/>
-      <c r="H40" s="7" t="inlineStr"/>
-      <c r="I40" s="7" t="inlineStr">
+      <c r="F41" s="7" t="inlineStr"/>
+      <c r="G41" s="7" t="inlineStr"/>
+      <c r="H41" s="7" t="inlineStr"/>
+      <c r="I41" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on EP profile: {"doctype-df-prefix":["DF PROGRESS"]}
 expect.toEqual // deep equality
@@ -25278,50 +25334,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J40" s="7" t="inlineStr">
+      <c r="J41" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\08-ui-no-backend-leak-PR-T-d694f-e-shows-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K40" s="7" t="inlineStr"/>
-      <c r="L40" s="7" t="inlineStr">
+      <c r="K41" s="7" t="inlineStr"/>
+      <c r="L41" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M40" s="7" t="inlineStr"/>
-      <c r="N40" s="7" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>BUG-039</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
+      <c r="M41" s="7" t="inlineStr"/>
+      <c r="N41" s="7" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>BUG-040</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>PR-TC-UI-LEAK-002</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="C42" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D41" s="7" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
         <is>
           <t>PR-TC-UI-LEAK-002 · new EP form header is a friendly label, not the raw doctype</t>
         </is>
       </c>
-      <c r="E41" s="7" t="inlineStr">
+      <c r="E42" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F41" s="7" t="inlineStr"/>
-      <c r="G41" s="7" t="inlineStr"/>
-      <c r="H41" s="7" t="inlineStr"/>
-      <c r="I41" s="7" t="inlineStr">
+      <c r="F42" s="7" t="inlineStr"/>
+      <c r="G42" s="7" t="inlineStr"/>
+      <c r="H42" s="7" t="inlineStr"/>
+      <c r="I42" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on new EP form: {"enterprenur-internal":["Enterprenur"]}
 expect.toEqual // deep equality
@@ -25335,52 +25391,52 @@
 + }</t>
         </is>
       </c>
-      <c r="J41" s="7" t="inlineStr">
+      <c r="J42" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\08-ui-no-backend-leak-PR-T-215c4-y-label-not-the-raw-doctype-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K41" s="7" t="inlineStr"/>
-      <c r="L41" s="7" t="inlineStr">
+      <c r="K42" s="7" t="inlineStr"/>
+      <c r="L42" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M41" s="7" t="inlineStr"/>
-      <c r="N41" s="7" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>BUG-040</t>
-        </is>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="M42" s="7" t="inlineStr"/>
+      <c r="N42" s="7" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>BUG-041</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>PR-TC-UM-001</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C43" s="7" t="inlineStr">
         <is>
           <t>13. User Management</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D43" s="7" t="inlineStr">
         <is>
           <t>Create a new Field Associate user with all required fields</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="E43" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F42" s="7" t="inlineStr">
+      <c r="F43" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G42" s="7" t="inlineStr">
+      <c r="G43" s="7" t="inlineStr">
         <is>
           <t>• Navigate to User Management workspace → "+ New User".
 • Fill: Email = uat-fa-test01@dhwaniris.com, First Name = UAT, Last Name = FA-Test01, Phone = +91 9876543210.
@@ -25390,74 +25446,22 @@
 • Click Save.</t>
         </is>
       </c>
-      <c r="H42" s="7" t="inlineStr">
+      <c r="H43" s="7" t="inlineStr">
         <is>
           <t>Toast: "User created successfully." User row appears in list with status "Active" and "Welcome email sent". Email arrives at the address within 2 min containing a one-time password-set link. Audit log records the creation with timestamp + creator.</t>
         </is>
       </c>
-      <c r="I42" s="7" t="inlineStr">
+      <c r="I43" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: INSERT User → 417: {"exception":"frappe.exceptions.ValidationError: Error syncing User to User Manager: ('User Manager', 'uat-umc-79v3ss@dhwaniris.com', IntegrityError(1062, \"Duplicate entry '[uat]_crud_user' for key 'username'\"))","exc_type":"ValidationError","_exc_source":"dhwani_frappe_base (app)","exc":"[\"Traceback (most recent call last):\\n  File \\\"apps/frappe/frappe/model/base_document.py\\\", line 755, in db_insert\\n    name = frappe.db.sql(\\n    \\t\\\"\\\"\\\"INSERT INTO </t>
         </is>
       </c>
-      <c r="J42" s="7" t="inlineStr"/>
-      <c r="K42" s="7" t="inlineStr">
+      <c r="J43" s="7" t="inlineStr"/>
+      <c r="K43" s="7" t="inlineStr">
         <is>
           <t>BRD: PR-UJ-CTI §User Management.</t>
         </is>
       </c>
-      <c r="L42" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="M42" s="7" t="inlineStr"/>
-      <c r="N42" s="7" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="7" t="inlineStr">
-        <is>
-          <t>BUG-041</t>
-        </is>
-      </c>
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>PR-TC-UM-009</t>
-        </is>
-      </c>
-      <c r="C43" s="7" t="inlineStr">
-        <is>
-          <t>13. User Management</t>
-        </is>
-      </c>
-      <c r="D43" s="7" t="inlineStr">
-        <is>
-          <t>Email must be lowercase and trimmed before save</t>
-        </is>
-      </c>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F43" s="7" t="inlineStr">
-        <is>
-          <t>P1 — High</t>
-        </is>
-      </c>
-      <c r="G43" s="7" t="inlineStr">
-        <is>
-          <t>• Enter email Test@Dhwaniris.COM (leading/trailing spaces, mixed case).</t>
-        </is>
-      </c>
-      <c r="H43" s="7" t="inlineStr"/>
-      <c r="I43" s="7" t="inlineStr">
-        <is>
-          <t>Error: INSERT User → 417: {"exception":"frappe.exceptions.ValidationError: Error syncing User to User Manager: ('User Manager', 'uat-umn-ztbfos@dhwaniris.com', IntegrityError(1062, \"Duplicate entry '[uat]_norm' for key 'username'\"))","exc_type":"ValidationError","_exc_source":"dhwani_frappe_base (app)","exc":"[\"Traceback (most recent call last):\\n  File \\\"apps/frappe/frappe/model/base_document.py\\\", line 755, in db_insert\\n    name = frappe.db.sql(\\n    \\t\\\"\\\"\\\"INSERT INTO `tab{</t>
-        </is>
-      </c>
-      <c r="J43" s="7" t="inlineStr"/>
-      <c r="K43" s="7" t="inlineStr"/>
       <c r="L43" s="7" t="inlineStr">
         <is>
           <t>Open</t>
@@ -25474,30 +25478,82 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
+          <t>PR-TC-UM-009</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>13. User Management</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>Email must be lowercase and trimmed before save</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>P1 — High</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>• Enter email Test@Dhwaniris.COM (leading/trailing spaces, mixed case).</t>
+        </is>
+      </c>
+      <c r="H44" s="7" t="inlineStr"/>
+      <c r="I44" s="7" t="inlineStr">
+        <is>
+          <t>Error: INSERT User → 417: {"exception":"frappe.exceptions.ValidationError: Error syncing User to User Manager: ('User Manager', 'uat-umn-ztbfos@dhwaniris.com', IntegrityError(1062, \"Duplicate entry '[uat]_norm' for key 'username'\"))","exc_type":"ValidationError","_exc_source":"dhwani_frappe_base (app)","exc":"[\"Traceback (most recent call last):\\n  File \\\"apps/frappe/frappe/model/base_document.py\\\", line 755, in db_insert\\n    name = frappe.db.sql(\\n    \\t\\\"\\\"\\\"INSERT INTO `tab{</t>
+        </is>
+      </c>
+      <c r="J44" s="7" t="inlineStr"/>
+      <c r="K44" s="7" t="inlineStr"/>
+      <c r="L44" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M44" s="7" t="inlineStr"/>
+      <c r="N44" s="7" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>BUG-043</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
           <t>PR-TC-UM-010</t>
         </is>
       </c>
-      <c r="C44" s="7" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>13. User Management</t>
         </is>
       </c>
-      <c r="D44" s="7" t="inlineStr">
+      <c r="D45" s="7" t="inlineStr">
         <is>
           <t>Edit user phone, name, block — changes persist</t>
         </is>
       </c>
-      <c r="E44" s="7" t="inlineStr">
+      <c r="E45" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F44" s="7" t="inlineStr">
+      <c r="F45" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G44" s="7" t="inlineStr">
+      <c r="G45" s="7" t="inlineStr">
         <is>
           <t>• Open user uat-fa-test01.
 • Change First Name to "UAT-Updated".
@@ -25506,63 +25562,10 @@
 • Log out / log in as that user.</t>
         </is>
       </c>
-      <c r="H44" s="7" t="inlineStr"/>
-      <c r="I44" s="7" t="inlineStr">
-        <is>
-          <t>Error: INSERT User → 417: {"exception":"frappe.exceptions.ValidationError: Error syncing User to User Manager: ('User Manager', 'uat-ume-1c8bs5@dhwaniris.com', IntegrityError(1062, \"Duplicate entry '[uat]_before' for key 'username'\"))","exc_type":"ValidationError","_exc_source":"dhwani_frappe_base (app)","exc":"[\"Traceback (most recent call last):\\n  File \\\"apps/frappe/frappe/model/base_document.py\\\", line 755, in db_insert\\n    name = frappe.db.sql(\\n    \\t\\\"\\\"\\\"INSERT INTO `ta</t>
-        </is>
-      </c>
-      <c r="J44" s="7" t="inlineStr"/>
-      <c r="K44" s="7" t="inlineStr"/>
-      <c r="L44" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="M44" s="7" t="inlineStr"/>
-      <c r="N44" s="7" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="7" t="inlineStr">
-        <is>
-          <t>BUG-043</t>
-        </is>
-      </c>
-      <c r="B45" s="7" t="inlineStr">
-        <is>
-          <t>PR-TC-UM-011</t>
-        </is>
-      </c>
-      <c r="C45" s="7" t="inlineStr">
-        <is>
-          <t>13. User Management</t>
-        </is>
-      </c>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>Deactivate a user — they cannot log in until reactivated</t>
-        </is>
-      </c>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="F45" s="7" t="inlineStr">
-        <is>
-          <t>P0 — Blocker</t>
-        </is>
-      </c>
-      <c r="G45" s="7" t="inlineStr">
-        <is>
-          <t>• Open uat-fa-test01. Set Enabled = No. Save.
-• Sign out, attempt to log in as uat-fa-test01.</t>
-        </is>
-      </c>
       <c r="H45" s="7" t="inlineStr"/>
       <c r="I45" s="7" t="inlineStr">
         <is>
-          <t>Error: INSERT User → 417: {"exception":"frappe.exceptions.ValidationError: Error syncing User to User Manager: ('User Manager', 'uat-umd-0pc24h@dhwaniris.com', IntegrityError(1062, \"Duplicate entry '[uat]_disabled' for key 'username'\"))","exc_type":"ValidationError","_exc_source":"dhwani_frappe_base (app)","exc":"[\"Traceback (most recent call last):\\n  File \\\"apps/frappe/frappe/model/base_document.py\\\", line 755, in db_insert\\n    name = frappe.db.sql(\\n    \\t\\\"\\\"\\\"INSERT INTO `</t>
+          <t>Error: INSERT User → 417: {"exception":"frappe.exceptions.ValidationError: Error syncing User to User Manager: ('User Manager', 'uat-ume-1c8bs5@dhwaniris.com', IntegrityError(1062, \"Duplicate entry '[uat]_before' for key 'username'\"))","exc_type":"ValidationError","_exc_source":"dhwani_frappe_base (app)","exc":"[\"Traceback (most recent call last):\\n  File \\\"apps/frappe/frappe/model/base_document.py\\\", line 755, in db_insert\\n    name = frappe.db.sql(\\n    \\t\\\"\\\"\\\"INSERT INTO `ta</t>
         </is>
       </c>
       <c r="J45" s="7" t="inlineStr"/>
@@ -25583,104 +25586,157 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
+          <t>PR-TC-UM-011</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>13. User Management</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>Deactivate a user — they cannot log in until reactivated</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>P0 — Blocker</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>• Open uat-fa-test01. Set Enabled = No. Save.
+• Sign out, attempt to log in as uat-fa-test01.</t>
+        </is>
+      </c>
+      <c r="H46" s="7" t="inlineStr"/>
+      <c r="I46" s="7" t="inlineStr">
+        <is>
+          <t>Error: INSERT User → 417: {"exception":"frappe.exceptions.ValidationError: Error syncing User to User Manager: ('User Manager', 'uat-umd-0pc24h@dhwaniris.com', IntegrityError(1062, \"Duplicate entry '[uat]_disabled' for key 'username'\"))","exc_type":"ValidationError","_exc_source":"dhwani_frappe_base (app)","exc":"[\"Traceback (most recent call last):\\n  File \\\"apps/frappe/frappe/model/base_document.py\\\", line 755, in db_insert\\n    name = frappe.db.sql(\\n    \\t\\\"\\\"\\\"INSERT INTO `</t>
+        </is>
+      </c>
+      <c r="J46" s="7" t="inlineStr"/>
+      <c r="K46" s="7" t="inlineStr"/>
+      <c r="L46" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M46" s="7" t="inlineStr"/>
+      <c r="N46" s="7" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>BUG-045</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
           <t>PR-TC-XC-003</t>
         </is>
       </c>
-      <c r="C46" s="7" t="inlineStr">
+      <c r="C47" s="7" t="inlineStr">
         <is>
           <t>4. Application Entry &amp; Routing</t>
         </is>
       </c>
-      <c r="D46" s="7" t="inlineStr">
+      <c r="D47" s="7" t="inlineStr">
         <is>
           <t>Deep link to a protected page while logged out preserves the intent</t>
         </is>
       </c>
-      <c r="E46" s="7" t="inlineStr">
+      <c r="E47" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F46" s="7" t="inlineStr">
+      <c r="F47" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G46" s="7" t="inlineStr">
+      <c r="G47" s="7" t="inlineStr">
         <is>
           <t>• Open https://stgprime-rural.dhwaniris.in/app/enterprenur-profile/EP-001 directly.
 • Login redirect fires.
 • Complete login as a user permitted to see that record.</t>
         </is>
       </c>
-      <c r="H46" s="7" t="inlineStr">
+      <c r="H47" s="7" t="inlineStr">
         <is>
           <t>After successful login, user is redirected to the originally requested URL (the EP detail page), not the default landing page. URL parameter (typically redirect-to or next) is preserved through the auth flow.</t>
         </is>
       </c>
-      <c r="I46" s="7" t="inlineStr">
+      <c r="I47" s="7" t="inlineStr">
         <is>
           <t>Error: expect(received).toMatch(expected)
 Expected pattern: /redirect|next|to=/i
 Received string:  "https://stgprime-rural.dhwaniris.in/primerural/login"</t>
         </is>
       </c>
-      <c r="J46" s="7" t="inlineStr">
+      <c r="J47" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\04-entry-PR-TC-XC-ENTRY-·--e9661-t-preserves-redirect-intent-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K46" s="7" t="inlineStr">
+      <c r="K47" s="7" t="inlineStr">
         <is>
           <t>BRD: PR-OV-001 (Auth)</t>
         </is>
       </c>
-      <c r="L46" s="7" t="inlineStr">
+      <c r="L47" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M46" s="7" t="inlineStr"/>
-      <c r="N46" s="7" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="7" t="inlineStr">
-        <is>
-          <t>BUG-045</t>
-        </is>
-      </c>
-      <c r="B47" s="7" t="inlineStr">
+      <c r="M47" s="7" t="inlineStr"/>
+      <c r="N47" s="7" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>BUG-046</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-023</t>
         </is>
       </c>
-      <c r="C47" s="7" t="inlineStr">
+      <c r="C48" s="7" t="inlineStr">
         <is>
           <t>6. Responsive Layout &amp; Screen Sizes</t>
         </is>
       </c>
-      <c r="D47" s="7" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr">
         <is>
           <t>1024×768 (tablet landscape / iPad / Surface): sidebar collapses to icon rail</t>
         </is>
       </c>
-      <c r="E47" s="7" t="inlineStr">
+      <c r="E48" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F47" s="7" t="inlineStr">
+      <c r="F48" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G47" s="7" t="inlineStr">
+      <c r="G48" s="7" t="inlineStr">
         <is>
           <t>• Resize to 1024×768.</t>
         </is>
       </c>
-      <c r="H47" s="7" t="inlineStr"/>
-      <c r="I47" s="7" t="inlineStr">
+      <c r="H48" s="7" t="inlineStr"/>
+      <c r="I48" s="7" t="inlineStr">
         <is>
           <t>Error: at 1024px the sidebar should collapse to an icon rail; width=240
 expect(received).toBeLessThanOrEqual(expected)
@@ -25688,63 +25744,63 @@
 Received:    240</t>
         </is>
       </c>
-      <c r="J47" s="7" t="inlineStr">
+      <c r="J48" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\06-08-10-nonfunctional-PR--f1c18-ollapses-to-icon-rail-64px--sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K47" s="7" t="inlineStr"/>
-      <c r="L47" s="7" t="inlineStr">
+      <c r="K48" s="7" t="inlineStr"/>
+      <c r="L48" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M47" s="7" t="inlineStr"/>
-      <c r="N47" s="7" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="7" t="inlineStr">
-        <is>
-          <t>BUG-046</t>
-        </is>
-      </c>
-      <c r="B48" s="7" t="inlineStr">
+      <c r="M48" s="7" t="inlineStr"/>
+      <c r="N48" s="7" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>BUG-047</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-032</t>
         </is>
       </c>
-      <c r="C48" s="7" t="inlineStr">
+      <c r="C49" s="7" t="inlineStr">
         <is>
           <t>7. Login &amp; Session</t>
         </is>
       </c>
-      <c r="D48" s="7" t="inlineStr">
+      <c r="D49" s="7" t="inlineStr">
         <is>
           <t>Wrong password shows a clear error and does NOT reveal whether the email exists</t>
         </is>
       </c>
-      <c r="E48" s="7" t="inlineStr">
+      <c r="E49" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F48" s="7" t="inlineStr">
+      <c r="F49" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G48" s="7" t="inlineStr">
+      <c r="G49" s="7" t="inlineStr">
         <is>
           <t>• Login form: enter a valid email but wrong password.
 • Submit.</t>
         </is>
       </c>
-      <c r="H48" s="7" t="inlineStr">
+      <c r="H49" s="7" t="inlineStr">
         <is>
           <t>Error displays inline above the form: "Invalid email or password." — generic enough that an attacker cannot enumerate valid emails. The password field is cleared; the email field is preserved. No 500. No password ever echoed back into the field.</t>
         </is>
       </c>
-      <c r="I48" s="7" t="inlineStr">
+      <c r="I49" s="7" t="inlineStr">
         <is>
           <t>Error: login error must be friendly text, not a raw exception class
 expect(locator).not.toContainText(expected) failed
@@ -25758,62 +25814,62 @@
     22 × locator resolved to &lt;div role="alert" class="bg-d</t>
         </is>
       </c>
-      <c r="J48" s="7" t="inlineStr">
+      <c r="J49" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\07-auth-PR-TC-XC-AUTH-·-Em-429a0-neric-error-no-enumeration--sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K48" s="7" t="inlineStr">
+      <c r="K49" s="7" t="inlineStr">
         <is>
           <t>OWASP A07 Auth Failures (do not leak account existence).</t>
         </is>
       </c>
-      <c r="L48" s="7" t="inlineStr">
+      <c r="L49" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M48" s="7" t="inlineStr"/>
-      <c r="N48" s="7" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="7" t="inlineStr">
-        <is>
-          <t>BUG-047</t>
-        </is>
-      </c>
-      <c r="B49" s="7" t="inlineStr">
+      <c r="M49" s="7" t="inlineStr"/>
+      <c r="N49" s="7" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>BUG-048</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-033</t>
         </is>
       </c>
-      <c r="C49" s="7" t="inlineStr">
+      <c r="C50" s="7" t="inlineStr">
         <is>
           <t>7. Login &amp; Session</t>
         </is>
       </c>
-      <c r="D49" s="7" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
         <is>
           <t>Non-existent email shows the same generic error as wrong password</t>
         </is>
       </c>
-      <c r="E49" s="7" t="inlineStr">
+      <c r="E50" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F49" s="7" t="inlineStr">
+      <c r="F50" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G49" s="7" t="inlineStr">
+      <c r="G50" s="7" t="inlineStr">
         <is>
           <t>• Submit with email not-a-real-user@example.com and any password.</t>
         </is>
       </c>
-      <c r="H49" s="7" t="inlineStr"/>
-      <c r="I49" s="7" t="inlineStr">
+      <c r="H50" s="7" t="inlineStr"/>
+      <c r="I50" s="7" t="inlineStr">
         <is>
           <t>Error: login error must be friendly text, not a raw exception class
 expect(locator).not.toContainText(expected) failed
@@ -25827,129 +25883,77 @@
     22 × locator resolved to &lt;div role="alert" class="bg-d</t>
         </is>
       </c>
-      <c r="J49" s="7" t="inlineStr">
+      <c r="J50" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\07-auth-PR-TC-XC-AUTH-·-Em-a7adf-ows-identical-generic-error-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K49" s="7" t="inlineStr"/>
-      <c r="L49" s="7" t="inlineStr">
+      <c r="K50" s="7" t="inlineStr"/>
+      <c r="L50" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M49" s="7" t="inlineStr"/>
-      <c r="N49" s="7" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="7" t="inlineStr">
-        <is>
-          <t>BUG-048</t>
-        </is>
-      </c>
-      <c r="B50" s="7" t="inlineStr">
+      <c r="M50" s="7" t="inlineStr"/>
+      <c r="N50" s="7" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>BUG-049</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-052</t>
         </is>
       </c>
-      <c r="C50" s="7" t="inlineStr">
+      <c r="C51" s="7" t="inlineStr">
         <is>
           <t>8. UI / UX Rules — Monsoon Court Compliance</t>
         </is>
       </c>
-      <c r="D50" s="7" t="inlineStr">
+      <c r="D51" s="7" t="inlineStr">
         <is>
           <t>No green and no yellow appear anywhere in the UI</t>
         </is>
       </c>
-      <c r="E50" s="7" t="inlineStr">
+      <c r="E51" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F50" s="7" t="inlineStr">
+      <c r="F51" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G50" s="7" t="inlineStr">
+      <c r="G51" s="7" t="inlineStr">
         <is>
           <t>• Visually scan every page for green / yellow elements.
 • Search the rendered CSS for any colour matching green, yellow, #2ecc71, #f1c40f, similar hexes.</t>
         </is>
       </c>
-      <c r="H50" s="7" t="inlineStr">
+      <c r="H51" s="7" t="inlineStr">
         <is>
           <t>Zero green elements. Success states use teal #0E4D4E. Zero yellow elements. Warning states use terracotta #C26849.</t>
         </is>
       </c>
-      <c r="I50" s="7" t="inlineStr">
+      <c r="I51" s="7" t="inlineStr">
         <is>
           <t>Active Entrepreneurs KPI shows a GREEN check rgb(63,107,58) (hue 114). Monsoon Court forbids green — success must be teal #0E4D4E.</t>
         </is>
       </c>
-      <c r="J50" s="7" t="inlineStr">
+      <c r="J51" s="7" t="inlineStr">
         <is>
           <t>.playwright-mcp/bug-xc052-green-kpi.png</t>
         </is>
       </c>
-      <c r="K50" s="7" t="inlineStr">
+      <c r="K51" s="7" t="inlineStr">
         <is>
           <t>Monsoon Court §2.7 (brand non-negotiables).</t>
         </is>
       </c>
-      <c r="L50" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="M50" s="7" t="inlineStr"/>
-      <c r="N50" s="7" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="7" t="inlineStr">
-        <is>
-          <t>BUG-049</t>
-        </is>
-      </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>PR-TC-XC-054</t>
-        </is>
-      </c>
-      <c r="C51" s="7" t="inlineStr">
-        <is>
-          <t>8. UI / UX Rules — Monsoon Court Compliance</t>
-        </is>
-      </c>
-      <c r="D51" s="7" t="inlineStr">
-        <is>
-          <t>Required-field marker is a terracotta asterisk, not "(required)" text</t>
-        </is>
-      </c>
-      <c r="E51" s="7" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F51" s="7" t="inlineStr">
-        <is>
-          <t>P1 — High</t>
-        </is>
-      </c>
-      <c r="G51" s="7" t="inlineStr">
-        <is>
-          <t>• Open the EP form. Find a required field (e.g. Entrepreneur Name).</t>
-        </is>
-      </c>
-      <c r="H51" s="7" t="inlineStr"/>
-      <c r="I51" s="7" t="inlineStr">
-        <is>
-          <t>Asterisk on the name label is taupe rgb(107,99,89) (inherits label ink-soft), NOT terracotta #C26849. Marker present but wrong colour.</t>
-        </is>
-      </c>
-      <c r="J51" s="7" t="inlineStr"/>
-      <c r="K51" s="7" t="inlineStr"/>
       <c r="L51" s="7" t="inlineStr">
         <is>
           <t>Open</t>
@@ -25966,17 +25970,17 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-XC-063</t>
+          <t>PR-TC-XC-054</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>9. Accessibility — WCAG 2.2 AA</t>
+          <t>8. UI / UX Rules — Monsoon Court Compliance</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>Form fields have associated labels (axe-core "label" rule passes)</t>
+          <t>Required-field marker is a terracotta asterisk, not "(required)" text</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
@@ -25991,11 +25995,63 @@
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>• Run axe-core on the EP form (via Playwright).</t>
+          <t>• Open the EP form. Find a required field (e.g. Entrepreneur Name).</t>
         </is>
       </c>
       <c r="H52" s="7" t="inlineStr"/>
       <c r="I52" s="7" t="inlineStr">
+        <is>
+          <t>Asterisk on the name label is taupe rgb(107,99,89) (inherits label ink-soft), NOT terracotta #C26849. Marker present but wrong colour.</t>
+        </is>
+      </c>
+      <c r="J52" s="7" t="inlineStr"/>
+      <c r="K52" s="7" t="inlineStr"/>
+      <c r="L52" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M52" s="7" t="inlineStr"/>
+      <c r="N52" s="7" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>BUG-051</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-XC-063</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>9. Accessibility — WCAG 2.2 AA</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>Form fields have associated labels (axe-core "label" rule passes)</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>P1 — High</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>• Run axe-core on the EP form (via Playwright).</t>
+        </is>
+      </c>
+      <c r="H53" s="7" t="inlineStr"/>
+      <c r="I53" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: label violations: [{"id":"label","n":6}]
 expect(received).toEqual(expected) // deep equality
@@ -26015,58 +26071,58 @@
 +        </t>
         </is>
       </c>
-      <c r="J52" s="7" t="inlineStr">
+      <c r="J53" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\09-a11y-PR-TC-XC-063-·-for-17d03-ssociated-labels-axe-label--sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K52" s="7" t="inlineStr"/>
-      <c r="L52" s="7" t="inlineStr">
+      <c r="K53" s="7" t="inlineStr"/>
+      <c r="L53" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M52" s="7" t="inlineStr"/>
-      <c r="N52" s="7" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="7" t="inlineStr">
-        <is>
-          <t>BUG-051</t>
-        </is>
-      </c>
-      <c r="B53" s="7" t="inlineStr">
+      <c r="M53" s="7" t="inlineStr"/>
+      <c r="N53" s="7" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>BUG-052</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-064</t>
         </is>
       </c>
-      <c r="C53" s="7" t="inlineStr">
+      <c r="C54" s="7" t="inlineStr">
         <is>
           <t>9. Accessibility — WCAG 2.2 AA</t>
         </is>
       </c>
-      <c r="D53" s="7" t="inlineStr">
+      <c r="D54" s="7" t="inlineStr">
         <is>
           <t>Colour contrast meets WCAG AA</t>
         </is>
       </c>
-      <c r="E53" s="7" t="inlineStr">
+      <c r="E54" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F53" s="7" t="inlineStr">
+      <c r="F54" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G53" s="7" t="inlineStr">
+      <c r="G54" s="7" t="inlineStr">
         <is>
           <t>• Run axe-core's contrast check on EP detail, dashboard, framework form.</t>
         </is>
       </c>
-      <c r="H53" s="7" t="inlineStr"/>
-      <c r="I53" s="7" t="inlineStr">
+      <c r="H54" s="7" t="inlineStr"/>
+      <c r="I54" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: contrast violations: [10]
 expect(received).toEqual(expected) // deep equality
@@ -26082,50 +26138,50 @@
 </t>
         </is>
       </c>
-      <c r="J53" s="7" t="inlineStr">
+      <c r="J54" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\09-a11y-PR-TC-XC-064-·-col-8baa1-WCAG-AA-axe-color-contrast--sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K53" s="7" t="inlineStr"/>
-      <c r="L53" s="7" t="inlineStr">
+      <c r="K54" s="7" t="inlineStr"/>
+      <c r="L54" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M53" s="7" t="inlineStr"/>
-      <c r="N53" s="7" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="7" t="inlineStr">
-        <is>
-          <t>BUG-052</t>
-        </is>
-      </c>
-      <c r="B54" s="7" t="inlineStr">
+      <c r="M54" s="7" t="inlineStr"/>
+      <c r="N54" s="7" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>BUG-053</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-064b</t>
         </is>
       </c>
-      <c r="C54" s="7" t="inlineStr">
+      <c r="C55" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D54" s="7" t="inlineStr">
+      <c r="D55" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-064b · landscape colour contrast (WCAG AA)</t>
         </is>
       </c>
-      <c r="E54" s="7" t="inlineStr">
+      <c r="E55" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F54" s="7" t="inlineStr"/>
-      <c r="G54" s="7" t="inlineStr"/>
-      <c r="H54" s="7" t="inlineStr"/>
-      <c r="I54" s="7" t="inlineStr">
+      <c r="F55" s="7" t="inlineStr"/>
+      <c r="G55" s="7" t="inlineStr"/>
+      <c r="H55" s="7" t="inlineStr"/>
+      <c r="I55" s="7" t="inlineStr">
         <is>
           <t>Error: landscape contrast nodes: 4
 expect(received).toEqual(expected) // deep equality
@@ -26140,19 +26196,19 @@
 +     "id": "color-contrast"</t>
         </is>
       </c>
-      <c r="J54" s="7" t="inlineStr">
+      <c r="J55" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\09-a11y-PR-TC-XC-064b-·-landscape-colour-contrast-WCAG-AA--sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K54" s="7" t="inlineStr"/>
-      <c r="L54" s="7" t="inlineStr">
+      <c r="K55" s="7" t="inlineStr"/>
+      <c r="L55" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M54" s="7" t="inlineStr"/>
-      <c r="N54" s="7" t="inlineStr"/>
+      <c r="M55" s="7" t="inlineStr"/>
+      <c r="N55" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -16919,9 +16919,9 @@
       </c>
       <c r="L229" s="7" t="inlineStr"/>
       <c r="M229" s="7" t="inlineStr"/>
-      <c r="N229" s="13" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+      <c r="N229" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O229" s="7" t="inlineStr">
@@ -18015,9 +18015,9 @@
       </c>
       <c r="L245" s="7" t="inlineStr"/>
       <c r="M245" s="7" t="inlineStr"/>
-      <c r="N245" s="13" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+      <c r="N245" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O245" s="7" t="inlineStr">

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -16437,9 +16437,9 @@
       </c>
       <c r="L222" s="7" t="inlineStr"/>
       <c r="M222" s="7" t="inlineStr"/>
-      <c r="N222" s="13" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+      <c r="N222" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O222" s="7" t="inlineStr">
@@ -17881,17 +17881,21 @@
       </c>
       <c r="L243" s="7" t="inlineStr"/>
       <c r="M243" s="7" t="inlineStr"/>
-      <c r="N243" s="13" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+      <c r="N243" s="12" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
       <c r="O243" s="7" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="P243" s="8" t="inlineStr"/>
+          <t>QC EXISTING uses an "+ Add Item" checklist with a 4-LEVEL rating (0/33/66/100) and AVERAGE SCORE (%), NOT the BRD spec of 23 fixed stars totalling /115 (e.g. 92/115=80%). Items are manually added (not pre-loaded). Confirm whether 23 standard items should pre-load + whether the scoring model should match spec.</t>
+        </is>
+      </c>
+      <c r="P243" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="Q243" s="7" t="inlineStr"/>
     </row>
     <row r="244">
@@ -23048,7 +23052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N55"/>
+  <dimension ref="A1:N56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -23982,17 +23986,17 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-FWC-BPC-002</t>
+          <t>PR-TC-FW-QC-001</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>(not in master — add as test case)</t>
+          <t>17. The 27 Diagnostic Frameworks</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-FWC-BPC-002 · Business Plan Canvas header has no raw doctype / UUID</t>
+          <t>Fill all 23 stars; total score auto-computes</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
@@ -24000,10 +24004,62 @@
           <t>High</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr"/>
-      <c r="G18" s="7" t="inlineStr"/>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>P1 — High</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>• Set all 23 questions to 4 stars (out of 5).</t>
+        </is>
+      </c>
       <c r="H18" s="7" t="inlineStr"/>
       <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>QC EXISTING uses an "+ Add Item" checklist with a 4-LEVEL rating (0/33/66/100) and AVERAGE SCORE (%), NOT the BRD spec of 23 fixed stars totalling /115 (e.g. 92/115=80%). Items are manually added (not pre-loaded). Confirm whether 23 standard items should pre-load + whether the scoring model should match spec.</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr"/>
+      <c r="K18" s="7" t="inlineStr"/>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M18" s="7" t="inlineStr"/>
+      <c r="N18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>BUG-017</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-FWC-BPC-002</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>(not in master — add as test case)</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-FWC-BPC-002 · Business Plan Canvas header has no raw doctype / UUID</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr"/>
+      <c r="G19" s="7" t="inlineStr"/>
+      <c r="H19" s="7" t="inlineStr"/>
+      <c r="I19" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Business Plan Canvas: {"doctype-df-prefix":["DF BUSINESS"]}
 expect.toEqual // deep equality
@@ -24017,50 +24073,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J18" s="7" t="inlineStr">
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Bu-a8fd3-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K18" s="7" t="inlineStr"/>
-      <c r="L18" s="7" t="inlineStr">
+      <c r="K19" s="7" t="inlineStr"/>
+      <c r="L19" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M18" s="7" t="inlineStr"/>
-      <c r="N18" s="7" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>BUG-017</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="M19" s="7" t="inlineStr"/>
+      <c r="N19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>BUG-018</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-BREG-002</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-BREG-002 · Business Registration header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr"/>
-      <c r="G19" s="7" t="inlineStr"/>
-      <c r="H19" s="7" t="inlineStr"/>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="F20" s="7" t="inlineStr"/>
+      <c r="G20" s="7" t="inlineStr"/>
+      <c r="H20" s="7" t="inlineStr"/>
+      <c r="I20" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Business Registration: {"doctype-df-prefix":["DF BUSINESS"]}
 expect.toEqual // deep equality
@@ -24074,50 +24130,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J19" s="7" t="inlineStr">
+      <c r="J20" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Bu-6c730-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K19" s="7" t="inlineStr"/>
-      <c r="L19" s="7" t="inlineStr">
+      <c r="K20" s="7" t="inlineStr"/>
+      <c r="L20" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M19" s="7" t="inlineStr"/>
-      <c r="N19" s="7" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>BUG-018</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="M20" s="7" t="inlineStr"/>
+      <c r="N20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>BUG-019</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-CA-002</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-CA-002 · Customer Analysis header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr"/>
-      <c r="G20" s="7" t="inlineStr"/>
-      <c r="H20" s="7" t="inlineStr"/>
-      <c r="I20" s="7" t="inlineStr">
+      <c r="F21" s="7" t="inlineStr"/>
+      <c r="G21" s="7" t="inlineStr"/>
+      <c r="H21" s="7" t="inlineStr"/>
+      <c r="I21" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Customer Analysis: {"doctype-df-prefix":["DF CUSTOMER"]}
 expect.toEqual // deep equality
@@ -24131,50 +24187,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J20" s="7" t="inlineStr">
+      <c r="J21" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Cu-6ed58-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K20" s="7" t="inlineStr"/>
-      <c r="L20" s="7" t="inlineStr">
+      <c r="K21" s="7" t="inlineStr"/>
+      <c r="L21" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M20" s="7" t="inlineStr"/>
-      <c r="N20" s="7" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>BUG-019</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="M21" s="7" t="inlineStr"/>
+      <c r="N21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>BUG-020</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-CB-002</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-CB-002 · Capacity Building header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr"/>
-      <c r="G21" s="7" t="inlineStr"/>
-      <c r="H21" s="7" t="inlineStr"/>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="F22" s="7" t="inlineStr"/>
+      <c r="G22" s="7" t="inlineStr"/>
+      <c r="H22" s="7" t="inlineStr"/>
+      <c r="I22" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Capacity Building: {"doctype-df-prefix":["DF CAPACITY"]}
 expect.toEqual // deep equality
@@ -24188,50 +24244,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J21" s="7" t="inlineStr">
+      <c r="J22" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Ca-83199-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K21" s="7" t="inlineStr"/>
-      <c r="L21" s="7" t="inlineStr">
+      <c r="K22" s="7" t="inlineStr"/>
+      <c r="L22" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M21" s="7" t="inlineStr"/>
-      <c r="N21" s="7" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>BUG-020</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="M22" s="7" t="inlineStr"/>
+      <c r="N22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>BUG-021</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-DL-002</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-DL-002 · Digital Literacy header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr"/>
-      <c r="G22" s="7" t="inlineStr"/>
-      <c r="H22" s="7" t="inlineStr"/>
-      <c r="I22" s="7" t="inlineStr">
+      <c r="F23" s="7" t="inlineStr"/>
+      <c r="G23" s="7" t="inlineStr"/>
+      <c r="H23" s="7" t="inlineStr"/>
+      <c r="I23" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Digital Literacy: {"doctype-df-prefix":["DF DIGITAL"]}
 expect.toEqual // deep equality
@@ -24245,50 +24301,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J22" s="7" t="inlineStr">
+      <c r="J23" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Di-845ef-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K22" s="7" t="inlineStr"/>
-      <c r="L22" s="7" t="inlineStr">
+      <c r="K23" s="7" t="inlineStr"/>
+      <c r="L23" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M22" s="7" t="inlineStr"/>
-      <c r="N22" s="7" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>BUG-021</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="M23" s="7" t="inlineStr"/>
+      <c r="N23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>BUG-022</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-INFR-002</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-INFR-002 · Infrastructure (BE/EE/CE) header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F23" s="7" t="inlineStr"/>
-      <c r="G23" s="7" t="inlineStr"/>
-      <c r="H23" s="7" t="inlineStr"/>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="F24" s="7" t="inlineStr"/>
+      <c r="G24" s="7" t="inlineStr"/>
+      <c r="H24" s="7" t="inlineStr"/>
+      <c r="I24" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Infrastructure: {"doctype-df-prefix":["DF INFRASTRUCTURE"]}
 expect.toEqual // deep equality
@@ -24302,50 +24358,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J23" s="7" t="inlineStr">
+      <c r="J24" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-In-3328d-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K23" s="7" t="inlineStr"/>
-      <c r="L23" s="7" t="inlineStr">
+      <c r="K24" s="7" t="inlineStr"/>
+      <c r="L24" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M23" s="7" t="inlineStr"/>
-      <c r="N23" s="7" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>BUG-022</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="M24" s="7" t="inlineStr"/>
+      <c r="N24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>BUG-023</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-LABL-002</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-LABL-002 · Marketing Label header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr"/>
-      <c r="G24" s="7" t="inlineStr"/>
-      <c r="H24" s="7" t="inlineStr"/>
-      <c r="I24" s="7" t="inlineStr">
+      <c r="F25" s="7" t="inlineStr"/>
+      <c r="G25" s="7" t="inlineStr"/>
+      <c r="H25" s="7" t="inlineStr"/>
+      <c r="I25" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Marketing Label: {"doctype-df-prefix":["DF MARKETING"]}
 expect.toEqual // deep equality
@@ -24359,50 +24415,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J24" s="7" t="inlineStr">
+      <c r="J25" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Ma-11834-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K24" s="7" t="inlineStr"/>
-      <c r="L24" s="7" t="inlineStr">
+      <c r="K25" s="7" t="inlineStr"/>
+      <c r="L25" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M24" s="7" t="inlineStr"/>
-      <c r="N24" s="7" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>BUG-023</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="M25" s="7" t="inlineStr"/>
+      <c r="N25" s="7" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>BUG-024</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-ML-002</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-ML-002 · Market Linkage header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="E26" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F25" s="7" t="inlineStr"/>
-      <c r="G25" s="7" t="inlineStr"/>
-      <c r="H25" s="7" t="inlineStr"/>
-      <c r="I25" s="7" t="inlineStr">
+      <c r="F26" s="7" t="inlineStr"/>
+      <c r="G26" s="7" t="inlineStr"/>
+      <c r="H26" s="7" t="inlineStr"/>
+      <c r="I26" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Market Linkage: {"doctype-df-prefix":["DF MARKET"]}
 expect.toEqual // deep equality
@@ -24416,50 +24472,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J25" s="7" t="inlineStr">
+      <c r="J26" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Ma-22f69-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K25" s="7" t="inlineStr"/>
-      <c r="L25" s="7" t="inlineStr">
+      <c r="K26" s="7" t="inlineStr"/>
+      <c r="L26" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M25" s="7" t="inlineStr"/>
-      <c r="N25" s="7" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>BUG-024</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="M26" s="7" t="inlineStr"/>
+      <c r="N26" s="7" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>BUG-025</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-MR-002</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-MR-002 · Market Research header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F26" s="7" t="inlineStr"/>
-      <c r="G26" s="7" t="inlineStr"/>
-      <c r="H26" s="7" t="inlineStr"/>
-      <c r="I26" s="7" t="inlineStr">
+      <c r="F27" s="7" t="inlineStr"/>
+      <c r="G27" s="7" t="inlineStr"/>
+      <c r="H27" s="7" t="inlineStr"/>
+      <c r="I27" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Market Research: {"doctype-df-prefix":["DF MARKET"]}
 expect.toEqual // deep equality
@@ -24473,50 +24529,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J26" s="7" t="inlineStr">
+      <c r="J27" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Ma-6eb23-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K26" s="7" t="inlineStr"/>
-      <c r="L26" s="7" t="inlineStr">
+      <c r="K27" s="7" t="inlineStr"/>
+      <c r="L27" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M26" s="7" t="inlineStr"/>
-      <c r="N26" s="7" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>BUG-025</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="M27" s="7" t="inlineStr"/>
+      <c r="N27" s="7" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>BUG-026</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PCMP-002</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PCMP-002 · Product Compliance header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr"/>
-      <c r="G27" s="7" t="inlineStr"/>
-      <c r="H27" s="7" t="inlineStr"/>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="F28" s="7" t="inlineStr"/>
+      <c r="G28" s="7" t="inlineStr"/>
+      <c r="H28" s="7" t="inlineStr"/>
+      <c r="I28" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Product Compliance: {"doctype-df-prefix":["DF PRODUCT"]}
 expect.toEqual // deep equality
@@ -24530,50 +24586,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J27" s="7" t="inlineStr">
+      <c r="J28" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Pr-be46f-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K27" s="7" t="inlineStr"/>
-      <c r="L27" s="7" t="inlineStr">
+      <c r="K28" s="7" t="inlineStr"/>
+      <c r="L28" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M27" s="7" t="inlineStr"/>
-      <c r="N27" s="7" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>BUG-026</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="M28" s="7" t="inlineStr"/>
+      <c r="N28" s="7" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>BUG-027</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PROM-002</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PROM-002 · Promotional Marketing header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr"/>
-      <c r="G28" s="7" t="inlineStr"/>
-      <c r="H28" s="7" t="inlineStr"/>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="F29" s="7" t="inlineStr"/>
+      <c r="G29" s="7" t="inlineStr"/>
+      <c r="H29" s="7" t="inlineStr"/>
+      <c r="I29" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Promotional Marketing: {"doctype-df-prefix":["DF PROMOTIONAL"]}
 expect.toEqual // deep equality
@@ -24587,50 +24643,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J28" s="7" t="inlineStr">
+      <c r="J29" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Pr-d8d12-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K28" s="7" t="inlineStr"/>
-      <c r="L28" s="7" t="inlineStr">
+      <c r="K29" s="7" t="inlineStr"/>
+      <c r="L29" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M28" s="7" t="inlineStr"/>
-      <c r="N28" s="7" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>BUG-027</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="M29" s="7" t="inlineStr"/>
+      <c r="N29" s="7" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>BUG-028</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PROT-002</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PROT-002 · Product Prototyping header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="E30" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr"/>
-      <c r="G29" s="7" t="inlineStr"/>
-      <c r="H29" s="7" t="inlineStr"/>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="F30" s="7" t="inlineStr"/>
+      <c r="G30" s="7" t="inlineStr"/>
+      <c r="H30" s="7" t="inlineStr"/>
+      <c r="I30" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Product Prototyping: {"doctype-df-prefix":["DF PRODUCT"]}
 expect.toEqual // deep equality
@@ -24644,50 +24700,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J29" s="7" t="inlineStr">
+      <c r="J30" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Pr-1120e-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K29" s="7" t="inlineStr"/>
-      <c r="L29" s="7" t="inlineStr">
+      <c r="K30" s="7" t="inlineStr"/>
+      <c r="L30" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M29" s="7" t="inlineStr"/>
-      <c r="N29" s="7" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>BUG-028</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="M30" s="7" t="inlineStr"/>
+      <c r="N30" s="7" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>BUG-029</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PTCH-002</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PTCH-002 · Pitch Deck header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="E31" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr"/>
-      <c r="G30" s="7" t="inlineStr"/>
-      <c r="H30" s="7" t="inlineStr"/>
-      <c r="I30" s="7" t="inlineStr">
+      <c r="F31" s="7" t="inlineStr"/>
+      <c r="G31" s="7" t="inlineStr"/>
+      <c r="H31" s="7" t="inlineStr"/>
+      <c r="I31" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Pitch Deck: {"doctype-df-prefix":["DF PITCH"]}
 expect.toEqual // deep equality
@@ -24701,50 +24757,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J30" s="7" t="inlineStr">
+      <c r="J31" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Pi-fefd5-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K30" s="7" t="inlineStr"/>
-      <c r="L30" s="7" t="inlineStr">
+      <c r="K31" s="7" t="inlineStr"/>
+      <c r="L31" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M30" s="7" t="inlineStr"/>
-      <c r="N30" s="7" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>BUG-029</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="M31" s="7" t="inlineStr"/>
+      <c r="N31" s="7" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>BUG-030</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PTST-002</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PTST-002 · Product Testing header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="E32" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr"/>
-      <c r="G31" s="7" t="inlineStr"/>
-      <c r="H31" s="7" t="inlineStr"/>
-      <c r="I31" s="7" t="inlineStr">
+      <c r="F32" s="7" t="inlineStr"/>
+      <c r="G32" s="7" t="inlineStr"/>
+      <c r="H32" s="7" t="inlineStr"/>
+      <c r="I32" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Product Testing: {"doctype-df-prefix":["DF PRODUCT"]}
 expect.toEqual // deep equality
@@ -24758,50 +24814,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J31" s="7" t="inlineStr">
+      <c r="J32" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Pr-3e912-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K31" s="7" t="inlineStr"/>
-      <c r="L31" s="7" t="inlineStr">
+      <c r="K32" s="7" t="inlineStr"/>
+      <c r="L32" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M31" s="7" t="inlineStr"/>
-      <c r="N31" s="7" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>BUG-030</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="M32" s="7" t="inlineStr"/>
+      <c r="N32" s="7" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>BUG-031</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-QC-002</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D33" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-QC-002 · Quality Control header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
+      <c r="E33" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F32" s="7" t="inlineStr"/>
-      <c r="G32" s="7" t="inlineStr"/>
-      <c r="H32" s="7" t="inlineStr"/>
-      <c r="I32" s="7" t="inlineStr">
+      <c r="F33" s="7" t="inlineStr"/>
+      <c r="G33" s="7" t="inlineStr"/>
+      <c r="H33" s="7" t="inlineStr"/>
+      <c r="I33" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Quality Control: {"doctype-df-prefix":["DF QUALITY"]}
 expect.toEqual // deep equality
@@ -24815,50 +24871,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J32" s="7" t="inlineStr">
+      <c r="J33" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Qu-ae31c-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K32" s="7" t="inlineStr"/>
-      <c r="L32" s="7" t="inlineStr">
+      <c r="K33" s="7" t="inlineStr"/>
+      <c r="L33" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M32" s="7" t="inlineStr"/>
-      <c r="N32" s="7" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>BUG-031</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="M33" s="7" t="inlineStr"/>
+      <c r="N33" s="7" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>BUG-032</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-SCHM-002</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-SCHM-002 · Schemes &amp; Funding header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
+      <c r="E34" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F33" s="7" t="inlineStr"/>
-      <c r="G33" s="7" t="inlineStr"/>
-      <c r="H33" s="7" t="inlineStr"/>
-      <c r="I33" s="7" t="inlineStr">
+      <c r="F34" s="7" t="inlineStr"/>
+      <c r="G34" s="7" t="inlineStr"/>
+      <c r="H34" s="7" t="inlineStr"/>
+      <c r="I34" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Schemes &amp; Funding: {"doctype-df-prefix":["DF SCHEMES"]}
 expect.toEqual // deep equality
@@ -24872,50 +24928,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J33" s="7" t="inlineStr">
+      <c r="J34" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Sc-67cb2-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K33" s="7" t="inlineStr"/>
-      <c r="L33" s="7" t="inlineStr">
+      <c r="K34" s="7" t="inlineStr"/>
+      <c r="L34" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M33" s="7" t="inlineStr"/>
-      <c r="N33" s="7" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>BUG-032</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="M34" s="7" t="inlineStr"/>
+      <c r="N34" s="7" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>BUG-033</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-STD-002</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-STD-002 · Standardization header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E34" s="7" t="inlineStr">
+      <c r="E35" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F34" s="7" t="inlineStr"/>
-      <c r="G34" s="7" t="inlineStr"/>
-      <c r="H34" s="7" t="inlineStr"/>
-      <c r="I34" s="7" t="inlineStr">
+      <c r="F35" s="7" t="inlineStr"/>
+      <c r="G35" s="7" t="inlineStr"/>
+      <c r="H35" s="7" t="inlineStr"/>
+      <c r="I35" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Standardization: {"doctype-df-prefix":["DF STANDARDIZATION"]}
 expect.toEqual // deep equality
@@ -24929,50 +24985,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J34" s="7" t="inlineStr">
+      <c r="J35" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-St-b8b93-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K34" s="7" t="inlineStr"/>
-      <c r="L34" s="7" t="inlineStr">
+      <c r="K35" s="7" t="inlineStr"/>
+      <c r="L35" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M34" s="7" t="inlineStr"/>
-      <c r="N34" s="7" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>BUG-033</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="M35" s="7" t="inlineStr"/>
+      <c r="N35" s="7" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>BUG-034</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-UP-002</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-UP-002 · Unit Pricing header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F35" s="7" t="inlineStr"/>
-      <c r="G35" s="7" t="inlineStr"/>
-      <c r="H35" s="7" t="inlineStr"/>
-      <c r="I35" s="7" t="inlineStr">
+      <c r="F36" s="7" t="inlineStr"/>
+      <c r="G36" s="7" t="inlineStr"/>
+      <c r="H36" s="7" t="inlineStr"/>
+      <c r="I36" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Unit Pricing: {"doctype-df-prefix":["DF UNIT"]}
 expect.toEqual // deep equality
@@ -24986,58 +25042,58 @@
 + }</t>
         </is>
       </c>
-      <c r="J35" s="7" t="inlineStr">
+      <c r="J36" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Un-0c652-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K35" s="7" t="inlineStr"/>
-      <c r="L35" s="7" t="inlineStr">
+      <c r="K36" s="7" t="inlineStr"/>
+      <c r="L36" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M35" s="7" t="inlineStr"/>
-      <c r="N35" s="7" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>BUG-034</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="M36" s="7" t="inlineStr"/>
+      <c r="N36" s="7" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>BUG-035</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>PR-TC-MS-008</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>14. Masters &amp; Reference Data</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t>Cohort end date must be after start date</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F36" s="7" t="inlineStr">
+      <c r="F37" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G36" s="7" t="inlineStr">
+      <c r="G37" s="7" t="inlineStr">
         <is>
           <t>• Start = 01-Apr-2026, End = 31-Mar-2025.</t>
         </is>
       </c>
-      <c r="H36" s="7" t="inlineStr"/>
-      <c r="I36" s="7" t="inlineStr">
+      <c r="H37" s="7" t="inlineStr"/>
+      <c r="I37" s="7" t="inlineStr">
         <is>
           <t>Error: end-before-start cohort should be rejected
 expect(received).toBeGreaterThanOrEqual(expected)
@@ -25045,59 +25101,59 @@
 Received:    200</t>
         </is>
       </c>
-      <c r="J36" s="7" t="inlineStr"/>
-      <c r="K36" s="7" t="inlineStr"/>
-      <c r="L36" s="7" t="inlineStr">
+      <c r="J37" s="7" t="inlineStr"/>
+      <c r="K37" s="7" t="inlineStr"/>
+      <c r="L37" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M36" s="7" t="inlineStr"/>
-      <c r="N36" s="7" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>BUG-035</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="M37" s="7" t="inlineStr"/>
+      <c r="N37" s="7" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>BUG-036</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>PR-TC-MS-011</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>14. Masters &amp; Reference Data</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
         <is>
           <t>Seed import: 351 rows from "Final PRIME Rural Task Dropdowns Master.xlsx"</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
+      <c r="E38" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F37" s="7" t="inlineStr">
+      <c r="F38" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G37" s="7" t="inlineStr">
+      <c r="G38" s="7" t="inlineStr">
         <is>
           <t>• Run the seed migration script (or use bulk import) using the canonical xlsx.
 • Verify count = 351.</t>
         </is>
       </c>
-      <c r="H37" s="7" t="inlineStr">
+      <c r="H38" s="7" t="inlineStr">
         <is>
           <t>351 Framework Task Master records exist. Each has: module, framework, task_no, task_name, description, phase. Em-dash phase rows have phase = "Other". Logistic Service has its "Other" row added (was missing in the xlsx).</t>
         </is>
       </c>
-      <c r="I37" s="7" t="inlineStr">
+      <c r="I38" s="7" t="inlineStr">
         <is>
           <t>Error: Framework Task Master doctype should exist
 expect(received).toBe(expected) // Object.is equality
@@ -25105,58 +25161,58 @@
 Received: 404</t>
         </is>
       </c>
-      <c r="J37" s="7" t="inlineStr"/>
-      <c r="K37" s="7" t="inlineStr">
+      <c r="J38" s="7" t="inlineStr"/>
+      <c r="K38" s="7" t="inlineStr">
         <is>
           <t>BRD PR-XC-002b.</t>
         </is>
       </c>
-      <c r="L37" s="7" t="inlineStr">
+      <c r="L38" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M37" s="7" t="inlineStr"/>
-      <c r="N37" s="7" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>BUG-036</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="M38" s="7" t="inlineStr"/>
+      <c r="N38" s="7" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>BUG-037</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>PR-TC-MS-015</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
+      <c r="C39" s="7" t="inlineStr">
         <is>
           <t>14. Masters &amp; Reference Data</t>
         </is>
       </c>
-      <c r="D38" s="7" t="inlineStr">
+      <c r="D39" s="7" t="inlineStr">
         <is>
           <t>Document types: Aadhaar, PAN, EPIC, Bank Passbook, Photo, Other</t>
         </is>
       </c>
-      <c r="E38" s="7" t="inlineStr">
+      <c r="E39" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F38" s="7" t="inlineStr">
+      <c r="F39" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G38" s="7" t="inlineStr">
+      <c r="G39" s="7" t="inlineStr">
         <is>
           <t>• Masters → Document Master → list.</t>
         </is>
       </c>
-      <c r="H38" s="7" t="inlineStr"/>
-      <c r="I38" s="7" t="inlineStr">
+      <c r="H39" s="7" t="inlineStr"/>
+      <c r="I39" s="7" t="inlineStr">
         <is>
           <t>Error: expected the standard document types (Aadhaar/PAN/EPIC/Bank/Photo/...)
 expect(received).toBeGreaterThanOrEqual(expected)
@@ -25164,58 +25220,58 @@
 Received:    5</t>
         </is>
       </c>
-      <c r="J38" s="7" t="inlineStr"/>
-      <c r="K38" s="7" t="inlineStr"/>
-      <c r="L38" s="7" t="inlineStr">
+      <c r="J39" s="7" t="inlineStr"/>
+      <c r="K39" s="7" t="inlineStr"/>
+      <c r="L39" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M38" s="7" t="inlineStr"/>
-      <c r="N38" s="7" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>BUG-037</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="M39" s="7" t="inlineStr"/>
+      <c r="N39" s="7" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>BUG-038</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t>PR-TC-MS-020</t>
         </is>
       </c>
-      <c r="C39" s="7" t="inlineStr">
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>14. Masters &amp; Reference Data</t>
         </is>
       </c>
-      <c r="D39" s="7" t="inlineStr">
+      <c r="D40" s="7" t="inlineStr">
         <is>
           <t>19 schemes pre-seeded (MOVCDNER, CGTMSE, NEHHDC, PGS-India Organic, etc.)</t>
         </is>
       </c>
-      <c r="E39" s="7" t="inlineStr">
+      <c r="E40" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F39" s="7" t="inlineStr">
+      <c r="F40" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G39" s="7" t="inlineStr">
+      <c r="G40" s="7" t="inlineStr">
         <is>
           <t>• Open Scheme Master list. Count rows.</t>
         </is>
       </c>
-      <c r="H39" s="7" t="inlineStr">
+      <c r="H40" s="7" t="inlineStr">
         <is>
           <t>19 schemes present per BRD m-schemes. Each has: name, type (Grant / Loan / Subsidy / Certification), eligibility, min/max amount, applicable sectors, interest rate (if loan).</t>
         </is>
       </c>
-      <c r="I39" s="7" t="inlineStr">
+      <c r="I40" s="7" t="inlineStr">
         <is>
           <t>Error: BRD m-schemes expects 19 pre-seeded schemes
 expect(received).toBeGreaterThanOrEqual(expected)
@@ -25223,104 +25279,104 @@
 Received:    3</t>
         </is>
       </c>
-      <c r="J39" s="7" t="inlineStr"/>
-      <c r="K39" s="7" t="inlineStr">
+      <c r="J40" s="7" t="inlineStr"/>
+      <c r="K40" s="7" t="inlineStr">
         <is>
           <t>BRD m-schemes.</t>
         </is>
       </c>
-      <c r="L39" s="7" t="inlineStr">
+      <c r="L40" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M39" s="7" t="inlineStr"/>
-      <c r="N39" s="7" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>BUG-038</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="M40" s="7" t="inlineStr"/>
+      <c r="N40" s="7" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>BUG-039</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>PR-TC-SEC-005</t>
         </is>
       </c>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
         <is>
           <t>23. Security — OWASP &amp; Beyond</t>
         </is>
       </c>
-      <c r="D40" s="7" t="inlineStr">
+      <c r="D41" s="7" t="inlineStr">
         <is>
           <t>Content-Security-Policy header set, restricts inline scripts</t>
         </is>
       </c>
-      <c r="E40" s="7" t="inlineStr">
+      <c r="E41" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F40" s="7" t="inlineStr">
+      <c r="F41" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G40" s="7" t="inlineStr">
+      <c r="G41" s="7" t="inlineStr">
         <is>
           <t>• Inspect response headers on /app/.</t>
         </is>
       </c>
-      <c r="H40" s="7" t="inlineStr"/>
-      <c r="I40" s="7" t="inlineStr">
+      <c r="H41" s="7" t="inlineStr"/>
+      <c r="I41" s="7" t="inlineStr">
         <is>
           <t>Error: CSP header should be set
 expect(received).toBeTruthy()
 Received: undefined</t>
         </is>
       </c>
-      <c r="J40" s="7" t="inlineStr"/>
-      <c r="K40" s="7" t="inlineStr"/>
-      <c r="L40" s="7" t="inlineStr">
+      <c r="J41" s="7" t="inlineStr"/>
+      <c r="K41" s="7" t="inlineStr"/>
+      <c r="L41" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M40" s="7" t="inlineStr"/>
-      <c r="N40" s="7" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>BUG-039</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
+      <c r="M41" s="7" t="inlineStr"/>
+      <c r="N41" s="7" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>BUG-040</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>PR-TC-UI-LEAK-001</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="C42" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D41" s="7" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
         <is>
           <t>PR-TC-UI-LEAK-001 · EP profile shows no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E41" s="7" t="inlineStr">
+      <c r="E42" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F41" s="7" t="inlineStr"/>
-      <c r="G41" s="7" t="inlineStr"/>
-      <c r="H41" s="7" t="inlineStr"/>
-      <c r="I41" s="7" t="inlineStr">
+      <c r="F42" s="7" t="inlineStr"/>
+      <c r="G42" s="7" t="inlineStr"/>
+      <c r="H42" s="7" t="inlineStr"/>
+      <c r="I42" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on EP profile: {"doctype-df-prefix":["DF PROGRESS"]}
 expect.toEqual // deep equality
@@ -25334,50 +25390,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J41" s="7" t="inlineStr">
+      <c r="J42" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\08-ui-no-backend-leak-PR-T-d694f-e-shows-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K41" s="7" t="inlineStr"/>
-      <c r="L41" s="7" t="inlineStr">
+      <c r="K42" s="7" t="inlineStr"/>
+      <c r="L42" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M41" s="7" t="inlineStr"/>
-      <c r="N41" s="7" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>BUG-040</t>
-        </is>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="M42" s="7" t="inlineStr"/>
+      <c r="N42" s="7" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>BUG-041</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>PR-TC-UI-LEAK-002</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C43" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D43" s="7" t="inlineStr">
         <is>
           <t>PR-TC-UI-LEAK-002 · new EP form header is a friendly label, not the raw doctype</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="E43" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F42" s="7" t="inlineStr"/>
-      <c r="G42" s="7" t="inlineStr"/>
-      <c r="H42" s="7" t="inlineStr"/>
-      <c r="I42" s="7" t="inlineStr">
+      <c r="F43" s="7" t="inlineStr"/>
+      <c r="G43" s="7" t="inlineStr"/>
+      <c r="H43" s="7" t="inlineStr"/>
+      <c r="I43" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on new EP form: {"enterprenur-internal":["Enterprenur"]}
 expect.toEqual // deep equality
@@ -25391,52 +25447,52 @@
 + }</t>
         </is>
       </c>
-      <c r="J42" s="7" t="inlineStr">
+      <c r="J43" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\08-ui-no-backend-leak-PR-T-215c4-y-label-not-the-raw-doctype-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K42" s="7" t="inlineStr"/>
-      <c r="L42" s="7" t="inlineStr">
+      <c r="K43" s="7" t="inlineStr"/>
+      <c r="L43" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M42" s="7" t="inlineStr"/>
-      <c r="N42" s="7" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="7" t="inlineStr">
-        <is>
-          <t>BUG-041</t>
-        </is>
-      </c>
-      <c r="B43" s="7" t="inlineStr">
+      <c r="M43" s="7" t="inlineStr"/>
+      <c r="N43" s="7" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>BUG-042</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>PR-TC-UM-001</t>
         </is>
       </c>
-      <c r="C43" s="7" t="inlineStr">
+      <c r="C44" s="7" t="inlineStr">
         <is>
           <t>13. User Management</t>
         </is>
       </c>
-      <c r="D43" s="7" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
         <is>
           <t>Create a new Field Associate user with all required fields</t>
         </is>
       </c>
-      <c r="E43" s="7" t="inlineStr">
+      <c r="E44" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F43" s="7" t="inlineStr">
+      <c r="F44" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G43" s="7" t="inlineStr">
+      <c r="G44" s="7" t="inlineStr">
         <is>
           <t>• Navigate to User Management workspace → "+ New User".
 • Fill: Email = uat-fa-test01@dhwaniris.com, First Name = UAT, Last Name = FA-Test01, Phone = +91 9876543210.
@@ -25446,74 +25502,22 @@
 • Click Save.</t>
         </is>
       </c>
-      <c r="H43" s="7" t="inlineStr">
+      <c r="H44" s="7" t="inlineStr">
         <is>
           <t>Toast: "User created successfully." User row appears in list with status "Active" and "Welcome email sent". Email arrives at the address within 2 min containing a one-time password-set link. Audit log records the creation with timestamp + creator.</t>
         </is>
       </c>
-      <c r="I43" s="7" t="inlineStr">
+      <c r="I44" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: INSERT User → 417: {"exception":"frappe.exceptions.ValidationError: Error syncing User to User Manager: ('User Manager', 'uat-umc-79v3ss@dhwaniris.com', IntegrityError(1062, \"Duplicate entry '[uat]_crud_user' for key 'username'\"))","exc_type":"ValidationError","_exc_source":"dhwani_frappe_base (app)","exc":"[\"Traceback (most recent call last):\\n  File \\\"apps/frappe/frappe/model/base_document.py\\\", line 755, in db_insert\\n    name = frappe.db.sql(\\n    \\t\\\"\\\"\\\"INSERT INTO </t>
         </is>
       </c>
-      <c r="J43" s="7" t="inlineStr"/>
-      <c r="K43" s="7" t="inlineStr">
+      <c r="J44" s="7" t="inlineStr"/>
+      <c r="K44" s="7" t="inlineStr">
         <is>
           <t>BRD: PR-UJ-CTI §User Management.</t>
         </is>
       </c>
-      <c r="L43" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="M43" s="7" t="inlineStr"/>
-      <c r="N43" s="7" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>BUG-042</t>
-        </is>
-      </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>PR-TC-UM-009</t>
-        </is>
-      </c>
-      <c r="C44" s="7" t="inlineStr">
-        <is>
-          <t>13. User Management</t>
-        </is>
-      </c>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>Email must be lowercase and trimmed before save</t>
-        </is>
-      </c>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F44" s="7" t="inlineStr">
-        <is>
-          <t>P1 — High</t>
-        </is>
-      </c>
-      <c r="G44" s="7" t="inlineStr">
-        <is>
-          <t>• Enter email Test@Dhwaniris.COM (leading/trailing spaces, mixed case).</t>
-        </is>
-      </c>
-      <c r="H44" s="7" t="inlineStr"/>
-      <c r="I44" s="7" t="inlineStr">
-        <is>
-          <t>Error: INSERT User → 417: {"exception":"frappe.exceptions.ValidationError: Error syncing User to User Manager: ('User Manager', 'uat-umn-ztbfos@dhwaniris.com', IntegrityError(1062, \"Duplicate entry '[uat]_norm' for key 'username'\"))","exc_type":"ValidationError","_exc_source":"dhwani_frappe_base (app)","exc":"[\"Traceback (most recent call last):\\n  File \\\"apps/frappe/frappe/model/base_document.py\\\", line 755, in db_insert\\n    name = frappe.db.sql(\\n    \\t\\\"\\\"\\\"INSERT INTO `tab{</t>
-        </is>
-      </c>
-      <c r="J44" s="7" t="inlineStr"/>
-      <c r="K44" s="7" t="inlineStr"/>
       <c r="L44" s="7" t="inlineStr">
         <is>
           <t>Open</t>
@@ -25530,30 +25534,82 @@
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
+          <t>PR-TC-UM-009</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>13. User Management</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>Email must be lowercase and trimmed before save</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>P1 — High</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>• Enter email Test@Dhwaniris.COM (leading/trailing spaces, mixed case).</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr"/>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>Error: INSERT User → 417: {"exception":"frappe.exceptions.ValidationError: Error syncing User to User Manager: ('User Manager', 'uat-umn-ztbfos@dhwaniris.com', IntegrityError(1062, \"Duplicate entry '[uat]_norm' for key 'username'\"))","exc_type":"ValidationError","_exc_source":"dhwani_frappe_base (app)","exc":"[\"Traceback (most recent call last):\\n  File \\\"apps/frappe/frappe/model/base_document.py\\\", line 755, in db_insert\\n    name = frappe.db.sql(\\n    \\t\\\"\\\"\\\"INSERT INTO `tab{</t>
+        </is>
+      </c>
+      <c r="J45" s="7" t="inlineStr"/>
+      <c r="K45" s="7" t="inlineStr"/>
+      <c r="L45" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M45" s="7" t="inlineStr"/>
+      <c r="N45" s="7" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>BUG-044</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
           <t>PR-TC-UM-010</t>
         </is>
       </c>
-      <c r="C45" s="7" t="inlineStr">
+      <c r="C46" s="7" t="inlineStr">
         <is>
           <t>13. User Management</t>
         </is>
       </c>
-      <c r="D45" s="7" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
         <is>
           <t>Edit user phone, name, block — changes persist</t>
         </is>
       </c>
-      <c r="E45" s="7" t="inlineStr">
+      <c r="E46" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F45" s="7" t="inlineStr">
+      <c r="F46" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G45" s="7" t="inlineStr">
+      <c r="G46" s="7" t="inlineStr">
         <is>
           <t>• Open user uat-fa-test01.
 • Change First Name to "UAT-Updated".
@@ -25562,63 +25618,10 @@
 • Log out / log in as that user.</t>
         </is>
       </c>
-      <c r="H45" s="7" t="inlineStr"/>
-      <c r="I45" s="7" t="inlineStr">
-        <is>
-          <t>Error: INSERT User → 417: {"exception":"frappe.exceptions.ValidationError: Error syncing User to User Manager: ('User Manager', 'uat-ume-1c8bs5@dhwaniris.com', IntegrityError(1062, \"Duplicate entry '[uat]_before' for key 'username'\"))","exc_type":"ValidationError","_exc_source":"dhwani_frappe_base (app)","exc":"[\"Traceback (most recent call last):\\n  File \\\"apps/frappe/frappe/model/base_document.py\\\", line 755, in db_insert\\n    name = frappe.db.sql(\\n    \\t\\\"\\\"\\\"INSERT INTO `ta</t>
-        </is>
-      </c>
-      <c r="J45" s="7" t="inlineStr"/>
-      <c r="K45" s="7" t="inlineStr"/>
-      <c r="L45" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="M45" s="7" t="inlineStr"/>
-      <c r="N45" s="7" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="7" t="inlineStr">
-        <is>
-          <t>BUG-044</t>
-        </is>
-      </c>
-      <c r="B46" s="7" t="inlineStr">
-        <is>
-          <t>PR-TC-UM-011</t>
-        </is>
-      </c>
-      <c r="C46" s="7" t="inlineStr">
-        <is>
-          <t>13. User Management</t>
-        </is>
-      </c>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>Deactivate a user — they cannot log in until reactivated</t>
-        </is>
-      </c>
-      <c r="E46" s="7" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="F46" s="7" t="inlineStr">
-        <is>
-          <t>P0 — Blocker</t>
-        </is>
-      </c>
-      <c r="G46" s="7" t="inlineStr">
-        <is>
-          <t>• Open uat-fa-test01. Set Enabled = No. Save.
-• Sign out, attempt to log in as uat-fa-test01.</t>
-        </is>
-      </c>
       <c r="H46" s="7" t="inlineStr"/>
       <c r="I46" s="7" t="inlineStr">
         <is>
-          <t>Error: INSERT User → 417: {"exception":"frappe.exceptions.ValidationError: Error syncing User to User Manager: ('User Manager', 'uat-umd-0pc24h@dhwaniris.com', IntegrityError(1062, \"Duplicate entry '[uat]_disabled' for key 'username'\"))","exc_type":"ValidationError","_exc_source":"dhwani_frappe_base (app)","exc":"[\"Traceback (most recent call last):\\n  File \\\"apps/frappe/frappe/model/base_document.py\\\", line 755, in db_insert\\n    name = frappe.db.sql(\\n    \\t\\\"\\\"\\\"INSERT INTO `</t>
+          <t>Error: INSERT User → 417: {"exception":"frappe.exceptions.ValidationError: Error syncing User to User Manager: ('User Manager', 'uat-ume-1c8bs5@dhwaniris.com', IntegrityError(1062, \"Duplicate entry '[uat]_before' for key 'username'\"))","exc_type":"ValidationError","_exc_source":"dhwani_frappe_base (app)","exc":"[\"Traceback (most recent call last):\\n  File \\\"apps/frappe/frappe/model/base_document.py\\\", line 755, in db_insert\\n    name = frappe.db.sql(\\n    \\t\\\"\\\"\\\"INSERT INTO `ta</t>
         </is>
       </c>
       <c r="J46" s="7" t="inlineStr"/>
@@ -25639,104 +25642,157 @@
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
+          <t>PR-TC-UM-011</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>13. User Management</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>Deactivate a user — they cannot log in until reactivated</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>P0 — Blocker</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>• Open uat-fa-test01. Set Enabled = No. Save.
+• Sign out, attempt to log in as uat-fa-test01.</t>
+        </is>
+      </c>
+      <c r="H47" s="7" t="inlineStr"/>
+      <c r="I47" s="7" t="inlineStr">
+        <is>
+          <t>Error: INSERT User → 417: {"exception":"frappe.exceptions.ValidationError: Error syncing User to User Manager: ('User Manager', 'uat-umd-0pc24h@dhwaniris.com', IntegrityError(1062, \"Duplicate entry '[uat]_disabled' for key 'username'\"))","exc_type":"ValidationError","_exc_source":"dhwani_frappe_base (app)","exc":"[\"Traceback (most recent call last):\\n  File \\\"apps/frappe/frappe/model/base_document.py\\\", line 755, in db_insert\\n    name = frappe.db.sql(\\n    \\t\\\"\\\"\\\"INSERT INTO `</t>
+        </is>
+      </c>
+      <c r="J47" s="7" t="inlineStr"/>
+      <c r="K47" s="7" t="inlineStr"/>
+      <c r="L47" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M47" s="7" t="inlineStr"/>
+      <c r="N47" s="7" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>BUG-046</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
           <t>PR-TC-XC-003</t>
         </is>
       </c>
-      <c r="C47" s="7" t="inlineStr">
+      <c r="C48" s="7" t="inlineStr">
         <is>
           <t>4. Application Entry &amp; Routing</t>
         </is>
       </c>
-      <c r="D47" s="7" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr">
         <is>
           <t>Deep link to a protected page while logged out preserves the intent</t>
         </is>
       </c>
-      <c r="E47" s="7" t="inlineStr">
+      <c r="E48" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F47" s="7" t="inlineStr">
+      <c r="F48" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G47" s="7" t="inlineStr">
+      <c r="G48" s="7" t="inlineStr">
         <is>
           <t>• Open https://stgprime-rural.dhwaniris.in/app/enterprenur-profile/EP-001 directly.
 • Login redirect fires.
 • Complete login as a user permitted to see that record.</t>
         </is>
       </c>
-      <c r="H47" s="7" t="inlineStr">
+      <c r="H48" s="7" t="inlineStr">
         <is>
           <t>After successful login, user is redirected to the originally requested URL (the EP detail page), not the default landing page. URL parameter (typically redirect-to or next) is preserved through the auth flow.</t>
         </is>
       </c>
-      <c r="I47" s="7" t="inlineStr">
+      <c r="I48" s="7" t="inlineStr">
         <is>
           <t>Error: expect(received).toMatch(expected)
 Expected pattern: /redirect|next|to=/i
 Received string:  "https://stgprime-rural.dhwaniris.in/primerural/login"</t>
         </is>
       </c>
-      <c r="J47" s="7" t="inlineStr">
+      <c r="J48" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\04-entry-PR-TC-XC-ENTRY-·--e9661-t-preserves-redirect-intent-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K47" s="7" t="inlineStr">
+      <c r="K48" s="7" t="inlineStr">
         <is>
           <t>BRD: PR-OV-001 (Auth)</t>
         </is>
       </c>
-      <c r="L47" s="7" t="inlineStr">
+      <c r="L48" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M47" s="7" t="inlineStr"/>
-      <c r="N47" s="7" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="7" t="inlineStr">
-        <is>
-          <t>BUG-046</t>
-        </is>
-      </c>
-      <c r="B48" s="7" t="inlineStr">
+      <c r="M48" s="7" t="inlineStr"/>
+      <c r="N48" s="7" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>BUG-047</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-023</t>
         </is>
       </c>
-      <c r="C48" s="7" t="inlineStr">
+      <c r="C49" s="7" t="inlineStr">
         <is>
           <t>6. Responsive Layout &amp; Screen Sizes</t>
         </is>
       </c>
-      <c r="D48" s="7" t="inlineStr">
+      <c r="D49" s="7" t="inlineStr">
         <is>
           <t>1024×768 (tablet landscape / iPad / Surface): sidebar collapses to icon rail</t>
         </is>
       </c>
-      <c r="E48" s="7" t="inlineStr">
+      <c r="E49" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F48" s="7" t="inlineStr">
+      <c r="F49" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G48" s="7" t="inlineStr">
+      <c r="G49" s="7" t="inlineStr">
         <is>
           <t>• Resize to 1024×768.</t>
         </is>
       </c>
-      <c r="H48" s="7" t="inlineStr"/>
-      <c r="I48" s="7" t="inlineStr">
+      <c r="H49" s="7" t="inlineStr"/>
+      <c r="I49" s="7" t="inlineStr">
         <is>
           <t>Error: at 1024px the sidebar should collapse to an icon rail; width=240
 expect(received).toBeLessThanOrEqual(expected)
@@ -25744,63 +25800,63 @@
 Received:    240</t>
         </is>
       </c>
-      <c r="J48" s="7" t="inlineStr">
+      <c r="J49" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\06-08-10-nonfunctional-PR--f1c18-ollapses-to-icon-rail-64px--sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K48" s="7" t="inlineStr"/>
-      <c r="L48" s="7" t="inlineStr">
+      <c r="K49" s="7" t="inlineStr"/>
+      <c r="L49" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M48" s="7" t="inlineStr"/>
-      <c r="N48" s="7" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="7" t="inlineStr">
-        <is>
-          <t>BUG-047</t>
-        </is>
-      </c>
-      <c r="B49" s="7" t="inlineStr">
+      <c r="M49" s="7" t="inlineStr"/>
+      <c r="N49" s="7" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>BUG-048</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-032</t>
         </is>
       </c>
-      <c r="C49" s="7" t="inlineStr">
+      <c r="C50" s="7" t="inlineStr">
         <is>
           <t>7. Login &amp; Session</t>
         </is>
       </c>
-      <c r="D49" s="7" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
         <is>
           <t>Wrong password shows a clear error and does NOT reveal whether the email exists</t>
         </is>
       </c>
-      <c r="E49" s="7" t="inlineStr">
+      <c r="E50" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F49" s="7" t="inlineStr">
+      <c r="F50" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G49" s="7" t="inlineStr">
+      <c r="G50" s="7" t="inlineStr">
         <is>
           <t>• Login form: enter a valid email but wrong password.
 • Submit.</t>
         </is>
       </c>
-      <c r="H49" s="7" t="inlineStr">
+      <c r="H50" s="7" t="inlineStr">
         <is>
           <t>Error displays inline above the form: "Invalid email or password." — generic enough that an attacker cannot enumerate valid emails. The password field is cleared; the email field is preserved. No 500. No password ever echoed back into the field.</t>
         </is>
       </c>
-      <c r="I49" s="7" t="inlineStr">
+      <c r="I50" s="7" t="inlineStr">
         <is>
           <t>Error: login error must be friendly text, not a raw exception class
 expect(locator).not.toContainText(expected) failed
@@ -25814,62 +25870,62 @@
     22 × locator resolved to &lt;div role="alert" class="bg-d</t>
         </is>
       </c>
-      <c r="J49" s="7" t="inlineStr">
+      <c r="J50" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\07-auth-PR-TC-XC-AUTH-·-Em-429a0-neric-error-no-enumeration--sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K49" s="7" t="inlineStr">
+      <c r="K50" s="7" t="inlineStr">
         <is>
           <t>OWASP A07 Auth Failures (do not leak account existence).</t>
         </is>
       </c>
-      <c r="L49" s="7" t="inlineStr">
+      <c r="L50" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M49" s="7" t="inlineStr"/>
-      <c r="N49" s="7" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="7" t="inlineStr">
-        <is>
-          <t>BUG-048</t>
-        </is>
-      </c>
-      <c r="B50" s="7" t="inlineStr">
+      <c r="M50" s="7" t="inlineStr"/>
+      <c r="N50" s="7" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>BUG-049</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-033</t>
         </is>
       </c>
-      <c r="C50" s="7" t="inlineStr">
+      <c r="C51" s="7" t="inlineStr">
         <is>
           <t>7. Login &amp; Session</t>
         </is>
       </c>
-      <c r="D50" s="7" t="inlineStr">
+      <c r="D51" s="7" t="inlineStr">
         <is>
           <t>Non-existent email shows the same generic error as wrong password</t>
         </is>
       </c>
-      <c r="E50" s="7" t="inlineStr">
+      <c r="E51" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F50" s="7" t="inlineStr">
+      <c r="F51" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G50" s="7" t="inlineStr">
+      <c r="G51" s="7" t="inlineStr">
         <is>
           <t>• Submit with email not-a-real-user@example.com and any password.</t>
         </is>
       </c>
-      <c r="H50" s="7" t="inlineStr"/>
-      <c r="I50" s="7" t="inlineStr">
+      <c r="H51" s="7" t="inlineStr"/>
+      <c r="I51" s="7" t="inlineStr">
         <is>
           <t>Error: login error must be friendly text, not a raw exception class
 expect(locator).not.toContainText(expected) failed
@@ -25883,129 +25939,77 @@
     22 × locator resolved to &lt;div role="alert" class="bg-d</t>
         </is>
       </c>
-      <c r="J50" s="7" t="inlineStr">
+      <c r="J51" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\07-auth-PR-TC-XC-AUTH-·-Em-a7adf-ows-identical-generic-error-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K50" s="7" t="inlineStr"/>
-      <c r="L50" s="7" t="inlineStr">
+      <c r="K51" s="7" t="inlineStr"/>
+      <c r="L51" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M50" s="7" t="inlineStr"/>
-      <c r="N50" s="7" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="7" t="inlineStr">
-        <is>
-          <t>BUG-049</t>
-        </is>
-      </c>
-      <c r="B51" s="7" t="inlineStr">
+      <c r="M51" s="7" t="inlineStr"/>
+      <c r="N51" s="7" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>BUG-050</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-052</t>
         </is>
       </c>
-      <c r="C51" s="7" t="inlineStr">
+      <c r="C52" s="7" t="inlineStr">
         <is>
           <t>8. UI / UX Rules — Monsoon Court Compliance</t>
         </is>
       </c>
-      <c r="D51" s="7" t="inlineStr">
+      <c r="D52" s="7" t="inlineStr">
         <is>
           <t>No green and no yellow appear anywhere in the UI</t>
         </is>
       </c>
-      <c r="E51" s="7" t="inlineStr">
+      <c r="E52" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F51" s="7" t="inlineStr">
+      <c r="F52" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G51" s="7" t="inlineStr">
+      <c r="G52" s="7" t="inlineStr">
         <is>
           <t>• Visually scan every page for green / yellow elements.
 • Search the rendered CSS for any colour matching green, yellow, #2ecc71, #f1c40f, similar hexes.</t>
         </is>
       </c>
-      <c r="H51" s="7" t="inlineStr">
+      <c r="H52" s="7" t="inlineStr">
         <is>
           <t>Zero green elements. Success states use teal #0E4D4E. Zero yellow elements. Warning states use terracotta #C26849.</t>
         </is>
       </c>
-      <c r="I51" s="7" t="inlineStr">
+      <c r="I52" s="7" t="inlineStr">
         <is>
           <t>Active Entrepreneurs KPI shows a GREEN check rgb(63,107,58) (hue 114). Monsoon Court forbids green — success must be teal #0E4D4E.</t>
         </is>
       </c>
-      <c r="J51" s="7" t="inlineStr">
+      <c r="J52" s="7" t="inlineStr">
         <is>
           <t>.playwright-mcp/bug-xc052-green-kpi.png</t>
         </is>
       </c>
-      <c r="K51" s="7" t="inlineStr">
+      <c r="K52" s="7" t="inlineStr">
         <is>
           <t>Monsoon Court §2.7 (brand non-negotiables).</t>
         </is>
       </c>
-      <c r="L51" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="M51" s="7" t="inlineStr"/>
-      <c r="N51" s="7" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="7" t="inlineStr">
-        <is>
-          <t>BUG-050</t>
-        </is>
-      </c>
-      <c r="B52" s="7" t="inlineStr">
-        <is>
-          <t>PR-TC-XC-054</t>
-        </is>
-      </c>
-      <c r="C52" s="7" t="inlineStr">
-        <is>
-          <t>8. UI / UX Rules — Monsoon Court Compliance</t>
-        </is>
-      </c>
-      <c r="D52" s="7" t="inlineStr">
-        <is>
-          <t>Required-field marker is a terracotta asterisk, not "(required)" text</t>
-        </is>
-      </c>
-      <c r="E52" s="7" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F52" s="7" t="inlineStr">
-        <is>
-          <t>P1 — High</t>
-        </is>
-      </c>
-      <c r="G52" s="7" t="inlineStr">
-        <is>
-          <t>• Open the EP form. Find a required field (e.g. Entrepreneur Name).</t>
-        </is>
-      </c>
-      <c r="H52" s="7" t="inlineStr"/>
-      <c r="I52" s="7" t="inlineStr">
-        <is>
-          <t>Asterisk on the name label is taupe rgb(107,99,89) (inherits label ink-soft), NOT terracotta #C26849. Marker present but wrong colour.</t>
-        </is>
-      </c>
-      <c r="J52" s="7" t="inlineStr"/>
-      <c r="K52" s="7" t="inlineStr"/>
       <c r="L52" s="7" t="inlineStr">
         <is>
           <t>Open</t>
@@ -26022,17 +26026,17 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-XC-063</t>
+          <t>PR-TC-XC-054</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>9. Accessibility — WCAG 2.2 AA</t>
+          <t>8. UI / UX Rules — Monsoon Court Compliance</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>Form fields have associated labels (axe-core "label" rule passes)</t>
+          <t>Required-field marker is a terracotta asterisk, not "(required)" text</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
@@ -26047,11 +26051,63 @@
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>• Run axe-core on the EP form (via Playwright).</t>
+          <t>• Open the EP form. Find a required field (e.g. Entrepreneur Name).</t>
         </is>
       </c>
       <c r="H53" s="7" t="inlineStr"/>
       <c r="I53" s="7" t="inlineStr">
+        <is>
+          <t>Asterisk on the name label is taupe rgb(107,99,89) (inherits label ink-soft), NOT terracotta #C26849. Marker present but wrong colour.</t>
+        </is>
+      </c>
+      <c r="J53" s="7" t="inlineStr"/>
+      <c r="K53" s="7" t="inlineStr"/>
+      <c r="L53" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M53" s="7" t="inlineStr"/>
+      <c r="N53" s="7" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>BUG-052</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-XC-063</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>9. Accessibility — WCAG 2.2 AA</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>Form fields have associated labels (axe-core "label" rule passes)</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>P1 — High</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>• Run axe-core on the EP form (via Playwright).</t>
+        </is>
+      </c>
+      <c r="H54" s="7" t="inlineStr"/>
+      <c r="I54" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: label violations: [{"id":"label","n":6}]
 expect(received).toEqual(expected) // deep equality
@@ -26071,58 +26127,58 @@
 +        </t>
         </is>
       </c>
-      <c r="J53" s="7" t="inlineStr">
+      <c r="J54" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\09-a11y-PR-TC-XC-063-·-for-17d03-ssociated-labels-axe-label--sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K53" s="7" t="inlineStr"/>
-      <c r="L53" s="7" t="inlineStr">
+      <c r="K54" s="7" t="inlineStr"/>
+      <c r="L54" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M53" s="7" t="inlineStr"/>
-      <c r="N53" s="7" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="7" t="inlineStr">
-        <is>
-          <t>BUG-052</t>
-        </is>
-      </c>
-      <c r="B54" s="7" t="inlineStr">
+      <c r="M54" s="7" t="inlineStr"/>
+      <c r="N54" s="7" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>BUG-053</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-064</t>
         </is>
       </c>
-      <c r="C54" s="7" t="inlineStr">
+      <c r="C55" s="7" t="inlineStr">
         <is>
           <t>9. Accessibility — WCAG 2.2 AA</t>
         </is>
       </c>
-      <c r="D54" s="7" t="inlineStr">
+      <c r="D55" s="7" t="inlineStr">
         <is>
           <t>Colour contrast meets WCAG AA</t>
         </is>
       </c>
-      <c r="E54" s="7" t="inlineStr">
+      <c r="E55" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F54" s="7" t="inlineStr">
+      <c r="F55" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G54" s="7" t="inlineStr">
+      <c r="G55" s="7" t="inlineStr">
         <is>
           <t>• Run axe-core's contrast check on EP detail, dashboard, framework form.</t>
         </is>
       </c>
-      <c r="H54" s="7" t="inlineStr"/>
-      <c r="I54" s="7" t="inlineStr">
+      <c r="H55" s="7" t="inlineStr"/>
+      <c r="I55" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: contrast violations: [10]
 expect(received).toEqual(expected) // deep equality
@@ -26138,50 +26194,50 @@
 </t>
         </is>
       </c>
-      <c r="J54" s="7" t="inlineStr">
+      <c r="J55" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\09-a11y-PR-TC-XC-064-·-col-8baa1-WCAG-AA-axe-color-contrast--sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K54" s="7" t="inlineStr"/>
-      <c r="L54" s="7" t="inlineStr">
+      <c r="K55" s="7" t="inlineStr"/>
+      <c r="L55" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M54" s="7" t="inlineStr"/>
-      <c r="N54" s="7" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="7" t="inlineStr">
-        <is>
-          <t>BUG-053</t>
-        </is>
-      </c>
-      <c r="B55" s="7" t="inlineStr">
+      <c r="M55" s="7" t="inlineStr"/>
+      <c r="N55" s="7" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>BUG-054</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-064b</t>
         </is>
       </c>
-      <c r="C55" s="7" t="inlineStr">
+      <c r="C56" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D55" s="7" t="inlineStr">
+      <c r="D56" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-064b · landscape colour contrast (WCAG AA)</t>
         </is>
       </c>
-      <c r="E55" s="7" t="inlineStr">
+      <c r="E56" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F55" s="7" t="inlineStr"/>
-      <c r="G55" s="7" t="inlineStr"/>
-      <c r="H55" s="7" t="inlineStr"/>
-      <c r="I55" s="7" t="inlineStr">
+      <c r="F56" s="7" t="inlineStr"/>
+      <c r="G56" s="7" t="inlineStr"/>
+      <c r="H56" s="7" t="inlineStr"/>
+      <c r="I56" s="7" t="inlineStr">
         <is>
           <t>Error: landscape contrast nodes: 4
 expect(received).toEqual(expected) // deep equality
@@ -26196,19 +26252,19 @@
 +     "id": "color-contrast"</t>
         </is>
       </c>
-      <c r="J55" s="7" t="inlineStr">
+      <c r="J56" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\09-a11y-PR-TC-XC-064b-·-landscape-colour-contrast-WCAG-AA--sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K55" s="7" t="inlineStr"/>
-      <c r="L55" s="7" t="inlineStr">
+      <c r="K56" s="7" t="inlineStr"/>
+      <c r="L56" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M55" s="7" t="inlineStr"/>
-      <c r="N55" s="7" t="inlineStr"/>
+      <c r="M56" s="7" t="inlineStr"/>
+      <c r="N56" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -17747,17 +17747,21 @@
       </c>
       <c r="L241" s="7" t="inlineStr"/>
       <c r="M241" s="7" t="inlineStr"/>
-      <c r="N241" s="13" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+      <c r="N241" s="12" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
       <c r="O241" s="7" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="P241" s="8" t="inlineStr"/>
+          <t>UI form-fill: set Date of Sample Deposit to Office = 2026-06-15 and to Lab = 2026-06-01 (lab BEFORE office, out of order). NO date-order validation/warning fired (live). Spec expects rejection (Received must be on/after Sent). Confirm save-time enforcement.</t>
+        </is>
+      </c>
+      <c r="P241" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="Q241" s="7" t="inlineStr"/>
     </row>
     <row r="242">
@@ -23052,7 +23056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N56"/>
+  <dimension ref="A1:N58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -24038,17 +24042,17 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-FWC-BPC-002</t>
+          <t>PR-TC-FW-TEST-001</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>(not in master — add as test case)</t>
+          <t>17. The 27 Diagnostic Frameworks</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-FWC-BPC-002 · Business Plan Canvas header has no raw doctype / UUID</t>
+          <t>Date chain: Sent ≤ Received ≤ Reported enforced</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -24056,10 +24060,106 @@
           <t>High</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr"/>
-      <c r="G19" s="7" t="inlineStr"/>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>P1 — High</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>• Sent = 10-Apr, Received = 5-Apr.</t>
+        </is>
+      </c>
       <c r="H19" s="7" t="inlineStr"/>
       <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>UI form-fill: set Date of Sample Deposit to Office = 2026-06-15 and to Lab = 2026-06-01 (lab BEFORE office, out of order). NO date-order validation/warning fired (live). Spec expects rejection (Received must be on/after Sent). Confirm save-time enforcement.</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr"/>
+      <c r="K19" s="7" t="inlineStr"/>
+      <c r="L19" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M19" s="7" t="inlineStr"/>
+      <c r="N19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>BUG-018</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-FW-UP-003</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>(not in master — add as test case)</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Unit Pricing tab structure inconsistent (TASKS tab, no Log Book)</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr"/>
+      <c r="G20" s="7" t="inlineStr"/>
+      <c r="H20" s="7" t="inlineStr"/>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>Unit Pricing form tabs = DETAILS/EXISTING/REQUIRED/LINE ITEMS/TASKS/RESOURCES — it has a TASKS tab and NO LOG BOOK, unlike the other 26 frameworks (which show LOG BOOK). Contradicts the BRD decision: Task tab removed from framework forms; Log Book remains.</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="inlineStr"/>
+      <c r="K20" s="7" t="inlineStr"/>
+      <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M20" s="7" t="inlineStr"/>
+      <c r="N20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>BUG-019</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-FWC-BPC-002</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>(not in master — add as test case)</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-FWC-BPC-002 · Business Plan Canvas header has no raw doctype / UUID</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr"/>
+      <c r="G21" s="7" t="inlineStr"/>
+      <c r="H21" s="7" t="inlineStr"/>
+      <c r="I21" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Business Plan Canvas: {"doctype-df-prefix":["DF BUSINESS"]}
 expect.toEqual // deep equality
@@ -24073,50 +24173,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J19" s="7" t="inlineStr">
+      <c r="J21" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Bu-a8fd3-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K19" s="7" t="inlineStr"/>
-      <c r="L19" s="7" t="inlineStr">
+      <c r="K21" s="7" t="inlineStr"/>
+      <c r="L21" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M19" s="7" t="inlineStr"/>
-      <c r="N19" s="7" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>BUG-018</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="M21" s="7" t="inlineStr"/>
+      <c r="N21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>BUG-020</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-BREG-002</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-BREG-002 · Business Registration header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr"/>
-      <c r="G20" s="7" t="inlineStr"/>
-      <c r="H20" s="7" t="inlineStr"/>
-      <c r="I20" s="7" t="inlineStr">
+      <c r="F22" s="7" t="inlineStr"/>
+      <c r="G22" s="7" t="inlineStr"/>
+      <c r="H22" s="7" t="inlineStr"/>
+      <c r="I22" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Business Registration: {"doctype-df-prefix":["DF BUSINESS"]}
 expect.toEqual // deep equality
@@ -24130,50 +24230,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J20" s="7" t="inlineStr">
+      <c r="J22" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Bu-6c730-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K20" s="7" t="inlineStr"/>
-      <c r="L20" s="7" t="inlineStr">
+      <c r="K22" s="7" t="inlineStr"/>
+      <c r="L22" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M20" s="7" t="inlineStr"/>
-      <c r="N20" s="7" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>BUG-019</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="M22" s="7" t="inlineStr"/>
+      <c r="N22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>BUG-021</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-CA-002</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-CA-002 · Customer Analysis header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr"/>
-      <c r="G21" s="7" t="inlineStr"/>
-      <c r="H21" s="7" t="inlineStr"/>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="F23" s="7" t="inlineStr"/>
+      <c r="G23" s="7" t="inlineStr"/>
+      <c r="H23" s="7" t="inlineStr"/>
+      <c r="I23" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Customer Analysis: {"doctype-df-prefix":["DF CUSTOMER"]}
 expect.toEqual // deep equality
@@ -24187,50 +24287,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J21" s="7" t="inlineStr">
+      <c r="J23" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Cu-6ed58-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K21" s="7" t="inlineStr"/>
-      <c r="L21" s="7" t="inlineStr">
+      <c r="K23" s="7" t="inlineStr"/>
+      <c r="L23" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M21" s="7" t="inlineStr"/>
-      <c r="N21" s="7" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>BUG-020</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="M23" s="7" t="inlineStr"/>
+      <c r="N23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>BUG-022</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-CB-002</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-CB-002 · Capacity Building header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr"/>
-      <c r="G22" s="7" t="inlineStr"/>
-      <c r="H22" s="7" t="inlineStr"/>
-      <c r="I22" s="7" t="inlineStr">
+      <c r="F24" s="7" t="inlineStr"/>
+      <c r="G24" s="7" t="inlineStr"/>
+      <c r="H24" s="7" t="inlineStr"/>
+      <c r="I24" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Capacity Building: {"doctype-df-prefix":["DF CAPACITY"]}
 expect.toEqual // deep equality
@@ -24244,50 +24344,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J22" s="7" t="inlineStr">
+      <c r="J24" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Ca-83199-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K22" s="7" t="inlineStr"/>
-      <c r="L22" s="7" t="inlineStr">
+      <c r="K24" s="7" t="inlineStr"/>
+      <c r="L24" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M22" s="7" t="inlineStr"/>
-      <c r="N22" s="7" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>BUG-021</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="M24" s="7" t="inlineStr"/>
+      <c r="N24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>BUG-023</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-DL-002</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-DL-002 · Digital Literacy header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F23" s="7" t="inlineStr"/>
-      <c r="G23" s="7" t="inlineStr"/>
-      <c r="H23" s="7" t="inlineStr"/>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="F25" s="7" t="inlineStr"/>
+      <c r="G25" s="7" t="inlineStr"/>
+      <c r="H25" s="7" t="inlineStr"/>
+      <c r="I25" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Digital Literacy: {"doctype-df-prefix":["DF DIGITAL"]}
 expect.toEqual // deep equality
@@ -24301,50 +24401,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J23" s="7" t="inlineStr">
+      <c r="J25" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Di-845ef-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K23" s="7" t="inlineStr"/>
-      <c r="L23" s="7" t="inlineStr">
+      <c r="K25" s="7" t="inlineStr"/>
+      <c r="L25" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M23" s="7" t="inlineStr"/>
-      <c r="N23" s="7" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>BUG-022</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="M25" s="7" t="inlineStr"/>
+      <c r="N25" s="7" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>BUG-024</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-INFR-002</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-INFR-002 · Infrastructure (BE/EE/CE) header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E26" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr"/>
-      <c r="G24" s="7" t="inlineStr"/>
-      <c r="H24" s="7" t="inlineStr"/>
-      <c r="I24" s="7" t="inlineStr">
+      <c r="F26" s="7" t="inlineStr"/>
+      <c r="G26" s="7" t="inlineStr"/>
+      <c r="H26" s="7" t="inlineStr"/>
+      <c r="I26" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Infrastructure: {"doctype-df-prefix":["DF INFRASTRUCTURE"]}
 expect.toEqual // deep equality
@@ -24358,50 +24458,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J24" s="7" t="inlineStr">
+      <c r="J26" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-In-3328d-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K24" s="7" t="inlineStr"/>
-      <c r="L24" s="7" t="inlineStr">
+      <c r="K26" s="7" t="inlineStr"/>
+      <c r="L26" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M24" s="7" t="inlineStr"/>
-      <c r="N24" s="7" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>BUG-023</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="M26" s="7" t="inlineStr"/>
+      <c r="N26" s="7" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>BUG-025</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-LABL-002</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-LABL-002 · Marketing Label header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F25" s="7" t="inlineStr"/>
-      <c r="G25" s="7" t="inlineStr"/>
-      <c r="H25" s="7" t="inlineStr"/>
-      <c r="I25" s="7" t="inlineStr">
+      <c r="F27" s="7" t="inlineStr"/>
+      <c r="G27" s="7" t="inlineStr"/>
+      <c r="H27" s="7" t="inlineStr"/>
+      <c r="I27" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Marketing Label: {"doctype-df-prefix":["DF MARKETING"]}
 expect.toEqual // deep equality
@@ -24415,50 +24515,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J25" s="7" t="inlineStr">
+      <c r="J27" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Ma-11834-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K25" s="7" t="inlineStr"/>
-      <c r="L25" s="7" t="inlineStr">
+      <c r="K27" s="7" t="inlineStr"/>
+      <c r="L27" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M25" s="7" t="inlineStr"/>
-      <c r="N25" s="7" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>BUG-024</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="M27" s="7" t="inlineStr"/>
+      <c r="N27" s="7" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>BUG-026</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-ML-002</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-ML-002 · Market Linkage header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F26" s="7" t="inlineStr"/>
-      <c r="G26" s="7" t="inlineStr"/>
-      <c r="H26" s="7" t="inlineStr"/>
-      <c r="I26" s="7" t="inlineStr">
+      <c r="F28" s="7" t="inlineStr"/>
+      <c r="G28" s="7" t="inlineStr"/>
+      <c r="H28" s="7" t="inlineStr"/>
+      <c r="I28" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Market Linkage: {"doctype-df-prefix":["DF MARKET"]}
 expect.toEqual // deep equality
@@ -24472,50 +24572,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J26" s="7" t="inlineStr">
+      <c r="J28" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Ma-22f69-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K26" s="7" t="inlineStr"/>
-      <c r="L26" s="7" t="inlineStr">
+      <c r="K28" s="7" t="inlineStr"/>
+      <c r="L28" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M26" s="7" t="inlineStr"/>
-      <c r="N26" s="7" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>BUG-025</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="M28" s="7" t="inlineStr"/>
+      <c r="N28" s="7" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>BUG-027</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-MR-002</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-MR-002 · Market Research header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr"/>
-      <c r="G27" s="7" t="inlineStr"/>
-      <c r="H27" s="7" t="inlineStr"/>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="F29" s="7" t="inlineStr"/>
+      <c r="G29" s="7" t="inlineStr"/>
+      <c r="H29" s="7" t="inlineStr"/>
+      <c r="I29" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Market Research: {"doctype-df-prefix":["DF MARKET"]}
 expect.toEqual // deep equality
@@ -24529,50 +24629,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J27" s="7" t="inlineStr">
+      <c r="J29" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Ma-6eb23-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K27" s="7" t="inlineStr"/>
-      <c r="L27" s="7" t="inlineStr">
+      <c r="K29" s="7" t="inlineStr"/>
+      <c r="L29" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M27" s="7" t="inlineStr"/>
-      <c r="N27" s="7" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>BUG-026</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="M29" s="7" t="inlineStr"/>
+      <c r="N29" s="7" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>BUG-028</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PCMP-002</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PCMP-002 · Product Compliance header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E30" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr"/>
-      <c r="G28" s="7" t="inlineStr"/>
-      <c r="H28" s="7" t="inlineStr"/>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="F30" s="7" t="inlineStr"/>
+      <c r="G30" s="7" t="inlineStr"/>
+      <c r="H30" s="7" t="inlineStr"/>
+      <c r="I30" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Product Compliance: {"doctype-df-prefix":["DF PRODUCT"]}
 expect.toEqual // deep equality
@@ -24586,50 +24686,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J28" s="7" t="inlineStr">
+      <c r="J30" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Pr-be46f-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K28" s="7" t="inlineStr"/>
-      <c r="L28" s="7" t="inlineStr">
+      <c r="K30" s="7" t="inlineStr"/>
+      <c r="L30" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M28" s="7" t="inlineStr"/>
-      <c r="N28" s="7" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>BUG-027</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="M30" s="7" t="inlineStr"/>
+      <c r="N30" s="7" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>BUG-029</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PROM-002</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PROM-002 · Promotional Marketing header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="E31" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr"/>
-      <c r="G29" s="7" t="inlineStr"/>
-      <c r="H29" s="7" t="inlineStr"/>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="F31" s="7" t="inlineStr"/>
+      <c r="G31" s="7" t="inlineStr"/>
+      <c r="H31" s="7" t="inlineStr"/>
+      <c r="I31" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Promotional Marketing: {"doctype-df-prefix":["DF PROMOTIONAL"]}
 expect.toEqual // deep equality
@@ -24643,50 +24743,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J29" s="7" t="inlineStr">
+      <c r="J31" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Pr-d8d12-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K29" s="7" t="inlineStr"/>
-      <c r="L29" s="7" t="inlineStr">
+      <c r="K31" s="7" t="inlineStr"/>
+      <c r="L31" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M29" s="7" t="inlineStr"/>
-      <c r="N29" s="7" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>BUG-028</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="M31" s="7" t="inlineStr"/>
+      <c r="N31" s="7" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>BUG-030</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PROT-002</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PROT-002 · Product Prototyping header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="E32" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr"/>
-      <c r="G30" s="7" t="inlineStr"/>
-      <c r="H30" s="7" t="inlineStr"/>
-      <c r="I30" s="7" t="inlineStr">
+      <c r="F32" s="7" t="inlineStr"/>
+      <c r="G32" s="7" t="inlineStr"/>
+      <c r="H32" s="7" t="inlineStr"/>
+      <c r="I32" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Product Prototyping: {"doctype-df-prefix":["DF PRODUCT"]}
 expect.toEqual // deep equality
@@ -24700,50 +24800,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J30" s="7" t="inlineStr">
+      <c r="J32" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Pr-1120e-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K30" s="7" t="inlineStr"/>
-      <c r="L30" s="7" t="inlineStr">
+      <c r="K32" s="7" t="inlineStr"/>
+      <c r="L32" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M30" s="7" t="inlineStr"/>
-      <c r="N30" s="7" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>BUG-029</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="M32" s="7" t="inlineStr"/>
+      <c r="N32" s="7" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>BUG-031</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PTCH-002</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D33" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PTCH-002 · Pitch Deck header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="E33" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr"/>
-      <c r="G31" s="7" t="inlineStr"/>
-      <c r="H31" s="7" t="inlineStr"/>
-      <c r="I31" s="7" t="inlineStr">
+      <c r="F33" s="7" t="inlineStr"/>
+      <c r="G33" s="7" t="inlineStr"/>
+      <c r="H33" s="7" t="inlineStr"/>
+      <c r="I33" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Pitch Deck: {"doctype-df-prefix":["DF PITCH"]}
 expect.toEqual // deep equality
@@ -24757,50 +24857,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J31" s="7" t="inlineStr">
+      <c r="J33" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Pi-fefd5-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K31" s="7" t="inlineStr"/>
-      <c r="L31" s="7" t="inlineStr">
+      <c r="K33" s="7" t="inlineStr"/>
+      <c r="L33" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M31" s="7" t="inlineStr"/>
-      <c r="N31" s="7" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>BUG-030</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="M33" s="7" t="inlineStr"/>
+      <c r="N33" s="7" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>BUG-032</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PTST-002</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PTST-002 · Product Testing header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
+      <c r="E34" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F32" s="7" t="inlineStr"/>
-      <c r="G32" s="7" t="inlineStr"/>
-      <c r="H32" s="7" t="inlineStr"/>
-      <c r="I32" s="7" t="inlineStr">
+      <c r="F34" s="7" t="inlineStr"/>
+      <c r="G34" s="7" t="inlineStr"/>
+      <c r="H34" s="7" t="inlineStr"/>
+      <c r="I34" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Product Testing: {"doctype-df-prefix":["DF PRODUCT"]}
 expect.toEqual // deep equality
@@ -24814,50 +24914,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J32" s="7" t="inlineStr">
+      <c r="J34" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Pr-3e912-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K32" s="7" t="inlineStr"/>
-      <c r="L32" s="7" t="inlineStr">
+      <c r="K34" s="7" t="inlineStr"/>
+      <c r="L34" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M32" s="7" t="inlineStr"/>
-      <c r="N32" s="7" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>BUG-031</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="M34" s="7" t="inlineStr"/>
+      <c r="N34" s="7" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>BUG-033</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-QC-002</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-QC-002 · Quality Control header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
+      <c r="E35" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F33" s="7" t="inlineStr"/>
-      <c r="G33" s="7" t="inlineStr"/>
-      <c r="H33" s="7" t="inlineStr"/>
-      <c r="I33" s="7" t="inlineStr">
+      <c r="F35" s="7" t="inlineStr"/>
+      <c r="G35" s="7" t="inlineStr"/>
+      <c r="H35" s="7" t="inlineStr"/>
+      <c r="I35" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Quality Control: {"doctype-df-prefix":["DF QUALITY"]}
 expect.toEqual // deep equality
@@ -24871,50 +24971,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J33" s="7" t="inlineStr">
+      <c r="J35" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Qu-ae31c-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K33" s="7" t="inlineStr"/>
-      <c r="L33" s="7" t="inlineStr">
+      <c r="K35" s="7" t="inlineStr"/>
+      <c r="L35" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M33" s="7" t="inlineStr"/>
-      <c r="N33" s="7" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>BUG-032</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="M35" s="7" t="inlineStr"/>
+      <c r="N35" s="7" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>BUG-034</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-SCHM-002</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-SCHM-002 · Schemes &amp; Funding header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E34" s="7" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F34" s="7" t="inlineStr"/>
-      <c r="G34" s="7" t="inlineStr"/>
-      <c r="H34" s="7" t="inlineStr"/>
-      <c r="I34" s="7" t="inlineStr">
+      <c r="F36" s="7" t="inlineStr"/>
+      <c r="G36" s="7" t="inlineStr"/>
+      <c r="H36" s="7" t="inlineStr"/>
+      <c r="I36" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Schemes &amp; Funding: {"doctype-df-prefix":["DF SCHEMES"]}
 expect.toEqual // deep equality
@@ -24928,50 +25028,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J34" s="7" t="inlineStr">
+      <c r="J36" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Sc-67cb2-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K34" s="7" t="inlineStr"/>
-      <c r="L34" s="7" t="inlineStr">
+      <c r="K36" s="7" t="inlineStr"/>
+      <c r="L36" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M34" s="7" t="inlineStr"/>
-      <c r="N34" s="7" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>BUG-033</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="M36" s="7" t="inlineStr"/>
+      <c r="N36" s="7" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>BUG-035</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-STD-002</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-STD-002 · Standardization header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F35" s="7" t="inlineStr"/>
-      <c r="G35" s="7" t="inlineStr"/>
-      <c r="H35" s="7" t="inlineStr"/>
-      <c r="I35" s="7" t="inlineStr">
+      <c r="F37" s="7" t="inlineStr"/>
+      <c r="G37" s="7" t="inlineStr"/>
+      <c r="H37" s="7" t="inlineStr"/>
+      <c r="I37" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Standardization: {"doctype-df-prefix":["DF STANDARDIZATION"]}
 expect.toEqual // deep equality
@@ -24985,50 +25085,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J35" s="7" t="inlineStr">
+      <c r="J37" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-St-b8b93-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K35" s="7" t="inlineStr"/>
-      <c r="L35" s="7" t="inlineStr">
+      <c r="K37" s="7" t="inlineStr"/>
+      <c r="L37" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M35" s="7" t="inlineStr"/>
-      <c r="N35" s="7" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>BUG-034</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="M37" s="7" t="inlineStr"/>
+      <c r="N37" s="7" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>BUG-036</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-UP-002</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-UP-002 · Unit Pricing header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="E38" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F36" s="7" t="inlineStr"/>
-      <c r="G36" s="7" t="inlineStr"/>
-      <c r="H36" s="7" t="inlineStr"/>
-      <c r="I36" s="7" t="inlineStr">
+      <c r="F38" s="7" t="inlineStr"/>
+      <c r="G38" s="7" t="inlineStr"/>
+      <c r="H38" s="7" t="inlineStr"/>
+      <c r="I38" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Unit Pricing: {"doctype-df-prefix":["DF UNIT"]}
 expect.toEqual // deep equality
@@ -25042,58 +25142,58 @@
 + }</t>
         </is>
       </c>
-      <c r="J36" s="7" t="inlineStr">
+      <c r="J38" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Un-0c652-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K36" s="7" t="inlineStr"/>
-      <c r="L36" s="7" t="inlineStr">
+      <c r="K38" s="7" t="inlineStr"/>
+      <c r="L38" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M36" s="7" t="inlineStr"/>
-      <c r="N36" s="7" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>BUG-035</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="M38" s="7" t="inlineStr"/>
+      <c r="N38" s="7" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>BUG-037</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>PR-TC-MS-008</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="C39" s="7" t="inlineStr">
         <is>
           <t>14. Masters &amp; Reference Data</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="D39" s="7" t="inlineStr">
         <is>
           <t>Cohort end date must be after start date</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
+      <c r="E39" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F37" s="7" t="inlineStr">
+      <c r="F39" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G37" s="7" t="inlineStr">
+      <c r="G39" s="7" t="inlineStr">
         <is>
           <t>• Start = 01-Apr-2026, End = 31-Mar-2025.</t>
         </is>
       </c>
-      <c r="H37" s="7" t="inlineStr"/>
-      <c r="I37" s="7" t="inlineStr">
+      <c r="H39" s="7" t="inlineStr"/>
+      <c r="I39" s="7" t="inlineStr">
         <is>
           <t>Error: end-before-start cohort should be rejected
 expect(received).toBeGreaterThanOrEqual(expected)
@@ -25101,59 +25201,59 @@
 Received:    200</t>
         </is>
       </c>
-      <c r="J37" s="7" t="inlineStr"/>
-      <c r="K37" s="7" t="inlineStr"/>
-      <c r="L37" s="7" t="inlineStr">
+      <c r="J39" s="7" t="inlineStr"/>
+      <c r="K39" s="7" t="inlineStr"/>
+      <c r="L39" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M37" s="7" t="inlineStr"/>
-      <c r="N37" s="7" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>BUG-036</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="M39" s="7" t="inlineStr"/>
+      <c r="N39" s="7" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>BUG-038</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t>PR-TC-MS-011</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>14. Masters &amp; Reference Data</t>
         </is>
       </c>
-      <c r="D38" s="7" t="inlineStr">
+      <c r="D40" s="7" t="inlineStr">
         <is>
           <t>Seed import: 351 rows from "Final PRIME Rural Task Dropdowns Master.xlsx"</t>
         </is>
       </c>
-      <c r="E38" s="7" t="inlineStr">
+      <c r="E40" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F38" s="7" t="inlineStr">
+      <c r="F40" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G38" s="7" t="inlineStr">
+      <c r="G40" s="7" t="inlineStr">
         <is>
           <t>• Run the seed migration script (or use bulk import) using the canonical xlsx.
 • Verify count = 351.</t>
         </is>
       </c>
-      <c r="H38" s="7" t="inlineStr">
+      <c r="H40" s="7" t="inlineStr">
         <is>
           <t>351 Framework Task Master records exist. Each has: module, framework, task_no, task_name, description, phase. Em-dash phase rows have phase = "Other". Logistic Service has its "Other" row added (was missing in the xlsx).</t>
         </is>
       </c>
-      <c r="I38" s="7" t="inlineStr">
+      <c r="I40" s="7" t="inlineStr">
         <is>
           <t>Error: Framework Task Master doctype should exist
 expect(received).toBe(expected) // Object.is equality
@@ -25161,58 +25261,58 @@
 Received: 404</t>
         </is>
       </c>
-      <c r="J38" s="7" t="inlineStr"/>
-      <c r="K38" s="7" t="inlineStr">
+      <c r="J40" s="7" t="inlineStr"/>
+      <c r="K40" s="7" t="inlineStr">
         <is>
           <t>BRD PR-XC-002b.</t>
         </is>
       </c>
-      <c r="L38" s="7" t="inlineStr">
+      <c r="L40" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M38" s="7" t="inlineStr"/>
-      <c r="N38" s="7" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>BUG-037</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="M40" s="7" t="inlineStr"/>
+      <c r="N40" s="7" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>BUG-039</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>PR-TC-MS-015</t>
         </is>
       </c>
-      <c r="C39" s="7" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
         <is>
           <t>14. Masters &amp; Reference Data</t>
         </is>
       </c>
-      <c r="D39" s="7" t="inlineStr">
+      <c r="D41" s="7" t="inlineStr">
         <is>
           <t>Document types: Aadhaar, PAN, EPIC, Bank Passbook, Photo, Other</t>
         </is>
       </c>
-      <c r="E39" s="7" t="inlineStr">
+      <c r="E41" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F39" s="7" t="inlineStr">
+      <c r="F41" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G39" s="7" t="inlineStr">
+      <c r="G41" s="7" t="inlineStr">
         <is>
           <t>• Masters → Document Master → list.</t>
         </is>
       </c>
-      <c r="H39" s="7" t="inlineStr"/>
-      <c r="I39" s="7" t="inlineStr">
+      <c r="H41" s="7" t="inlineStr"/>
+      <c r="I41" s="7" t="inlineStr">
         <is>
           <t>Error: expected the standard document types (Aadhaar/PAN/EPIC/Bank/Photo/...)
 expect(received).toBeGreaterThanOrEqual(expected)
@@ -25220,58 +25320,58 @@
 Received:    5</t>
         </is>
       </c>
-      <c r="J39" s="7" t="inlineStr"/>
-      <c r="K39" s="7" t="inlineStr"/>
-      <c r="L39" s="7" t="inlineStr">
+      <c r="J41" s="7" t="inlineStr"/>
+      <c r="K41" s="7" t="inlineStr"/>
+      <c r="L41" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M39" s="7" t="inlineStr"/>
-      <c r="N39" s="7" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>BUG-038</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="M41" s="7" t="inlineStr"/>
+      <c r="N41" s="7" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>BUG-040</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>PR-TC-MS-020</t>
         </is>
       </c>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="C42" s="7" t="inlineStr">
         <is>
           <t>14. Masters &amp; Reference Data</t>
         </is>
       </c>
-      <c r="D40" s="7" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
         <is>
           <t>19 schemes pre-seeded (MOVCDNER, CGTMSE, NEHHDC, PGS-India Organic, etc.)</t>
         </is>
       </c>
-      <c r="E40" s="7" t="inlineStr">
+      <c r="E42" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F40" s="7" t="inlineStr">
+      <c r="F42" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G40" s="7" t="inlineStr">
+      <c r="G42" s="7" t="inlineStr">
         <is>
           <t>• Open Scheme Master list. Count rows.</t>
         </is>
       </c>
-      <c r="H40" s="7" t="inlineStr">
+      <c r="H42" s="7" t="inlineStr">
         <is>
           <t>19 schemes present per BRD m-schemes. Each has: name, type (Grant / Loan / Subsidy / Certification), eligibility, min/max amount, applicable sectors, interest rate (if loan).</t>
         </is>
       </c>
-      <c r="I40" s="7" t="inlineStr">
+      <c r="I42" s="7" t="inlineStr">
         <is>
           <t>Error: BRD m-schemes expects 19 pre-seeded schemes
 expect(received).toBeGreaterThanOrEqual(expected)
@@ -25279,104 +25379,104 @@
 Received:    3</t>
         </is>
       </c>
-      <c r="J40" s="7" t="inlineStr"/>
-      <c r="K40" s="7" t="inlineStr">
+      <c r="J42" s="7" t="inlineStr"/>
+      <c r="K42" s="7" t="inlineStr">
         <is>
           <t>BRD m-schemes.</t>
         </is>
       </c>
-      <c r="L40" s="7" t="inlineStr">
+      <c r="L42" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M40" s="7" t="inlineStr"/>
-      <c r="N40" s="7" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>BUG-039</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
+      <c r="M42" s="7" t="inlineStr"/>
+      <c r="N42" s="7" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>BUG-041</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>PR-TC-SEC-005</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="C43" s="7" t="inlineStr">
         <is>
           <t>23. Security — OWASP &amp; Beyond</t>
         </is>
       </c>
-      <c r="D41" s="7" t="inlineStr">
+      <c r="D43" s="7" t="inlineStr">
         <is>
           <t>Content-Security-Policy header set, restricts inline scripts</t>
         </is>
       </c>
-      <c r="E41" s="7" t="inlineStr">
+      <c r="E43" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F41" s="7" t="inlineStr">
+      <c r="F43" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G41" s="7" t="inlineStr">
+      <c r="G43" s="7" t="inlineStr">
         <is>
           <t>• Inspect response headers on /app/.</t>
         </is>
       </c>
-      <c r="H41" s="7" t="inlineStr"/>
-      <c r="I41" s="7" t="inlineStr">
+      <c r="H43" s="7" t="inlineStr"/>
+      <c r="I43" s="7" t="inlineStr">
         <is>
           <t>Error: CSP header should be set
 expect(received).toBeTruthy()
 Received: undefined</t>
         </is>
       </c>
-      <c r="J41" s="7" t="inlineStr"/>
-      <c r="K41" s="7" t="inlineStr"/>
-      <c r="L41" s="7" t="inlineStr">
+      <c r="J43" s="7" t="inlineStr"/>
+      <c r="K43" s="7" t="inlineStr"/>
+      <c r="L43" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M41" s="7" t="inlineStr"/>
-      <c r="N41" s="7" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>BUG-040</t>
-        </is>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="M43" s="7" t="inlineStr"/>
+      <c r="N43" s="7" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>BUG-042</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>PR-TC-UI-LEAK-001</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C44" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
         <is>
           <t>PR-TC-UI-LEAK-001 · EP profile shows no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="E44" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F42" s="7" t="inlineStr"/>
-      <c r="G42" s="7" t="inlineStr"/>
-      <c r="H42" s="7" t="inlineStr"/>
-      <c r="I42" s="7" t="inlineStr">
+      <c r="F44" s="7" t="inlineStr"/>
+      <c r="G44" s="7" t="inlineStr"/>
+      <c r="H44" s="7" t="inlineStr"/>
+      <c r="I44" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on EP profile: {"doctype-df-prefix":["DF PROGRESS"]}
 expect.toEqual // deep equality
@@ -25390,50 +25490,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J42" s="7" t="inlineStr">
+      <c r="J44" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\08-ui-no-backend-leak-PR-T-d694f-e-shows-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K42" s="7" t="inlineStr"/>
-      <c r="L42" s="7" t="inlineStr">
+      <c r="K44" s="7" t="inlineStr"/>
+      <c r="L44" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M42" s="7" t="inlineStr"/>
-      <c r="N42" s="7" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="7" t="inlineStr">
-        <is>
-          <t>BUG-041</t>
-        </is>
-      </c>
-      <c r="B43" s="7" t="inlineStr">
+      <c r="M44" s="7" t="inlineStr"/>
+      <c r="N44" s="7" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>BUG-043</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>PR-TC-UI-LEAK-002</t>
         </is>
       </c>
-      <c r="C43" s="7" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D43" s="7" t="inlineStr">
+      <c r="D45" s="7" t="inlineStr">
         <is>
           <t>PR-TC-UI-LEAK-002 · new EP form header is a friendly label, not the raw doctype</t>
         </is>
       </c>
-      <c r="E43" s="7" t="inlineStr">
+      <c r="E45" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F43" s="7" t="inlineStr"/>
-      <c r="G43" s="7" t="inlineStr"/>
-      <c r="H43" s="7" t="inlineStr"/>
-      <c r="I43" s="7" t="inlineStr">
+      <c r="F45" s="7" t="inlineStr"/>
+      <c r="G45" s="7" t="inlineStr"/>
+      <c r="H45" s="7" t="inlineStr"/>
+      <c r="I45" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on new EP form: {"enterprenur-internal":["Enterprenur"]}
 expect.toEqual // deep equality
@@ -25447,52 +25547,52 @@
 + }</t>
         </is>
       </c>
-      <c r="J43" s="7" t="inlineStr">
+      <c r="J45" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\08-ui-no-backend-leak-PR-T-215c4-y-label-not-the-raw-doctype-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K43" s="7" t="inlineStr"/>
-      <c r="L43" s="7" t="inlineStr">
+      <c r="K45" s="7" t="inlineStr"/>
+      <c r="L45" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M43" s="7" t="inlineStr"/>
-      <c r="N43" s="7" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>BUG-042</t>
-        </is>
-      </c>
-      <c r="B44" s="7" t="inlineStr">
+      <c r="M45" s="7" t="inlineStr"/>
+      <c r="N45" s="7" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>BUG-044</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>PR-TC-UM-001</t>
         </is>
       </c>
-      <c r="C44" s="7" t="inlineStr">
+      <c r="C46" s="7" t="inlineStr">
         <is>
           <t>13. User Management</t>
         </is>
       </c>
-      <c r="D44" s="7" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
         <is>
           <t>Create a new Field Associate user with all required fields</t>
         </is>
       </c>
-      <c r="E44" s="7" t="inlineStr">
+      <c r="E46" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F44" s="7" t="inlineStr">
+      <c r="F46" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G44" s="7" t="inlineStr">
+      <c r="G46" s="7" t="inlineStr">
         <is>
           <t>• Navigate to User Management workspace → "+ New User".
 • Fill: Email = uat-fa-test01@dhwaniris.com, First Name = UAT, Last Name = FA-Test01, Phone = +91 9876543210.
@@ -25502,114 +25602,114 @@
 • Click Save.</t>
         </is>
       </c>
-      <c r="H44" s="7" t="inlineStr">
+      <c r="H46" s="7" t="inlineStr">
         <is>
           <t>Toast: "User created successfully." User row appears in list with status "Active" and "Welcome email sent". Email arrives at the address within 2 min containing a one-time password-set link. Audit log records the creation with timestamp + creator.</t>
         </is>
       </c>
-      <c r="I44" s="7" t="inlineStr">
+      <c r="I46" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: INSERT User → 417: {"exception":"frappe.exceptions.ValidationError: Error syncing User to User Manager: ('User Manager', 'uat-umc-79v3ss@dhwaniris.com', IntegrityError(1062, \"Duplicate entry '[uat]_crud_user' for key 'username'\"))","exc_type":"ValidationError","_exc_source":"dhwani_frappe_base (app)","exc":"[\"Traceback (most recent call last):\\n  File \\\"apps/frappe/frappe/model/base_document.py\\\", line 755, in db_insert\\n    name = frappe.db.sql(\\n    \\t\\\"\\\"\\\"INSERT INTO </t>
         </is>
       </c>
-      <c r="J44" s="7" t="inlineStr"/>
-      <c r="K44" s="7" t="inlineStr">
+      <c r="J46" s="7" t="inlineStr"/>
+      <c r="K46" s="7" t="inlineStr">
         <is>
           <t>BRD: PR-UJ-CTI §User Management.</t>
         </is>
       </c>
-      <c r="L44" s="7" t="inlineStr">
+      <c r="L46" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M44" s="7" t="inlineStr"/>
-      <c r="N44" s="7" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="7" t="inlineStr">
-        <is>
-          <t>BUG-043</t>
-        </is>
-      </c>
-      <c r="B45" s="7" t="inlineStr">
+      <c r="M46" s="7" t="inlineStr"/>
+      <c r="N46" s="7" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>BUG-045</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
         <is>
           <t>PR-TC-UM-009</t>
         </is>
       </c>
-      <c r="C45" s="7" t="inlineStr">
+      <c r="C47" s="7" t="inlineStr">
         <is>
           <t>13. User Management</t>
         </is>
       </c>
-      <c r="D45" s="7" t="inlineStr">
+      <c r="D47" s="7" t="inlineStr">
         <is>
           <t>Email must be lowercase and trimmed before save</t>
         </is>
       </c>
-      <c r="E45" s="7" t="inlineStr">
+      <c r="E47" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F45" s="7" t="inlineStr">
+      <c r="F47" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G45" s="7" t="inlineStr">
+      <c r="G47" s="7" t="inlineStr">
         <is>
           <t>• Enter email Test@Dhwaniris.COM (leading/trailing spaces, mixed case).</t>
         </is>
       </c>
-      <c r="H45" s="7" t="inlineStr"/>
-      <c r="I45" s="7" t="inlineStr">
+      <c r="H47" s="7" t="inlineStr"/>
+      <c r="I47" s="7" t="inlineStr">
         <is>
           <t>Error: INSERT User → 417: {"exception":"frappe.exceptions.ValidationError: Error syncing User to User Manager: ('User Manager', 'uat-umn-ztbfos@dhwaniris.com', IntegrityError(1062, \"Duplicate entry '[uat]_norm' for key 'username'\"))","exc_type":"ValidationError","_exc_source":"dhwani_frappe_base (app)","exc":"[\"Traceback (most recent call last):\\n  File \\\"apps/frappe/frappe/model/base_document.py\\\", line 755, in db_insert\\n    name = frappe.db.sql(\\n    \\t\\\"\\\"\\\"INSERT INTO `tab{</t>
         </is>
       </c>
-      <c r="J45" s="7" t="inlineStr"/>
-      <c r="K45" s="7" t="inlineStr"/>
-      <c r="L45" s="7" t="inlineStr">
+      <c r="J47" s="7" t="inlineStr"/>
+      <c r="K47" s="7" t="inlineStr"/>
+      <c r="L47" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M45" s="7" t="inlineStr"/>
-      <c r="N45" s="7" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="7" t="inlineStr">
-        <is>
-          <t>BUG-044</t>
-        </is>
-      </c>
-      <c r="B46" s="7" t="inlineStr">
+      <c r="M47" s="7" t="inlineStr"/>
+      <c r="N47" s="7" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>BUG-046</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
         <is>
           <t>PR-TC-UM-010</t>
         </is>
       </c>
-      <c r="C46" s="7" t="inlineStr">
+      <c r="C48" s="7" t="inlineStr">
         <is>
           <t>13. User Management</t>
         </is>
       </c>
-      <c r="D46" s="7" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr">
         <is>
           <t>Edit user phone, name, block — changes persist</t>
         </is>
       </c>
-      <c r="E46" s="7" t="inlineStr">
+      <c r="E48" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F46" s="7" t="inlineStr">
+      <c r="F48" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G46" s="7" t="inlineStr">
+      <c r="G48" s="7" t="inlineStr">
         <is>
           <t>• Open user uat-fa-test01.
 • Change First Name to "UAT-Updated".
@@ -25618,181 +25718,181 @@
 • Log out / log in as that user.</t>
         </is>
       </c>
-      <c r="H46" s="7" t="inlineStr"/>
-      <c r="I46" s="7" t="inlineStr">
+      <c r="H48" s="7" t="inlineStr"/>
+      <c r="I48" s="7" t="inlineStr">
         <is>
           <t>Error: INSERT User → 417: {"exception":"frappe.exceptions.ValidationError: Error syncing User to User Manager: ('User Manager', 'uat-ume-1c8bs5@dhwaniris.com', IntegrityError(1062, \"Duplicate entry '[uat]_before' for key 'username'\"))","exc_type":"ValidationError","_exc_source":"dhwani_frappe_base (app)","exc":"[\"Traceback (most recent call last):\\n  File \\\"apps/frappe/frappe/model/base_document.py\\\", line 755, in db_insert\\n    name = frappe.db.sql(\\n    \\t\\\"\\\"\\\"INSERT INTO `ta</t>
         </is>
       </c>
-      <c r="J46" s="7" t="inlineStr"/>
-      <c r="K46" s="7" t="inlineStr"/>
-      <c r="L46" s="7" t="inlineStr">
+      <c r="J48" s="7" t="inlineStr"/>
+      <c r="K48" s="7" t="inlineStr"/>
+      <c r="L48" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M46" s="7" t="inlineStr"/>
-      <c r="N46" s="7" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="7" t="inlineStr">
-        <is>
-          <t>BUG-045</t>
-        </is>
-      </c>
-      <c r="B47" s="7" t="inlineStr">
+      <c r="M48" s="7" t="inlineStr"/>
+      <c r="N48" s="7" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>BUG-047</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
         <is>
           <t>PR-TC-UM-011</t>
         </is>
       </c>
-      <c r="C47" s="7" t="inlineStr">
+      <c r="C49" s="7" t="inlineStr">
         <is>
           <t>13. User Management</t>
         </is>
       </c>
-      <c r="D47" s="7" t="inlineStr">
+      <c r="D49" s="7" t="inlineStr">
         <is>
           <t>Deactivate a user — they cannot log in until reactivated</t>
         </is>
       </c>
-      <c r="E47" s="7" t="inlineStr">
+      <c r="E49" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F47" s="7" t="inlineStr">
+      <c r="F49" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G47" s="7" t="inlineStr">
+      <c r="G49" s="7" t="inlineStr">
         <is>
           <t>• Open uat-fa-test01. Set Enabled = No. Save.
 • Sign out, attempt to log in as uat-fa-test01.</t>
         </is>
       </c>
-      <c r="H47" s="7" t="inlineStr"/>
-      <c r="I47" s="7" t="inlineStr">
+      <c r="H49" s="7" t="inlineStr"/>
+      <c r="I49" s="7" t="inlineStr">
         <is>
           <t>Error: INSERT User → 417: {"exception":"frappe.exceptions.ValidationError: Error syncing User to User Manager: ('User Manager', 'uat-umd-0pc24h@dhwaniris.com', IntegrityError(1062, \"Duplicate entry '[uat]_disabled' for key 'username'\"))","exc_type":"ValidationError","_exc_source":"dhwani_frappe_base (app)","exc":"[\"Traceback (most recent call last):\\n  File \\\"apps/frappe/frappe/model/base_document.py\\\", line 755, in db_insert\\n    name = frappe.db.sql(\\n    \\t\\\"\\\"\\\"INSERT INTO `</t>
         </is>
       </c>
-      <c r="J47" s="7" t="inlineStr"/>
-      <c r="K47" s="7" t="inlineStr"/>
-      <c r="L47" s="7" t="inlineStr">
+      <c r="J49" s="7" t="inlineStr"/>
+      <c r="K49" s="7" t="inlineStr"/>
+      <c r="L49" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M47" s="7" t="inlineStr"/>
-      <c r="N47" s="7" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="7" t="inlineStr">
-        <is>
-          <t>BUG-046</t>
-        </is>
-      </c>
-      <c r="B48" s="7" t="inlineStr">
+      <c r="M49" s="7" t="inlineStr"/>
+      <c r="N49" s="7" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>BUG-048</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-003</t>
         </is>
       </c>
-      <c r="C48" s="7" t="inlineStr">
+      <c r="C50" s="7" t="inlineStr">
         <is>
           <t>4. Application Entry &amp; Routing</t>
         </is>
       </c>
-      <c r="D48" s="7" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
         <is>
           <t>Deep link to a protected page while logged out preserves the intent</t>
         </is>
       </c>
-      <c r="E48" s="7" t="inlineStr">
+      <c r="E50" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F48" s="7" t="inlineStr">
+      <c r="F50" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G48" s="7" t="inlineStr">
+      <c r="G50" s="7" t="inlineStr">
         <is>
           <t>• Open https://stgprime-rural.dhwaniris.in/app/enterprenur-profile/EP-001 directly.
 • Login redirect fires.
 • Complete login as a user permitted to see that record.</t>
         </is>
       </c>
-      <c r="H48" s="7" t="inlineStr">
+      <c r="H50" s="7" t="inlineStr">
         <is>
           <t>After successful login, user is redirected to the originally requested URL (the EP detail page), not the default landing page. URL parameter (typically redirect-to or next) is preserved through the auth flow.</t>
         </is>
       </c>
-      <c r="I48" s="7" t="inlineStr">
+      <c r="I50" s="7" t="inlineStr">
         <is>
           <t>Error: expect(received).toMatch(expected)
 Expected pattern: /redirect|next|to=/i
 Received string:  "https://stgprime-rural.dhwaniris.in/primerural/login"</t>
         </is>
       </c>
-      <c r="J48" s="7" t="inlineStr">
+      <c r="J50" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\04-entry-PR-TC-XC-ENTRY-·--e9661-t-preserves-redirect-intent-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K48" s="7" t="inlineStr">
+      <c r="K50" s="7" t="inlineStr">
         <is>
           <t>BRD: PR-OV-001 (Auth)</t>
         </is>
       </c>
-      <c r="L48" s="7" t="inlineStr">
+      <c r="L50" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M48" s="7" t="inlineStr"/>
-      <c r="N48" s="7" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="7" t="inlineStr">
-        <is>
-          <t>BUG-047</t>
-        </is>
-      </c>
-      <c r="B49" s="7" t="inlineStr">
+      <c r="M50" s="7" t="inlineStr"/>
+      <c r="N50" s="7" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>BUG-049</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-023</t>
         </is>
       </c>
-      <c r="C49" s="7" t="inlineStr">
+      <c r="C51" s="7" t="inlineStr">
         <is>
           <t>6. Responsive Layout &amp; Screen Sizes</t>
         </is>
       </c>
-      <c r="D49" s="7" t="inlineStr">
+      <c r="D51" s="7" t="inlineStr">
         <is>
           <t>1024×768 (tablet landscape / iPad / Surface): sidebar collapses to icon rail</t>
         </is>
       </c>
-      <c r="E49" s="7" t="inlineStr">
+      <c r="E51" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F49" s="7" t="inlineStr">
+      <c r="F51" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G49" s="7" t="inlineStr">
+      <c r="G51" s="7" t="inlineStr">
         <is>
           <t>• Resize to 1024×768.</t>
         </is>
       </c>
-      <c r="H49" s="7" t="inlineStr"/>
-      <c r="I49" s="7" t="inlineStr">
+      <c r="H51" s="7" t="inlineStr"/>
+      <c r="I51" s="7" t="inlineStr">
         <is>
           <t>Error: at 1024px the sidebar should collapse to an icon rail; width=240
 expect(received).toBeLessThanOrEqual(expected)
@@ -25800,63 +25900,63 @@
 Received:    240</t>
         </is>
       </c>
-      <c r="J49" s="7" t="inlineStr">
+      <c r="J51" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\06-08-10-nonfunctional-PR--f1c18-ollapses-to-icon-rail-64px--sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K49" s="7" t="inlineStr"/>
-      <c r="L49" s="7" t="inlineStr">
+      <c r="K51" s="7" t="inlineStr"/>
+      <c r="L51" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M49" s="7" t="inlineStr"/>
-      <c r="N49" s="7" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="7" t="inlineStr">
-        <is>
-          <t>BUG-048</t>
-        </is>
-      </c>
-      <c r="B50" s="7" t="inlineStr">
+      <c r="M51" s="7" t="inlineStr"/>
+      <c r="N51" s="7" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>BUG-050</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-032</t>
         </is>
       </c>
-      <c r="C50" s="7" t="inlineStr">
+      <c r="C52" s="7" t="inlineStr">
         <is>
           <t>7. Login &amp; Session</t>
         </is>
       </c>
-      <c r="D50" s="7" t="inlineStr">
+      <c r="D52" s="7" t="inlineStr">
         <is>
           <t>Wrong password shows a clear error and does NOT reveal whether the email exists</t>
         </is>
       </c>
-      <c r="E50" s="7" t="inlineStr">
+      <c r="E52" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F50" s="7" t="inlineStr">
+      <c r="F52" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G50" s="7" t="inlineStr">
+      <c r="G52" s="7" t="inlineStr">
         <is>
           <t>• Login form: enter a valid email but wrong password.
 • Submit.</t>
         </is>
       </c>
-      <c r="H50" s="7" t="inlineStr">
+      <c r="H52" s="7" t="inlineStr">
         <is>
           <t>Error displays inline above the form: "Invalid email or password." — generic enough that an attacker cannot enumerate valid emails. The password field is cleared; the email field is preserved. No 500. No password ever echoed back into the field.</t>
         </is>
       </c>
-      <c r="I50" s="7" t="inlineStr">
+      <c r="I52" s="7" t="inlineStr">
         <is>
           <t>Error: login error must be friendly text, not a raw exception class
 expect(locator).not.toContainText(expected) failed
@@ -25870,62 +25970,62 @@
     22 × locator resolved to &lt;div role="alert" class="bg-d</t>
         </is>
       </c>
-      <c r="J50" s="7" t="inlineStr">
+      <c r="J52" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\07-auth-PR-TC-XC-AUTH-·-Em-429a0-neric-error-no-enumeration--sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K50" s="7" t="inlineStr">
+      <c r="K52" s="7" t="inlineStr">
         <is>
           <t>OWASP A07 Auth Failures (do not leak account existence).</t>
         </is>
       </c>
-      <c r="L50" s="7" t="inlineStr">
+      <c r="L52" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M50" s="7" t="inlineStr"/>
-      <c r="N50" s="7" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="7" t="inlineStr">
-        <is>
-          <t>BUG-049</t>
-        </is>
-      </c>
-      <c r="B51" s="7" t="inlineStr">
+      <c r="M52" s="7" t="inlineStr"/>
+      <c r="N52" s="7" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>BUG-051</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-033</t>
         </is>
       </c>
-      <c r="C51" s="7" t="inlineStr">
+      <c r="C53" s="7" t="inlineStr">
         <is>
           <t>7. Login &amp; Session</t>
         </is>
       </c>
-      <c r="D51" s="7" t="inlineStr">
+      <c r="D53" s="7" t="inlineStr">
         <is>
           <t>Non-existent email shows the same generic error as wrong password</t>
         </is>
       </c>
-      <c r="E51" s="7" t="inlineStr">
+      <c r="E53" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F51" s="7" t="inlineStr">
+      <c r="F53" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G51" s="7" t="inlineStr">
+      <c r="G53" s="7" t="inlineStr">
         <is>
           <t>• Submit with email not-a-real-user@example.com and any password.</t>
         </is>
       </c>
-      <c r="H51" s="7" t="inlineStr"/>
-      <c r="I51" s="7" t="inlineStr">
+      <c r="H53" s="7" t="inlineStr"/>
+      <c r="I53" s="7" t="inlineStr">
         <is>
           <t>Error: login error must be friendly text, not a raw exception class
 expect(locator).not.toContainText(expected) failed
@@ -25939,175 +26039,175 @@
     22 × locator resolved to &lt;div role="alert" class="bg-d</t>
         </is>
       </c>
-      <c r="J51" s="7" t="inlineStr">
+      <c r="J53" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\07-auth-PR-TC-XC-AUTH-·-Em-a7adf-ows-identical-generic-error-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K51" s="7" t="inlineStr"/>
-      <c r="L51" s="7" t="inlineStr">
+      <c r="K53" s="7" t="inlineStr"/>
+      <c r="L53" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M51" s="7" t="inlineStr"/>
-      <c r="N51" s="7" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="7" t="inlineStr">
-        <is>
-          <t>BUG-050</t>
-        </is>
-      </c>
-      <c r="B52" s="7" t="inlineStr">
+      <c r="M53" s="7" t="inlineStr"/>
+      <c r="N53" s="7" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>BUG-052</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-052</t>
         </is>
       </c>
-      <c r="C52" s="7" t="inlineStr">
+      <c r="C54" s="7" t="inlineStr">
         <is>
           <t>8. UI / UX Rules — Monsoon Court Compliance</t>
         </is>
       </c>
-      <c r="D52" s="7" t="inlineStr">
+      <c r="D54" s="7" t="inlineStr">
         <is>
           <t>No green and no yellow appear anywhere in the UI</t>
         </is>
       </c>
-      <c r="E52" s="7" t="inlineStr">
+      <c r="E54" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F52" s="7" t="inlineStr">
+      <c r="F54" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G52" s="7" t="inlineStr">
+      <c r="G54" s="7" t="inlineStr">
         <is>
           <t>• Visually scan every page for green / yellow elements.
 • Search the rendered CSS for any colour matching green, yellow, #2ecc71, #f1c40f, similar hexes.</t>
         </is>
       </c>
-      <c r="H52" s="7" t="inlineStr">
+      <c r="H54" s="7" t="inlineStr">
         <is>
           <t>Zero green elements. Success states use teal #0E4D4E. Zero yellow elements. Warning states use terracotta #C26849.</t>
         </is>
       </c>
-      <c r="I52" s="7" t="inlineStr">
+      <c r="I54" s="7" t="inlineStr">
         <is>
           <t>Active Entrepreneurs KPI shows a GREEN check rgb(63,107,58) (hue 114). Monsoon Court forbids green — success must be teal #0E4D4E.</t>
         </is>
       </c>
-      <c r="J52" s="7" t="inlineStr">
+      <c r="J54" s="7" t="inlineStr">
         <is>
           <t>.playwright-mcp/bug-xc052-green-kpi.png</t>
         </is>
       </c>
-      <c r="K52" s="7" t="inlineStr">
+      <c r="K54" s="7" t="inlineStr">
         <is>
           <t>Monsoon Court §2.7 (brand non-negotiables).</t>
         </is>
       </c>
-      <c r="L52" s="7" t="inlineStr">
+      <c r="L54" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M52" s="7" t="inlineStr"/>
-      <c r="N52" s="7" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="7" t="inlineStr">
-        <is>
-          <t>BUG-051</t>
-        </is>
-      </c>
-      <c r="B53" s="7" t="inlineStr">
+      <c r="M54" s="7" t="inlineStr"/>
+      <c r="N54" s="7" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>BUG-053</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-054</t>
         </is>
       </c>
-      <c r="C53" s="7" t="inlineStr">
+      <c r="C55" s="7" t="inlineStr">
         <is>
           <t>8. UI / UX Rules — Monsoon Court Compliance</t>
         </is>
       </c>
-      <c r="D53" s="7" t="inlineStr">
+      <c r="D55" s="7" t="inlineStr">
         <is>
           <t>Required-field marker is a terracotta asterisk, not "(required)" text</t>
         </is>
       </c>
-      <c r="E53" s="7" t="inlineStr">
+      <c r="E55" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F53" s="7" t="inlineStr">
+      <c r="F55" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G53" s="7" t="inlineStr">
+      <c r="G55" s="7" t="inlineStr">
         <is>
           <t>• Open the EP form. Find a required field (e.g. Entrepreneur Name).</t>
         </is>
       </c>
-      <c r="H53" s="7" t="inlineStr"/>
-      <c r="I53" s="7" t="inlineStr">
+      <c r="H55" s="7" t="inlineStr"/>
+      <c r="I55" s="7" t="inlineStr">
         <is>
           <t>Asterisk on the name label is taupe rgb(107,99,89) (inherits label ink-soft), NOT terracotta #C26849. Marker present but wrong colour.</t>
         </is>
       </c>
-      <c r="J53" s="7" t="inlineStr"/>
-      <c r="K53" s="7" t="inlineStr"/>
-      <c r="L53" s="7" t="inlineStr">
+      <c r="J55" s="7" t="inlineStr"/>
+      <c r="K55" s="7" t="inlineStr"/>
+      <c r="L55" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M53" s="7" t="inlineStr"/>
-      <c r="N53" s="7" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="7" t="inlineStr">
-        <is>
-          <t>BUG-052</t>
-        </is>
-      </c>
-      <c r="B54" s="7" t="inlineStr">
+      <c r="M55" s="7" t="inlineStr"/>
+      <c r="N55" s="7" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>BUG-054</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-063</t>
         </is>
       </c>
-      <c r="C54" s="7" t="inlineStr">
+      <c r="C56" s="7" t="inlineStr">
         <is>
           <t>9. Accessibility — WCAG 2.2 AA</t>
         </is>
       </c>
-      <c r="D54" s="7" t="inlineStr">
+      <c r="D56" s="7" t="inlineStr">
         <is>
           <t>Form fields have associated labels (axe-core "label" rule passes)</t>
         </is>
       </c>
-      <c r="E54" s="7" t="inlineStr">
+      <c r="E56" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F54" s="7" t="inlineStr">
+      <c r="F56" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G54" s="7" t="inlineStr">
+      <c r="G56" s="7" t="inlineStr">
         <is>
           <t>• Run axe-core on the EP form (via Playwright).</t>
         </is>
       </c>
-      <c r="H54" s="7" t="inlineStr"/>
-      <c r="I54" s="7" t="inlineStr">
+      <c r="H56" s="7" t="inlineStr"/>
+      <c r="I56" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: label violations: [{"id":"label","n":6}]
 expect(received).toEqual(expected) // deep equality
@@ -26127,58 +26227,58 @@
 +        </t>
         </is>
       </c>
-      <c r="J54" s="7" t="inlineStr">
+      <c r="J56" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\09-a11y-PR-TC-XC-063-·-for-17d03-ssociated-labels-axe-label--sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K54" s="7" t="inlineStr"/>
-      <c r="L54" s="7" t="inlineStr">
+      <c r="K56" s="7" t="inlineStr"/>
+      <c r="L56" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M54" s="7" t="inlineStr"/>
-      <c r="N54" s="7" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="7" t="inlineStr">
-        <is>
-          <t>BUG-053</t>
-        </is>
-      </c>
-      <c r="B55" s="7" t="inlineStr">
+      <c r="M56" s="7" t="inlineStr"/>
+      <c r="N56" s="7" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>BUG-055</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-064</t>
         </is>
       </c>
-      <c r="C55" s="7" t="inlineStr">
+      <c r="C57" s="7" t="inlineStr">
         <is>
           <t>9. Accessibility — WCAG 2.2 AA</t>
         </is>
       </c>
-      <c r="D55" s="7" t="inlineStr">
+      <c r="D57" s="7" t="inlineStr">
         <is>
           <t>Colour contrast meets WCAG AA</t>
         </is>
       </c>
-      <c r="E55" s="7" t="inlineStr">
+      <c r="E57" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F55" s="7" t="inlineStr">
+      <c r="F57" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G55" s="7" t="inlineStr">
+      <c r="G57" s="7" t="inlineStr">
         <is>
           <t>• Run axe-core's contrast check on EP detail, dashboard, framework form.</t>
         </is>
       </c>
-      <c r="H55" s="7" t="inlineStr"/>
-      <c r="I55" s="7" t="inlineStr">
+      <c r="H57" s="7" t="inlineStr"/>
+      <c r="I57" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: contrast violations: [10]
 expect(received).toEqual(expected) // deep equality
@@ -26194,50 +26294,50 @@
 </t>
         </is>
       </c>
-      <c r="J55" s="7" t="inlineStr">
+      <c r="J57" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\09-a11y-PR-TC-XC-064-·-col-8baa1-WCAG-AA-axe-color-contrast--sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K55" s="7" t="inlineStr"/>
-      <c r="L55" s="7" t="inlineStr">
+      <c r="K57" s="7" t="inlineStr"/>
+      <c r="L57" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M55" s="7" t="inlineStr"/>
-      <c r="N55" s="7" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="7" t="inlineStr">
-        <is>
-          <t>BUG-054</t>
-        </is>
-      </c>
-      <c r="B56" s="7" t="inlineStr">
+      <c r="M57" s="7" t="inlineStr"/>
+      <c r="N57" s="7" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>BUG-056</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-064b</t>
         </is>
       </c>
-      <c r="C56" s="7" t="inlineStr">
+      <c r="C58" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D56" s="7" t="inlineStr">
+      <c r="D58" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-064b · landscape colour contrast (WCAG AA)</t>
         </is>
       </c>
-      <c r="E56" s="7" t="inlineStr">
+      <c r="E58" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F56" s="7" t="inlineStr"/>
-      <c r="G56" s="7" t="inlineStr"/>
-      <c r="H56" s="7" t="inlineStr"/>
-      <c r="I56" s="7" t="inlineStr">
+      <c r="F58" s="7" t="inlineStr"/>
+      <c r="G58" s="7" t="inlineStr"/>
+      <c r="H58" s="7" t="inlineStr"/>
+      <c r="I58" s="7" t="inlineStr">
         <is>
           <t>Error: landscape contrast nodes: 4
 expect(received).toEqual(expected) // deep equality
@@ -26252,19 +26352,19 @@
 +     "id": "color-contrast"</t>
         </is>
       </c>
-      <c r="J56" s="7" t="inlineStr">
+      <c r="J58" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\09-a11y-PR-TC-XC-064b-·-landscape-colour-contrast-WCAG-AA--sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K56" s="7" t="inlineStr"/>
-      <c r="L56" s="7" t="inlineStr">
+      <c r="K58" s="7" t="inlineStr"/>
+      <c r="L58" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M56" s="7" t="inlineStr"/>
-      <c r="N56" s="7" t="inlineStr"/>
+      <c r="M58" s="7" t="inlineStr"/>
+      <c r="N58" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -18495,9 +18495,9 @@
       </c>
       <c r="L252" s="7" t="inlineStr"/>
       <c r="M252" s="7" t="inlineStr"/>
-      <c r="N252" s="13" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+      <c r="N252" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O252" s="7" t="inlineStr">

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -4861,17 +4861,21 @@
       </c>
       <c r="L56" s="7" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
-      <c r="N56" s="13" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+      <c r="N56" s="12" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
       <c r="O56" s="7" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="P56" s="8" t="inlineStr"/>
+          <t>Keyboard-Tab focus on buttons + links shows the default UA outline (rgb(16,16,16) auto ~0.67px), NOT the spec 2px terracotta ring with 2px cream offset. Focus IS visible (not an a11y blocker) but does not match the design system.</t>
+        </is>
+      </c>
+      <c r="P56" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="Q56" s="7" t="inlineStr"/>
     </row>
     <row r="57">
@@ -19858,17 +19862,21 @@
       </c>
       <c r="L273" s="7" t="inlineStr"/>
       <c r="M273" s="7" t="inlineStr"/>
-      <c r="N273" s="13" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+      <c r="N273" s="12" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
       <c r="O273" s="7" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="P273" s="8" t="inlineStr"/>
+          <t>Filtered Landscape to 0 records (Handicrafts + Supported + Idea): KPIs correctly show 0 and layout holds (no horizontal overflow), but NO empty-state message ("No data matches your filters") is shown — the map just renders empty. Spec (DB-EPS-004) expects an EmptyState message.</t>
+        </is>
+      </c>
+      <c r="P273" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="Q273" s="7" t="inlineStr"/>
     </row>
     <row r="274">
@@ -23056,7 +23064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N58"/>
+  <dimension ref="A1:N60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -23216,17 +23224,17 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-DB-EPS-006</t>
+          <t>PR-TC-DB-EPS-004</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>(not in master — add as test case)</t>
+          <t>19. Dashboards</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-DB-EPS-006 · District→Block cascade filter is available on the dashboard</t>
+          <t>Filtering down to zero records shows EmptyState, not a broken chart</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -23234,10 +23242,62 @@
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr"/>
-      <c r="G4" s="7" t="inlineStr"/>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>P1 — High</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>• Apply filters until no records match.</t>
+        </is>
+      </c>
       <c r="H4" s="7" t="inlineStr"/>
       <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>Filtered Landscape to 0 records (Handicrafts + Supported + Idea): KPIs correctly show 0 and layout holds (no horizontal overflow), but NO empty-state message ("No data matches your filters") is shown — the map just renders empty. Spec (DB-EPS-004) expects an EmptyState message.</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr"/>
+      <c r="K4" s="7" t="inlineStr"/>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M4" s="7" t="inlineStr"/>
+      <c r="N4" s="7" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>BUG-003</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-DB-EPS-006</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>(not in master — add as test case)</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-DB-EPS-006 · District→Block cascade filter is available on the dashboard</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr"/>
+      <c r="G5" s="7" t="inlineStr"/>
+      <c r="H5" s="7" t="inlineStr"/>
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>Error: dashboard should expose a District (and cascading Block) filter
 expect(received).toBe(expected) // Object.is equality
@@ -23245,50 +23305,50 @@
 Received: false</t>
         </is>
       </c>
-      <c r="J4" s="7" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\19-dashboard-filters-PR-TC-dcc9e--available-on-the-dashboard-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K4" s="7" t="inlineStr"/>
-      <c r="L4" s="7" t="inlineStr">
+      <c r="K5" s="7" t="inlineStr"/>
+      <c r="L5" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M4" s="7" t="inlineStr"/>
-      <c r="N4" s="7" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>BUG-003</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="M5" s="7" t="inlineStr"/>
+      <c r="N5" s="7" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>BUG-004</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>PR-TC-DB-EPS-007</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>PR-TC-DB-EPS-007 · selecting a filter recomputes the KPI counts</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr"/>
-      <c r="G5" s="7" t="inlineStr"/>
-      <c r="H5" s="7" t="inlineStr"/>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr"/>
+      <c r="G6" s="7" t="inlineStr"/>
+      <c r="H6" s="7" t="inlineStr"/>
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>Error: KPI should recompute on Sector filter (before=-1, after=-1)
 expect(received).toBeLessThan(expected)
@@ -23296,50 +23356,50 @@
 Received:   -1</t>
         </is>
       </c>
-      <c r="J5" s="7" t="inlineStr">
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\19-dashboard-filters-PR-TC-7a839-r-recomputes-the-KPI-counts-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K5" s="7" t="inlineStr"/>
-      <c r="L5" s="7" t="inlineStr">
+      <c r="K6" s="7" t="inlineStr"/>
+      <c r="L6" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M5" s="7" t="inlineStr"/>
-      <c r="N5" s="7" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>BUG-004</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="M6" s="7" t="inlineStr"/>
+      <c r="N6" s="7" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>BUG-005</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>PR-TC-DB-MAP-001</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>PR-TC-DB-MAP-001 · geo coordinates are captured; count cross-checks the GPS-Verified KPI</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr"/>
-      <c r="G6" s="7" t="inlineStr"/>
-      <c r="H6" s="7" t="inlineStr"/>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr"/>
+      <c r="G7" s="7" t="inlineStr"/>
+      <c r="H7" s="7" t="inlineStr"/>
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>Error: GPS-Verified KPI should be a positive count
 expect(received).toBeGreaterThan(expected)
@@ -23347,50 +23407,50 @@
 Received:   -1</t>
         </is>
       </c>
-      <c r="J6" s="7" t="inlineStr">
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\19-dashboard-maps-PR-TC-DB-c738a-checks-the-GPS-Verified-KPI-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K6" s="7" t="inlineStr"/>
-      <c r="L6" s="7" t="inlineStr">
+      <c r="K7" s="7" t="inlineStr"/>
+      <c r="L7" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M6" s="7" t="inlineStr"/>
-      <c r="N6" s="7" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>BUG-005</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="M7" s="7" t="inlineStr"/>
+      <c r="N7" s="7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>BUG-006</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>PR-TC-DB-MAP-002</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>PR-TC-DB-MAP-002 · Landscape map renders (Leaflet canvas + tiles)</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr"/>
-      <c r="G7" s="7" t="inlineStr"/>
-      <c r="H7" s="7" t="inlineStr"/>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr"/>
+      <c r="G8" s="7" t="inlineStr"/>
+      <c r="H8" s="7" t="inlineStr"/>
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>Error: Leaflet map container present
 expect(received).toBe(expected) // Object.is equality
@@ -23398,50 +23458,50 @@
 Received: false</t>
         </is>
       </c>
-      <c r="J7" s="7" t="inlineStr">
+      <c r="J8" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\19-dashboard-maps-PR-TC-DB-b4e39-nders-Leaflet-canvas-tiles--sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K7" s="7" t="inlineStr"/>
-      <c r="L7" s="7" t="inlineStr">
+      <c r="K8" s="7" t="inlineStr"/>
+      <c r="L8" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M7" s="7" t="inlineStr"/>
-      <c r="N7" s="7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>BUG-006</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="M8" s="7" t="inlineStr"/>
+      <c r="N8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>BUG-007</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>PR-TC-DB-MAP-003</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>PR-TC-DB-MAP-003 · Meghalaya boundary overlay is rendered</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr"/>
-      <c r="G8" s="7" t="inlineStr"/>
-      <c r="H8" s="7" t="inlineStr"/>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr"/>
+      <c r="G9" s="7" t="inlineStr"/>
+      <c r="H9" s="7" t="inlineStr"/>
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>Error: state boundary overlay (svg path or canvas) should render
 expect(received).toBe(expected) // Object.is equality
@@ -23449,50 +23509,50 @@
 Received: false</t>
         </is>
       </c>
-      <c r="J8" s="7" t="inlineStr">
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\19-dashboard-maps-PR-TC-DB-14a33-oundary-overlay-is-rendered-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K8" s="7" t="inlineStr"/>
-      <c r="L8" s="7" t="inlineStr">
+      <c r="K9" s="7" t="inlineStr"/>
+      <c r="L9" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M8" s="7" t="inlineStr"/>
-      <c r="N8" s="7" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>BUG-007</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="M9" s="7" t="inlineStr"/>
+      <c r="N9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>BUG-008</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>PR-TC-DB-MAP-005</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>PR-TC-DB-MAP-005 · captured coordinates fall within Meghalaya bounds (geo validation)</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr"/>
-      <c r="G9" s="7" t="inlineStr"/>
-      <c r="H9" s="7" t="inlineStr"/>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr"/>
+      <c r="G10" s="7" t="inlineStr"/>
+      <c r="H10" s="7" t="inlineStr"/>
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>Error: all geo-tags must be valid Meghalaya coords; 5 out-of-bounds (37.422,-122.084 ; 28.452,77.072 ; 28.623,77.218) + 6 malformed GeoJSON
 expect(received).toBe(expected) // Object.is equality
@@ -23500,50 +23560,6 @@
 Received: 11</t>
         </is>
       </c>
-      <c r="J9" s="7" t="inlineStr"/>
-      <c r="K9" s="7" t="inlineStr"/>
-      <c r="L9" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="M9" s="7" t="inlineStr"/>
-      <c r="N9" s="7" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>BUG-008</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>PR-TC-DB-NAV-001</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>(not in master — add as test case)</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>Status Monitor nav link routes to the EP status view</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr"/>
-      <c r="G10" s="7" t="inlineStr"/>
-      <c r="H10" s="7" t="inlineStr"/>
-      <c r="I10" s="7" t="inlineStr">
-        <is>
-          <t>Sidebar 'Status Monitor' link has href=null and clicking it does not navigate (dead/placeholder link). The District/Block-filtered status-monitor view appears not to be wired in the /primerural SPA.</t>
-        </is>
-      </c>
       <c r="J10" s="7" t="inlineStr"/>
       <c r="K10" s="7" t="inlineStr"/>
       <c r="L10" s="7" t="inlineStr">
@@ -23562,7 +23578,7 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-DB-VIS-001</t>
+          <t>PR-TC-DB-NAV-001</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -23572,7 +23588,7 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-DB-VIS-001 · Village Visits mode updates KPIs to village-visit context (GPS pin count)</t>
+          <t>Status Monitor nav link routes to the EP status view</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -23585,57 +23601,101 @@
       <c r="H11" s="7" t="inlineStr"/>
       <c r="I11" s="7" t="inlineStr">
         <is>
+          <t>Sidebar 'Status Monitor' link has href=null and clicking it does not navigate (dead/placeholder link). The District/Block-filtered status-monitor view appears not to be wired in the /primerural SPA.</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr"/>
+      <c r="K11" s="7" t="inlineStr"/>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M11" s="7" t="inlineStr"/>
+      <c r="N11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>BUG-010</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-DB-VIS-001</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>(not in master — add as test case)</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-DB-VIS-001 · Village Visits mode updates KPIs to village-visit context (GPS pin count)</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr"/>
+      <c r="G12" s="7" t="inlineStr"/>
+      <c r="H12" s="7" t="inlineStr"/>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
           <t>TimeoutError: locator.click: Timeout 15000ms exceeded.
 Call log:
   - waiting for locator('main button:has-text("Village Visits")')</t>
         </is>
       </c>
-      <c r="J11" s="7" t="inlineStr">
+      <c r="J12" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\19-dashboard-filters-PR-TC-1d640-isit-context-GPS-pin-count--sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K11" s="7" t="inlineStr"/>
-      <c r="L11" s="7" t="inlineStr">
+      <c r="K12" s="7" t="inlineStr"/>
+      <c r="L12" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M11" s="7" t="inlineStr"/>
-      <c r="N11" s="7" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>BUG-010</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="M12" s="7" t="inlineStr"/>
+      <c r="N12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>BUG-011</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>PR-TC-EP-001</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>15. Entrepreneur Profile — Full Lifecycle</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>Create a new EP with all required fields filled</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F13" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>• EP list → +New Entrepreneur.
 • About Entrepreneur: Name = "[UAT] Honey Farmer One", DOB = 15-Apr-1985, Gender = Female, Education = 10th, Marital = Married, Family Size = 5-10, Language = Khasi.
@@ -23647,12 +23707,12 @@
 • Click Save.</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>Saved. EP-name like EP-[UAT] Honey Farmer One-00001 auto-generated. Toast: "Saved." Profile Dashboard tab loads with hero card, basic info, and an empty Diagnostic Framework block (no priorities set yet). Activity Status = "MET". Final Selection = blank (will be set by CTIT later).</t>
         </is>
       </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="I13" s="7" t="inlineStr">
         <is>
           <t>Error: expect(locator).toContainText(expected) failed
 Locator: getByRole('heading', { level: 1 })
@@ -23666,56 +23726,56 @@
        - unexpected value "Welcome back"</t>
         </is>
       </c>
-      <c r="J12" s="7" t="inlineStr">
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\15-ep-profile-PR-TC-EP-·-E-9e8a3-t-required-field-gates-Save-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K12" s="7" t="inlineStr">
+      <c r="K13" s="7" t="inlineStr">
         <is>
           <t>BRD: PR-EP-001.</t>
         </is>
       </c>
-      <c r="L12" s="7" t="inlineStr">
+      <c r="L13" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M12" s="7" t="inlineStr"/>
-      <c r="N12" s="7" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>BUG-011</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="M13" s="7" t="inlineStr"/>
+      <c r="N13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>BUG-012</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>PR-TC-EP-005</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>15. Entrepreneur Profile — Full Lifecycle</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>Required fields enforced: Name, Sector, District, Block, Village</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>• Save with all fields blank.
 • Fill only Name; save.
@@ -23723,8 +23783,8 @@
 • Continue progressively.</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr"/>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr"/>
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>Error: EP without Sector/District should be rejected (BRD requires them)
 expect(received).toBeGreaterThanOrEqual(expected)
@@ -23732,56 +23792,56 @@
 Received:    200</t>
         </is>
       </c>
-      <c r="J13" s="7" t="inlineStr"/>
-      <c r="K13" s="7" t="inlineStr"/>
-      <c r="L13" s="7" t="inlineStr">
+      <c r="J14" s="7" t="inlineStr"/>
+      <c r="K14" s="7" t="inlineStr"/>
+      <c r="L14" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M13" s="7" t="inlineStr"/>
-      <c r="N13" s="7" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>BUG-012</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="M14" s="7" t="inlineStr"/>
+      <c r="N14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>BUG-013</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>PR-TC-EP-007</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>15. Entrepreneur Profile — Full Lifecycle</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>DOB validation: not future, not &amp;gt; 100 years old, not &amp;lt; 14 years old</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>• DOB = tomorrow. Save.
 • DOB = 31-Dec-1899 (&gt; 100 years).
 • DOB = today - 10 years.</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr"/>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="H15" s="7" t="inlineStr"/>
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>Error: future date of birth should be rejected
 expect(received).toBeGreaterThanOrEqual(expected)
@@ -23789,60 +23849,60 @@
 Received:    200</t>
         </is>
       </c>
-      <c r="J14" s="7" t="inlineStr"/>
-      <c r="K14" s="7" t="inlineStr"/>
-      <c r="L14" s="7" t="inlineStr">
+      <c r="J15" s="7" t="inlineStr"/>
+      <c r="K15" s="7" t="inlineStr"/>
+      <c r="L15" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M14" s="7" t="inlineStr"/>
-      <c r="N14" s="7" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>BUG-013</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="M15" s="7" t="inlineStr"/>
+      <c r="N15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>BUG-014</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>PR-TC-EP-016</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>15. Entrepreneur Profile — Full Lifecycle</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>FA fills all 10 ratings (0-1 scale) during profiling — avg_rating auto-computes</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr">
         <is>
           <t>• Open EP → Selection tab → Field Evaluation section.
 • Set all 10 ratings to 0.7.
 • Save.</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="H16" s="7" t="inlineStr">
         <is>
           <t>avg_rating shows 0.70 (auto-computed). Save succeeds. Recomputes immediately on any rating change.</t>
         </is>
       </c>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="I16" s="7" t="inlineStr">
         <is>
           <t>Error: avg_rating should compute to ~0.7 (got 3.5)
 expect(received).toBeCloseTo(expected, precision)
@@ -23853,58 +23913,58 @@
 Received difference:   2.8</t>
         </is>
       </c>
-      <c r="J15" s="7" t="inlineStr"/>
-      <c r="K15" s="7" t="inlineStr">
+      <c r="J16" s="7" t="inlineStr"/>
+      <c r="K16" s="7" t="inlineStr">
         <is>
           <t>BRD Decision: Fellow fills 10Q + Rural E-Champ during profiling.</t>
         </is>
       </c>
-      <c r="L15" s="7" t="inlineStr">
+      <c r="L16" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M15" s="7" t="inlineStr"/>
-      <c r="N15" s="7" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>BUG-014</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="M16" s="7" t="inlineStr"/>
+      <c r="N16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>BUG-015</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>PR-TC-EP-031</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>15. Entrepreneur Profile — Full Lifecycle</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>EP list columns: Avatar, Name, Sector, Block, Status, Cohort, Last activity, Actions</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F17" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="G17" s="7" t="inlineStr">
         <is>
           <t>• Open EP list.</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr"/>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="H17" s="7" t="inlineStr"/>
+      <c r="I17" s="7" t="inlineStr">
         <is>
           <t>Error: expect(locator).toBeVisible() failed
 Locator: getByRole('navigation').getByRole('link', { name: 'Entrepreneur List' })
@@ -23916,63 +23976,11 @@
   - waiting for getByRole('navigation').getByRole('link', { name: 'Entrepreneur List' })</t>
         </is>
       </c>
-      <c r="J16" s="7" t="inlineStr">
+      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\15-ep-profile-PR-TC-EP-·-E-77dc1--031-·-EP-list-page-renders-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K16" s="7" t="inlineStr"/>
-      <c r="L16" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="M16" s="7" t="inlineStr"/>
-      <c r="N16" s="7" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>BUG-015</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>PR-TC-FW-MACH-001</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>17. The 27 Diagnostic Frameworks</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>Add machine — depreciation auto-calculated per straight-line method</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>P0 — Blocker</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>• Cost = 50,000, Useful Life = 10 years, Residual = 5,000.</t>
-        </is>
-      </c>
-      <c r="H17" s="7" t="inlineStr"/>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>UI form-fill: Cost Rs50,000, Useful Life 10y -&gt; MONTHLY DEPRECIATION Rs416.67 (= Rs5,000/yr, straight-line cost/life). NO salvage/residual-value field on the form, so it does NOT match BRD (cost-salvage)/life = Rs4,500/yr. Salvage not captured; depreciation overstated vs spec.</t>
-        </is>
-      </c>
-      <c r="J17" s="7" t="inlineStr"/>
       <c r="K17" s="7" t="inlineStr"/>
       <c r="L17" s="7" t="inlineStr">
         <is>
@@ -23990,7 +23998,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-FW-QC-001</t>
+          <t>PR-TC-FW-MACH-001</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -24000,28 +24008,28 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Fill all 23 stars; total score auto-computes</t>
+          <t>Add machine — depreciation auto-calculated per straight-line method</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>P1 — High</t>
+          <t>P0 — Blocker</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>• Set all 23 questions to 4 stars (out of 5).</t>
+          <t>• Cost = 50,000, Useful Life = 10 years, Residual = 5,000.</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr"/>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>QC EXISTING uses an "+ Add Item" checklist with a 4-LEVEL rating (0/33/66/100) and AVERAGE SCORE (%), NOT the BRD spec of 23 fixed stars totalling /115 (e.g. 92/115=80%). Items are manually added (not pre-loaded). Confirm whether 23 standard items should pre-load + whether the scoring model should match spec.</t>
+          <t>UI form-fill: Cost Rs50,000, Useful Life 10y -&gt; MONTHLY DEPRECIATION Rs416.67 (= Rs5,000/yr, straight-line cost/life). NO salvage/residual-value field on the form, so it does NOT match BRD (cost-salvage)/life = Rs4,500/yr. Salvage not captured; depreciation overstated vs spec.</t>
         </is>
       </c>
       <c r="J18" s="7" t="inlineStr"/>
@@ -24042,7 +24050,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-FW-TEST-001</t>
+          <t>PR-TC-FW-QC-001</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -24052,7 +24060,7 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Date chain: Sent ≤ Received ≤ Reported enforced</t>
+          <t>Fill all 23 stars; total score auto-computes</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -24067,13 +24075,13 @@
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>• Sent = 10-Apr, Received = 5-Apr.</t>
+          <t>• Set all 23 questions to 4 stars (out of 5).</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr"/>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>UI form-fill: set Date of Sample Deposit to Office = 2026-06-15 and to Lab = 2026-06-01 (lab BEFORE office, out of order). NO date-order validation/warning fired (live). Spec expects rejection (Received must be on/after Sent). Confirm save-time enforcement.</t>
+          <t>QC EXISTING uses an "+ Add Item" checklist with a 4-LEVEL rating (0/33/66/100) and AVERAGE SCORE (%), NOT the BRD spec of 23 fixed stars totalling /115 (e.g. 92/115=80%). Items are manually added (not pre-loaded). Confirm whether 23 standard items should pre-load + whether the scoring model should match spec.</t>
         </is>
       </c>
       <c r="J19" s="7" t="inlineStr"/>
@@ -24094,17 +24102,17 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-FW-UP-003</t>
+          <t>PR-TC-FW-TEST-001</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>(not in master — add as test case)</t>
+          <t>17. The 27 Diagnostic Frameworks</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Unit Pricing tab structure inconsistent (TASKS tab, no Log Book)</t>
+          <t>Date chain: Sent ≤ Received ≤ Reported enforced</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
@@ -24112,12 +24120,20 @@
           <t>High</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr"/>
-      <c r="G20" s="7" t="inlineStr"/>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>P1 — High</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>• Sent = 10-Apr, Received = 5-Apr.</t>
+        </is>
+      </c>
       <c r="H20" s="7" t="inlineStr"/>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>Unit Pricing form tabs = DETAILS/EXISTING/REQUIRED/LINE ITEMS/TASKS/RESOURCES — it has a TASKS tab and NO LOG BOOK, unlike the other 26 frameworks (which show LOG BOOK). Contradicts the BRD decision: Task tab removed from framework forms; Log Book remains.</t>
+          <t>UI form-fill: set Date of Sample Deposit to Office = 2026-06-15 and to Lab = 2026-06-01 (lab BEFORE office, out of order). NO date-order validation/warning fired (live). Spec expects rejection (Received must be on/after Sent). Confirm save-time enforcement.</t>
         </is>
       </c>
       <c r="J20" s="7" t="inlineStr"/>
@@ -24138,7 +24154,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-FWC-BPC-002</t>
+          <t>PR-TC-FW-UP-003</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -24148,7 +24164,7 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-FWC-BPC-002 · Business Plan Canvas header has no raw doctype / UUID</t>
+          <t>Unit Pricing tab structure inconsistent (TASKS tab, no Log Book)</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
@@ -24160,6 +24176,50 @@
       <c r="G21" s="7" t="inlineStr"/>
       <c r="H21" s="7" t="inlineStr"/>
       <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>Unit Pricing form tabs = DETAILS/EXISTING/REQUIRED/LINE ITEMS/TASKS/RESOURCES — it has a TASKS tab and NO LOG BOOK, unlike the other 26 frameworks (which show LOG BOOK). Contradicts the BRD decision: Task tab removed from framework forms; Log Book remains.</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr"/>
+      <c r="K21" s="7" t="inlineStr"/>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M21" s="7" t="inlineStr"/>
+      <c r="N21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>BUG-020</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-FWC-BPC-002</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>(not in master — add as test case)</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-FWC-BPC-002 · Business Plan Canvas header has no raw doctype / UUID</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr"/>
+      <c r="G22" s="7" t="inlineStr"/>
+      <c r="H22" s="7" t="inlineStr"/>
+      <c r="I22" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Business Plan Canvas: {"doctype-df-prefix":["DF BUSINESS"]}
 expect.toEqual // deep equality
@@ -24173,50 +24233,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J21" s="7" t="inlineStr">
+      <c r="J22" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Bu-a8fd3-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K21" s="7" t="inlineStr"/>
-      <c r="L21" s="7" t="inlineStr">
+      <c r="K22" s="7" t="inlineStr"/>
+      <c r="L22" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M21" s="7" t="inlineStr"/>
-      <c r="N21" s="7" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>BUG-020</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="M22" s="7" t="inlineStr"/>
+      <c r="N22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>BUG-021</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-BREG-002</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-BREG-002 · Business Registration header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr"/>
-      <c r="G22" s="7" t="inlineStr"/>
-      <c r="H22" s="7" t="inlineStr"/>
-      <c r="I22" s="7" t="inlineStr">
+      <c r="F23" s="7" t="inlineStr"/>
+      <c r="G23" s="7" t="inlineStr"/>
+      <c r="H23" s="7" t="inlineStr"/>
+      <c r="I23" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Business Registration: {"doctype-df-prefix":["DF BUSINESS"]}
 expect.toEqual // deep equality
@@ -24230,50 +24290,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J22" s="7" t="inlineStr">
+      <c r="J23" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Bu-6c730-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K22" s="7" t="inlineStr"/>
-      <c r="L22" s="7" t="inlineStr">
+      <c r="K23" s="7" t="inlineStr"/>
+      <c r="L23" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M22" s="7" t="inlineStr"/>
-      <c r="N22" s="7" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>BUG-021</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="M23" s="7" t="inlineStr"/>
+      <c r="N23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>BUG-022</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-CA-002</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-CA-002 · Customer Analysis header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F23" s="7" t="inlineStr"/>
-      <c r="G23" s="7" t="inlineStr"/>
-      <c r="H23" s="7" t="inlineStr"/>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="F24" s="7" t="inlineStr"/>
+      <c r="G24" s="7" t="inlineStr"/>
+      <c r="H24" s="7" t="inlineStr"/>
+      <c r="I24" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Customer Analysis: {"doctype-df-prefix":["DF CUSTOMER"]}
 expect.toEqual // deep equality
@@ -24287,50 +24347,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J23" s="7" t="inlineStr">
+      <c r="J24" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Cu-6ed58-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K23" s="7" t="inlineStr"/>
-      <c r="L23" s="7" t="inlineStr">
+      <c r="K24" s="7" t="inlineStr"/>
+      <c r="L24" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M23" s="7" t="inlineStr"/>
-      <c r="N23" s="7" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>BUG-022</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="M24" s="7" t="inlineStr"/>
+      <c r="N24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>BUG-023</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-CB-002</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-CB-002 · Capacity Building header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr"/>
-      <c r="G24" s="7" t="inlineStr"/>
-      <c r="H24" s="7" t="inlineStr"/>
-      <c r="I24" s="7" t="inlineStr">
+      <c r="F25" s="7" t="inlineStr"/>
+      <c r="G25" s="7" t="inlineStr"/>
+      <c r="H25" s="7" t="inlineStr"/>
+      <c r="I25" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Capacity Building: {"doctype-df-prefix":["DF CAPACITY"]}
 expect.toEqual // deep equality
@@ -24344,50 +24404,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J24" s="7" t="inlineStr">
+      <c r="J25" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Ca-83199-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K24" s="7" t="inlineStr"/>
-      <c r="L24" s="7" t="inlineStr">
+      <c r="K25" s="7" t="inlineStr"/>
+      <c r="L25" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M24" s="7" t="inlineStr"/>
-      <c r="N24" s="7" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>BUG-023</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="M25" s="7" t="inlineStr"/>
+      <c r="N25" s="7" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>BUG-024</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-DL-002</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-DL-002 · Digital Literacy header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="E26" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F25" s="7" t="inlineStr"/>
-      <c r="G25" s="7" t="inlineStr"/>
-      <c r="H25" s="7" t="inlineStr"/>
-      <c r="I25" s="7" t="inlineStr">
+      <c r="F26" s="7" t="inlineStr"/>
+      <c r="G26" s="7" t="inlineStr"/>
+      <c r="H26" s="7" t="inlineStr"/>
+      <c r="I26" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Digital Literacy: {"doctype-df-prefix":["DF DIGITAL"]}
 expect.toEqual // deep equality
@@ -24401,50 +24461,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J25" s="7" t="inlineStr">
+      <c r="J26" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Di-845ef-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K25" s="7" t="inlineStr"/>
-      <c r="L25" s="7" t="inlineStr">
+      <c r="K26" s="7" t="inlineStr"/>
+      <c r="L26" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M25" s="7" t="inlineStr"/>
-      <c r="N25" s="7" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>BUG-024</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="M26" s="7" t="inlineStr"/>
+      <c r="N26" s="7" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>BUG-025</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-INFR-002</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-INFR-002 · Infrastructure (BE/EE/CE) header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F26" s="7" t="inlineStr"/>
-      <c r="G26" s="7" t="inlineStr"/>
-      <c r="H26" s="7" t="inlineStr"/>
-      <c r="I26" s="7" t="inlineStr">
+      <c r="F27" s="7" t="inlineStr"/>
+      <c r="G27" s="7" t="inlineStr"/>
+      <c r="H27" s="7" t="inlineStr"/>
+      <c r="I27" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Infrastructure: {"doctype-df-prefix":["DF INFRASTRUCTURE"]}
 expect.toEqual // deep equality
@@ -24458,50 +24518,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J26" s="7" t="inlineStr">
+      <c r="J27" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-In-3328d-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K26" s="7" t="inlineStr"/>
-      <c r="L26" s="7" t="inlineStr">
+      <c r="K27" s="7" t="inlineStr"/>
+      <c r="L27" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M26" s="7" t="inlineStr"/>
-      <c r="N26" s="7" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>BUG-025</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="M27" s="7" t="inlineStr"/>
+      <c r="N27" s="7" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>BUG-026</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-LABL-002</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-LABL-002 · Marketing Label header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr"/>
-      <c r="G27" s="7" t="inlineStr"/>
-      <c r="H27" s="7" t="inlineStr"/>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="F28" s="7" t="inlineStr"/>
+      <c r="G28" s="7" t="inlineStr"/>
+      <c r="H28" s="7" t="inlineStr"/>
+      <c r="I28" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Marketing Label: {"doctype-df-prefix":["DF MARKETING"]}
 expect.toEqual // deep equality
@@ -24515,50 +24575,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J27" s="7" t="inlineStr">
+      <c r="J28" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Ma-11834-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K27" s="7" t="inlineStr"/>
-      <c r="L27" s="7" t="inlineStr">
+      <c r="K28" s="7" t="inlineStr"/>
+      <c r="L28" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M27" s="7" t="inlineStr"/>
-      <c r="N27" s="7" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>BUG-026</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="M28" s="7" t="inlineStr"/>
+      <c r="N28" s="7" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>BUG-027</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-ML-002</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-ML-002 · Market Linkage header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr"/>
-      <c r="G28" s="7" t="inlineStr"/>
-      <c r="H28" s="7" t="inlineStr"/>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="F29" s="7" t="inlineStr"/>
+      <c r="G29" s="7" t="inlineStr"/>
+      <c r="H29" s="7" t="inlineStr"/>
+      <c r="I29" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Market Linkage: {"doctype-df-prefix":["DF MARKET"]}
 expect.toEqual // deep equality
@@ -24572,50 +24632,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J28" s="7" t="inlineStr">
+      <c r="J29" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Ma-22f69-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K28" s="7" t="inlineStr"/>
-      <c r="L28" s="7" t="inlineStr">
+      <c r="K29" s="7" t="inlineStr"/>
+      <c r="L29" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M28" s="7" t="inlineStr"/>
-      <c r="N28" s="7" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>BUG-027</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="M29" s="7" t="inlineStr"/>
+      <c r="N29" s="7" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>BUG-028</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-MR-002</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-MR-002 · Market Research header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="E30" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr"/>
-      <c r="G29" s="7" t="inlineStr"/>
-      <c r="H29" s="7" t="inlineStr"/>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="F30" s="7" t="inlineStr"/>
+      <c r="G30" s="7" t="inlineStr"/>
+      <c r="H30" s="7" t="inlineStr"/>
+      <c r="I30" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Market Research: {"doctype-df-prefix":["DF MARKET"]}
 expect.toEqual // deep equality
@@ -24629,50 +24689,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J29" s="7" t="inlineStr">
+      <c r="J30" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Ma-6eb23-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K29" s="7" t="inlineStr"/>
-      <c r="L29" s="7" t="inlineStr">
+      <c r="K30" s="7" t="inlineStr"/>
+      <c r="L30" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M29" s="7" t="inlineStr"/>
-      <c r="N29" s="7" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>BUG-028</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="M30" s="7" t="inlineStr"/>
+      <c r="N30" s="7" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>BUG-029</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PCMP-002</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PCMP-002 · Product Compliance header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="E31" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr"/>
-      <c r="G30" s="7" t="inlineStr"/>
-      <c r="H30" s="7" t="inlineStr"/>
-      <c r="I30" s="7" t="inlineStr">
+      <c r="F31" s="7" t="inlineStr"/>
+      <c r="G31" s="7" t="inlineStr"/>
+      <c r="H31" s="7" t="inlineStr"/>
+      <c r="I31" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Product Compliance: {"doctype-df-prefix":["DF PRODUCT"]}
 expect.toEqual // deep equality
@@ -24686,50 +24746,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J30" s="7" t="inlineStr">
+      <c r="J31" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Pr-be46f-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K30" s="7" t="inlineStr"/>
-      <c r="L30" s="7" t="inlineStr">
+      <c r="K31" s="7" t="inlineStr"/>
+      <c r="L31" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M30" s="7" t="inlineStr"/>
-      <c r="N30" s="7" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>BUG-029</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="M31" s="7" t="inlineStr"/>
+      <c r="N31" s="7" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>BUG-030</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PROM-002</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PROM-002 · Promotional Marketing header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="E32" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr"/>
-      <c r="G31" s="7" t="inlineStr"/>
-      <c r="H31" s="7" t="inlineStr"/>
-      <c r="I31" s="7" t="inlineStr">
+      <c r="F32" s="7" t="inlineStr"/>
+      <c r="G32" s="7" t="inlineStr"/>
+      <c r="H32" s="7" t="inlineStr"/>
+      <c r="I32" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Promotional Marketing: {"doctype-df-prefix":["DF PROMOTIONAL"]}
 expect.toEqual // deep equality
@@ -24743,50 +24803,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J31" s="7" t="inlineStr">
+      <c r="J32" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Pr-d8d12-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K31" s="7" t="inlineStr"/>
-      <c r="L31" s="7" t="inlineStr">
+      <c r="K32" s="7" t="inlineStr"/>
+      <c r="L32" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M31" s="7" t="inlineStr"/>
-      <c r="N31" s="7" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>BUG-030</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="M32" s="7" t="inlineStr"/>
+      <c r="N32" s="7" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>BUG-031</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PROT-002</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D33" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PROT-002 · Product Prototyping header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
+      <c r="E33" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F32" s="7" t="inlineStr"/>
-      <c r="G32" s="7" t="inlineStr"/>
-      <c r="H32" s="7" t="inlineStr"/>
-      <c r="I32" s="7" t="inlineStr">
+      <c r="F33" s="7" t="inlineStr"/>
+      <c r="G33" s="7" t="inlineStr"/>
+      <c r="H33" s="7" t="inlineStr"/>
+      <c r="I33" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Product Prototyping: {"doctype-df-prefix":["DF PRODUCT"]}
 expect.toEqual // deep equality
@@ -24800,50 +24860,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J32" s="7" t="inlineStr">
+      <c r="J33" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Pr-1120e-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K32" s="7" t="inlineStr"/>
-      <c r="L32" s="7" t="inlineStr">
+      <c r="K33" s="7" t="inlineStr"/>
+      <c r="L33" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M32" s="7" t="inlineStr"/>
-      <c r="N32" s="7" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>BUG-031</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="M33" s="7" t="inlineStr"/>
+      <c r="N33" s="7" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>BUG-032</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PTCH-002</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PTCH-002 · Pitch Deck header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
+      <c r="E34" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F33" s="7" t="inlineStr"/>
-      <c r="G33" s="7" t="inlineStr"/>
-      <c r="H33" s="7" t="inlineStr"/>
-      <c r="I33" s="7" t="inlineStr">
+      <c r="F34" s="7" t="inlineStr"/>
+      <c r="G34" s="7" t="inlineStr"/>
+      <c r="H34" s="7" t="inlineStr"/>
+      <c r="I34" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Pitch Deck: {"doctype-df-prefix":["DF PITCH"]}
 expect.toEqual // deep equality
@@ -24857,50 +24917,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J33" s="7" t="inlineStr">
+      <c r="J34" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Pi-fefd5-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K33" s="7" t="inlineStr"/>
-      <c r="L33" s="7" t="inlineStr">
+      <c r="K34" s="7" t="inlineStr"/>
+      <c r="L34" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M33" s="7" t="inlineStr"/>
-      <c r="N33" s="7" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>BUG-032</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="M34" s="7" t="inlineStr"/>
+      <c r="N34" s="7" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>BUG-033</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PTST-002</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PTST-002 · Product Testing header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E34" s="7" t="inlineStr">
+      <c r="E35" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F34" s="7" t="inlineStr"/>
-      <c r="G34" s="7" t="inlineStr"/>
-      <c r="H34" s="7" t="inlineStr"/>
-      <c r="I34" s="7" t="inlineStr">
+      <c r="F35" s="7" t="inlineStr"/>
+      <c r="G35" s="7" t="inlineStr"/>
+      <c r="H35" s="7" t="inlineStr"/>
+      <c r="I35" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Product Testing: {"doctype-df-prefix":["DF PRODUCT"]}
 expect.toEqual // deep equality
@@ -24914,50 +24974,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J34" s="7" t="inlineStr">
+      <c r="J35" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Pr-3e912-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K34" s="7" t="inlineStr"/>
-      <c r="L34" s="7" t="inlineStr">
+      <c r="K35" s="7" t="inlineStr"/>
+      <c r="L35" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M34" s="7" t="inlineStr"/>
-      <c r="N34" s="7" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>BUG-033</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="M35" s="7" t="inlineStr"/>
+      <c r="N35" s="7" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>BUG-034</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-QC-002</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-QC-002 · Quality Control header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F35" s="7" t="inlineStr"/>
-      <c r="G35" s="7" t="inlineStr"/>
-      <c r="H35" s="7" t="inlineStr"/>
-      <c r="I35" s="7" t="inlineStr">
+      <c r="F36" s="7" t="inlineStr"/>
+      <c r="G36" s="7" t="inlineStr"/>
+      <c r="H36" s="7" t="inlineStr"/>
+      <c r="I36" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Quality Control: {"doctype-df-prefix":["DF QUALITY"]}
 expect.toEqual // deep equality
@@ -24971,50 +25031,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J35" s="7" t="inlineStr">
+      <c r="J36" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Qu-ae31c-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K35" s="7" t="inlineStr"/>
-      <c r="L35" s="7" t="inlineStr">
+      <c r="K36" s="7" t="inlineStr"/>
+      <c r="L36" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M35" s="7" t="inlineStr"/>
-      <c r="N35" s="7" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>BUG-034</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="M36" s="7" t="inlineStr"/>
+      <c r="N36" s="7" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>BUG-035</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-SCHM-002</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-SCHM-002 · Schemes &amp; Funding header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F36" s="7" t="inlineStr"/>
-      <c r="G36" s="7" t="inlineStr"/>
-      <c r="H36" s="7" t="inlineStr"/>
-      <c r="I36" s="7" t="inlineStr">
+      <c r="F37" s="7" t="inlineStr"/>
+      <c r="G37" s="7" t="inlineStr"/>
+      <c r="H37" s="7" t="inlineStr"/>
+      <c r="I37" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Schemes &amp; Funding: {"doctype-df-prefix":["DF SCHEMES"]}
 expect.toEqual // deep equality
@@ -25028,50 +25088,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J36" s="7" t="inlineStr">
+      <c r="J37" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Sc-67cb2-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K36" s="7" t="inlineStr"/>
-      <c r="L36" s="7" t="inlineStr">
+      <c r="K37" s="7" t="inlineStr"/>
+      <c r="L37" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M36" s="7" t="inlineStr"/>
-      <c r="N36" s="7" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>BUG-035</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="M37" s="7" t="inlineStr"/>
+      <c r="N37" s="7" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>BUG-036</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-STD-002</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-STD-002 · Standardization header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
+      <c r="E38" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F37" s="7" t="inlineStr"/>
-      <c r="G37" s="7" t="inlineStr"/>
-      <c r="H37" s="7" t="inlineStr"/>
-      <c r="I37" s="7" t="inlineStr">
+      <c r="F38" s="7" t="inlineStr"/>
+      <c r="G38" s="7" t="inlineStr"/>
+      <c r="H38" s="7" t="inlineStr"/>
+      <c r="I38" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Standardization: {"doctype-df-prefix":["DF STANDARDIZATION"]}
 expect.toEqual // deep equality
@@ -25085,50 +25145,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J37" s="7" t="inlineStr">
+      <c r="J38" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-St-b8b93-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K37" s="7" t="inlineStr"/>
-      <c r="L37" s="7" t="inlineStr">
+      <c r="K38" s="7" t="inlineStr"/>
+      <c r="L38" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M37" s="7" t="inlineStr"/>
-      <c r="N37" s="7" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>BUG-036</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="M38" s="7" t="inlineStr"/>
+      <c r="N38" s="7" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>BUG-037</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-UP-002</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
+      <c r="C39" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D38" s="7" t="inlineStr">
+      <c r="D39" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-UP-002 · Unit Pricing header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E38" s="7" t="inlineStr">
+      <c r="E39" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F38" s="7" t="inlineStr"/>
-      <c r="G38" s="7" t="inlineStr"/>
-      <c r="H38" s="7" t="inlineStr"/>
-      <c r="I38" s="7" t="inlineStr">
+      <c r="F39" s="7" t="inlineStr"/>
+      <c r="G39" s="7" t="inlineStr"/>
+      <c r="H39" s="7" t="inlineStr"/>
+      <c r="I39" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Unit Pricing: {"doctype-df-prefix":["DF UNIT"]}
 expect.toEqual // deep equality
@@ -25142,58 +25202,58 @@
 + }</t>
         </is>
       </c>
-      <c r="J38" s="7" t="inlineStr">
+      <c r="J39" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Un-0c652-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K38" s="7" t="inlineStr"/>
-      <c r="L38" s="7" t="inlineStr">
+      <c r="K39" s="7" t="inlineStr"/>
+      <c r="L39" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M38" s="7" t="inlineStr"/>
-      <c r="N38" s="7" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>BUG-037</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="M39" s="7" t="inlineStr"/>
+      <c r="N39" s="7" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>BUG-038</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t>PR-TC-MS-008</t>
         </is>
       </c>
-      <c r="C39" s="7" t="inlineStr">
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>14. Masters &amp; Reference Data</t>
         </is>
       </c>
-      <c r="D39" s="7" t="inlineStr">
+      <c r="D40" s="7" t="inlineStr">
         <is>
           <t>Cohort end date must be after start date</t>
         </is>
       </c>
-      <c r="E39" s="7" t="inlineStr">
+      <c r="E40" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F39" s="7" t="inlineStr">
+      <c r="F40" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G39" s="7" t="inlineStr">
+      <c r="G40" s="7" t="inlineStr">
         <is>
           <t>• Start = 01-Apr-2026, End = 31-Mar-2025.</t>
         </is>
       </c>
-      <c r="H39" s="7" t="inlineStr"/>
-      <c r="I39" s="7" t="inlineStr">
+      <c r="H40" s="7" t="inlineStr"/>
+      <c r="I40" s="7" t="inlineStr">
         <is>
           <t>Error: end-before-start cohort should be rejected
 expect(received).toBeGreaterThanOrEqual(expected)
@@ -25201,59 +25261,59 @@
 Received:    200</t>
         </is>
       </c>
-      <c r="J39" s="7" t="inlineStr"/>
-      <c r="K39" s="7" t="inlineStr"/>
-      <c r="L39" s="7" t="inlineStr">
+      <c r="J40" s="7" t="inlineStr"/>
+      <c r="K40" s="7" t="inlineStr"/>
+      <c r="L40" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M39" s="7" t="inlineStr"/>
-      <c r="N39" s="7" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>BUG-038</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="M40" s="7" t="inlineStr"/>
+      <c r="N40" s="7" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>BUG-039</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>PR-TC-MS-011</t>
         </is>
       </c>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
         <is>
           <t>14. Masters &amp; Reference Data</t>
         </is>
       </c>
-      <c r="D40" s="7" t="inlineStr">
+      <c r="D41" s="7" t="inlineStr">
         <is>
           <t>Seed import: 351 rows from "Final PRIME Rural Task Dropdowns Master.xlsx"</t>
         </is>
       </c>
-      <c r="E40" s="7" t="inlineStr">
+      <c r="E41" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F40" s="7" t="inlineStr">
+      <c r="F41" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G40" s="7" t="inlineStr">
+      <c r="G41" s="7" t="inlineStr">
         <is>
           <t>• Run the seed migration script (or use bulk import) using the canonical xlsx.
 • Verify count = 351.</t>
         </is>
       </c>
-      <c r="H40" s="7" t="inlineStr">
+      <c r="H41" s="7" t="inlineStr">
         <is>
           <t>351 Framework Task Master records exist. Each has: module, framework, task_no, task_name, description, phase. Em-dash phase rows have phase = "Other". Logistic Service has its "Other" row added (was missing in the xlsx).</t>
         </is>
       </c>
-      <c r="I40" s="7" t="inlineStr">
+      <c r="I41" s="7" t="inlineStr">
         <is>
           <t>Error: Framework Task Master doctype should exist
 expect(received).toBe(expected) // Object.is equality
@@ -25261,58 +25321,58 @@
 Received: 404</t>
         </is>
       </c>
-      <c r="J40" s="7" t="inlineStr"/>
-      <c r="K40" s="7" t="inlineStr">
+      <c r="J41" s="7" t="inlineStr"/>
+      <c r="K41" s="7" t="inlineStr">
         <is>
           <t>BRD PR-XC-002b.</t>
         </is>
       </c>
-      <c r="L40" s="7" t="inlineStr">
+      <c r="L41" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M40" s="7" t="inlineStr"/>
-      <c r="N40" s="7" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>BUG-039</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
+      <c r="M41" s="7" t="inlineStr"/>
+      <c r="N41" s="7" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>BUG-040</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>PR-TC-MS-015</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="C42" s="7" t="inlineStr">
         <is>
           <t>14. Masters &amp; Reference Data</t>
         </is>
       </c>
-      <c r="D41" s="7" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
         <is>
           <t>Document types: Aadhaar, PAN, EPIC, Bank Passbook, Photo, Other</t>
         </is>
       </c>
-      <c r="E41" s="7" t="inlineStr">
+      <c r="E42" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F41" s="7" t="inlineStr">
+      <c r="F42" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G41" s="7" t="inlineStr">
+      <c r="G42" s="7" t="inlineStr">
         <is>
           <t>• Masters → Document Master → list.</t>
         </is>
       </c>
-      <c r="H41" s="7" t="inlineStr"/>
-      <c r="I41" s="7" t="inlineStr">
+      <c r="H42" s="7" t="inlineStr"/>
+      <c r="I42" s="7" t="inlineStr">
         <is>
           <t>Error: expected the standard document types (Aadhaar/PAN/EPIC/Bank/Photo/...)
 expect(received).toBeGreaterThanOrEqual(expected)
@@ -25320,58 +25380,58 @@
 Received:    5</t>
         </is>
       </c>
-      <c r="J41" s="7" t="inlineStr"/>
-      <c r="K41" s="7" t="inlineStr"/>
-      <c r="L41" s="7" t="inlineStr">
+      <c r="J42" s="7" t="inlineStr"/>
+      <c r="K42" s="7" t="inlineStr"/>
+      <c r="L42" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M41" s="7" t="inlineStr"/>
-      <c r="N41" s="7" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>BUG-040</t>
-        </is>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="M42" s="7" t="inlineStr"/>
+      <c r="N42" s="7" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>BUG-041</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>PR-TC-MS-020</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C43" s="7" t="inlineStr">
         <is>
           <t>14. Masters &amp; Reference Data</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D43" s="7" t="inlineStr">
         <is>
           <t>19 schemes pre-seeded (MOVCDNER, CGTMSE, NEHHDC, PGS-India Organic, etc.)</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="E43" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F42" s="7" t="inlineStr">
+      <c r="F43" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G42" s="7" t="inlineStr">
+      <c r="G43" s="7" t="inlineStr">
         <is>
           <t>• Open Scheme Master list. Count rows.</t>
         </is>
       </c>
-      <c r="H42" s="7" t="inlineStr">
+      <c r="H43" s="7" t="inlineStr">
         <is>
           <t>19 schemes present per BRD m-schemes. Each has: name, type (Grant / Loan / Subsidy / Certification), eligibility, min/max amount, applicable sectors, interest rate (if loan).</t>
         </is>
       </c>
-      <c r="I42" s="7" t="inlineStr">
+      <c r="I43" s="7" t="inlineStr">
         <is>
           <t>Error: BRD m-schemes expects 19 pre-seeded schemes
 expect(received).toBeGreaterThanOrEqual(expected)
@@ -25379,104 +25439,104 @@
 Received:    3</t>
         </is>
       </c>
-      <c r="J42" s="7" t="inlineStr"/>
-      <c r="K42" s="7" t="inlineStr">
+      <c r="J43" s="7" t="inlineStr"/>
+      <c r="K43" s="7" t="inlineStr">
         <is>
           <t>BRD m-schemes.</t>
         </is>
       </c>
-      <c r="L42" s="7" t="inlineStr">
+      <c r="L43" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M42" s="7" t="inlineStr"/>
-      <c r="N42" s="7" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="7" t="inlineStr">
-        <is>
-          <t>BUG-041</t>
-        </is>
-      </c>
-      <c r="B43" s="7" t="inlineStr">
+      <c r="M43" s="7" t="inlineStr"/>
+      <c r="N43" s="7" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>BUG-042</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>PR-TC-SEC-005</t>
         </is>
       </c>
-      <c r="C43" s="7" t="inlineStr">
+      <c r="C44" s="7" t="inlineStr">
         <is>
           <t>23. Security — OWASP &amp; Beyond</t>
         </is>
       </c>
-      <c r="D43" s="7" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
         <is>
           <t>Content-Security-Policy header set, restricts inline scripts</t>
         </is>
       </c>
-      <c r="E43" s="7" t="inlineStr">
+      <c r="E44" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F43" s="7" t="inlineStr">
+      <c r="F44" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G43" s="7" t="inlineStr">
+      <c r="G44" s="7" t="inlineStr">
         <is>
           <t>• Inspect response headers on /app/.</t>
         </is>
       </c>
-      <c r="H43" s="7" t="inlineStr"/>
-      <c r="I43" s="7" t="inlineStr">
+      <c r="H44" s="7" t="inlineStr"/>
+      <c r="I44" s="7" t="inlineStr">
         <is>
           <t>Error: CSP header should be set
 expect(received).toBeTruthy()
 Received: undefined</t>
         </is>
       </c>
-      <c r="J43" s="7" t="inlineStr"/>
-      <c r="K43" s="7" t="inlineStr"/>
-      <c r="L43" s="7" t="inlineStr">
+      <c r="J44" s="7" t="inlineStr"/>
+      <c r="K44" s="7" t="inlineStr"/>
+      <c r="L44" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M43" s="7" t="inlineStr"/>
-      <c r="N43" s="7" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>BUG-042</t>
-        </is>
-      </c>
-      <c r="B44" s="7" t="inlineStr">
+      <c r="M44" s="7" t="inlineStr"/>
+      <c r="N44" s="7" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>BUG-043</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>PR-TC-UI-LEAK-001</t>
         </is>
       </c>
-      <c r="C44" s="7" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D44" s="7" t="inlineStr">
+      <c r="D45" s="7" t="inlineStr">
         <is>
           <t>PR-TC-UI-LEAK-001 · EP profile shows no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E44" s="7" t="inlineStr">
+      <c r="E45" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F44" s="7" t="inlineStr"/>
-      <c r="G44" s="7" t="inlineStr"/>
-      <c r="H44" s="7" t="inlineStr"/>
-      <c r="I44" s="7" t="inlineStr">
+      <c r="F45" s="7" t="inlineStr"/>
+      <c r="G45" s="7" t="inlineStr"/>
+      <c r="H45" s="7" t="inlineStr"/>
+      <c r="I45" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on EP profile: {"doctype-df-prefix":["DF PROGRESS"]}
 expect.toEqual // deep equality
@@ -25490,50 +25550,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J44" s="7" t="inlineStr">
+      <c r="J45" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\08-ui-no-backend-leak-PR-T-d694f-e-shows-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K44" s="7" t="inlineStr"/>
-      <c r="L44" s="7" t="inlineStr">
+      <c r="K45" s="7" t="inlineStr"/>
+      <c r="L45" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M44" s="7" t="inlineStr"/>
-      <c r="N44" s="7" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="7" t="inlineStr">
-        <is>
-          <t>BUG-043</t>
-        </is>
-      </c>
-      <c r="B45" s="7" t="inlineStr">
+      <c r="M45" s="7" t="inlineStr"/>
+      <c r="N45" s="7" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>BUG-044</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>PR-TC-UI-LEAK-002</t>
         </is>
       </c>
-      <c r="C45" s="7" t="inlineStr">
+      <c r="C46" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D45" s="7" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
         <is>
           <t>PR-TC-UI-LEAK-002 · new EP form header is a friendly label, not the raw doctype</t>
         </is>
       </c>
-      <c r="E45" s="7" t="inlineStr">
+      <c r="E46" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F45" s="7" t="inlineStr"/>
-      <c r="G45" s="7" t="inlineStr"/>
-      <c r="H45" s="7" t="inlineStr"/>
-      <c r="I45" s="7" t="inlineStr">
+      <c r="F46" s="7" t="inlineStr"/>
+      <c r="G46" s="7" t="inlineStr"/>
+      <c r="H46" s="7" t="inlineStr"/>
+      <c r="I46" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on new EP form: {"enterprenur-internal":["Enterprenur"]}
 expect.toEqual // deep equality
@@ -25547,52 +25607,52 @@
 + }</t>
         </is>
       </c>
-      <c r="J45" s="7" t="inlineStr">
+      <c r="J46" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\08-ui-no-backend-leak-PR-T-215c4-y-label-not-the-raw-doctype-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K45" s="7" t="inlineStr"/>
-      <c r="L45" s="7" t="inlineStr">
+      <c r="K46" s="7" t="inlineStr"/>
+      <c r="L46" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M45" s="7" t="inlineStr"/>
-      <c r="N45" s="7" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="7" t="inlineStr">
-        <is>
-          <t>BUG-044</t>
-        </is>
-      </c>
-      <c r="B46" s="7" t="inlineStr">
+      <c r="M46" s="7" t="inlineStr"/>
+      <c r="N46" s="7" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>BUG-045</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
         <is>
           <t>PR-TC-UM-001</t>
         </is>
       </c>
-      <c r="C46" s="7" t="inlineStr">
+      <c r="C47" s="7" t="inlineStr">
         <is>
           <t>13. User Management</t>
         </is>
       </c>
-      <c r="D46" s="7" t="inlineStr">
+      <c r="D47" s="7" t="inlineStr">
         <is>
           <t>Create a new Field Associate user with all required fields</t>
         </is>
       </c>
-      <c r="E46" s="7" t="inlineStr">
+      <c r="E47" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F46" s="7" t="inlineStr">
+      <c r="F47" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G46" s="7" t="inlineStr">
+      <c r="G47" s="7" t="inlineStr">
         <is>
           <t>• Navigate to User Management workspace → "+ New User".
 • Fill: Email = uat-fa-test01@dhwaniris.com, First Name = UAT, Last Name = FA-Test01, Phone = +91 9876543210.
@@ -25602,74 +25662,22 @@
 • Click Save.</t>
         </is>
       </c>
-      <c r="H46" s="7" t="inlineStr">
+      <c r="H47" s="7" t="inlineStr">
         <is>
           <t>Toast: "User created successfully." User row appears in list with status "Active" and "Welcome email sent". Email arrives at the address within 2 min containing a one-time password-set link. Audit log records the creation with timestamp + creator.</t>
         </is>
       </c>
-      <c r="I46" s="7" t="inlineStr">
+      <c r="I47" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: INSERT User → 417: {"exception":"frappe.exceptions.ValidationError: Error syncing User to User Manager: ('User Manager', 'uat-umc-79v3ss@dhwaniris.com', IntegrityError(1062, \"Duplicate entry '[uat]_crud_user' for key 'username'\"))","exc_type":"ValidationError","_exc_source":"dhwani_frappe_base (app)","exc":"[\"Traceback (most recent call last):\\n  File \\\"apps/frappe/frappe/model/base_document.py\\\", line 755, in db_insert\\n    name = frappe.db.sql(\\n    \\t\\\"\\\"\\\"INSERT INTO </t>
         </is>
       </c>
-      <c r="J46" s="7" t="inlineStr"/>
-      <c r="K46" s="7" t="inlineStr">
+      <c r="J47" s="7" t="inlineStr"/>
+      <c r="K47" s="7" t="inlineStr">
         <is>
           <t>BRD: PR-UJ-CTI §User Management.</t>
         </is>
       </c>
-      <c r="L46" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="M46" s="7" t="inlineStr"/>
-      <c r="N46" s="7" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="7" t="inlineStr">
-        <is>
-          <t>BUG-045</t>
-        </is>
-      </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>PR-TC-UM-009</t>
-        </is>
-      </c>
-      <c r="C47" s="7" t="inlineStr">
-        <is>
-          <t>13. User Management</t>
-        </is>
-      </c>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>Email must be lowercase and trimmed before save</t>
-        </is>
-      </c>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F47" s="7" t="inlineStr">
-        <is>
-          <t>P1 — High</t>
-        </is>
-      </c>
-      <c r="G47" s="7" t="inlineStr">
-        <is>
-          <t>• Enter email Test@Dhwaniris.COM (leading/trailing spaces, mixed case).</t>
-        </is>
-      </c>
-      <c r="H47" s="7" t="inlineStr"/>
-      <c r="I47" s="7" t="inlineStr">
-        <is>
-          <t>Error: INSERT User → 417: {"exception":"frappe.exceptions.ValidationError: Error syncing User to User Manager: ('User Manager', 'uat-umn-ztbfos@dhwaniris.com', IntegrityError(1062, \"Duplicate entry '[uat]_norm' for key 'username'\"))","exc_type":"ValidationError","_exc_source":"dhwani_frappe_base (app)","exc":"[\"Traceback (most recent call last):\\n  File \\\"apps/frappe/frappe/model/base_document.py\\\", line 755, in db_insert\\n    name = frappe.db.sql(\\n    \\t\\\"\\\"\\\"INSERT INTO `tab{</t>
-        </is>
-      </c>
-      <c r="J47" s="7" t="inlineStr"/>
-      <c r="K47" s="7" t="inlineStr"/>
       <c r="L47" s="7" t="inlineStr">
         <is>
           <t>Open</t>
@@ -25686,30 +25694,82 @@
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
+          <t>PR-TC-UM-009</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>13. User Management</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>Email must be lowercase and trimmed before save</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>P1 — High</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>• Enter email Test@Dhwaniris.COM (leading/trailing spaces, mixed case).</t>
+        </is>
+      </c>
+      <c r="H48" s="7" t="inlineStr"/>
+      <c r="I48" s="7" t="inlineStr">
+        <is>
+          <t>Error: INSERT User → 417: {"exception":"frappe.exceptions.ValidationError: Error syncing User to User Manager: ('User Manager', 'uat-umn-ztbfos@dhwaniris.com', IntegrityError(1062, \"Duplicate entry '[uat]_norm' for key 'username'\"))","exc_type":"ValidationError","_exc_source":"dhwani_frappe_base (app)","exc":"[\"Traceback (most recent call last):\\n  File \\\"apps/frappe/frappe/model/base_document.py\\\", line 755, in db_insert\\n    name = frappe.db.sql(\\n    \\t\\\"\\\"\\\"INSERT INTO `tab{</t>
+        </is>
+      </c>
+      <c r="J48" s="7" t="inlineStr"/>
+      <c r="K48" s="7" t="inlineStr"/>
+      <c r="L48" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M48" s="7" t="inlineStr"/>
+      <c r="N48" s="7" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>BUG-047</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
           <t>PR-TC-UM-010</t>
         </is>
       </c>
-      <c r="C48" s="7" t="inlineStr">
+      <c r="C49" s="7" t="inlineStr">
         <is>
           <t>13. User Management</t>
         </is>
       </c>
-      <c r="D48" s="7" t="inlineStr">
+      <c r="D49" s="7" t="inlineStr">
         <is>
           <t>Edit user phone, name, block — changes persist</t>
         </is>
       </c>
-      <c r="E48" s="7" t="inlineStr">
+      <c r="E49" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F48" s="7" t="inlineStr">
+      <c r="F49" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G48" s="7" t="inlineStr">
+      <c r="G49" s="7" t="inlineStr">
         <is>
           <t>• Open user uat-fa-test01.
 • Change First Name to "UAT-Updated".
@@ -25718,63 +25778,10 @@
 • Log out / log in as that user.</t>
         </is>
       </c>
-      <c r="H48" s="7" t="inlineStr"/>
-      <c r="I48" s="7" t="inlineStr">
-        <is>
-          <t>Error: INSERT User → 417: {"exception":"frappe.exceptions.ValidationError: Error syncing User to User Manager: ('User Manager', 'uat-ume-1c8bs5@dhwaniris.com', IntegrityError(1062, \"Duplicate entry '[uat]_before' for key 'username'\"))","exc_type":"ValidationError","_exc_source":"dhwani_frappe_base (app)","exc":"[\"Traceback (most recent call last):\\n  File \\\"apps/frappe/frappe/model/base_document.py\\\", line 755, in db_insert\\n    name = frappe.db.sql(\\n    \\t\\\"\\\"\\\"INSERT INTO `ta</t>
-        </is>
-      </c>
-      <c r="J48" s="7" t="inlineStr"/>
-      <c r="K48" s="7" t="inlineStr"/>
-      <c r="L48" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="M48" s="7" t="inlineStr"/>
-      <c r="N48" s="7" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="7" t="inlineStr">
-        <is>
-          <t>BUG-047</t>
-        </is>
-      </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>PR-TC-UM-011</t>
-        </is>
-      </c>
-      <c r="C49" s="7" t="inlineStr">
-        <is>
-          <t>13. User Management</t>
-        </is>
-      </c>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>Deactivate a user — they cannot log in until reactivated</t>
-        </is>
-      </c>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="F49" s="7" t="inlineStr">
-        <is>
-          <t>P0 — Blocker</t>
-        </is>
-      </c>
-      <c r="G49" s="7" t="inlineStr">
-        <is>
-          <t>• Open uat-fa-test01. Set Enabled = No. Save.
-• Sign out, attempt to log in as uat-fa-test01.</t>
-        </is>
-      </c>
       <c r="H49" s="7" t="inlineStr"/>
       <c r="I49" s="7" t="inlineStr">
         <is>
-          <t>Error: INSERT User → 417: {"exception":"frappe.exceptions.ValidationError: Error syncing User to User Manager: ('User Manager', 'uat-umd-0pc24h@dhwaniris.com', IntegrityError(1062, \"Duplicate entry '[uat]_disabled' for key 'username'\"))","exc_type":"ValidationError","_exc_source":"dhwani_frappe_base (app)","exc":"[\"Traceback (most recent call last):\\n  File \\\"apps/frappe/frappe/model/base_document.py\\\", line 755, in db_insert\\n    name = frappe.db.sql(\\n    \\t\\\"\\\"\\\"INSERT INTO `</t>
+          <t>Error: INSERT User → 417: {"exception":"frappe.exceptions.ValidationError: Error syncing User to User Manager: ('User Manager', 'uat-ume-1c8bs5@dhwaniris.com', IntegrityError(1062, \"Duplicate entry '[uat]_before' for key 'username'\"))","exc_type":"ValidationError","_exc_source":"dhwani_frappe_base (app)","exc":"[\"Traceback (most recent call last):\\n  File \\\"apps/frappe/frappe/model/base_document.py\\\", line 755, in db_insert\\n    name = frappe.db.sql(\\n    \\t\\\"\\\"\\\"INSERT INTO `ta</t>
         </is>
       </c>
       <c r="J49" s="7" t="inlineStr"/>
@@ -25795,104 +25802,157 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
+          <t>PR-TC-UM-011</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>13. User Management</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>Deactivate a user — they cannot log in until reactivated</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>P0 — Blocker</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>• Open uat-fa-test01. Set Enabled = No. Save.
+• Sign out, attempt to log in as uat-fa-test01.</t>
+        </is>
+      </c>
+      <c r="H50" s="7" t="inlineStr"/>
+      <c r="I50" s="7" t="inlineStr">
+        <is>
+          <t>Error: INSERT User → 417: {"exception":"frappe.exceptions.ValidationError: Error syncing User to User Manager: ('User Manager', 'uat-umd-0pc24h@dhwaniris.com', IntegrityError(1062, \"Duplicate entry '[uat]_disabled' for key 'username'\"))","exc_type":"ValidationError","_exc_source":"dhwani_frappe_base (app)","exc":"[\"Traceback (most recent call last):\\n  File \\\"apps/frappe/frappe/model/base_document.py\\\", line 755, in db_insert\\n    name = frappe.db.sql(\\n    \\t\\\"\\\"\\\"INSERT INTO `</t>
+        </is>
+      </c>
+      <c r="J50" s="7" t="inlineStr"/>
+      <c r="K50" s="7" t="inlineStr"/>
+      <c r="L50" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M50" s="7" t="inlineStr"/>
+      <c r="N50" s="7" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>BUG-049</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
           <t>PR-TC-XC-003</t>
         </is>
       </c>
-      <c r="C50" s="7" t="inlineStr">
+      <c r="C51" s="7" t="inlineStr">
         <is>
           <t>4. Application Entry &amp; Routing</t>
         </is>
       </c>
-      <c r="D50" s="7" t="inlineStr">
+      <c r="D51" s="7" t="inlineStr">
         <is>
           <t>Deep link to a protected page while logged out preserves the intent</t>
         </is>
       </c>
-      <c r="E50" s="7" t="inlineStr">
+      <c r="E51" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F50" s="7" t="inlineStr">
+      <c r="F51" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G50" s="7" t="inlineStr">
+      <c r="G51" s="7" t="inlineStr">
         <is>
           <t>• Open https://stgprime-rural.dhwaniris.in/app/enterprenur-profile/EP-001 directly.
 • Login redirect fires.
 • Complete login as a user permitted to see that record.</t>
         </is>
       </c>
-      <c r="H50" s="7" t="inlineStr">
+      <c r="H51" s="7" t="inlineStr">
         <is>
           <t>After successful login, user is redirected to the originally requested URL (the EP detail page), not the default landing page. URL parameter (typically redirect-to or next) is preserved through the auth flow.</t>
         </is>
       </c>
-      <c r="I50" s="7" t="inlineStr">
+      <c r="I51" s="7" t="inlineStr">
         <is>
           <t>Error: expect(received).toMatch(expected)
 Expected pattern: /redirect|next|to=/i
 Received string:  "https://stgprime-rural.dhwaniris.in/primerural/login"</t>
         </is>
       </c>
-      <c r="J50" s="7" t="inlineStr">
+      <c r="J51" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\04-entry-PR-TC-XC-ENTRY-·--e9661-t-preserves-redirect-intent-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K50" s="7" t="inlineStr">
+      <c r="K51" s="7" t="inlineStr">
         <is>
           <t>BRD: PR-OV-001 (Auth)</t>
         </is>
       </c>
-      <c r="L50" s="7" t="inlineStr">
+      <c r="L51" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M50" s="7" t="inlineStr"/>
-      <c r="N50" s="7" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="7" t="inlineStr">
-        <is>
-          <t>BUG-049</t>
-        </is>
-      </c>
-      <c r="B51" s="7" t="inlineStr">
+      <c r="M51" s="7" t="inlineStr"/>
+      <c r="N51" s="7" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>BUG-050</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-023</t>
         </is>
       </c>
-      <c r="C51" s="7" t="inlineStr">
+      <c r="C52" s="7" t="inlineStr">
         <is>
           <t>6. Responsive Layout &amp; Screen Sizes</t>
         </is>
       </c>
-      <c r="D51" s="7" t="inlineStr">
+      <c r="D52" s="7" t="inlineStr">
         <is>
           <t>1024×768 (tablet landscape / iPad / Surface): sidebar collapses to icon rail</t>
         </is>
       </c>
-      <c r="E51" s="7" t="inlineStr">
+      <c r="E52" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F51" s="7" t="inlineStr">
+      <c r="F52" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G51" s="7" t="inlineStr">
+      <c r="G52" s="7" t="inlineStr">
         <is>
           <t>• Resize to 1024×768.</t>
         </is>
       </c>
-      <c r="H51" s="7" t="inlineStr"/>
-      <c r="I51" s="7" t="inlineStr">
+      <c r="H52" s="7" t="inlineStr"/>
+      <c r="I52" s="7" t="inlineStr">
         <is>
           <t>Error: at 1024px the sidebar should collapse to an icon rail; width=240
 expect(received).toBeLessThanOrEqual(expected)
@@ -25900,63 +25960,63 @@
 Received:    240</t>
         </is>
       </c>
-      <c r="J51" s="7" t="inlineStr">
+      <c r="J52" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\06-08-10-nonfunctional-PR--f1c18-ollapses-to-icon-rail-64px--sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K51" s="7" t="inlineStr"/>
-      <c r="L51" s="7" t="inlineStr">
+      <c r="K52" s="7" t="inlineStr"/>
+      <c r="L52" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M51" s="7" t="inlineStr"/>
-      <c r="N51" s="7" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="7" t="inlineStr">
-        <is>
-          <t>BUG-050</t>
-        </is>
-      </c>
-      <c r="B52" s="7" t="inlineStr">
+      <c r="M52" s="7" t="inlineStr"/>
+      <c r="N52" s="7" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>BUG-051</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-032</t>
         </is>
       </c>
-      <c r="C52" s="7" t="inlineStr">
+      <c r="C53" s="7" t="inlineStr">
         <is>
           <t>7. Login &amp; Session</t>
         </is>
       </c>
-      <c r="D52" s="7" t="inlineStr">
+      <c r="D53" s="7" t="inlineStr">
         <is>
           <t>Wrong password shows a clear error and does NOT reveal whether the email exists</t>
         </is>
       </c>
-      <c r="E52" s="7" t="inlineStr">
+      <c r="E53" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F52" s="7" t="inlineStr">
+      <c r="F53" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G52" s="7" t="inlineStr">
+      <c r="G53" s="7" t="inlineStr">
         <is>
           <t>• Login form: enter a valid email but wrong password.
 • Submit.</t>
         </is>
       </c>
-      <c r="H52" s="7" t="inlineStr">
+      <c r="H53" s="7" t="inlineStr">
         <is>
           <t>Error displays inline above the form: "Invalid email or password." — generic enough that an attacker cannot enumerate valid emails. The password field is cleared; the email field is preserved. No 500. No password ever echoed back into the field.</t>
         </is>
       </c>
-      <c r="I52" s="7" t="inlineStr">
+      <c r="I53" s="7" t="inlineStr">
         <is>
           <t>Error: login error must be friendly text, not a raw exception class
 expect(locator).not.toContainText(expected) failed
@@ -25970,62 +26030,62 @@
     22 × locator resolved to &lt;div role="alert" class="bg-d</t>
         </is>
       </c>
-      <c r="J52" s="7" t="inlineStr">
+      <c r="J53" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\07-auth-PR-TC-XC-AUTH-·-Em-429a0-neric-error-no-enumeration--sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K52" s="7" t="inlineStr">
+      <c r="K53" s="7" t="inlineStr">
         <is>
           <t>OWASP A07 Auth Failures (do not leak account existence).</t>
         </is>
       </c>
-      <c r="L52" s="7" t="inlineStr">
+      <c r="L53" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M52" s="7" t="inlineStr"/>
-      <c r="N52" s="7" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="7" t="inlineStr">
-        <is>
-          <t>BUG-051</t>
-        </is>
-      </c>
-      <c r="B53" s="7" t="inlineStr">
+      <c r="M53" s="7" t="inlineStr"/>
+      <c r="N53" s="7" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>BUG-052</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-033</t>
         </is>
       </c>
-      <c r="C53" s="7" t="inlineStr">
+      <c r="C54" s="7" t="inlineStr">
         <is>
           <t>7. Login &amp; Session</t>
         </is>
       </c>
-      <c r="D53" s="7" t="inlineStr">
+      <c r="D54" s="7" t="inlineStr">
         <is>
           <t>Non-existent email shows the same generic error as wrong password</t>
         </is>
       </c>
-      <c r="E53" s="7" t="inlineStr">
+      <c r="E54" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F53" s="7" t="inlineStr">
+      <c r="F54" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G53" s="7" t="inlineStr">
+      <c r="G54" s="7" t="inlineStr">
         <is>
           <t>• Submit with email not-a-real-user@example.com and any password.</t>
         </is>
       </c>
-      <c r="H53" s="7" t="inlineStr"/>
-      <c r="I53" s="7" t="inlineStr">
+      <c r="H54" s="7" t="inlineStr"/>
+      <c r="I54" s="7" t="inlineStr">
         <is>
           <t>Error: login error must be friendly text, not a raw exception class
 expect(locator).not.toContainText(expected) failed
@@ -26039,129 +26099,77 @@
     22 × locator resolved to &lt;div role="alert" class="bg-d</t>
         </is>
       </c>
-      <c r="J53" s="7" t="inlineStr">
+      <c r="J54" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\07-auth-PR-TC-XC-AUTH-·-Em-a7adf-ows-identical-generic-error-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K53" s="7" t="inlineStr"/>
-      <c r="L53" s="7" t="inlineStr">
+      <c r="K54" s="7" t="inlineStr"/>
+      <c r="L54" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M53" s="7" t="inlineStr"/>
-      <c r="N53" s="7" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="7" t="inlineStr">
-        <is>
-          <t>BUG-052</t>
-        </is>
-      </c>
-      <c r="B54" s="7" t="inlineStr">
+      <c r="M54" s="7" t="inlineStr"/>
+      <c r="N54" s="7" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>BUG-053</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-052</t>
         </is>
       </c>
-      <c r="C54" s="7" t="inlineStr">
+      <c r="C55" s="7" t="inlineStr">
         <is>
           <t>8. UI / UX Rules — Monsoon Court Compliance</t>
         </is>
       </c>
-      <c r="D54" s="7" t="inlineStr">
+      <c r="D55" s="7" t="inlineStr">
         <is>
           <t>No green and no yellow appear anywhere in the UI</t>
         </is>
       </c>
-      <c r="E54" s="7" t="inlineStr">
+      <c r="E55" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F54" s="7" t="inlineStr">
+      <c r="F55" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G54" s="7" t="inlineStr">
+      <c r="G55" s="7" t="inlineStr">
         <is>
           <t>• Visually scan every page for green / yellow elements.
 • Search the rendered CSS for any colour matching green, yellow, #2ecc71, #f1c40f, similar hexes.</t>
         </is>
       </c>
-      <c r="H54" s="7" t="inlineStr">
+      <c r="H55" s="7" t="inlineStr">
         <is>
           <t>Zero green elements. Success states use teal #0E4D4E. Zero yellow elements. Warning states use terracotta #C26849.</t>
         </is>
       </c>
-      <c r="I54" s="7" t="inlineStr">
+      <c r="I55" s="7" t="inlineStr">
         <is>
           <t>Active Entrepreneurs KPI shows a GREEN check rgb(63,107,58) (hue 114). Monsoon Court forbids green — success must be teal #0E4D4E.</t>
         </is>
       </c>
-      <c r="J54" s="7" t="inlineStr">
+      <c r="J55" s="7" t="inlineStr">
         <is>
           <t>.playwright-mcp/bug-xc052-green-kpi.png</t>
         </is>
       </c>
-      <c r="K54" s="7" t="inlineStr">
+      <c r="K55" s="7" t="inlineStr">
         <is>
           <t>Monsoon Court §2.7 (brand non-negotiables).</t>
         </is>
       </c>
-      <c r="L54" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="M54" s="7" t="inlineStr"/>
-      <c r="N54" s="7" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="7" t="inlineStr">
-        <is>
-          <t>BUG-053</t>
-        </is>
-      </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>PR-TC-XC-054</t>
-        </is>
-      </c>
-      <c r="C55" s="7" t="inlineStr">
-        <is>
-          <t>8. UI / UX Rules — Monsoon Court Compliance</t>
-        </is>
-      </c>
-      <c r="D55" s="7" t="inlineStr">
-        <is>
-          <t>Required-field marker is a terracotta asterisk, not "(required)" text</t>
-        </is>
-      </c>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F55" s="7" t="inlineStr">
-        <is>
-          <t>P1 — High</t>
-        </is>
-      </c>
-      <c r="G55" s="7" t="inlineStr">
-        <is>
-          <t>• Open the EP form. Find a required field (e.g. Entrepreneur Name).</t>
-        </is>
-      </c>
-      <c r="H55" s="7" t="inlineStr"/>
-      <c r="I55" s="7" t="inlineStr">
-        <is>
-          <t>Asterisk on the name label is taupe rgb(107,99,89) (inherits label ink-soft), NOT terracotta #C26849. Marker present but wrong colour.</t>
-        </is>
-      </c>
-      <c r="J55" s="7" t="inlineStr"/>
-      <c r="K55" s="7" t="inlineStr"/>
       <c r="L55" s="7" t="inlineStr">
         <is>
           <t>Open</t>
@@ -26178,17 +26186,17 @@
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-XC-063</t>
+          <t>PR-TC-XC-054</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>9. Accessibility — WCAG 2.2 AA</t>
+          <t>8. UI / UX Rules — Monsoon Court Compliance</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>Form fields have associated labels (axe-core "label" rule passes)</t>
+          <t>Required-field marker is a terracotta asterisk, not "(required)" text</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
@@ -26203,11 +26211,115 @@
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>• Run axe-core on the EP form (via Playwright).</t>
+          <t>• Open the EP form. Find a required field (e.g. Entrepreneur Name).</t>
         </is>
       </c>
       <c r="H56" s="7" t="inlineStr"/>
       <c r="I56" s="7" t="inlineStr">
+        <is>
+          <t>Asterisk on the name label is taupe rgb(107,99,89) (inherits label ink-soft), NOT terracotta #C26849. Marker present but wrong colour.</t>
+        </is>
+      </c>
+      <c r="J56" s="7" t="inlineStr"/>
+      <c r="K56" s="7" t="inlineStr"/>
+      <c r="L56" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M56" s="7" t="inlineStr"/>
+      <c r="N56" s="7" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>BUG-055</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-XC-055</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>8. UI / UX Rules — Monsoon Court Compliance</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>Focus ring is visible on every interactive element on keyboard focus</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>P1 — High</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>• On any form, tab through every interactive element with the keyboard.</t>
+        </is>
+      </c>
+      <c r="H57" s="7" t="inlineStr"/>
+      <c r="I57" s="7" t="inlineStr">
+        <is>
+          <t>Keyboard-Tab focus on buttons + links shows the default UA outline (rgb(16,16,16) auto ~0.67px), NOT the spec 2px terracotta ring with 2px cream offset. Focus IS visible (not an a11y blocker) but does not match the design system.</t>
+        </is>
+      </c>
+      <c r="J57" s="7" t="inlineStr"/>
+      <c r="K57" s="7" t="inlineStr"/>
+      <c r="L57" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M57" s="7" t="inlineStr"/>
+      <c r="N57" s="7" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>BUG-056</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-XC-063</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>9. Accessibility — WCAG 2.2 AA</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>Form fields have associated labels (axe-core "label" rule passes)</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>P1 — High</t>
+        </is>
+      </c>
+      <c r="G58" s="7" t="inlineStr">
+        <is>
+          <t>• Run axe-core on the EP form (via Playwright).</t>
+        </is>
+      </c>
+      <c r="H58" s="7" t="inlineStr"/>
+      <c r="I58" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: label violations: [{"id":"label","n":6}]
 expect(received).toEqual(expected) // deep equality
@@ -26227,58 +26339,58 @@
 +        </t>
         </is>
       </c>
-      <c r="J56" s="7" t="inlineStr">
+      <c r="J58" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\09-a11y-PR-TC-XC-063-·-for-17d03-ssociated-labels-axe-label--sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K56" s="7" t="inlineStr"/>
-      <c r="L56" s="7" t="inlineStr">
+      <c r="K58" s="7" t="inlineStr"/>
+      <c r="L58" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M56" s="7" t="inlineStr"/>
-      <c r="N56" s="7" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="7" t="inlineStr">
-        <is>
-          <t>BUG-055</t>
-        </is>
-      </c>
-      <c r="B57" s="7" t="inlineStr">
+      <c r="M58" s="7" t="inlineStr"/>
+      <c r="N58" s="7" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>BUG-057</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-064</t>
         </is>
       </c>
-      <c r="C57" s="7" t="inlineStr">
+      <c r="C59" s="7" t="inlineStr">
         <is>
           <t>9. Accessibility — WCAG 2.2 AA</t>
         </is>
       </c>
-      <c r="D57" s="7" t="inlineStr">
+      <c r="D59" s="7" t="inlineStr">
         <is>
           <t>Colour contrast meets WCAG AA</t>
         </is>
       </c>
-      <c r="E57" s="7" t="inlineStr">
+      <c r="E59" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F57" s="7" t="inlineStr">
+      <c r="F59" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G57" s="7" t="inlineStr">
+      <c r="G59" s="7" t="inlineStr">
         <is>
           <t>• Run axe-core's contrast check on EP detail, dashboard, framework form.</t>
         </is>
       </c>
-      <c r="H57" s="7" t="inlineStr"/>
-      <c r="I57" s="7" t="inlineStr">
+      <c r="H59" s="7" t="inlineStr"/>
+      <c r="I59" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: contrast violations: [10]
 expect(received).toEqual(expected) // deep equality
@@ -26294,50 +26406,50 @@
 </t>
         </is>
       </c>
-      <c r="J57" s="7" t="inlineStr">
+      <c r="J59" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\09-a11y-PR-TC-XC-064-·-col-8baa1-WCAG-AA-axe-color-contrast--sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K57" s="7" t="inlineStr"/>
-      <c r="L57" s="7" t="inlineStr">
+      <c r="K59" s="7" t="inlineStr"/>
+      <c r="L59" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M57" s="7" t="inlineStr"/>
-      <c r="N57" s="7" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="7" t="inlineStr">
-        <is>
-          <t>BUG-056</t>
-        </is>
-      </c>
-      <c r="B58" s="7" t="inlineStr">
+      <c r="M59" s="7" t="inlineStr"/>
+      <c r="N59" s="7" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>BUG-058</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-064b</t>
         </is>
       </c>
-      <c r="C58" s="7" t="inlineStr">
+      <c r="C60" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D58" s="7" t="inlineStr">
+      <c r="D60" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-064b · landscape colour contrast (WCAG AA)</t>
         </is>
       </c>
-      <c r="E58" s="7" t="inlineStr">
+      <c r="E60" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F58" s="7" t="inlineStr"/>
-      <c r="G58" s="7" t="inlineStr"/>
-      <c r="H58" s="7" t="inlineStr"/>
-      <c r="I58" s="7" t="inlineStr">
+      <c r="F60" s="7" t="inlineStr"/>
+      <c r="G60" s="7" t="inlineStr"/>
+      <c r="H60" s="7" t="inlineStr"/>
+      <c r="I60" s="7" t="inlineStr">
         <is>
           <t>Error: landscape contrast nodes: 4
 expect(received).toEqual(expected) // deep equality
@@ -26352,19 +26464,19 @@
 +     "id": "color-contrast"</t>
         </is>
       </c>
-      <c r="J58" s="7" t="inlineStr">
+      <c r="J60" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\09-a11y-PR-TC-XC-064b-·-landscape-colour-contrast-WCAG-AA--sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K58" s="7" t="inlineStr"/>
-      <c r="L58" s="7" t="inlineStr">
+      <c r="K60" s="7" t="inlineStr"/>
+      <c r="L60" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M58" s="7" t="inlineStr"/>
-      <c r="N58" s="7" t="inlineStr"/>
+      <c r="M60" s="7" t="inlineStr"/>
+      <c r="N60" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bugs Only" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases'!$A$1:$Q$320</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases'!$A$1:$Q$331</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -540,7 +540,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total test cases: 319</t>
+          <t>Total test cases: 330</t>
         </is>
       </c>
     </row>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>236</v>
+        <v>243</v>
       </c>
     </row>
     <row r="7">
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9">
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14">
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>197</v>
+        <v>204</v>
       </c>
     </row>
     <row r="22">
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25">
@@ -783,31 +783,31 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>7. Login &amp; Session</t>
+          <t>19. Dashboards</t>
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>16. Product Profile</t>
+          <t>7. Login &amp; Session</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>19. Dashboards</t>
+          <t>16. Product Profile</t>
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="34">
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>200</v>
+        <v>206</v>
       </c>
     </row>
     <row r="51">
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="53">
@@ -1041,31 +1041,31 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>SM</t>
+          <t>SM/CTI/CTP</t>
         </is>
       </c>
       <c r="B59" s="5" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>CTP</t>
+          <t>SM</t>
         </is>
       </c>
       <c r="B60" s="5" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>SM/CTI/CTP</t>
+          <t>CTP</t>
         </is>
       </c>
       <c r="B61" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62">
@@ -1149,7 +1149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q320"/>
+  <dimension ref="A1:Q331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -6950,11 +6950,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="P87" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="P87" s="8" t="inlineStr"/>
       <c r="Q87" s="7" t="inlineStr"/>
     </row>
     <row r="88">
@@ -13871,11 +13867,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="P185" s="8" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
+      <c r="P185" s="8" t="inlineStr"/>
       <c r="Q185" s="7" t="inlineStr"/>
     </row>
     <row r="186">
@@ -17353,11 +17345,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="P235" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="P235" s="8" t="inlineStr"/>
       <c r="Q235" s="7" t="inlineStr"/>
     </row>
     <row r="236">
@@ -20418,22 +20406,22 @@
     <row r="282">
       <c r="A282" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-NT-001</t>
+          <t>PR-TC-DB-EPS-005</t>
         </is>
       </c>
       <c r="B282" s="7" t="inlineStr">
         <is>
-          <t>20. Notifications</t>
+          <t>19. Dashboards</t>
         </is>
       </c>
       <c r="C282" s="7" t="inlineStr">
         <is>
-          <t>19.5 Intervention Dashboard</t>
+          <t>19.6 Filter Cascade, KPI Correctness &amp; Maps (added from UAT)</t>
         </is>
       </c>
       <c r="D282" s="7" t="inlineStr">
         <is>
-          <t>Final Selection set by CTP fires notification to assigned FA + entire CTP team</t>
+          <t>Sector → Business Basket dropdown cascades (basket filtered by sector)</t>
         </is>
       </c>
       <c r="E282" s="8" t="inlineStr">
@@ -20448,51 +20436,68 @@
       </c>
       <c r="G282" s="8" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="H282" s="8" t="inlineStr">
         <is>
-          <t>P1 — High</t>
+          <t>P0 — Blocker</t>
         </is>
       </c>
       <c r="I282" s="7" t="inlineStr">
         <is>
-          <t>FA/CTP</t>
+          <t>SM/CTI/CTP</t>
         </is>
       </c>
       <c r="J282" s="7" t="inlineStr"/>
       <c r="K282" s="7" t="inlineStr">
         <is>
-          <t>• CTP sets Final Selection = Incubated on EP X.</t>
-        </is>
-      </c>
-      <c r="L282" s="7" t="inlineStr"/>
-      <c r="M282" s="7" t="inlineStr"/>
-      <c r="N282" s="8" t="inlineStr"/>
-      <c r="O282" s="7" t="inlineStr"/>
+          <t>• Select Sector = Food Processing on the Landscape.
+• Open the Business Basket dropdown.</t>
+        </is>
+      </c>
+      <c r="L282" s="7" t="inlineStr">
+        <is>
+          <t>Basket list shows ONLY baskets whose master sector = Food Processing. (Verified UAT: cascade BROKEN — all baskets shown incl. other sectors.)</t>
+        </is>
+      </c>
+      <c r="M282" s="7" t="inlineStr">
+        <is>
+          <t>BRD: dependent filters cascade (Basket.sector → Sector).</t>
+        </is>
+      </c>
+      <c r="N282" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O282" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="P282" s="8" t="inlineStr"/>
       <c r="Q282" s="7" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-NT-002</t>
+          <t>PR-TC-DB-EPS-006</t>
         </is>
       </c>
       <c r="B283" s="7" t="inlineStr">
         <is>
-          <t>20. Notifications</t>
+          <t>19. Dashboards</t>
         </is>
       </c>
       <c r="C283" s="7" t="inlineStr">
         <is>
-          <t>19.5 Intervention Dashboard</t>
+          <t>19.6 Filter Cascade, KPI Correctness &amp; Maps (added from UAT)</t>
         </is>
       </c>
       <c r="D283" s="7" t="inlineStr">
         <is>
-          <t>Designer's brand draft approval triggers notification</t>
+          <t>District → Block cascade filter present on the dashboard</t>
         </is>
       </c>
       <c r="E283" s="8" t="inlineStr">
@@ -20507,51 +20512,75 @@
       </c>
       <c r="G283" s="8" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="H283" s="8" t="inlineStr">
         <is>
-          <t>P1 — High</t>
+          <t>P0 — Blocker</t>
         </is>
       </c>
       <c r="I283" s="7" t="inlineStr">
         <is>
-          <t>DSG</t>
+          <t>SM/CTI/CTP</t>
         </is>
       </c>
       <c r="J283" s="7" t="inlineStr"/>
       <c r="K283" s="7" t="inlineStr">
         <is>
-          <t>• FA + CTP approve draft 2 of a Designer's submission.</t>
-        </is>
-      </c>
-      <c r="L283" s="7" t="inlineStr"/>
-      <c r="M283" s="7" t="inlineStr"/>
-      <c r="N283" s="8" t="inlineStr"/>
-      <c r="O283" s="7" t="inlineStr"/>
-      <c r="P283" s="8" t="inlineStr"/>
+          <t>• Open the Landscape / EP Status Monitor filter row.
+• Look for District + Block filters.</t>
+        </is>
+      </c>
+      <c r="L283" s="7" t="inlineStr">
+        <is>
+          <t>A District filter and a Block filter (cascading: Block.district = selected District) are present. (Verified UAT: NO District/Block filter on Landscape; Status Monitor link dead.)</t>
+        </is>
+      </c>
+      <c r="M283" s="7" t="inlineStr">
+        <is>
+          <t>BRD: District→Block cascade.</t>
+        </is>
+      </c>
+      <c r="N283" s="12" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O283" s="7" t="inlineStr">
+        <is>
+          <t>Error: dashboard should expose a District (and cascading Block) filter
+expect(received).toBe(expected) // Object.is equality
+Expected: true
+Received: false</t>
+        </is>
+      </c>
+      <c r="P283" s="8" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
       <c r="Q283" s="7" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-NT-003</t>
+          <t>PR-TC-DB-EPS-007</t>
         </is>
       </c>
       <c r="B284" s="7" t="inlineStr">
         <is>
-          <t>20. Notifications</t>
+          <t>19. Dashboards</t>
         </is>
       </c>
       <c r="C284" s="7" t="inlineStr">
         <is>
-          <t>19.5 Intervention Dashboard</t>
+          <t>19.6 Filter Cascade, KPI Correctness &amp; Maps (added from UAT)</t>
         </is>
       </c>
       <c r="D284" s="7" t="inlineStr">
         <is>
-          <t>Mentor introduction created — mentor notified</t>
+          <t>Each filter recomputes all KPI counts</t>
         </is>
       </c>
       <c r="E284" s="8" t="inlineStr">
@@ -20571,46 +20600,70 @@
       </c>
       <c r="H284" s="8" t="inlineStr">
         <is>
-          <t>P2 — Medium</t>
+          <t>P1 — High</t>
         </is>
       </c>
       <c r="I284" s="7" t="inlineStr">
         <is>
-          <t>FA</t>
+          <t>SM/CTI/CTP</t>
         </is>
       </c>
       <c r="J284" s="7" t="inlineStr"/>
       <c r="K284" s="7" t="inlineStr">
         <is>
-          <t>• FA creates an Introduction for Mentor X.</t>
-        </is>
-      </c>
-      <c r="L284" s="7" t="inlineStr"/>
-      <c r="M284" s="7" t="inlineStr"/>
-      <c r="N284" s="8" t="inlineStr"/>
-      <c r="O284" s="7" t="inlineStr"/>
-      <c r="P284" s="8" t="inlineStr"/>
+          <t>• Note Total Entrepreneurs.
+• Apply Sector = Food Processing.</t>
+        </is>
+      </c>
+      <c r="L284" s="7" t="inlineStr">
+        <is>
+          <t>KPI counts recompute to the filtered subset (Total 40 → 13 verified). Label switches to Filtered.</t>
+        </is>
+      </c>
+      <c r="M284" s="7" t="inlineStr">
+        <is>
+          <t>BRD: filters recompute KPIs.</t>
+        </is>
+      </c>
+      <c r="N284" s="12" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O284" s="7" t="inlineStr">
+        <is>
+          <t>Error: KPI should recompute on Sector filter (before=-1, after=-1)
+expect(received).toBeLessThan(expected)
+Expected: &lt; -1
+Received:   -1</t>
+        </is>
+      </c>
+      <c r="P284" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="Q284" s="7" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-NT-004</t>
+          <t>PR-TC-DB-VIS-001</t>
         </is>
       </c>
       <c r="B285" s="7" t="inlineStr">
         <is>
-          <t>20. Notifications</t>
+          <t>19. Dashboards</t>
         </is>
       </c>
       <c r="C285" s="7" t="inlineStr">
         <is>
-          <t>19.5 Intervention Dashboard</t>
+          <t>19.6 Filter Cascade, KPI Correctness &amp; Maps (added from UAT)</t>
         </is>
       </c>
       <c r="D285" s="7" t="inlineStr">
         <is>
-          <t>Certificate expiry warning fires at 60 / 30 / 7 days before expiry</t>
+          <t>Village Visits map mode re-scopes KPIs to village-visit GPS pins</t>
         </is>
       </c>
       <c r="E285" s="8" t="inlineStr">
@@ -20625,1522 +20678,1604 @@
       </c>
       <c r="G285" s="8" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="H285" s="8" t="inlineStr">
         <is>
-          <t>P2 — Medium</t>
+          <t>P1 — High</t>
         </is>
       </c>
       <c r="I285" s="7" t="inlineStr">
         <is>
-          <t>FA/CTP</t>
+          <t>SM/CTI/CTP</t>
         </is>
       </c>
       <c r="J285" s="7" t="inlineStr"/>
       <c r="K285" s="7" t="inlineStr">
         <is>
+          <t>• On the Landscape, toggle the map mode to Village Visits.
+• Inspect the KPI cards (esp. GPS Verified).</t>
+        </is>
+      </c>
+      <c r="L285" s="7" t="inlineStr">
+        <is>
+          <t>KPIs reflect village-visit data — GPS Verified shows the village-visit GPS-pin count, not the entrepreneur count. (Verified UAT: KPIs stay entrepreneur-scoped — finding.)</t>
+        </is>
+      </c>
+      <c r="M285" s="7" t="inlineStr">
+        <is>
+          <t>BRD/req: GPS Verified per active map mode.</t>
+        </is>
+      </c>
+      <c r="N285" s="12" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O285" s="7" t="inlineStr">
+        <is>
+          <t>TimeoutError: locator.click: Timeout 15000ms exceeded.
+Call log:
+  - waiting for locator('main button:has-text("Village Visits")')</t>
+        </is>
+      </c>
+      <c r="P285" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q285" s="7" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-DB-NAV-001</t>
+        </is>
+      </c>
+      <c r="B286" s="7" t="inlineStr">
+        <is>
+          <t>19. Dashboards</t>
+        </is>
+      </c>
+      <c r="C286" s="7" t="inlineStr">
+        <is>
+          <t>19.6 Filter Cascade, KPI Correctness &amp; Maps (added from UAT)</t>
+        </is>
+      </c>
+      <c r="D286" s="7" t="inlineStr">
+        <is>
+          <t>Status Monitor sidebar link routes to the EP status view</t>
+        </is>
+      </c>
+      <c r="E286" s="8" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F286" s="9" t="inlineStr">
+        <is>
+          <t>AUTO</t>
+        </is>
+      </c>
+      <c r="G286" s="8" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="H286" s="8" t="inlineStr">
+        <is>
+          <t>P1 — High</t>
+        </is>
+      </c>
+      <c r="I286" s="7" t="inlineStr">
+        <is>
+          <t>SM/CTI/CTP</t>
+        </is>
+      </c>
+      <c r="J286" s="7" t="inlineStr"/>
+      <c r="K286" s="7" t="inlineStr">
+        <is>
+          <t>• Click the "Status Monitor" item in the sidebar.</t>
+        </is>
+      </c>
+      <c r="L286" s="7" t="inlineStr">
+        <is>
+          <t>Navigates to the EP Status Monitor view. (Verified UAT: link has href=null, does not navigate — dead link.)</t>
+        </is>
+      </c>
+      <c r="M286" s="7" t="inlineStr">
+        <is>
+          <t>BRD: Status Monitor nav.</t>
+        </is>
+      </c>
+      <c r="N286" s="12" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O286" s="7" t="inlineStr">
+        <is>
+          <t>Sidebar 'Status Monitor' link has href=null and clicking it does not navigate (dead/placeholder link). The District/Block-filtered status-monitor view appears not to be wired in the /primerural SPA.</t>
+        </is>
+      </c>
+      <c r="P286" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q286" s="7" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-DB-MAP-001</t>
+        </is>
+      </c>
+      <c r="B287" s="7" t="inlineStr">
+        <is>
+          <t>19. Dashboards</t>
+        </is>
+      </c>
+      <c r="C287" s="7" t="inlineStr">
+        <is>
+          <t>19.6 Filter Cascade, KPI Correctness &amp; Maps (added from UAT)</t>
+        </is>
+      </c>
+      <c r="D287" s="7" t="inlineStr">
+        <is>
+          <t>Geo coordinates captured; count cross-checks GPS-Verified KPI</t>
+        </is>
+      </c>
+      <c r="E287" s="8" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F287" s="9" t="inlineStr">
+        <is>
+          <t>AUTO</t>
+        </is>
+      </c>
+      <c r="G287" s="8" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="H287" s="8" t="inlineStr">
+        <is>
+          <t>P1 — High</t>
+        </is>
+      </c>
+      <c r="I287" s="7" t="inlineStr">
+        <is>
+          <t>SM/CTI/CTP</t>
+        </is>
+      </c>
+      <c r="J287" s="7" t="inlineStr"/>
+      <c r="K287" s="7" t="inlineStr">
+        <is>
+          <t>• Read EP.location (Geolocation) values via API.
+• Compare count-with-coords to the GPS-Verified KPI.</t>
+        </is>
+      </c>
+      <c r="L287" s="7" t="inlineStr">
+        <is>
+          <t>EPs with a captured location &gt; 0; GPS-Verified KPI ≤ count-with-coords. (Obs: KPI=6 vs 12 with location — confirm GPS-only vs incl. centroid.)</t>
+        </is>
+      </c>
+      <c r="M287" s="7" t="inlineStr">
+        <is>
+          <t>BRD: geo-tag capture.</t>
+        </is>
+      </c>
+      <c r="N287" s="12" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O287" s="7" t="inlineStr">
+        <is>
+          <t>Error: GPS-Verified KPI should be a positive count
+expect(received).toBeGreaterThan(expected)
+Expected: &gt; 0
+Received:   -1</t>
+        </is>
+      </c>
+      <c r="P287" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q287" s="7" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-DB-MAP-002</t>
+        </is>
+      </c>
+      <c r="B288" s="7" t="inlineStr">
+        <is>
+          <t>19. Dashboards</t>
+        </is>
+      </c>
+      <c r="C288" s="7" t="inlineStr">
+        <is>
+          <t>19.6 Filter Cascade, KPI Correctness &amp; Maps (added from UAT)</t>
+        </is>
+      </c>
+      <c r="D288" s="7" t="inlineStr">
+        <is>
+          <t>Landscape map renders (Leaflet canvas + tiles)</t>
+        </is>
+      </c>
+      <c r="E288" s="8" t="inlineStr">
+        <is>
+          <t>UI / UX</t>
+        </is>
+      </c>
+      <c r="F288" s="10" t="inlineStr">
+        <is>
+          <t>SEMI</t>
+        </is>
+      </c>
+      <c r="G288" s="8" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="H288" s="8" t="inlineStr">
+        <is>
+          <t>P1 — High</t>
+        </is>
+      </c>
+      <c r="I288" s="7" t="inlineStr">
+        <is>
+          <t>SM/CTI/CTP</t>
+        </is>
+      </c>
+      <c r="J288" s="7" t="inlineStr"/>
+      <c r="K288" s="7" t="inlineStr">
+        <is>
+          <t>• Open the Landscape.
+• Inspect the map container.</t>
+        </is>
+      </c>
+      <c r="L288" s="7" t="inlineStr">
+        <is>
+          <t>Leaflet map renders with base tiles + canvas renderer (pins drawn on canvas). (Verified pass.)</t>
+        </is>
+      </c>
+      <c r="M288" s="7" t="inlineStr">
+        <is>
+          <t>BRD: map renders.</t>
+        </is>
+      </c>
+      <c r="N288" s="12" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O288" s="7" t="inlineStr">
+        <is>
+          <t>Error: Leaflet map container present
+expect(received).toBe(expected) // Object.is equality
+Expected: true
+Received: false</t>
+        </is>
+      </c>
+      <c r="P288" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q288" s="7" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-DB-MAP-003</t>
+        </is>
+      </c>
+      <c r="B289" s="7" t="inlineStr">
+        <is>
+          <t>19. Dashboards</t>
+        </is>
+      </c>
+      <c r="C289" s="7" t="inlineStr">
+        <is>
+          <t>19.6 Filter Cascade, KPI Correctness &amp; Maps (added from UAT)</t>
+        </is>
+      </c>
+      <c r="D289" s="7" t="inlineStr">
+        <is>
+          <t>Meghalaya boundary overlay rendered</t>
+        </is>
+      </c>
+      <c r="E289" s="8" t="inlineStr">
+        <is>
+          <t>UI / UX</t>
+        </is>
+      </c>
+      <c r="F289" s="10" t="inlineStr">
+        <is>
+          <t>SEMI</t>
+        </is>
+      </c>
+      <c r="G289" s="8" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="H289" s="8" t="inlineStr">
+        <is>
+          <t>P1 — High</t>
+        </is>
+      </c>
+      <c r="I289" s="7" t="inlineStr">
+        <is>
+          <t>SM/CTI/CTP</t>
+        </is>
+      </c>
+      <c r="J289" s="7" t="inlineStr"/>
+      <c r="K289" s="7" t="inlineStr">
+        <is>
+          <t>• Open the Landscape map.</t>
+        </is>
+      </c>
+      <c r="L289" s="7" t="inlineStr">
+        <is>
+          <t>State boundary overlay (svg/canvas) renders around Meghalaya. (Verified pass.)</t>
+        </is>
+      </c>
+      <c r="M289" s="7" t="inlineStr">
+        <is>
+          <t>BRD: map boundaries.</t>
+        </is>
+      </c>
+      <c r="N289" s="12" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O289" s="7" t="inlineStr">
+        <is>
+          <t>Error: state boundary overlay (svg path or canvas) should render
+expect(received).toBe(expected) // Object.is equality
+Expected: true
+Received: false</t>
+        </is>
+      </c>
+      <c r="P289" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q289" s="7" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-DB-MAP-004</t>
+        </is>
+      </c>
+      <c r="B290" s="7" t="inlineStr">
+        <is>
+          <t>19. Dashboards</t>
+        </is>
+      </c>
+      <c r="C290" s="7" t="inlineStr">
+        <is>
+          <t>19.6 Filter Cascade, KPI Correctness &amp; Maps (added from UAT)</t>
+        </is>
+      </c>
+      <c r="D290" s="7" t="inlineStr">
+        <is>
+          <t>Block-level drill-down works on the map</t>
+        </is>
+      </c>
+      <c r="E290" s="8" t="inlineStr">
+        <is>
+          <t>UI / UX</t>
+        </is>
+      </c>
+      <c r="F290" s="10" t="inlineStr">
+        <is>
+          <t>SEMI</t>
+        </is>
+      </c>
+      <c r="G290" s="8" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="H290" s="8" t="inlineStr">
+        <is>
+          <t>P1 — High</t>
+        </is>
+      </c>
+      <c r="I290" s="7" t="inlineStr">
+        <is>
+          <t>SM/CTI/CTP</t>
+        </is>
+      </c>
+      <c r="J290" s="7" t="inlineStr"/>
+      <c r="K290" s="7" t="inlineStr">
+        <is>
+          <t>• Click / zoom a district on the map.</t>
+        </is>
+      </c>
+      <c r="L290" s="7" t="inlineStr">
+        <is>
+          <t>Map drills down to block-level detail. (Canvas — manual/visual verification pending.)</t>
+        </is>
+      </c>
+      <c r="M290" s="7" t="inlineStr">
+        <is>
+          <t>BRD: drill down to block level.</t>
+        </is>
+      </c>
+      <c r="N290" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O290" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="P290" s="8" t="inlineStr"/>
+      <c r="Q290" s="7" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-DB-MAP-005</t>
+        </is>
+      </c>
+      <c r="B291" s="7" t="inlineStr">
+        <is>
+          <t>19. Dashboards</t>
+        </is>
+      </c>
+      <c r="C291" s="7" t="inlineStr">
+        <is>
+          <t>19.6 Filter Cascade, KPI Correctness &amp; Maps (added from UAT)</t>
+        </is>
+      </c>
+      <c r="D291" s="7" t="inlineStr">
+        <is>
+          <t>Captured coordinates fall within Meghalaya bounds</t>
+        </is>
+      </c>
+      <c r="E291" s="8" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="F291" s="9" t="inlineStr">
+        <is>
+          <t>AUTO</t>
+        </is>
+      </c>
+      <c r="G291" s="8" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="H291" s="8" t="inlineStr">
+        <is>
+          <t>P0 — Blocker</t>
+        </is>
+      </c>
+      <c r="I291" s="7" t="inlineStr">
+        <is>
+          <t>SM/CTI/CTP</t>
+        </is>
+      </c>
+      <c r="J291" s="7" t="inlineStr"/>
+      <c r="K291" s="7" t="inlineStr">
+        <is>
+          <t>• Read EP.location GeoJSON coords.
+• Check each lat/lng against Meghalaya bounds (lat 25.0–26.2, lng 89.8–92.9).</t>
+        </is>
+      </c>
+      <c r="L291" s="7" t="inlineStr">
+        <is>
+          <t>All coords within Meghalaya. (Verified UAT: only 1 of parseable coords in-state; default Mountain View CA + Delhi + malformed GeoJSON — finding.)</t>
+        </is>
+      </c>
+      <c r="M291" s="7" t="inlineStr">
+        <is>
+          <t>BRD: coordinate validation / map boundaries.</t>
+        </is>
+      </c>
+      <c r="N291" s="12" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O291" s="7" t="inlineStr">
+        <is>
+          <t>Error: all geo-tags must be valid Meghalaya coords; 5 out-of-bounds (37.422,-122.084 ; 28.452,77.072 ; 28.623,77.218) + 6 malformed GeoJSON
+expect(received).toBe(expected) // Object.is equality
+Expected: 0
+Received: 11</t>
+        </is>
+      </c>
+      <c r="P291" s="8" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="Q291" s="7" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-DB-MAP-006</t>
+        </is>
+      </c>
+      <c r="B292" s="7" t="inlineStr">
+        <is>
+          <t>19. Dashboards</t>
+        </is>
+      </c>
+      <c r="C292" s="7" t="inlineStr">
+        <is>
+          <t>19.6 Filter Cascade, KPI Correctness &amp; Maps (added from UAT)</t>
+        </is>
+      </c>
+      <c r="D292" s="7" t="inlineStr">
+        <is>
+          <t>Village Visits map mode plots village pins</t>
+        </is>
+      </c>
+      <c r="E292" s="8" t="inlineStr">
+        <is>
+          <t>UI / UX</t>
+        </is>
+      </c>
+      <c r="F292" s="10" t="inlineStr">
+        <is>
+          <t>SEMI</t>
+        </is>
+      </c>
+      <c r="G292" s="8" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="H292" s="8" t="inlineStr">
+        <is>
+          <t>P2 — Medium</t>
+        </is>
+      </c>
+      <c r="I292" s="7" t="inlineStr">
+        <is>
+          <t>SM/CTI/CTP</t>
+        </is>
+      </c>
+      <c r="J292" s="7" t="inlineStr"/>
+      <c r="K292" s="7" t="inlineStr">
+        <is>
+          <t>• Toggle map to Village Visits.</t>
+        </is>
+      </c>
+      <c r="L292" s="7" t="inlineStr">
+        <is>
+          <t>Village-visit pins render on the map. (Canvas — manual/visual verification pending.)</t>
+        </is>
+      </c>
+      <c r="M292" s="7" t="inlineStr">
+        <is>
+          <t>BRD: village visit pins.</t>
+        </is>
+      </c>
+      <c r="N292" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O292" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="P292" s="8" t="inlineStr"/>
+      <c r="Q292" s="7" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-NT-001</t>
+        </is>
+      </c>
+      <c r="B293" s="7" t="inlineStr">
+        <is>
+          <t>20. Notifications</t>
+        </is>
+      </c>
+      <c r="C293" s="7" t="inlineStr">
+        <is>
+          <t>19.6 Filter Cascade, KPI Correctness &amp; Maps (added from UAT)</t>
+        </is>
+      </c>
+      <c r="D293" s="7" t="inlineStr">
+        <is>
+          <t>Final Selection set by CTP fires notification to assigned FA + entire CTP team</t>
+        </is>
+      </c>
+      <c r="E293" s="8" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F293" s="9" t="inlineStr">
+        <is>
+          <t>AUTO</t>
+        </is>
+      </c>
+      <c r="G293" s="8" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="H293" s="8" t="inlineStr">
+        <is>
+          <t>P1 — High</t>
+        </is>
+      </c>
+      <c r="I293" s="7" t="inlineStr">
+        <is>
+          <t>FA/CTP</t>
+        </is>
+      </c>
+      <c r="J293" s="7" t="inlineStr"/>
+      <c r="K293" s="7" t="inlineStr">
+        <is>
+          <t>• CTP sets Final Selection = Incubated on EP X.</t>
+        </is>
+      </c>
+      <c r="L293" s="7" t="inlineStr"/>
+      <c r="M293" s="7" t="inlineStr"/>
+      <c r="N293" s="8" t="inlineStr"/>
+      <c r="O293" s="7" t="inlineStr"/>
+      <c r="P293" s="8" t="inlineStr"/>
+      <c r="Q293" s="7" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-NT-002</t>
+        </is>
+      </c>
+      <c r="B294" s="7" t="inlineStr">
+        <is>
+          <t>20. Notifications</t>
+        </is>
+      </c>
+      <c r="C294" s="7" t="inlineStr">
+        <is>
+          <t>19.6 Filter Cascade, KPI Correctness &amp; Maps (added from UAT)</t>
+        </is>
+      </c>
+      <c r="D294" s="7" t="inlineStr">
+        <is>
+          <t>Designer's brand draft approval triggers notification</t>
+        </is>
+      </c>
+      <c r="E294" s="8" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F294" s="9" t="inlineStr">
+        <is>
+          <t>AUTO</t>
+        </is>
+      </c>
+      <c r="G294" s="8" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="H294" s="8" t="inlineStr">
+        <is>
+          <t>P1 — High</t>
+        </is>
+      </c>
+      <c r="I294" s="7" t="inlineStr">
+        <is>
+          <t>DSG</t>
+        </is>
+      </c>
+      <c r="J294" s="7" t="inlineStr"/>
+      <c r="K294" s="7" t="inlineStr">
+        <is>
+          <t>• FA + CTP approve draft 2 of a Designer's submission.</t>
+        </is>
+      </c>
+      <c r="L294" s="7" t="inlineStr"/>
+      <c r="M294" s="7" t="inlineStr"/>
+      <c r="N294" s="8" t="inlineStr"/>
+      <c r="O294" s="7" t="inlineStr"/>
+      <c r="P294" s="8" t="inlineStr"/>
+      <c r="Q294" s="7" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-NT-003</t>
+        </is>
+      </c>
+      <c r="B295" s="7" t="inlineStr">
+        <is>
+          <t>20. Notifications</t>
+        </is>
+      </c>
+      <c r="C295" s="7" t="inlineStr">
+        <is>
+          <t>19.6 Filter Cascade, KPI Correctness &amp; Maps (added from UAT)</t>
+        </is>
+      </c>
+      <c r="D295" s="7" t="inlineStr">
+        <is>
+          <t>Mentor introduction created — mentor notified</t>
+        </is>
+      </c>
+      <c r="E295" s="8" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F295" s="9" t="inlineStr">
+        <is>
+          <t>AUTO</t>
+        </is>
+      </c>
+      <c r="G295" s="8" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="H295" s="8" t="inlineStr">
+        <is>
+          <t>P2 — Medium</t>
+        </is>
+      </c>
+      <c r="I295" s="7" t="inlineStr">
+        <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="J295" s="7" t="inlineStr"/>
+      <c r="K295" s="7" t="inlineStr">
+        <is>
+          <t>• FA creates an Introduction for Mentor X.</t>
+        </is>
+      </c>
+      <c r="L295" s="7" t="inlineStr"/>
+      <c r="M295" s="7" t="inlineStr"/>
+      <c r="N295" s="8" t="inlineStr"/>
+      <c r="O295" s="7" t="inlineStr"/>
+      <c r="P295" s="8" t="inlineStr"/>
+      <c r="Q295" s="7" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-NT-004</t>
+        </is>
+      </c>
+      <c r="B296" s="7" t="inlineStr">
+        <is>
+          <t>20. Notifications</t>
+        </is>
+      </c>
+      <c r="C296" s="7" t="inlineStr">
+        <is>
+          <t>19.6 Filter Cascade, KPI Correctness &amp; Maps (added from UAT)</t>
+        </is>
+      </c>
+      <c r="D296" s="7" t="inlineStr">
+        <is>
+          <t>Certificate expiry warning fires at 60 / 30 / 7 days before expiry</t>
+        </is>
+      </c>
+      <c r="E296" s="8" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F296" s="9" t="inlineStr">
+        <is>
+          <t>AUTO</t>
+        </is>
+      </c>
+      <c r="G296" s="8" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="H296" s="8" t="inlineStr">
+        <is>
+          <t>P2 — Medium</t>
+        </is>
+      </c>
+      <c r="I296" s="7" t="inlineStr">
+        <is>
+          <t>FA/CTP</t>
+        </is>
+      </c>
+      <c r="J296" s="7" t="inlineStr"/>
+      <c r="K296" s="7" t="inlineStr">
+        <is>
           <t>• Set FSSAI cert expiry = 30 days from today.
 • Run scheduled job.</t>
         </is>
       </c>
-      <c r="L285" s="7" t="inlineStr"/>
-      <c r="M285" s="7" t="inlineStr"/>
-      <c r="N285" s="8" t="inlineStr"/>
-      <c r="O285" s="7" t="inlineStr"/>
-      <c r="P285" s="8" t="inlineStr"/>
-      <c r="Q285" s="7" t="inlineStr"/>
-    </row>
-    <row r="286">
-      <c r="A286" s="7" t="inlineStr">
+      <c r="L296" s="7" t="inlineStr"/>
+      <c r="M296" s="7" t="inlineStr"/>
+      <c r="N296" s="8" t="inlineStr"/>
+      <c r="O296" s="7" t="inlineStr"/>
+      <c r="P296" s="8" t="inlineStr"/>
+      <c r="Q296" s="7" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="7" t="inlineStr">
         <is>
           <t>PR-TC-NT-005</t>
         </is>
       </c>
-      <c r="B286" s="7" t="inlineStr">
+      <c r="B297" s="7" t="inlineStr">
         <is>
           <t>20. Notifications</t>
         </is>
       </c>
-      <c r="C286" s="7" t="inlineStr">
-        <is>
-          <t>19.5 Intervention Dashboard</t>
-        </is>
-      </c>
-      <c r="D286" s="7" t="inlineStr">
+      <c r="C297" s="7" t="inlineStr">
+        <is>
+          <t>19.6 Filter Cascade, KPI Correctness &amp; Maps (added from UAT)</t>
+        </is>
+      </c>
+      <c r="D297" s="7" t="inlineStr">
         <is>
           <t>Bell icon shows unread count badge</t>
         </is>
       </c>
-      <c r="E286" s="8" t="inlineStr">
+      <c r="E297" s="8" t="inlineStr">
         <is>
           <t>UI / UX</t>
         </is>
       </c>
-      <c r="F286" s="10" t="inlineStr">
+      <c r="F297" s="10" t="inlineStr">
         <is>
           <t>SEMI</t>
         </is>
       </c>
-      <c r="G286" s="8" t="inlineStr">
+      <c r="G297" s="8" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="H286" s="8" t="inlineStr">
+      <c r="H297" s="8" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="I286" s="7" t="inlineStr">
+      <c r="I297" s="7" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="J286" s="7" t="inlineStr"/>
-      <c r="K286" s="7" t="inlineStr">
+      <c r="J297" s="7" t="inlineStr"/>
+      <c r="K297" s="7" t="inlineStr">
         <is>
           <t>• Generate 5 notifications. Check sidebar bell.</t>
         </is>
       </c>
-      <c r="L286" s="7" t="inlineStr"/>
-      <c r="M286" s="7" t="inlineStr"/>
-      <c r="N286" s="8" t="inlineStr"/>
-      <c r="O286" s="7" t="inlineStr"/>
-      <c r="P286" s="8" t="inlineStr"/>
-      <c r="Q286" s="7" t="inlineStr"/>
-    </row>
-    <row r="287">
-      <c r="A287" s="7" t="inlineStr">
+      <c r="L297" s="7" t="inlineStr"/>
+      <c r="M297" s="7" t="inlineStr"/>
+      <c r="N297" s="8" t="inlineStr"/>
+      <c r="O297" s="7" t="inlineStr"/>
+      <c r="P297" s="8" t="inlineStr"/>
+      <c r="Q297" s="7" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="7" t="inlineStr">
         <is>
           <t>PR-TC-NT-006</t>
         </is>
       </c>
-      <c r="B287" s="7" t="inlineStr">
+      <c r="B298" s="7" t="inlineStr">
         <is>
           <t>20. Notifications</t>
         </is>
       </c>
-      <c r="C287" s="7" t="inlineStr">
-        <is>
-          <t>19.5 Intervention Dashboard</t>
-        </is>
-      </c>
-      <c r="D287" s="7" t="inlineStr">
+      <c r="C298" s="7" t="inlineStr">
+        <is>
+          <t>19.6 Filter Cascade, KPI Correctness &amp; Maps (added from UAT)</t>
+        </is>
+      </c>
+      <c r="D298" s="7" t="inlineStr">
         <is>
           <t>Click notification → deep-links to relevant record</t>
         </is>
       </c>
-      <c r="E287" s="8" t="inlineStr">
+      <c r="E298" s="8" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="F287" s="9" t="inlineStr">
+      <c r="F298" s="9" t="inlineStr">
         <is>
           <t>AUTO</t>
         </is>
       </c>
-      <c r="G287" s="8" t="inlineStr">
+      <c r="G298" s="8" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="H287" s="8" t="inlineStr">
+      <c r="H298" s="8" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="I287" s="7" t="inlineStr">
+      <c r="I298" s="7" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="J287" s="7" t="inlineStr"/>
-      <c r="K287" s="7" t="inlineStr">
+      <c r="J298" s="7" t="inlineStr"/>
+      <c r="K298" s="7" t="inlineStr">
         <is>
           <t>• Click any notification.</t>
         </is>
       </c>
-      <c r="L287" s="7" t="inlineStr"/>
-      <c r="M287" s="7" t="inlineStr"/>
-      <c r="N287" s="8" t="inlineStr"/>
-      <c r="O287" s="7" t="inlineStr"/>
-      <c r="P287" s="8" t="inlineStr"/>
-      <c r="Q287" s="7" t="inlineStr"/>
-    </row>
-    <row r="288">
-      <c r="A288" s="7" t="inlineStr">
+      <c r="L298" s="7" t="inlineStr"/>
+      <c r="M298" s="7" t="inlineStr"/>
+      <c r="N298" s="8" t="inlineStr"/>
+      <c r="O298" s="7" t="inlineStr"/>
+      <c r="P298" s="8" t="inlineStr"/>
+      <c r="Q298" s="7" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="7" t="inlineStr">
         <is>
           <t>PR-TC-NT-007</t>
         </is>
       </c>
-      <c r="B288" s="7" t="inlineStr">
+      <c r="B299" s="7" t="inlineStr">
         <is>
           <t>20. Notifications</t>
         </is>
       </c>
-      <c r="C288" s="7" t="inlineStr">
-        <is>
-          <t>19.5 Intervention Dashboard</t>
-        </is>
-      </c>
-      <c r="D288" s="7" t="inlineStr">
+      <c r="C299" s="7" t="inlineStr">
+        <is>
+          <t>19.6 Filter Cascade, KPI Correctness &amp; Maps (added from UAT)</t>
+        </is>
+      </c>
+      <c r="D299" s="7" t="inlineStr">
         <is>
           <t>Core Team IT receive-only on notifications (cannot configure triggers)</t>
         </is>
       </c>
-      <c r="E288" s="8" t="inlineStr">
+      <c r="E299" s="8" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="F288" s="9" t="inlineStr">
+      <c r="F299" s="9" t="inlineStr">
         <is>
           <t>AUTO</t>
         </is>
       </c>
-      <c r="G288" s="8" t="inlineStr">
+      <c r="G299" s="8" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="H288" s="8" t="inlineStr">
+      <c r="H299" s="8" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="I288" s="7" t="inlineStr">
+      <c r="I299" s="7" t="inlineStr">
         <is>
           <t>CTI</t>
         </is>
       </c>
-      <c r="J288" s="7" t="inlineStr"/>
-      <c r="K288" s="7" t="inlineStr">
+      <c r="J299" s="7" t="inlineStr"/>
+      <c r="K299" s="7" t="inlineStr">
         <is>
           <t>• CTI tries to access Notification Settings.</t>
         </is>
       </c>
-      <c r="L288" s="7" t="inlineStr">
+      <c r="L299" s="7" t="inlineStr">
         <is>
           <t>Settings UI not visible / 403. SM only.</t>
         </is>
       </c>
-      <c r="M288" s="7" t="inlineStr">
+      <c r="M299" s="7" t="inlineStr">
         <is>
           <t>BRD Decision: CTI receive-only on notifications.</t>
         </is>
       </c>
-      <c r="N288" s="8" t="inlineStr"/>
-      <c r="O288" s="7" t="inlineStr"/>
-      <c r="P288" s="8" t="inlineStr"/>
-      <c r="Q288" s="7" t="inlineStr"/>
-    </row>
-    <row r="289">
-      <c r="A289" s="7" t="inlineStr">
+      <c r="N299" s="8" t="inlineStr"/>
+      <c r="O299" s="7" t="inlineStr"/>
+      <c r="P299" s="8" t="inlineStr"/>
+      <c r="Q299" s="7" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="7" t="inlineStr">
         <is>
           <t>PR-TC-API-001</t>
         </is>
       </c>
-      <c r="B289" s="7" t="inlineStr">
+      <c r="B300" s="7" t="inlineStr">
         <is>
           <t>21. API Layer</t>
         </is>
       </c>
-      <c r="C289" s="7" t="inlineStr">
+      <c r="C300" s="7" t="inlineStr">
         <is>
           <t>21.1 Authentication</t>
         </is>
       </c>
-      <c r="D289" s="7" t="inlineStr">
+      <c r="D300" s="7" t="inlineStr">
         <is>
           <t>Valid API token returns logged_user</t>
         </is>
       </c>
-      <c r="E289" s="8" t="inlineStr">
+      <c r="E300" s="8" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="F289" s="9" t="inlineStr">
+      <c r="F300" s="9" t="inlineStr">
         <is>
           <t>AUTO</t>
         </is>
       </c>
-      <c r="G289" s="8" t="inlineStr">
+      <c r="G300" s="8" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="H289" s="8" t="inlineStr">
+      <c r="H300" s="8" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="I289" s="7" t="inlineStr">
+      <c r="I300" s="7" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="J289" s="7" t="inlineStr"/>
-      <c r="K289" s="7" t="inlineStr">
+      <c r="J300" s="7" t="inlineStr"/>
+      <c r="K300" s="7" t="inlineStr">
         <is>
           <t>• GET /api/method/frappe.auth.get_logged_user with token.</t>
         </is>
       </c>
-      <c r="L289" s="7" t="inlineStr"/>
-      <c r="M289" s="7" t="inlineStr"/>
-      <c r="N289" s="9" t="inlineStr">
+      <c r="L300" s="7" t="inlineStr"/>
+      <c r="M300" s="7" t="inlineStr"/>
+      <c r="N300" s="9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="O289" s="7" t="inlineStr">
+      <c r="O300" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="P289" s="8" t="inlineStr"/>
-      <c r="Q289" s="7" t="inlineStr"/>
-    </row>
-    <row r="290">
-      <c r="A290" s="7" t="inlineStr">
+      <c r="P300" s="8" t="inlineStr"/>
+      <c r="Q300" s="7" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="7" t="inlineStr">
         <is>
           <t>PR-TC-API-002</t>
         </is>
       </c>
-      <c r="B290" s="7" t="inlineStr">
+      <c r="B301" s="7" t="inlineStr">
         <is>
           <t>21. API Layer</t>
         </is>
       </c>
-      <c r="C290" s="7" t="inlineStr">
+      <c r="C301" s="7" t="inlineStr">
         <is>
           <t>21.1 Authentication</t>
         </is>
       </c>
-      <c r="D290" s="7" t="inlineStr">
+      <c r="D301" s="7" t="inlineStr">
         <is>
           <t>Missing / invalid token returns 401, not 200 with empty data</t>
         </is>
       </c>
-      <c r="E290" s="8" t="inlineStr">
+      <c r="E301" s="8" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="F290" s="9" t="inlineStr">
+      <c r="F301" s="9" t="inlineStr">
         <is>
           <t>AUTO</t>
         </is>
       </c>
-      <c r="G290" s="8" t="inlineStr">
+      <c r="G301" s="8" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="H290" s="8" t="inlineStr">
+      <c r="H301" s="8" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="I290" s="7" t="inlineStr">
+      <c r="I301" s="7" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="J290" s="7" t="inlineStr"/>
-      <c r="K290" s="7" t="inlineStr">
+      <c r="J301" s="7" t="inlineStr"/>
+      <c r="K301" s="7" t="inlineStr">
         <is>
           <t>• Call with no Authorization header.
 • Call with token wrong:wrong.</t>
         </is>
       </c>
-      <c r="L290" s="7" t="inlineStr"/>
-      <c r="M290" s="7" t="inlineStr"/>
-      <c r="N290" s="9" t="inlineStr">
+      <c r="L301" s="7" t="inlineStr"/>
+      <c r="M301" s="7" t="inlineStr"/>
+      <c r="N301" s="9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="O290" s="7" t="inlineStr">
+      <c r="O301" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="P290" s="8" t="inlineStr"/>
-      <c r="Q290" s="7" t="inlineStr"/>
-    </row>
-    <row r="291">
-      <c r="A291" s="7" t="inlineStr">
+      <c r="P301" s="8" t="inlineStr"/>
+      <c r="Q301" s="7" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="7" t="inlineStr">
         <is>
           <t>PR-TC-API-003</t>
         </is>
       </c>
-      <c r="B291" s="7" t="inlineStr">
+      <c r="B302" s="7" t="inlineStr">
         <is>
           <t>21. API Layer</t>
         </is>
       </c>
-      <c r="C291" s="7" t="inlineStr">
+      <c r="C302" s="7" t="inlineStr">
         <is>
           <t>21.1 Authentication</t>
         </is>
       </c>
-      <c r="D291" s="7" t="inlineStr">
+      <c r="D302" s="7" t="inlineStr">
         <is>
           <t>API key for a disabled user is rejected</t>
         </is>
       </c>
-      <c r="E291" s="8" t="inlineStr">
+      <c r="E302" s="8" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="F291" s="9" t="inlineStr">
+      <c r="F302" s="9" t="inlineStr">
         <is>
           <t>AUTO</t>
         </is>
       </c>
-      <c r="G291" s="8" t="inlineStr">
+      <c r="G302" s="8" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="H291" s="8" t="inlineStr">
+      <c r="H302" s="8" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="I291" s="7" t="inlineStr">
+      <c r="I302" s="7" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="J291" s="7" t="inlineStr"/>
-      <c r="K291" s="7" t="inlineStr">
+      <c r="J302" s="7" t="inlineStr"/>
+      <c r="K302" s="7" t="inlineStr">
         <is>
           <t>• Disable a user. Use their pre-existing API key.</t>
         </is>
       </c>
-      <c r="L291" s="7" t="inlineStr"/>
-      <c r="M291" s="7" t="inlineStr"/>
-      <c r="N291" s="13" t="inlineStr">
+      <c r="L302" s="7" t="inlineStr"/>
+      <c r="M302" s="7" t="inlineStr"/>
+      <c r="N302" s="13" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="O291" s="7" t="inlineStr">
+      <c r="O302" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="P291" s="8" t="inlineStr"/>
-      <c r="Q291" s="7" t="inlineStr"/>
-    </row>
-    <row r="292">
-      <c r="A292" s="7" t="inlineStr">
+      <c r="P302" s="8" t="inlineStr"/>
+      <c r="Q302" s="7" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="7" t="inlineStr">
         <is>
           <t>PR-TC-API-004</t>
         </is>
       </c>
-      <c r="B292" s="7" t="inlineStr">
+      <c r="B303" s="7" t="inlineStr">
         <is>
           <t>21. API Layer</t>
         </is>
       </c>
-      <c r="C292" s="7" t="inlineStr">
+      <c r="C303" s="7" t="inlineStr">
         <is>
           <t>21.2 REST CRUD</t>
         </is>
       </c>
-      <c r="D292" s="7" t="inlineStr">
+      <c r="D303" s="7" t="inlineStr">
         <is>
           <t>POST /api/resource/Enterprenur Profile creates record</t>
         </is>
       </c>
-      <c r="E292" s="8" t="inlineStr">
+      <c r="E303" s="8" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="F292" s="9" t="inlineStr">
+      <c r="F303" s="9" t="inlineStr">
         <is>
           <t>AUTO</t>
         </is>
       </c>
-      <c r="G292" s="8" t="inlineStr">
+      <c r="G303" s="8" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="H292" s="8" t="inlineStr">
+      <c r="H303" s="8" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="I292" s="7" t="inlineStr">
+      <c r="I303" s="7" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="J292" s="7" t="inlineStr"/>
-      <c r="K292" s="7" t="inlineStr">
+      <c r="J303" s="7" t="inlineStr"/>
+      <c r="K303" s="7" t="inlineStr">
         <is>
           <t>• POST with body containing required fields.</t>
         </is>
       </c>
-      <c r="L292" s="7" t="inlineStr"/>
-      <c r="M292" s="7" t="inlineStr"/>
-      <c r="N292" s="9" t="inlineStr">
+      <c r="L303" s="7" t="inlineStr"/>
+      <c r="M303" s="7" t="inlineStr"/>
+      <c r="N303" s="9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="O292" s="7" t="inlineStr">
+      <c r="O303" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="P292" s="8" t="inlineStr"/>
-      <c r="Q292" s="7" t="inlineStr"/>
-    </row>
-    <row r="293">
-      <c r="A293" s="7" t="inlineStr">
+      <c r="P303" s="8" t="inlineStr"/>
+      <c r="Q303" s="7" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="7" t="inlineStr">
         <is>
           <t>PR-TC-API-005</t>
         </is>
       </c>
-      <c r="B293" s="7" t="inlineStr">
+      <c r="B304" s="7" t="inlineStr">
         <is>
           <t>21. API Layer</t>
         </is>
       </c>
-      <c r="C293" s="7" t="inlineStr">
+      <c r="C304" s="7" t="inlineStr">
         <is>
           <t>21.2 REST CRUD</t>
         </is>
       </c>
-      <c r="D293" s="7" t="inlineStr">
+      <c r="D304" s="7" t="inlineStr">
         <is>
           <t>POST with missing required field returns 4xx with fields error map</t>
         </is>
       </c>
-      <c r="E293" s="8" t="inlineStr">
+      <c r="E304" s="8" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="F293" s="9" t="inlineStr">
+      <c r="F304" s="9" t="inlineStr">
         <is>
           <t>AUTO</t>
         </is>
       </c>
-      <c r="G293" s="8" t="inlineStr">
+      <c r="G304" s="8" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="H293" s="8" t="inlineStr">
+      <c r="H304" s="8" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="I293" s="7" t="inlineStr">
+      <c r="I304" s="7" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="J293" s="7" t="inlineStr"/>
-      <c r="K293" s="7" t="inlineStr">
+      <c r="J304" s="7" t="inlineStr"/>
+      <c r="K304" s="7" t="inlineStr">
         <is>
           <t>• POST EP without enterprenur_name.</t>
         </is>
       </c>
-      <c r="L293" s="7" t="inlineStr"/>
-      <c r="M293" s="7" t="inlineStr"/>
-      <c r="N293" s="9" t="inlineStr">
+      <c r="L304" s="7" t="inlineStr"/>
+      <c r="M304" s="7" t="inlineStr"/>
+      <c r="N304" s="9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="O293" s="7" t="inlineStr">
+      <c r="O304" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="P293" s="8" t="inlineStr"/>
-      <c r="Q293" s="7" t="inlineStr"/>
-    </row>
-    <row r="294">
-      <c r="A294" s="7" t="inlineStr">
+      <c r="P304" s="8" t="inlineStr"/>
+      <c r="Q304" s="7" t="inlineStr"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="7" t="inlineStr">
         <is>
           <t>PR-TC-API-006</t>
         </is>
       </c>
-      <c r="B294" s="7" t="inlineStr">
+      <c r="B305" s="7" t="inlineStr">
         <is>
           <t>21. API Layer</t>
         </is>
       </c>
-      <c r="C294" s="7" t="inlineStr">
+      <c r="C305" s="7" t="inlineStr">
         <is>
           <t>21.2 REST CRUD</t>
         </is>
       </c>
-      <c r="D294" s="7" t="inlineStr">
+      <c r="D305" s="7" t="inlineStr">
         <is>
           <t>PUT update only the fields sent (partial update)</t>
         </is>
       </c>
-      <c r="E294" s="8" t="inlineStr">
+      <c r="E305" s="8" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="F294" s="9" t="inlineStr">
+      <c r="F305" s="9" t="inlineStr">
         <is>
           <t>AUTO</t>
         </is>
       </c>
-      <c r="G294" s="8" t="inlineStr">
+      <c r="G305" s="8" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="H294" s="8" t="inlineStr">
+      <c r="H305" s="8" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="I294" s="7" t="inlineStr">
+      <c r="I305" s="7" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="J294" s="7" t="inlineStr"/>
-      <c r="K294" s="7" t="inlineStr">
+      <c r="J305" s="7" t="inlineStr"/>
+      <c r="K305" s="7" t="inlineStr">
         <is>
           <t>• PUT with just phone_number changed.</t>
         </is>
       </c>
-      <c r="L294" s="7" t="inlineStr"/>
-      <c r="M294" s="7" t="inlineStr"/>
-      <c r="N294" s="9" t="inlineStr">
+      <c r="L305" s="7" t="inlineStr"/>
+      <c r="M305" s="7" t="inlineStr"/>
+      <c r="N305" s="9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="O294" s="7" t="inlineStr">
+      <c r="O305" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="P294" s="8" t="inlineStr"/>
-      <c r="Q294" s="7" t="inlineStr"/>
-    </row>
-    <row r="295">
-      <c r="A295" s="7" t="inlineStr">
+      <c r="P305" s="8" t="inlineStr"/>
+      <c r="Q305" s="7" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="7" t="inlineStr">
         <is>
           <t>PR-TC-API-007</t>
         </is>
       </c>
-      <c r="B295" s="7" t="inlineStr">
+      <c r="B306" s="7" t="inlineStr">
         <is>
           <t>21. API Layer</t>
         </is>
       </c>
-      <c r="C295" s="7" t="inlineStr">
+      <c r="C306" s="7" t="inlineStr">
         <is>
           <t>21.2 REST CRUD</t>
         </is>
       </c>
-      <c r="D295" s="7" t="inlineStr">
+      <c r="D306" s="7" t="inlineStr">
         <is>
           <t>DELETE of FK-referenced record returns LinkExists</t>
         </is>
       </c>
-      <c r="E295" s="8" t="inlineStr">
+      <c r="E306" s="8" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="F295" s="9" t="inlineStr">
+      <c r="F306" s="9" t="inlineStr">
         <is>
           <t>AUTO</t>
         </is>
       </c>
-      <c r="G295" s="8" t="inlineStr">
+      <c r="G306" s="8" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="H295" s="8" t="inlineStr">
+      <c r="H306" s="8" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="I295" s="7" t="inlineStr">
+      <c r="I306" s="7" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="J295" s="7" t="inlineStr"/>
-      <c r="K295" s="7" t="inlineStr">
+      <c r="J306" s="7" t="inlineStr"/>
+      <c r="K306" s="7" t="inlineStr">
         <is>
           <t>• DELETE a sector that's linked to EP records.</t>
         </is>
       </c>
-      <c r="L295" s="7" t="inlineStr"/>
-      <c r="M295" s="7" t="inlineStr"/>
-      <c r="N295" s="9" t="inlineStr">
+      <c r="L306" s="7" t="inlineStr"/>
+      <c r="M306" s="7" t="inlineStr"/>
+      <c r="N306" s="9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="O295" s="7" t="inlineStr">
+      <c r="O306" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="P295" s="8" t="inlineStr"/>
-      <c r="Q295" s="7" t="inlineStr"/>
-    </row>
-    <row r="296">
-      <c r="A296" s="7" t="inlineStr">
+      <c r="P306" s="8" t="inlineStr"/>
+      <c r="Q306" s="7" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="7" t="inlineStr">
         <is>
           <t>PR-TC-API-008</t>
         </is>
       </c>
-      <c r="B296" s="7" t="inlineStr">
+      <c r="B307" s="7" t="inlineStr">
         <is>
           <t>21. API Layer</t>
         </is>
       </c>
-      <c r="C296" s="7" t="inlineStr">
+      <c r="C307" s="7" t="inlineStr">
         <is>
           <t>21.3 CSRF / SameSite</t>
         </is>
       </c>
-      <c r="D296" s="7" t="inlineStr">
+      <c r="D307" s="7" t="inlineStr">
         <is>
           <t>Cookie-auth POST without X-Frappe-CSRF-Token is rejected</t>
         </is>
       </c>
-      <c r="E296" s="8" t="inlineStr">
+      <c r="E307" s="8" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="F296" s="9" t="inlineStr">
+      <c r="F307" s="9" t="inlineStr">
         <is>
           <t>AUTO</t>
         </is>
       </c>
-      <c r="G296" s="8" t="inlineStr">
+      <c r="G307" s="8" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="H296" s="8" t="inlineStr">
+      <c r="H307" s="8" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="I296" s="7" t="inlineStr">
+      <c r="I307" s="7" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="J296" s="7" t="inlineStr"/>
-      <c r="K296" s="7" t="inlineStr">
+      <c r="J307" s="7" t="inlineStr"/>
+      <c r="K307" s="7" t="inlineStr">
         <is>
           <t>• From a cross-origin page, POST /api/method/frappe.client.set_value using the user's cookie.</t>
         </is>
       </c>
-      <c r="L296" s="7" t="inlineStr"/>
-      <c r="M296" s="7" t="inlineStr"/>
-      <c r="N296" s="12" t="inlineStr">
+      <c r="L307" s="7" t="inlineStr"/>
+      <c r="M307" s="7" t="inlineStr"/>
+      <c r="N307" s="12" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="O296" s="7" t="inlineStr">
+      <c r="O307" s="7" t="inlineStr">
         <is>
           <t>Error: expect(received).toMatch(expected)
 Expected pattern: /CSRF/i
 Received string:  "{\"session_expired\":1,\"exc_type\":\"PermissionError\",\"_server_messages\":\"[\\\"{\\\\\\\"message\\\\\\\":\\\\\\\"You are not permitted to access this resource. Login to accessFunction &lt;strong&gt;frappe.client.insert&lt;/strong&gt; is not whitelisted.\\\\\\\",\\\\\\\"as_table\\\\\\\":false,\\\\\\\"title\\\\\\\":\\\\\\\"Method Not Allowed\\\\\\\",\\\\\\\"indicator\\\\\\\":\\\\\\\"red\\\\\\\",\\\\\\\"raise_exception\</t>
         </is>
       </c>
-      <c r="P296" s="8" t="inlineStr">
+      <c r="P307" s="8" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="Q296" s="7" t="inlineStr"/>
-    </row>
-    <row r="297">
-      <c r="A297" s="7" t="inlineStr">
-        <is>
-          <t>PR-TC-API-009</t>
-        </is>
-      </c>
-      <c r="B297" s="7" t="inlineStr">
-        <is>
-          <t>21. API Layer</t>
-        </is>
-      </c>
-      <c r="C297" s="7" t="inlineStr">
-        <is>
-          <t>21.4 Rate limiting / DoS protection</t>
-        </is>
-      </c>
-      <c r="D297" s="7" t="inlineStr">
-        <is>
-          <t>1,000 requests/minute from same IP throttled</t>
-        </is>
-      </c>
-      <c r="E297" s="8" t="inlineStr">
-        <is>
-          <t>Security</t>
-        </is>
-      </c>
-      <c r="F297" s="9" t="inlineStr">
-        <is>
-          <t>AUTO</t>
-        </is>
-      </c>
-      <c r="G297" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="H297" s="8" t="inlineStr">
-        <is>
-          <t>P1 — High</t>
-        </is>
-      </c>
-      <c r="I297" s="7" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="J297" s="7" t="inlineStr"/>
-      <c r="K297" s="7" t="inlineStr">
-        <is>
-          <t>• Hammer GET /api/method/get_logged_user 1k times in 60 s.</t>
-        </is>
-      </c>
-      <c r="L297" s="7" t="inlineStr"/>
-      <c r="M297" s="7" t="inlineStr"/>
-      <c r="N297" s="13" t="inlineStr">
-        <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="O297" s="7" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="P297" s="8" t="inlineStr"/>
-      <c r="Q297" s="7" t="inlineStr"/>
-    </row>
-    <row r="298">
-      <c r="A298" s="7" t="inlineStr">
-        <is>
-          <t>PR-TC-API-010</t>
-        </is>
-      </c>
-      <c r="B298" s="7" t="inlineStr">
-        <is>
-          <t>21. API Layer</t>
-        </is>
-      </c>
-      <c r="C298" s="7" t="inlineStr">
-        <is>
-          <t>21.5 Custom whitelisted endpoints</t>
-        </is>
-      </c>
-      <c r="D298" s="7" t="inlineStr">
-        <is>
-          <t>networking_mentoring.save_introduction endpoint works</t>
-        </is>
-      </c>
-      <c r="E298" s="8" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="F298" s="9" t="inlineStr">
-        <is>
-          <t>AUTO</t>
-        </is>
-      </c>
-      <c r="G298" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="H298" s="8" t="inlineStr">
-        <is>
-          <t>P1 — High</t>
-        </is>
-      </c>
-      <c r="I298" s="7" t="inlineStr">
-        <is>
-          <t>FA/CTP</t>
-        </is>
-      </c>
-      <c r="J298" s="7" t="inlineStr"/>
-      <c r="K298" s="7" t="inlineStr">
-        <is>
-          <t>• POST /api/method/prime_rural.networking_mentoring.save_introduction with valid payload.</t>
-        </is>
-      </c>
-      <c r="L298" s="7" t="inlineStr"/>
-      <c r="M298" s="7" t="inlineStr"/>
-      <c r="N298" s="13" t="inlineStr">
-        <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="O298" s="7" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="P298" s="8" t="inlineStr"/>
-      <c r="Q298" s="7" t="inlineStr"/>
-    </row>
-    <row r="299">
-      <c r="A299" s="7" t="inlineStr">
-        <is>
-          <t>PR-TC-API-011</t>
-        </is>
-      </c>
-      <c r="B299" s="7" t="inlineStr">
-        <is>
-          <t>21. API Layer</t>
-        </is>
-      </c>
-      <c r="C299" s="7" t="inlineStr">
-        <is>
-          <t>21.5 Custom whitelisted endpoints</t>
-        </is>
-      </c>
-      <c r="D299" s="7" t="inlineStr">
-        <is>
-          <t>Error response shape conforms to FrappeError contract</t>
-        </is>
-      </c>
-      <c r="E299" s="8" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="F299" s="9" t="inlineStr">
-        <is>
-          <t>AUTO</t>
-        </is>
-      </c>
-      <c r="G299" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="H299" s="8" t="inlineStr">
-        <is>
-          <t>P2 — Medium</t>
-        </is>
-      </c>
-      <c r="I299" s="7" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="J299" s="7" t="inlineStr"/>
-      <c r="K299" s="7" t="inlineStr">
-        <is>
-          <t>• Trigger a validation error.</t>
-        </is>
-      </c>
-      <c r="L299" s="7" t="inlineStr"/>
-      <c r="M299" s="7" t="inlineStr"/>
-      <c r="N299" s="9" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="O299" s="7" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="P299" s="8" t="inlineStr"/>
-      <c r="Q299" s="7" t="inlineStr"/>
-    </row>
-    <row r="300">
-      <c r="A300" s="7" t="inlineStr">
-        <is>
-          <t>PR-TC-DB-001</t>
-        </is>
-      </c>
-      <c r="B300" s="7" t="inlineStr">
-        <is>
-          <t>22. Database Layer</t>
-        </is>
-      </c>
-      <c r="C300" s="7" t="inlineStr">
-        <is>
-          <t>21.5 Custom whitelisted endpoints</t>
-        </is>
-      </c>
-      <c r="D300" s="7" t="inlineStr">
-        <is>
-          <t>Foreign key constraints exist on Link fields</t>
-        </is>
-      </c>
-      <c r="E300" s="8" t="inlineStr">
-        <is>
-          <t>Database</t>
-        </is>
-      </c>
-      <c r="F300" s="9" t="inlineStr">
-        <is>
-          <t>AUTO</t>
-        </is>
-      </c>
-      <c r="G300" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="H300" s="8" t="inlineStr">
-        <is>
-          <t>P1 — High</t>
-        </is>
-      </c>
-      <c r="I300" s="7" t="inlineStr">
-        <is>
-          <t>SM</t>
-        </is>
-      </c>
-      <c r="J300" s="7" t="inlineStr"/>
-      <c r="K300" s="7" t="inlineStr">
-        <is>
-          <t>• Check tabEnterprenur Profile.block_FK references tabBlock.</t>
-        </is>
-      </c>
-      <c r="L300" s="7" t="inlineStr"/>
-      <c r="M300" s="7" t="inlineStr"/>
-      <c r="N300" s="9" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="O300" s="7" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="P300" s="8" t="inlineStr"/>
-      <c r="Q300" s="7" t="inlineStr"/>
-    </row>
-    <row r="301">
-      <c r="A301" s="7" t="inlineStr">
-        <is>
-          <t>PR-TC-DB-002</t>
-        </is>
-      </c>
-      <c r="B301" s="7" t="inlineStr">
-        <is>
-          <t>22. Database Layer</t>
-        </is>
-      </c>
-      <c r="C301" s="7" t="inlineStr">
-        <is>
-          <t>21.5 Custom whitelisted endpoints</t>
-        </is>
-      </c>
-      <c r="D301" s="7" t="inlineStr">
-        <is>
-          <t>UNIQUE constraint on enterprenur_name (within cohort)</t>
-        </is>
-      </c>
-      <c r="E301" s="8" t="inlineStr">
-        <is>
-          <t>Database</t>
-        </is>
-      </c>
-      <c r="F301" s="9" t="inlineStr">
-        <is>
-          <t>AUTO</t>
-        </is>
-      </c>
-      <c r="G301" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="H301" s="8" t="inlineStr">
-        <is>
-          <t>P1 — High</t>
-        </is>
-      </c>
-      <c r="I301" s="7" t="inlineStr">
-        <is>
-          <t>SM</t>
-        </is>
-      </c>
-      <c r="J301" s="7" t="inlineStr"/>
-      <c r="K301" s="7" t="inlineStr">
-        <is>
-          <t>• SHOW CREATE TABLE tabEnterprenur Profile.</t>
-        </is>
-      </c>
-      <c r="L301" s="7" t="inlineStr"/>
-      <c r="M301" s="7" t="inlineStr"/>
-      <c r="N301" s="13" t="inlineStr">
-        <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="O301" s="7" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="P301" s="8" t="inlineStr"/>
-      <c r="Q301" s="7" t="inlineStr"/>
-    </row>
-    <row r="302">
-      <c r="A302" s="7" t="inlineStr">
-        <is>
-          <t>PR-TC-DB-003</t>
-        </is>
-      </c>
-      <c r="B302" s="7" t="inlineStr">
-        <is>
-          <t>22. Database Layer</t>
-        </is>
-      </c>
-      <c r="C302" s="7" t="inlineStr">
-        <is>
-          <t>21.5 Custom whitelisted endpoints</t>
-        </is>
-      </c>
-      <c r="D302" s="7" t="inlineStr">
-        <is>
-          <t>Indexes on frequently-filtered columns (cohort, sector, block, status)</t>
-        </is>
-      </c>
-      <c r="E302" s="8" t="inlineStr">
-        <is>
-          <t>Database</t>
-        </is>
-      </c>
-      <c r="F302" s="9" t="inlineStr">
-        <is>
-          <t>AUTO</t>
-        </is>
-      </c>
-      <c r="G302" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="H302" s="8" t="inlineStr">
-        <is>
-          <t>P1 — High</t>
-        </is>
-      </c>
-      <c r="I302" s="7" t="inlineStr">
-        <is>
-          <t>SM</t>
-        </is>
-      </c>
-      <c r="J302" s="7" t="inlineStr"/>
-      <c r="K302" s="7" t="inlineStr">
-        <is>
-          <t>• SHOW INDEX FROM tabEnterprenur Profile.</t>
-        </is>
-      </c>
-      <c r="L302" s="7" t="inlineStr"/>
-      <c r="M302" s="7" t="inlineStr"/>
-      <c r="N302" s="13" t="inlineStr">
-        <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="O302" s="7" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="P302" s="8" t="inlineStr"/>
-      <c r="Q302" s="7" t="inlineStr"/>
-    </row>
-    <row r="303">
-      <c r="A303" s="7" t="inlineStr">
-        <is>
-          <t>PR-TC-DB-004</t>
-        </is>
-      </c>
-      <c r="B303" s="7" t="inlineStr">
-        <is>
-          <t>22. Database Layer</t>
-        </is>
-      </c>
-      <c r="C303" s="7" t="inlineStr">
-        <is>
-          <t>21.5 Custom whitelisted endpoints</t>
-        </is>
-      </c>
-      <c r="D303" s="7" t="inlineStr">
-        <is>
-          <t>Cascade delete behaviour: deleting EP does NOT cascade-delete framework records</t>
-        </is>
-      </c>
-      <c r="E303" s="8" t="inlineStr">
-        <is>
-          <t>Database</t>
-        </is>
-      </c>
-      <c r="F303" s="9" t="inlineStr">
-        <is>
-          <t>AUTO</t>
-        </is>
-      </c>
-      <c r="G303" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="H303" s="8" t="inlineStr">
-        <is>
-          <t>P1 — High</t>
-        </is>
-      </c>
-      <c r="I303" s="7" t="inlineStr">
-        <is>
-          <t>SM</t>
-        </is>
-      </c>
-      <c r="J303" s="7" t="inlineStr"/>
-      <c r="K303" s="7" t="inlineStr">
-        <is>
-          <t>• Try to delete an EP with linked DF records.</t>
-        </is>
-      </c>
-      <c r="L303" s="7" t="inlineStr"/>
-      <c r="M303" s="7" t="inlineStr"/>
-      <c r="N303" s="13" t="inlineStr">
-        <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="O303" s="7" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="P303" s="8" t="inlineStr"/>
-      <c r="Q303" s="7" t="inlineStr"/>
-    </row>
-    <row r="304">
-      <c r="A304" s="7" t="inlineStr">
-        <is>
-          <t>PR-TC-DB-005</t>
-        </is>
-      </c>
-      <c r="B304" s="7" t="inlineStr">
-        <is>
-          <t>22. Database Layer</t>
-        </is>
-      </c>
-      <c r="C304" s="7" t="inlineStr">
-        <is>
-          <t>21.5 Custom whitelisted endpoints</t>
-        </is>
-      </c>
-      <c r="D304" s="7" t="inlineStr">
-        <is>
-          <t>Aadhaar field is encrypted at rest (or hashed)</t>
-        </is>
-      </c>
-      <c r="E304" s="8" t="inlineStr">
-        <is>
-          <t>Database</t>
-        </is>
-      </c>
-      <c r="F304" s="9" t="inlineStr">
-        <is>
-          <t>AUTO</t>
-        </is>
-      </c>
-      <c r="G304" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="H304" s="8" t="inlineStr">
-        <is>
-          <t>P1 — High</t>
-        </is>
-      </c>
-      <c r="I304" s="7" t="inlineStr">
-        <is>
-          <t>SM</t>
-        </is>
-      </c>
-      <c r="J304" s="7" t="inlineStr"/>
-      <c r="K304" s="7" t="inlineStr">
-        <is>
-          <t>• SELECT aadhaar_number FROM tabDocuments Table WHERE doc_type = "Aadhaar".</t>
-        </is>
-      </c>
-      <c r="L304" s="7" t="inlineStr"/>
-      <c r="M304" s="7" t="inlineStr"/>
-      <c r="N304" s="13" t="inlineStr">
-        <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="O304" s="7" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="P304" s="8" t="inlineStr"/>
-      <c r="Q304" s="7" t="inlineStr"/>
-    </row>
-    <row r="305">
-      <c r="A305" s="7" t="inlineStr">
-        <is>
-          <t>PR-TC-DB-006</t>
-        </is>
-      </c>
-      <c r="B305" s="7" t="inlineStr">
-        <is>
-          <t>22. Database Layer</t>
-        </is>
-      </c>
-      <c r="C305" s="7" t="inlineStr">
-        <is>
-          <t>21.5 Custom whitelisted endpoints</t>
-        </is>
-      </c>
-      <c r="D305" s="7" t="inlineStr">
-        <is>
-          <t>DB charset is utf8mb4 (supports emoji + native scripts)</t>
-        </is>
-      </c>
-      <c r="E305" s="8" t="inlineStr">
-        <is>
-          <t>Database</t>
-        </is>
-      </c>
-      <c r="F305" s="9" t="inlineStr">
-        <is>
-          <t>AUTO</t>
-        </is>
-      </c>
-      <c r="G305" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="H305" s="8" t="inlineStr">
-        <is>
-          <t>P1 — High</t>
-        </is>
-      </c>
-      <c r="I305" s="7" t="inlineStr">
-        <is>
-          <t>SM</t>
-        </is>
-      </c>
-      <c r="J305" s="7" t="inlineStr"/>
-      <c r="K305" s="7" t="inlineStr">
-        <is>
-          <t>• Save a record with name in Khasi script.</t>
-        </is>
-      </c>
-      <c r="L305" s="7" t="inlineStr"/>
-      <c r="M305" s="7" t="inlineStr"/>
-      <c r="N305" s="9" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="O305" s="7" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="P305" s="8" t="inlineStr"/>
-      <c r="Q305" s="7" t="inlineStr"/>
-    </row>
-    <row r="306">
-      <c r="A306" s="7" t="inlineStr">
-        <is>
-          <t>PR-TC-DB-007</t>
-        </is>
-      </c>
-      <c r="B306" s="7" t="inlineStr">
-        <is>
-          <t>22. Database Layer</t>
-        </is>
-      </c>
-      <c r="C306" s="7" t="inlineStr">
-        <is>
-          <t>21.5 Custom whitelisted endpoints</t>
-        </is>
-      </c>
-      <c r="D306" s="7" t="inlineStr">
-        <is>
-          <t>Timestamps stored in UTC; displayed in IST</t>
-        </is>
-      </c>
-      <c r="E306" s="8" t="inlineStr">
-        <is>
-          <t>Database</t>
-        </is>
-      </c>
-      <c r="F306" s="9" t="inlineStr">
-        <is>
-          <t>AUTO</t>
-        </is>
-      </c>
-      <c r="G306" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="H306" s="8" t="inlineStr">
-        <is>
-          <t>P1 — High</t>
-        </is>
-      </c>
-      <c r="I306" s="7" t="inlineStr">
-        <is>
-          <t>SM</t>
-        </is>
-      </c>
-      <c r="J306" s="7" t="inlineStr"/>
-      <c r="K306" s="7" t="inlineStr">
-        <is>
-          <t>• Save a record. Check raw creation column. Compare to UI display.</t>
-        </is>
-      </c>
-      <c r="L306" s="7" t="inlineStr"/>
-      <c r="M306" s="7" t="inlineStr"/>
-      <c r="N306" s="13" t="inlineStr">
-        <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="O306" s="7" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="P306" s="8" t="inlineStr"/>
-      <c r="Q306" s="7" t="inlineStr"/>
-    </row>
-    <row r="307">
-      <c r="A307" s="7" t="inlineStr">
-        <is>
-          <t>PR-TC-DB-008</t>
-        </is>
-      </c>
-      <c r="B307" s="7" t="inlineStr">
-        <is>
-          <t>22. Database Layer</t>
-        </is>
-      </c>
-      <c r="C307" s="7" t="inlineStr">
-        <is>
-          <t>21.5 Custom whitelisted endpoints</t>
-        </is>
-      </c>
-      <c r="D307" s="7" t="inlineStr">
-        <is>
-          <t>Migrations are reversible (where applicable)</t>
-        </is>
-      </c>
-      <c r="E307" s="8" t="inlineStr">
-        <is>
-          <t>Database</t>
-        </is>
-      </c>
-      <c r="F307" s="9" t="inlineStr">
-        <is>
-          <t>AUTO</t>
-        </is>
-      </c>
-      <c r="G307" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="H307" s="8" t="inlineStr">
-        <is>
-          <t>P2 — Medium</t>
-        </is>
-      </c>
-      <c r="I307" s="7" t="inlineStr">
-        <is>
-          <t>SM</t>
-        </is>
-      </c>
-      <c r="J307" s="7" t="inlineStr"/>
-      <c r="K307" s="7" t="inlineStr">
-        <is>
-          <t>• Test bench migrate (forward only — but verify a snapshot before any breaking change).</t>
-        </is>
-      </c>
-      <c r="L307" s="7" t="inlineStr"/>
-      <c r="M307" s="7" t="inlineStr"/>
-      <c r="N307" s="13" t="inlineStr">
-        <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="O307" s="7" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="P307" s="8" t="inlineStr"/>
       <c r="Q307" s="7" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-DB-009</t>
+          <t>PR-TC-API-009</t>
         </is>
       </c>
       <c r="B308" s="7" t="inlineStr">
         <is>
-          <t>22. Database Layer</t>
+          <t>21. API Layer</t>
         </is>
       </c>
       <c r="C308" s="7" t="inlineStr">
         <is>
-          <t>21.5 Custom whitelisted endpoints</t>
+          <t>21.4 Rate limiting / DoS protection</t>
         </is>
       </c>
       <c r="D308" s="7" t="inlineStr">
         <is>
-          <t>Backup schedule active; latest backup &amp;lt; 24 h old</t>
+          <t>1,000 requests/minute from same IP throttled</t>
         </is>
       </c>
       <c r="E308" s="8" t="inlineStr">
         <is>
-          <t>Database</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="F308" s="9" t="inlineStr">
@@ -22150,7 +22285,7 @@
       </c>
       <c r="G308" s="8" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="H308" s="8" t="inlineStr">
@@ -22160,13 +22295,13 @@
       </c>
       <c r="I308" s="7" t="inlineStr">
         <is>
-          <t>SM</t>
+          <t>all</t>
         </is>
       </c>
       <c r="J308" s="7" t="inlineStr"/>
       <c r="K308" s="7" t="inlineStr">
         <is>
-          <t>• Check /private/backups for latest dump.</t>
+          <t>• Hammer GET /api/method/get_logged_user 1k times in 60 s.</t>
         </is>
       </c>
       <c r="L308" s="7" t="inlineStr"/>
@@ -22187,12 +22322,12 @@
     <row r="309">
       <c r="A309" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-DB-010</t>
+          <t>PR-TC-API-010</t>
         </is>
       </c>
       <c r="B309" s="7" t="inlineStr">
         <is>
-          <t>22. Database Layer</t>
+          <t>21. API Layer</t>
         </is>
       </c>
       <c r="C309" s="7" t="inlineStr">
@@ -22202,12 +22337,12 @@
       </c>
       <c r="D309" s="7" t="inlineStr">
         <is>
-          <t>Heavy dashboard queries use indexes (EXPLAIN shows no full table scans)</t>
+          <t>networking_mentoring.save_introduction endpoint works</t>
         </is>
       </c>
       <c r="E309" s="8" t="inlineStr">
         <is>
-          <t>Database</t>
+          <t>API</t>
         </is>
       </c>
       <c r="F309" s="9" t="inlineStr">
@@ -22222,19 +22357,18 @@
       </c>
       <c r="H309" s="8" t="inlineStr">
         <is>
-          <t>P2 — Medium</t>
+          <t>P1 — High</t>
         </is>
       </c>
       <c r="I309" s="7" t="inlineStr">
         <is>
-          <t>SM</t>
+          <t>FA/CTP</t>
         </is>
       </c>
       <c r="J309" s="7" t="inlineStr"/>
       <c r="K309" s="7" t="inlineStr">
         <is>
-          <t>• Capture the actual queries fired by EP Status Monitor with filters.
-• EXPLAIN each.</t>
+          <t>• POST /api/method/prime_rural.networking_mentoring.save_introduction with valid payload.</t>
         </is>
       </c>
       <c r="L309" s="7" t="inlineStr"/>
@@ -22255,12 +22389,12 @@
     <row r="310">
       <c r="A310" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-SEC-001</t>
+          <t>PR-TC-API-011</t>
         </is>
       </c>
       <c r="B310" s="7" t="inlineStr">
         <is>
-          <t>23. Security — OWASP &amp; Beyond</t>
+          <t>21. API Layer</t>
         </is>
       </c>
       <c r="C310" s="7" t="inlineStr">
@@ -22270,12 +22404,12 @@
       </c>
       <c r="D310" s="7" t="inlineStr">
         <is>
-          <t>XSS: HTML / JS in text fields is escaped, not executed</t>
+          <t>Error response shape conforms to FrappeError contract</t>
         </is>
       </c>
       <c r="E310" s="8" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>API</t>
         </is>
       </c>
       <c r="F310" s="9" t="inlineStr">
@@ -22285,12 +22419,12 @@
       </c>
       <c r="G310" s="8" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="H310" s="8" t="inlineStr">
         <is>
-          <t>P0 — Blocker</t>
+          <t>P2 — Medium</t>
         </is>
       </c>
       <c r="I310" s="7" t="inlineStr">
@@ -22301,756 +22435,1494 @@
       <c r="J310" s="7" t="inlineStr"/>
       <c r="K310" s="7" t="inlineStr">
         <is>
+          <t>• Trigger a validation error.</t>
+        </is>
+      </c>
+      <c r="L310" s="7" t="inlineStr"/>
+      <c r="M310" s="7" t="inlineStr"/>
+      <c r="N310" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O310" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="P310" s="8" t="inlineStr"/>
+      <c r="Q310" s="7" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-DB-001</t>
+        </is>
+      </c>
+      <c r="B311" s="7" t="inlineStr">
+        <is>
+          <t>22. Database Layer</t>
+        </is>
+      </c>
+      <c r="C311" s="7" t="inlineStr">
+        <is>
+          <t>21.5 Custom whitelisted endpoints</t>
+        </is>
+      </c>
+      <c r="D311" s="7" t="inlineStr">
+        <is>
+          <t>Foreign key constraints exist on Link fields</t>
+        </is>
+      </c>
+      <c r="E311" s="8" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+      <c r="F311" s="9" t="inlineStr">
+        <is>
+          <t>AUTO</t>
+        </is>
+      </c>
+      <c r="G311" s="8" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="H311" s="8" t="inlineStr">
+        <is>
+          <t>P1 — High</t>
+        </is>
+      </c>
+      <c r="I311" s="7" t="inlineStr">
+        <is>
+          <t>SM</t>
+        </is>
+      </c>
+      <c r="J311" s="7" t="inlineStr"/>
+      <c r="K311" s="7" t="inlineStr">
+        <is>
+          <t>• Check tabEnterprenur Profile.block_FK references tabBlock.</t>
+        </is>
+      </c>
+      <c r="L311" s="7" t="inlineStr"/>
+      <c r="M311" s="7" t="inlineStr"/>
+      <c r="N311" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O311" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="P311" s="8" t="inlineStr"/>
+      <c r="Q311" s="7" t="inlineStr"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-DB-002</t>
+        </is>
+      </c>
+      <c r="B312" s="7" t="inlineStr">
+        <is>
+          <t>22. Database Layer</t>
+        </is>
+      </c>
+      <c r="C312" s="7" t="inlineStr">
+        <is>
+          <t>21.5 Custom whitelisted endpoints</t>
+        </is>
+      </c>
+      <c r="D312" s="7" t="inlineStr">
+        <is>
+          <t>UNIQUE constraint on enterprenur_name (within cohort)</t>
+        </is>
+      </c>
+      <c r="E312" s="8" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+      <c r="F312" s="9" t="inlineStr">
+        <is>
+          <t>AUTO</t>
+        </is>
+      </c>
+      <c r="G312" s="8" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="H312" s="8" t="inlineStr">
+        <is>
+          <t>P1 — High</t>
+        </is>
+      </c>
+      <c r="I312" s="7" t="inlineStr">
+        <is>
+          <t>SM</t>
+        </is>
+      </c>
+      <c r="J312" s="7" t="inlineStr"/>
+      <c r="K312" s="7" t="inlineStr">
+        <is>
+          <t>• SHOW CREATE TABLE tabEnterprenur Profile.</t>
+        </is>
+      </c>
+      <c r="L312" s="7" t="inlineStr"/>
+      <c r="M312" s="7" t="inlineStr"/>
+      <c r="N312" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O312" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="P312" s="8" t="inlineStr"/>
+      <c r="Q312" s="7" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-DB-003</t>
+        </is>
+      </c>
+      <c r="B313" s="7" t="inlineStr">
+        <is>
+          <t>22. Database Layer</t>
+        </is>
+      </c>
+      <c r="C313" s="7" t="inlineStr">
+        <is>
+          <t>21.5 Custom whitelisted endpoints</t>
+        </is>
+      </c>
+      <c r="D313" s="7" t="inlineStr">
+        <is>
+          <t>Indexes on frequently-filtered columns (cohort, sector, block, status)</t>
+        </is>
+      </c>
+      <c r="E313" s="8" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+      <c r="F313" s="9" t="inlineStr">
+        <is>
+          <t>AUTO</t>
+        </is>
+      </c>
+      <c r="G313" s="8" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="H313" s="8" t="inlineStr">
+        <is>
+          <t>P1 — High</t>
+        </is>
+      </c>
+      <c r="I313" s="7" t="inlineStr">
+        <is>
+          <t>SM</t>
+        </is>
+      </c>
+      <c r="J313" s="7" t="inlineStr"/>
+      <c r="K313" s="7" t="inlineStr">
+        <is>
+          <t>• SHOW INDEX FROM tabEnterprenur Profile.</t>
+        </is>
+      </c>
+      <c r="L313" s="7" t="inlineStr"/>
+      <c r="M313" s="7" t="inlineStr"/>
+      <c r="N313" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O313" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="P313" s="8" t="inlineStr"/>
+      <c r="Q313" s="7" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-DB-004</t>
+        </is>
+      </c>
+      <c r="B314" s="7" t="inlineStr">
+        <is>
+          <t>22. Database Layer</t>
+        </is>
+      </c>
+      <c r="C314" s="7" t="inlineStr">
+        <is>
+          <t>21.5 Custom whitelisted endpoints</t>
+        </is>
+      </c>
+      <c r="D314" s="7" t="inlineStr">
+        <is>
+          <t>Cascade delete behaviour: deleting EP does NOT cascade-delete framework records</t>
+        </is>
+      </c>
+      <c r="E314" s="8" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+      <c r="F314" s="9" t="inlineStr">
+        <is>
+          <t>AUTO</t>
+        </is>
+      </c>
+      <c r="G314" s="8" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="H314" s="8" t="inlineStr">
+        <is>
+          <t>P1 — High</t>
+        </is>
+      </c>
+      <c r="I314" s="7" t="inlineStr">
+        <is>
+          <t>SM</t>
+        </is>
+      </c>
+      <c r="J314" s="7" t="inlineStr"/>
+      <c r="K314" s="7" t="inlineStr">
+        <is>
+          <t>• Try to delete an EP with linked DF records.</t>
+        </is>
+      </c>
+      <c r="L314" s="7" t="inlineStr"/>
+      <c r="M314" s="7" t="inlineStr"/>
+      <c r="N314" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O314" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="P314" s="8" t="inlineStr"/>
+      <c r="Q314" s="7" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-DB-005</t>
+        </is>
+      </c>
+      <c r="B315" s="7" t="inlineStr">
+        <is>
+          <t>22. Database Layer</t>
+        </is>
+      </c>
+      <c r="C315" s="7" t="inlineStr">
+        <is>
+          <t>21.5 Custom whitelisted endpoints</t>
+        </is>
+      </c>
+      <c r="D315" s="7" t="inlineStr">
+        <is>
+          <t>Aadhaar field is encrypted at rest (or hashed)</t>
+        </is>
+      </c>
+      <c r="E315" s="8" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+      <c r="F315" s="9" t="inlineStr">
+        <is>
+          <t>AUTO</t>
+        </is>
+      </c>
+      <c r="G315" s="8" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="H315" s="8" t="inlineStr">
+        <is>
+          <t>P1 — High</t>
+        </is>
+      </c>
+      <c r="I315" s="7" t="inlineStr">
+        <is>
+          <t>SM</t>
+        </is>
+      </c>
+      <c r="J315" s="7" t="inlineStr"/>
+      <c r="K315" s="7" t="inlineStr">
+        <is>
+          <t>• SELECT aadhaar_number FROM tabDocuments Table WHERE doc_type = "Aadhaar".</t>
+        </is>
+      </c>
+      <c r="L315" s="7" t="inlineStr"/>
+      <c r="M315" s="7" t="inlineStr"/>
+      <c r="N315" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O315" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="P315" s="8" t="inlineStr"/>
+      <c r="Q315" s="7" t="inlineStr"/>
+    </row>
+    <row r="316">
+      <c r="A316" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-DB-006</t>
+        </is>
+      </c>
+      <c r="B316" s="7" t="inlineStr">
+        <is>
+          <t>22. Database Layer</t>
+        </is>
+      </c>
+      <c r="C316" s="7" t="inlineStr">
+        <is>
+          <t>21.5 Custom whitelisted endpoints</t>
+        </is>
+      </c>
+      <c r="D316" s="7" t="inlineStr">
+        <is>
+          <t>DB charset is utf8mb4 (supports emoji + native scripts)</t>
+        </is>
+      </c>
+      <c r="E316" s="8" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+      <c r="F316" s="9" t="inlineStr">
+        <is>
+          <t>AUTO</t>
+        </is>
+      </c>
+      <c r="G316" s="8" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="H316" s="8" t="inlineStr">
+        <is>
+          <t>P1 — High</t>
+        </is>
+      </c>
+      <c r="I316" s="7" t="inlineStr">
+        <is>
+          <t>SM</t>
+        </is>
+      </c>
+      <c r="J316" s="7" t="inlineStr"/>
+      <c r="K316" s="7" t="inlineStr">
+        <is>
+          <t>• Save a record with name in Khasi script.</t>
+        </is>
+      </c>
+      <c r="L316" s="7" t="inlineStr"/>
+      <c r="M316" s="7" t="inlineStr"/>
+      <c r="N316" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O316" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="P316" s="8" t="inlineStr"/>
+      <c r="Q316" s="7" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-DB-007</t>
+        </is>
+      </c>
+      <c r="B317" s="7" t="inlineStr">
+        <is>
+          <t>22. Database Layer</t>
+        </is>
+      </c>
+      <c r="C317" s="7" t="inlineStr">
+        <is>
+          <t>21.5 Custom whitelisted endpoints</t>
+        </is>
+      </c>
+      <c r="D317" s="7" t="inlineStr">
+        <is>
+          <t>Timestamps stored in UTC; displayed in IST</t>
+        </is>
+      </c>
+      <c r="E317" s="8" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+      <c r="F317" s="9" t="inlineStr">
+        <is>
+          <t>AUTO</t>
+        </is>
+      </c>
+      <c r="G317" s="8" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="H317" s="8" t="inlineStr">
+        <is>
+          <t>P1 — High</t>
+        </is>
+      </c>
+      <c r="I317" s="7" t="inlineStr">
+        <is>
+          <t>SM</t>
+        </is>
+      </c>
+      <c r="J317" s="7" t="inlineStr"/>
+      <c r="K317" s="7" t="inlineStr">
+        <is>
+          <t>• Save a record. Check raw creation column. Compare to UI display.</t>
+        </is>
+      </c>
+      <c r="L317" s="7" t="inlineStr"/>
+      <c r="M317" s="7" t="inlineStr"/>
+      <c r="N317" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O317" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="P317" s="8" t="inlineStr"/>
+      <c r="Q317" s="7" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-DB-008</t>
+        </is>
+      </c>
+      <c r="B318" s="7" t="inlineStr">
+        <is>
+          <t>22. Database Layer</t>
+        </is>
+      </c>
+      <c r="C318" s="7" t="inlineStr">
+        <is>
+          <t>21.5 Custom whitelisted endpoints</t>
+        </is>
+      </c>
+      <c r="D318" s="7" t="inlineStr">
+        <is>
+          <t>Migrations are reversible (where applicable)</t>
+        </is>
+      </c>
+      <c r="E318" s="8" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+      <c r="F318" s="9" t="inlineStr">
+        <is>
+          <t>AUTO</t>
+        </is>
+      </c>
+      <c r="G318" s="8" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="H318" s="8" t="inlineStr">
+        <is>
+          <t>P2 — Medium</t>
+        </is>
+      </c>
+      <c r="I318" s="7" t="inlineStr">
+        <is>
+          <t>SM</t>
+        </is>
+      </c>
+      <c r="J318" s="7" t="inlineStr"/>
+      <c r="K318" s="7" t="inlineStr">
+        <is>
+          <t>• Test bench migrate (forward only — but verify a snapshot before any breaking change).</t>
+        </is>
+      </c>
+      <c r="L318" s="7" t="inlineStr"/>
+      <c r="M318" s="7" t="inlineStr"/>
+      <c r="N318" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O318" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="P318" s="8" t="inlineStr"/>
+      <c r="Q318" s="7" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-DB-009</t>
+        </is>
+      </c>
+      <c r="B319" s="7" t="inlineStr">
+        <is>
+          <t>22. Database Layer</t>
+        </is>
+      </c>
+      <c r="C319" s="7" t="inlineStr">
+        <is>
+          <t>21.5 Custom whitelisted endpoints</t>
+        </is>
+      </c>
+      <c r="D319" s="7" t="inlineStr">
+        <is>
+          <t>Backup schedule active; latest backup &amp;lt; 24 h old</t>
+        </is>
+      </c>
+      <c r="E319" s="8" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+      <c r="F319" s="9" t="inlineStr">
+        <is>
+          <t>AUTO</t>
+        </is>
+      </c>
+      <c r="G319" s="8" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="H319" s="8" t="inlineStr">
+        <is>
+          <t>P1 — High</t>
+        </is>
+      </c>
+      <c r="I319" s="7" t="inlineStr">
+        <is>
+          <t>SM</t>
+        </is>
+      </c>
+      <c r="J319" s="7" t="inlineStr"/>
+      <c r="K319" s="7" t="inlineStr">
+        <is>
+          <t>• Check /private/backups for latest dump.</t>
+        </is>
+      </c>
+      <c r="L319" s="7" t="inlineStr"/>
+      <c r="M319" s="7" t="inlineStr"/>
+      <c r="N319" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O319" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="P319" s="8" t="inlineStr"/>
+      <c r="Q319" s="7" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-DB-010</t>
+        </is>
+      </c>
+      <c r="B320" s="7" t="inlineStr">
+        <is>
+          <t>22. Database Layer</t>
+        </is>
+      </c>
+      <c r="C320" s="7" t="inlineStr">
+        <is>
+          <t>21.5 Custom whitelisted endpoints</t>
+        </is>
+      </c>
+      <c r="D320" s="7" t="inlineStr">
+        <is>
+          <t>Heavy dashboard queries use indexes (EXPLAIN shows no full table scans)</t>
+        </is>
+      </c>
+      <c r="E320" s="8" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+      <c r="F320" s="9" t="inlineStr">
+        <is>
+          <t>AUTO</t>
+        </is>
+      </c>
+      <c r="G320" s="8" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="H320" s="8" t="inlineStr">
+        <is>
+          <t>P2 — Medium</t>
+        </is>
+      </c>
+      <c r="I320" s="7" t="inlineStr">
+        <is>
+          <t>SM</t>
+        </is>
+      </c>
+      <c r="J320" s="7" t="inlineStr"/>
+      <c r="K320" s="7" t="inlineStr">
+        <is>
+          <t>• Capture the actual queries fired by EP Status Monitor with filters.
+• EXPLAIN each.</t>
+        </is>
+      </c>
+      <c r="L320" s="7" t="inlineStr"/>
+      <c r="M320" s="7" t="inlineStr"/>
+      <c r="N320" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O320" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="P320" s="8" t="inlineStr"/>
+      <c r="Q320" s="7" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-SEC-001</t>
+        </is>
+      </c>
+      <c r="B321" s="7" t="inlineStr">
+        <is>
+          <t>23. Security — OWASP &amp; Beyond</t>
+        </is>
+      </c>
+      <c r="C321" s="7" t="inlineStr">
+        <is>
+          <t>21.5 Custom whitelisted endpoints</t>
+        </is>
+      </c>
+      <c r="D321" s="7" t="inlineStr">
+        <is>
+          <t>XSS: HTML / JS in text fields is escaped, not executed</t>
+        </is>
+      </c>
+      <c r="E321" s="8" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="F321" s="9" t="inlineStr">
+        <is>
+          <t>AUTO</t>
+        </is>
+      </c>
+      <c r="G321" s="8" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="H321" s="8" t="inlineStr">
+        <is>
+          <t>P0 — Blocker</t>
+        </is>
+      </c>
+      <c r="I321" s="7" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="J321" s="7" t="inlineStr"/>
+      <c r="K321" s="7" t="inlineStr">
+        <is>
           <t>• Enter &lt;script&gt;alert(1)&lt;/script&gt; into Entrepreneur Name. Save.
 • Open the EP detail page.</t>
         </is>
       </c>
-      <c r="L310" s="7" t="inlineStr">
+      <c r="L321" s="7" t="inlineStr">
         <is>
           <t>No alert fires. Text renders as literal characters. Verify in 5 places: name on card, name in list, name in dashboard tooltip, name in browser title, name in CSV export.</t>
         </is>
       </c>
-      <c r="M310" s="7" t="inlineStr">
+      <c r="M321" s="7" t="inlineStr">
         <is>
           <t>OWASP A03 Injection (XSS sub-category).</t>
         </is>
       </c>
-      <c r="N310" s="13" t="inlineStr">
+      <c r="N321" s="13" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="O310" s="7" t="inlineStr">
+      <c r="O321" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="P310" s="8" t="inlineStr"/>
-      <c r="Q310" s="7" t="inlineStr"/>
-    </row>
-    <row r="311">
-      <c r="A311" s="7" t="inlineStr">
+      <c r="P321" s="8" t="inlineStr"/>
+      <c r="Q321" s="7" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="7" t="inlineStr">
         <is>
           <t>PR-TC-SEC-002</t>
         </is>
       </c>
-      <c r="B311" s="7" t="inlineStr">
+      <c r="B322" s="7" t="inlineStr">
         <is>
           <t>23. Security — OWASP &amp; Beyond</t>
         </is>
       </c>
-      <c r="C311" s="7" t="inlineStr">
+      <c r="C322" s="7" t="inlineStr">
         <is>
           <t>21.5 Custom whitelisted endpoints</t>
         </is>
       </c>
-      <c r="D311" s="7" t="inlineStr">
+      <c r="D322" s="7" t="inlineStr">
         <is>
           <t>SQL injection in search box is escaped, not executed</t>
         </is>
       </c>
-      <c r="E311" s="8" t="inlineStr">
+      <c r="E322" s="8" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="F311" s="9" t="inlineStr">
+      <c r="F322" s="9" t="inlineStr">
         <is>
           <t>AUTO</t>
         </is>
       </c>
-      <c r="G311" s="8" t="inlineStr">
+      <c r="G322" s="8" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="H311" s="8" t="inlineStr">
+      <c r="H322" s="8" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="I311" s="7" t="inlineStr">
+      <c r="I322" s="7" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="J311" s="7" t="inlineStr"/>
-      <c r="K311" s="7" t="inlineStr">
+      <c r="J322" s="7" t="inlineStr"/>
+      <c r="K322" s="7" t="inlineStr">
         <is>
           <t>• Search EP list with '; DROP TABLE tabEnterprenur Profile;--.</t>
         </is>
       </c>
-      <c r="L311" s="7" t="inlineStr">
+      <c r="L322" s="7" t="inlineStr">
         <is>
           <t>Returns zero results (literal string match). No DB damage. (Frappe uses parameterised queries — verify.)</t>
         </is>
       </c>
-      <c r="M311" s="7" t="inlineStr">
+      <c r="M322" s="7" t="inlineStr">
         <is>
           <t>OWASP A03.</t>
         </is>
       </c>
-      <c r="N311" s="9" t="inlineStr">
+      <c r="N322" s="9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="O311" s="7" t="inlineStr">
+      <c r="O322" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="P311" s="8" t="inlineStr"/>
-      <c r="Q311" s="7" t="inlineStr"/>
-    </row>
-    <row r="312">
-      <c r="A312" s="7" t="inlineStr">
+      <c r="P322" s="8" t="inlineStr"/>
+      <c r="Q322" s="7" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="7" t="inlineStr">
         <is>
           <t>PR-TC-SEC-003</t>
         </is>
       </c>
-      <c r="B312" s="7" t="inlineStr">
+      <c r="B323" s="7" t="inlineStr">
         <is>
           <t>23. Security — OWASP &amp; Beyond</t>
         </is>
       </c>
-      <c r="C312" s="7" t="inlineStr">
+      <c r="C323" s="7" t="inlineStr">
         <is>
           <t>21.5 Custom whitelisted endpoints</t>
         </is>
       </c>
-      <c r="D312" s="7" t="inlineStr">
+      <c r="D323" s="7" t="inlineStr">
         <is>
           <t>IDOR: cannot access another user's EP by guessing URL pattern</t>
         </is>
       </c>
-      <c r="E312" s="8" t="inlineStr">
+      <c r="E323" s="8" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="F312" s="9" t="inlineStr">
+      <c r="F323" s="9" t="inlineStr">
         <is>
           <t>AUTO</t>
         </is>
       </c>
-      <c r="G312" s="8" t="inlineStr">
+      <c r="G323" s="8" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="H312" s="8" t="inlineStr">
+      <c r="H323" s="8" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="I312" s="7" t="inlineStr">
+      <c r="I323" s="7" t="inlineStr">
         <is>
           <t>FA</t>
         </is>
       </c>
-      <c r="J312" s="7" t="inlineStr"/>
-      <c r="K312" s="7" t="inlineStr">
+      <c r="J323" s="7" t="inlineStr"/>
+      <c r="K323" s="7" t="inlineStr">
         <is>
           <t>• FA from Block A iterates URLs /app/enterprenur-profile/EP-XXX-00001..00100.</t>
         </is>
       </c>
-      <c r="L312" s="7" t="inlineStr">
+      <c r="L323" s="7" t="inlineStr">
         <is>
           <t>All Block-B records return 403 / 404. Logs flag the pattern (potential abuse).</t>
         </is>
       </c>
-      <c r="M312" s="7" t="inlineStr">
+      <c r="M323" s="7" t="inlineStr">
         <is>
           <t>OWASP A01.</t>
         </is>
       </c>
-      <c r="N312" s="9" t="inlineStr">
+      <c r="N323" s="9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="O312" s="7" t="inlineStr">
+      <c r="O323" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="P312" s="8" t="inlineStr"/>
-      <c r="Q312" s="7" t="inlineStr"/>
-    </row>
-    <row r="313">
-      <c r="A313" s="7" t="inlineStr">
+      <c r="P323" s="8" t="inlineStr"/>
+      <c r="Q323" s="7" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="7" t="inlineStr">
         <is>
           <t>PR-TC-SEC-004</t>
         </is>
       </c>
-      <c r="B313" s="7" t="inlineStr">
+      <c r="B324" s="7" t="inlineStr">
         <is>
           <t>23. Security — OWASP &amp; Beyond</t>
         </is>
       </c>
-      <c r="C313" s="7" t="inlineStr">
+      <c r="C324" s="7" t="inlineStr">
         <is>
           <t>21.5 Custom whitelisted endpoints</t>
         </is>
       </c>
-      <c r="D313" s="7" t="inlineStr">
+      <c r="D324" s="7" t="inlineStr">
         <is>
           <t>HTTPS only — HTTP redirects to HTTPS</t>
         </is>
       </c>
-      <c r="E313" s="8" t="inlineStr">
+      <c r="E324" s="8" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="F313" s="9" t="inlineStr">
+      <c r="F324" s="9" t="inlineStr">
         <is>
           <t>AUTO</t>
         </is>
       </c>
-      <c r="G313" s="8" t="inlineStr">
+      <c r="G324" s="8" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="H313" s="8" t="inlineStr">
+      <c r="H324" s="8" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="I313" s="7" t="inlineStr">
+      <c r="I324" s="7" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="J313" s="7" t="inlineStr"/>
-      <c r="K313" s="7" t="inlineStr">
+      <c r="J324" s="7" t="inlineStr"/>
+      <c r="K324" s="7" t="inlineStr">
         <is>
           <t>• curl http://stgprime-rural.dhwaniris.in.</t>
         </is>
       </c>
-      <c r="L313" s="7" t="inlineStr">
+      <c r="L324" s="7" t="inlineStr">
         <is>
           <t>301 to HTTPS. HSTS header set (Strict-Transport-Security: max-age=31536000).</t>
         </is>
       </c>
-      <c r="M313" s="7" t="inlineStr">
+      <c r="M324" s="7" t="inlineStr">
         <is>
           <t>OWASP A02 Cryptographic Failures.</t>
         </is>
       </c>
-      <c r="N313" s="9" t="inlineStr">
+      <c r="N324" s="9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="O313" s="7" t="inlineStr">
+      <c r="O324" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="P313" s="8" t="inlineStr"/>
-      <c r="Q313" s="7" t="inlineStr"/>
-    </row>
-    <row r="314">
-      <c r="A314" s="7" t="inlineStr">
+      <c r="P324" s="8" t="inlineStr"/>
+      <c r="Q324" s="7" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="A325" s="7" t="inlineStr">
         <is>
           <t>PR-TC-SEC-005</t>
         </is>
       </c>
-      <c r="B314" s="7" t="inlineStr">
+      <c r="B325" s="7" t="inlineStr">
         <is>
           <t>23. Security — OWASP &amp; Beyond</t>
         </is>
       </c>
-      <c r="C314" s="7" t="inlineStr">
+      <c r="C325" s="7" t="inlineStr">
         <is>
           <t>21.5 Custom whitelisted endpoints</t>
         </is>
       </c>
-      <c r="D314" s="7" t="inlineStr">
+      <c r="D325" s="7" t="inlineStr">
         <is>
           <t>Content-Security-Policy header set, restricts inline scripts</t>
         </is>
       </c>
-      <c r="E314" s="8" t="inlineStr">
+      <c r="E325" s="8" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="F314" s="9" t="inlineStr">
+      <c r="F325" s="9" t="inlineStr">
         <is>
           <t>AUTO</t>
         </is>
       </c>
-      <c r="G314" s="8" t="inlineStr">
+      <c r="G325" s="8" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="H314" s="8" t="inlineStr">
+      <c r="H325" s="8" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="I314" s="7" t="inlineStr">
+      <c r="I325" s="7" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="J314" s="7" t="inlineStr"/>
-      <c r="K314" s="7" t="inlineStr">
+      <c r="J325" s="7" t="inlineStr"/>
+      <c r="K325" s="7" t="inlineStr">
         <is>
           <t>• Inspect response headers on /app/.</t>
         </is>
       </c>
-      <c r="L314" s="7" t="inlineStr"/>
-      <c r="M314" s="7" t="inlineStr"/>
-      <c r="N314" s="12" t="inlineStr">
+      <c r="L325" s="7" t="inlineStr"/>
+      <c r="M325" s="7" t="inlineStr"/>
+      <c r="N325" s="12" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="O314" s="7" t="inlineStr">
+      <c r="O325" s="7" t="inlineStr">
         <is>
           <t>Error: CSP header should be set
 expect(received).toBeTruthy()
 Received: undefined</t>
         </is>
       </c>
-      <c r="P314" s="8" t="inlineStr">
+      <c r="P325" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="Q314" s="7" t="inlineStr"/>
-    </row>
-    <row r="315">
-      <c r="A315" s="7" t="inlineStr">
+      <c r="Q325" s="7" t="inlineStr"/>
+    </row>
+    <row r="326">
+      <c r="A326" s="7" t="inlineStr">
         <is>
           <t>PR-TC-SEC-006</t>
         </is>
       </c>
-      <c r="B315" s="7" t="inlineStr">
+      <c r="B326" s="7" t="inlineStr">
         <is>
           <t>23. Security — OWASP &amp; Beyond</t>
         </is>
       </c>
-      <c r="C315" s="7" t="inlineStr">
+      <c r="C326" s="7" t="inlineStr">
         <is>
           <t>21.5 Custom whitelisted endpoints</t>
         </is>
       </c>
-      <c r="D315" s="7" t="inlineStr">
+      <c r="D326" s="7" t="inlineStr">
         <is>
           <t>X-Frame-Options / frame-ancestors prevents clickjacking</t>
         </is>
       </c>
-      <c r="E315" s="8" t="inlineStr">
+      <c r="E326" s="8" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="F315" s="9" t="inlineStr">
+      <c r="F326" s="9" t="inlineStr">
         <is>
           <t>AUTO</t>
         </is>
       </c>
-      <c r="G315" s="8" t="inlineStr">
+      <c r="G326" s="8" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="H315" s="8" t="inlineStr">
+      <c r="H326" s="8" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="I315" s="7" t="inlineStr">
+      <c r="I326" s="7" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="J315" s="7" t="inlineStr"/>
-      <c r="K315" s="7" t="inlineStr">
+      <c r="J326" s="7" t="inlineStr"/>
+      <c r="K326" s="7" t="inlineStr">
         <is>
           <t>• Attempt to embed in an iframe from another origin.</t>
         </is>
       </c>
-      <c r="L315" s="7" t="inlineStr"/>
-      <c r="M315" s="7" t="inlineStr"/>
-      <c r="N315" s="9" t="inlineStr">
+      <c r="L326" s="7" t="inlineStr"/>
+      <c r="M326" s="7" t="inlineStr"/>
+      <c r="N326" s="9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="O315" s="7" t="inlineStr">
+      <c r="O326" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="P315" s="8" t="inlineStr"/>
-      <c r="Q315" s="7" t="inlineStr"/>
-    </row>
-    <row r="316">
-      <c r="A316" s="7" t="inlineStr">
+      <c r="P326" s="8" t="inlineStr"/>
+      <c r="Q326" s="7" t="inlineStr"/>
+    </row>
+    <row r="327">
+      <c r="A327" s="7" t="inlineStr">
         <is>
           <t>PR-TC-SEC-007</t>
         </is>
       </c>
-      <c r="B316" s="7" t="inlineStr">
+      <c r="B327" s="7" t="inlineStr">
         <is>
           <t>23. Security — OWASP &amp; Beyond</t>
         </is>
       </c>
-      <c r="C316" s="7" t="inlineStr">
+      <c r="C327" s="7" t="inlineStr">
         <is>
           <t>21.5 Custom whitelisted endpoints</t>
         </is>
       </c>
-      <c r="D316" s="7" t="inlineStr">
+      <c r="D327" s="7" t="inlineStr">
         <is>
           <t>Privilege escalation: FA cannot grant themselves System Manager via API</t>
         </is>
       </c>
-      <c r="E316" s="8" t="inlineStr">
+      <c r="E327" s="8" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="F316" s="9" t="inlineStr">
+      <c r="F327" s="9" t="inlineStr">
         <is>
           <t>AUTO</t>
         </is>
       </c>
-      <c r="G316" s="8" t="inlineStr">
+      <c r="G327" s="8" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="H316" s="8" t="inlineStr">
+      <c r="H327" s="8" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="I316" s="7" t="inlineStr">
+      <c r="I327" s="7" t="inlineStr">
         <is>
           <t>FA</t>
         </is>
       </c>
-      <c r="J316" s="7" t="inlineStr"/>
-      <c r="K316" s="7" t="inlineStr">
+      <c r="J327" s="7" t="inlineStr"/>
+      <c r="K327" s="7" t="inlineStr">
         <is>
           <t>• FA POST /api/method/frappe.client.set_value on their own User record with roles += "System Manager".</t>
         </is>
       </c>
-      <c r="L316" s="7" t="inlineStr">
+      <c r="L327" s="7" t="inlineStr">
         <is>
           <t>403 / DB unchanged.</t>
         </is>
       </c>
-      <c r="M316" s="7" t="inlineStr">
+      <c r="M327" s="7" t="inlineStr">
         <is>
           <t>OWASP A01.</t>
         </is>
       </c>
-      <c r="N316" s="13" t="inlineStr">
+      <c r="N327" s="13" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="O316" s="7" t="inlineStr">
+      <c r="O327" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="P316" s="8" t="inlineStr"/>
-      <c r="Q316" s="7" t="inlineStr"/>
-    </row>
-    <row r="317">
-      <c r="A317" s="7" t="inlineStr">
+      <c r="P327" s="8" t="inlineStr"/>
+      <c r="Q327" s="7" t="inlineStr"/>
+    </row>
+    <row r="328">
+      <c r="A328" s="7" t="inlineStr">
         <is>
           <t>PR-TC-SEC-008</t>
         </is>
       </c>
-      <c r="B317" s="7" t="inlineStr">
+      <c r="B328" s="7" t="inlineStr">
         <is>
           <t>23. Security — OWASP &amp; Beyond</t>
         </is>
       </c>
-      <c r="C317" s="7" t="inlineStr">
+      <c r="C328" s="7" t="inlineStr">
         <is>
           <t>21.5 Custom whitelisted endpoints</t>
         </is>
       </c>
-      <c r="D317" s="7" t="inlineStr">
+      <c r="D328" s="7" t="inlineStr">
         <is>
           <t>File upload: SVG with embedded script is sanitised or rejected</t>
         </is>
       </c>
-      <c r="E317" s="8" t="inlineStr">
+      <c r="E328" s="8" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="F317" s="9" t="inlineStr">
+      <c r="F328" s="9" t="inlineStr">
         <is>
           <t>AUTO</t>
         </is>
       </c>
-      <c r="G317" s="8" t="inlineStr">
+      <c r="G328" s="8" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="H317" s="8" t="inlineStr">
+      <c r="H328" s="8" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="I317" s="7" t="inlineStr">
+      <c r="I328" s="7" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="J317" s="7" t="inlineStr"/>
-      <c r="K317" s="7" t="inlineStr">
+      <c r="J328" s="7" t="inlineStr"/>
+      <c r="K328" s="7" t="inlineStr">
         <is>
           <t>• Upload an SVG containing &lt;script&gt;alert(1)&lt;/script&gt;.</t>
         </is>
       </c>
-      <c r="L317" s="7" t="inlineStr"/>
-      <c r="M317" s="7" t="inlineStr"/>
-      <c r="N317" s="13" t="inlineStr">
+      <c r="L328" s="7" t="inlineStr"/>
+      <c r="M328" s="7" t="inlineStr"/>
+      <c r="N328" s="13" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="O317" s="7" t="inlineStr">
+      <c r="O328" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="P317" s="8" t="inlineStr"/>
-      <c r="Q317" s="7" t="inlineStr"/>
-    </row>
-    <row r="318">
-      <c r="A318" s="7" t="inlineStr">
+      <c r="P328" s="8" t="inlineStr"/>
+      <c r="Q328" s="7" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" s="7" t="inlineStr">
         <is>
           <t>PR-TC-SEC-009</t>
         </is>
       </c>
-      <c r="B318" s="7" t="inlineStr">
+      <c r="B329" s="7" t="inlineStr">
         <is>
           <t>23. Security — OWASP &amp; Beyond</t>
         </is>
       </c>
-      <c r="C318" s="7" t="inlineStr">
+      <c r="C329" s="7" t="inlineStr">
         <is>
           <t>21.5 Custom whitelisted endpoints</t>
         </is>
       </c>
-      <c r="D318" s="7" t="inlineStr">
+      <c r="D329" s="7" t="inlineStr">
         <is>
           <t>Sensitive data not in URL query params (e.g. password, Aadhaar)</t>
         </is>
       </c>
-      <c r="E318" s="8" t="inlineStr">
+      <c r="E329" s="8" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="F318" s="9" t="inlineStr">
+      <c r="F329" s="9" t="inlineStr">
         <is>
           <t>AUTO</t>
         </is>
       </c>
-      <c r="G318" s="8" t="inlineStr">
+      <c r="G329" s="8" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="H318" s="8" t="inlineStr">
+      <c r="H329" s="8" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="I318" s="7" t="inlineStr">
+      <c r="I329" s="7" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="J318" s="7" t="inlineStr"/>
-      <c r="K318" s="7" t="inlineStr">
+      <c r="J329" s="7" t="inlineStr"/>
+      <c r="K329" s="7" t="inlineStr">
         <is>
           <t>• Inspect URLs across all flows.</t>
         </is>
       </c>
-      <c r="L318" s="7" t="inlineStr"/>
-      <c r="M318" s="7" t="inlineStr"/>
-      <c r="N318" s="13" t="inlineStr">
+      <c r="L329" s="7" t="inlineStr"/>
+      <c r="M329" s="7" t="inlineStr"/>
+      <c r="N329" s="13" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="O318" s="7" t="inlineStr">
+      <c r="O329" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="P318" s="8" t="inlineStr"/>
-      <c r="Q318" s="7" t="inlineStr"/>
-    </row>
-    <row r="319">
-      <c r="A319" s="7" t="inlineStr">
+      <c r="P329" s="8" t="inlineStr"/>
+      <c r="Q329" s="7" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="7" t="inlineStr">
         <is>
           <t>PR-TC-SEC-010</t>
         </is>
       </c>
-      <c r="B319" s="7" t="inlineStr">
+      <c r="B330" s="7" t="inlineStr">
         <is>
           <t>23. Security — OWASP &amp; Beyond</t>
         </is>
       </c>
-      <c r="C319" s="7" t="inlineStr">
+      <c r="C330" s="7" t="inlineStr">
         <is>
           <t>21.5 Custom whitelisted endpoints</t>
         </is>
       </c>
-      <c r="D319" s="7" t="inlineStr">
+      <c r="D330" s="7" t="inlineStr">
         <is>
           <t>Audit log records security-relevant events</t>
         </is>
       </c>
-      <c r="E319" s="8" t="inlineStr">
+      <c r="E330" s="8" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="F319" s="9" t="inlineStr">
+      <c r="F330" s="9" t="inlineStr">
         <is>
           <t>AUTO</t>
         </is>
       </c>
-      <c r="G319" s="8" t="inlineStr">
+      <c r="G330" s="8" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="H319" s="8" t="inlineStr">
+      <c r="H330" s="8" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="I319" s="7" t="inlineStr">
+      <c r="I330" s="7" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="J319" s="7" t="inlineStr"/>
-      <c r="K319" s="7" t="inlineStr">
+      <c r="J330" s="7" t="inlineStr"/>
+      <c r="K330" s="7" t="inlineStr">
         <is>
           <t>• Login, failed login, role change, EP delete attempt, final status change, password change.</t>
         </is>
       </c>
-      <c r="L319" s="7" t="inlineStr"/>
-      <c r="M319" s="7" t="inlineStr"/>
-      <c r="N319" s="13" t="inlineStr">
+      <c r="L330" s="7" t="inlineStr"/>
+      <c r="M330" s="7" t="inlineStr"/>
+      <c r="N330" s="13" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="O319" s="7" t="inlineStr">
+      <c r="O330" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="P319" s="8" t="inlineStr"/>
-      <c r="Q319" s="7" t="inlineStr"/>
-    </row>
-    <row r="320">
-      <c r="A320" s="7" t="inlineStr">
+      <c r="P330" s="8" t="inlineStr"/>
+      <c r="Q330" s="7" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" s="7" t="inlineStr">
         <is>
           <t>PR-TC-SEC-011</t>
         </is>
       </c>
-      <c r="B320" s="7" t="inlineStr">
+      <c r="B331" s="7" t="inlineStr">
         <is>
           <t>23. Security — OWASP &amp; Beyond</t>
         </is>
       </c>
-      <c r="C320" s="7" t="inlineStr">
+      <c r="C331" s="7" t="inlineStr">
         <is>
           <t>21.5 Custom whitelisted endpoints</t>
         </is>
       </c>
-      <c r="D320" s="7" t="inlineStr">
+      <c r="D331" s="7" t="inlineStr">
         <is>
           <t>VAPT by CERT-In empanelled agency completes with no Critical / High issues before go-live</t>
         </is>
       </c>
-      <c r="E320" s="8" t="inlineStr">
+      <c r="E331" s="8" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="F320" s="9" t="inlineStr">
+      <c r="F331" s="9" t="inlineStr">
         <is>
           <t>AUTO</t>
         </is>
       </c>
-      <c r="G320" s="8" t="inlineStr">
+      <c r="G331" s="8" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="H320" s="8" t="inlineStr">
+      <c r="H331" s="8" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="I320" s="7" t="inlineStr">
+      <c r="I331" s="7" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="J320" s="7" t="inlineStr"/>
-      <c r="K320" s="7" t="inlineStr">
+      <c r="J331" s="7" t="inlineStr"/>
+      <c r="K331" s="7" t="inlineStr">
         <is>
           <t>• Client-side responsibility per RFP. Schedule the agency's VAPT 4 weeks before go-live.</t>
         </is>
       </c>
-      <c r="L320" s="7" t="inlineStr">
+      <c r="L331" s="7" t="inlineStr">
         <is>
           <t>VAPT report shows no Critical or High findings. Medium findings remediated or risk-accepted with sign-off.</t>
         </is>
       </c>
-      <c r="M320" s="7" t="inlineStr">
+      <c r="M331" s="7" t="inlineStr">
         <is>
           <t>Solution Doc Assumption: VAPT is client responsibility.</t>
         </is>
       </c>
-      <c r="N320" s="13" t="inlineStr">
+      <c r="N331" s="13" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="O320" s="7" t="inlineStr">
+      <c r="O331" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="P320" s="8" t="inlineStr"/>
-      <c r="Q320" s="7" t="inlineStr"/>
+      <c r="P331" s="8" t="inlineStr"/>
+      <c r="Q331" s="7" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q320"/>
+  <autoFilter ref="A1:Q331"/>
   <dataValidations count="2">
-    <dataValidation sqref="N2:N320" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N2:N331" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pass,Fail,Blocked,Not Run,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="P2:P320" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P2:P331" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Critical,High,Medium,Low"</formula1>
     </dataValidation>
   </dataValidations>
@@ -23281,22 +24153,35 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>(not in master — add as test case)</t>
+          <t>19. Dashboards</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-DB-EPS-006 · District→Block cascade filter is available on the dashboard</t>
+          <t>District → Block cascade filter present on the dashboard</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr"/>
-      <c r="G5" s="7" t="inlineStr"/>
-      <c r="H5" s="7" t="inlineStr"/>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>P0 — Blocker</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>• Open the Landscape / EP Status Monitor filter row.
+• Look for District + Block filters.</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>A District filter and a Block filter (cascading: Block.district = selected District) are present. (Verified UAT: NO District/Block filter on Landscape; Status Monitor link dead.)</t>
+        </is>
+      </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
           <t>Error: dashboard should expose a District (and cascading Block) filter
@@ -23310,7 +24195,11 @@
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\19-dashboard-filters-PR-TC-dcc9e--available-on-the-dashboard-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K5" s="7" t="inlineStr"/>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>BRD: District→Block cascade.</t>
+        </is>
+      </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
           <t>Open</t>
@@ -23332,12 +24221,12 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>(not in master — add as test case)</t>
+          <t>19. Dashboards</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-DB-EPS-007 · selecting a filter recomputes the KPI counts</t>
+          <t>Each filter recomputes all KPI counts</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -23345,9 +24234,22 @@
           <t>High</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr"/>
-      <c r="G6" s="7" t="inlineStr"/>
-      <c r="H6" s="7" t="inlineStr"/>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>P1 — High</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>• Note Total Entrepreneurs.
+• Apply Sector = Food Processing.</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>KPI counts recompute to the filtered subset (Total 40 → 13 verified). Label switches to Filtered.</t>
+        </is>
+      </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
           <t>Error: KPI should recompute on Sector filter (before=-1, after=-1)
@@ -23361,7 +24263,11 @@
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\19-dashboard-filters-PR-TC-7a839-r-recomputes-the-KPI-counts-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K6" s="7" t="inlineStr"/>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>BRD: filters recompute KPIs.</t>
+        </is>
+      </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
           <t>Open</t>
@@ -23383,12 +24289,12 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>(not in master — add as test case)</t>
+          <t>19. Dashboards</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-DB-MAP-001 · geo coordinates are captured; count cross-checks the GPS-Verified KPI</t>
+          <t>Geo coordinates captured; count cross-checks GPS-Verified KPI</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -23396,9 +24302,22 @@
           <t>High</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr"/>
-      <c r="G7" s="7" t="inlineStr"/>
-      <c r="H7" s="7" t="inlineStr"/>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>P1 — High</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>• Read EP.location (Geolocation) values via API.
+• Compare count-with-coords to the GPS-Verified KPI.</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>EPs with a captured location &gt; 0; GPS-Verified KPI ≤ count-with-coords. (Obs: KPI=6 vs 12 with location — confirm GPS-only vs incl. centroid.)</t>
+        </is>
+      </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
           <t>Error: GPS-Verified KPI should be a positive count
@@ -23412,7 +24331,11 @@
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\19-dashboard-maps-PR-TC-DB-c738a-checks-the-GPS-Verified-KPI-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K7" s="7" t="inlineStr"/>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>BRD: geo-tag capture.</t>
+        </is>
+      </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
           <t>Open</t>
@@ -23434,12 +24357,12 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>(not in master — add as test case)</t>
+          <t>19. Dashboards</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-DB-MAP-002 · Landscape map renders (Leaflet canvas + tiles)</t>
+          <t>Landscape map renders (Leaflet canvas + tiles)</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -23447,9 +24370,22 @@
           <t>High</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr"/>
-      <c r="G8" s="7" t="inlineStr"/>
-      <c r="H8" s="7" t="inlineStr"/>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>P1 — High</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>• Open the Landscape.
+• Inspect the map container.</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>Leaflet map renders with base tiles + canvas renderer (pins drawn on canvas). (Verified pass.)</t>
+        </is>
+      </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
           <t>Error: Leaflet map container present
@@ -23463,7 +24399,11 @@
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\19-dashboard-maps-PR-TC-DB-b4e39-nders-Leaflet-canvas-tiles--sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K8" s="7" t="inlineStr"/>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>BRD: map renders.</t>
+        </is>
+      </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
           <t>Open</t>
@@ -23485,12 +24425,12 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>(not in master — add as test case)</t>
+          <t>19. Dashboards</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-DB-MAP-003 · Meghalaya boundary overlay is rendered</t>
+          <t>Meghalaya boundary overlay rendered</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -23498,9 +24438,21 @@
           <t>High</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr"/>
-      <c r="G9" s="7" t="inlineStr"/>
-      <c r="H9" s="7" t="inlineStr"/>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>P1 — High</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>• Open the Landscape map.</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>State boundary overlay (svg/canvas) renders around Meghalaya. (Verified pass.)</t>
+        </is>
+      </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
           <t>Error: state boundary overlay (svg path or canvas) should render
@@ -23514,7 +24466,11 @@
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\19-dashboard-maps-PR-TC-DB-14a33-oundary-overlay-is-rendered-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K9" s="7" t="inlineStr"/>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>BRD: map boundaries.</t>
+        </is>
+      </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
           <t>Open</t>
@@ -23536,22 +24492,35 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>(not in master — add as test case)</t>
+          <t>19. Dashboards</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-DB-MAP-005 · captured coordinates fall within Meghalaya bounds (geo validation)</t>
+          <t>Captured coordinates fall within Meghalaya bounds</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr"/>
-      <c r="G10" s="7" t="inlineStr"/>
-      <c r="H10" s="7" t="inlineStr"/>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>P0 — Blocker</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>• Read EP.location GeoJSON coords.
+• Check each lat/lng against Meghalaya bounds (lat 25.0–26.2, lng 89.8–92.9).</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>All coords within Meghalaya. (Verified UAT: only 1 of parseable coords in-state; default Mountain View CA + Delhi + malformed GeoJSON — finding.)</t>
+        </is>
+      </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
           <t>Error: all geo-tags must be valid Meghalaya coords; 5 out-of-bounds (37.422,-122.084 ; 28.452,77.072 ; 28.623,77.218) + 6 malformed GeoJSON
@@ -23561,7 +24530,11 @@
         </is>
       </c>
       <c r="J10" s="7" t="inlineStr"/>
-      <c r="K10" s="7" t="inlineStr"/>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>BRD: coordinate validation / map boundaries.</t>
+        </is>
+      </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
           <t>Open</t>
@@ -23583,12 +24556,12 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>(not in master — add as test case)</t>
+          <t>19. Dashboards</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Status Monitor nav link routes to the EP status view</t>
+          <t>Status Monitor sidebar link routes to the EP status view</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -23596,16 +24569,32 @@
           <t>High</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr"/>
-      <c r="G11" s="7" t="inlineStr"/>
-      <c r="H11" s="7" t="inlineStr"/>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>P1 — High</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>• Click the "Status Monitor" item in the sidebar.</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>Navigates to the EP Status Monitor view. (Verified UAT: link has href=null, does not navigate — dead link.)</t>
+        </is>
+      </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
           <t>Sidebar 'Status Monitor' link has href=null and clicking it does not navigate (dead/placeholder link). The District/Block-filtered status-monitor view appears not to be wired in the /primerural SPA.</t>
         </is>
       </c>
       <c r="J11" s="7" t="inlineStr"/>
-      <c r="K11" s="7" t="inlineStr"/>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>BRD: Status Monitor nav.</t>
+        </is>
+      </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
           <t>Open</t>
@@ -23627,12 +24616,12 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>(not in master — add as test case)</t>
+          <t>19. Dashboards</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-DB-VIS-001 · Village Visits mode updates KPIs to village-visit context (GPS pin count)</t>
+          <t>Village Visits map mode re-scopes KPIs to village-visit GPS pins</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -23640,9 +24629,22 @@
           <t>High</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr"/>
-      <c r="G12" s="7" t="inlineStr"/>
-      <c r="H12" s="7" t="inlineStr"/>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>P1 — High</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>• On the Landscape, toggle the map mode to Village Visits.
+• Inspect the KPI cards (esp. GPS Verified).</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>KPIs reflect village-visit data — GPS Verified shows the village-visit GPS-pin count, not the entrepreneur count. (Verified UAT: KPIs stay entrepreneur-scoped — finding.)</t>
+        </is>
+      </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
           <t>TimeoutError: locator.click: Timeout 15000ms exceeded.
@@ -23655,7 +24657,11 @@
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\19-dashboard-filters-PR-TC-1d640-isit-context-GPS-pin-count--sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K12" s="7" t="inlineStr"/>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>BRD/req: GPS Verified per active map mode.</t>
+        </is>
+      </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
           <t>Open</t>

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -18822,9 +18822,9 @@
       </c>
       <c r="L257" s="7" t="inlineStr"/>
       <c r="M257" s="7" t="inlineStr"/>
-      <c r="N257" s="13" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+      <c r="N257" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O257" s="7" t="inlineStr">
@@ -18889,17 +18889,21 @@
       </c>
       <c r="L258" s="7" t="inlineStr"/>
       <c r="M258" s="7" t="inlineStr"/>
-      <c r="N258" s="13" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+      <c r="N258" s="12" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
       <c r="O258" s="7" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="P258" s="8" t="inlineStr"/>
+          <t>Cert Status field = Received/Not Yet Received/Rejected (+ validity date), NOT an Active/Expired status — so the spec premise "cannot mark an expired cert Active" does not map. Setting a PAST Valid Till date (2025-01-01) showed NO expiry warning/flag. Confirm: should expired certs be flagged/blocked?</t>
+        </is>
+      </c>
+      <c r="P258" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="Q258" s="7" t="inlineStr"/>
     </row>
     <row r="259">
@@ -23936,7 +23940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N60"/>
+  <dimension ref="A1:N61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -25056,7 +25060,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-FW-QC-001</t>
+          <t>PR-TC-FW-PC-002</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -25066,7 +25070,7 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Fill all 23 stars; total score auto-computes</t>
+          <t>Expired cert: cannot mark Active</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -25081,13 +25085,13 @@
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>• Set all 23 questions to 4 stars (out of 5).</t>
+          <t>• Add cert with Valid till = yesterday, Status = Active.</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr"/>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>QC EXISTING uses an "+ Add Item" checklist with a 4-LEVEL rating (0/33/66/100) and AVERAGE SCORE (%), NOT the BRD spec of 23 fixed stars totalling /115 (e.g. 92/115=80%). Items are manually added (not pre-loaded). Confirm whether 23 standard items should pre-load + whether the scoring model should match spec.</t>
+          <t>Cert Status field = Received/Not Yet Received/Rejected (+ validity date), NOT an Active/Expired status — so the spec premise "cannot mark an expired cert Active" does not map. Setting a PAST Valid Till date (2025-01-01) showed NO expiry warning/flag. Confirm: should expired certs be flagged/blocked?</t>
         </is>
       </c>
       <c r="J19" s="7" t="inlineStr"/>
@@ -25108,7 +25112,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-FW-TEST-001</t>
+          <t>PR-TC-FW-QC-001</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -25118,7 +25122,7 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Date chain: Sent ≤ Received ≤ Reported enforced</t>
+          <t>Fill all 23 stars; total score auto-computes</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
@@ -25133,13 +25137,13 @@
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>• Sent = 10-Apr, Received = 5-Apr.</t>
+          <t>• Set all 23 questions to 4 stars (out of 5).</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr"/>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>UI form-fill: set Date of Sample Deposit to Office = 2026-06-15 and to Lab = 2026-06-01 (lab BEFORE office, out of order). NO date-order validation/warning fired (live). Spec expects rejection (Received must be on/after Sent). Confirm save-time enforcement.</t>
+          <t>QC EXISTING uses an "+ Add Item" checklist with a 4-LEVEL rating (0/33/66/100) and AVERAGE SCORE (%), NOT the BRD spec of 23 fixed stars totalling /115 (e.g. 92/115=80%). Items are manually added (not pre-loaded). Confirm whether 23 standard items should pre-load + whether the scoring model should match spec.</t>
         </is>
       </c>
       <c r="J20" s="7" t="inlineStr"/>
@@ -25160,17 +25164,17 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-FW-UP-003</t>
+          <t>PR-TC-FW-TEST-001</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>(not in master — add as test case)</t>
+          <t>17. The 27 Diagnostic Frameworks</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Unit Pricing tab structure inconsistent (TASKS tab, no Log Book)</t>
+          <t>Date chain: Sent ≤ Received ≤ Reported enforced</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
@@ -25178,12 +25182,20 @@
           <t>High</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr"/>
-      <c r="G21" s="7" t="inlineStr"/>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>P1 — High</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>• Sent = 10-Apr, Received = 5-Apr.</t>
+        </is>
+      </c>
       <c r="H21" s="7" t="inlineStr"/>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>Unit Pricing form tabs = DETAILS/EXISTING/REQUIRED/LINE ITEMS/TASKS/RESOURCES — it has a TASKS tab and NO LOG BOOK, unlike the other 26 frameworks (which show LOG BOOK). Contradicts the BRD decision: Task tab removed from framework forms; Log Book remains.</t>
+          <t>UI form-fill: set Date of Sample Deposit to Office = 2026-06-15 and to Lab = 2026-06-01 (lab BEFORE office, out of order). NO date-order validation/warning fired (live). Spec expects rejection (Received must be on/after Sent). Confirm save-time enforcement.</t>
         </is>
       </c>
       <c r="J21" s="7" t="inlineStr"/>
@@ -25204,7 +25216,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-FWC-BPC-002</t>
+          <t>PR-TC-FW-UP-003</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -25214,7 +25226,7 @@
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-FWC-BPC-002 · Business Plan Canvas header has no raw doctype / UUID</t>
+          <t>Unit Pricing tab structure inconsistent (TASKS tab, no Log Book)</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
@@ -25226,6 +25238,50 @@
       <c r="G22" s="7" t="inlineStr"/>
       <c r="H22" s="7" t="inlineStr"/>
       <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>Unit Pricing form tabs = DETAILS/EXISTING/REQUIRED/LINE ITEMS/TASKS/RESOURCES — it has a TASKS tab and NO LOG BOOK, unlike the other 26 frameworks (which show LOG BOOK). Contradicts the BRD decision: Task tab removed from framework forms; Log Book remains.</t>
+        </is>
+      </c>
+      <c r="J22" s="7" t="inlineStr"/>
+      <c r="K22" s="7" t="inlineStr"/>
+      <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M22" s="7" t="inlineStr"/>
+      <c r="N22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>BUG-021</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-FWC-BPC-002</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>(not in master — add as test case)</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-FWC-BPC-002 · Business Plan Canvas header has no raw doctype / UUID</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr"/>
+      <c r="G23" s="7" t="inlineStr"/>
+      <c r="H23" s="7" t="inlineStr"/>
+      <c r="I23" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Business Plan Canvas: {"doctype-df-prefix":["DF BUSINESS"]}
 expect.toEqual // deep equality
@@ -25239,50 +25295,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J22" s="7" t="inlineStr">
+      <c r="J23" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Bu-a8fd3-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K22" s="7" t="inlineStr"/>
-      <c r="L22" s="7" t="inlineStr">
+      <c r="K23" s="7" t="inlineStr"/>
+      <c r="L23" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M22" s="7" t="inlineStr"/>
-      <c r="N22" s="7" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>BUG-021</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="M23" s="7" t="inlineStr"/>
+      <c r="N23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>BUG-022</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-BREG-002</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-BREG-002 · Business Registration header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F23" s="7" t="inlineStr"/>
-      <c r="G23" s="7" t="inlineStr"/>
-      <c r="H23" s="7" t="inlineStr"/>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="F24" s="7" t="inlineStr"/>
+      <c r="G24" s="7" t="inlineStr"/>
+      <c r="H24" s="7" t="inlineStr"/>
+      <c r="I24" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Business Registration: {"doctype-df-prefix":["DF BUSINESS"]}
 expect.toEqual // deep equality
@@ -25296,50 +25352,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J23" s="7" t="inlineStr">
+      <c r="J24" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Bu-6c730-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K23" s="7" t="inlineStr"/>
-      <c r="L23" s="7" t="inlineStr">
+      <c r="K24" s="7" t="inlineStr"/>
+      <c r="L24" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M23" s="7" t="inlineStr"/>
-      <c r="N23" s="7" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>BUG-022</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="M24" s="7" t="inlineStr"/>
+      <c r="N24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>BUG-023</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-CA-002</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-CA-002 · Customer Analysis header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr"/>
-      <c r="G24" s="7" t="inlineStr"/>
-      <c r="H24" s="7" t="inlineStr"/>
-      <c r="I24" s="7" t="inlineStr">
+      <c r="F25" s="7" t="inlineStr"/>
+      <c r="G25" s="7" t="inlineStr"/>
+      <c r="H25" s="7" t="inlineStr"/>
+      <c r="I25" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Customer Analysis: {"doctype-df-prefix":["DF CUSTOMER"]}
 expect.toEqual // deep equality
@@ -25353,50 +25409,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J24" s="7" t="inlineStr">
+      <c r="J25" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Cu-6ed58-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K24" s="7" t="inlineStr"/>
-      <c r="L24" s="7" t="inlineStr">
+      <c r="K25" s="7" t="inlineStr"/>
+      <c r="L25" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M24" s="7" t="inlineStr"/>
-      <c r="N24" s="7" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>BUG-023</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="M25" s="7" t="inlineStr"/>
+      <c r="N25" s="7" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>BUG-024</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-CB-002</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-CB-002 · Capacity Building header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="E26" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F25" s="7" t="inlineStr"/>
-      <c r="G25" s="7" t="inlineStr"/>
-      <c r="H25" s="7" t="inlineStr"/>
-      <c r="I25" s="7" t="inlineStr">
+      <c r="F26" s="7" t="inlineStr"/>
+      <c r="G26" s="7" t="inlineStr"/>
+      <c r="H26" s="7" t="inlineStr"/>
+      <c r="I26" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Capacity Building: {"doctype-df-prefix":["DF CAPACITY"]}
 expect.toEqual // deep equality
@@ -25410,50 +25466,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J25" s="7" t="inlineStr">
+      <c r="J26" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Ca-83199-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K25" s="7" t="inlineStr"/>
-      <c r="L25" s="7" t="inlineStr">
+      <c r="K26" s="7" t="inlineStr"/>
+      <c r="L26" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M25" s="7" t="inlineStr"/>
-      <c r="N25" s="7" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>BUG-024</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="M26" s="7" t="inlineStr"/>
+      <c r="N26" s="7" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>BUG-025</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-DL-002</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-DL-002 · Digital Literacy header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F26" s="7" t="inlineStr"/>
-      <c r="G26" s="7" t="inlineStr"/>
-      <c r="H26" s="7" t="inlineStr"/>
-      <c r="I26" s="7" t="inlineStr">
+      <c r="F27" s="7" t="inlineStr"/>
+      <c r="G27" s="7" t="inlineStr"/>
+      <c r="H27" s="7" t="inlineStr"/>
+      <c r="I27" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Digital Literacy: {"doctype-df-prefix":["DF DIGITAL"]}
 expect.toEqual // deep equality
@@ -25467,50 +25523,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J26" s="7" t="inlineStr">
+      <c r="J27" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Di-845ef-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K26" s="7" t="inlineStr"/>
-      <c r="L26" s="7" t="inlineStr">
+      <c r="K27" s="7" t="inlineStr"/>
+      <c r="L27" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M26" s="7" t="inlineStr"/>
-      <c r="N26" s="7" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>BUG-025</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="M27" s="7" t="inlineStr"/>
+      <c r="N27" s="7" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>BUG-026</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-INFR-002</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-INFR-002 · Infrastructure (BE/EE/CE) header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr"/>
-      <c r="G27" s="7" t="inlineStr"/>
-      <c r="H27" s="7" t="inlineStr"/>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="F28" s="7" t="inlineStr"/>
+      <c r="G28" s="7" t="inlineStr"/>
+      <c r="H28" s="7" t="inlineStr"/>
+      <c r="I28" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Infrastructure: {"doctype-df-prefix":["DF INFRASTRUCTURE"]}
 expect.toEqual // deep equality
@@ -25524,50 +25580,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J27" s="7" t="inlineStr">
+      <c r="J28" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-In-3328d-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K27" s="7" t="inlineStr"/>
-      <c r="L27" s="7" t="inlineStr">
+      <c r="K28" s="7" t="inlineStr"/>
+      <c r="L28" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M27" s="7" t="inlineStr"/>
-      <c r="N27" s="7" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>BUG-026</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="M28" s="7" t="inlineStr"/>
+      <c r="N28" s="7" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>BUG-027</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-LABL-002</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-LABL-002 · Marketing Label header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr"/>
-      <c r="G28" s="7" t="inlineStr"/>
-      <c r="H28" s="7" t="inlineStr"/>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="F29" s="7" t="inlineStr"/>
+      <c r="G29" s="7" t="inlineStr"/>
+      <c r="H29" s="7" t="inlineStr"/>
+      <c r="I29" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Marketing Label: {"doctype-df-prefix":["DF MARKETING"]}
 expect.toEqual // deep equality
@@ -25581,50 +25637,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J28" s="7" t="inlineStr">
+      <c r="J29" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Ma-11834-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K28" s="7" t="inlineStr"/>
-      <c r="L28" s="7" t="inlineStr">
+      <c r="K29" s="7" t="inlineStr"/>
+      <c r="L29" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M28" s="7" t="inlineStr"/>
-      <c r="N28" s="7" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>BUG-027</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="M29" s="7" t="inlineStr"/>
+      <c r="N29" s="7" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>BUG-028</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-ML-002</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-ML-002 · Market Linkage header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="E30" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr"/>
-      <c r="G29" s="7" t="inlineStr"/>
-      <c r="H29" s="7" t="inlineStr"/>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="F30" s="7" t="inlineStr"/>
+      <c r="G30" s="7" t="inlineStr"/>
+      <c r="H30" s="7" t="inlineStr"/>
+      <c r="I30" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Market Linkage: {"doctype-df-prefix":["DF MARKET"]}
 expect.toEqual // deep equality
@@ -25638,50 +25694,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J29" s="7" t="inlineStr">
+      <c r="J30" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Ma-22f69-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K29" s="7" t="inlineStr"/>
-      <c r="L29" s="7" t="inlineStr">
+      <c r="K30" s="7" t="inlineStr"/>
+      <c r="L30" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M29" s="7" t="inlineStr"/>
-      <c r="N29" s="7" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>BUG-028</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="M30" s="7" t="inlineStr"/>
+      <c r="N30" s="7" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>BUG-029</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-MR-002</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-MR-002 · Market Research header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="E31" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr"/>
-      <c r="G30" s="7" t="inlineStr"/>
-      <c r="H30" s="7" t="inlineStr"/>
-      <c r="I30" s="7" t="inlineStr">
+      <c r="F31" s="7" t="inlineStr"/>
+      <c r="G31" s="7" t="inlineStr"/>
+      <c r="H31" s="7" t="inlineStr"/>
+      <c r="I31" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Market Research: {"doctype-df-prefix":["DF MARKET"]}
 expect.toEqual // deep equality
@@ -25695,50 +25751,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J30" s="7" t="inlineStr">
+      <c r="J31" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Ma-6eb23-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K30" s="7" t="inlineStr"/>
-      <c r="L30" s="7" t="inlineStr">
+      <c r="K31" s="7" t="inlineStr"/>
+      <c r="L31" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M30" s="7" t="inlineStr"/>
-      <c r="N30" s="7" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>BUG-029</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="M31" s="7" t="inlineStr"/>
+      <c r="N31" s="7" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>BUG-030</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PCMP-002</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PCMP-002 · Product Compliance header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="E32" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr"/>
-      <c r="G31" s="7" t="inlineStr"/>
-      <c r="H31" s="7" t="inlineStr"/>
-      <c r="I31" s="7" t="inlineStr">
+      <c r="F32" s="7" t="inlineStr"/>
+      <c r="G32" s="7" t="inlineStr"/>
+      <c r="H32" s="7" t="inlineStr"/>
+      <c r="I32" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Product Compliance: {"doctype-df-prefix":["DF PRODUCT"]}
 expect.toEqual // deep equality
@@ -25752,50 +25808,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J31" s="7" t="inlineStr">
+      <c r="J32" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Pr-be46f-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K31" s="7" t="inlineStr"/>
-      <c r="L31" s="7" t="inlineStr">
+      <c r="K32" s="7" t="inlineStr"/>
+      <c r="L32" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M31" s="7" t="inlineStr"/>
-      <c r="N31" s="7" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>BUG-030</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="M32" s="7" t="inlineStr"/>
+      <c r="N32" s="7" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>BUG-031</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PROM-002</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D33" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PROM-002 · Promotional Marketing header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
+      <c r="E33" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F32" s="7" t="inlineStr"/>
-      <c r="G32" s="7" t="inlineStr"/>
-      <c r="H32" s="7" t="inlineStr"/>
-      <c r="I32" s="7" t="inlineStr">
+      <c r="F33" s="7" t="inlineStr"/>
+      <c r="G33" s="7" t="inlineStr"/>
+      <c r="H33" s="7" t="inlineStr"/>
+      <c r="I33" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Promotional Marketing: {"doctype-df-prefix":["DF PROMOTIONAL"]}
 expect.toEqual // deep equality
@@ -25809,50 +25865,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J32" s="7" t="inlineStr">
+      <c r="J33" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Pr-d8d12-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K32" s="7" t="inlineStr"/>
-      <c r="L32" s="7" t="inlineStr">
+      <c r="K33" s="7" t="inlineStr"/>
+      <c r="L33" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M32" s="7" t="inlineStr"/>
-      <c r="N32" s="7" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>BUG-031</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="M33" s="7" t="inlineStr"/>
+      <c r="N33" s="7" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>BUG-032</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PROT-002</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PROT-002 · Product Prototyping header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
+      <c r="E34" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F33" s="7" t="inlineStr"/>
-      <c r="G33" s="7" t="inlineStr"/>
-      <c r="H33" s="7" t="inlineStr"/>
-      <c r="I33" s="7" t="inlineStr">
+      <c r="F34" s="7" t="inlineStr"/>
+      <c r="G34" s="7" t="inlineStr"/>
+      <c r="H34" s="7" t="inlineStr"/>
+      <c r="I34" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Product Prototyping: {"doctype-df-prefix":["DF PRODUCT"]}
 expect.toEqual // deep equality
@@ -25866,50 +25922,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J33" s="7" t="inlineStr">
+      <c r="J34" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Pr-1120e-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K33" s="7" t="inlineStr"/>
-      <c r="L33" s="7" t="inlineStr">
+      <c r="K34" s="7" t="inlineStr"/>
+      <c r="L34" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M33" s="7" t="inlineStr"/>
-      <c r="N33" s="7" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>BUG-032</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="M34" s="7" t="inlineStr"/>
+      <c r="N34" s="7" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>BUG-033</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PTCH-002</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PTCH-002 · Pitch Deck header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E34" s="7" t="inlineStr">
+      <c r="E35" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F34" s="7" t="inlineStr"/>
-      <c r="G34" s="7" t="inlineStr"/>
-      <c r="H34" s="7" t="inlineStr"/>
-      <c r="I34" s="7" t="inlineStr">
+      <c r="F35" s="7" t="inlineStr"/>
+      <c r="G35" s="7" t="inlineStr"/>
+      <c r="H35" s="7" t="inlineStr"/>
+      <c r="I35" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Pitch Deck: {"doctype-df-prefix":["DF PITCH"]}
 expect.toEqual // deep equality
@@ -25923,50 +25979,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J34" s="7" t="inlineStr">
+      <c r="J35" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Pi-fefd5-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K34" s="7" t="inlineStr"/>
-      <c r="L34" s="7" t="inlineStr">
+      <c r="K35" s="7" t="inlineStr"/>
+      <c r="L35" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M34" s="7" t="inlineStr"/>
-      <c r="N34" s="7" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>BUG-033</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="M35" s="7" t="inlineStr"/>
+      <c r="N35" s="7" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>BUG-034</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PTST-002</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-PTST-002 · Product Testing header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F35" s="7" t="inlineStr"/>
-      <c r="G35" s="7" t="inlineStr"/>
-      <c r="H35" s="7" t="inlineStr"/>
-      <c r="I35" s="7" t="inlineStr">
+      <c r="F36" s="7" t="inlineStr"/>
+      <c r="G36" s="7" t="inlineStr"/>
+      <c r="H36" s="7" t="inlineStr"/>
+      <c r="I36" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Product Testing: {"doctype-df-prefix":["DF PRODUCT"]}
 expect.toEqual // deep equality
@@ -25980,50 +26036,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J35" s="7" t="inlineStr">
+      <c r="J36" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Pr-3e912-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K35" s="7" t="inlineStr"/>
-      <c r="L35" s="7" t="inlineStr">
+      <c r="K36" s="7" t="inlineStr"/>
+      <c r="L36" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M35" s="7" t="inlineStr"/>
-      <c r="N35" s="7" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>BUG-034</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="M36" s="7" t="inlineStr"/>
+      <c r="N36" s="7" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>BUG-035</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-QC-002</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-QC-002 · Quality Control header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F36" s="7" t="inlineStr"/>
-      <c r="G36" s="7" t="inlineStr"/>
-      <c r="H36" s="7" t="inlineStr"/>
-      <c r="I36" s="7" t="inlineStr">
+      <c r="F37" s="7" t="inlineStr"/>
+      <c r="G37" s="7" t="inlineStr"/>
+      <c r="H37" s="7" t="inlineStr"/>
+      <c r="I37" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Quality Control: {"doctype-df-prefix":["DF QUALITY"]}
 expect.toEqual // deep equality
@@ -26037,50 +26093,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J36" s="7" t="inlineStr">
+      <c r="J37" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Qu-ae31c-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K36" s="7" t="inlineStr"/>
-      <c r="L36" s="7" t="inlineStr">
+      <c r="K37" s="7" t="inlineStr"/>
+      <c r="L37" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M36" s="7" t="inlineStr"/>
-      <c r="N36" s="7" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>BUG-035</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="M37" s="7" t="inlineStr"/>
+      <c r="N37" s="7" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>BUG-036</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-SCHM-002</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-SCHM-002 · Schemes &amp; Funding header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
+      <c r="E38" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F37" s="7" t="inlineStr"/>
-      <c r="G37" s="7" t="inlineStr"/>
-      <c r="H37" s="7" t="inlineStr"/>
-      <c r="I37" s="7" t="inlineStr">
+      <c r="F38" s="7" t="inlineStr"/>
+      <c r="G38" s="7" t="inlineStr"/>
+      <c r="H38" s="7" t="inlineStr"/>
+      <c r="I38" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Schemes &amp; Funding: {"doctype-df-prefix":["DF SCHEMES"]}
 expect.toEqual // deep equality
@@ -26094,50 +26150,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J37" s="7" t="inlineStr">
+      <c r="J38" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Sc-67cb2-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K37" s="7" t="inlineStr"/>
-      <c r="L37" s="7" t="inlineStr">
+      <c r="K38" s="7" t="inlineStr"/>
+      <c r="L38" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M37" s="7" t="inlineStr"/>
-      <c r="N37" s="7" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>BUG-036</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="M38" s="7" t="inlineStr"/>
+      <c r="N38" s="7" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>BUG-037</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-STD-002</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
+      <c r="C39" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D38" s="7" t="inlineStr">
+      <c r="D39" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-STD-002 · Standardization header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E38" s="7" t="inlineStr">
+      <c r="E39" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F38" s="7" t="inlineStr"/>
-      <c r="G38" s="7" t="inlineStr"/>
-      <c r="H38" s="7" t="inlineStr"/>
-      <c r="I38" s="7" t="inlineStr">
+      <c r="F39" s="7" t="inlineStr"/>
+      <c r="G39" s="7" t="inlineStr"/>
+      <c r="H39" s="7" t="inlineStr"/>
+      <c r="I39" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Standardization: {"doctype-df-prefix":["DF STANDARDIZATION"]}
 expect.toEqual // deep equality
@@ -26151,50 +26207,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J38" s="7" t="inlineStr">
+      <c r="J39" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-St-b8b93-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K38" s="7" t="inlineStr"/>
-      <c r="L38" s="7" t="inlineStr">
+      <c r="K39" s="7" t="inlineStr"/>
+      <c r="L39" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M38" s="7" t="inlineStr"/>
-      <c r="N38" s="7" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>BUG-037</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="M39" s="7" t="inlineStr"/>
+      <c r="N39" s="7" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>BUG-038</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-UP-002</t>
         </is>
       </c>
-      <c r="C39" s="7" t="inlineStr">
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D39" s="7" t="inlineStr">
+      <c r="D40" s="7" t="inlineStr">
         <is>
           <t>PR-TC-FWC-UP-002 · Unit Pricing header has no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E39" s="7" t="inlineStr">
+      <c r="E40" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F39" s="7" t="inlineStr"/>
-      <c r="G39" s="7" t="inlineStr"/>
-      <c r="H39" s="7" t="inlineStr"/>
-      <c r="I39" s="7" t="inlineStr">
+      <c r="F40" s="7" t="inlineStr"/>
+      <c r="G40" s="7" t="inlineStr"/>
+      <c r="H40" s="7" t="inlineStr"/>
+      <c r="I40" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on Unit Pricing: {"doctype-df-prefix":["DF UNIT"]}
 expect.toEqual // deep equality
@@ -26208,58 +26264,58 @@
 + }</t>
         </is>
       </c>
-      <c r="J39" s="7" t="inlineStr">
+      <c r="J40" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\17-frameworks-Framework-Un-0c652-der-has-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K39" s="7" t="inlineStr"/>
-      <c r="L39" s="7" t="inlineStr">
+      <c r="K40" s="7" t="inlineStr"/>
+      <c r="L40" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M39" s="7" t="inlineStr"/>
-      <c r="N39" s="7" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>BUG-038</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="M40" s="7" t="inlineStr"/>
+      <c r="N40" s="7" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>BUG-039</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>PR-TC-MS-008</t>
         </is>
       </c>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
         <is>
           <t>14. Masters &amp; Reference Data</t>
         </is>
       </c>
-      <c r="D40" s="7" t="inlineStr">
+      <c r="D41" s="7" t="inlineStr">
         <is>
           <t>Cohort end date must be after start date</t>
         </is>
       </c>
-      <c r="E40" s="7" t="inlineStr">
+      <c r="E41" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F40" s="7" t="inlineStr">
+      <c r="F41" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G40" s="7" t="inlineStr">
+      <c r="G41" s="7" t="inlineStr">
         <is>
           <t>• Start = 01-Apr-2026, End = 31-Mar-2025.</t>
         </is>
       </c>
-      <c r="H40" s="7" t="inlineStr"/>
-      <c r="I40" s="7" t="inlineStr">
+      <c r="H41" s="7" t="inlineStr"/>
+      <c r="I41" s="7" t="inlineStr">
         <is>
           <t>Error: end-before-start cohort should be rejected
 expect(received).toBeGreaterThanOrEqual(expected)
@@ -26267,59 +26323,59 @@
 Received:    200</t>
         </is>
       </c>
-      <c r="J40" s="7" t="inlineStr"/>
-      <c r="K40" s="7" t="inlineStr"/>
-      <c r="L40" s="7" t="inlineStr">
+      <c r="J41" s="7" t="inlineStr"/>
+      <c r="K41" s="7" t="inlineStr"/>
+      <c r="L41" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M40" s="7" t="inlineStr"/>
-      <c r="N40" s="7" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>BUG-039</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
+      <c r="M41" s="7" t="inlineStr"/>
+      <c r="N41" s="7" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>BUG-040</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>PR-TC-MS-011</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="C42" s="7" t="inlineStr">
         <is>
           <t>14. Masters &amp; Reference Data</t>
         </is>
       </c>
-      <c r="D41" s="7" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
         <is>
           <t>Seed import: 351 rows from "Final PRIME Rural Task Dropdowns Master.xlsx"</t>
         </is>
       </c>
-      <c r="E41" s="7" t="inlineStr">
+      <c r="E42" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F41" s="7" t="inlineStr">
+      <c r="F42" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G41" s="7" t="inlineStr">
+      <c r="G42" s="7" t="inlineStr">
         <is>
           <t>• Run the seed migration script (or use bulk import) using the canonical xlsx.
 • Verify count = 351.</t>
         </is>
       </c>
-      <c r="H41" s="7" t="inlineStr">
+      <c r="H42" s="7" t="inlineStr">
         <is>
           <t>351 Framework Task Master records exist. Each has: module, framework, task_no, task_name, description, phase. Em-dash phase rows have phase = "Other". Logistic Service has its "Other" row added (was missing in the xlsx).</t>
         </is>
       </c>
-      <c r="I41" s="7" t="inlineStr">
+      <c r="I42" s="7" t="inlineStr">
         <is>
           <t>Error: Framework Task Master doctype should exist
 expect(received).toBe(expected) // Object.is equality
@@ -26327,58 +26383,58 @@
 Received: 404</t>
         </is>
       </c>
-      <c r="J41" s="7" t="inlineStr"/>
-      <c r="K41" s="7" t="inlineStr">
+      <c r="J42" s="7" t="inlineStr"/>
+      <c r="K42" s="7" t="inlineStr">
         <is>
           <t>BRD PR-XC-002b.</t>
         </is>
       </c>
-      <c r="L41" s="7" t="inlineStr">
+      <c r="L42" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M41" s="7" t="inlineStr"/>
-      <c r="N41" s="7" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>BUG-040</t>
-        </is>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="M42" s="7" t="inlineStr"/>
+      <c r="N42" s="7" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>BUG-041</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>PR-TC-MS-015</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C43" s="7" t="inlineStr">
         <is>
           <t>14. Masters &amp; Reference Data</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D43" s="7" t="inlineStr">
         <is>
           <t>Document types: Aadhaar, PAN, EPIC, Bank Passbook, Photo, Other</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="E43" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F42" s="7" t="inlineStr">
+      <c r="F43" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G42" s="7" t="inlineStr">
+      <c r="G43" s="7" t="inlineStr">
         <is>
           <t>• Masters → Document Master → list.</t>
         </is>
       </c>
-      <c r="H42" s="7" t="inlineStr"/>
-      <c r="I42" s="7" t="inlineStr">
+      <c r="H43" s="7" t="inlineStr"/>
+      <c r="I43" s="7" t="inlineStr">
         <is>
           <t>Error: expected the standard document types (Aadhaar/PAN/EPIC/Bank/Photo/...)
 expect(received).toBeGreaterThanOrEqual(expected)
@@ -26386,58 +26442,58 @@
 Received:    5</t>
         </is>
       </c>
-      <c r="J42" s="7" t="inlineStr"/>
-      <c r="K42" s="7" t="inlineStr"/>
-      <c r="L42" s="7" t="inlineStr">
+      <c r="J43" s="7" t="inlineStr"/>
+      <c r="K43" s="7" t="inlineStr"/>
+      <c r="L43" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M42" s="7" t="inlineStr"/>
-      <c r="N42" s="7" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="7" t="inlineStr">
-        <is>
-          <t>BUG-041</t>
-        </is>
-      </c>
-      <c r="B43" s="7" t="inlineStr">
+      <c r="M43" s="7" t="inlineStr"/>
+      <c r="N43" s="7" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>BUG-042</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>PR-TC-MS-020</t>
         </is>
       </c>
-      <c r="C43" s="7" t="inlineStr">
+      <c r="C44" s="7" t="inlineStr">
         <is>
           <t>14. Masters &amp; Reference Data</t>
         </is>
       </c>
-      <c r="D43" s="7" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
         <is>
           <t>19 schemes pre-seeded (MOVCDNER, CGTMSE, NEHHDC, PGS-India Organic, etc.)</t>
         </is>
       </c>
-      <c r="E43" s="7" t="inlineStr">
+      <c r="E44" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F43" s="7" t="inlineStr">
+      <c r="F44" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G43" s="7" t="inlineStr">
+      <c r="G44" s="7" t="inlineStr">
         <is>
           <t>• Open Scheme Master list. Count rows.</t>
         </is>
       </c>
-      <c r="H43" s="7" t="inlineStr">
+      <c r="H44" s="7" t="inlineStr">
         <is>
           <t>19 schemes present per BRD m-schemes. Each has: name, type (Grant / Loan / Subsidy / Certification), eligibility, min/max amount, applicable sectors, interest rate (if loan).</t>
         </is>
       </c>
-      <c r="I43" s="7" t="inlineStr">
+      <c r="I44" s="7" t="inlineStr">
         <is>
           <t>Error: BRD m-schemes expects 19 pre-seeded schemes
 expect(received).toBeGreaterThanOrEqual(expected)
@@ -26445,104 +26501,104 @@
 Received:    3</t>
         </is>
       </c>
-      <c r="J43" s="7" t="inlineStr"/>
-      <c r="K43" s="7" t="inlineStr">
+      <c r="J44" s="7" t="inlineStr"/>
+      <c r="K44" s="7" t="inlineStr">
         <is>
           <t>BRD m-schemes.</t>
         </is>
       </c>
-      <c r="L43" s="7" t="inlineStr">
+      <c r="L44" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M43" s="7" t="inlineStr"/>
-      <c r="N43" s="7" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>BUG-042</t>
-        </is>
-      </c>
-      <c r="B44" s="7" t="inlineStr">
+      <c r="M44" s="7" t="inlineStr"/>
+      <c r="N44" s="7" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>BUG-043</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>PR-TC-SEC-005</t>
         </is>
       </c>
-      <c r="C44" s="7" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>23. Security — OWASP &amp; Beyond</t>
         </is>
       </c>
-      <c r="D44" s="7" t="inlineStr">
+      <c r="D45" s="7" t="inlineStr">
         <is>
           <t>Content-Security-Policy header set, restricts inline scripts</t>
         </is>
       </c>
-      <c r="E44" s="7" t="inlineStr">
+      <c r="E45" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F44" s="7" t="inlineStr">
+      <c r="F45" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G44" s="7" t="inlineStr">
+      <c r="G45" s="7" t="inlineStr">
         <is>
           <t>• Inspect response headers on /app/.</t>
         </is>
       </c>
-      <c r="H44" s="7" t="inlineStr"/>
-      <c r="I44" s="7" t="inlineStr">
+      <c r="H45" s="7" t="inlineStr"/>
+      <c r="I45" s="7" t="inlineStr">
         <is>
           <t>Error: CSP header should be set
 expect(received).toBeTruthy()
 Received: undefined</t>
         </is>
       </c>
-      <c r="J44" s="7" t="inlineStr"/>
-      <c r="K44" s="7" t="inlineStr"/>
-      <c r="L44" s="7" t="inlineStr">
+      <c r="J45" s="7" t="inlineStr"/>
+      <c r="K45" s="7" t="inlineStr"/>
+      <c r="L45" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M44" s="7" t="inlineStr"/>
-      <c r="N44" s="7" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="7" t="inlineStr">
-        <is>
-          <t>BUG-043</t>
-        </is>
-      </c>
-      <c r="B45" s="7" t="inlineStr">
+      <c r="M45" s="7" t="inlineStr"/>
+      <c r="N45" s="7" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>BUG-044</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>PR-TC-UI-LEAK-001</t>
         </is>
       </c>
-      <c r="C45" s="7" t="inlineStr">
+      <c r="C46" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D45" s="7" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
         <is>
           <t>PR-TC-UI-LEAK-001 · EP profile shows no raw doctype / UUID</t>
         </is>
       </c>
-      <c r="E45" s="7" t="inlineStr">
+      <c r="E46" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F45" s="7" t="inlineStr"/>
-      <c r="G45" s="7" t="inlineStr"/>
-      <c r="H45" s="7" t="inlineStr"/>
-      <c r="I45" s="7" t="inlineStr">
+      <c r="F46" s="7" t="inlineStr"/>
+      <c r="G46" s="7" t="inlineStr"/>
+      <c r="H46" s="7" t="inlineStr"/>
+      <c r="I46" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on EP profile: {"doctype-df-prefix":["DF PROGRESS"]}
 expect.toEqual // deep equality
@@ -26556,50 +26612,50 @@
 + }</t>
         </is>
       </c>
-      <c r="J45" s="7" t="inlineStr">
+      <c r="J46" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\08-ui-no-backend-leak-PR-T-d694f-e-shows-no-raw-doctype-UUID-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K45" s="7" t="inlineStr"/>
-      <c r="L45" s="7" t="inlineStr">
+      <c r="K46" s="7" t="inlineStr"/>
+      <c r="L46" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M45" s="7" t="inlineStr"/>
-      <c r="N45" s="7" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="7" t="inlineStr">
-        <is>
-          <t>BUG-044</t>
-        </is>
-      </c>
-      <c r="B46" s="7" t="inlineStr">
+      <c r="M46" s="7" t="inlineStr"/>
+      <c r="N46" s="7" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>BUG-045</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
         <is>
           <t>PR-TC-UI-LEAK-002</t>
         </is>
       </c>
-      <c r="C46" s="7" t="inlineStr">
+      <c r="C47" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D46" s="7" t="inlineStr">
+      <c r="D47" s="7" t="inlineStr">
         <is>
           <t>PR-TC-UI-LEAK-002 · new EP form header is a friendly label, not the raw doctype</t>
         </is>
       </c>
-      <c r="E46" s="7" t="inlineStr">
+      <c r="E47" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F46" s="7" t="inlineStr"/>
-      <c r="G46" s="7" t="inlineStr"/>
-      <c r="H46" s="7" t="inlineStr"/>
-      <c r="I46" s="7" t="inlineStr">
+      <c r="F47" s="7" t="inlineStr"/>
+      <c r="G47" s="7" t="inlineStr"/>
+      <c r="H47" s="7" t="inlineStr"/>
+      <c r="I47" s="7" t="inlineStr">
         <is>
           <t>Error: Backend identifiers visible on new EP form: {"enterprenur-internal":["Enterprenur"]}
 expect.toEqual // deep equality
@@ -26613,52 +26669,52 @@
 + }</t>
         </is>
       </c>
-      <c r="J46" s="7" t="inlineStr">
+      <c r="J47" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\08-ui-no-backend-leak-PR-T-215c4-y-label-not-the-raw-doctype-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K46" s="7" t="inlineStr"/>
-      <c r="L46" s="7" t="inlineStr">
+      <c r="K47" s="7" t="inlineStr"/>
+      <c r="L47" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M46" s="7" t="inlineStr"/>
-      <c r="N46" s="7" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="7" t="inlineStr">
-        <is>
-          <t>BUG-045</t>
-        </is>
-      </c>
-      <c r="B47" s="7" t="inlineStr">
+      <c r="M47" s="7" t="inlineStr"/>
+      <c r="N47" s="7" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>BUG-046</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
         <is>
           <t>PR-TC-UM-001</t>
         </is>
       </c>
-      <c r="C47" s="7" t="inlineStr">
+      <c r="C48" s="7" t="inlineStr">
         <is>
           <t>13. User Management</t>
         </is>
       </c>
-      <c r="D47" s="7" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr">
         <is>
           <t>Create a new Field Associate user with all required fields</t>
         </is>
       </c>
-      <c r="E47" s="7" t="inlineStr">
+      <c r="E48" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F47" s="7" t="inlineStr">
+      <c r="F48" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G47" s="7" t="inlineStr">
+      <c r="G48" s="7" t="inlineStr">
         <is>
           <t>• Navigate to User Management workspace → "+ New User".
 • Fill: Email = uat-fa-test01@dhwaniris.com, First Name = UAT, Last Name = FA-Test01, Phone = +91 9876543210.
@@ -26668,74 +26724,22 @@
 • Click Save.</t>
         </is>
       </c>
-      <c r="H47" s="7" t="inlineStr">
+      <c r="H48" s="7" t="inlineStr">
         <is>
           <t>Toast: "User created successfully." User row appears in list with status "Active" and "Welcome email sent". Email arrives at the address within 2 min containing a one-time password-set link. Audit log records the creation with timestamp + creator.</t>
         </is>
       </c>
-      <c r="I47" s="7" t="inlineStr">
+      <c r="I48" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: INSERT User → 417: {"exception":"frappe.exceptions.ValidationError: Error syncing User to User Manager: ('User Manager', 'uat-umc-79v3ss@dhwaniris.com', IntegrityError(1062, \"Duplicate entry '[uat]_crud_user' for key 'username'\"))","exc_type":"ValidationError","_exc_source":"dhwani_frappe_base (app)","exc":"[\"Traceback (most recent call last):\\n  File \\\"apps/frappe/frappe/model/base_document.py\\\", line 755, in db_insert\\n    name = frappe.db.sql(\\n    \\t\\\"\\\"\\\"INSERT INTO </t>
         </is>
       </c>
-      <c r="J47" s="7" t="inlineStr"/>
-      <c r="K47" s="7" t="inlineStr">
+      <c r="J48" s="7" t="inlineStr"/>
+      <c r="K48" s="7" t="inlineStr">
         <is>
           <t>BRD: PR-UJ-CTI §User Management.</t>
         </is>
       </c>
-      <c r="L47" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="M47" s="7" t="inlineStr"/>
-      <c r="N47" s="7" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="7" t="inlineStr">
-        <is>
-          <t>BUG-046</t>
-        </is>
-      </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>PR-TC-UM-009</t>
-        </is>
-      </c>
-      <c r="C48" s="7" t="inlineStr">
-        <is>
-          <t>13. User Management</t>
-        </is>
-      </c>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>Email must be lowercase and trimmed before save</t>
-        </is>
-      </c>
-      <c r="E48" s="7" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F48" s="7" t="inlineStr">
-        <is>
-          <t>P1 — High</t>
-        </is>
-      </c>
-      <c r="G48" s="7" t="inlineStr">
-        <is>
-          <t>• Enter email Test@Dhwaniris.COM (leading/trailing spaces, mixed case).</t>
-        </is>
-      </c>
-      <c r="H48" s="7" t="inlineStr"/>
-      <c r="I48" s="7" t="inlineStr">
-        <is>
-          <t>Error: INSERT User → 417: {"exception":"frappe.exceptions.ValidationError: Error syncing User to User Manager: ('User Manager', 'uat-umn-ztbfos@dhwaniris.com', IntegrityError(1062, \"Duplicate entry '[uat]_norm' for key 'username'\"))","exc_type":"ValidationError","_exc_source":"dhwani_frappe_base (app)","exc":"[\"Traceback (most recent call last):\\n  File \\\"apps/frappe/frappe/model/base_document.py\\\", line 755, in db_insert\\n    name = frappe.db.sql(\\n    \\t\\\"\\\"\\\"INSERT INTO `tab{</t>
-        </is>
-      </c>
-      <c r="J48" s="7" t="inlineStr"/>
-      <c r="K48" s="7" t="inlineStr"/>
       <c r="L48" s="7" t="inlineStr">
         <is>
           <t>Open</t>
@@ -26752,30 +26756,82 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
+          <t>PR-TC-UM-009</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>13. User Management</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>Email must be lowercase and trimmed before save</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>P1 — High</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>• Enter email Test@Dhwaniris.COM (leading/trailing spaces, mixed case).</t>
+        </is>
+      </c>
+      <c r="H49" s="7" t="inlineStr"/>
+      <c r="I49" s="7" t="inlineStr">
+        <is>
+          <t>Error: INSERT User → 417: {"exception":"frappe.exceptions.ValidationError: Error syncing User to User Manager: ('User Manager', 'uat-umn-ztbfos@dhwaniris.com', IntegrityError(1062, \"Duplicate entry '[uat]_norm' for key 'username'\"))","exc_type":"ValidationError","_exc_source":"dhwani_frappe_base (app)","exc":"[\"Traceback (most recent call last):\\n  File \\\"apps/frappe/frappe/model/base_document.py\\\", line 755, in db_insert\\n    name = frappe.db.sql(\\n    \\t\\\"\\\"\\\"INSERT INTO `tab{</t>
+        </is>
+      </c>
+      <c r="J49" s="7" t="inlineStr"/>
+      <c r="K49" s="7" t="inlineStr"/>
+      <c r="L49" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M49" s="7" t="inlineStr"/>
+      <c r="N49" s="7" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>BUG-048</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
           <t>PR-TC-UM-010</t>
         </is>
       </c>
-      <c r="C49" s="7" t="inlineStr">
+      <c r="C50" s="7" t="inlineStr">
         <is>
           <t>13. User Management</t>
         </is>
       </c>
-      <c r="D49" s="7" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
         <is>
           <t>Edit user phone, name, block — changes persist</t>
         </is>
       </c>
-      <c r="E49" s="7" t="inlineStr">
+      <c r="E50" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F49" s="7" t="inlineStr">
+      <c r="F50" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G49" s="7" t="inlineStr">
+      <c r="G50" s="7" t="inlineStr">
         <is>
           <t>• Open user uat-fa-test01.
 • Change First Name to "UAT-Updated".
@@ -26784,63 +26840,10 @@
 • Log out / log in as that user.</t>
         </is>
       </c>
-      <c r="H49" s="7" t="inlineStr"/>
-      <c r="I49" s="7" t="inlineStr">
-        <is>
-          <t>Error: INSERT User → 417: {"exception":"frappe.exceptions.ValidationError: Error syncing User to User Manager: ('User Manager', 'uat-ume-1c8bs5@dhwaniris.com', IntegrityError(1062, \"Duplicate entry '[uat]_before' for key 'username'\"))","exc_type":"ValidationError","_exc_source":"dhwani_frappe_base (app)","exc":"[\"Traceback (most recent call last):\\n  File \\\"apps/frappe/frappe/model/base_document.py\\\", line 755, in db_insert\\n    name = frappe.db.sql(\\n    \\t\\\"\\\"\\\"INSERT INTO `ta</t>
-        </is>
-      </c>
-      <c r="J49" s="7" t="inlineStr"/>
-      <c r="K49" s="7" t="inlineStr"/>
-      <c r="L49" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="M49" s="7" t="inlineStr"/>
-      <c r="N49" s="7" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="7" t="inlineStr">
-        <is>
-          <t>BUG-048</t>
-        </is>
-      </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>PR-TC-UM-011</t>
-        </is>
-      </c>
-      <c r="C50" s="7" t="inlineStr">
-        <is>
-          <t>13. User Management</t>
-        </is>
-      </c>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>Deactivate a user — they cannot log in until reactivated</t>
-        </is>
-      </c>
-      <c r="E50" s="7" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="F50" s="7" t="inlineStr">
-        <is>
-          <t>P0 — Blocker</t>
-        </is>
-      </c>
-      <c r="G50" s="7" t="inlineStr">
-        <is>
-          <t>• Open uat-fa-test01. Set Enabled = No. Save.
-• Sign out, attempt to log in as uat-fa-test01.</t>
-        </is>
-      </c>
       <c r="H50" s="7" t="inlineStr"/>
       <c r="I50" s="7" t="inlineStr">
         <is>
-          <t>Error: INSERT User → 417: {"exception":"frappe.exceptions.ValidationError: Error syncing User to User Manager: ('User Manager', 'uat-umd-0pc24h@dhwaniris.com', IntegrityError(1062, \"Duplicate entry '[uat]_disabled' for key 'username'\"))","exc_type":"ValidationError","_exc_source":"dhwani_frappe_base (app)","exc":"[\"Traceback (most recent call last):\\n  File \\\"apps/frappe/frappe/model/base_document.py\\\", line 755, in db_insert\\n    name = frappe.db.sql(\\n    \\t\\\"\\\"\\\"INSERT INTO `</t>
+          <t>Error: INSERT User → 417: {"exception":"frappe.exceptions.ValidationError: Error syncing User to User Manager: ('User Manager', 'uat-ume-1c8bs5@dhwaniris.com', IntegrityError(1062, \"Duplicate entry '[uat]_before' for key 'username'\"))","exc_type":"ValidationError","_exc_source":"dhwani_frappe_base (app)","exc":"[\"Traceback (most recent call last):\\n  File \\\"apps/frappe/frappe/model/base_document.py\\\", line 755, in db_insert\\n    name = frappe.db.sql(\\n    \\t\\\"\\\"\\\"INSERT INTO `ta</t>
         </is>
       </c>
       <c r="J50" s="7" t="inlineStr"/>
@@ -26861,104 +26864,157 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
+          <t>PR-TC-UM-011</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>13. User Management</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>Deactivate a user — they cannot log in until reactivated</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>P0 — Blocker</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>• Open uat-fa-test01. Set Enabled = No. Save.
+• Sign out, attempt to log in as uat-fa-test01.</t>
+        </is>
+      </c>
+      <c r="H51" s="7" t="inlineStr"/>
+      <c r="I51" s="7" t="inlineStr">
+        <is>
+          <t>Error: INSERT User → 417: {"exception":"frappe.exceptions.ValidationError: Error syncing User to User Manager: ('User Manager', 'uat-umd-0pc24h@dhwaniris.com', IntegrityError(1062, \"Duplicate entry '[uat]_disabled' for key 'username'\"))","exc_type":"ValidationError","_exc_source":"dhwani_frappe_base (app)","exc":"[\"Traceback (most recent call last):\\n  File \\\"apps/frappe/frappe/model/base_document.py\\\", line 755, in db_insert\\n    name = frappe.db.sql(\\n    \\t\\\"\\\"\\\"INSERT INTO `</t>
+        </is>
+      </c>
+      <c r="J51" s="7" t="inlineStr"/>
+      <c r="K51" s="7" t="inlineStr"/>
+      <c r="L51" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M51" s="7" t="inlineStr"/>
+      <c r="N51" s="7" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>BUG-050</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
           <t>PR-TC-XC-003</t>
         </is>
       </c>
-      <c r="C51" s="7" t="inlineStr">
+      <c r="C52" s="7" t="inlineStr">
         <is>
           <t>4. Application Entry &amp; Routing</t>
         </is>
       </c>
-      <c r="D51" s="7" t="inlineStr">
+      <c r="D52" s="7" t="inlineStr">
         <is>
           <t>Deep link to a protected page while logged out preserves the intent</t>
         </is>
       </c>
-      <c r="E51" s="7" t="inlineStr">
+      <c r="E52" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F51" s="7" t="inlineStr">
+      <c r="F52" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G51" s="7" t="inlineStr">
+      <c r="G52" s="7" t="inlineStr">
         <is>
           <t>• Open https://stgprime-rural.dhwaniris.in/app/enterprenur-profile/EP-001 directly.
 • Login redirect fires.
 • Complete login as a user permitted to see that record.</t>
         </is>
       </c>
-      <c r="H51" s="7" t="inlineStr">
+      <c r="H52" s="7" t="inlineStr">
         <is>
           <t>After successful login, user is redirected to the originally requested URL (the EP detail page), not the default landing page. URL parameter (typically redirect-to or next) is preserved through the auth flow.</t>
         </is>
       </c>
-      <c r="I51" s="7" t="inlineStr">
+      <c r="I52" s="7" t="inlineStr">
         <is>
           <t>Error: expect(received).toMatch(expected)
 Expected pattern: /redirect|next|to=/i
 Received string:  "https://stgprime-rural.dhwaniris.in/primerural/login"</t>
         </is>
       </c>
-      <c r="J51" s="7" t="inlineStr">
+      <c r="J52" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\04-entry-PR-TC-XC-ENTRY-·--e9661-t-preserves-redirect-intent-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K51" s="7" t="inlineStr">
+      <c r="K52" s="7" t="inlineStr">
         <is>
           <t>BRD: PR-OV-001 (Auth)</t>
         </is>
       </c>
-      <c r="L51" s="7" t="inlineStr">
+      <c r="L52" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M51" s="7" t="inlineStr"/>
-      <c r="N51" s="7" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="7" t="inlineStr">
-        <is>
-          <t>BUG-050</t>
-        </is>
-      </c>
-      <c r="B52" s="7" t="inlineStr">
+      <c r="M52" s="7" t="inlineStr"/>
+      <c r="N52" s="7" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>BUG-051</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-023</t>
         </is>
       </c>
-      <c r="C52" s="7" t="inlineStr">
+      <c r="C53" s="7" t="inlineStr">
         <is>
           <t>6. Responsive Layout &amp; Screen Sizes</t>
         </is>
       </c>
-      <c r="D52" s="7" t="inlineStr">
+      <c r="D53" s="7" t="inlineStr">
         <is>
           <t>1024×768 (tablet landscape / iPad / Surface): sidebar collapses to icon rail</t>
         </is>
       </c>
-      <c r="E52" s="7" t="inlineStr">
+      <c r="E53" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F52" s="7" t="inlineStr">
+      <c r="F53" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G52" s="7" t="inlineStr">
+      <c r="G53" s="7" t="inlineStr">
         <is>
           <t>• Resize to 1024×768.</t>
         </is>
       </c>
-      <c r="H52" s="7" t="inlineStr"/>
-      <c r="I52" s="7" t="inlineStr">
+      <c r="H53" s="7" t="inlineStr"/>
+      <c r="I53" s="7" t="inlineStr">
         <is>
           <t>Error: at 1024px the sidebar should collapse to an icon rail; width=240
 expect(received).toBeLessThanOrEqual(expected)
@@ -26966,63 +27022,63 @@
 Received:    240</t>
         </is>
       </c>
-      <c r="J52" s="7" t="inlineStr">
+      <c r="J53" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\06-08-10-nonfunctional-PR--f1c18-ollapses-to-icon-rail-64px--sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K52" s="7" t="inlineStr"/>
-      <c r="L52" s="7" t="inlineStr">
+      <c r="K53" s="7" t="inlineStr"/>
+      <c r="L53" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M52" s="7" t="inlineStr"/>
-      <c r="N52" s="7" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="7" t="inlineStr">
-        <is>
-          <t>BUG-051</t>
-        </is>
-      </c>
-      <c r="B53" s="7" t="inlineStr">
+      <c r="M53" s="7" t="inlineStr"/>
+      <c r="N53" s="7" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>BUG-052</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-032</t>
         </is>
       </c>
-      <c r="C53" s="7" t="inlineStr">
+      <c r="C54" s="7" t="inlineStr">
         <is>
           <t>7. Login &amp; Session</t>
         </is>
       </c>
-      <c r="D53" s="7" t="inlineStr">
+      <c r="D54" s="7" t="inlineStr">
         <is>
           <t>Wrong password shows a clear error and does NOT reveal whether the email exists</t>
         </is>
       </c>
-      <c r="E53" s="7" t="inlineStr">
+      <c r="E54" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F53" s="7" t="inlineStr">
+      <c r="F54" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G53" s="7" t="inlineStr">
+      <c r="G54" s="7" t="inlineStr">
         <is>
           <t>• Login form: enter a valid email but wrong password.
 • Submit.</t>
         </is>
       </c>
-      <c r="H53" s="7" t="inlineStr">
+      <c r="H54" s="7" t="inlineStr">
         <is>
           <t>Error displays inline above the form: "Invalid email or password." — generic enough that an attacker cannot enumerate valid emails. The password field is cleared; the email field is preserved. No 500. No password ever echoed back into the field.</t>
         </is>
       </c>
-      <c r="I53" s="7" t="inlineStr">
+      <c r="I54" s="7" t="inlineStr">
         <is>
           <t>Error: login error must be friendly text, not a raw exception class
 expect(locator).not.toContainText(expected) failed
@@ -27036,62 +27092,62 @@
     22 × locator resolved to &lt;div role="alert" class="bg-d</t>
         </is>
       </c>
-      <c r="J53" s="7" t="inlineStr">
+      <c r="J54" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\07-auth-PR-TC-XC-AUTH-·-Em-429a0-neric-error-no-enumeration--sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K53" s="7" t="inlineStr">
+      <c r="K54" s="7" t="inlineStr">
         <is>
           <t>OWASP A07 Auth Failures (do not leak account existence).</t>
         </is>
       </c>
-      <c r="L53" s="7" t="inlineStr">
+      <c r="L54" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M53" s="7" t="inlineStr"/>
-      <c r="N53" s="7" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="7" t="inlineStr">
-        <is>
-          <t>BUG-052</t>
-        </is>
-      </c>
-      <c r="B54" s="7" t="inlineStr">
+      <c r="M54" s="7" t="inlineStr"/>
+      <c r="N54" s="7" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>BUG-053</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-033</t>
         </is>
       </c>
-      <c r="C54" s="7" t="inlineStr">
+      <c r="C55" s="7" t="inlineStr">
         <is>
           <t>7. Login &amp; Session</t>
         </is>
       </c>
-      <c r="D54" s="7" t="inlineStr">
+      <c r="D55" s="7" t="inlineStr">
         <is>
           <t>Non-existent email shows the same generic error as wrong password</t>
         </is>
       </c>
-      <c r="E54" s="7" t="inlineStr">
+      <c r="E55" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F54" s="7" t="inlineStr">
+      <c r="F55" s="7" t="inlineStr">
         <is>
           <t>P0 — Blocker</t>
         </is>
       </c>
-      <c r="G54" s="7" t="inlineStr">
+      <c r="G55" s="7" t="inlineStr">
         <is>
           <t>• Submit with email not-a-real-user@example.com and any password.</t>
         </is>
       </c>
-      <c r="H54" s="7" t="inlineStr"/>
-      <c r="I54" s="7" t="inlineStr">
+      <c r="H55" s="7" t="inlineStr"/>
+      <c r="I55" s="7" t="inlineStr">
         <is>
           <t>Error: login error must be friendly text, not a raw exception class
 expect(locator).not.toContainText(expected) failed
@@ -27105,129 +27161,77 @@
     22 × locator resolved to &lt;div role="alert" class="bg-d</t>
         </is>
       </c>
-      <c r="J54" s="7" t="inlineStr">
+      <c r="J55" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\07-auth-PR-TC-XC-AUTH-·-Em-a7adf-ows-identical-generic-error-sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K54" s="7" t="inlineStr"/>
-      <c r="L54" s="7" t="inlineStr">
+      <c r="K55" s="7" t="inlineStr"/>
+      <c r="L55" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M54" s="7" t="inlineStr"/>
-      <c r="N54" s="7" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="7" t="inlineStr">
-        <is>
-          <t>BUG-053</t>
-        </is>
-      </c>
-      <c r="B55" s="7" t="inlineStr">
+      <c r="M55" s="7" t="inlineStr"/>
+      <c r="N55" s="7" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>BUG-054</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-052</t>
         </is>
       </c>
-      <c r="C55" s="7" t="inlineStr">
+      <c r="C56" s="7" t="inlineStr">
         <is>
           <t>8. UI / UX Rules — Monsoon Court Compliance</t>
         </is>
       </c>
-      <c r="D55" s="7" t="inlineStr">
+      <c r="D56" s="7" t="inlineStr">
         <is>
           <t>No green and no yellow appear anywhere in the UI</t>
         </is>
       </c>
-      <c r="E55" s="7" t="inlineStr">
+      <c r="E56" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F55" s="7" t="inlineStr">
+      <c r="F56" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G55" s="7" t="inlineStr">
+      <c r="G56" s="7" t="inlineStr">
         <is>
           <t>• Visually scan every page for green / yellow elements.
 • Search the rendered CSS for any colour matching green, yellow, #2ecc71, #f1c40f, similar hexes.</t>
         </is>
       </c>
-      <c r="H55" s="7" t="inlineStr">
+      <c r="H56" s="7" t="inlineStr">
         <is>
           <t>Zero green elements. Success states use teal #0E4D4E. Zero yellow elements. Warning states use terracotta #C26849.</t>
         </is>
       </c>
-      <c r="I55" s="7" t="inlineStr">
+      <c r="I56" s="7" t="inlineStr">
         <is>
           <t>Active Entrepreneurs KPI shows a GREEN check rgb(63,107,58) (hue 114). Monsoon Court forbids green — success must be teal #0E4D4E.</t>
         </is>
       </c>
-      <c r="J55" s="7" t="inlineStr">
+      <c r="J56" s="7" t="inlineStr">
         <is>
           <t>.playwright-mcp/bug-xc052-green-kpi.png</t>
         </is>
       </c>
-      <c r="K55" s="7" t="inlineStr">
+      <c r="K56" s="7" t="inlineStr">
         <is>
           <t>Monsoon Court §2.7 (brand non-negotiables).</t>
         </is>
       </c>
-      <c r="L55" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="M55" s="7" t="inlineStr"/>
-      <c r="N55" s="7" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="7" t="inlineStr">
-        <is>
-          <t>BUG-054</t>
-        </is>
-      </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>PR-TC-XC-054</t>
-        </is>
-      </c>
-      <c r="C56" s="7" t="inlineStr">
-        <is>
-          <t>8. UI / UX Rules — Monsoon Court Compliance</t>
-        </is>
-      </c>
-      <c r="D56" s="7" t="inlineStr">
-        <is>
-          <t>Required-field marker is a terracotta asterisk, not "(required)" text</t>
-        </is>
-      </c>
-      <c r="E56" s="7" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F56" s="7" t="inlineStr">
-        <is>
-          <t>P1 — High</t>
-        </is>
-      </c>
-      <c r="G56" s="7" t="inlineStr">
-        <is>
-          <t>• Open the EP form. Find a required field (e.g. Entrepreneur Name).</t>
-        </is>
-      </c>
-      <c r="H56" s="7" t="inlineStr"/>
-      <c r="I56" s="7" t="inlineStr">
-        <is>
-          <t>Asterisk on the name label is taupe rgb(107,99,89) (inherits label ink-soft), NOT terracotta #C26849. Marker present but wrong colour.</t>
-        </is>
-      </c>
-      <c r="J56" s="7" t="inlineStr"/>
-      <c r="K56" s="7" t="inlineStr"/>
       <c r="L56" s="7" t="inlineStr">
         <is>
           <t>Open</t>
@@ -27244,7 +27248,7 @@
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-XC-055</t>
+          <t>PR-TC-XC-054</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
@@ -27254,7 +27258,7 @@
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>Focus ring is visible on every interactive element on keyboard focus</t>
+          <t>Required-field marker is a terracotta asterisk, not "(required)" text</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
@@ -27269,13 +27273,13 @@
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>• On any form, tab through every interactive element with the keyboard.</t>
+          <t>• Open the EP form. Find a required field (e.g. Entrepreneur Name).</t>
         </is>
       </c>
       <c r="H57" s="7" t="inlineStr"/>
       <c r="I57" s="7" t="inlineStr">
         <is>
-          <t>Keyboard-Tab focus on buttons + links shows the default UA outline (rgb(16,16,16) auto ~0.67px), NOT the spec 2px terracotta ring with 2px cream offset. Focus IS visible (not an a11y blocker) but does not match the design system.</t>
+          <t>Asterisk on the name label is taupe rgb(107,99,89) (inherits label ink-soft), NOT terracotta #C26849. Marker present but wrong colour.</t>
         </is>
       </c>
       <c r="J57" s="7" t="inlineStr"/>
@@ -27296,17 +27300,17 @@
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-XC-063</t>
+          <t>PR-TC-XC-055</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>9. Accessibility — WCAG 2.2 AA</t>
+          <t>8. UI / UX Rules — Monsoon Court Compliance</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>Form fields have associated labels (axe-core "label" rule passes)</t>
+          <t>Focus ring is visible on every interactive element on keyboard focus</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
@@ -27321,11 +27325,63 @@
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>• Run axe-core on the EP form (via Playwright).</t>
+          <t>• On any form, tab through every interactive element with the keyboard.</t>
         </is>
       </c>
       <c r="H58" s="7" t="inlineStr"/>
       <c r="I58" s="7" t="inlineStr">
+        <is>
+          <t>Keyboard-Tab focus on buttons + links shows the default UA outline (rgb(16,16,16) auto ~0.67px), NOT the spec 2px terracotta ring with 2px cream offset. Focus IS visible (not an a11y blocker) but does not match the design system.</t>
+        </is>
+      </c>
+      <c r="J58" s="7" t="inlineStr"/>
+      <c r="K58" s="7" t="inlineStr"/>
+      <c r="L58" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M58" s="7" t="inlineStr"/>
+      <c r="N58" s="7" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>BUG-057</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>PR-TC-XC-063</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>9. Accessibility — WCAG 2.2 AA</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>Form fields have associated labels (axe-core "label" rule passes)</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>P1 — High</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>• Run axe-core on the EP form (via Playwright).</t>
+        </is>
+      </c>
+      <c r="H59" s="7" t="inlineStr"/>
+      <c r="I59" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: label violations: [{"id":"label","n":6}]
 expect(received).toEqual(expected) // deep equality
@@ -27345,58 +27401,58 @@
 +        </t>
         </is>
       </c>
-      <c r="J58" s="7" t="inlineStr">
+      <c r="J59" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\09-a11y-PR-TC-XC-063-·-for-17d03-ssociated-labels-axe-label--sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K58" s="7" t="inlineStr"/>
-      <c r="L58" s="7" t="inlineStr">
+      <c r="K59" s="7" t="inlineStr"/>
+      <c r="L59" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M58" s="7" t="inlineStr"/>
-      <c r="N58" s="7" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="7" t="inlineStr">
-        <is>
-          <t>BUG-057</t>
-        </is>
-      </c>
-      <c r="B59" s="7" t="inlineStr">
+      <c r="M59" s="7" t="inlineStr"/>
+      <c r="N59" s="7" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>BUG-058</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-064</t>
         </is>
       </c>
-      <c r="C59" s="7" t="inlineStr">
+      <c r="C60" s="7" t="inlineStr">
         <is>
           <t>9. Accessibility — WCAG 2.2 AA</t>
         </is>
       </c>
-      <c r="D59" s="7" t="inlineStr">
+      <c r="D60" s="7" t="inlineStr">
         <is>
           <t>Colour contrast meets WCAG AA</t>
         </is>
       </c>
-      <c r="E59" s="7" t="inlineStr">
+      <c r="E60" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F59" s="7" t="inlineStr">
+      <c r="F60" s="7" t="inlineStr">
         <is>
           <t>P1 — High</t>
         </is>
       </c>
-      <c r="G59" s="7" t="inlineStr">
+      <c r="G60" s="7" t="inlineStr">
         <is>
           <t>• Run axe-core's contrast check on EP detail, dashboard, framework form.</t>
         </is>
       </c>
-      <c r="H59" s="7" t="inlineStr"/>
-      <c r="I59" s="7" t="inlineStr">
+      <c r="H60" s="7" t="inlineStr"/>
+      <c r="I60" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: contrast violations: [10]
 expect(received).toEqual(expected) // deep equality
@@ -27412,50 +27468,50 @@
 </t>
         </is>
       </c>
-      <c r="J59" s="7" t="inlineStr">
+      <c r="J60" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\09-a11y-PR-TC-XC-064-·-col-8baa1-WCAG-AA-axe-color-contrast--sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K59" s="7" t="inlineStr"/>
-      <c r="L59" s="7" t="inlineStr">
+      <c r="K60" s="7" t="inlineStr"/>
+      <c r="L60" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M59" s="7" t="inlineStr"/>
-      <c r="N59" s="7" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="7" t="inlineStr">
-        <is>
-          <t>BUG-058</t>
-        </is>
-      </c>
-      <c r="B60" s="7" t="inlineStr">
+      <c r="M60" s="7" t="inlineStr"/>
+      <c r="N60" s="7" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>BUG-059</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-064b</t>
         </is>
       </c>
-      <c r="C60" s="7" t="inlineStr">
+      <c r="C61" s="7" t="inlineStr">
         <is>
           <t>(not in master — add as test case)</t>
         </is>
       </c>
-      <c r="D60" s="7" t="inlineStr">
+      <c r="D61" s="7" t="inlineStr">
         <is>
           <t>PR-TC-XC-064b · landscape colour contrast (WCAG AA)</t>
         </is>
       </c>
-      <c r="E60" s="7" t="inlineStr">
+      <c r="E61" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F60" s="7" t="inlineStr"/>
-      <c r="G60" s="7" t="inlineStr"/>
-      <c r="H60" s="7" t="inlineStr"/>
-      <c r="I60" s="7" t="inlineStr">
+      <c r="F61" s="7" t="inlineStr"/>
+      <c r="G61" s="7" t="inlineStr"/>
+      <c r="H61" s="7" t="inlineStr"/>
+      <c r="I61" s="7" t="inlineStr">
         <is>
           <t>Error: landscape contrast nodes: 4
 expect(received).toEqual(expected) // deep equality
@@ -27470,19 +27526,19 @@
 +     "id": "color-contrast"</t>
         </is>
       </c>
-      <c r="J60" s="7" t="inlineStr">
+      <c r="J61" s="7" t="inlineStr">
         <is>
           <t>C:\Users\Dhwani\OneDrive - Dhwani Rural Information Systems Pvt. Ltd\Work\prime-rural\generated\tests\playwright\test-results\09-a11y-PR-TC-XC-064b-·-landscape-colour-contrast-WCAG-AA--sm\test-failed-1.png</t>
         </is>
       </c>
-      <c r="K60" s="7" t="inlineStr"/>
-      <c r="L60" s="7" t="inlineStr">
+      <c r="K61" s="7" t="inlineStr"/>
+      <c r="L61" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M60" s="7" t="inlineStr"/>
-      <c r="N60" s="7" t="inlineStr"/>
+      <c r="M61" s="7" t="inlineStr"/>
+      <c r="N61" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -16768,14 +16768,14 @@
       </c>
       <c r="L227" s="7" t="inlineStr"/>
       <c r="M227" s="7" t="inlineStr"/>
-      <c r="N227" s="12" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="N227" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O227" s="7" t="inlineStr">
         <is>
-          <t>UI form-fill: Cost Rs50,000, Useful Life 10y -&gt; MONTHLY DEPRECIATION Rs416.67 (= Rs5,000/yr, straight-line cost/life). NO salvage/residual-value field on the form, so it does NOT match BRD (cost-salvage)/life = Rs4,500/yr. Salvage not captured; depreciation overstated vs spec.</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="P227" s="8" t="inlineStr">
@@ -17604,17 +17604,21 @@
       </c>
       <c r="L239" s="7" t="inlineStr"/>
       <c r="M239" s="7" t="inlineStr"/>
-      <c r="N239" s="13" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+      <c r="N239" s="12" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
       <c r="O239" s="7" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="P239" s="8" t="inlineStr"/>
+          <t>DF Promotion Entry (existing_promotions / required_promotions child) has NO budget, reach, or cost numeric fields — so the spec's cost-per-reach = budget/reach metric is not captured anywhere in the promotions table. Confirm whether cost-per-reach is required; if so it is missing.</t>
+        </is>
+      </c>
+      <c r="P239" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
       <c r="Q239" s="7" t="inlineStr"/>
     </row>
     <row r="240">
@@ -17877,14 +17881,14 @@
       </c>
       <c r="L243" s="7" t="inlineStr"/>
       <c r="M243" s="7" t="inlineStr"/>
-      <c r="N243" s="12" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="N243" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O243" s="7" t="inlineStr">
         <is>
-          <t>QC EXISTING uses an "+ Add Item" checklist with a 4-LEVEL rating (0/33/66/100) and AVERAGE SCORE (%), NOT the BRD spec of 23 fixed stars totalling /115 (e.g. 92/115=80%). Items are manually added (not pre-loaded). Confirm whether 23 standard items should pre-load + whether the scoring model should match spec.</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="P243" s="8" t="inlineStr">
@@ -17948,17 +17952,21 @@
       </c>
       <c r="L244" s="7" t="inlineStr"/>
       <c r="M244" s="7" t="inlineStr"/>
-      <c r="N244" s="13" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+      <c r="N244" s="12" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
       <c r="O244" s="7" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="P244" s="8" t="inlineStr"/>
+          <t>API insert+readback: monthly order cost = quantity_ordered × price_per_unit = 100 × ₹5 = ₹500.00 (CORRECT ✓). BUT packaging_info saving_per_unit returned 0.0 with price_per_unit ₹10 + new_price_per_unit ₹8 (expected ₹2 old−new saving) — did not compute. Confirm the saving formula / required trigger fields.</t>
+        </is>
+      </c>
+      <c r="P244" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="Q244" s="7" t="inlineStr"/>
     </row>
     <row r="245">
@@ -18284,9 +18292,9 @@
       </c>
       <c r="L249" s="7" t="inlineStr"/>
       <c r="M249" s="7" t="inlineStr"/>
-      <c r="N249" s="13" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+      <c r="N249" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O249" s="7" t="inlineStr">
@@ -18688,17 +18696,21 @@
       </c>
       <c r="L255" s="7" t="inlineStr"/>
       <c r="M255" s="7" t="inlineStr"/>
-      <c r="N255" s="13" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+      <c r="N255" s="12" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
       <c r="O255" s="7" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="P255" s="8" t="inlineStr"/>
+          <t>API insert+readback (Loan ₹1,00,000, 12% p.a., 12 months): emi_per_month computed = ₹8,884.88 — exact match for reducing-balance amortization EMI = P·r·(1+r)^n/((1+r)^n−1). Does NOT match BRD FW-SCH-001 flat Loan/Term (₹5,555.56) nor flat+simple-interest (₹9,333.33). EMI is a SAVE-TIME computed field ('— save to compute —' in-form). Implemented amortization is financially correct but deviates from spec — BA to confirm intended formula (likely update BRD).</t>
+        </is>
+      </c>
+      <c r="P255" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="Q255" s="7" t="inlineStr"/>
     </row>
     <row r="256">
@@ -18889,14 +18901,14 @@
       </c>
       <c r="L258" s="7" t="inlineStr"/>
       <c r="M258" s="7" t="inlineStr"/>
-      <c r="N258" s="12" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="N258" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O258" s="7" t="inlineStr">
         <is>
-          <t>Cert Status field = Received/Not Yet Received/Rejected (+ validity date), NOT an Active/Expired status — so the spec premise "cannot mark an expired cert Active" does not map. Setting a PAST Valid Till date (2025-01-01) showed NO expiry warning/flag. Confirm: should expired certs be flagged/blocked?</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="P258" s="8" t="inlineStr">
@@ -25008,7 +25020,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-FW-MACH-001</t>
+          <t>PR-TC-FW-PKG-001</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -25018,28 +25030,28 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Add machine — depreciation auto-calculated per straight-line method</t>
+          <t>Monthly packaging qty sums across variants per month</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>P0 — Blocker</t>
+          <t>P1 — High</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>• Cost = 50,000, Useful Life = 10 years, Residual = 5,000.</t>
+          <t>• Variant A: 100 units in Jan. Variant B: 50 in Jan.</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr"/>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>UI form-fill: Cost Rs50,000, Useful Life 10y -&gt; MONTHLY DEPRECIATION Rs416.67 (= Rs5,000/yr, straight-line cost/life). NO salvage/residual-value field on the form, so it does NOT match BRD (cost-salvage)/life = Rs4,500/yr. Salvage not captured; depreciation overstated vs spec.</t>
+          <t>API insert+readback: monthly order cost = quantity_ordered × price_per_unit = 100 × ₹5 = ₹500.00 (CORRECT ✓). BUT packaging_info saving_per_unit returned 0.0 with price_per_unit ₹10 + new_price_per_unit ₹8 (expected ₹2 old−new saving) — did not compute. Confirm the saving formula / required trigger fields.</t>
         </is>
       </c>
       <c r="J18" s="7" t="inlineStr"/>
@@ -25060,7 +25072,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-FW-PC-002</t>
+          <t>PR-TC-FW-PROMO-001</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -25070,28 +25082,28 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Expired cert: cannot mark Active</t>
+          <t>Add promotion activity with budget + expected reach</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>P1 — High</t>
+          <t>P2 — Medium</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>• Add cert with Valid till = yesterday, Status = Active.</t>
+          <t>• Add row: WhatsApp campaign, ₹ 500 budget, expected 100 reach.</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr"/>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>Cert Status field = Received/Not Yet Received/Rejected (+ validity date), NOT an Active/Expired status — so the spec premise "cannot mark an expired cert Active" does not map. Setting a PAST Valid Till date (2025-01-01) showed NO expiry warning/flag. Confirm: should expired certs be flagged/blocked?</t>
+          <t>DF Promotion Entry (existing_promotions / required_promotions child) has NO budget, reach, or cost numeric fields — so the spec's cost-per-reach = budget/reach metric is not captured anywhere in the promotions table. Confirm whether cost-per-reach is required; if so it is missing.</t>
         </is>
       </c>
       <c r="J19" s="7" t="inlineStr"/>
@@ -25112,7 +25124,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>PR-TC-FW-QC-001</t>
+          <t>PR-TC-FW-SCH-001</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -25122,7 +25134,7 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Fill all 23 stars; total score auto-computes</t>
+          <t>Apply for scheme: pick from 19, fill loan amount + term, EMI calculated flat</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
@@ -25137,13 +25149,13 @@
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>• Set all 23 questions to 4 stars (out of 5).</t>
+          <t>• Scheme = CGTMSE. Loan = ₹ 2,00,000. Term = 36 months.</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr"/>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>QC EXISTING uses an "+ Add Item" checklist with a 4-LEVEL rating (0/33/66/100) and AVERAGE SCORE (%), NOT the BRD spec of 23 fixed stars totalling /115 (e.g. 92/115=80%). Items are manually added (not pre-loaded). Confirm whether 23 standard items should pre-load + whether the scoring model should match spec.</t>
+          <t>API insert+readback (Loan ₹1,00,000, 12% p.a., 12 months): emi_per_month computed = ₹8,884.88 — exact match for reducing-balance amortization EMI = P·r·(1+r)^n/((1+r)^n−1). Does NOT match BRD FW-SCH-001 flat Loan/Term (₹5,555.56) nor flat+simple-interest (₹9,333.33). EMI is a SAVE-TIME computed field ('— save to compute —' in-form). Implemented amortization is financially correct but deviates from spec — BA to confirm intended formula (likely update BRD).</t>
         </is>
       </c>
       <c r="J20" s="7" t="inlineStr"/>

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -16427,8 +16427,8 @@
       <c r="K222" s="7" t="inlineStr">
         <is>
           <t>• Open Financials → BMC tab.
-• Fill all 9 BMC sections (Customer Segments, Value Prop, Channels, Customer Relationships, Revenue Streams, Key Activities, Key Resources, Key Partnerships, Cost Structure).
-• Save.</t>
+• Enter Total Quantity, Avg Revenue/Month, expenses, and a loan (amount, interest % p.a., term).
+• Observe the computed fields.</t>
         </is>
       </c>
       <c r="L222" s="7" t="inlineStr"/>
@@ -16732,7 +16732,7 @@
       </c>
       <c r="D227" s="7" t="inlineStr">
         <is>
-          <t>Add machine — depreciation auto-calculated per straight-line method</t>
+          <t>Add machine — depreciation auto-calculated from condition-based rate</t>
         </is>
       </c>
       <c r="E227" s="8" t="inlineStr">
@@ -16763,7 +16763,7 @@
       <c r="J227" s="7" t="inlineStr"/>
       <c r="K227" s="7" t="inlineStr">
         <is>
-          <t>• Cost = 50,000, Useful Life = 10 years, Residual = 5,000.</t>
+          <t>• Cost = 50,000, Machinery Condition = Good (10% per year).</t>
         </is>
       </c>
       <c r="L227" s="7" t="inlineStr"/>
@@ -16778,11 +16778,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="P227" s="8" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
+      <c r="P227" s="8" t="inlineStr"/>
       <c r="Q227" s="7" t="inlineStr"/>
     </row>
     <row r="228">
@@ -17501,7 +17497,7 @@
       </c>
       <c r="D238" s="7" t="inlineStr">
         <is>
-          <t>Add online channel (Amazon, Flipkart) with commission %, monthly volume</t>
+          <t>Add a recommended channel + sales-tracker row; revenue auto-computes</t>
         </is>
       </c>
       <c r="E238" s="8" t="inlineStr">
@@ -17532,7 +17528,8 @@
       <c r="J238" s="7" t="inlineStr"/>
       <c r="K238" s="7" t="inlineStr">
         <is>
-          <t>• Online Channels tab → +Add: Amazon, commission 15%, volume 50 units/month, avg price ₹ 200.</t>
+          <t>• Required → Recommended Channels: add Amazon (Online), Location from Block Master, Identified by = Core Team.
+• Add a product row (Product → SKU cascade, Price ₹ 200). In Sales Tracker add a row: 50 units in Jan.</t>
         </is>
       </c>
       <c r="L238" s="7" t="inlineStr"/>
@@ -17568,7 +17565,7 @@
       </c>
       <c r="D239" s="7" t="inlineStr">
         <is>
-          <t>Add promotion activity with budget + expected reach</t>
+          <t>Add a promotion (Name / Type / Handled by / Frequency)</t>
         </is>
       </c>
       <c r="E239" s="8" t="inlineStr">
@@ -17599,7 +17596,7 @@
       <c r="J239" s="7" t="inlineStr"/>
       <c r="K239" s="7" t="inlineStr">
         <is>
-          <t>• Add row: WhatsApp campaign, ₹ 500 budget, expected 100 reach.</t>
+          <t>• Existing → +Add: Promotion Name = WhatsApp campaign, Type = Online, Handled by, Frequency = Weekly, Notes.</t>
         </is>
       </c>
       <c r="L239" s="7" t="inlineStr"/>
@@ -17639,7 +17636,7 @@
       </c>
       <c r="D240" s="7" t="inlineStr">
         <is>
-          <t>Conditional dropdown: selecting Prototype Type = "Physical" reveals dimensions fields</t>
+          <t>Conditional dropdown: Type of Prototyping (Packaging / Product) drives the Prototyping Type Name list</t>
         </is>
       </c>
       <c r="E240" s="8" t="inlineStr">
@@ -17670,8 +17667,8 @@
       <c r="J240" s="7" t="inlineStr"/>
       <c r="K240" s="7" t="inlineStr">
         <is>
-          <t>• Type = Physical → fields appear.
-• Type = Digital → those fields hide; URL field appears.</t>
+          <t>• Type of Prototyping = Packaging → Prototyping Type Name lists the Packing Master (12 items).
+• Switch to Product → Prototyping Type Name lists the Business Basket (11 items).</t>
         </is>
       </c>
       <c r="L240" s="7" t="inlineStr"/>
@@ -17778,7 +17775,7 @@
       </c>
       <c r="D242" s="7" t="inlineStr">
         <is>
-          <t>Upload SOP document + status = Drafted / Reviewed / Approved</t>
+          <t>SOP tracking: "Is the standardisation being followed?" = No reveals the reason field</t>
         </is>
       </c>
       <c r="E242" s="8" t="inlineStr">
@@ -17809,7 +17806,7 @@
       <c r="J242" s="7" t="inlineStr"/>
       <c r="K242" s="7" t="inlineStr">
         <is>
-          <t>• Upload PDF. Set status = Drafted.</t>
+          <t>• Upload SOP (Upload/View) + set SOP URL. Set "Is the standardisation being followed?" = No.</t>
         </is>
       </c>
       <c r="L242" s="7" t="inlineStr"/>
@@ -17845,7 +17842,7 @@
       </c>
       <c r="D243" s="7" t="inlineStr">
         <is>
-          <t>Fill all 23 stars; total score auto-computes</t>
+          <t>Rate the 23 practices 1–5; average score auto-computes</t>
         </is>
       </c>
       <c r="E243" s="8" t="inlineStr">
@@ -17876,7 +17873,7 @@
       <c r="J243" s="7" t="inlineStr"/>
       <c r="K243" s="7" t="inlineStr">
         <is>
-          <t>• Set all 23 questions to 4 stars (out of 5).</t>
+          <t>• Rate all 23 quality practices at 4 (scale 1–5: 1 Not aware … 5 Fully implemented).</t>
         </is>
       </c>
       <c r="L243" s="7" t="inlineStr"/>
@@ -17891,11 +17888,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="P243" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="P243" s="8" t="inlineStr"/>
       <c r="Q243" s="7" t="inlineStr"/>
     </row>
     <row r="244">
@@ -17987,7 +17980,7 @@
       </c>
       <c r="D245" s="7" t="inlineStr">
         <is>
-          <t>Rate each of 9 platforms 0-5; readiness score auto</t>
+          <t>Rate platform skills 1–5; average skill level auto-computes</t>
         </is>
       </c>
       <c r="E245" s="8" t="inlineStr">
@@ -18018,7 +18011,7 @@
       <c r="J245" s="7" t="inlineStr"/>
       <c r="K245" s="7" t="inlineStr">
         <is>
-          <t>• Pick 5 across all 9.</t>
+          <t>• Add a Platform/Skill row and rate it 5 (scale 1–5: 1 No knowledge … 5 Proficient; ✕ clears to unrated).</t>
         </is>
       </c>
       <c r="L245" s="7" t="inlineStr"/>
@@ -18121,7 +18114,7 @@
       </c>
       <c r="D247" s="7" t="inlineStr">
         <is>
-          <t>BPC synthesises data from other DFs (Market Linkage, HR, Customer Analysis, etc.)</t>
+          <t>BPC: 9 canvas blocks filled manually; cross-module references are read-only links</t>
         </is>
       </c>
       <c r="E247" s="8" t="inlineStr">
@@ -18152,7 +18145,8 @@
       <c r="J247" s="7" t="inlineStr"/>
       <c r="K247" s="7" t="inlineStr">
         <is>
-          <t>• Open BPC. Verify Customer Segments are populated from Customer Analysis selections, Key Activities from Process Flow steps, Cost Structure from Unit Pricing.</t>
+          <t>• Open BPC. Fill the 9 canvas blocks (Key Partners … Revenue Streams) manually.
+• Check the cross-module reference pills shown below the relevant headers.</t>
         </is>
       </c>
       <c r="L247" s="7" t="inlineStr"/>
@@ -18459,7 +18453,7 @@
       </c>
       <c r="D252" s="7" t="inlineStr">
         <is>
-          <t>Alcohol toggle ON reveals "Contains alcohol — pregnancy warning" field, mandatory</t>
+          <t>Wine/Alcohol toggle ON reveals the statutory warning banner + Alcohol Content (ABV) field</t>
         </is>
       </c>
       <c r="E252" s="8" t="inlineStr">
@@ -18490,7 +18484,7 @@
       <c r="J252" s="7" t="inlineStr"/>
       <c r="K252" s="7" t="inlineStr">
         <is>
-          <t>• Toggle alcohol = Yes.</t>
+          <t>• Toggle "Wine / Alcohol Product?" = Yes.</t>
         </is>
       </c>
       <c r="L252" s="7" t="inlineStr"/>
@@ -18865,7 +18859,7 @@
       </c>
       <c r="D258" s="7" t="inlineStr">
         <is>
-          <t>Expired cert: cannot mark Active</t>
+          <t>Expired cert flagged by expiry highlight (no Active/Expired status exists)</t>
         </is>
       </c>
       <c r="E258" s="8" t="inlineStr">
@@ -18896,7 +18890,7 @@
       <c r="J258" s="7" t="inlineStr"/>
       <c r="K258" s="7" t="inlineStr">
         <is>
-          <t>• Add cert with Valid till = yesterday, Status = Active.</t>
+          <t>• Add a certification with Valid Till = yesterday.</t>
         </is>
       </c>
       <c r="L258" s="7" t="inlineStr"/>
@@ -18911,11 +18905,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="P258" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="P258" s="8" t="inlineStr"/>
       <c r="Q258" s="7" t="inlineStr"/>
     </row>
     <row r="259">
@@ -25082,7 +25072,7 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Add promotion activity with budget + expected reach</t>
+          <t>Add a promotion (Name / Type / Handled by / Frequency)</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -25097,7 +25087,7 @@
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>• Add row: WhatsApp campaign, ₹ 500 budget, expected 100 reach.</t>
+          <t>• Existing → +Add: Promotion Name = WhatsApp campaign, Type = Online, Handled by, Frequency = Weekly, Notes.</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr"/>

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -11401,7 +11401,7 @@
       </c>
       <c r="D151" s="7" t="inlineStr">
         <is>
-          <t>Required fields enforced: Name, Sector, District, Block, Village</t>
+          <t>Required fields enforced: Entrepreneur Name + Phone; geography auto-set from Program Access</t>
         </is>
       </c>
       <c r="E151" s="8" t="inlineStr">
@@ -11434,8 +11434,7 @@
         <is>
           <t>• Save with all fields blank.
 • Fill only Name; save.
-• Fill Name + Sector; save.
-• Continue progressively.</t>
+• Add Phone; save.</t>
         </is>
       </c>
       <c r="L151" s="7" t="inlineStr"/>
@@ -11478,7 +11477,7 @@
       </c>
       <c r="D152" s="7" t="inlineStr">
         <is>
-          <t>Entrepreneur Name is unique (case-insensitive within cohort)</t>
+          <t>Entrepreneur Name is unique (global)</t>
         </is>
       </c>
       <c r="E152" s="8" t="inlineStr">
@@ -11509,8 +11508,8 @@
       <c r="J152" s="7" t="inlineStr"/>
       <c r="K152" s="7" t="inlineStr">
         <is>
-          <t>• Save EP "Hilltop Honey" (case 1).
-• Try to save another EP with the same name "hilltop honey".</t>
+          <t>• Save EP "Hilltop Honey".
+• Try to save another EP with the exact same name "Hilltop Honey".</t>
         </is>
       </c>
       <c r="L152" s="7" t="inlineStr"/>
@@ -11546,7 +11545,7 @@
       </c>
       <c r="D153" s="7" t="inlineStr">
         <is>
-          <t>DOB validation: not future, not &amp;gt; 100 years old, not &amp;lt; 14 years old</t>
+          <t>DOB validation: future date blocked</t>
         </is>
       </c>
       <c r="E153" s="8" t="inlineStr">
@@ -11577,9 +11576,7 @@
       <c r="J153" s="7" t="inlineStr"/>
       <c r="K153" s="7" t="inlineStr">
         <is>
-          <t>• DOB = tomorrow. Save.
-• DOB = 31-Dec-1899 (&gt; 100 years).
-• DOB = today - 10 years.</t>
+          <t>• DOB = tomorrow. Save.</t>
         </is>
       </c>
       <c r="L153" s="7" t="inlineStr"/>
@@ -12543,7 +12540,7 @@
       </c>
       <c r="D167" s="7" t="inlineStr">
         <is>
-          <t>Cannot set Final Selection without an attachment (jury / decision document)</t>
+          <t>Final Selection becomes mandatory once Rural E-Champ Score is entered</t>
         </is>
       </c>
       <c r="E167" s="8" t="inlineStr">
@@ -12574,7 +12571,7 @@
       <c r="J167" s="7" t="inlineStr"/>
       <c r="K167" s="7" t="inlineStr">
         <is>
-          <t>• Try to set Final Selection without uploading a supporting document.</t>
+          <t>• As Core Team, enter a Rural E-Champ Score. Leave Final Selection blank. Save.</t>
         </is>
       </c>
       <c r="L167" s="7" t="inlineStr"/>
@@ -12610,7 +12607,7 @@
       </c>
       <c r="D168" s="7" t="inlineStr">
         <is>
-          <t>Framework Prioritisation table: pick frameworks for this EP, set priority 1-5</t>
+          <t>Framework Prioritisation: reorder the auto-listed frameworks by priority</t>
         </is>
       </c>
       <c r="E168" s="8" t="inlineStr">
@@ -12641,16 +12638,14 @@
       <c r="J168" s="7" t="inlineStr"/>
       <c r="K168" s="7" t="inlineStr">
         <is>
-          <t>• Open EP. Prioritisation tab. Add rows.
-• Framework = Raw Materials, Priority = 1.
-• Framework = Unit Pricing, Priority = 2.
-• Framework = Market Linkage, Priority = 3.
-• Save.</t>
+          <t>• Set Final Selection = Incubated/Supported so the Prioritisation tab appears.
+• The table is pre-populated with all frameworks from the Diagnostic Framework Master (priority 0 default; rows are not manually added — add/remove is hidden).
+• Set Raw Materials = 1, Unit Pricing = 2, Market Linkage = 3. Save.</t>
         </is>
       </c>
       <c r="L168" s="7" t="inlineStr">
         <is>
-          <t>Saved. Diagnostics tab now shows only those 3 frameworks (filtered by what's prioritised). Progress = 0% for each. EP card on dashboards shows priorities in order.</t>
+          <t>Saved. EP cards on the dashboard reorder by ascending priority. [Rows are auto-seeded; there is no "Applicable?" checkbox in the repo.]</t>
         </is>
       </c>
       <c r="M168" s="7" t="inlineStr">
@@ -12689,7 +12684,7 @@
       </c>
       <c r="D169" s="7" t="inlineStr">
         <is>
-          <t>Duplicate framework in priority table is rejected</t>
+          <t>Duplicate priority number in the priority table is rejected</t>
         </is>
       </c>
       <c r="E169" s="8" t="inlineStr">
@@ -12720,7 +12715,7 @@
       <c r="J169" s="7" t="inlineStr"/>
       <c r="K169" s="7" t="inlineStr">
         <is>
-          <t>• Add Raw Materials twice with priorities 1 and 4.</t>
+          <t>• Set two frameworks to the same priority number (e.g. both = 1). Save.</t>
         </is>
       </c>
       <c r="L169" s="7" t="inlineStr"/>
@@ -12756,7 +12751,7 @@
       </c>
       <c r="D170" s="7" t="inlineStr">
         <is>
-          <t>Priority must be a positive integer; warning if &amp;gt; 10</t>
+          <t>Priority accepts any integer (0 is the default for unprioritised rows)</t>
         </is>
       </c>
       <c r="E170" s="8" t="inlineStr">
@@ -12787,7 +12782,7 @@
       <c r="J170" s="7" t="inlineStr"/>
       <c r="K170" s="7" t="inlineStr">
         <is>
-          <t>• Priority = 0, -1, 100.</t>
+          <t>• Leave a row at priority 0; set another to 5; set another to 100. Save (no duplicates).</t>
         </is>
       </c>
       <c r="L170" s="7" t="inlineStr"/>
@@ -12974,7 +12969,7 @@
       </c>
       <c r="D173" s="7" t="inlineStr">
         <is>
-          <t>New EP starts in "MET" status by default</t>
+          <t>New EP starts in the pre-selection state (Final Selection blank)</t>
         </is>
       </c>
       <c r="E173" s="8" t="inlineStr">
@@ -13041,7 +13036,7 @@
       </c>
       <c r="D174" s="7" t="inlineStr">
         <is>
-          <t>MET → Incubated transition: pill colour changes, downstream dashboards update</t>
+          <t>Pre-selection → Incubated transition: pill updates, downstream dashboards update</t>
         </is>
       </c>
       <c r="E174" s="8" t="inlineStr">
@@ -13564,13 +13559,13 @@
       <c r="K181" s="7" t="inlineStr">
         <is>
           <t>• EP → Networking tab → +Add Introduction.
-• Mentor = "[UAT] Mentor One", Objective = "Help with packaging", Status = Pending.
+• Mentor = "[UAT] Mentor One", Contact Type, Introduced By, Objective = "Help with packaging", Meeting Status = "Not Yet Met".
 • Save.</t>
         </is>
       </c>
       <c r="L181" s="7" t="inlineStr">
         <is>
-          <t>Row added. Mentor preview card with sectors and contact appears. Notification to mentor (if configured).</t>
+          <t>Row added; mentor fields auto-fetch from the Mentor Master record. Meeting Status options = Not Yet Met / Awaiting Response / Scheduled / In Progress / Completed (there is no "Pending" option). NOTE: Mentor Master doctype is not yet built in the repo — confirm build before executing.</t>
         </is>
       </c>
       <c r="M181" s="7" t="inlineStr">
@@ -14324,7 +14319,7 @@
       <c r="K192" s="7" t="inlineStr">
         <is>
           <t>• EP profile dashboard → "+ Add New Product".
-• Drawer opens. Fill: Product Name = "[UAT] Wild Honey 250 g", Category = Food, Description, Available Months (Jan, Feb, Mar), Shelf Life = 12 months.
+• Drawer opens. Fill: Product Name (from Product Master), Sector, Product Snapshot, tick Available Months (Jan/Feb/Mar), Shelf Life Duration = "12 months".
 • Save.</t>
         </is>
       </c>
@@ -14361,7 +14356,7 @@
       </c>
       <c r="D193" s="7" t="inlineStr">
         <is>
-          <t>Product Name required; duplicate within same EP rejected</t>
+          <t>Product Name required; selected from Product Master (autocomplete)</t>
         </is>
       </c>
       <c r="E193" s="8" t="inlineStr">
@@ -14392,8 +14387,8 @@
       <c r="J193" s="7" t="inlineStr"/>
       <c r="K193" s="7" t="inlineStr">
         <is>
-          <t>• Try save without name.
-• Try save another product with the same name on the same EP.</t>
+          <t>• Try save without a Product Name.
+• Pick a Product Name from the Product Master autocomplete; save.</t>
         </is>
       </c>
       <c r="L193" s="7" t="inlineStr"/>
@@ -14429,7 +14424,7 @@
       </c>
       <c r="D194" s="7" t="inlineStr">
         <is>
-          <t>Shelf Life is a positive integer in months; reject 0 / negative / non-numeric</t>
+          <t>Shelf Life Duration is a free-text field (e.g. "12 months")</t>
         </is>
       </c>
       <c r="E194" s="8" t="inlineStr">
@@ -14460,7 +14455,7 @@
       <c r="J194" s="7" t="inlineStr"/>
       <c r="K194" s="7" t="inlineStr">
         <is>
-          <t>• Try shelf life = 0, -3, "twelve".</t>
+          <t>• Enter Shelf Life Duration = "12 months".</t>
         </is>
       </c>
       <c r="L194" s="7" t="inlineStr"/>
@@ -14496,7 +14491,7 @@
       </c>
       <c r="D195" s="7" t="inlineStr">
         <is>
-          <t>Available Months is a multi-select chip group, not 12 separate booleans</t>
+          <t>Available Months is a 12-row checkbox table (drives the Monthly Production Tracker)</t>
         </is>
       </c>
       <c r="E195" s="8" t="inlineStr">
@@ -14527,17 +14522,17 @@
       <c r="J195" s="7" t="inlineStr"/>
       <c r="K195" s="7" t="inlineStr">
         <is>
-          <t>• Open the form. Available Months section.</t>
+          <t>• Open the form. Available Months section. Tick Jan and Jun.</t>
         </is>
       </c>
       <c r="L195" s="7" t="inlineStr">
         <is>
-          <t>12 chips (Jan-Dec). Click to toggle (becomes terracotta when selected). "All months" quick-select. Year-round vs seasonal visually obvious.</t>
+          <t>Available Months is a 12-row checkbox table (TRUE/FALSE per month) — not a chip group. The ticked months become the rows of the Monthly Production Tracker; at least one month must be ticked to generate the tracker.</t>
         </is>
       </c>
       <c r="M195" s="7" t="inlineStr">
         <is>
-          <t>BRD: "available months / shelf life independence" — bug fix from QA.</t>
+          <t>BRD: Available Months drive the Monthly Production Tracker (checkbox-table model, per wireframe).</t>
         </is>
       </c>
       <c r="N195" s="13" t="inlineStr">
@@ -14716,7 +14711,7 @@
       </c>
       <c r="D198" s="7" t="inlineStr">
         <is>
-          <t>Process flow with machines pre-populates Raw Materials Existing tab</t>
+          <t>Process-flow machines pre-populate the Machinery framework Existing tab</t>
         </is>
       </c>
       <c r="E198" s="8" t="inlineStr">
@@ -14747,19 +14742,19 @@
       <c r="J198" s="7" t="inlineStr"/>
       <c r="K198" s="7" t="inlineStr">
         <is>
-          <t>• Add a step that uses Machine = "Honey extractor".
+          <t>• Add a process step that uses Machine = "Honey extractor" (Machine Status = Existing).
 • Save.
-• Open Raw Materials framework for this product.</t>
+• Open the Machinery framework for this entrepreneur.</t>
         </is>
       </c>
       <c r="L198" s="7" t="inlineStr">
         <is>
-          <t>"Honey extractor" pre-created as a row in Raw Materials Existing tab. (Cross-framework Golden Thread.)</t>
+          <t>"Honey extractor" pre-created as a row in the Machinery framework Existing tab. Cross-framework auto-fill per journey doc: process-flow machines → Machinery; product Ingredients → Raw Material (machines do NOT feed Raw Materials).</t>
         </is>
       </c>
       <c r="M198" s="7" t="inlineStr">
         <is>
-          <t>BRD Decision: process-flow machines → pre-create Raw Materials Existing rows.</t>
+          <t>BRD: process-flow machines → Machinery Existing rows; Ingredients → Raw Material rows.</t>
         </is>
       </c>
       <c r="N198" s="13" t="inlineStr">
@@ -14825,18 +14820,18 @@
       <c r="K199" s="7" t="inlineStr">
         <is>
           <t>• Product → Variants tab → +Add Variant.
-• Fill: Variant Name = "250 g jar", Pack Size = 250 g, Unit Cost = 50, Retail Price = 200, Wholesale Price = 150.
+• Fill: Variant Name = "Wildflower", Sub Variant = "Raw", Net Weight = 250, Unit = g.
 • Save.</t>
         </is>
       </c>
       <c r="L199" s="7" t="inlineStr">
         <is>
-          <t>SKU auto-generated per the SKU framework (e.g. APIC-HHF-250G-001). Visible in the row. Reused across the system (catalogue, market linkage, packaging).</t>
+          <t>SKU auto-generated as VARIANT-SUBVARIANT-WEIGHT-UNIT (spaces stripped, UPPERCASED, empty segments dropped) → e.g. WILDFLOWER-RAW-250-G. Read-only; reused across catalogue / market linkage / packaging. [Retail Price is read-only, fetched from Unit Pricing; there is no Unit Cost / Wholesale field on the variant — pricing lives in the Unit Pricing module.]</t>
         </is>
       </c>
       <c r="M199" s="7" t="inlineStr">
         <is>
-          <t>BRD: SKU framework + Variants tab fields.</t>
+          <t>BRD: SKU = Variant-SubVariant-Weight-Unit join (per wireframe).</t>
         </is>
       </c>
       <c r="N199" s="13" t="inlineStr">
@@ -14870,7 +14865,7 @@
       </c>
       <c r="D200" s="7" t="inlineStr">
         <is>
-          <t>Wholesale Price &amp;lt; Unit Cost shows a warning (selling at loss)</t>
+          <t>Variant Retail Price is read-only, fetched from Unit Pricing</t>
         </is>
       </c>
       <c r="E200" s="8" t="inlineStr">
@@ -14901,7 +14896,7 @@
       <c r="J200" s="7" t="inlineStr"/>
       <c r="K200" s="7" t="inlineStr">
         <is>
-          <t>• Unit Cost = 100, Wholesale Price = 80.</t>
+          <t>• Open a variant row. Attempt to edit Retail Price.</t>
         </is>
       </c>
       <c r="L200" s="7" t="inlineStr"/>
@@ -14937,7 +14932,7 @@
       </c>
       <c r="D201" s="7" t="inlineStr">
         <is>
-          <t>Retail Price &amp;lt; Wholesale Price hard-blocks save</t>
+          <t>Variant Volume auto-computes from L × B × H</t>
         </is>
       </c>
       <c r="E201" s="8" t="inlineStr">
@@ -14968,7 +14963,7 @@
       <c r="J201" s="7" t="inlineStr"/>
       <c r="K201" s="7" t="inlineStr">
         <is>
-          <t>• Wholesale = 150, Retail = 100.</t>
+          <t>• Set variant dimensions: L = 10, B = 5, H = 4 (cm).</t>
         </is>
       </c>
       <c r="L201" s="7" t="inlineStr"/>
@@ -15230,7 +15225,7 @@
       </c>
       <c r="D205" s="7" t="inlineStr">
         <is>
-          <t>Master SKU correctly expands to variant SKUs</t>
+          <t>Variant SKU auto-generates from Variant + Sub Variant + Net Weight + Unit</t>
         </is>
       </c>
       <c r="E205" s="8" t="inlineStr">
@@ -15261,18 +15256,17 @@
       <c r="J205" s="7" t="inlineStr"/>
       <c r="K205" s="7" t="inlineStr">
         <is>
-          <t>• Product Master SKU = APIC-HHF.
-• Add variants 250g, 500g, 1kg.</t>
+          <t>• Add variants: (Wildflower, Raw, 250, g), (Wildflower, Raw, 500, g), (Wildflower, Raw, 1, kg).</t>
         </is>
       </c>
       <c r="L205" s="7" t="inlineStr">
         <is>
-          <t>Variant SKUs: APIC-HHF-250G-001, APIC-HHF-500G-001, APIC-HHF-1KG-001. (Logic per SKU framework — verify against the SKU reference HTML.)</t>
+          <t>Variant SKUs = WILDFLOWER-RAW-250-G, WILDFLOWER-RAW-500-G, WILDFLOWER-RAW-1-KG (join of Variant-SubVariant-Weight-Unit; stripped, UPPERCASED, empty segments dropped). [No "APIC-HHF" master-expansion-with-numeric-suffix scheme exists in the wireframe.]</t>
         </is>
       </c>
       <c r="M205" s="7" t="inlineStr">
         <is>
-          <t>BRD QA fix: Master SKU expansion logic.</t>
+          <t>BRD: SKU = Variant-SubVariant-Weight-Unit join (per wireframe).</t>
         </is>
       </c>
       <c r="N205" s="13" t="inlineStr">
@@ -24774,7 +24768,7 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Required fields enforced: Name, Sector, District, Block, Village</t>
+          <t>Required fields enforced: Entrepreneur Name + Phone; geography auto-set from Program Access</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
@@ -24791,8 +24785,7 @@
         <is>
           <t>• Save with all fields blank.
 • Fill only Name; save.
-• Fill Name + Sector; save.
-• Continue progressively.</t>
+• Add Phone; save.</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr"/>
@@ -24832,7 +24825,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>DOB validation: not future, not &amp;gt; 100 years old, not &amp;lt; 14 years old</t>
+          <t>DOB validation: future date blocked</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -24847,9 +24840,7 @@
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>• DOB = tomorrow. Save.
-• DOB = 31-Dec-1899 (&gt; 100 years).
-• DOB = today - 10 years.</t>
+          <t>• DOB = tomorrow. Save.</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr"/>

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -1293,11 +1293,11 @@
         </is>
       </c>
       <c r="B85" s="5" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>13%</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
         </is>
       </c>
       <c r="B88" s="5" t="n">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Executed (Pass+Fail): 137  |  Pass rate of executed: 69%</t>
+          <t>Executed (Pass+Fail): 138  |  Pass rate of executed: 70%</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>16 / 5 / 0 / 28</t>
+          <t>17 / 5 / 0 / 27</t>
         </is>
       </c>
     </row>
@@ -19062,7 +19062,7 @@
       </c>
       <c r="D249" s="7" t="inlineStr">
         <is>
-          <t>Add 2 route legs with frequency; monthly cost auto-computed</t>
+          <t>Add a route with legs + a frequency; monthly/annual cost auto-computed (route-frequency model)</t>
         </is>
       </c>
       <c r="E249" s="8" t="inlineStr">
@@ -19093,20 +19093,20 @@
       <c r="J249" s="7" t="inlineStr"/>
       <c r="K249" s="7" t="inlineStr">
         <is>
-          <t>• Leg 1: Mawphlang → Shillong, ₹ 500/trip, 4 trips/month.
-• Leg 2: Shillong → Guwahati, ₹ 1,500/trip, 2 trips/month.</t>
+          <t>• Existing tab → + Add Logistics Route. Set Route name, Direction = Outbound, Frequency = Weekly (the build's frequency multipliers: Daily ×30/month · Twice a week · Weekly ×4 · Twice a month ×2 · Monthly ×1 · Every 2 months ×0.5).
+• Save once (legs need the saved parent route ID), then + Add Leg ×2: Leg 1 Mawphlang → Shillong, Cost ₹ 500; Leg 2 Shillong → Guwahati, Cost ₹ 1,500.</t>
         </is>
       </c>
       <c r="L249" s="7" t="inlineStr"/>
       <c r="M249" s="7" t="inlineStr"/>
-      <c r="N249" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="N249" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O249" s="7" t="inlineStr">
         <is>
-          <t>MODEL/SPEC MISMATCH (Logistic Service): live build MATCHES the BRD - route-level Frequency dropdown (Daily x30/Weekly/Twice-a-month/...) x sum-of-leg-costs = Monthly Cost -&gt; Annual x12. The TEST CASE assumes per-leg trips/month (500x4 + 1500x2) which maps to neither BRD nor build -&gt; test case needs REWRITE to the route-frequency model. Numeric roll-up not driven (legs require a saved parent route ID).</t>
+          <t>VERIFIED LIVE+SAVE (Logistic Service, record then deleted): route-frequency model. Route Frequency = Weekly (x4) at the ROUTE level; 2 legs (Rs 500 + Rs 1500). Total Cost Per Trip = Rs 2,000 (sum of legs); Trips/Month = 4; Monthly Cost = 2000 x 4 = Rs 8,000; Annual Cost = 8000 x 12 = Rs 96,000 - all computed exact. Test case REWRITTEN (S26) from the wrong per-leg-trips model to this route-frequency model; matches BRD + build. (Legs require a saved parent route ID - save first, then add legs.)</t>
         </is>
       </c>
       <c r="P249" s="8" t="inlineStr"/>

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="B85" s="5" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
@@ -1308,11 +1308,11 @@
         </is>
       </c>
       <c r="B86" s="5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>6%</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
         </is>
       </c>
       <c r="B88" s="5" t="n">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Executed (Pass+Fail): 138  |  Pass rate of executed: 70%</t>
+          <t>Executed (Pass+Fail): 140  |  Pass rate of executed: 69%</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>4 / 0 / 0 / 14</t>
+          <t>5 / 1 / 0 / 12</t>
         </is>
       </c>
     </row>
@@ -15759,18 +15759,18 @@
       </c>
       <c r="L201" s="7" t="inlineStr"/>
       <c r="M201" s="7" t="inlineStr"/>
-      <c r="N201" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O201" s="7" t="inlineStr"/>
+      <c r="N201" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O201" s="7" t="inlineStr">
+        <is>
+          <t>VERIFIED via API POST (Product PRD-2026-00007, then deleted): sku_data row L=10/B=5/H=4 -&gt; volume = 200 (server-computed = L x B x H, exact). Field is "volume" on the "Sku Data" child table.</t>
+        </is>
+      </c>
       <c r="P201" s="8" t="inlineStr"/>
-      <c r="Q201" s="7" t="inlineStr">
-        <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
-        </is>
-      </c>
+      <c r="Q201" s="7" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="7" t="inlineStr">
@@ -16060,16 +16060,24 @@
           <t>BRD: SKU = Variant-SubVariant-Weight-Unit join (per wireframe).</t>
         </is>
       </c>
-      <c r="N205" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O205" s="7" t="inlineStr"/>
-      <c r="P205" s="8" t="inlineStr"/>
+      <c r="N205" s="15" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O205" s="7" t="inlineStr">
+        <is>
+          <t>MODEL DEVIATION (Product variant SKU): build generates sku_code = "{size_variant}-{net_weight}{unit}" e.g. "Wildflower Raw-250gram" (verified via API POST, deleted). Spec PR-014 expects "WILDFLOWER-RAW-250-G" (UPPERCASED, Variant + Sub-Variant hyphen-joined, hyphen before an ABBREVIATED unit). Build = Title-case, single size_variant field, full unit name, no hyphen before unit. Also a separate auto-id product_sku (SKU-00000NN). Reconcile spec&lt;-&gt;build (PM call).</t>
+        </is>
+      </c>
+      <c r="P205" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="Q205" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Product variant SKU format deviates from spec.</t>
         </is>
       </c>
     </row>
@@ -17435,18 +17443,18 @@
       </c>
       <c r="L225" s="7" t="inlineStr"/>
       <c r="M225" s="7" t="inlineStr"/>
-      <c r="N225" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O225" s="7" t="inlineStr"/>
+      <c r="N225" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O225" s="7" t="inlineStr">
+        <is>
+          <t>LIVE (Raw Material, client-side): Amount Per Batch = Qty x Price = 10 x Rs 800 = Rs 8,000; RM Cost/Unit = Amount Per Batch / Batch Size = 8000 / 1 = Rs 8,000; TOTAL LANDED COST/UNIT Rs 8,000. Matches BRD (RM Cost/Unit = Amount Per Batch / Batch Size).</t>
+        </is>
+      </c>
       <c r="P225" s="8" t="inlineStr"/>
-      <c r="Q225" s="7" t="inlineStr">
-        <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
-        </is>
-      </c>
+      <c r="Q225" s="7" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="7" t="inlineStr">
@@ -18011,13 +18019,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="O233" s="7" t="inlineStr"/>
+      <c r="O233" s="7" t="inlineStr">
+        <is>
+          <t>BUILD GAP + spec mismatch (Infrastructure EMI): the deployed Infrastructure framework surfaces the FUNDING model only (Financial Model tab: project type -&gt; SELCO/MBMA/LIFCOM/User % split of Total Infrastructure Cost; LIFCOM = the loan portion) but exposes NO EMI / repayment-schedule field (checked Financial Model + Tracker tabs). The case expects flat EMI = Loan/Term (1,00,000/24 = Rs 4,166.67); the BRD specs a FIXED-tenure LIFCOM EMI (LIFCOM/60 for 5yr, /36 for 3yr) - neither an arbitrary 24-mo term nor any EMI readout is present. Flag to dev: is the LIFCOM repayment/EMI implemented? Then reconcile the term model.</t>
+        </is>
+      </c>
       <c r="P233" s="8" t="inlineStr"/>
-      <c r="Q233" s="7" t="inlineStr">
-        <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
-        </is>
-      </c>
+      <c r="Q233" s="7" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="7" t="inlineStr">
@@ -18767,13 +18775,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="O244" s="7" t="inlineStr"/>
+      <c r="O244" s="7" t="inlineStr">
+        <is>
+          <t>STRUCTURE CONFIRMED, test case MIS-MODELED (Product Packaging): build = per-packaging-card "Monthly Order Schedule" (Month/Qty/Price-Unit/Total; Total = Qty x Price/Unit; card running total + "All Existing - Total" Monthly/Annual roll-up). The case models it per-VARIANT-per-month (Jan A100+B50=150) -&gt; needs rewrite to the per-packaging monthly model (like LSVC-001). Numeric not driven: month rows need a selected product + packaging type (and likely a save-to-bridge); product autocomplete did not surface options via automation.</t>
+        </is>
+      </c>
       <c r="P244" s="8" t="inlineStr"/>
-      <c r="Q244" s="7" t="inlineStr">
-        <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
-        </is>
-      </c>
+      <c r="Q244" s="7" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" s="7" t="inlineStr">
@@ -19031,14 +19039,14 @@
       </c>
       <c r="L248" s="7" t="inlineStr"/>
       <c r="M248" s="7" t="inlineStr"/>
-      <c r="N248" s="9" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="N248" s="14" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="O248" s="7" t="inlineStr">
         <is>
-          <t>Logistic Packing core create+save+persist (FA).</t>
+          <t>STRUCTURE CONFIRMED, test case MIS-MODELED (Logistic Packing): build = "Monthly Shipment Quantities" matrix (one row/month, one column/packing item; "Cost columns multiply qty x Price/Unit") -&gt; "All Existing Packing - Total" Monthly/Annual cost. The case models a 3-layer transit spec (outer carton/secondary pouch/inner sealed with weights) -&gt; needs rewrite to the monthly-shipment-qty model. Numeric not driven (needs product + packing type + qty). NOTE: core create+save+persist was OK in S20; this ID is the transit-COST calc.</t>
         </is>
       </c>
       <c r="P248" s="8" t="inlineStr"/>

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="B85" s="5" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
@@ -1308,11 +1308,11 @@
         </is>
       </c>
       <c r="B86" s="5" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>5%</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Executed (Pass+Fail): 140  |  Pass rate of executed: 69%</t>
+          <t>Executed (Pass+Fail): 140  |  Pass rate of executed: 70%</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>5 / 1 / 0 / 12</t>
+          <t>6 / 0 / 0 / 12</t>
         </is>
       </c>
     </row>
@@ -16016,7 +16016,7 @@
       </c>
       <c r="D205" s="7" t="inlineStr">
         <is>
-          <t>Variant SKU auto-generates from Variant + Sub Variant + Net Weight + Unit</t>
+          <t>Variant SKU (sku_code) auto-generates from Variant + Sub Variant + Net Weight + Unit</t>
         </is>
       </c>
       <c r="E205" s="8" t="inlineStr">
@@ -16047,12 +16047,12 @@
       <c r="J205" s="7" t="inlineStr"/>
       <c r="K205" s="7" t="inlineStr">
         <is>
-          <t>• Add variants: (Wildflower, Raw, 250, g), (Wildflower, Raw, 500, g), (Wildflower, Raw, 1, kg).</t>
+          <t>• Add a variant: Variant = Wildflower, Sub Variant = Raw, Net Weight = 250, Unit = gram, (L=10, B=5, H=4).</t>
         </is>
       </c>
       <c r="L205" s="7" t="inlineStr">
         <is>
-          <t>Variant SKUs = WILDFLOWER-RAW-250-G, WILDFLOWER-RAW-500-G, WILDFLOWER-RAW-1-KG (join of Variant-SubVariant-Weight-Unit; stripped, UPPERCASED, empty segments dropped). [No "APIC-HHF" master-expansion-with-numeric-suffix scheme exists in the wireframe.]</t>
+          <t>sku_code = {Variant Name} {Sub Variant}-{Net Weight}{Unit} = "Wildflower Raw-250gram" (Variant + Sub-Variant combine into size_variant; weight+unit concatenated with no separator). A separate auto-id product_sku (SKU-00000NN) is also assigned. Title-case as stored — NOT uppercased/hyphen-segmented. [Verified live via API, S26 15-Jun-2026: sku_code = "Wildflower Raw-250gram". Reconciled to deployed build; flagged a recommendation to UPPERCASE if SKUs are used as keys.]</t>
         </is>
       </c>
       <c r="M205" s="7" t="inlineStr">
@@ -16060,26 +16060,18 @@
           <t>BRD: SKU = Variant-SubVariant-Weight-Unit join (per wireframe).</t>
         </is>
       </c>
-      <c r="N205" s="15" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="N205" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O205" s="7" t="inlineStr">
         <is>
-          <t>MODEL DEVIATION (Product variant SKU): build generates sku_code = "{size_variant}-{net_weight}{unit}" e.g. "Wildflower Raw-250gram" (verified via API POST, deleted). Spec PR-014 expects "WILDFLOWER-RAW-250-G" (UPPERCASED, Variant + Sub-Variant hyphen-joined, hyphen before an ABBREVIATED unit). Build = Title-case, single size_variant field, full unit name, no hyphen before unit. Also a separate auto-id product_sku (SKU-00000NN). Reconcile spec&lt;-&gt;build (PM call).</t>
-        </is>
-      </c>
-      <c r="P205" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="Q205" s="7" t="inlineStr">
-        <is>
-          <t>Product variant SKU format deviates from spec.</t>
-        </is>
-      </c>
+          <t>RECONCILED to build (S26, PM "take 1"): sku_code = "{Variant} {Sub Variant}-{Net Weight}{Unit}" = "Wildflower Raw-250gram" (verified live via API POST, deleted). BRD PR-EP-001 variant block + test case updated to this format (+ separate auto-id product_sku SKU-00000NN). Flagged a recommendation to UPPERCASE/strip-spaces if SKUs become keys. Build now matches the (updated) spec.</t>
+        </is>
+      </c>
+      <c r="P205" s="8" t="inlineStr"/>
+      <c r="Q205" s="7" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="7" t="inlineStr">
@@ -18734,7 +18726,7 @@
       </c>
       <c r="D244" s="7" t="inlineStr">
         <is>
-          <t>Monthly packaging qty sums across variants per month</t>
+          <t>Packaging Monthly Order Schedule: Total = Qty × Price/Unit; qty rolls up to annual</t>
         </is>
       </c>
       <c r="E244" s="8" t="inlineStr">
@@ -18765,7 +18757,7 @@
       <c r="J244" s="7" t="inlineStr"/>
       <c r="K244" s="7" t="inlineStr">
         <is>
-          <t>• Variant A: 100 units in Jan. Variant B: 50 in Jan.</t>
+          <t>• Existing tab → + Add Packaging (pick a product + packaging Type + Price per Unit). In Section III "Monthly Order Schedule", + Add Month rows with Qty and Price/Unit (e.g. Jan Qty 100 @ ₹5, Feb Qty 50 @ ₹5).</t>
         </is>
       </c>
       <c r="L244" s="7" t="inlineStr"/>
@@ -18777,7 +18769,7 @@
       </c>
       <c r="O244" s="7" t="inlineStr">
         <is>
-          <t>STRUCTURE CONFIRMED, test case MIS-MODELED (Product Packaging): build = per-packaging-card "Monthly Order Schedule" (Month/Qty/Price-Unit/Total; Total = Qty x Price/Unit; card running total + "All Existing - Total" Monthly/Annual roll-up). The case models it per-VARIANT-per-month (Jan A100+B50=150) -&gt; needs rewrite to the per-packaging monthly model (like LSVC-001). Numeric not driven: month rows need a selected product + packaging type (and likely a save-to-bridge); product autocomplete did not surface options via automation.</t>
+          <t>REWRITTEN to build model (S26): per-packaging "Monthly Order Schedule" (Month/Qty/Price-Unit/Total; Total = Qty x Price/Unit; parent total_annual_quantity = sum of monthly Qty; "All Existing - Total" Monthly Spend). Model + fields verified live (packaging_info_existing row has price_per_unit + avg_monthly_qty; parent total_annual_quantity). End-to-end roll-up to a NON-ZERO total NOT driven (month rows need product + packaging type + save-to-bridge; product autocomplete not automatable) -&gt; kept Not Run, manual spot-check pending. Deliberately NOT marked Pass per the bug-bar (cf Bug 82: a Unit Pricing roll-up silently stayed Rs 0).</t>
         </is>
       </c>
       <c r="P244" s="8" t="inlineStr"/>
@@ -19003,7 +18995,7 @@
       </c>
       <c r="D248" s="7" t="inlineStr">
         <is>
-          <t>Add transit packaging spec: outer carton, secondary pouch, inner sealed</t>
+          <t>Logistic Packing: per-product transit layers + monthly shipment matrix → Monthly/Annual cost</t>
         </is>
       </c>
       <c r="E248" s="8" t="inlineStr">
@@ -19034,7 +19026,8 @@
       <c r="J248" s="7" t="inlineStr"/>
       <c r="K248" s="7" t="inlineStr">
         <is>
-          <t>• 3 layers, weights, costs.</t>
+          <t>• Existing tab → + Add Product → Save (product needs a saved ID). In Section I "Packing Details", + Add Row packing items: Type of Packing = Outer / Inner / Cushion, Unit = ml / kg / meter, with Price per Unit (e.g. Outer ₹50, Inner ₹10) and Qty/Month.
+• In "Monthly Shipment Quantities" matrix (one row/month, one column per packing item), enter monthly quantities.</t>
         </is>
       </c>
       <c r="L248" s="7" t="inlineStr"/>
@@ -19046,7 +19039,7 @@
       </c>
       <c r="O248" s="7" t="inlineStr">
         <is>
-          <t>STRUCTURE CONFIRMED, test case MIS-MODELED (Logistic Packing): build = "Monthly Shipment Quantities" matrix (one row/month, one column/packing item; "Cost columns multiply qty x Price/Unit") -&gt; "All Existing Packing - Total" Monthly/Annual cost. The case models a 3-layer transit spec (outer carton/secondary pouch/inner sealed with weights) -&gt; needs rewrite to the monthly-shipment-qty model. Numeric not driven (needs product + packing type + qty). NOTE: core create+save+persist was OK in S20; this ID is the transit-COST calc.</t>
+          <t>REWRITTEN to build model (S26): per-PRODUCT blocks; packing items by transit LAYER (Type of Packing enum = Inner/Outer/Cushion; Unit enum = ml/kg/meter; per-item price_per_unit + qty_per_month) - all verified live by saving a record (LP-Donbok Rymbai-00001, deleted). Cost = "Monthly Shipment Quantities" matrix qty x Price/Unit -&gt; "All Existing Packing - Total" Monthly/Annual (x12). The old case (3-layer transit weights) was close-but-mis-modeled -&gt; rewritten. End-to-end matrix roll-up to a NON-ZERO total NOT driven (nested product-&gt;save-&gt;packing-item-&gt;save-&gt;matrix flow) -&gt; Not Run, manual spot-check pending (cf Bug 82).</t>
         </is>
       </c>
       <c r="P248" s="8" t="inlineStr"/>

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -18769,7 +18769,7 @@
       </c>
       <c r="O244" s="7" t="inlineStr">
         <is>
-          <t>REWRITTEN to build model (S26): per-packaging "Monthly Order Schedule" (Month/Qty/Price-Unit/Total; Total = Qty x Price/Unit; parent total_annual_quantity = sum of monthly Qty; "All Existing - Total" Monthly Spend). Model + fields verified live (packaging_info_existing row has price_per_unit + avg_monthly_qty; parent total_annual_quantity). End-to-end roll-up to a NON-ZERO total NOT driven (month rows need product + packaging type + save-to-bridge; product autocomplete not automatable) -&gt; kept Not Run, manual spot-check pending. Deliberately NOT marked Pass per the bug-bar (cf Bug 82: a Unit Pricing roll-up silently stayed Rs 0).</t>
+          <t>REWRITTEN to build model (S26): per-packaging "Monthly Order Schedule" (Month/Qty/Price-Unit/Total; Total = Qty x Price/Unit; parent total_annual_quantity = sum of monthly Qty; "All Existing - Total" Monthly Spend). Model + fields verified live (packaging_info_existing row has price_per_unit + avg_monthly_qty; parent total_annual_quantity). SPOT-CHECK ATTEMPTED 15-Jun and BLOCKED by automation: the async product autocomplete (portal search) intermittently returns no options to the driver, and Monthly Cost is a UI-only aggregate gated behind product + nested save-bridges -&gt; needs a HUMAN QA to click through (~10 min). Kept Not Run; deliberately NOT marked Pass per the bug-bar (cf Bug 82: a Unit Pricing roll-up silently stayed Rs 0).</t>
         </is>
       </c>
       <c r="P244" s="8" t="inlineStr"/>
@@ -19039,7 +19039,7 @@
       </c>
       <c r="O248" s="7" t="inlineStr">
         <is>
-          <t>REWRITTEN to build model (S26): per-PRODUCT blocks; packing items by transit LAYER (Type of Packing enum = Inner/Outer/Cushion; Unit enum = ml/kg/meter; per-item price_per_unit + qty_per_month) - all verified live by saving a record (LP-Donbok Rymbai-00001, deleted). Cost = "Monthly Shipment Quantities" matrix qty x Price/Unit -&gt; "All Existing Packing - Total" Monthly/Annual (x12). The old case (3-layer transit weights) was close-but-mis-modeled -&gt; rewritten. End-to-end matrix roll-up to a NON-ZERO total NOT driven (nested product-&gt;save-&gt;packing-item-&gt;save-&gt;matrix flow) -&gt; Not Run, manual spot-check pending (cf Bug 82).</t>
+          <t>REWRITTEN to build model (S26): per-PRODUCT blocks; packing items by transit LAYER (Type of Packing enum = Inner/Outer/Cushion; Unit enum = ml/kg/meter; per-item price_per_unit + qty_per_month) - all verified live by saving a record (LP-Donbok Rymbai-00001, deleted). Cost = "Monthly Shipment Quantities" matrix qty x Price/Unit -&gt; "All Existing Packing - Total" Monthly/Annual (x12). The old case (3-layer transit weights) was close-but-mis-modeled -&gt; rewritten. End-to-end matrix roll-up to a NON-ZERO total NOT driven. SPOT-CHECK ATTEMPTED 15-Jun and BLOCKED: posted a record with entries (qty_per_month/price) but Monthly Cost stayed Rs 0 because cost is driven by the lp_monthly MATRIX, not the entries; the matrix is gated behind the async product autocomplete + nested save-bridges (not automatable) -&gt; needs HUMAN QA. NOTE: no existing LPACK record populates lp_monthly either (feature under-exercised). Kept Not Run (cf Bug 82).</t>
         </is>
       </c>
       <c r="P248" s="8" t="inlineStr"/>

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -19039,7 +19039,7 @@
       </c>
       <c r="O248" s="7" t="inlineStr">
         <is>
-          <t>REWRITTEN to build model (S26): per-PRODUCT blocks; packing items by transit LAYER (Type of Packing enum = Inner/Outer/Cushion; Unit enum = ml/kg/meter; per-item price_per_unit + qty_per_month) - all verified live by saving a record (LP-Donbok Rymbai-00001, deleted). Cost = "Monthly Shipment Quantities" matrix qty x Price/Unit -&gt; "All Existing Packing - Total" Monthly/Annual (x12). The old case (3-layer transit weights) was close-but-mis-modeled -&gt; rewritten. End-to-end matrix roll-up to a NON-ZERO total NOT driven. SPOT-CHECK ATTEMPTED 15-Jun and BLOCKED: posted a record with entries (qty_per_month/price) but Monthly Cost stayed Rs 0 because cost is driven by the lp_monthly MATRIX, not the entries; the matrix is gated behind the async product autocomplete + nested save-bridges (not automatable) -&gt; needs HUMAN QA. NOTE: no existing LPACK record populates lp_monthly either (feature under-exercised). Kept Not Run (cf Bug 82).</t>
+          <t>REWRITTEN to build model (S26): per-PRODUCT blocks; packing items by transit LAYER (Type of Packing enum = Inner/Outer/Cushion; Unit enum = ml/kg/meter; per-item price_per_unit + qty_per_month) - all verified live by saving a record (LP-Donbok Rymbai-00001, deleted). Cost = "Monthly Shipment Quantities" matrix qty x Price/Unit -&gt; "All Existing Packing - Total" Monthly/Annual (x12). The old case (3-layer transit weights) was close-but-mis-modeled -&gt; rewritten. End-to-end matrix roll-up to a NON-ZERO total NOT reached. SPOT-CHECK DRIVEN LIVE 15-Jun (full UI): EP + Product selected, product block saved, packing item added (Unit=kg, Price/Unit=Rs 50 committed) - BUT the "Type of Packing" picker returned NO options for Outer/Inner/Cushion, so type_of_packing never committed (saved lp_items row had price but no type). The monthly shipment matrix exposes a column only for a packing type WITH a price -&gt; with no committed type the matrix stays empty and Monthly Cost = Rs 0. This is a likely BLOCKER (packing-type picker/master), consistent with NO existing LPACK record populating the matrix. Candidate Bug 84 - needs dev confirm (is the packing-type master seeded? what does the picker query?). Kept Not Run.</t>
         </is>
       </c>
       <c r="P248" s="8" t="inlineStr"/>

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -19039,7 +19039,7 @@
       </c>
       <c r="O248" s="7" t="inlineStr">
         <is>
-          <t>REWRITTEN to build model (S26): per-PRODUCT blocks; packing items by transit LAYER (Type of Packing enum = Inner/Outer/Cushion; Unit enum = ml/kg/meter; per-item price_per_unit + qty_per_month) - all verified live by saving a record (LP-Donbok Rymbai-00001, deleted). Cost = "Monthly Shipment Quantities" matrix qty x Price/Unit -&gt; "All Existing Packing - Total" Monthly/Annual (x12). The old case (3-layer transit weights) was close-but-mis-modeled -&gt; rewritten. End-to-end matrix roll-up to a NON-ZERO total NOT reached. SPOT-CHECK DRIVEN LIVE 15-Jun (full UI): EP + Product selected, product block saved, packing item added (Unit=kg, Price/Unit=Rs 50 committed) - BUT the "Type of Packing" picker returned NO options for Outer/Inner/Cushion, so type_of_packing never committed (saved lp_items row had price but no type). The monthly shipment matrix exposes a column only for a packing type WITH a price -&gt; with no committed type the matrix stays empty and Monthly Cost = Rs 0. This is a likely BLOCKER (packing-type picker/master), consistent with NO existing LPACK record populating the matrix. Candidate Bug 84 - needs dev confirm (is the packing-type master seeded? what does the picker query?). Kept Not Run.</t>
+          <t>REWRITTEN to build model (S26): per-PRODUCT blocks; packing items by transit LAYER (Type of Packing enum = Inner/Outer/Cushion; Unit enum = ml/kg/meter; per-item price_per_unit + qty_per_month) - all verified live by saving a record (LP-Donbok Rymbai-00001, deleted). Cost = "Monthly Shipment Quantities" matrix qty x Price/Unit -&gt; "All Existing Packing - Total" Monthly/Annual (x12). The old case (3-layer transit weights) was close-but-mis-modeled -&gt; rewritten. End-to-end matrix roll-up to a NON-ZERO total NOT reached. SPOT-CHECK DRIVEN LIVE 15-Jun (full UI): EP + Product selected, product block saved, packing item added (Unit=kg, Price/Unit=Rs 50 committed) - BUT the "Type of Packing" picker returned NO options for Outer/Inner/Cushion, so type_of_packing never committed (saved lp_items row had price but no type). The monthly shipment matrix exposes a column only for a packing type WITH a price -&gt; with no committed type the matrix stays empty and Monthly Cost = Rs 0. ROOT CAUSE CONFIRMED (15-Jun): the Type-of-Packing field is a Link to the "Logistic Packing Type" master, which has 0 records (and "Logistic Packing Material" = 0 too) - verified via get_list. The picker works; the masters are UNSEEDED -&gt; no type selectable -&gt; matrix never populates -&gt; Monthly/Annual cost stuck Rs 0. LOGGED as Bug 84 (P2, data/config gap - seed the masters; not calc code). Calc itself remains untestable end-to-end until seeded. Kept Not Run.</t>
         </is>
       </c>
       <c r="P248" s="8" t="inlineStr"/>

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -18769,7 +18769,7 @@
       </c>
       <c r="O244" s="7" t="inlineStr">
         <is>
-          <t>REWRITTEN to build model (S26): per-packaging "Monthly Order Schedule" (Month/Qty/Price-Unit/Total; Total = Qty x Price/Unit; parent total_annual_quantity = sum of monthly Qty; "All Existing - Total" Monthly Spend). Model + fields verified live (packaging_info_existing row has price_per_unit + avg_monthly_qty; parent total_annual_quantity). SPOT-CHECK ATTEMPTED 15-Jun and BLOCKED by automation: the async product autocomplete (portal search) intermittently returns no options to the driver, and Monthly Cost is a UI-only aggregate gated behind product + nested save-bridges -&gt; needs a HUMAN QA to click through (~10 min). Kept Not Run; deliberately NOT marked Pass per the bug-bar (cf Bug 82: a Unit Pricing roll-up silently stayed Rs 0).</t>
+          <t>REWRITTEN to build model (S26): per-packaging "Monthly Order Schedule" (Month/Qty/Price-Unit/Total; Total = Qty x Price/Unit; parent total_annual_quantity = sum of monthly Qty; "All Existing - Total" Monthly Spend). Model + fields verified live (packaging_info_existing row has price_per_unit + avg_monthly_qty; parent total_annual_quantity). SPOT-CHECK 15-Jun: the roll-up is gated behind product + packaging type + the monthly schedule (nested save-bridges). Its masters ARE seeded (verified: "Packaging Type" = 6 records [Pieces/HDPE Pouch/Glass Jar/Kraft Paper Box/Cloth Wrap/Box]; "DF Module Material" = 126), so PKG is NOT affected by the LPACK empty-master gap (Bug 84) - it is completable. End-to-end monthly roll-up to a non-zero total not driven here -&gt; needs a HUMAN QA click-through (~10 min) to flip to Pass. Kept Not Run; not marked Pass per the bug-bar (cf Bug 82).</t>
         </is>
       </c>
       <c r="P244" s="8" t="inlineStr"/>

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="B85" s="5" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
@@ -1338,11 +1338,11 @@
         </is>
       </c>
       <c r="B88" s="5" t="n">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>81%</t>
+          <t>80%</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Executed (Pass+Fail): 140  |  Pass rate of executed: 70%</t>
+          <t>Executed (Pass+Fail): 141  |  Pass rate of executed: 70%</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>17 / 5 / 0 / 27</t>
+          <t>18 / 5 / 0 / 26</t>
         </is>
       </c>
     </row>
@@ -19026,20 +19026,21 @@
       <c r="J248" s="7" t="inlineStr"/>
       <c r="K248" s="7" t="inlineStr">
         <is>
-          <t>• Existing tab → + Add Product → Save (product needs a saved ID). In Section I "Packing Details", + Add Row packing items: Type of Packing = Outer / Inner / Cushion, Unit = ml / kg / meter, with Price per Unit (e.g. Outer ₹50, Inner ₹10) and Qty/Month.
-• In "Monthly Shipment Quantities" matrix (one row/month, one column per packing item), enter monthly quantities.</t>
+          <t>• Pre-req: the Logistic Packing Type master must be seeded (e.g. Inner / Outer / Cushion) — see Bug 84.
+• Existing tab → + Add Product → Save (product needs a saved ID). In Section I "Packing Details", + Add Row: Type of Packing = Outer (from the master), Unit = kg, Price per Unit = ₹50.
+• In the "Monthly Shipment Quantities" matrix (one row/month, one column per packing item), enter a monthly quantity (e.g. Apr = 100).</t>
         </is>
       </c>
       <c r="L248" s="7" t="inlineStr"/>
       <c r="M248" s="7" t="inlineStr"/>
-      <c r="N248" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="N248" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O248" s="7" t="inlineStr">
         <is>
-          <t>REWRITTEN to build model (S26): per-PRODUCT blocks; packing items by transit LAYER (Type of Packing enum = Inner/Outer/Cushion; Unit enum = ml/kg/meter; per-item price_per_unit + qty_per_month) - all verified live by saving a record (LP-Donbok Rymbai-00001, deleted). Cost = "Monthly Shipment Quantities" matrix qty x Price/Unit -&gt; "All Existing Packing - Total" Monthly/Annual (x12). The old case (3-layer transit weights) was close-but-mis-modeled -&gt; rewritten. End-to-end matrix roll-up to a NON-ZERO total NOT reached. SPOT-CHECK DRIVEN LIVE 15-Jun (full UI): EP + Product selected, product block saved, packing item added (Unit=kg, Price/Unit=Rs 50 committed) - BUT the "Type of Packing" picker returned NO options for Outer/Inner/Cushion, so type_of_packing never committed (saved lp_items row had price but no type). The monthly shipment matrix exposes a column only for a packing type WITH a price -&gt; with no committed type the matrix stays empty and Monthly Cost = Rs 0. ROOT CAUSE CONFIRMED (15-Jun): the Type-of-Packing field is a Link to the "Logistic Packing Type" master, which has 0 records (and "Logistic Packing Material" = 0 too) - verified via get_list. The picker works; the masters are UNSEEDED -&gt; no type selectable -&gt; matrix never populates -&gt; Monthly/Annual cost stuck Rs 0. LOGGED as Bug 84 (P2, data/config gap - seed the masters; not calc code). Calc itself remains untestable end-to-end until seeded. Kept Not Run.</t>
+          <t>VERIFIED LIVE 15-Jun after seeding the "Logistic Packing Type" master (Inner/Outer/Cushion - per user go-ahead; the Bug 84 fix). Built a record via API (product EP-PROD-0017 + packing item Type=Outer/Unit=kg/Price Rs 50 + monthly shipment Apr qty=100), opened in UI: matrix column "Outer @ Rs 50/unit"; Month Total = qty x Price/Unit = 100 x 50 = Rs 5,000; "All Existing Packing - Total" footer: Annual Units = sum monthly qty = 100, Annual Cost = sum(qty x Price/Unit) = Rs 5,000, Monthly Cost = Annual/12 (avg) = Rs 417. Calc CORRECT. The earlier Rs 0 was solely the unseeded master (Bug 84), not a calc defect. Test case rewritten to this verified model; transaction record deleted (master seed retained as the Bug-84 fix).</t>
         </is>
       </c>
       <c r="P248" s="8" t="inlineStr"/>

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="B85" s="5" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         </is>
       </c>
       <c r="B88" s="5" t="n">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Executed (Pass+Fail): 141  |  Pass rate of executed: 70%</t>
+          <t>Executed (Pass+Fail): 142  |  Pass rate of executed: 70%</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>18 / 5 / 0 / 26</t>
+          <t>19 / 5 / 0 / 25</t>
         </is>
       </c>
     </row>
@@ -18757,19 +18757,19 @@
       <c r="J244" s="7" t="inlineStr"/>
       <c r="K244" s="7" t="inlineStr">
         <is>
-          <t>• Existing tab → + Add Packaging (pick a product + packaging Type + Price per Unit). In Section III "Monthly Order Schedule", + Add Month rows with Qty and Price/Unit (e.g. Jan Qty 100 @ ₹5, Feb Qty 50 @ ₹5).</t>
+          <t>• Existing tab → + Add Packaging (Type of Packaging from the Packaging Master, Material from Material Master, Price per Unit ₹5). In the "Monthly Order Schedule", + Add Month with Qty (e.g. 100).</t>
         </is>
       </c>
       <c r="L244" s="7" t="inlineStr"/>
       <c r="M244" s="7" t="inlineStr"/>
-      <c r="N244" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="N244" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O244" s="7" t="inlineStr">
         <is>
-          <t>REWRITTEN to build model (S26): per-packaging "Monthly Order Schedule" (Month/Qty/Price-Unit/Total; Total = Qty x Price/Unit; parent total_annual_quantity = sum of monthly Qty; "All Existing - Total" Monthly Spend). Model + fields verified live (packaging_info_existing row has price_per_unit + avg_monthly_qty; parent total_annual_quantity). SPOT-CHECK 15-Jun: the roll-up is gated behind product + packaging type + the monthly schedule (nested save-bridges). Its masters ARE seeded (verified: "Packaging Type" = 6 records [Pieces/HDPE Pouch/Glass Jar/Kraft Paper Box/Cloth Wrap/Box]; "DF Module Material" = 126), so PKG is NOT affected by the LPACK empty-master gap (Bug 84) - it is completable. End-to-end monthly roll-up to a non-zero total not driven here -&gt; needs a HUMAN QA click-through (~10 min) to flip to Pass. Kept Not Run; not marked Pass per the bug-bar (cf Bug 82).</t>
+          <t>VERIFIED LIVE 15-Jun via an API-built record (DF Packaging for EP-00023, then deleted): packaging card Type="Plastic Packaging"/Material="Plastic Sheets"/Price Rs 5 + monthly schedule (Apr, Quantity Ordered 100). Per-month total_order_cost = Qty x Price/Unit = 100 x 5 = Rs 500 (SERVER-COMPUTED, exact); opened in UI -&gt; month-row Total Rs 500 + card running total "Qty 100 - Rs 500". Calc CORRECT. Masters seeded (real link targets: Packaging Master=1 "Plastic Packaging", Material Master=1 "Plastic Sheets" - NOT the "Packaging Type"=6 doctype I first checked, but both actual targets have records, so PKG is not blocked). MINOR data-quality note: the persisted parent total_annual_quantity stays 0 on save (UI computes/displays the correct per-card qty/cost; the denormalized field is not set server-side) - only matters if a report reads it directly.</t>
         </is>
       </c>
       <c r="P244" s="8" t="inlineStr"/>

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -1293,11 +1293,11 @@
         </is>
       </c>
       <c r="B85" s="5" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>14%</t>
         </is>
       </c>
     </row>
@@ -1308,11 +1308,11 @@
         </is>
       </c>
       <c r="B86" s="5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>6%</t>
         </is>
       </c>
     </row>
@@ -1323,11 +1323,11 @@
         </is>
       </c>
       <c r="B87" s="5" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>3%</t>
         </is>
       </c>
     </row>
@@ -1338,11 +1338,11 @@
         </is>
       </c>
       <c r="B88" s="5" t="n">
-        <v>614</v>
+        <v>593</v>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>78%</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Executed (Pass+Fail): 142  |  Pass rate of executed: 70%</t>
+          <t>Executed (Pass+Fail): 151  |  Pass rate of executed: 72%</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>0 / 0 / 0 / 10</t>
+          <t>3 / 1 / 0 / 6</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>1 / 0 / 0 / 19</t>
+          <t>4 / 0 / 7 / 9</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>2 / 0 / 0 / 8</t>
+          <t>2 / 0 / 5 / 3</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>2 / 2 / 1 / 6</t>
+          <t>4 / 2 / 1 / 4</t>
         </is>
       </c>
     </row>
@@ -1844,18 +1844,18 @@
           <t>BRD: PR-OV-001 (System Architecture &amp; Auth)</t>
         </is>
       </c>
-      <c r="N2" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O2" s="7" t="inlineStr"/>
+      <c r="N2" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O2" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: unauthenticated base URL -&gt; redirected to /primerural/login (observed at session start).</t>
+        </is>
+      </c>
       <c r="P2" s="8" t="inlineStr"/>
-      <c r="Q2" s="7" t="inlineStr">
-        <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
-        </is>
-      </c>
+      <c r="Q2" s="7" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
@@ -2071,18 +2071,18 @@
       </c>
       <c r="L5" s="7" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
-      <c r="N5" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O5" s="7" t="inlineStr"/>
+      <c r="N5" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O5" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: invalid route (/primerural/this-route-does-not-exist-xyz) -&gt; graceful redirect to Landscape, NO stack trace. (Minor: no explicit 404 page; silent fallback to landing.)</t>
+        </is>
+      </c>
       <c r="P5" s="8" t="inlineStr"/>
-      <c r="Q5" s="7" t="inlineStr">
-        <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
-        </is>
-      </c>
+      <c r="Q5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -2138,18 +2138,18 @@
       </c>
       <c r="L6" s="7" t="inlineStr"/>
       <c r="M6" s="7" t="inlineStr"/>
-      <c r="N6" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O6" s="7" t="inlineStr"/>
+      <c r="N6" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O6" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: route to a non-existent record (DF Financials/NOPE-999) -&gt; app shell, NO Python traceback exposed.</t>
+        </is>
+      </c>
       <c r="P6" s="8" t="inlineStr"/>
-      <c r="Q6" s="7" t="inlineStr">
-        <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
-        </is>
-      </c>
+      <c r="Q6" s="7" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -2274,16 +2274,24 @@
       </c>
       <c r="L8" s="7" t="inlineStr"/>
       <c r="M8" s="7" t="inlineStr"/>
-      <c r="N8" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O8" s="7" t="inlineStr"/>
-      <c r="P8" s="8" t="inlineStr"/>
+      <c r="N8" s="15" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O8" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: browser tab title does NOT update per route - always "PRIME Rural Meghalaya" on Landscape, framework forms, bad routes. Spec wants the title to reflect the active route.</t>
+        </is>
+      </c>
+      <c r="P8" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="Q8" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Tab title static across routes.</t>
         </is>
       </c>
     </row>
@@ -4067,18 +4075,18 @@
       </c>
       <c r="L34" s="7" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
-      <c r="N34" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O34" s="7" t="inlineStr"/>
+      <c r="N34" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O34" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: login with a non-existent email -&gt; 401 "Invalid login credentials" - generic message, does not reveal whether the email exists. (Tested non-existent email to avoid locking a real account.)</t>
+        </is>
+      </c>
       <c r="P34" s="8" t="inlineStr"/>
-      <c r="Q34" s="7" t="inlineStr">
-        <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
-        </is>
-      </c>
+      <c r="Q34" s="7" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
@@ -4279,16 +4287,20 @@
           <t>OWASP A07; Frappe default lockout settings.</t>
         </is>
       </c>
-      <c r="N37" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O37" s="7" t="inlineStr"/>
+      <c r="N37" s="16" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O37" s="7" t="inlineStr">
+        <is>
+          <t>Brute-force lockout - NOT exercised: 5+ failed logins would lock a real staging account. Recommend dev/manual verify against a throwaway user.</t>
+        </is>
+      </c>
       <c r="P37" s="8" t="inlineStr"/>
       <c r="Q37" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Would lock real accounts.</t>
         </is>
       </c>
     </row>
@@ -4346,18 +4358,18 @@
       </c>
       <c r="L38" s="7" t="inlineStr"/>
       <c r="M38" s="7" t="inlineStr"/>
-      <c r="N38" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O38" s="7" t="inlineStr"/>
+      <c r="N38" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O38" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: login password field is type=password (masked) with a "Show" toggle.</t>
+        </is>
+      </c>
       <c r="P38" s="8" t="inlineStr"/>
-      <c r="Q38" s="7" t="inlineStr">
-        <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
-        </is>
-      </c>
+      <c r="Q38" s="7" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
@@ -4619,16 +4631,20 @@
       </c>
       <c r="L42" s="7" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
-      <c r="N42" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O42" s="7" t="inlineStr"/>
+      <c r="N42" s="16" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O42" s="7" t="inlineStr">
+        <is>
+          <t>Google SSO paths - need a real Google account / IdP consent flow (not drivable here). "Continue with Google" link present + correctly formed on the login page.</t>
+        </is>
+      </c>
       <c r="P42" s="8" t="inlineStr"/>
       <c r="Q42" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Needs Google IdP.</t>
         </is>
       </c>
     </row>
@@ -4686,16 +4702,20 @@
       </c>
       <c r="L43" s="7" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
-      <c r="N43" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O43" s="7" t="inlineStr"/>
+      <c r="N43" s="16" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O43" s="7" t="inlineStr">
+        <is>
+          <t>Google SSO paths - need a real Google account / IdP consent flow (not drivable here). "Continue with Google" link present + correctly formed on the login page.</t>
+        </is>
+      </c>
       <c r="P43" s="8" t="inlineStr"/>
       <c r="Q43" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Needs Google IdP.</t>
         </is>
       </c>
     </row>
@@ -4753,16 +4773,20 @@
       </c>
       <c r="L44" s="7" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
-      <c r="N44" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O44" s="7" t="inlineStr"/>
+      <c r="N44" s="16" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O44" s="7" t="inlineStr">
+        <is>
+          <t>Google SSO paths - need a real Google account / IdP consent flow (not drivable here). "Continue with Google" link present + correctly formed on the login page.</t>
+        </is>
+      </c>
       <c r="P44" s="8" t="inlineStr"/>
       <c r="Q44" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Needs Google IdP.</t>
         </is>
       </c>
     </row>
@@ -4889,16 +4913,20 @@
       </c>
       <c r="L46" s="7" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
-      <c r="N46" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O46" s="7" t="inlineStr"/>
+      <c r="N46" s="16" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O46" s="7" t="inlineStr">
+        <is>
+          <t>Idle session timeout - needs a long idle wait (default Frappe ~3 days/configurable); not drivable in-session.</t>
+        </is>
+      </c>
       <c r="P46" s="8" t="inlineStr"/>
       <c r="Q46" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Needs idle wait.</t>
         </is>
       </c>
     </row>
@@ -4956,18 +4984,18 @@
       </c>
       <c r="L47" s="7" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
-      <c r="N47" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O47" s="7" t="inlineStr"/>
+      <c r="N47" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O47" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: session "sid" cookie is NOT readable via document.cookie (HttpOnly inferred) and the context is HTTPS (Secure). (SameSite not asserted here.)</t>
+        </is>
+      </c>
       <c r="P47" s="8" t="inlineStr"/>
-      <c r="Q47" s="7" t="inlineStr">
-        <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
-        </is>
-      </c>
+      <c r="Q47" s="7" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
@@ -5094,16 +5122,20 @@
       </c>
       <c r="L49" s="7" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
-      <c r="N49" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O49" s="7" t="inlineStr"/>
+      <c r="N49" s="16" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O49" s="7" t="inlineStr">
+        <is>
+          <t>Concurrent-device sessions / stolen-sid-from-different-IP - need a second device/session + IP control.</t>
+        </is>
+      </c>
       <c r="P49" s="8" t="inlineStr"/>
       <c r="Q49" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Needs multi-session/IP.</t>
         </is>
       </c>
     </row>
@@ -5163,16 +5195,20 @@
       </c>
       <c r="L50" s="7" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
-      <c r="N50" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O50" s="7" t="inlineStr"/>
+      <c r="N50" s="16" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O50" s="7" t="inlineStr">
+        <is>
+          <t>Concurrent-device sessions / stolen-sid-from-different-IP - need a second device/session + IP control.</t>
+        </is>
+      </c>
       <c r="P50" s="8" t="inlineStr"/>
       <c r="Q50" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Needs multi-session/IP.</t>
         </is>
       </c>
     </row>
@@ -23620,16 +23656,20 @@
       </c>
       <c r="L313" s="7" t="inlineStr"/>
       <c r="M313" s="7" t="inlineStr"/>
-      <c r="N313" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O313" s="7" t="inlineStr"/>
+      <c r="N313" s="16" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O313" s="7" t="inlineStr">
+        <is>
+          <t>DB internals (indexes, encryption-at-rest, migration reversibility, backup freshness, EXPLAIN no-full-scan) - require DB/server-shell access, not available via the app/API as CT-IT. Dev/infra to verify.</t>
+        </is>
+      </c>
       <c r="P313" s="8" t="inlineStr"/>
       <c r="Q313" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Needs DB/server access.</t>
         </is>
       </c>
     </row>
@@ -23754,16 +23794,20 @@
       </c>
       <c r="L315" s="7" t="inlineStr"/>
       <c r="M315" s="7" t="inlineStr"/>
-      <c r="N315" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O315" s="7" t="inlineStr"/>
+      <c r="N315" s="16" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O315" s="7" t="inlineStr">
+        <is>
+          <t>DB internals (indexes, encryption-at-rest, migration reversibility, backup freshness, EXPLAIN no-full-scan) - require DB/server-shell access, not available via the app/API as CT-IT. Dev/infra to verify.</t>
+        </is>
+      </c>
       <c r="P315" s="8" t="inlineStr"/>
       <c r="Q315" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Needs DB/server access.</t>
         </is>
       </c>
     </row>
@@ -23955,16 +23999,20 @@
       </c>
       <c r="L318" s="7" t="inlineStr"/>
       <c r="M318" s="7" t="inlineStr"/>
-      <c r="N318" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O318" s="7" t="inlineStr"/>
+      <c r="N318" s="16" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O318" s="7" t="inlineStr">
+        <is>
+          <t>DB internals (indexes, encryption-at-rest, migration reversibility, backup freshness, EXPLAIN no-full-scan) - require DB/server-shell access, not available via the app/API as CT-IT. Dev/infra to verify.</t>
+        </is>
+      </c>
       <c r="P318" s="8" t="inlineStr"/>
       <c r="Q318" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Needs DB/server access.</t>
         </is>
       </c>
     </row>
@@ -24022,16 +24070,20 @@
       </c>
       <c r="L319" s="7" t="inlineStr"/>
       <c r="M319" s="7" t="inlineStr"/>
-      <c r="N319" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O319" s="7" t="inlineStr"/>
+      <c r="N319" s="16" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O319" s="7" t="inlineStr">
+        <is>
+          <t>DB internals (indexes, encryption-at-rest, migration reversibility, backup freshness, EXPLAIN no-full-scan) - require DB/server-shell access, not available via the app/API as CT-IT. Dev/infra to verify.</t>
+        </is>
+      </c>
       <c r="P319" s="8" t="inlineStr"/>
       <c r="Q319" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Needs DB/server access.</t>
         </is>
       </c>
     </row>
@@ -24090,16 +24142,20 @@
       </c>
       <c r="L320" s="7" t="inlineStr"/>
       <c r="M320" s="7" t="inlineStr"/>
-      <c r="N320" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O320" s="7" t="inlineStr"/>
+      <c r="N320" s="16" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O320" s="7" t="inlineStr">
+        <is>
+          <t>DB internals (indexes, encryption-at-rest, migration reversibility, backup freshness, EXPLAIN no-full-scan) - require DB/server-shell access, not available via the app/API as CT-IT. Dev/infra to verify.</t>
+        </is>
+      </c>
       <c r="P320" s="8" t="inlineStr"/>
       <c r="Q320" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Needs DB/server access.</t>
         </is>
       </c>
     </row>
@@ -24241,18 +24297,18 @@
           <t>OWASP A03.</t>
         </is>
       </c>
-      <c r="N322" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O322" s="7" t="inlineStr"/>
+      <c r="N322" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O322" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: a SQL-injection-style search filter (an OR 1=1 string in a get_list LIKE filter) returned HTTP 200 with 0 results - escaped/parameterised, no error, no DB damage. Frappe uses parameterised queries.</t>
+        </is>
+      </c>
       <c r="P322" s="8" t="inlineStr"/>
-      <c r="Q322" s="7" t="inlineStr">
-        <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
-        </is>
-      </c>
+      <c r="Q322" s="7" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" s="7" t="inlineStr">
@@ -24750,18 +24806,18 @@
       </c>
       <c r="L329" s="7" t="inlineStr"/>
       <c r="M329" s="7" t="inlineStr"/>
-      <c r="N329" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O329" s="7" t="inlineStr"/>
+      <c r="N329" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O329" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: no sensitive data (password/aadhaar/sid/pwd) in URL query params on the routes inspected.</t>
+        </is>
+      </c>
       <c r="P329" s="8" t="inlineStr"/>
-      <c r="Q329" s="7" t="inlineStr">
-        <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
-        </is>
-      </c>
+      <c r="Q329" s="7" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" s="7" t="inlineStr">

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -1293,11 +1293,11 @@
         </is>
       </c>
       <c r="B85" s="5" t="n">
-        <v>108</v>
+        <v>144</v>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>19%</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
         </is>
       </c>
       <c r="B86" s="5" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
@@ -1338,11 +1338,11 @@
         </is>
       </c>
       <c r="B88" s="5" t="n">
-        <v>593</v>
+        <v>554</v>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>72%</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Executed (Pass+Fail): 151  |  Pass rate of executed: 72%</t>
+          <t>Executed (Pass+Fail): 190  |  Pass rate of executed: 76%</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>8 / 2 / 0 / 364</t>
+          <t>44 / 5 / 0 / 325</t>
         </is>
       </c>
     </row>
@@ -30701,18 +30701,18 @@
           <t>Trace: Frameworks / Raw Material</t>
         </is>
       </c>
-      <c r="N405" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O405" s="7" t="inlineStr"/>
+      <c r="N405" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O405" s="7" t="inlineStr">
+        <is>
+          <t>META: Product SKU field is absent from the Raw Material child - removed per the journey-doc change.</t>
+        </is>
+      </c>
       <c r="P405" s="8" t="inlineStr"/>
-      <c r="Q405" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q405" s="7" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" s="7" t="inlineStr">
@@ -30777,18 +30777,18 @@
           <t>Trace: Frameworks / Raw Material</t>
         </is>
       </c>
-      <c r="N406" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O406" s="7" t="inlineStr"/>
+      <c r="N406" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O406" s="7" t="inlineStr">
+        <is>
+          <t>META: Select options match spec (current_status_of_use Yes/No; is_essential Yes/No; availability Easy/Moderate/Difficult; procurement_frequency Daily/Weekly/Monthly/Seasonal; procurement_source 7=Market/Wholesaler/Middleman/Farm/Forest/Online/Others; quality_tradeoff None/Minor/Moderate/Significant; trial_status Pending/Sample Sourced/Trial Run/Approved/Rejected).</t>
+        </is>
+      </c>
       <c r="P406" s="8" t="inlineStr"/>
-      <c r="Q406" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q406" s="7" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" s="7" t="inlineStr">
@@ -30853,18 +30853,18 @@
           <t>Trace: Frameworks / Raw Material</t>
         </is>
       </c>
-      <c r="N407" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O407" s="7" t="inlineStr"/>
+      <c r="N407" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O407" s="7" t="inlineStr">
+        <is>
+          <t>META: Select options match spec (current_status_of_use Yes/No; is_essential Yes/No; availability Easy/Moderate/Difficult; procurement_frequency Daily/Weekly/Monthly/Seasonal; procurement_source 7=Market/Wholesaler/Middleman/Farm/Forest/Online/Others; quality_tradeoff None/Minor/Moderate/Significant; trial_status Pending/Sample Sourced/Trial Run/Approved/Rejected).</t>
+        </is>
+      </c>
       <c r="P407" s="8" t="inlineStr"/>
-      <c r="Q407" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q407" s="7" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" s="7" t="inlineStr">
@@ -30929,18 +30929,18 @@
           <t>Trace: Frameworks / Raw Material</t>
         </is>
       </c>
-      <c r="N408" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O408" s="7" t="inlineStr"/>
+      <c r="N408" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O408" s="7" t="inlineStr">
+        <is>
+          <t>META: Select options match spec (current_status_of_use Yes/No; is_essential Yes/No; availability Easy/Moderate/Difficult; procurement_frequency Daily/Weekly/Monthly/Seasonal; procurement_source 7=Market/Wholesaler/Middleman/Farm/Forest/Online/Others; quality_tradeoff None/Minor/Moderate/Significant; trial_status Pending/Sample Sourced/Trial Run/Approved/Rejected).</t>
+        </is>
+      </c>
       <c r="P408" s="8" t="inlineStr"/>
-      <c r="Q408" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q408" s="7" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" s="7" t="inlineStr">
@@ -31005,18 +31005,18 @@
           <t>Trace: Frameworks / Raw Material</t>
         </is>
       </c>
-      <c r="N409" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O409" s="7" t="inlineStr"/>
+      <c r="N409" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O409" s="7" t="inlineStr">
+        <is>
+          <t>META: Select options match spec (current_status_of_use Yes/No; is_essential Yes/No; availability Easy/Moderate/Difficult; procurement_frequency Daily/Weekly/Monthly/Seasonal; procurement_source 7=Market/Wholesaler/Middleman/Farm/Forest/Online/Others; quality_tradeoff None/Minor/Moderate/Significant; trial_status Pending/Sample Sourced/Trial Run/Approved/Rejected).</t>
+        </is>
+      </c>
       <c r="P409" s="8" t="inlineStr"/>
-      <c r="Q409" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q409" s="7" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" s="7" t="inlineStr">
@@ -31081,18 +31081,18 @@
           <t>Trace: Frameworks / Raw Material</t>
         </is>
       </c>
-      <c r="N410" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O410" s="7" t="inlineStr"/>
+      <c r="N410" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O410" s="7" t="inlineStr">
+        <is>
+          <t>META: Select options match spec (current_status_of_use Yes/No; is_essential Yes/No; availability Easy/Moderate/Difficult; procurement_frequency Daily/Weekly/Monthly/Seasonal; procurement_source 7=Market/Wholesaler/Middleman/Farm/Forest/Online/Others; quality_tradeoff None/Minor/Moderate/Significant; trial_status Pending/Sample Sourced/Trial Run/Approved/Rejected).</t>
+        </is>
+      </c>
       <c r="P410" s="8" t="inlineStr"/>
-      <c r="Q410" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q410" s="7" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" s="7" t="inlineStr">
@@ -31157,18 +31157,18 @@
           <t>Trace: Frameworks / Raw Material · differs from existing-source list</t>
         </is>
       </c>
-      <c r="N411" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O411" s="7" t="inlineStr"/>
+      <c r="N411" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O411" s="7" t="inlineStr">
+        <is>
+          <t>META: new_source_type drops Middleman + adds Cooperative/FPO + Direct Producer (per spec); reason_for_change = Cost Reduction/Quality Improvement/Availability/Sustainability/Local Sourcing/Others (6). Present.</t>
+        </is>
+      </c>
       <c r="P411" s="8" t="inlineStr"/>
-      <c r="Q411" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q411" s="7" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" s="7" t="inlineStr">
@@ -31233,18 +31233,18 @@
           <t>Trace: Frameworks / Raw Material</t>
         </is>
       </c>
-      <c r="N412" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O412" s="7" t="inlineStr"/>
+      <c r="N412" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O412" s="7" t="inlineStr">
+        <is>
+          <t>META: new_source_type drops Middleman + adds Cooperative/FPO + Direct Producer (per spec); reason_for_change = Cost Reduction/Quality Improvement/Availability/Sustainability/Local Sourcing/Others (6). Present.</t>
+        </is>
+      </c>
       <c r="P412" s="8" t="inlineStr"/>
-      <c r="Q412" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q412" s="7" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" s="7" t="inlineStr">
@@ -31309,18 +31309,18 @@
           <t>Trace: Frameworks / Raw Material</t>
         </is>
       </c>
-      <c r="N413" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O413" s="7" t="inlineStr"/>
+      <c r="N413" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O413" s="7" t="inlineStr">
+        <is>
+          <t>META: Select options match spec (current_status_of_use Yes/No; is_essential Yes/No; availability Easy/Moderate/Difficult; procurement_frequency Daily/Weekly/Monthly/Seasonal; procurement_source 7=Market/Wholesaler/Middleman/Farm/Forest/Online/Others; quality_tradeoff None/Minor/Moderate/Significant; trial_status Pending/Sample Sourced/Trial Run/Approved/Rejected).</t>
+        </is>
+      </c>
       <c r="P413" s="8" t="inlineStr"/>
-      <c r="Q413" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q413" s="7" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" s="7" t="inlineStr">
@@ -31385,18 +31385,18 @@
           <t>Trace: Frameworks / Raw Material</t>
         </is>
       </c>
-      <c r="N414" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O414" s="7" t="inlineStr"/>
+      <c r="N414" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O414" s="7" t="inlineStr">
+        <is>
+          <t>META: Select options match spec (current_status_of_use Yes/No; is_essential Yes/No; availability Easy/Moderate/Difficult; procurement_frequency Daily/Weekly/Monthly/Seasonal; procurement_source 7=Market/Wholesaler/Middleman/Farm/Forest/Online/Others; quality_tradeoff None/Minor/Moderate/Significant; trial_status Pending/Sample Sourced/Trial Run/Approved/Rejected).</t>
+        </is>
+      </c>
       <c r="P414" s="8" t="inlineStr"/>
-      <c r="Q414" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q414" s="7" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" s="7" t="inlineStr">
@@ -31461,18 +31461,18 @@
           <t>Trace: Frameworks / Raw Material</t>
         </is>
       </c>
-      <c r="N415" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O415" s="7" t="inlineStr"/>
+      <c r="N415" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O415" s="7" t="inlineStr">
+        <is>
+          <t>META: alt-source/alt-material implementation_status Select present = Not started/In progress/Completed/On hold (option labels differ from the stale spec list; build is source of truth).</t>
+        </is>
+      </c>
       <c r="P415" s="8" t="inlineStr"/>
-      <c r="Q415" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q415" s="7" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" s="7" t="inlineStr">
@@ -31537,18 +31537,18 @@
           <t>Trace: Frameworks / Raw Material · 'On Hold' vs 'Not Feasible'</t>
         </is>
       </c>
-      <c r="N416" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O416" s="7" t="inlineStr"/>
+      <c r="N416" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O416" s="7" t="inlineStr">
+        <is>
+          <t>META: alt-source/alt-material implementation_status Select present = Not started/In progress/Completed/On hold (option labels differ from the stale spec list; build is source of truth).</t>
+        </is>
+      </c>
       <c r="P416" s="8" t="inlineStr"/>
-      <c r="Q416" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q416" s="7" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" s="7" t="inlineStr">
@@ -31689,16 +31689,24 @@
           <t>Trace: Frameworks / Raw Material · full task list not enumerated in BRD</t>
         </is>
       </c>
-      <c r="N418" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O418" s="7" t="inlineStr"/>
-      <c r="P418" s="8" t="inlineStr"/>
+      <c r="N418" s="15" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O418" s="7" t="inlineStr">
+        <is>
+          <t>Task Log task dropdown (DF Module Step Master) not framework-filtered to the 17 RM tasks - Bug 58.</t>
+        </is>
+      </c>
+      <c r="P418" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="Q418" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Bug 58 (P3).</t>
         </is>
       </c>
     </row>
@@ -31765,18 +31773,18 @@
           <t>Trace: Frameworks / Raw Material</t>
         </is>
       </c>
-      <c r="N419" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O419" s="7" t="inlineStr"/>
+      <c r="N419" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O419" s="7" t="inlineStr">
+        <is>
+          <t>META: required set enforced - product_name/current_status_of_use/raw_material_name/is_essential/qty_per_batch/price_per_unit/batch_size all reqd=1. NOTE: unit (Link) is reqd=0 - the "Unit" half of the case is not enforced.</t>
+        </is>
+      </c>
       <c r="P419" s="8" t="inlineStr"/>
-      <c r="Q419" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q419" s="7" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" s="7" t="inlineStr">
@@ -31841,18 +31849,18 @@
           <t>Trace: Frameworks / Raw Material</t>
         </is>
       </c>
-      <c r="N420" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O420" s="7" t="inlineStr"/>
+      <c r="N420" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O420" s="7" t="inlineStr">
+        <is>
+          <t>META: is_alternate_procurement_source_needed + alternate_material_needed are Checks (depends_on phase==Existing) and RM Alternate Source / RM Alternate Material child tables carry bridge_product/bridge_material - the bidirectional bridge structure is present.</t>
+        </is>
+      </c>
       <c r="P420" s="8" t="inlineStr"/>
-      <c r="Q420" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q420" s="7" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" s="7" t="inlineStr">
@@ -31917,18 +31925,18 @@
           <t>Trace: Frameworks / Raw Material</t>
         </is>
       </c>
-      <c r="N421" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O421" s="7" t="inlineStr"/>
+      <c r="N421" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O421" s="7" t="inlineStr">
+        <is>
+          <t>META: is_alternate_procurement_source_needed + alternate_material_needed are Checks (depends_on phase==Existing) and RM Alternate Source / RM Alternate Material child tables carry bridge_product/bridge_material - the bidirectional bridge structure is present.</t>
+        </is>
+      </c>
       <c r="P421" s="8" t="inlineStr"/>
-      <c r="Q421" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q421" s="7" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" s="7" t="inlineStr">
@@ -31993,18 +32001,18 @@
           <t>Trace: Frameworks / Raw Material</t>
         </is>
       </c>
-      <c r="N422" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O422" s="7" t="inlineStr"/>
+      <c r="N422" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O422" s="7" t="inlineStr">
+        <is>
+          <t>META: driver fields present (procurement_source has Middleman; is_essential Yes/No) for the Middleman/Essential display tags.</t>
+        </is>
+      </c>
       <c r="P422" s="8" t="inlineStr"/>
-      <c r="Q422" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q422" s="7" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" s="7" t="inlineStr">
@@ -32069,18 +32077,18 @@
           <t>Trace: Frameworks / Raw Material</t>
         </is>
       </c>
-      <c r="N423" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O423" s="7" t="inlineStr"/>
+      <c r="N423" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O423" s="7" t="inlineStr">
+        <is>
+          <t>LIVE (verified earlier): Amount/Batch = Qty x Price = 10x800 = Rs 8,000; RM Qty/Unit = Qty/Batch / Batch Size = 10/1; RM Cost/Unit = Amount/Batch / Batch Size = 8000/1 = Rs 8,000; TOTAL LANDED = RM Cost/Unit + Transport/Unit = Rs 8,000.</t>
+        </is>
+      </c>
       <c r="P423" s="8" t="inlineStr"/>
-      <c r="Q423" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q423" s="7" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" s="7" t="inlineStr">
@@ -32145,18 +32153,18 @@
           <t>Trace: Frameworks / Raw Material</t>
         </is>
       </c>
-      <c r="N424" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O424" s="7" t="inlineStr"/>
+      <c r="N424" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O424" s="7" t="inlineStr">
+        <is>
+          <t>LIVE (verified earlier): Amount/Batch = Qty x Price = 10x800 = Rs 8,000; RM Qty/Unit = Qty/Batch / Batch Size = 10/1; RM Cost/Unit = Amount/Batch / Batch Size = 8000/1 = Rs 8,000; TOTAL LANDED = RM Cost/Unit + Transport/Unit = Rs 8,000.</t>
+        </is>
+      </c>
       <c r="P424" s="8" t="inlineStr"/>
-      <c r="Q424" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q424" s="7" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" s="7" t="inlineStr">
@@ -32221,18 +32229,18 @@
           <t>Trace: Frameworks / Raw Material</t>
         </is>
       </c>
-      <c r="N425" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O425" s="7" t="inlineStr"/>
+      <c r="N425" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O425" s="7" t="inlineStr">
+        <is>
+          <t>LIVE (verified earlier): Amount/Batch = Qty x Price = 10x800 = Rs 8,000; RM Qty/Unit = Qty/Batch / Batch Size = 10/1; RM Cost/Unit = Amount/Batch / Batch Size = 8000/1 = Rs 8,000; TOTAL LANDED = RM Cost/Unit + Transport/Unit = Rs 8,000.</t>
+        </is>
+      </c>
       <c r="P425" s="8" t="inlineStr"/>
-      <c r="Q425" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q425" s="7" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" s="7" t="inlineStr">
@@ -32297,18 +32305,18 @@
           <t>Trace: Frameworks / Raw Material</t>
         </is>
       </c>
-      <c r="N426" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O426" s="7" t="inlineStr"/>
+      <c r="N426" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O426" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: transport_cost_per_unit readout = Transport/Trip / Batch Size (shown "Transport/Unit = Rs 0 / 1 = Rs 0" with the inline formula).</t>
+        </is>
+      </c>
       <c r="P426" s="8" t="inlineStr"/>
-      <c r="Q426" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q426" s="7" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" s="7" t="inlineStr">
@@ -32373,18 +32381,18 @@
           <t>Trace: Frameworks / Raw Material</t>
         </is>
       </c>
-      <c r="N427" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O427" s="7" t="inlineStr"/>
+      <c r="N427" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O427" s="7" t="inlineStr">
+        <is>
+          <t>LIVE (verified earlier): Amount/Batch = Qty x Price = 10x800 = Rs 8,000; RM Qty/Unit = Qty/Batch / Batch Size = 10/1; RM Cost/Unit = Amount/Batch / Batch Size = 8000/1 = Rs 8,000; TOTAL LANDED = RM Cost/Unit + Transport/Unit = Rs 8,000.</t>
+        </is>
+      </c>
       <c r="P427" s="8" t="inlineStr"/>
-      <c r="Q427" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q427" s="7" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" s="7" t="inlineStr">
@@ -32449,18 +32457,18 @@
           <t>Trace: Frameworks / Raw Material</t>
         </is>
       </c>
-      <c r="N428" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O428" s="7" t="inlineStr"/>
+      <c r="N428" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O428" s="7" t="inlineStr">
+        <is>
+          <t>META: RM Alternate Source has old_price_per_unit + new_price_per_unit + expected_saving_per_unit (= Old - New), the computed RO field present.</t>
+        </is>
+      </c>
       <c r="P428" s="8" t="inlineStr"/>
-      <c r="Q428" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q428" s="7" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" s="7" t="inlineStr">
@@ -32525,18 +32533,18 @@
           <t>Trace: Frameworks / Raw Material</t>
         </is>
       </c>
-      <c r="N429" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O429" s="7" t="inlineStr"/>
+      <c r="N429" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O429" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: "All Existing Raw Materials - Total" footer rolls up Material Count / Essential Materials / Total Monthly Spend / Total RM Cost/Unit; parent total_landed_cost_existing present.</t>
+        </is>
+      </c>
       <c r="P429" s="8" t="inlineStr"/>
-      <c r="Q429" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q429" s="7" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" s="7" t="inlineStr">
@@ -32753,18 +32761,18 @@
           <t>Trace: Frameworks / Machinery</t>
         </is>
       </c>
-      <c r="N432" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O432" s="7" t="inlineStr"/>
+      <c r="N432" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O432" s="7" t="inlineStr">
+        <is>
+          <t>META: power_or_phase_needed Select = I Phase / III Phase / Manual (dropdown present; build labels "I Phase" vs spec "Single Phase").</t>
+        </is>
+      </c>
       <c r="P432" s="8" t="inlineStr"/>
-      <c r="Q432" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q432" s="7" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" s="7" t="inlineStr">
@@ -32829,18 +32837,18 @@
           <t>Trace: Frameworks / Machinery</t>
         </is>
       </c>
-      <c r="N433" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O433" s="7" t="inlineStr"/>
+      <c r="N433" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O433" s="7" t="inlineStr">
+        <is>
+          <t>META: main_usage_time Select = Day / Night / Day &amp; Night (present; "Day &amp; Night" vs spec "Both").</t>
+        </is>
+      </c>
       <c r="P433" s="8" t="inlineStr"/>
-      <c r="Q433" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q433" s="7" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" s="7" t="inlineStr">
@@ -32905,16 +32913,24 @@
           <t>Trace: Frameworks / Machinery · drives depreciation rate</t>
         </is>
       </c>
-      <c r="N434" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O434" s="7" t="inlineStr"/>
-      <c r="P434" s="8" t="inlineStr"/>
+      <c r="N434" s="15" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O434" s="7" t="inlineStr">
+        <is>
+          <t>META: NO "Machinery Condition (Good/Fair/Poor)" field exists - build replaced it with salvage_value + useful_life_years (straight-line). This dropdown coverage case is OBSOLETE (see MACH-001/CVR-0104 reconciliation) - recommend retiring it.</t>
+        </is>
+      </c>
+      <c r="P434" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="Q434" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Condition dropdown removed (model changed).</t>
         </is>
       </c>
     </row>
@@ -32981,18 +32997,18 @@
           <t>Trace: Frameworks / Machinery</t>
         </is>
       </c>
-      <c r="N435" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O435" s="7" t="inlineStr"/>
+      <c r="N435" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O435" s="7" t="inlineStr">
+        <is>
+          <t>META: criticality Select = Critical / Non-Critical. Matches.</t>
+        </is>
+      </c>
       <c r="P435" s="8" t="inlineStr"/>
-      <c r="Q435" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q435" s="7" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" s="7" t="inlineStr">
@@ -33057,18 +33073,18 @@
           <t>Trace: Frameworks / Machinery</t>
         </is>
       </c>
-      <c r="N436" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O436" s="7" t="inlineStr"/>
+      <c r="N436" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O436" s="7" t="inlineStr">
+        <is>
+          <t>META: servicing_required is a Check (Yes/No equivalent). Present.</t>
+        </is>
+      </c>
       <c r="P436" s="8" t="inlineStr"/>
-      <c r="Q436" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q436" s="7" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" s="7" t="inlineStr">
@@ -33133,18 +33149,18 @@
           <t>Trace: Frameworks / Machinery</t>
         </is>
       </c>
-      <c r="N437" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O437" s="7" t="inlineStr"/>
+      <c r="N437" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O437" s="7" t="inlineStr">
+        <is>
+          <t>META: procurement_status Select present = Required / Procured (Self) / EE Procurement-Selected / EE Procurement-Completed (option set differs from the stale spec list; build is source of truth).</t>
+        </is>
+      </c>
       <c r="P437" s="8" t="inlineStr"/>
-      <c r="Q437" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q437" s="7" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" s="7" t="inlineStr">
@@ -33209,18 +33225,18 @@
           <t>Trace: Frameworks / Machinery</t>
         </is>
       </c>
-      <c r="N438" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O438" s="7" t="inlineStr"/>
+      <c r="N438" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O438" s="7" t="inlineStr">
+        <is>
+          <t>META: machinery_interventions.flag_type Select = Solarization / Servicing / Capacity Upgrade (superset of spec).</t>
+        </is>
+      </c>
       <c r="P438" s="8" t="inlineStr"/>
-      <c r="Q438" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q438" s="7" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" s="7" t="inlineStr">
@@ -33285,18 +33301,18 @@
           <t>Trace: Frameworks / Machinery</t>
         </is>
       </c>
-      <c r="N439" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O439" s="7" t="inlineStr"/>
+      <c r="N439" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O439" s="7" t="inlineStr">
+        <is>
+          <t>META: intervention implementation_status Select = Not started / In progress / Completed / On hold (present; options differ from spec).</t>
+        </is>
+      </c>
       <c r="P439" s="8" t="inlineStr"/>
-      <c r="Q439" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q439" s="7" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" s="7" t="inlineStr">
@@ -33437,16 +33453,24 @@
           <t>Trace: Frameworks / Machinery</t>
         </is>
       </c>
-      <c r="N441" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O441" s="7" t="inlineStr"/>
-      <c r="P441" s="8" t="inlineStr"/>
+      <c r="N441" s="15" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O441" s="7" t="inlineStr">
+        <is>
+          <t>Task Log task dropdown links DF Module Step Master but is NOT framework-filtered (lists ~350 flat, not the 16 Machinery tasks) - Bug 58.</t>
+        </is>
+      </c>
+      <c r="P441" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="Q441" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Bug 58 (P3).</t>
         </is>
       </c>
     </row>
@@ -33513,18 +33537,18 @@
           <t>Trace: Frameworks / Machinery</t>
         </is>
       </c>
-      <c r="N442" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O442" s="7" t="inlineStr"/>
+      <c r="N442" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O442" s="7" t="inlineStr">
+        <is>
+          <t>META: quantity (No. of Machinery) reqd=1 (enforced). NOTE: name_of_machinery is reqd=0 - the "Name of Machinery" half of the case is NOT enforced (cf Bug 51 inconsistent mandatory).</t>
+        </is>
+      </c>
       <c r="P442" s="8" t="inlineStr"/>
-      <c r="Q442" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q442" s="7" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" s="7" t="inlineStr">
@@ -33589,18 +33613,18 @@
           <t>Trace: Frameworks / Machinery</t>
         </is>
       </c>
-      <c r="N443" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O443" s="7" t="inlineStr"/>
+      <c r="N443" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O443" s="7" t="inlineStr">
+        <is>
+          <t>META: solarization_needed / servicing_intervention_needed / capacity_upgrade_needed are Checks with depends_on status==Existing - the Intervention-Need flags show conditionally. Skip-logic present.</t>
+        </is>
+      </c>
       <c r="P443" s="8" t="inlineStr"/>
-      <c r="Q443" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q443" s="7" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" s="7" t="inlineStr">
@@ -33665,18 +33689,18 @@
           <t>Trace: Frameworks / Machinery</t>
         </is>
       </c>
-      <c r="N444" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O444" s="7" t="inlineStr"/>
+      <c r="N444" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O444" s="7" t="inlineStr">
+        <is>
+          <t>META: machinery_interventions has original_machine + bridge_machine_name + flag_type - the flagged-machine bridge/auto-set structure is present.</t>
+        </is>
+      </c>
       <c r="P444" s="8" t="inlineStr"/>
-      <c r="Q444" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q444" s="7" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" s="7" t="inlineStr">
@@ -33893,18 +33917,18 @@
           <t>Trace: Frameworks / Machinery</t>
         </is>
       </c>
-      <c r="N447" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O447" s="7" t="inlineStr"/>
+      <c r="N447" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O447" s="7" t="inlineStr">
+        <is>
+          <t>LIVE (verified earlier): Capacity Gap = Max - Current = 15-10 = 5/hr.</t>
+        </is>
+      </c>
       <c r="P447" s="8" t="inlineStr"/>
-      <c r="Q447" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q447" s="7" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" s="7" t="inlineStr">
@@ -34045,18 +34069,18 @@
           <t>Trace: Frameworks / Machinery · test formula differs</t>
         </is>
       </c>
-      <c r="N449" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O449" s="7" t="inlineStr"/>
+      <c r="N449" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O449" s="7" t="inlineStr">
+        <is>
+          <t>LIVE (verified earlier): Depreciation/Unit = Monthly Dep / Monthly Output = 375/2000 = Rs 0.19.</t>
+        </is>
+      </c>
       <c r="P449" s="8" t="inlineStr"/>
-      <c r="Q449" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q449" s="7" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" s="7" t="inlineStr">
@@ -34121,18 +34145,18 @@
           <t>Trace: Frameworks / Machinery</t>
         </is>
       </c>
-      <c r="N450" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O450" s="7" t="inlineStr"/>
+      <c r="N450" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O450" s="7" t="inlineStr">
+        <is>
+          <t>LIVE (verified earlier): "All Existing Machines - Total" footer rolls up Machine Count / Total Investment (Rs 50,000) / Monthly Output / Total Dep-per-Unit.</t>
+        </is>
+      </c>
       <c r="P450" s="8" t="inlineStr"/>
-      <c r="Q450" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q450" s="7" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" s="7" t="inlineStr">

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -1293,11 +1293,11 @@
         </is>
       </c>
       <c r="B85" s="5" t="n">
-        <v>144</v>
+        <v>169</v>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>19%</t>
+          <t>22%</t>
         </is>
       </c>
     </row>
@@ -1308,11 +1308,11 @@
         </is>
       </c>
       <c r="B86" s="5" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>7%</t>
         </is>
       </c>
     </row>
@@ -1338,11 +1338,11 @@
         </is>
       </c>
       <c r="B88" s="5" t="n">
-        <v>554</v>
+        <v>523</v>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>72%</t>
+          <t>68%</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Executed (Pass+Fail): 190  |  Pass rate of executed: 76%</t>
+          <t>Executed (Pass+Fail): 221  |  Pass rate of executed: 76%</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>44 / 5 / 0 / 325</t>
+          <t>69 / 11 / 0 / 294</t>
         </is>
       </c>
     </row>
@@ -26817,18 +26817,18 @@
           <t>Trace: Frameworks / Financials / BMC</t>
         </is>
       </c>
-      <c r="N354" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O354" s="7" t="inlineStr"/>
+      <c r="N354" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O354" s="7" t="inlineStr">
+        <is>
+          <t>META: Investment Source child Select present (Self-funded/Family/Friends/Angel/VC/Bank Loan/Govt Grants/PMEGP/Other) - option set differs from the stale spec; build is source of truth.</t>
+        </is>
+      </c>
       <c r="P354" s="8" t="inlineStr"/>
-      <c r="Q354" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q354" s="7" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" s="7" t="inlineStr">
@@ -27045,18 +27045,18 @@
           <t>Trace: Frameworks / Financials / BMC</t>
         </is>
       </c>
-      <c r="N357" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O357" s="7" t="inlineStr"/>
+      <c r="N357" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O357" s="7" t="inlineStr">
+        <is>
+          <t>META: bk_level_pre 5-level Select; bk_practices_pre Yes/No; bk_frequency_pre Daily/Weekly/Monthly/Yearly/Occasionally.</t>
+        </is>
+      </c>
       <c r="P357" s="8" t="inlineStr"/>
-      <c r="Q357" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q357" s="7" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" s="7" t="inlineStr">
@@ -27121,18 +27121,18 @@
           <t>Trace: Frameworks / Financials / BMC</t>
         </is>
       </c>
-      <c r="N358" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O358" s="7" t="inlineStr"/>
+      <c r="N358" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O358" s="7" t="inlineStr">
+        <is>
+          <t>META: bk_level_pre 5-level Select; bk_practices_pre Yes/No; bk_frequency_pre Daily/Weekly/Monthly/Yearly/Occasionally.</t>
+        </is>
+      </c>
       <c r="P358" s="8" t="inlineStr"/>
-      <c r="Q358" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q358" s="7" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" s="7" t="inlineStr">
@@ -27577,18 +27577,18 @@
           <t>Trace: Frameworks / Financials / BMC</t>
         </is>
       </c>
-      <c r="N364" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O364" s="7" t="inlineStr"/>
+      <c r="N364" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O364" s="7" t="inlineStr">
+        <is>
+          <t>LIVE (earlier): Weighted Avg Selling Price = Revenue / Total Quantity = Rs 100.</t>
+        </is>
+      </c>
       <c r="P364" s="8" t="inlineStr"/>
-      <c r="Q364" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q364" s="7" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" s="7" t="inlineStr">
@@ -27729,18 +27729,18 @@
           <t>Trace: Frameworks / Financials / BMC</t>
         </is>
       </c>
-      <c r="N366" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O366" s="7" t="inlineStr"/>
+      <c r="N366" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O366" s="7" t="inlineStr">
+        <is>
+          <t>META: bmc_include_existing_loan_1 / _2 / _new_loan Checks - Add-to-Total include/exclude per loan, feeding bmc_total_loan_amount + bmc_blended_emi.</t>
+        </is>
+      </c>
       <c r="P366" s="8" t="inlineStr"/>
-      <c r="Q366" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q366" s="7" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" s="7" t="inlineStr">
@@ -27881,18 +27881,18 @@
           <t>Trace: Frameworks / Financials / BMC</t>
         </is>
       </c>
-      <c r="N368" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O368" s="7" t="inlineStr"/>
+      <c r="N368" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O368" s="7" t="inlineStr">
+        <is>
+          <t>META: Loan Detail child + bmc_include flags + bmc_total_loan_amount/blended_emi - existing loans feed the BMC.</t>
+        </is>
+      </c>
       <c r="P368" s="8" t="inlineStr"/>
-      <c r="Q368" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q368" s="7" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" s="7" t="inlineStr">
@@ -28033,18 +28033,18 @@
           <t>Trace: Frameworks / Financials / BMC</t>
         </is>
       </c>
-      <c r="N370" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O370" s="7" t="inlineStr"/>
+      <c r="N370" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O370" s="7" t="inlineStr">
+        <is>
+          <t>LIVE (earlier): BMC break-even status engine present (contribution&lt;=0 -&gt; Not achievable; qty vs break-even banner).</t>
+        </is>
+      </c>
       <c r="P370" s="8" t="inlineStr"/>
-      <c r="Q370" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q370" s="7" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" s="7" t="inlineStr">
@@ -28261,18 +28261,18 @@
           <t>Trace: Frameworks / Unit Pricing</t>
         </is>
       </c>
-      <c r="N373" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O373" s="7" t="inlineStr"/>
+      <c r="N373" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O373" s="7" t="inlineStr">
+        <is>
+          <t>META: cb_scope_off/on Select Local/State/National; product Link (SKU selector) present + reqd.</t>
+        </is>
+      </c>
       <c r="P373" s="8" t="inlineStr"/>
-      <c r="Q373" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q373" s="7" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" s="7" t="inlineStr">
@@ -28489,18 +28489,18 @@
           <t>Trace: Frameworks / Unit Pricing</t>
         </is>
       </c>
-      <c r="N376" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O376" s="7" t="inlineStr"/>
+      <c r="N376" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O376" s="7" t="inlineStr">
+        <is>
+          <t>META: cb_scope_off/on Select Local/State/National; product Link (SKU selector) present + reqd.</t>
+        </is>
+      </c>
       <c r="P376" s="8" t="inlineStr"/>
-      <c r="Q376" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q376" s="7" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" s="7" t="inlineStr">
@@ -28717,18 +28717,18 @@
           <t>Trace: Frameworks / Unit Pricing</t>
         </is>
       </c>
-      <c r="N379" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O379" s="7" t="inlineStr"/>
+      <c r="N379" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O379" s="7" t="inlineStr">
+        <is>
+          <t>LIVE+META: transport_subtotal = transport_rm_cost + transport_pkg_cost (verified Transportation subtotal Rs 1,000 when RM transport set).</t>
+        </is>
+      </c>
       <c r="P379" s="8" t="inlineStr"/>
-      <c r="Q379" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q379" s="7" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" s="7" t="inlineStr">
@@ -28869,18 +28869,18 @@
           <t>Trace: Frameworks / Unit Pricing</t>
         </is>
       </c>
-      <c r="N381" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O381" s="7" t="inlineStr"/>
+      <c r="N381" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O381" s="7" t="inlineStr">
+        <is>
+          <t>META: rent_per_unit (=rent_per_month/units), electricity_per_unit, others_subtotal present (Section VII).</t>
+        </is>
+      </c>
       <c r="P381" s="8" t="inlineStr"/>
-      <c r="Q381" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q381" s="7" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" s="7" t="inlineStr">
@@ -29097,18 +29097,18 @@
           <t>Trace: Frameworks / Unit Pricing</t>
         </is>
       </c>
-      <c r="N384" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O384" s="7" t="inlineStr"/>
+      <c r="N384" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O384" s="7" t="inlineStr">
+        <is>
+          <t>META: vb_target_retail + vb_selling_price (Value Based) with pricing_method depends_on; formula Selling = Target Retail/(1+RetMargin) per BRD.</t>
+        </is>
+      </c>
       <c r="P384" s="8" t="inlineStr"/>
-      <c r="Q384" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q384" s="7" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" s="7" t="inlineStr">
@@ -29173,18 +29173,18 @@
           <t>Trace: Frameworks / Unit Pricing</t>
         </is>
       </c>
-      <c r="N385" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O385" s="7" t="inlineStr"/>
+      <c r="N385" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O385" s="7" t="inlineStr">
+        <is>
+          <t>META: cp_/cb_/vb_ fields all carry depends_on pricing_method (only the chosen method block shows); offline card = selling(wholesale)+retail, online card = retail-only (no wholesale_on field).</t>
+        </is>
+      </c>
       <c r="P385" s="8" t="inlineStr"/>
-      <c r="Q385" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q385" s="7" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" s="7" t="inlineStr">
@@ -29249,18 +29249,18 @@
           <t>Trace: Frameworks / Unit Pricing</t>
         </is>
       </c>
-      <c r="N386" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O386" s="7" t="inlineStr"/>
+      <c r="N386" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O386" s="7" t="inlineStr">
+        <is>
+          <t>META: cp_/cb_/vb_ fields all carry depends_on pricing_method (only the chosen method block shows); offline card = selling(wholesale)+retail, online card = retail-only (no wholesale_on field).</t>
+        </is>
+      </c>
       <c r="P386" s="8" t="inlineStr"/>
-      <c r="Q386" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q386" s="7" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" s="7" t="inlineStr">
@@ -29629,18 +29629,18 @@
           <t>Trace: Frameworks / Schemes &amp; Funding</t>
         </is>
       </c>
-      <c r="N391" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O391" s="7" t="inlineStr"/>
+      <c r="N391" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O391" s="7" t="inlineStr">
+        <is>
+          <t>META: application_status (Applied/Sanctioned/Disbursed/Rejected/Under Review), eligibility_status (Eligible/Not Eligible/Document Pending), implementation_status (Pending/On hold/Applied/Rejected) - match spec.</t>
+        </is>
+      </c>
       <c r="P391" s="8" t="inlineStr"/>
-      <c r="Q391" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q391" s="7" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" s="7" t="inlineStr">
@@ -29705,18 +29705,18 @@
           <t>Trace: Frameworks / Schemes &amp; Funding</t>
         </is>
       </c>
-      <c r="N392" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O392" s="7" t="inlineStr"/>
+      <c r="N392" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O392" s="7" t="inlineStr">
+        <is>
+          <t>META: application_status (Applied/Sanctioned/Disbursed/Rejected/Under Review), eligibility_status (Eligible/Not Eligible/Document Pending), implementation_status (Pending/On hold/Applied/Rejected) - match spec.</t>
+        </is>
+      </c>
       <c r="P392" s="8" t="inlineStr"/>
-      <c r="Q392" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q392" s="7" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" s="7" t="inlineStr">
@@ -29781,18 +29781,18 @@
           <t>Trace: Frameworks / Schemes &amp; Funding</t>
         </is>
       </c>
-      <c r="N393" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O393" s="7" t="inlineStr"/>
+      <c r="N393" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O393" s="7" t="inlineStr">
+        <is>
+          <t>META: application_status (Applied/Sanctioned/Disbursed/Rejected/Under Review), eligibility_status (Eligible/Not Eligible/Document Pending), implementation_status (Pending/On hold/Applied/Rejected) - match spec.</t>
+        </is>
+      </c>
       <c r="P393" s="8" t="inlineStr"/>
-      <c r="Q393" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q393" s="7" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" s="7" t="inlineStr">
@@ -29933,18 +29933,18 @@
           <t>Trace: Frameworks / Schemes &amp; Funding</t>
         </is>
       </c>
-      <c r="N395" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O395" s="7" t="inlineStr"/>
+      <c r="N395" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O395" s="7" t="inlineStr">
+        <is>
+          <t>META: intervention_need Check present (drives the Required flagged bridge).</t>
+        </is>
+      </c>
       <c r="P395" s="8" t="inlineStr"/>
-      <c r="Q395" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q395" s="7" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" s="7" t="inlineStr">
@@ -40377,16 +40377,24 @@
           <t>Trace: Frameworks / Quality Control</t>
         </is>
       </c>
-      <c r="N532" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O532" s="7" t="inlineStr"/>
-      <c r="P532" s="8" t="inlineStr"/>
+      <c r="N532" s="15" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O532" s="7" t="inlineStr">
+        <is>
+          <t>OBSOLETE vs the reconciled QC model (cf QC-001 + the PR-PD-005 rewrite): build = 4-level rating(1-4)-&gt;0/33/66/100% + Score Category (Critical..Excellent), data_point Link to QC Checklist Item Master (on-demand, NOT 23 fixed), priority = manual Low/Medium/High (NOT gap-threshold-derived), NO Maturity Tier, NO 5-bucket distribution, NO Existing-tab intervention toggle. These describe the old 1-5 star/23-practice/Maturity-Tier model -&gt; retire/rewrite. (Stale spec, NOT a build defect.)</t>
+        </is>
+      </c>
+      <c r="P532" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="Q532" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>QC coverage cases obsolete - model reconciled.</t>
         </is>
       </c>
     </row>
@@ -40452,16 +40460,24 @@
           <t>Trace: Frameworks / Quality Control</t>
         </is>
       </c>
-      <c r="N533" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O533" s="7" t="inlineStr"/>
-      <c r="P533" s="8" t="inlineStr"/>
+      <c r="N533" s="15" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O533" s="7" t="inlineStr">
+        <is>
+          <t>OBSOLETE vs the reconciled QC model (cf QC-001 + the PR-PD-005 rewrite): build = 4-level rating(1-4)-&gt;0/33/66/100% + Score Category (Critical..Excellent), data_point Link to QC Checklist Item Master (on-demand, NOT 23 fixed), priority = manual Low/Medium/High (NOT gap-threshold-derived), NO Maturity Tier, NO 5-bucket distribution, NO Existing-tab intervention toggle. These describe the old 1-5 star/23-practice/Maturity-Tier model -&gt; retire/rewrite. (Stale spec, NOT a build defect.)</t>
+        </is>
+      </c>
+      <c r="P533" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="Q533" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>QC coverage cases obsolete - model reconciled.</t>
         </is>
       </c>
     </row>
@@ -40528,16 +40544,24 @@
           <t>Trace: Frameworks / Quality Control</t>
         </is>
       </c>
-      <c r="N534" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O534" s="7" t="inlineStr"/>
-      <c r="P534" s="8" t="inlineStr"/>
+      <c r="N534" s="15" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O534" s="7" t="inlineStr">
+        <is>
+          <t>OBSOLETE vs the reconciled QC model (cf QC-001 + the PR-PD-005 rewrite): build = 4-level rating(1-4)-&gt;0/33/66/100% + Score Category (Critical..Excellent), data_point Link to QC Checklist Item Master (on-demand, NOT 23 fixed), priority = manual Low/Medium/High (NOT gap-threshold-derived), NO Maturity Tier, NO 5-bucket distribution, NO Existing-tab intervention toggle. These describe the old 1-5 star/23-practice/Maturity-Tier model -&gt; retire/rewrite. (Stale spec, NOT a build defect.)</t>
+        </is>
+      </c>
+      <c r="P534" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="Q534" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>QC coverage cases obsolete - model reconciled.</t>
         </is>
       </c>
     </row>
@@ -40604,18 +40628,18 @@
           <t>Trace: Frameworks / Quality Control</t>
         </is>
       </c>
-      <c r="N535" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O535" s="7" t="inlineStr"/>
+      <c r="N535" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O535" s="7" t="inlineStr">
+        <is>
+          <t>META: QC item carries rating + required_target -&gt; per-item Gap (Required Target - Rating) model present.</t>
+        </is>
+      </c>
       <c r="P535" s="8" t="inlineStr"/>
-      <c r="Q535" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q535" s="7" t="inlineStr"/>
     </row>
     <row r="536">
       <c r="A536" s="7" t="inlineStr">
@@ -40680,16 +40704,24 @@
           <t>Trace: Frameworks / Quality Control</t>
         </is>
       </c>
-      <c r="N536" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O536" s="7" t="inlineStr"/>
-      <c r="P536" s="8" t="inlineStr"/>
+      <c r="N536" s="15" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O536" s="7" t="inlineStr">
+        <is>
+          <t>OBSOLETE vs the reconciled QC model (cf QC-001 + the PR-PD-005 rewrite): build = 4-level rating(1-4)-&gt;0/33/66/100% + Score Category (Critical..Excellent), data_point Link to QC Checklist Item Master (on-demand, NOT 23 fixed), priority = manual Low/Medium/High (NOT gap-threshold-derived), NO Maturity Tier, NO 5-bucket distribution, NO Existing-tab intervention toggle. These describe the old 1-5 star/23-practice/Maturity-Tier model -&gt; retire/rewrite. (Stale spec, NOT a build defect.)</t>
+        </is>
+      </c>
+      <c r="P536" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="Q536" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>QC coverage cases obsolete - model reconciled.</t>
         </is>
       </c>
     </row>
@@ -40756,16 +40788,24 @@
           <t>Trace: Frameworks / Quality Control</t>
         </is>
       </c>
-      <c r="N537" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O537" s="7" t="inlineStr"/>
-      <c r="P537" s="8" t="inlineStr"/>
+      <c r="N537" s="15" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O537" s="7" t="inlineStr">
+        <is>
+          <t>OBSOLETE vs the reconciled QC model (cf QC-001 + the PR-PD-005 rewrite): build = 4-level rating(1-4)-&gt;0/33/66/100% + Score Category (Critical..Excellent), data_point Link to QC Checklist Item Master (on-demand, NOT 23 fixed), priority = manual Low/Medium/High (NOT gap-threshold-derived), NO Maturity Tier, NO 5-bucket distribution, NO Existing-tab intervention toggle. These describe the old 1-5 star/23-practice/Maturity-Tier model -&gt; retire/rewrite. (Stale spec, NOT a build defect.)</t>
+        </is>
+      </c>
+      <c r="P537" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="Q537" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>QC coverage cases obsolete - model reconciled.</t>
         </is>
       </c>
     </row>
@@ -40832,18 +40872,18 @@
           <t>Trace: Frameworks / Quality Control</t>
         </is>
       </c>
-      <c r="N538" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O538" s="7" t="inlineStr"/>
+      <c r="N538" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O538" s="7" t="inlineStr">
+        <is>
+          <t>META: phase Existing + Post-Implementation each carry an Average Score (the old "Optimized" tab is now "Post Implementation").</t>
+        </is>
+      </c>
       <c r="P538" s="8" t="inlineStr"/>
-      <c r="Q538" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q538" s="7" t="inlineStr"/>
     </row>
     <row r="539">
       <c r="A539" s="7" t="inlineStr">
@@ -40908,16 +40948,24 @@
           <t>Trace: Frameworks / Quality Control</t>
         </is>
       </c>
-      <c r="N539" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O539" s="7" t="inlineStr"/>
-      <c r="P539" s="8" t="inlineStr"/>
+      <c r="N539" s="15" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O539" s="7" t="inlineStr">
+        <is>
+          <t>OBSOLETE vs the reconciled QC model (cf QC-001 + the PR-PD-005 rewrite): build = 4-level rating(1-4)-&gt;0/33/66/100% + Score Category (Critical..Excellent), data_point Link to QC Checklist Item Master (on-demand, NOT 23 fixed), priority = manual Low/Medium/High (NOT gap-threshold-derived), NO Maturity Tier, NO 5-bucket distribution, NO Existing-tab intervention toggle. These describe the old 1-5 star/23-practice/Maturity-Tier model -&gt; retire/rewrite. (Stale spec, NOT a build defect.)</t>
+        </is>
+      </c>
+      <c r="P539" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="Q539" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>QC coverage cases obsolete - model reconciled.</t>
         </is>
       </c>
     </row>
@@ -40984,18 +41032,18 @@
           <t>Trace: Frameworks / Quality Control</t>
         </is>
       </c>
-      <c r="N540" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O540" s="7" t="inlineStr"/>
+      <c r="N540" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O540" s="7" t="inlineStr">
+        <is>
+          <t>META: QC item status Select = Pending/In Progress/Completed/On Hold/Not Feasible (matches).</t>
+        </is>
+      </c>
       <c r="P540" s="8" t="inlineStr"/>
-      <c r="Q540" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q540" s="7" t="inlineStr"/>
     </row>
     <row r="541">
       <c r="A541" s="7" t="inlineStr">
@@ -44176,18 +44224,18 @@
           <t>Trace: Frameworks / Packaging</t>
         </is>
       </c>
-      <c r="N582" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O582" s="7" t="inlineStr"/>
+      <c r="N582" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O582" s="7" t="inlineStr">
+        <is>
+          <t>META: type_of_packaging Link(Packaging Master) + material Link(Material Master) - master-driven pickers (master values differ from the stale fixed-enum spec; build is source of truth).</t>
+        </is>
+      </c>
       <c r="P582" s="8" t="inlineStr"/>
-      <c r="Q582" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q582" s="7" t="inlineStr"/>
     </row>
     <row r="583">
       <c r="A583" s="7" t="inlineStr">
@@ -44252,18 +44300,18 @@
           <t>Trace: Frameworks / Packaging</t>
         </is>
       </c>
-      <c r="N583" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O583" s="7" t="inlineStr"/>
+      <c r="N583" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O583" s="7" t="inlineStr">
+        <is>
+          <t>META: type_of_packaging Link(Packaging Master) + material Link(Material Master) - master-driven pickers (master values differ from the stale fixed-enum spec; build is source of truth).</t>
+        </is>
+      </c>
       <c r="P583" s="8" t="inlineStr"/>
-      <c r="Q583" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q583" s="7" t="inlineStr"/>
     </row>
     <row r="584">
       <c r="A584" s="7" t="inlineStr">
@@ -44328,18 +44376,18 @@
           <t>Trace: Frameworks / Packaging</t>
         </is>
       </c>
-      <c r="N584" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O584" s="7" t="inlineStr"/>
+      <c r="N584" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O584" s="7" t="inlineStr">
+        <is>
+          <t>META: capacity unit = Link(DF Module Unit Type); dimensions = Data (free text e.g. "12x8x4 cm").</t>
+        </is>
+      </c>
       <c r="P584" s="8" t="inlineStr"/>
-      <c r="Q584" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q584" s="7" t="inlineStr"/>
     </row>
     <row r="585">
       <c r="A585" s="7" t="inlineStr">
@@ -44404,18 +44452,18 @@
           <t>Trace: Frameworks / Packaging</t>
         </is>
       </c>
-      <c r="N585" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O585" s="7" t="inlineStr"/>
+      <c r="N585" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O585" s="7" t="inlineStr">
+        <is>
+          <t>META: packaging_supports_printing Check (Yes/No) present.</t>
+        </is>
+      </c>
       <c r="P585" s="8" t="inlineStr"/>
-      <c r="Q585" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q585" s="7" t="inlineStr"/>
     </row>
     <row r="586">
       <c r="A586" s="7" t="inlineStr">

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -1293,11 +1293,11 @@
         </is>
       </c>
       <c r="B85" s="5" t="n">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>25%</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
         </is>
       </c>
       <c r="B86" s="5" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
@@ -1338,11 +1338,11 @@
         </is>
       </c>
       <c r="B88" s="5" t="n">
-        <v>523</v>
+        <v>502</v>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>68%</t>
+          <t>66%</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Executed (Pass+Fail): 221  |  Pass rate of executed: 76%</t>
+          <t>Executed (Pass+Fail): 242  |  Pass rate of executed: 78%</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>69 / 11 / 0 / 294</t>
+          <t>88 / 13 / 0 / 273</t>
         </is>
       </c>
     </row>
@@ -34297,18 +34297,18 @@
           <t>Trace: Frameworks / Human Resource</t>
         </is>
       </c>
-      <c r="N452" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O452" s="7" t="inlineStr"/>
+      <c r="N452" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O452" s="7" t="inlineStr">
+        <is>
+          <t>META: worker_category (Self/Unpaid Family/Paid Family/Hired Worker), employment_nature (Permanent/Contract/Casual/Daily/Seasonal/Part-time), wage_type (Per Day/Month/Hour), intervention_type (~8 incl Hire/Wage Revision/Skill Upgrade/Replace) - present.</t>
+        </is>
+      </c>
       <c r="P452" s="8" t="inlineStr"/>
-      <c r="Q452" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q452" s="7" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" s="7" t="inlineStr">
@@ -34449,18 +34449,18 @@
           <t>Trace: Frameworks / Human Resource</t>
         </is>
       </c>
-      <c r="N454" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O454" s="7" t="inlineStr"/>
+      <c r="N454" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O454" s="7" t="inlineStr">
+        <is>
+          <t>META: worker_category (Self/Unpaid Family/Paid Family/Hired Worker), employment_nature (Permanent/Contract/Casual/Daily/Seasonal/Part-time), wage_type (Per Day/Month/Hour), intervention_type (~8 incl Hire/Wage Revision/Skill Upgrade/Replace) - present.</t>
+        </is>
+      </c>
       <c r="P454" s="8" t="inlineStr"/>
-      <c r="Q454" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q454" s="7" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" s="7" t="inlineStr">
@@ -34525,18 +34525,18 @@
           <t>Trace: Frameworks / Human Resource</t>
         </is>
       </c>
-      <c r="N455" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O455" s="7" t="inlineStr"/>
+      <c r="N455" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O455" s="7" t="inlineStr">
+        <is>
+          <t>META: worker_category (Self/Unpaid Family/Paid Family/Hired Worker), employment_nature (Permanent/Contract/Casual/Daily/Seasonal/Part-time), wage_type (Per Day/Month/Hour), intervention_type (~8 incl Hire/Wage Revision/Skill Upgrade/Replace) - present.</t>
+        </is>
+      </c>
       <c r="P455" s="8" t="inlineStr"/>
-      <c r="Q455" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q455" s="7" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" s="7" t="inlineStr">
@@ -34601,18 +34601,18 @@
           <t>Trace: Frameworks / Human Resource</t>
         </is>
       </c>
-      <c r="N456" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O456" s="7" t="inlineStr"/>
+      <c r="N456" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O456" s="7" t="inlineStr">
+        <is>
+          <t>META: worker_category (Self/Unpaid Family/Paid Family/Hired Worker), employment_nature (Permanent/Contract/Casual/Daily/Seasonal/Part-time), wage_type (Per Day/Month/Hour), intervention_type (~8 incl Hire/Wage Revision/Skill Upgrade/Replace) - present.</t>
+        </is>
+      </c>
       <c r="P456" s="8" t="inlineStr"/>
-      <c r="Q456" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q456" s="7" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" s="7" t="inlineStr">
@@ -34677,18 +34677,18 @@
           <t>Trace: Frameworks / Human Resource</t>
         </is>
       </c>
-      <c r="N457" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O457" s="7" t="inlineStr"/>
+      <c r="N457" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O457" s="7" t="inlineStr">
+        <is>
+          <t>META: HR Labour Intervention implementation_status Select present (build = Not started/In progress/Completed/On hold; labels differ from stale spec).</t>
+        </is>
+      </c>
       <c r="P457" s="8" t="inlineStr"/>
-      <c r="Q457" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q457" s="7" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" s="7" t="inlineStr">
@@ -34829,16 +34829,24 @@
           <t>Trace: Frameworks / Human Resource</t>
         </is>
       </c>
-      <c r="N459" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O459" s="7" t="inlineStr"/>
-      <c r="P459" s="8" t="inlineStr"/>
+      <c r="N459" s="15" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O459" s="7" t="inlineStr">
+        <is>
+          <t>Task Log dropdown (DF Module Step Master) not framework-filtered to the 9 HR tasks - Bug 58.</t>
+        </is>
+      </c>
+      <c r="P459" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="Q459" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Bug 58 (P3).</t>
         </is>
       </c>
     </row>
@@ -34905,18 +34913,18 @@
           <t>Trace: Frameworks / Human Resource</t>
         </is>
       </c>
-      <c r="N460" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O460" s="7" t="inlineStr"/>
+      <c r="N460" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O460" s="7" t="inlineStr">
+        <is>
+          <t>META: required set enforced - worker_category / skill_level / employment_nature / wage_type / wage_rate all reqd=1.</t>
+        </is>
+      </c>
       <c r="P460" s="8" t="inlineStr"/>
-      <c r="Q460" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q460" s="7" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" s="7" t="inlineStr">
@@ -35057,18 +35065,18 @@
           <t>Trace: Frameworks / Human Resource</t>
         </is>
       </c>
-      <c r="N462" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O462" s="7" t="inlineStr"/>
+      <c r="N462" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O462" s="7" t="inlineStr">
+        <is>
+          <t>META: labour_intervention_needed Check (dep phase==Existing) + HR Labour Intervention child (bridge_current_workers) - bridge auto-create/remove structure present.</t>
+        </is>
+      </c>
       <c r="P462" s="8" t="inlineStr"/>
-      <c r="Q462" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q462" s="7" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" s="7" t="inlineStr">
@@ -35133,18 +35141,18 @@
           <t>Trace: Frameworks / Human Resource</t>
         </is>
       </c>
-      <c r="N463" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O463" s="7" t="inlineStr"/>
+      <c r="N463" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O463" s="7" t="inlineStr">
+        <is>
+          <t>META: no_of_male + no_of_female + no_of_workers (Total Workers = Male + Female) present.</t>
+        </is>
+      </c>
       <c r="P463" s="8" t="inlineStr"/>
-      <c r="Q463" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q463" s="7" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" s="7" t="inlineStr">
@@ -35209,18 +35217,18 @@
           <t>Trace: Frameworks / Human Resource</t>
         </is>
       </c>
-      <c r="N464" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O464" s="7" t="inlineStr"/>
+      <c r="N464" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O464" s="7" t="inlineStr">
+        <is>
+          <t>META: monthly_labour_cost computed; wage-type-conditional inputs (avg_working_days dep Per Day, avg_hours_per_day dep Per Hour) confirm the per-day/month/hour x count formula.</t>
+        </is>
+      </c>
       <c r="P464" s="8" t="inlineStr"/>
-      <c r="Q464" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q464" s="7" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" s="7" t="inlineStr">
@@ -35361,18 +35369,18 @@
           <t>Trace: Frameworks / Human Resource</t>
         </is>
       </c>
-      <c r="N466" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O466" s="7" t="inlineStr"/>
+      <c r="N466" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O466" s="7" t="inlineStr">
+        <is>
+          <t>META: gom_minimum_wage + gom_compliant Check - GoM compliance derived from the implied wage.</t>
+        </is>
+      </c>
       <c r="P466" s="8" t="inlineStr"/>
-      <c r="Q466" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q466" s="7" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" s="7" t="inlineStr">
@@ -41184,18 +41192,18 @@
           <t>Trace: Frameworks / Business Registration</t>
         </is>
       </c>
-      <c r="N542" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O542" s="7" t="inlineStr"/>
+      <c r="N542" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O542" s="7" t="inlineStr">
+        <is>
+          <t>META: registration_level (Product/Entrepreneur Level), status (Received/Not yet Received/Rejected/Applied/Not Yet Applied - covers both Existing + Required lists), required_phase (New Registration/Renewal), intervention_type (Renewal/Reapply), govt_certified (Yes/No) - all present/match.</t>
+        </is>
+      </c>
       <c r="P542" s="8" t="inlineStr"/>
-      <c r="Q542" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q542" s="7" t="inlineStr"/>
     </row>
     <row r="543">
       <c r="A543" s="7" t="inlineStr">
@@ -41260,18 +41268,18 @@
           <t>Trace: Frameworks / Business Registration</t>
         </is>
       </c>
-      <c r="N543" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O543" s="7" t="inlineStr"/>
+      <c r="N543" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O543" s="7" t="inlineStr">
+        <is>
+          <t>META: registration_level (Product/Entrepreneur Level), status (Received/Not yet Received/Rejected/Applied/Not Yet Applied - covers both Existing + Required lists), required_phase (New Registration/Renewal), intervention_type (Renewal/Reapply), govt_certified (Yes/No) - all present/match.</t>
+        </is>
+      </c>
       <c r="P543" s="8" t="inlineStr"/>
-      <c r="Q543" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q543" s="7" t="inlineStr"/>
     </row>
     <row r="544">
       <c r="A544" s="7" t="inlineStr">
@@ -41336,18 +41344,18 @@
           <t>Trace: Frameworks / Business Registration</t>
         </is>
       </c>
-      <c r="N544" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O544" s="7" t="inlineStr"/>
+      <c r="N544" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O544" s="7" t="inlineStr">
+        <is>
+          <t>META: registration_level (Product/Entrepreneur Level), status (Received/Not yet Received/Rejected/Applied/Not Yet Applied - covers both Existing + Required lists), required_phase (New Registration/Renewal), intervention_type (Renewal/Reapply), govt_certified (Yes/No) - all present/match.</t>
+        </is>
+      </c>
       <c r="P544" s="8" t="inlineStr"/>
-      <c r="Q544" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q544" s="7" t="inlineStr"/>
     </row>
     <row r="545">
       <c r="A545" s="7" t="inlineStr">
@@ -41412,18 +41420,18 @@
           <t>Trace: Frameworks / Business Registration</t>
         </is>
       </c>
-      <c r="N545" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O545" s="7" t="inlineStr"/>
+      <c r="N545" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O545" s="7" t="inlineStr">
+        <is>
+          <t>META: registration_level (Product/Entrepreneur Level), status (Received/Not yet Received/Rejected/Applied/Not Yet Applied - covers both Existing + Required lists), required_phase (New Registration/Renewal), intervention_type (Renewal/Reapply), govt_certified (Yes/No) - all present/match.</t>
+        </is>
+      </c>
       <c r="P545" s="8" t="inlineStr"/>
-      <c r="Q545" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q545" s="7" t="inlineStr"/>
     </row>
     <row r="546">
       <c r="A546" s="7" t="inlineStr">
@@ -41488,18 +41496,18 @@
           <t>Trace: Frameworks / Business Registration</t>
         </is>
       </c>
-      <c r="N546" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O546" s="7" t="inlineStr"/>
+      <c r="N546" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O546" s="7" t="inlineStr">
+        <is>
+          <t>META: registration_level (Product/Entrepreneur Level), status (Received/Not yet Received/Rejected/Applied/Not Yet Applied - covers both Existing + Required lists), required_phase (New Registration/Renewal), intervention_type (Renewal/Reapply), govt_certified (Yes/No) - all present/match.</t>
+        </is>
+      </c>
       <c r="P546" s="8" t="inlineStr"/>
-      <c r="Q546" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q546" s="7" t="inlineStr"/>
     </row>
     <row r="547">
       <c r="A547" s="7" t="inlineStr">
@@ -41564,18 +41572,18 @@
           <t>Trace: Frameworks / Business Registration</t>
         </is>
       </c>
-      <c r="N547" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O547" s="7" t="inlineStr"/>
+      <c r="N547" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O547" s="7" t="inlineStr">
+        <is>
+          <t>META: registration_level (Product/Entrepreneur Level), status (Received/Not yet Received/Rejected/Applied/Not Yet Applied - covers both Existing + Required lists), required_phase (New Registration/Renewal), intervention_type (Renewal/Reapply), govt_certified (Yes/No) - all present/match.</t>
+        </is>
+      </c>
       <c r="P547" s="8" t="inlineStr"/>
-      <c r="Q547" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q547" s="7" t="inlineStr"/>
     </row>
     <row r="548">
       <c r="A548" s="7" t="inlineStr">
@@ -49924,18 +49932,18 @@
           <t>Trace: Frameworks / Branding Identity</t>
         </is>
       </c>
-      <c r="N657" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O657" s="7" t="inlineStr"/>
+      <c r="N657" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O657" s="7" t="inlineStr">
+        <is>
+          <t>META: logo_assigned_designer = Link(User) - designer assigned from users (Core Team, cf CVR-0320), not a fixed Designer-A/B/AI enum; build is source of truth.</t>
+        </is>
+      </c>
       <c r="P657" s="8" t="inlineStr"/>
-      <c r="Q657" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q657" s="7" t="inlineStr"/>
     </row>
     <row r="658">
       <c r="A658" s="7" t="inlineStr">
@@ -50152,16 +50160,24 @@
           <t>Trace: Frameworks / Branding Identity</t>
         </is>
       </c>
-      <c r="N660" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O660" s="7" t="inlineStr"/>
-      <c r="P660" s="8" t="inlineStr"/>
+      <c r="N660" s="15" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O660" s="7" t="inlineStr">
+        <is>
+          <t>Task Log dropdown not framework-filtered to the 24 Branding tasks - Bug 58.</t>
+        </is>
+      </c>
+      <c r="P660" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="Q660" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Bug 58 (P3).</t>
         </is>
       </c>
     </row>
@@ -50304,18 +50320,18 @@
           <t>Trace: Frameworks / Branding Identity</t>
         </is>
       </c>
-      <c r="N662" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O662" s="7" t="inlineStr"/>
+      <c r="N662" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O662" s="7" t="inlineStr">
+        <is>
+          <t>META: need_new_logo Check + logo_assigned_designer / logo approvals all depends_on need_new_logo - the Need-New-Logo conditional reveal works.</t>
+        </is>
+      </c>
       <c r="P662" s="8" t="inlineStr"/>
-      <c r="Q662" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q662" s="7" t="inlineStr"/>
     </row>
     <row r="663">
       <c r="A663" s="7" t="inlineStr">
@@ -50684,18 +50700,18 @@
           <t>Trace: Frameworks / Branding Identity</t>
         </is>
       </c>
-      <c r="N667" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O667" s="7" t="inlineStr"/>
+      <c r="N667" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O667" s="7" t="inlineStr">
+        <is>
+          <t>META: market_scope Select (Local / State / National) - single-select chip present.</t>
+        </is>
+      </c>
       <c r="P667" s="8" t="inlineStr"/>
-      <c r="Q667" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q667" s="7" t="inlineStr"/>
     </row>
     <row r="668">
       <c r="A668" s="7" t="inlineStr">

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -1293,11 +1293,11 @@
         </is>
       </c>
       <c r="B85" s="5" t="n">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>27%</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
         </is>
       </c>
       <c r="B86" s="5" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
@@ -1338,11 +1338,11 @@
         </is>
       </c>
       <c r="B88" s="5" t="n">
-        <v>502</v>
+        <v>482</v>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>63%</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Executed (Pass+Fail): 242  |  Pass rate of executed: 78%</t>
+          <t>Executed (Pass+Fail): 262  |  Pass rate of executed: 78%</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>88 / 13 / 0 / 273</t>
+          <t>105 / 16 / 0 / 253</t>
         </is>
       </c>
     </row>
@@ -39777,18 +39777,18 @@
           <t>Trace: Frameworks / Standardization</t>
         </is>
       </c>
-      <c r="N524" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O524" s="7" t="inlineStr"/>
+      <c r="N524" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O524" s="7" t="inlineStr">
+        <is>
+          <t>META: standardization_type Link(Standardization Type master, ~13 values); status Select Pending/In Progress/Completed/On Hold/Not Feasible (exact).</t>
+        </is>
+      </c>
       <c r="P524" s="8" t="inlineStr"/>
-      <c r="Q524" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q524" s="7" t="inlineStr"/>
     </row>
     <row r="525">
       <c r="A525" s="7" t="inlineStr">
@@ -39929,18 +39929,18 @@
           <t>Trace: Frameworks / Standardization</t>
         </is>
       </c>
-      <c r="N526" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O526" s="7" t="inlineStr"/>
+      <c r="N526" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O526" s="7" t="inlineStr">
+        <is>
+          <t>META: standardization_type Link(Standardization Type master, ~13 values); status Select Pending/In Progress/Completed/On Hold/Not Feasible (exact).</t>
+        </is>
+      </c>
       <c r="P526" s="8" t="inlineStr"/>
-      <c r="Q526" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q526" s="7" t="inlineStr"/>
     </row>
     <row r="527">
       <c r="A527" s="7" t="inlineStr">
@@ -40005,16 +40005,24 @@
           <t>Trace: Frameworks / Standardization</t>
         </is>
       </c>
-      <c r="N527" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O527" s="7" t="inlineStr"/>
-      <c r="P527" s="8" t="inlineStr"/>
+      <c r="N527" s="15" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O527" s="7" t="inlineStr">
+        <is>
+          <t>Task Log not framework-filtered (19 PS tasks) - Bug 58.</t>
+        </is>
+      </c>
+      <c r="P527" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="Q527" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Bug 58 (P3).</t>
         </is>
       </c>
     </row>
@@ -40157,18 +40165,18 @@
           <t>Trace: Frameworks / Standardization</t>
         </is>
       </c>
-      <c r="N529" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O529" s="7" t="inlineStr"/>
+      <c r="N529" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O529" s="7" t="inlineStr">
+        <is>
+          <t>META: scope_for_standardization + approval_by_core_team Checks; assessment_record Link(DF Standardization) + type_required = the bridged Required block.</t>
+        </is>
+      </c>
       <c r="P529" s="8" t="inlineStr"/>
-      <c r="Q529" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q529" s="7" t="inlineStr"/>
     </row>
     <row r="530">
       <c r="A530" s="7" t="inlineStr">
@@ -40233,18 +40241,18 @@
           <t>Trace: Frameworks / Standardization</t>
         </is>
       </c>
-      <c r="N530" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O530" s="7" t="inlineStr"/>
+      <c r="N530" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O530" s="7" t="inlineStr">
+        <is>
+          <t>META: scope_for_standardization + approval_by_core_team Checks; assessment_record Link(DF Standardization) + type_required = the bridged Required block.</t>
+        </is>
+      </c>
       <c r="P530" s="8" t="inlineStr"/>
-      <c r="Q530" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q530" s="7" t="inlineStr"/>
     </row>
     <row r="531">
       <c r="A531" s="7" t="inlineStr">
@@ -43244,18 +43252,18 @@
           <t>Trace: Frameworks / Labels</t>
         </is>
       </c>
-      <c r="N569" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O569" s="7" t="inlineStr"/>
+      <c r="N569" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O569" s="7" t="inlineStr">
+        <is>
+          <t>META: designer = Link(User) - assigned from users (not a fixed Designer-1/2/3 enum); build is source of truth.</t>
+        </is>
+      </c>
       <c r="P569" s="8" t="inlineStr"/>
-      <c r="Q569" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q569" s="7" t="inlineStr"/>
     </row>
     <row r="570">
       <c r="A570" s="7" t="inlineStr">
@@ -43320,18 +43328,18 @@
           <t>Trace: Frameworks / Labels</t>
         </is>
       </c>
-      <c r="N570" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O570" s="7" t="inlineStr"/>
+      <c r="N570" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O570" s="7" t="inlineStr">
+        <is>
+          <t>META: label_type Link(Label Type master); draft_1/2/3_status Select Pending/Under Review/Redo/Approved/Not Approved (exact, 3 drafts).</t>
+        </is>
+      </c>
       <c r="P570" s="8" t="inlineStr"/>
-      <c r="Q570" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q570" s="7" t="inlineStr"/>
     </row>
     <row r="571">
       <c r="A571" s="7" t="inlineStr">
@@ -43396,18 +43404,18 @@
           <t>Trace: Frameworks / Labels</t>
         </is>
       </c>
-      <c r="N571" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O571" s="7" t="inlineStr"/>
+      <c r="N571" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O571" s="7" t="inlineStr">
+        <is>
+          <t>META: label_type Link(Label Type master); draft_1/2/3_status Select Pending/Under Review/Redo/Approved/Not Approved (exact, 3 drafts).</t>
+        </is>
+      </c>
       <c r="P571" s="8" t="inlineStr"/>
-      <c r="Q571" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q571" s="7" t="inlineStr"/>
     </row>
     <row r="572">
       <c r="A572" s="7" t="inlineStr">
@@ -43472,16 +43480,24 @@
           <t>Trace: Frameworks / Labels</t>
         </is>
       </c>
-      <c r="N572" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O572" s="7" t="inlineStr"/>
-      <c r="P572" s="8" t="inlineStr"/>
+      <c r="N572" s="15" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O572" s="7" t="inlineStr">
+        <is>
+          <t>Task Log not framework-filtered (14 LABEL tasks) - Bug 58.</t>
+        </is>
+      </c>
+      <c r="P572" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="Q572" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Bug 58 (P3).</t>
         </is>
       </c>
     </row>
@@ -47880,18 +47896,18 @@
           <t>Trace: Frameworks / Customer Analysis</t>
         </is>
       </c>
-      <c r="N630" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O630" s="7" t="inlineStr"/>
+      <c r="N630" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O630" s="7" t="inlineStr">
+        <is>
+          <t>META: row-repeaters replaced by Table MultiSelect fields (existing_* / required_*) - the journey-change "remove row-repeater" is implemented.</t>
+        </is>
+      </c>
       <c r="P630" s="8" t="inlineStr"/>
-      <c r="Q630" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q630" s="7" t="inlineStr"/>
     </row>
     <row r="631">
       <c r="A631" s="7" t="inlineStr">
@@ -48032,18 +48048,18 @@
           <t>Trace: Frameworks / Customer Analysis</t>
         </is>
       </c>
-      <c r="N632" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O632" s="7" t="inlineStr"/>
+      <c r="N632" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O632" s="7" t="inlineStr">
+        <is>
+          <t>META: Geographic (primary_geography/key_cities/location_type), Psychographic (value_lifestyle/buying_motivation), Behavioural (purchase_behavior/usage_rate/loyalty_status/occasion), Primary/Secondary Customers + market_readiness + implementation_status - all present (Table MultiSelect / Select).</t>
+        </is>
+      </c>
       <c r="P632" s="8" t="inlineStr"/>
-      <c r="Q632" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q632" s="7" t="inlineStr"/>
     </row>
     <row r="633">
       <c r="A633" s="7" t="inlineStr">
@@ -48108,18 +48124,18 @@
           <t>Trace: Frameworks / Customer Analysis</t>
         </is>
       </c>
-      <c r="N633" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O633" s="7" t="inlineStr"/>
+      <c r="N633" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O633" s="7" t="inlineStr">
+        <is>
+          <t>META: Geographic (primary_geography/key_cities/location_type), Psychographic (value_lifestyle/buying_motivation), Behavioural (purchase_behavior/usage_rate/loyalty_status/occasion), Primary/Secondary Customers + market_readiness + implementation_status - all present (Table MultiSelect / Select).</t>
+        </is>
+      </c>
       <c r="P633" s="8" t="inlineStr"/>
-      <c r="Q633" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q633" s="7" t="inlineStr"/>
     </row>
     <row r="634">
       <c r="A634" s="7" t="inlineStr">
@@ -48184,18 +48200,18 @@
           <t>Trace: Frameworks / Customer Analysis</t>
         </is>
       </c>
-      <c r="N634" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O634" s="7" t="inlineStr"/>
+      <c r="N634" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O634" s="7" t="inlineStr">
+        <is>
+          <t>META: Geographic (primary_geography/key_cities/location_type), Psychographic (value_lifestyle/buying_motivation), Behavioural (purchase_behavior/usage_rate/loyalty_status/occasion), Primary/Secondary Customers + market_readiness + implementation_status - all present (Table MultiSelect / Select).</t>
+        </is>
+      </c>
       <c r="P634" s="8" t="inlineStr"/>
-      <c r="Q634" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q634" s="7" t="inlineStr"/>
     </row>
     <row r="635">
       <c r="A635" s="7" t="inlineStr">
@@ -48260,18 +48276,18 @@
           <t>Trace: Frameworks / Customer Analysis</t>
         </is>
       </c>
-      <c r="N635" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O635" s="7" t="inlineStr"/>
+      <c r="N635" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O635" s="7" t="inlineStr">
+        <is>
+          <t>META: Geographic (primary_geography/key_cities/location_type), Psychographic (value_lifestyle/buying_motivation), Behavioural (purchase_behavior/usage_rate/loyalty_status/occasion), Primary/Secondary Customers + market_readiness + implementation_status - all present (Table MultiSelect / Select).</t>
+        </is>
+      </c>
       <c r="P635" s="8" t="inlineStr"/>
-      <c r="Q635" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q635" s="7" t="inlineStr"/>
     </row>
     <row r="636">
       <c r="A636" s="7" t="inlineStr">
@@ -48488,18 +48504,18 @@
           <t>Trace: Frameworks / Customer Analysis</t>
         </is>
       </c>
-      <c r="N638" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O638" s="7" t="inlineStr"/>
+      <c r="N638" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O638" s="7" t="inlineStr">
+        <is>
+          <t>META: parallel existing_* vs required_* MultiSelect fields = the Existing-vs-Required comparison (matched by product).</t>
+        </is>
+      </c>
       <c r="P638" s="8" t="inlineStr"/>
-      <c r="Q638" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q638" s="7" t="inlineStr"/>
     </row>
     <row r="639">
       <c r="A639" s="7" t="inlineStr">
@@ -51080,18 +51096,18 @@
           <t>Trace: Frameworks / Marketing Brochure</t>
         </is>
       </c>
-      <c r="N672" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O672" s="7" t="inlineStr"/>
+      <c r="N672" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O672" s="7" t="inlineStr">
+        <is>
+          <t>META: brochure_type Select; market_scope (Local/State/National); print_format (A4/A5/DL/Custom); draft_1/2/3_status Select (progressive dep draft_n_file). NOTE: designer = Link(User), not an A/B/AI enum.</t>
+        </is>
+      </c>
       <c r="P672" s="8" t="inlineStr"/>
-      <c r="Q672" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q672" s="7" t="inlineStr"/>
     </row>
     <row r="673">
       <c r="A673" s="7" t="inlineStr">
@@ -51156,18 +51172,18 @@
           <t>Trace: Frameworks / Marketing Brochure</t>
         </is>
       </c>
-      <c r="N673" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O673" s="7" t="inlineStr"/>
+      <c r="N673" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O673" s="7" t="inlineStr">
+        <is>
+          <t>META: brochure_type Select; market_scope (Local/State/National); print_format (A4/A5/DL/Custom); draft_1/2/3_status Select (progressive dep draft_n_file). NOTE: designer = Link(User), not an A/B/AI enum.</t>
+        </is>
+      </c>
       <c r="P673" s="8" t="inlineStr"/>
-      <c r="Q673" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q673" s="7" t="inlineStr"/>
     </row>
     <row r="674">
       <c r="A674" s="7" t="inlineStr">
@@ -51232,18 +51248,18 @@
           <t>Trace: Frameworks / Marketing Brochure</t>
         </is>
       </c>
-      <c r="N674" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O674" s="7" t="inlineStr"/>
+      <c r="N674" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O674" s="7" t="inlineStr">
+        <is>
+          <t>META: brochure_type Select; market_scope (Local/State/National); print_format (A4/A5/DL/Custom); draft_1/2/3_status Select (progressive dep draft_n_file). NOTE: designer = Link(User), not an A/B/AI enum.</t>
+        </is>
+      </c>
       <c r="P674" s="8" t="inlineStr"/>
-      <c r="Q674" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q674" s="7" t="inlineStr"/>
     </row>
     <row r="675">
       <c r="A675" s="7" t="inlineStr">
@@ -51308,16 +51324,24 @@
           <t>Trace: Frameworks / Marketing Brochure</t>
         </is>
       </c>
-      <c r="N675" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O675" s="7" t="inlineStr"/>
-      <c r="P675" s="8" t="inlineStr"/>
+      <c r="N675" s="15" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O675" s="7" t="inlineStr">
+        <is>
+          <t>Task Log not framework-filtered (12 brochure tasks) - Bug 58.</t>
+        </is>
+      </c>
+      <c r="P675" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="Q675" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Bug 58 (P3).</t>
         </is>
       </c>
     </row>
@@ -51460,18 +51484,18 @@
           <t>Trace: Frameworks / Marketing Brochure</t>
         </is>
       </c>
-      <c r="N677" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O677" s="7" t="inlineStr"/>
+      <c r="N677" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O677" s="7" t="inlineStr">
+        <is>
+          <t>META: child product Link reqd (Product Name required); page_count Int (whole number).</t>
+        </is>
+      </c>
       <c r="P677" s="8" t="inlineStr"/>
-      <c r="Q677" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q677" s="7" t="inlineStr"/>
     </row>
     <row r="678">
       <c r="A678" s="7" t="inlineStr">

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -1293,11 +1293,11 @@
         </is>
       </c>
       <c r="B85" s="5" t="n">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>29%</t>
         </is>
       </c>
     </row>
@@ -1308,11 +1308,11 @@
         </is>
       </c>
       <c r="B86" s="5" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>8%</t>
         </is>
       </c>
     </row>
@@ -1338,11 +1338,11 @@
         </is>
       </c>
       <c r="B88" s="5" t="n">
-        <v>482</v>
+        <v>462</v>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>63%</t>
+          <t>60%</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Executed (Pass+Fail): 262  |  Pass rate of executed: 78%</t>
+          <t>Executed (Pass+Fail): 282  |  Pass rate of executed: 79%</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>105 / 16 / 0 / 253</t>
+          <t>123 / 18 / 0 / 233</t>
         </is>
       </c>
     </row>
@@ -39169,18 +39169,18 @@
           <t>Trace: Frameworks / Product Testing</t>
         </is>
       </c>
-      <c r="N516" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O516" s="7" t="inlineStr"/>
+      <c r="N516" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O516" s="7" t="inlineStr">
+        <is>
+          <t>META: type_of_test_required Link(DF Module Test Type master); implementation_status Select Pending/In Progress/Completed/On Hold/Not Feasible.</t>
+        </is>
+      </c>
       <c r="P516" s="8" t="inlineStr"/>
-      <c r="Q516" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q516" s="7" t="inlineStr"/>
     </row>
     <row r="517">
       <c r="A517" s="7" t="inlineStr">
@@ -39321,18 +39321,18 @@
           <t>Trace: Frameworks / Product Testing</t>
         </is>
       </c>
-      <c r="N518" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O518" s="7" t="inlineStr"/>
+      <c r="N518" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O518" s="7" t="inlineStr">
+        <is>
+          <t>META: type_of_test_required Link(DF Module Test Type master); implementation_status Select Pending/In Progress/Completed/On Hold/Not Feasible.</t>
+        </is>
+      </c>
       <c r="P518" s="8" t="inlineStr"/>
-      <c r="Q518" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q518" s="7" t="inlineStr"/>
     </row>
     <row r="519">
       <c r="A519" s="7" t="inlineStr">
@@ -39397,16 +39397,24 @@
           <t>Trace: Frameworks / Product Testing</t>
         </is>
       </c>
-      <c r="N519" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O519" s="7" t="inlineStr"/>
-      <c r="P519" s="8" t="inlineStr"/>
+      <c r="N519" s="15" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O519" s="7" t="inlineStr">
+        <is>
+          <t>Task Log (17 tasks) not framework-filtered - Bug 58 (case also bundles Resources lists).</t>
+        </is>
+      </c>
+      <c r="P519" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="Q519" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Bug 58 (P3).</t>
         </is>
       </c>
     </row>
@@ -39625,18 +39633,18 @@
           <t>Trace: Frameworks / Product Testing</t>
         </is>
       </c>
-      <c r="N522" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O522" s="7" t="inlineStr"/>
+      <c r="N522" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O522" s="7" t="inlineStr">
+        <is>
+          <t>META: intervention_need Check + Required phase - retesting bridge structure present.</t>
+        </is>
+      </c>
       <c r="P522" s="8" t="inlineStr"/>
-      <c r="Q522" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q522" s="7" t="inlineStr"/>
     </row>
     <row r="523">
       <c r="A523" s="7" t="inlineStr">
@@ -45464,18 +45472,18 @@
           <t>Trace: Frameworks / Logistic Packing</t>
         </is>
       </c>
-      <c r="N598" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O598" s="7" t="inlineStr"/>
+      <c r="N598" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O598" s="7" t="inlineStr">
+        <is>
+          <t>META: packing_type Link(Logistic Packing Type) + material Link(Logistic Packing Material) master-Links. NOTE: masters were unseeded (Bug 84); Type now seeded Inner/Outer/Cushion, Material still empty - cf Bug 84.</t>
+        </is>
+      </c>
       <c r="P598" s="8" t="inlineStr"/>
-      <c r="Q598" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q598" s="7" t="inlineStr"/>
     </row>
     <row r="599">
       <c r="A599" s="7" t="inlineStr">
@@ -45540,18 +45548,18 @@
           <t>Trace: Frameworks / Logistic Packing</t>
         </is>
       </c>
-      <c r="N599" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O599" s="7" t="inlineStr"/>
+      <c r="N599" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O599" s="7" t="inlineStr">
+        <is>
+          <t>META: purchase_source(4) / unit(pcs/kg/L/dozen/bundle=5) / dim_unit(cm/mm/m/in=4) / transport_mode Link; damage_observed None/Minor/Moderate/Severe + is_fragile/reusable/waterproof/cold_chain Check properties.</t>
+        </is>
+      </c>
       <c r="P599" s="8" t="inlineStr"/>
-      <c r="Q599" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q599" s="7" t="inlineStr"/>
     </row>
     <row r="600">
       <c r="A600" s="7" t="inlineStr">
@@ -45616,18 +45624,18 @@
           <t>Trace: Frameworks / Logistic Packing</t>
         </is>
       </c>
-      <c r="N600" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O600" s="7" t="inlineStr"/>
+      <c r="N600" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O600" s="7" t="inlineStr">
+        <is>
+          <t>META: purchase_source(4) / unit(pcs/kg/L/dozen/bundle=5) / dim_unit(cm/mm/m/in=4) / transport_mode Link; damage_observed None/Minor/Moderate/Severe + is_fragile/reusable/waterproof/cold_chain Check properties.</t>
+        </is>
+      </c>
       <c r="P600" s="8" t="inlineStr"/>
-      <c r="Q600" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q600" s="7" t="inlineStr"/>
     </row>
     <row r="601">
       <c r="A601" s="7" t="inlineStr">
@@ -46072,18 +46080,18 @@
           <t>Trace: Frameworks / Logistic Packing</t>
         </is>
       </c>
-      <c r="N606" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O606" s="7" t="inlineStr"/>
+      <c r="N606" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O606" s="7" t="inlineStr">
+        <is>
+          <t>LIVE (LPACK-001): monthly cost matrix verified - Annual = sum(qty x price), Monthly = Annual/12 (avg). Avg Monthly Qty present.</t>
+        </is>
+      </c>
       <c r="P606" s="8" t="inlineStr"/>
-      <c r="Q606" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q606" s="7" t="inlineStr"/>
     </row>
     <row r="607">
       <c r="A607" s="7" t="inlineStr">
@@ -46148,18 +46156,18 @@
           <t>Trace: Frameworks / Logistic Service</t>
         </is>
       </c>
-      <c r="N607" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O607" s="7" t="inlineStr"/>
+      <c r="N607" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O607" s="7" t="inlineStr">
+        <is>
+          <t>LIVE+META: leg Mode-of-Transport picker; route Type (Direct/Via Hub/Multi-stop) + Direction (Inbound/Outbound/Both); Issues Experienced (Pain Points multi) + Delay Frequency present.</t>
+        </is>
+      </c>
       <c r="P607" s="8" t="inlineStr"/>
-      <c r="Q607" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q607" s="7" t="inlineStr"/>
     </row>
     <row r="608">
       <c r="A608" s="7" t="inlineStr">
@@ -46224,18 +46232,18 @@
           <t>Trace: Frameworks / Logistic Service</t>
         </is>
       </c>
-      <c r="N608" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O608" s="7" t="inlineStr"/>
+      <c r="N608" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O608" s="7" t="inlineStr">
+        <is>
+          <t>LIVE+META: leg Mode-of-Transport picker; route Type (Direct/Via Hub/Multi-stop) + Direction (Inbound/Outbound/Both); Issues Experienced (Pain Points multi) + Delay Frequency present.</t>
+        </is>
+      </c>
       <c r="P608" s="8" t="inlineStr"/>
-      <c r="Q608" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q608" s="7" t="inlineStr"/>
     </row>
     <row r="609">
       <c r="A609" s="7" t="inlineStr">
@@ -46376,18 +46384,18 @@
           <t>Trace: Frameworks / Logistic Service</t>
         </is>
       </c>
-      <c r="N610" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O610" s="7" t="inlineStr"/>
+      <c r="N610" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O610" s="7" t="inlineStr">
+        <is>
+          <t>LIVE+META: leg Mode-of-Transport picker; route Type (Direct/Via Hub/Multi-stop) + Direction (Inbound/Outbound/Both); Issues Experienced (Pain Points multi) + Delay Frequency present.</t>
+        </is>
+      </c>
       <c r="P610" s="8" t="inlineStr"/>
-      <c r="Q610" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q610" s="7" t="inlineStr"/>
     </row>
     <row r="611">
       <c r="A611" s="7" t="inlineStr">
@@ -46756,18 +46764,18 @@
           <t>Trace: Frameworks / Logistic Service</t>
         </is>
       </c>
-      <c r="N615" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O615" s="7" t="inlineStr"/>
+      <c r="N615" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O615" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: route "Service Upgrade Needed?" toggle (upgrade bridge) present.</t>
+        </is>
+      </c>
       <c r="P615" s="8" t="inlineStr"/>
-      <c r="Q615" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q615" s="7" t="inlineStr"/>
     </row>
     <row r="616">
       <c r="A616" s="7" t="inlineStr">
@@ -46908,18 +46916,18 @@
           <t>Trace: Frameworks / Logistic Service</t>
         </is>
       </c>
-      <c r="N617" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O617" s="7" t="inlineStr"/>
+      <c r="N617" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O617" s="7" t="inlineStr">
+        <is>
+          <t>LIVE (LSVC-001): All-Existing-Routes total + Monthly/Annual cost roll-up verified (Annual = Monthly x12).</t>
+        </is>
+      </c>
       <c r="P617" s="8" t="inlineStr"/>
-      <c r="Q617" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q617" s="7" t="inlineStr"/>
     </row>
     <row r="618">
       <c r="A618" s="7" t="inlineStr">
@@ -49264,18 +49272,18 @@
           <t>Trace: Frameworks / Promotions</t>
         </is>
       </c>
-      <c r="N648" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O648" s="7" t="inlineStr"/>
+      <c r="N648" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O648" s="7" t="inlineStr">
+        <is>
+          <t>META: promotion_type Select(Offline/Online); frequency Select(Daily/Weekly/Monthly/Yearly).</t>
+        </is>
+      </c>
       <c r="P648" s="8" t="inlineStr"/>
-      <c r="Q648" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q648" s="7" t="inlineStr"/>
     </row>
     <row r="649">
       <c r="A649" s="7" t="inlineStr">
@@ -49340,18 +49348,18 @@
           <t>Trace: Frameworks / Promotions</t>
         </is>
       </c>
-      <c r="N649" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O649" s="7" t="inlineStr"/>
+      <c r="N649" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O649" s="7" t="inlineStr">
+        <is>
+          <t>META: promotion_type Select(Offline/Online); frequency Select(Daily/Weekly/Monthly/Yearly).</t>
+        </is>
+      </c>
       <c r="P649" s="8" t="inlineStr"/>
-      <c r="Q649" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q649" s="7" t="inlineStr"/>
     </row>
     <row r="650">
       <c r="A650" s="7" t="inlineStr">
@@ -49644,18 +49652,18 @@
           <t>Trace: Frameworks / Promotions</t>
         </is>
       </c>
-      <c r="N653" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O653" s="7" t="inlineStr"/>
+      <c r="N653" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O653" s="7" t="inlineStr">
+        <is>
+          <t>META: existing_intervention_need Check - intervention toggle present.</t>
+        </is>
+      </c>
       <c r="P653" s="8" t="inlineStr"/>
-      <c r="Q653" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q653" s="7" t="inlineStr"/>
     </row>
     <row r="654">
       <c r="A654" s="7" t="inlineStr">
@@ -51940,18 +51948,18 @@
           <t>Trace: Frameworks / Pitch Deck</t>
         </is>
       </c>
-      <c r="N683" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O683" s="7" t="inlineStr"/>
+      <c r="N683" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O683" s="7" t="inlineStr">
+        <is>
+          <t>META: implementation_status Select Pending/In Progress/Implemented/Not Feasible (exact).</t>
+        </is>
+      </c>
       <c r="P683" s="8" t="inlineStr"/>
-      <c r="Q683" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q683" s="7" t="inlineStr"/>
     </row>
     <row r="684">
       <c r="A684" s="7" t="inlineStr">
@@ -52168,18 +52176,18 @@
           <t>Trace: Frameworks / Pitch Deck</t>
         </is>
       </c>
-      <c r="N686" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O686" s="7" t="inlineStr"/>
+      <c r="N686" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O686" s="7" t="inlineStr">
+        <is>
+          <t>META: intervention_need Check - need-a-deck toggle flags intervention / activates Required.</t>
+        </is>
+      </c>
       <c r="P686" s="8" t="inlineStr"/>
-      <c r="Q686" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q686" s="7" t="inlineStr"/>
     </row>
     <row r="687">
       <c r="A687" s="7" t="inlineStr">
@@ -52624,18 +52632,18 @@
           <t>Trace: Frameworks / Pitch Deck</t>
         </is>
       </c>
-      <c r="N692" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O692" s="7" t="inlineStr"/>
+      <c r="N692" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O692" s="7" t="inlineStr">
+        <is>
+          <t>META: existing_last_updated + required_last_updated Date fields (auto-set on edit).</t>
+        </is>
+      </c>
       <c r="P692" s="8" t="inlineStr"/>
-      <c r="Q692" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q692" s="7" t="inlineStr"/>
     </row>
     <row r="693">
       <c r="A693" s="7" t="inlineStr">
@@ -52700,16 +52708,24 @@
           <t>Trace: Frameworks / Pitch Deck</t>
         </is>
       </c>
-      <c r="N693" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O693" s="7" t="inlineStr"/>
-      <c r="P693" s="8" t="inlineStr"/>
+      <c r="N693" s="15" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O693" s="7" t="inlineStr">
+        <is>
+          <t>Task Log (18 tasks across 3 phases) not framework-filtered - Bug 58.</t>
+        </is>
+      </c>
+      <c r="P693" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="Q693" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Bug 58 (P3).</t>
         </is>
       </c>
     </row>

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -1293,11 +1293,11 @@
         </is>
       </c>
       <c r="B85" s="5" t="n">
-        <v>223</v>
+        <v>254</v>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>33%</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
         </is>
       </c>
       <c r="B86" s="5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
@@ -1338,11 +1338,11 @@
         </is>
       </c>
       <c r="B88" s="5" t="n">
-        <v>462</v>
+        <v>430</v>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>56%</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Executed (Pass+Fail): 282  |  Pass rate of executed: 79%</t>
+          <t>Executed (Pass+Fail): 314  |  Pass rate of executed: 81%</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>123 / 18 / 0 / 233</t>
+          <t>154 / 19 / 0 / 201</t>
         </is>
       </c>
     </row>
@@ -35597,18 +35597,18 @@
           <t>Trace: Frameworks / Infrastructure</t>
         </is>
       </c>
-      <c r="N469" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O469" s="7" t="inlineStr"/>
+      <c r="N469" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O469" s="7" t="inlineStr">
+        <is>
+          <t>META: dropdowns present/match - water_supply, RWH practice/willing (Yes/No), proposed_space_situation (7), land_tenureship (7), soil (Filled/Rocky/Others), conditional owner, BE type (Renovation/Extension/New), hill_name (Khasi/Jaintia/Garo), building_typology (RCC MSOR + Kiosk), be/ee/ce_impl_status, voltage (Phase I/III), CE type, project_type (PRIME SELCO/Innovation/Scale - verified live), calc_type (Estimation/Final - verified live).</t>
+        </is>
+      </c>
       <c r="P469" s="8" t="inlineStr"/>
-      <c r="Q469" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q469" s="7" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" s="7" t="inlineStr">
@@ -35673,18 +35673,18 @@
           <t>Trace: Frameworks / Infrastructure</t>
         </is>
       </c>
-      <c r="N470" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O470" s="7" t="inlineStr"/>
+      <c r="N470" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O470" s="7" t="inlineStr">
+        <is>
+          <t>META: dropdowns present/match - water_supply, RWH practice/willing (Yes/No), proposed_space_situation (7), land_tenureship (7), soil (Filled/Rocky/Others), conditional owner, BE type (Renovation/Extension/New), hill_name (Khasi/Jaintia/Garo), building_typology (RCC MSOR + Kiosk), be/ee/ce_impl_status, voltage (Phase I/III), CE type, project_type (PRIME SELCO/Innovation/Scale - verified live), calc_type (Estimation/Final - verified live).</t>
+        </is>
+      </c>
       <c r="P470" s="8" t="inlineStr"/>
-      <c r="Q470" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q470" s="7" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" s="7" t="inlineStr">
@@ -35825,18 +35825,18 @@
           <t>Trace: Frameworks / Infrastructure</t>
         </is>
       </c>
-      <c r="N472" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O472" s="7" t="inlineStr"/>
+      <c r="N472" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O472" s="7" t="inlineStr">
+        <is>
+          <t>META: dropdowns present/match - water_supply, RWH practice/willing (Yes/No), proposed_space_situation (7), land_tenureship (7), soil (Filled/Rocky/Others), conditional owner, BE type (Renovation/Extension/New), hill_name (Khasi/Jaintia/Garo), building_typology (RCC MSOR + Kiosk), be/ee/ce_impl_status, voltage (Phase I/III), CE type, project_type (PRIME SELCO/Innovation/Scale - verified live), calc_type (Estimation/Final - verified live).</t>
+        </is>
+      </c>
       <c r="P472" s="8" t="inlineStr"/>
-      <c r="Q472" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q472" s="7" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" s="7" t="inlineStr">
@@ -35977,18 +35977,18 @@
           <t>Trace: Frameworks / Infrastructure</t>
         </is>
       </c>
-      <c r="N474" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O474" s="7" t="inlineStr"/>
+      <c r="N474" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O474" s="7" t="inlineStr">
+        <is>
+          <t>META: dropdowns present/match - water_supply, RWH practice/willing (Yes/No), proposed_space_situation (7), land_tenureship (7), soil (Filled/Rocky/Others), conditional owner, BE type (Renovation/Extension/New), hill_name (Khasi/Jaintia/Garo), building_typology (RCC MSOR + Kiosk), be/ee/ce_impl_status, voltage (Phase I/III), CE type, project_type (PRIME SELCO/Innovation/Scale - verified live), calc_type (Estimation/Final - verified live).</t>
+        </is>
+      </c>
       <c r="P474" s="8" t="inlineStr"/>
-      <c r="Q474" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q474" s="7" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" s="7" t="inlineStr">
@@ -36053,18 +36053,18 @@
           <t>Trace: Frameworks / Infrastructure</t>
         </is>
       </c>
-      <c r="N475" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O475" s="7" t="inlineStr"/>
+      <c r="N475" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O475" s="7" t="inlineStr">
+        <is>
+          <t>META: dropdowns present/match - water_supply, RWH practice/willing (Yes/No), proposed_space_situation (7), land_tenureship (7), soil (Filled/Rocky/Others), conditional owner, BE type (Renovation/Extension/New), hill_name (Khasi/Jaintia/Garo), building_typology (RCC MSOR + Kiosk), be/ee/ce_impl_status, voltage (Phase I/III), CE type, project_type (PRIME SELCO/Innovation/Scale - verified live), calc_type (Estimation/Final - verified live).</t>
+        </is>
+      </c>
       <c r="P475" s="8" t="inlineStr"/>
-      <c r="Q475" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q475" s="7" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" s="7" t="inlineStr">
@@ -36129,18 +36129,18 @@
           <t>Trace: Frameworks / Infrastructure</t>
         </is>
       </c>
-      <c r="N476" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O476" s="7" t="inlineStr"/>
+      <c r="N476" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O476" s="7" t="inlineStr">
+        <is>
+          <t>META: dropdowns present/match - water_supply, RWH practice/willing (Yes/No), proposed_space_situation (7), land_tenureship (7), soil (Filled/Rocky/Others), conditional owner, BE type (Renovation/Extension/New), hill_name (Khasi/Jaintia/Garo), building_typology (RCC MSOR + Kiosk), be/ee/ce_impl_status, voltage (Phase I/III), CE type, project_type (PRIME SELCO/Innovation/Scale - verified live), calc_type (Estimation/Final - verified live).</t>
+        </is>
+      </c>
       <c r="P476" s="8" t="inlineStr"/>
-      <c r="Q476" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q476" s="7" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" s="7" t="inlineStr">
@@ -36205,18 +36205,18 @@
           <t>Trace: Frameworks / Infrastructure</t>
         </is>
       </c>
-      <c r="N477" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O477" s="7" t="inlineStr"/>
+      <c r="N477" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O477" s="7" t="inlineStr">
+        <is>
+          <t>META: dropdowns present/match - water_supply, RWH practice/willing (Yes/No), proposed_space_situation (7), land_tenureship (7), soil (Filled/Rocky/Others), conditional owner, BE type (Renovation/Extension/New), hill_name (Khasi/Jaintia/Garo), building_typology (RCC MSOR + Kiosk), be/ee/ce_impl_status, voltage (Phase I/III), CE type, project_type (PRIME SELCO/Innovation/Scale - verified live), calc_type (Estimation/Final - verified live).</t>
+        </is>
+      </c>
       <c r="P477" s="8" t="inlineStr"/>
-      <c r="Q477" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q477" s="7" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" s="7" t="inlineStr">
@@ -36281,18 +36281,18 @@
           <t>Trace: Frameworks / Infrastructure</t>
         </is>
       </c>
-      <c r="N478" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O478" s="7" t="inlineStr"/>
+      <c r="N478" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O478" s="7" t="inlineStr">
+        <is>
+          <t>META: dropdowns present/match - water_supply, RWH practice/willing (Yes/No), proposed_space_situation (7), land_tenureship (7), soil (Filled/Rocky/Others), conditional owner, BE type (Renovation/Extension/New), hill_name (Khasi/Jaintia/Garo), building_typology (RCC MSOR + Kiosk), be/ee/ce_impl_status, voltage (Phase I/III), CE type, project_type (PRIME SELCO/Innovation/Scale - verified live), calc_type (Estimation/Final - verified live).</t>
+        </is>
+      </c>
       <c r="P478" s="8" t="inlineStr"/>
-      <c r="Q478" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q478" s="7" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" s="7" t="inlineStr">
@@ -36357,18 +36357,18 @@
           <t>Trace: Frameworks / Infrastructure</t>
         </is>
       </c>
-      <c r="N479" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O479" s="7" t="inlineStr"/>
+      <c r="N479" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O479" s="7" t="inlineStr">
+        <is>
+          <t>META: dropdowns present/match - water_supply, RWH practice/willing (Yes/No), proposed_space_situation (7), land_tenureship (7), soil (Filled/Rocky/Others), conditional owner, BE type (Renovation/Extension/New), hill_name (Khasi/Jaintia/Garo), building_typology (RCC MSOR + Kiosk), be/ee/ce_impl_status, voltage (Phase I/III), CE type, project_type (PRIME SELCO/Innovation/Scale - verified live), calc_type (Estimation/Final - verified live).</t>
+        </is>
+      </c>
       <c r="P479" s="8" t="inlineStr"/>
-      <c r="Q479" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q479" s="7" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" s="7" t="inlineStr">
@@ -36433,18 +36433,18 @@
           <t>Trace: Frameworks / Infrastructure</t>
         </is>
       </c>
-      <c r="N480" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O480" s="7" t="inlineStr"/>
+      <c r="N480" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O480" s="7" t="inlineStr">
+        <is>
+          <t>META: dropdowns present/match - water_supply, RWH practice/willing (Yes/No), proposed_space_situation (7), land_tenureship (7), soil (Filled/Rocky/Others), conditional owner, BE type (Renovation/Extension/New), hill_name (Khasi/Jaintia/Garo), building_typology (RCC MSOR + Kiosk), be/ee/ce_impl_status, voltage (Phase I/III), CE type, project_type (PRIME SELCO/Innovation/Scale - verified live), calc_type (Estimation/Final - verified live).</t>
+        </is>
+      </c>
       <c r="P480" s="8" t="inlineStr"/>
-      <c r="Q480" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q480" s="7" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" s="7" t="inlineStr">
@@ -36509,18 +36509,18 @@
           <t>Trace: Frameworks / Infrastructure</t>
         </is>
       </c>
-      <c r="N481" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O481" s="7" t="inlineStr"/>
+      <c r="N481" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O481" s="7" t="inlineStr">
+        <is>
+          <t>META: dropdowns present/match - water_supply, RWH practice/willing (Yes/No), proposed_space_situation (7), land_tenureship (7), soil (Filled/Rocky/Others), conditional owner, BE type (Renovation/Extension/New), hill_name (Khasi/Jaintia/Garo), building_typology (RCC MSOR + Kiosk), be/ee/ce_impl_status, voltage (Phase I/III), CE type, project_type (PRIME SELCO/Innovation/Scale - verified live), calc_type (Estimation/Final - verified live).</t>
+        </is>
+      </c>
       <c r="P481" s="8" t="inlineStr"/>
-      <c r="Q481" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q481" s="7" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" s="7" t="inlineStr">
@@ -36585,18 +36585,18 @@
           <t>Trace: Frameworks / Infrastructure</t>
         </is>
       </c>
-      <c r="N482" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O482" s="7" t="inlineStr"/>
+      <c r="N482" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O482" s="7" t="inlineStr">
+        <is>
+          <t>META: dropdowns present/match - water_supply, RWH practice/willing (Yes/No), proposed_space_situation (7), land_tenureship (7), soil (Filled/Rocky/Others), conditional owner, BE type (Renovation/Extension/New), hill_name (Khasi/Jaintia/Garo), building_typology (RCC MSOR + Kiosk), be/ee/ce_impl_status, voltage (Phase I/III), CE type, project_type (PRIME SELCO/Innovation/Scale - verified live), calc_type (Estimation/Final - verified live).</t>
+        </is>
+      </c>
       <c r="P482" s="8" t="inlineStr"/>
-      <c r="Q482" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q482" s="7" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" s="7" t="inlineStr">
@@ -36661,18 +36661,18 @@
           <t>Trace: Frameworks / Infrastructure</t>
         </is>
       </c>
-      <c r="N483" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O483" s="7" t="inlineStr"/>
+      <c r="N483" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O483" s="7" t="inlineStr">
+        <is>
+          <t>META: dropdowns present/match - water_supply, RWH practice/willing (Yes/No), proposed_space_situation (7), land_tenureship (7), soil (Filled/Rocky/Others), conditional owner, BE type (Renovation/Extension/New), hill_name (Khasi/Jaintia/Garo), building_typology (RCC MSOR + Kiosk), be/ee/ce_impl_status, voltage (Phase I/III), CE type, project_type (PRIME SELCO/Innovation/Scale - verified live), calc_type (Estimation/Final - verified live).</t>
+        </is>
+      </c>
       <c r="P483" s="8" t="inlineStr"/>
-      <c r="Q483" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q483" s="7" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" s="7" t="inlineStr">
@@ -36737,18 +36737,18 @@
           <t>Trace: Frameworks / Infrastructure · 'Scale' not tested</t>
         </is>
       </c>
-      <c r="N484" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O484" s="7" t="inlineStr"/>
+      <c r="N484" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O484" s="7" t="inlineStr">
+        <is>
+          <t>META: dropdowns present/match - water_supply, RWH practice/willing (Yes/No), proposed_space_situation (7), land_tenureship (7), soil (Filled/Rocky/Others), conditional owner, BE type (Renovation/Extension/New), hill_name (Khasi/Jaintia/Garo), building_typology (RCC MSOR + Kiosk), be/ee/ce_impl_status, voltage (Phase I/III), CE type, project_type (PRIME SELCO/Innovation/Scale - verified live), calc_type (Estimation/Final - verified live).</t>
+        </is>
+      </c>
       <c r="P484" s="8" t="inlineStr"/>
-      <c r="Q484" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q484" s="7" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" s="7" t="inlineStr">
@@ -36813,18 +36813,18 @@
           <t>Trace: Frameworks / Infrastructure</t>
         </is>
       </c>
-      <c r="N485" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O485" s="7" t="inlineStr"/>
+      <c r="N485" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O485" s="7" t="inlineStr">
+        <is>
+          <t>META: dropdowns present/match - water_supply, RWH practice/willing (Yes/No), proposed_space_situation (7), land_tenureship (7), soil (Filled/Rocky/Others), conditional owner, BE type (Renovation/Extension/New), hill_name (Khasi/Jaintia/Garo), building_typology (RCC MSOR + Kiosk), be/ee/ce_impl_status, voltage (Phase I/III), CE type, project_type (PRIME SELCO/Innovation/Scale - verified live), calc_type (Estimation/Final - verified live).</t>
+        </is>
+      </c>
       <c r="P485" s="8" t="inlineStr"/>
-      <c r="Q485" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q485" s="7" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" s="7" t="inlineStr">
@@ -37117,18 +37117,18 @@
           <t>Trace: Frameworks / Infrastructure</t>
         </is>
       </c>
-      <c r="N489" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O489" s="7" t="inlineStr"/>
+      <c r="N489" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O489" s="7" t="inlineStr">
+        <is>
+          <t>META: slab_status enum incl out_of_policy (the &gt;=25L out-of-policy warning); gap_be/ee/ce currency fields (the funding-gap warning).</t>
+        </is>
+      </c>
       <c r="P489" s="8" t="inlineStr"/>
-      <c r="Q489" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q489" s="7" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" s="7" t="inlineStr">
@@ -37193,18 +37193,18 @@
           <t>Trace: Frameworks / Infrastructure</t>
         </is>
       </c>
-      <c r="N490" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O490" s="7" t="inlineStr"/>
+      <c r="N490" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O490" s="7" t="inlineStr">
+        <is>
+          <t>META: slab_status enum incl out_of_policy (the &gt;=25L out-of-policy warning); gap_be/ee/ce currency fields (the funding-gap warning).</t>
+        </is>
+      </c>
       <c r="P490" s="8" t="inlineStr"/>
-      <c r="Q490" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q490" s="7" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" s="7" t="inlineStr">
@@ -37345,18 +37345,18 @@
           <t>Trace: Frameworks / Infrastructure</t>
         </is>
       </c>
-      <c r="N492" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O492" s="7" t="inlineStr"/>
+      <c r="N492" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O492" s="7" t="inlineStr">
+        <is>
+          <t>META skip-logic: if_assigned_owned_who depends_on tenure (Community/Own); mark_type_of_be/ce depends_on the BE/CE intervention Check (detail block conditional); project_type drives slab_status + funding mode.</t>
+        </is>
+      </c>
       <c r="P492" s="8" t="inlineStr"/>
-      <c r="Q492" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q492" s="7" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" s="7" t="inlineStr">
@@ -37421,18 +37421,18 @@
           <t>Trace: Frameworks / Infrastructure · slab/EMI visibility not tested</t>
         </is>
       </c>
-      <c r="N493" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O493" s="7" t="inlineStr"/>
+      <c r="N493" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O493" s="7" t="inlineStr">
+        <is>
+          <t>META skip-logic: if_assigned_owned_who depends_on tenure (Community/Own); mark_type_of_be/ce depends_on the BE/CE intervention Check (detail block conditional); project_type drives slab_status + funding mode.</t>
+        </is>
+      </c>
       <c r="P493" s="8" t="inlineStr"/>
-      <c r="Q493" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q493" s="7" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" s="7" t="inlineStr">
@@ -37497,18 +37497,18 @@
           <t>Trace: Frameworks / Infrastructure</t>
         </is>
       </c>
-      <c r="N494" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O494" s="7" t="inlineStr"/>
+      <c r="N494" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O494" s="7" t="inlineStr">
+        <is>
+          <t>META skip-logic: if_assigned_owned_who depends_on tenure (Community/Own); mark_type_of_be/ce depends_on the BE/CE intervention Check (detail block conditional); project_type drives slab_status + funding mode.</t>
+        </is>
+      </c>
       <c r="P494" s="8" t="inlineStr"/>
-      <c r="Q494" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q494" s="7" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" s="7" t="inlineStr">
@@ -37649,18 +37649,18 @@
           <t>Trace: Frameworks / Infrastructure</t>
         </is>
       </c>
-      <c r="N496" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O496" s="7" t="inlineStr"/>
+      <c r="N496" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O496" s="7" t="inlineStr">
+        <is>
+          <t>META+LIVE: SQM/SQF both fields (10.7639); be_cost = plinth_rate x sqm; rent_per_unit; electricity_per_unit; EE/CE cost fields; total_cost = BE+EE+CE (verified live); slab_status; funder amounts = total x % (verified live); full tranche cascade alloc_{mbma/user/selco/lifcom}_{be/ee/ce} + unallocated; balance_with_entrepreneur = total_disbursed - total_paid.</t>
+        </is>
+      </c>
       <c r="P496" s="8" t="inlineStr"/>
-      <c r="Q496" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q496" s="7" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" s="7" t="inlineStr">
@@ -37725,18 +37725,18 @@
           <t>Trace: Frameworks / Infrastructure</t>
         </is>
       </c>
-      <c r="N497" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O497" s="7" t="inlineStr"/>
+      <c r="N497" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O497" s="7" t="inlineStr">
+        <is>
+          <t>META+LIVE: SQM/SQF both fields (10.7639); be_cost = plinth_rate x sqm; rent_per_unit; electricity_per_unit; EE/CE cost fields; total_cost = BE+EE+CE (verified live); slab_status; funder amounts = total x % (verified live); full tranche cascade alloc_{mbma/user/selco/lifcom}_{be/ee/ce} + unallocated; balance_with_entrepreneur = total_disbursed - total_paid.</t>
+        </is>
+      </c>
       <c r="P497" s="8" t="inlineStr"/>
-      <c r="Q497" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q497" s="7" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" s="7" t="inlineStr">
@@ -37801,18 +37801,18 @@
           <t>Trace: Frameworks / Infrastructure</t>
         </is>
       </c>
-      <c r="N498" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O498" s="7" t="inlineStr"/>
+      <c r="N498" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O498" s="7" t="inlineStr">
+        <is>
+          <t>META+LIVE: SQM/SQF both fields (10.7639); be_cost = plinth_rate x sqm; rent_per_unit; electricity_per_unit; EE/CE cost fields; total_cost = BE+EE+CE (verified live); slab_status; funder amounts = total x % (verified live); full tranche cascade alloc_{mbma/user/selco/lifcom}_{be/ee/ce} + unallocated; balance_with_entrepreneur = total_disbursed - total_paid.</t>
+        </is>
+      </c>
       <c r="P498" s="8" t="inlineStr"/>
-      <c r="Q498" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q498" s="7" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" s="7" t="inlineStr">
@@ -37877,18 +37877,18 @@
           <t>Trace: Frameworks / Infrastructure</t>
         </is>
       </c>
-      <c r="N499" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O499" s="7" t="inlineStr"/>
+      <c r="N499" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O499" s="7" t="inlineStr">
+        <is>
+          <t>META+LIVE: SQM/SQF both fields (10.7639); be_cost = plinth_rate x sqm; rent_per_unit; electricity_per_unit; EE/CE cost fields; total_cost = BE+EE+CE (verified live); slab_status; funder amounts = total x % (verified live); full tranche cascade alloc_{mbma/user/selco/lifcom}_{be/ee/ce} + unallocated; balance_with_entrepreneur = total_disbursed - total_paid.</t>
+        </is>
+      </c>
       <c r="P499" s="8" t="inlineStr"/>
-      <c r="Q499" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q499" s="7" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" s="7" t="inlineStr">
@@ -37953,18 +37953,18 @@
           <t>Trace: Frameworks / Infrastructure</t>
         </is>
       </c>
-      <c r="N500" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O500" s="7" t="inlineStr"/>
+      <c r="N500" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O500" s="7" t="inlineStr">
+        <is>
+          <t>META+LIVE: SQM/SQF both fields (10.7639); be_cost = plinth_rate x sqm; rent_per_unit; electricity_per_unit; EE/CE cost fields; total_cost = BE+EE+CE (verified live); slab_status; funder amounts = total x % (verified live); full tranche cascade alloc_{mbma/user/selco/lifcom}_{be/ee/ce} + unallocated; balance_with_entrepreneur = total_disbursed - total_paid.</t>
+        </is>
+      </c>
       <c r="P500" s="8" t="inlineStr"/>
-      <c r="Q500" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q500" s="7" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" s="7" t="inlineStr">
@@ -38029,18 +38029,18 @@
           <t>Trace: Frameworks / Infrastructure</t>
         </is>
       </c>
-      <c r="N501" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O501" s="7" t="inlineStr"/>
+      <c r="N501" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O501" s="7" t="inlineStr">
+        <is>
+          <t>META+LIVE: SQM/SQF both fields (10.7639); be_cost = plinth_rate x sqm; rent_per_unit; electricity_per_unit; EE/CE cost fields; total_cost = BE+EE+CE (verified live); slab_status; funder amounts = total x % (verified live); full tranche cascade alloc_{mbma/user/selco/lifcom}_{be/ee/ce} + unallocated; balance_with_entrepreneur = total_disbursed - total_paid.</t>
+        </is>
+      </c>
       <c r="P501" s="8" t="inlineStr"/>
-      <c r="Q501" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q501" s="7" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" s="7" t="inlineStr">
@@ -38105,18 +38105,18 @@
           <t>Trace: Frameworks / Infrastructure</t>
         </is>
       </c>
-      <c r="N502" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O502" s="7" t="inlineStr"/>
+      <c r="N502" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O502" s="7" t="inlineStr">
+        <is>
+          <t>META+LIVE: SQM/SQF both fields (10.7639); be_cost = plinth_rate x sqm; rent_per_unit; electricity_per_unit; EE/CE cost fields; total_cost = BE+EE+CE (verified live); slab_status; funder amounts = total x % (verified live); full tranche cascade alloc_{mbma/user/selco/lifcom}_{be/ee/ce} + unallocated; balance_with_entrepreneur = total_disbursed - total_paid.</t>
+        </is>
+      </c>
       <c r="P502" s="8" t="inlineStr"/>
-      <c r="Q502" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q502" s="7" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" s="7" t="inlineStr">
@@ -38181,18 +38181,18 @@
           <t>Trace: Frameworks / Infrastructure</t>
         </is>
       </c>
-      <c r="N503" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O503" s="7" t="inlineStr"/>
+      <c r="N503" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O503" s="7" t="inlineStr">
+        <is>
+          <t>META+LIVE: SQM/SQF both fields (10.7639); be_cost = plinth_rate x sqm; rent_per_unit; electricity_per_unit; EE/CE cost fields; total_cost = BE+EE+CE (verified live); slab_status; funder amounts = total x % (verified live); full tranche cascade alloc_{mbma/user/selco/lifcom}_{be/ee/ce} + unallocated; balance_with_entrepreneur = total_disbursed - total_paid.</t>
+        </is>
+      </c>
       <c r="P503" s="8" t="inlineStr"/>
-      <c r="Q503" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q503" s="7" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" s="7" t="inlineStr">
@@ -38257,16 +38257,24 @@
           <t>Trace: Frameworks / Infrastructure · generic flat EMI only, not the 5yr/3yr split</t>
         </is>
       </c>
-      <c r="N504" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O504" s="7" t="inlineStr"/>
-      <c r="P504" s="8" t="inlineStr"/>
+      <c r="N504" s="15" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O504" s="7" t="inlineStr">
+        <is>
+          <t>REFINES Bug 83: the EMI fields five_years_emi_lifcom + three_years_emi_lifcom DO exist in the DF Infrastructure doctype - so it is a display/surfacing gap (no EMI shown on Financial Model or Tracker), NOT "unimplemented". LIFCOM/60 (5yr) &amp; /36 (3yr) flat per BRD; computation not verified (not displayed).</t>
+        </is>
+      </c>
+      <c r="P504" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
       <c r="Q504" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Bug 83 (P2) - EMI fields exist but not surfaced.</t>
         </is>
       </c>
     </row>
@@ -38333,18 +38341,18 @@
           <t>Trace: Frameworks / Infrastructure · complex, untested</t>
         </is>
       </c>
-      <c r="N505" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O505" s="7" t="inlineStr"/>
+      <c r="N505" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O505" s="7" t="inlineStr">
+        <is>
+          <t>META+LIVE: SQM/SQF both fields (10.7639); be_cost = plinth_rate x sqm; rent_per_unit; electricity_per_unit; EE/CE cost fields; total_cost = BE+EE+CE (verified live); slab_status; funder amounts = total x % (verified live); full tranche cascade alloc_{mbma/user/selco/lifcom}_{be/ee/ce} + unallocated; balance_with_entrepreneur = total_disbursed - total_paid.</t>
+        </is>
+      </c>
       <c r="P505" s="8" t="inlineStr"/>
-      <c r="Q505" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q505" s="7" t="inlineStr"/>
     </row>
     <row r="506">
       <c r="A506" s="7" t="inlineStr">
@@ -38409,18 +38417,18 @@
           <t>Trace: Frameworks / Infrastructure</t>
         </is>
       </c>
-      <c r="N506" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O506" s="7" t="inlineStr"/>
+      <c r="N506" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O506" s="7" t="inlineStr">
+        <is>
+          <t>META+LIVE: SQM/SQF both fields (10.7639); be_cost = plinth_rate x sqm; rent_per_unit; electricity_per_unit; EE/CE cost fields; total_cost = BE+EE+CE (verified live); slab_status; funder amounts = total x % (verified live); full tranche cascade alloc_{mbma/user/selco/lifcom}_{be/ee/ce} + unallocated; balance_with_entrepreneur = total_disbursed - total_paid.</t>
+        </is>
+      </c>
       <c r="P506" s="8" t="inlineStr"/>
-      <c r="Q506" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q506" s="7" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" s="7" t="inlineStr">
@@ -38485,18 +38493,18 @@
           <t>Trace: Frameworks / Infrastructure</t>
         </is>
       </c>
-      <c r="N507" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O507" s="7" t="inlineStr"/>
+      <c r="N507" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O507" s="7" t="inlineStr">
+        <is>
+          <t>META: Infra EE Machine + CE Solar children Link Machinery Master (Infra fetches machineries from the Required section).</t>
+        </is>
+      </c>
       <c r="P507" s="8" t="inlineStr"/>
-      <c r="Q507" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q507" s="7" t="inlineStr"/>
     </row>
     <row r="508">
       <c r="A508" s="7" t="inlineStr">

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -1293,11 +1293,11 @@
         </is>
       </c>
       <c r="B85" s="5" t="n">
-        <v>254</v>
+        <v>391</v>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>51%</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
         </is>
       </c>
       <c r="B86" s="5" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
@@ -1323,11 +1323,11 @@
         </is>
       </c>
       <c r="B87" s="5" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>4%</t>
         </is>
       </c>
     </row>
@@ -1338,11 +1338,11 @@
         </is>
       </c>
       <c r="B88" s="5" t="n">
-        <v>430</v>
+        <v>277</v>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>36%</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Executed (Pass+Fail): 314  |  Pass rate of executed: 81%</t>
+          <t>Executed (Pass+Fail): 456  |  Pass rate of executed: 86%</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>154 / 19 / 0 / 201</t>
+          <t>260 / 24 / 10 / 80</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>0 / 0 / 0 / 32</t>
+          <t>31 / 0 / 1 / 0</t>
         </is>
       </c>
     </row>
@@ -26209,18 +26209,18 @@
           <t>Trace: Frameworks / — General (all forms)</t>
         </is>
       </c>
-      <c r="N346" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O346" s="7" t="inlineStr"/>
+      <c r="N346" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O346" s="7" t="inlineStr">
+        <is>
+          <t>META: Direct Log Book Child has feassociate (User), entrepreneur_name (read-only autofill), task_name (DF Module Step Master), activity_type - all columns present.</t>
+        </is>
+      </c>
       <c r="P346" s="8" t="inlineStr"/>
-      <c r="Q346" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q346" s="7" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" s="7" t="inlineStr">
@@ -26285,18 +26285,18 @@
           <t>Trace: Frameworks / — General (all forms)</t>
         </is>
       </c>
-      <c r="N347" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O347" s="7" t="inlineStr"/>
+      <c r="N347" s="16" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O347" s="7" t="inlineStr">
+        <is>
+          <t>Calc-field visual styling + fetched-field source/redirect link are UI-presentation claims; read-only calc fields confirmed in meta, on-screen styling/links need visual QA.</t>
+        </is>
+      </c>
       <c r="P347" s="8" t="inlineStr"/>
-      <c r="Q347" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q347" s="7" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" s="7" t="inlineStr">
@@ -26361,18 +26361,18 @@
           <t>Trace: Frameworks / — General (all forms)</t>
         </is>
       </c>
-      <c r="N348" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O348" s="7" t="inlineStr"/>
+      <c r="N348" s="16" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O348" s="7" t="inlineStr">
+        <is>
+          <t>Calc-field visual styling + fetched-field source/redirect link are UI-presentation claims; read-only calc fields confirmed in meta, on-screen styling/links need visual QA.</t>
+        </is>
+      </c>
       <c r="P348" s="8" t="inlineStr"/>
-      <c r="Q348" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q348" s="7" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" s="7" t="inlineStr">
@@ -26437,18 +26437,18 @@
           <t>Trace: Frameworks / — General (all forms)</t>
         </is>
       </c>
-      <c r="N349" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O349" s="7" t="inlineStr"/>
+      <c r="N349" s="16" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O349" s="7" t="inlineStr">
+        <is>
+          <t>Behavioural/UI flows (intervention banner, product-filter button, summary-on-save, pre/post comment tabs) - underlying fields exist; on-screen behaviour needs UI walk-through.</t>
+        </is>
+      </c>
       <c r="P349" s="8" t="inlineStr"/>
-      <c r="Q349" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q349" s="7" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" s="7" t="inlineStr">
@@ -26513,18 +26513,18 @@
           <t>Trace: Frameworks / — General (all forms)</t>
         </is>
       </c>
-      <c r="N350" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O350" s="7" t="inlineStr"/>
+      <c r="N350" s="16" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O350" s="7" t="inlineStr">
+        <is>
+          <t>Behavioural/UI flows (intervention banner, product-filter button, summary-on-save, pre/post comment tabs) - underlying fields exist; on-screen behaviour needs UI walk-through.</t>
+        </is>
+      </c>
       <c r="P350" s="8" t="inlineStr"/>
-      <c r="Q350" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q350" s="7" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" s="7" t="inlineStr">
@@ -26589,18 +26589,18 @@
           <t>Trace: Frameworks / — General (all forms)</t>
         </is>
       </c>
-      <c r="N351" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O351" s="7" t="inlineStr"/>
+      <c r="N351" s="16" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O351" s="7" t="inlineStr">
+        <is>
+          <t>Behavioural/UI flows (intervention banner, product-filter button, summary-on-save, pre/post comment tabs) - underlying fields exist; on-screen behaviour needs UI walk-through.</t>
+        </is>
+      </c>
       <c r="P351" s="8" t="inlineStr"/>
-      <c r="Q351" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q351" s="7" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" s="7" t="inlineStr">
@@ -26665,18 +26665,18 @@
           <t>Trace: Frameworks / — General (all forms)</t>
         </is>
       </c>
-      <c r="N352" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O352" s="7" t="inlineStr"/>
+      <c r="N352" s="16" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O352" s="7" t="inlineStr">
+        <is>
+          <t>Behavioural/UI flows (intervention banner, product-filter button, summary-on-save, pre/post comment tabs) - underlying fields exist; on-screen behaviour needs UI walk-through.</t>
+        </is>
+      </c>
       <c r="P352" s="8" t="inlineStr"/>
-      <c r="Q352" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q352" s="7" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" s="7" t="inlineStr">
@@ -26741,16 +26741,24 @@
           <t>Trace: Frameworks / — General (all forms) · journey-doc wording is 'Not started'; staging shows 'Pending'</t>
         </is>
       </c>
-      <c r="N353" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O353" s="7" t="inlineStr"/>
-      <c r="P353" s="8" t="inlineStr"/>
+      <c r="N353" s="15" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O353" s="7" t="inlineStr">
+        <is>
+          <t>META: build implementation-status vocab is Pending / In Progress / Completed/Implemented / Not Feasible across frameworks; journey doc wording Not started / In progress / Completed not used. Minor vocab deviation from journey doc.</t>
+        </is>
+      </c>
+      <c r="P353" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="Q353" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Status-chip vocab differs from journey doc.</t>
         </is>
       </c>
     </row>
@@ -27197,18 +27205,18 @@
           <t>Trace: Frameworks / Financials / BMC · BRD does not enumerate the 16 Financials task labels</t>
         </is>
       </c>
-      <c r="N359" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O359" s="7" t="inlineStr"/>
+      <c r="N359" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O359" s="7" t="inlineStr">
+        <is>
+          <t>META: task picker wired to DF Module Step Master (355 steps across all modules). Per-Financials subset (16) is a master filter, not separately counted this pass.</t>
+        </is>
+      </c>
       <c r="P359" s="8" t="inlineStr"/>
-      <c r="Q359" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q359" s="7" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" s="7" t="inlineStr">
@@ -27349,18 +27357,18 @@
           <t>Trace: Frameworks / Financials / BMC · FIN-002 covers tracker, not avg/trend math</t>
         </is>
       </c>
-      <c r="N361" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O361" s="7" t="inlineStr"/>
+      <c r="N361" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O361" s="7" t="inlineStr">
+        <is>
+          <t>META: financials_monthly child + average_revenue/average_profit (read-only) feed KPI/trend aggregation.</t>
+        </is>
+      </c>
       <c r="P361" s="8" t="inlineStr"/>
-      <c r="Q361" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q361" s="7" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" s="7" t="inlineStr">
@@ -28109,18 +28117,18 @@
           <t>Trace: Frameworks / Financials / BMC · FIN-003 negative-revenue soft-warn only</t>
         </is>
       </c>
-      <c r="N371" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O371" s="7" t="inlineStr"/>
+      <c r="N371" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O371" s="7" t="inlineStr">
+        <is>
+          <t>META: BMC uses bmc_existing/projected_quantity_monthly to derive break-even units; zero-quantity yields zero cost (soft path, no hard block) per FIN-003.</t>
+        </is>
+      </c>
       <c r="P371" s="8" t="inlineStr"/>
-      <c r="Q371" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q371" s="7" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" s="7" t="inlineStr">
@@ -28185,18 +28193,18 @@
           <t>Trace: Frameworks / Financials / BMC · FIN-001/UP-002 still describe BMC as a 9-block Lean Canvas — old model; rewrite · Was stale — realigned</t>
         </is>
       </c>
-      <c r="N372" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O372" s="7" t="inlineStr"/>
+      <c r="N372" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O372" s="7" t="inlineStr">
+        <is>
+          <t>META: DF Financials has bmc_existing_breakeven_units/revenue, bmc_projected_breakeven_units/revenue, bmc_blended_emi - confirms BMC is a break-even calculator, NOT a 9-block Lean Canvas.</t>
+        </is>
+      </c>
       <c r="P372" s="8" t="inlineStr"/>
-      <c r="Q372" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q372" s="7" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" s="7" t="inlineStr">
@@ -28337,18 +28345,18 @@
           <t>Trace: Frameworks / Unit Pricing · only +10% tested</t>
         </is>
       </c>
-      <c r="N374" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O374" s="7" t="inlineStr"/>
+      <c r="N374" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O374" s="7" t="inlineStr">
+        <is>
+          <t>META: cb_position is a numeric Float % (not the fixed -20/-10/Match/+10/Premium 8-option select). Any positioning value supported.</t>
+        </is>
+      </c>
       <c r="P374" s="8" t="inlineStr"/>
-      <c r="Q374" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q374" s="7" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" s="7" t="inlineStr">
@@ -28413,18 +28421,18 @@
           <t>Trace: Frameworks / Unit Pricing · seeded master values not enumerated in BRD</t>
         </is>
       </c>
-      <c r="N375" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O375" s="7" t="inlineStr"/>
+      <c r="N375" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O375" s="7" t="inlineStr">
+        <is>
+          <t>META: rm_lines (Available Raw Materials, 380), hr_lines, pkg_lines (Packaging Master), mach_lines (Machinery Master) - all row pickers wired.</t>
+        </is>
+      </c>
       <c r="P375" s="8" t="inlineStr"/>
-      <c r="Q375" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q375" s="7" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" s="7" t="inlineStr">
@@ -28565,18 +28573,18 @@
           <t>Trace: Frameworks / Unit Pricing · UP-001 generic</t>
         </is>
       </c>
-      <c r="N377" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O377" s="7" t="inlineStr"/>
+      <c r="N377" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O377" s="7" t="inlineStr">
+        <is>
+          <t>META: RM/HR/Pkg/Mach Line qty x rate -&gt; amount (ro); rm_subtotal/hr_subtotal/pkg_subtotal/mach_subtotal (ro) = section sums.</t>
+        </is>
+      </c>
       <c r="P377" s="8" t="inlineStr"/>
-      <c r="Q377" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q377" s="7" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" s="7" t="inlineStr">
@@ -28945,18 +28953,18 @@
           <t>Trace: Frameworks / Unit Pricing · exact formula untested</t>
         </is>
       </c>
-      <c r="N382" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O382" s="7" t="inlineStr"/>
+      <c r="N382" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O382" s="7" t="inlineStr">
+        <is>
+          <t>META: total_input_cost (ro), total_units_produced, overhead_per_unit (ro), cost_per_unit (ro) = (Total Input / Units) + Per-Unit Overheads.</t>
+        </is>
+      </c>
       <c r="P382" s="8" t="inlineStr"/>
-      <c r="Q382" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q382" s="7" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" s="7" t="inlineStr">
@@ -29021,18 +29029,18 @@
           <t>Trace: Frameworks / Unit Pricing · retail-margin leg untested</t>
         </is>
       </c>
-      <c r="N383" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O383" s="7" t="inlineStr"/>
+      <c r="N383" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O383" s="7" t="inlineStr">
+        <is>
+          <t>META: cb_competitor_avg + cb_position -&gt; cb_selling_price (ro) + cb_retail_price (ro) for both existing(_off) and optimized(_on) - competitor + retail-margin legs present.</t>
+        </is>
+      </c>
       <c r="P383" s="8" t="inlineStr"/>
-      <c r="Q383" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q383" s="7" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" s="7" t="inlineStr">
@@ -29401,18 +29409,18 @@
           <t>Trace: Frameworks / Unit Pricing · rule in neither BRD nor tests</t>
         </is>
       </c>
-      <c r="N388" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O388" s="7" t="inlineStr"/>
+      <c r="N388" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O388" s="7" t="inlineStr">
+        <is>
+          <t>META: no at-least-one-row / block-delete-last enforcement. Note confirms the rule is in neither BRD nor wireframe - not a build defect.</t>
+        </is>
+      </c>
       <c r="P388" s="8" t="inlineStr"/>
-      <c r="Q388" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q388" s="7" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" s="7" t="inlineStr">
@@ -29553,18 +29561,18 @@
           <t>Trace: Frameworks / Schemes &amp; Funding · SCH-001 names only CGTMSE</t>
         </is>
       </c>
-      <c r="N390" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O390" s="7" t="inlineStr"/>
+      <c r="N390" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O390" s="7" t="inlineStr">
+        <is>
+          <t>META: scheme_name[L]&gt;DF Funding Scheme Master, master count 23 (&gt;= 19 + Other). NOTE: earlier S15 finding 3/19 schemes is now resolved (23 seeded).</t>
+        </is>
+      </c>
       <c r="P390" s="8" t="inlineStr"/>
-      <c r="Q390" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q390" s="7" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" s="7" t="inlineStr">
@@ -29857,18 +29865,18 @@
           <t>Trace: Frameworks / Schemes &amp; Funding · BRD lists a different set (adds Follow-up/Interview; omits Site Visit/Phone Call/Mentoring) · BRD reconcile pending</t>
         </is>
       </c>
-      <c r="N394" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O394" s="7" t="inlineStr"/>
+      <c r="N394" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O394" s="7" t="inlineStr">
+        <is>
+          <t>META: log uses shared Direct Log Book Child visit_type (3 generic), not the 7-type mentoring funding list. BRD reconcile pending.</t>
+        </is>
+      </c>
       <c r="P394" s="8" t="inlineStr"/>
-      <c r="Q394" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q394" s="7" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" s="7" t="inlineStr">
@@ -31613,18 +31621,18 @@
           <t>Trace: Frameworks / Raw Material · confirm BRD lists resource option values</t>
         </is>
       </c>
-      <c r="N417" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O417" s="7" t="inlineStr"/>
+      <c r="N417" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O417" s="7" t="inlineStr">
+        <is>
+          <t>META: RM Child procurement_source (7), availability (3), procurement_frequency (4); RM Alternate Source new_source_type (8), Alternate Material reason_for_change (6) - resource/source lists present.</t>
+        </is>
+      </c>
       <c r="P417" s="8" t="inlineStr"/>
-      <c r="Q417" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q417" s="7" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" s="7" t="inlineStr">
@@ -32609,18 +32617,18 @@
           <t>Trace: Frameworks / Raw Material · confirm 'Completed only' averaging in BRD</t>
         </is>
       </c>
-      <c r="N430" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O430" s="7" t="inlineStr"/>
+      <c r="N430" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O430" s="7" t="inlineStr">
+        <is>
+          <t>META: RM Alternate Source new_price_per_unit, old_price_per_unit (ro), expected_saving_per_unit (ro), implementation_status incl. Completed - Cost Before/After + Saving present.</t>
+        </is>
+      </c>
       <c r="P430" s="8" t="inlineStr"/>
-      <c r="Q430" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q430" s="7" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" s="7" t="inlineStr">
@@ -32685,18 +32693,18 @@
           <t>Trace: Frameworks / Raw Material · external spec source — confirm fields landed in BRD</t>
         </is>
       </c>
-      <c r="N431" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O431" s="7" t="inlineStr"/>
+      <c r="N431" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O431" s="7" t="inlineStr">
+        <is>
+          <t>META: RM Child amount_per_batch (ro), raw_material_qty_per_unit (ro), raw_material_cost_per_unit (ro), transport_cost_per_unit (ro), total_rm_cost_per_unit (ro) - external-sheet cost-calc fields landed.</t>
+        </is>
+      </c>
       <c r="P431" s="8" t="inlineStr"/>
-      <c r="Q431" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q431" s="7" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" s="7" t="inlineStr">
@@ -34373,18 +34381,18 @@
           <t>Trace: Frameworks / Human Resource · sets GoM threshold</t>
         </is>
       </c>
-      <c r="N453" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O453" s="7" t="inlineStr"/>
+      <c r="N453" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O453" s="7" t="inlineStr">
+        <is>
+          <t>META: Workforce skill_level {Unskilled|Semi-skilled|Skilled|Highly Skilled} - confirmed.</t>
+        </is>
+      </c>
       <c r="P453" s="8" t="inlineStr"/>
-      <c r="Q453" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q453" s="7" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" s="7" t="inlineStr">
@@ -34989,18 +34997,18 @@
           <t>Trace: Frameworks / Human Resource · test fires a generic warning; per-skill thresholds not tested</t>
         </is>
       </c>
-      <c r="N461" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O461" s="7" t="inlineStr"/>
+      <c r="N461" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O461" s="7" t="inlineStr">
+        <is>
+          <t>META: Workforce gom_minimum_wage (ro) + gom_compliant (check) - per-skill GoM threshold computed (Unskilled 360 / Semi 410 / Skilled 480 / Highly higher).</t>
+        </is>
+      </c>
       <c r="P461" s="8" t="inlineStr"/>
-      <c r="Q461" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q461" s="7" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" s="7" t="inlineStr">
@@ -35521,18 +35529,18 @@
           <t>Trace: Frameworks / Human Resource · external spec source — confirm fields landed in BRD</t>
         </is>
       </c>
-      <c r="N468" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O468" s="7" t="inlineStr"/>
+      <c r="N468" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O468" s="7" t="inlineStr">
+        <is>
+          <t>META: Workforce worker_category, employment_nature, no_of_male/female, wage_type, monthly_labour_cost (ro) - external-sheet fields landed.</t>
+        </is>
+      </c>
       <c r="P468" s="8" t="inlineStr"/>
-      <c r="Q468" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q468" s="7" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" s="7" t="inlineStr">
@@ -38645,18 +38653,18 @@
           <t>Trace: Frameworks / Product Prototyping · BRD references master generically, not re-listed</t>
         </is>
       </c>
-      <c r="N509" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O509" s="7" t="inlineStr"/>
+      <c r="N509" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O509" s="7" t="inlineStr">
+        <is>
+          <t>META: Prototyping Product product[L]&gt;Product.</t>
+        </is>
+      </c>
       <c r="P509" s="8" t="inlineStr"/>
-      <c r="Q509" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q509" s="7" t="inlineStr"/>
     </row>
     <row r="510">
       <c r="A510" s="7" t="inlineStr">
@@ -38721,18 +38729,18 @@
           <t>Trace: Frameworks / Product Prototyping</t>
         </is>
       </c>
-      <c r="N510" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O510" s="7" t="inlineStr"/>
+      <c r="N510" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O510" s="7" t="inlineStr">
+        <is>
+          <t>META: implementation_status {Ideating|Iteration|Pilot Implemented|Scale Implementation} - exact match.</t>
+        </is>
+      </c>
       <c r="P510" s="8" t="inlineStr"/>
-      <c r="Q510" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q510" s="7" t="inlineStr"/>
     </row>
     <row r="511">
       <c r="A511" s="7" t="inlineStr">
@@ -38797,18 +38805,18 @@
           <t>Trace: Frameworks / Product Prototyping · not documented in Prototyping BRD</t>
         </is>
       </c>
-      <c r="N511" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O511" s="7" t="inlineStr"/>
+      <c r="N511" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O511" s="7" t="inlineStr">
+        <is>
+          <t>META: Resources Category/Type not in captured PP meta; Task Log -&gt; DF Module Step Master (per-PP 17 not isolated).</t>
+        </is>
+      </c>
       <c r="P511" s="8" t="inlineStr"/>
-      <c r="Q511" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q511" s="7" t="inlineStr"/>
     </row>
     <row r="512">
       <c r="A512" s="7" t="inlineStr">
@@ -38873,18 +38881,18 @@
           <t>Trace: Frameworks / Product Prototyping</t>
         </is>
       </c>
-      <c r="N512" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O512" s="7" t="inlineStr"/>
+      <c r="N512" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O512" s="7" t="inlineStr">
+        <is>
+          <t>META: Resources Category/Type not in captured PP meta; Task Log -&gt; DF Module Step Master (per-PP 17 not isolated).</t>
+        </is>
+      </c>
       <c r="P512" s="8" t="inlineStr"/>
-      <c r="Q512" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q512" s="7" t="inlineStr"/>
     </row>
     <row r="513">
       <c r="A513" s="7" t="inlineStr">
@@ -38949,18 +38957,18 @@
           <t>Trace: Frameworks / Product Prototyping</t>
         </is>
       </c>
-      <c r="N513" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O513" s="7" t="inlineStr"/>
+      <c r="N513" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O513" s="7" t="inlineStr">
+        <is>
+          <t>META: prototyping_type {Packaging|Product}; packing_type depends_on Packaging, business_basket depends_on Product - Type-Name switch by driver confirmed.</t>
+        </is>
+      </c>
       <c r="P513" s="8" t="inlineStr"/>
-      <c r="Q513" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q513" s="7" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" s="7" t="inlineStr">
@@ -39025,18 +39033,18 @@
           <t>Trace: Frameworks / Product Prototyping</t>
         </is>
       </c>
-      <c r="N514" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O514" s="7" t="inlineStr"/>
+      <c r="N514" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O514" s="7" t="inlineStr">
+        <is>
+          <t>META: Iteration child + Product child support Total/Packaging/Product counts + Avg Iterations rollups (computed).</t>
+        </is>
+      </c>
       <c r="P514" s="8" t="inlineStr"/>
-      <c r="Q514" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q514" s="7" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" s="7" t="inlineStr">
@@ -39489,16 +39497,24 @@
           <t>Trace: Frameworks / Product Testing · only 2-date Existing chain tested; live finding: no validation fires</t>
         </is>
       </c>
-      <c r="N520" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O520" s="7" t="inlineStr"/>
-      <c r="P520" s="8" t="inlineStr"/>
+      <c r="N520" s="15" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O520" s="7" t="inlineStr">
+        <is>
+          <t>META + live: no Office&lt;=Lab&lt;=Result 3-date-chain enforcement (no validation on date fields). Matches live finding: no validation fires. NOTE: Product Testing Master is also EMPTY (0 rows) - test_required picker unseeded.</t>
+        </is>
+      </c>
+      <c r="P520" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
       <c r="Q520" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Date-chain not enforced + master unseeded.</t>
         </is>
       </c>
     </row>
@@ -39565,16 +39581,24 @@
           <t>Trace: Frameworks / Product Testing · F-COND-007 checks reveal only, not the mandatory rule</t>
         </is>
       </c>
-      <c r="N521" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O521" s="7" t="inlineStr"/>
-      <c r="P521" s="8" t="inlineStr"/>
+      <c r="N521" s="15" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O521" s="7" t="inlineStr">
+        <is>
+          <t>META: consent_letter_signed is a checkbox; no reqd reason field gated on it. Matches note: reveal only, not mandatory.</t>
+        </is>
+      </c>
+      <c r="P521" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="Q521" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Consent-reason not mandatory.</t>
         </is>
       </c>
     </row>
@@ -41140,18 +41164,18 @@
           <t>Trace: Frameworks / Business Registration · TC says wrong group name 'Statutory'</t>
         </is>
       </c>
-      <c r="N541" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O541" s="7" t="inlineStr"/>
+      <c r="N541" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O541" s="7" t="inlineStr">
+        <is>
+          <t>META: name_of_registration[L]&gt;Registration Master. NOTE: Registration Master has 12 seeded rows (test claims 28 in 5 groups + Other) - master-seed/count drift.</t>
+        </is>
+      </c>
       <c r="P541" s="8" t="inlineStr"/>
-      <c r="Q541" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q541" s="7" t="inlineStr"/>
     </row>
     <row r="542">
       <c r="A542" s="7" t="inlineStr">
@@ -41748,18 +41772,18 @@
           <t>Trace: Frameworks / Business Registration · BRD lists generic ACTIVITY_TYPES, not the 12 BR_TASKS actually rendered · BRD reconcile pending</t>
         </is>
       </c>
-      <c r="N549" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O549" s="7" t="inlineStr"/>
+      <c r="N549" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O549" s="7" t="inlineStr">
+        <is>
+          <t>META: Task Log -&gt; DF Module Step Master (355 across modules); per-BR subset (12) is a master filter, not separately counted.</t>
+        </is>
+      </c>
       <c r="P549" s="8" t="inlineStr"/>
-      <c r="Q549" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q549" s="7" t="inlineStr"/>
     </row>
     <row r="550">
       <c r="A550" s="7" t="inlineStr">
@@ -41900,16 +41924,24 @@
           <t>Trace: Frameworks / Business Registration · BRD-added; wireframe JS does not enforce</t>
         </is>
       </c>
-      <c r="N551" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O551" s="7" t="inlineStr"/>
-      <c r="P551" s="8" t="inlineStr"/>
+      <c r="N551" s="15" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O551" s="7" t="inlineStr">
+        <is>
+          <t>META: no Issued&lt;=today / Valid Till&gt;Issued enforcement (no reqd/validation on date fields). Matches note: BRD-added rule, wireframe JS does not enforce.</t>
+        </is>
+      </c>
+      <c r="P551" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="Q551" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Date-order validation not enforced.</t>
         </is>
       </c>
     </row>
@@ -42204,18 +42236,18 @@
           <t>Trace: Frameworks / Business Registration · core mechanic untested</t>
         </is>
       </c>
-      <c r="N555" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O555" s="7" t="inlineStr"/>
+      <c r="N555" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O555" s="7" t="inlineStr">
+        <is>
+          <t>META: registration_existing + registration_table (dual) + intervention_need + intervention_type + required_phase {New Registration|Renewal} - bridge structure confirmed.</t>
+        </is>
+      </c>
       <c r="P555" s="8" t="inlineStr"/>
-      <c r="Q555" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q555" s="7" t="inlineStr"/>
     </row>
     <row r="556">
       <c r="A556" s="7" t="inlineStr">
@@ -42280,18 +42312,18 @@
           <t>Trace: Frameworks / Business Registration · NT-004 is a 60/30/7-day notify, different rule</t>
         </is>
       </c>
-      <c r="N556" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O556" s="7" t="inlineStr"/>
+      <c r="N556" s="16" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O556" s="7" t="inlineStr">
+        <is>
+          <t>90-day amber / expired red highlighting is a date-driven UI calc; needs visual QA.</t>
+        </is>
+      </c>
       <c r="P556" s="8" t="inlineStr"/>
-      <c r="Q556" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q556" s="7" t="inlineStr"/>
     </row>
     <row r="557">
       <c r="A557" s="7" t="inlineStr">
@@ -42432,18 +42464,18 @@
           <t>Trace: Frameworks / Product Compliance · PC-001 adds FSSAI only</t>
         </is>
       </c>
-      <c r="N558" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O558" s="7" t="inlineStr"/>
+      <c r="N558" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O558" s="7" t="inlineStr">
+        <is>
+          <t>META: compliance certs draw from Registration Master (12 seeded). NOTE: build uses one Registration Master, not a separate 22-value Certification Master in 6 groups; option set/count differs from spec.</t>
+        </is>
+      </c>
       <c r="P558" s="8" t="inlineStr"/>
-      <c r="Q558" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q558" s="7" t="inlineStr"/>
     </row>
     <row r="559">
       <c r="A559" s="7" t="inlineStr">
@@ -42508,18 +42540,18 @@
           <t>Trace: Frameworks / Product Compliance · BRD invented this field — NOT in the wireframe · BRD reconcile pending</t>
         </is>
       </c>
-      <c r="N559" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O559" s="7" t="inlineStr"/>
+      <c r="N559" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O559" s="7" t="inlineStr">
+        <is>
+          <t>META: DF Product Compliance has product_name[L]&gt;Product on the parent - the Applicable Product field exists in build.</t>
+        </is>
+      </c>
       <c r="P559" s="8" t="inlineStr"/>
-      <c r="Q559" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q559" s="7" t="inlineStr"/>
     </row>
     <row r="560">
       <c r="A560" s="7" t="inlineStr">
@@ -42584,18 +42616,18 @@
           <t>Trace: Frameworks / Product Compliance</t>
         </is>
       </c>
-      <c r="N560" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O560" s="7" t="inlineStr"/>
+      <c r="N560" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O560" s="7" t="inlineStr">
+        <is>
+          <t>META: Registration Child phase {Existing|Required}, status (5), govt_certified {Yes|No}, intervention_type {Renewal|Reapply} - all present.</t>
+        </is>
+      </c>
       <c r="P560" s="8" t="inlineStr"/>
-      <c r="Q560" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q560" s="7" t="inlineStr"/>
     </row>
     <row r="561">
       <c r="A561" s="7" t="inlineStr">
@@ -42660,18 +42692,18 @@
           <t>Trace: Frameworks / Product Compliance</t>
         </is>
       </c>
-      <c r="N561" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O561" s="7" t="inlineStr"/>
+      <c r="N561" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O561" s="7" t="inlineStr">
+        <is>
+          <t>META: Resources Category/Type table not in captured PC meta; Task Log task_name&gt;DF Module Step Master (355 steps, per-framework 12 not isolated).</t>
+        </is>
+      </c>
       <c r="P561" s="8" t="inlineStr"/>
-      <c r="Q561" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q561" s="7" t="inlineStr"/>
     </row>
     <row r="562">
       <c r="A562" s="7" t="inlineStr">
@@ -42736,18 +42768,18 @@
           <t>Trace: Frameworks / Product Compliance · BRD Task Log shows Status/Owner/Due cols the wireframe lacks; PC_TASKS not enumerated · BRD reconcile pending</t>
         </is>
       </c>
-      <c r="N562" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O562" s="7" t="inlineStr"/>
+      <c r="N562" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O562" s="7" t="inlineStr">
+        <is>
+          <t>META: Resources Category/Type table not in captured PC meta; Task Log task_name&gt;DF Module Step Master (355 steps, per-framework 12 not isolated).</t>
+        </is>
+      </c>
       <c r="P562" s="8" t="inlineStr"/>
-      <c r="Q562" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q562" s="7" t="inlineStr"/>
     </row>
     <row r="563">
       <c r="A563" s="7" t="inlineStr">
@@ -42812,18 +42844,18 @@
           <t>Trace: Frameworks / Product Compliance · date rules BRD-only</t>
         </is>
       </c>
-      <c r="N563" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O563" s="7" t="inlineStr"/>
+      <c r="N563" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O563" s="7" t="inlineStr">
+        <is>
+          <t>META: name_of_registration reqd; status depends on Required phase. NOTE: cert-uniqueness + Issued&lt;=today / Valid Till date-order not hard-enforced.</t>
+        </is>
+      </c>
       <c r="P563" s="8" t="inlineStr"/>
-      <c r="Q563" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q563" s="7" t="inlineStr"/>
     </row>
     <row r="564">
       <c r="A564" s="7" t="inlineStr">
@@ -42888,18 +42920,18 @@
           <t>Trace: Frameworks / Product Compliance</t>
         </is>
       </c>
-      <c r="N564" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O564" s="7" t="inlineStr"/>
+      <c r="N564" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O564" s="7" t="inlineStr">
+        <is>
+          <t>META: lifetime_validity, intervention_need, intervention_type checks/selects present to drive the Lifetime-hides-Valid-Till and Intervention-reveals-Type toggles.</t>
+        </is>
+      </c>
       <c r="P564" s="8" t="inlineStr"/>
-      <c r="Q564" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q564" s="7" t="inlineStr"/>
     </row>
     <row r="565">
       <c r="A565" s="7" t="inlineStr">
@@ -42964,18 +42996,18 @@
           <t>Trace: Frameworks / Product Compliance</t>
         </is>
       </c>
-      <c r="N565" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O565" s="7" t="inlineStr"/>
+      <c r="N565" s="16" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O565" s="7" t="inlineStr">
+        <is>
+          <t>Expiring-Soon chip + 90-day amber / expired red highlighting + Intervention Rate are date-driven UI calcs; need visual QA.</t>
+        </is>
+      </c>
       <c r="P565" s="8" t="inlineStr"/>
-      <c r="Q565" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q565" s="7" t="inlineStr"/>
     </row>
     <row r="566">
       <c r="A566" s="7" t="inlineStr">
@@ -43040,18 +43072,18 @@
           <t>Trace: Frameworks / Product Compliance</t>
         </is>
       </c>
-      <c r="N566" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O566" s="7" t="inlineStr"/>
+      <c r="N566" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O566" s="7" t="inlineStr">
+        <is>
+          <t>META: dual registration_existing + registration_table children = the bridge / two-way sync structure (same engine as Business Reg).</t>
+        </is>
+      </c>
       <c r="P566" s="8" t="inlineStr"/>
-      <c r="Q566" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q566" s="7" t="inlineStr"/>
     </row>
     <row r="567">
       <c r="A567" s="7" t="inlineStr">
@@ -43116,18 +43148,18 @@
           <t>Trace: Frameworks / Product Compliance · only 60/30/7-day notify (NT-004) exists</t>
         </is>
       </c>
-      <c r="N567" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O567" s="7" t="inlineStr"/>
+      <c r="N567" s="16" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O567" s="7" t="inlineStr">
+        <is>
+          <t>Expiring-Soon chip + 90-day amber / expired red highlighting + Intervention Rate are date-driven UI calcs; need visual QA.</t>
+        </is>
+      </c>
       <c r="P567" s="8" t="inlineStr"/>
-      <c r="Q567" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q567" s="7" t="inlineStr"/>
     </row>
     <row r="568">
       <c r="A568" s="7" t="inlineStr">
@@ -44568,18 +44600,18 @@
           <t>Trace: Frameworks / Packaging · sealing entirely untested</t>
         </is>
       </c>
-      <c r="N586" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O586" s="7" t="inlineStr"/>
+      <c r="N586" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O586" s="7" t="inlineStr">
+        <is>
+          <t>META: Packaging Material Master has induction_sealing / band_sealing / bottleneck_sealing / bottle_sealing_machine_ropp / bottle_sealing_machine_cap = 5 sealing checkboxes.</t>
+        </is>
+      </c>
       <c r="P586" s="8" t="inlineStr"/>
-      <c r="Q586" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q586" s="7" t="inlineStr"/>
     </row>
     <row r="587">
       <c r="A587" s="7" t="inlineStr">
@@ -44796,18 +44828,18 @@
           <t>Trace: Frameworks / Packaging · BRD omits Print Vendor / Sustainability Reference; Type list missing</t>
         </is>
       </c>
-      <c r="N589" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O589" s="7" t="inlineStr"/>
+      <c r="N589" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O589" s="7" t="inlineStr">
+        <is>
+          <t>META: Resources Category/Type not in captured Packaging meta; Log Book uses shared activity_type 7-list (build), not packaging-specific list.</t>
+        </is>
+      </c>
       <c r="P589" s="8" t="inlineStr"/>
-      <c r="Q589" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q589" s="7" t="inlineStr"/>
     </row>
     <row r="590">
       <c r="A590" s="7" t="inlineStr">
@@ -44872,18 +44904,18 @@
           <t>Trace: Frameworks / Packaging · BRD set shorter (omits Print Trial, Quality Check)</t>
         </is>
       </c>
-      <c r="N590" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O590" s="7" t="inlineStr"/>
+      <c r="N590" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O590" s="7" t="inlineStr">
+        <is>
+          <t>META: Resources Category/Type not in captured Packaging meta; Log Book uses shared activity_type 7-list (build), not packaging-specific list.</t>
+        </is>
+      </c>
       <c r="P590" s="8" t="inlineStr"/>
-      <c r="Q590" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q590" s="7" t="inlineStr"/>
     </row>
     <row r="591">
       <c r="A591" s="7" t="inlineStr">
@@ -45024,16 +45056,24 @@
           <t>Trace: Frameworks / Packaging · BRD-only; wireframe does not enforce</t>
         </is>
       </c>
-      <c r="N592" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O592" s="7" t="inlineStr"/>
-      <c r="P592" s="8" t="inlineStr"/>
+      <c r="N592" s="15" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O592" s="7" t="inlineStr">
+        <is>
+          <t>META: no cross-block variant-uniqueness enforcement. Matches note: BRD-only, wireframe does not enforce.</t>
+        </is>
+      </c>
+      <c r="P592" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="Q592" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Variant-not-twice not enforced.</t>
         </is>
       </c>
     </row>
@@ -45252,18 +45292,18 @@
           <t>Trace: Frameworks / Packaging · PKG-001 sums monthly qty only; grand-total feed untested</t>
         </is>
       </c>
-      <c r="N595" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O595" s="7" t="inlineStr"/>
+      <c r="N595" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O595" s="7" t="inlineStr">
+        <is>
+          <t>META: Packaging Monthly Data quantity_ordered x price_per_unit -&gt; total_order_cost (ro); annual per type + grand total computed.</t>
+        </is>
+      </c>
       <c r="P595" s="8" t="inlineStr"/>
-      <c r="Q595" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q595" s="7" t="inlineStr"/>
     </row>
     <row r="596">
       <c r="A596" s="7" t="inlineStr">
@@ -45404,18 +45444,18 @@
           <t>Trace: Frameworks / Packaging · live finding: saving_per_unit returned 0 (PKG-001); confirm formula/trigger · Was stale — realigned</t>
         </is>
       </c>
-      <c r="N597" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O597" s="7" t="inlineStr"/>
+      <c r="N597" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O597" s="7" t="inlineStr">
+        <is>
+          <t>META: Packaging Child new_price_per_unit + saving_per_unit (ro) = Existing - New.</t>
+        </is>
+      </c>
       <c r="P597" s="8" t="inlineStr"/>
-      <c r="Q597" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q597" s="7" t="inlineStr"/>
     </row>
     <row r="598">
       <c r="A598" s="7" t="inlineStr">
@@ -45708,18 +45748,18 @@
           <t>Trace: Frameworks / Logistic Packing · BRD says 'Completed' vs wireframe 'Implemented'; omits 'Replace Existing' · BRD reconcile pending</t>
         </is>
       </c>
-      <c r="N601" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O601" s="7" t="inlineStr"/>
+      <c r="N601" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O601" s="7" t="inlineStr">
+        <is>
+          <t>META: Logistic Packing Item implementation_status {Pending|In Progress|Implemented|Cancelled}; item_kind {Existing|Intervention|New}. NOTE: build uses Implemented (not Completed) and item_kind covers Replace via Intervention.</t>
+        </is>
+      </c>
       <c r="P601" s="8" t="inlineStr"/>
-      <c r="Q601" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q601" s="7" t="inlineStr"/>
     </row>
     <row r="602">
       <c r="A602" s="7" t="inlineStr">
@@ -45784,18 +45824,18 @@
           <t>Trace: Frameworks / Logistic Packing · BRD Category set differs; Log Book omits several activities · BRD reconcile pending</t>
         </is>
       </c>
-      <c r="N602" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O602" s="7" t="inlineStr"/>
+      <c r="N602" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O602" s="7" t="inlineStr">
+        <is>
+          <t>META: Resources Category not in captured meta; Log Book shared activity_type list.</t>
+        </is>
+      </c>
       <c r="P602" s="8" t="inlineStr"/>
-      <c r="Q602" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q602" s="7" t="inlineStr"/>
     </row>
     <row r="603">
       <c r="A603" s="7" t="inlineStr">
@@ -46012,18 +46052,18 @@
           <t>Trace: Frameworks / Logistic Packing · LPACK-001 expects a 3-layer transit cost, not the monthly grid</t>
         </is>
       </c>
-      <c r="N605" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O605" s="7" t="inlineStr"/>
+      <c r="N605" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O605" s="7" t="inlineStr">
+        <is>
+          <t>META: Logistic Packing Monthly Shipment quantity + Item price_per_unit -&gt; month/annual/grand totals (calc verified live earlier after master seed).</t>
+        </is>
+      </c>
       <c r="P605" s="8" t="inlineStr"/>
-      <c r="Q605" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q605" s="7" t="inlineStr"/>
     </row>
     <row r="606">
       <c r="A606" s="7" t="inlineStr">
@@ -46316,18 +46356,18 @@
           <t>Trace: Frameworks / Logistic Service · only Weekly x4 tested; fractional x0.5 untested</t>
         </is>
       </c>
-      <c r="N609" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O609" s="7" t="inlineStr"/>
+      <c r="N609" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O609" s="7" t="inlineStr">
+        <is>
+          <t>META: frequency_per_month is a numeric Float (multiplier applied in calc), not a fixed Daily x30/Weekly x4 select. Fractional values supported by the float.</t>
+        </is>
+      </c>
       <c r="P609" s="8" t="inlineStr"/>
-      <c r="Q609" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q609" s="7" t="inlineStr"/>
     </row>
     <row r="610">
       <c r="A610" s="7" t="inlineStr">
@@ -46468,18 +46508,18 @@
           <t>Trace: Frameworks / Logistic Service · BRD doesn't enumerate Courier/E-Commerce items</t>
         </is>
       </c>
-      <c r="N611" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O611" s="7" t="inlineStr"/>
+      <c r="N611" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O611" s="7" t="inlineStr">
+        <is>
+          <t>META: Available Services checkbox matrix (4 families ~21 items) not in captured LS meta - LS build is route/leg/RM/dispatch centric.</t>
+        </is>
+      </c>
       <c r="P611" s="8" t="inlineStr"/>
-      <c r="Q611" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q611" s="7" t="inlineStr"/>
     </row>
     <row r="612">
       <c r="A612" s="7" t="inlineStr">
@@ -46544,18 +46584,18 @@
           <t>Trace: Frameworks / Logistic Service · BRD says 'Completed' vs wireframe 'Implemented' · BRD reconcile pending</t>
         </is>
       </c>
-      <c r="N612" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O612" s="7" t="inlineStr"/>
+      <c r="N612" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O612" s="7" t="inlineStr">
+        <is>
+          <t>META: Route Child implementation_status {Pending|In Progress|Implemented|Cancelled} - build uses Implemented (BRD says Completed).</t>
+        </is>
+      </c>
       <c r="P612" s="8" t="inlineStr"/>
-      <c r="Q612" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q612" s="7" t="inlineStr"/>
     </row>
     <row r="613">
       <c r="A613" s="7" t="inlineStr">
@@ -46620,18 +46660,18 @@
           <t>Trace: Frameworks / Logistic Service · Log Book Activity values not in BRD</t>
         </is>
       </c>
-      <c r="N613" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O613" s="7" t="inlineStr"/>
+      <c r="N613" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O613" s="7" t="inlineStr">
+        <is>
+          <t>META: Resources Category / Log Book Activity not enumerated in captured LS meta (shared log child).</t>
+        </is>
+      </c>
       <c r="P613" s="8" t="inlineStr"/>
-      <c r="Q613" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q613" s="7" t="inlineStr"/>
     </row>
     <row r="614">
       <c r="A614" s="7" t="inlineStr">
@@ -46848,18 +46888,18 @@
           <t>Trace: Frameworks / Logistic Service · LSVC-001 expects 60,000; F-CALC-027 stops at monthly</t>
         </is>
       </c>
-      <c r="N616" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O616" s="7" t="inlineStr"/>
+      <c r="N616" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O616" s="7" t="inlineStr">
+        <is>
+          <t>META: Route Child monthly_cost (ro) + annual_cost (ro) = Monthly x 12.</t>
+        </is>
+      </c>
       <c r="P616" s="8" t="inlineStr"/>
-      <c r="Q616" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q616" s="7" t="inlineStr"/>
     </row>
     <row r="617">
       <c r="A617" s="7" t="inlineStr">
@@ -47000,18 +47040,18 @@
           <t>Trace: Frameworks / Market Research</t>
         </is>
       </c>
-      <c r="N618" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O618" s="7" t="inlineStr"/>
+      <c r="N618" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O618" s="7" t="inlineStr">
+        <is>
+          <t>META: product[L]&gt;Product confirmed. NOTE: Key Exporting Countries / Key States / Key Selling Locations fields not located in captured MR child meta.</t>
+        </is>
+      </c>
       <c r="P618" s="8" t="inlineStr"/>
-      <c r="Q618" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q618" s="7" t="inlineStr"/>
     </row>
     <row r="619">
       <c r="A619" s="7" t="inlineStr">
@@ -47076,18 +47116,18 @@
           <t>Trace: Frameworks / Market Research</t>
         </is>
       </c>
-      <c r="N619" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O619" s="7" t="inlineStr"/>
+      <c r="N619" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O619" s="7" t="inlineStr">
+        <is>
+          <t>META: shelf_placement = 6, origin[L]&gt;State, packing[L]&gt;Packaging Type confirmed. NOTE: build outlet_type = 9 options (test says 12) and platforms = 9 (test says 10) - option-count drift vs spec.</t>
+        </is>
+      </c>
       <c r="P619" s="8" t="inlineStr"/>
-      <c r="Q619" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q619" s="7" t="inlineStr"/>
     </row>
     <row r="620">
       <c r="A620" s="7" t="inlineStr">
@@ -47152,18 +47192,18 @@
           <t>Trace: Frameworks / Market Research · typo propagated into BRD too</t>
         </is>
       </c>
-      <c r="N620" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O620" s="7" t="inlineStr"/>
+      <c r="N620" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O620" s="7" t="inlineStr">
+        <is>
+          <t>META: district picker wired to District master. NOTE: the Eri Bhoi/Ri Bhoi typo is master-row data - not re-verified by listing District rows this pass.</t>
+        </is>
+      </c>
       <c r="P620" s="8" t="inlineStr"/>
-      <c r="Q620" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q620" s="7" t="inlineStr"/>
     </row>
     <row r="621">
       <c r="A621" s="7" t="inlineStr">
@@ -47228,18 +47268,18 @@
           <t>Trace: Frameworks / Market Research · wireframe/BRD use 7 broad bands; journey doc is fine-grained</t>
         </is>
       </c>
-      <c r="N621" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O621" s="7" t="inlineStr"/>
+      <c r="N621" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O621" s="7" t="inlineStr">
+        <is>
+          <t>META: Customer age_group = 7 broad bands (Below 18 / 18-25 / 26-35 / 36-45 / 46-55 / 56-65 / Above 65) - matches BRD (journey 16-band model not built).</t>
+        </is>
+      </c>
       <c r="P621" s="8" t="inlineStr"/>
-      <c r="Q621" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q621" s="7" t="inlineStr"/>
     </row>
     <row r="622">
       <c r="A622" s="7" t="inlineStr">
@@ -47304,18 +47344,18 @@
           <t>Trace: Frameworks / Market Research · wireframe simplified to 9</t>
         </is>
       </c>
-      <c r="N622" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O622" s="7" t="inlineStr"/>
+      <c r="N622" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O622" s="7" t="inlineStr">
+        <is>
+          <t>META: occupation[L]&gt;Occupation, master count 9 - matches wireframe (journey 25-item list not used).</t>
+        </is>
+      </c>
       <c r="P622" s="8" t="inlineStr"/>
-      <c r="Q622" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q622" s="7" t="inlineStr"/>
     </row>
     <row r="623">
       <c r="A623" s="7" t="inlineStr">
@@ -47380,18 +47420,18 @@
           <t>Trace: Frameworks / Market Research</t>
         </is>
       </c>
-      <c r="N623" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O623" s="7" t="inlineStr"/>
+      <c r="N623" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O623" s="7" t="inlineStr">
+        <is>
+          <t>META: Customer gender[L]&gt;Gender, state[L]&gt;State, district[L]&gt;District, block[L]&gt;Block - 4 independent Links (no real cascade), as described.</t>
+        </is>
+      </c>
       <c r="P623" s="8" t="inlineStr"/>
-      <c r="Q623" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q623" s="7" t="inlineStr"/>
     </row>
     <row r="624">
       <c r="A624" s="7" t="inlineStr">
@@ -47456,18 +47496,18 @@
           <t>Trace: Frameworks / Market Research · Resources lists not enumerated in MR BRD</t>
         </is>
       </c>
-      <c r="N624" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O624" s="7" t="inlineStr"/>
+      <c r="N624" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O624" s="7" t="inlineStr">
+        <is>
+          <t>META: Competitor Offline outlet (9) and Competitor Online platform (9) pickers confirmed.</t>
+        </is>
+      </c>
       <c r="P624" s="8" t="inlineStr"/>
-      <c r="Q624" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q624" s="7" t="inlineStr"/>
     </row>
     <row r="625">
       <c r="A625" s="7" t="inlineStr">
@@ -47532,18 +47572,18 @@
           <t>Trace: Frameworks / Market Research · generic F-COND-012, not in section 17</t>
         </is>
       </c>
-      <c r="N625" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O625" s="7" t="inlineStr"/>
+      <c r="N625" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O625" s="7" t="inlineStr">
+        <is>
+          <t>META: Customer purchase_frequency depends_on have_used_product==Yes - skip-logic confirmed.</t>
+        </is>
+      </c>
       <c r="P625" s="8" t="inlineStr"/>
-      <c r="Q625" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q625" s="7" t="inlineStr"/>
     </row>
     <row r="626">
       <c r="A626" s="7" t="inlineStr">
@@ -47608,18 +47648,18 @@
           <t>Trace: Frameworks / Market Research</t>
         </is>
       </c>
-      <c r="N626" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O626" s="7" t="inlineStr"/>
+      <c r="N626" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O626" s="7" t="inlineStr">
+        <is>
+          <t>META: price[C] on offline/online competitor + brand children -&gt; competitor-average + 6 cross-feed averages to Unit Pricing cb_competitor_avg + summary aggregates (calc structure present).</t>
+        </is>
+      </c>
       <c r="P626" s="8" t="inlineStr"/>
-      <c r="Q626" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q626" s="7" t="inlineStr"/>
     </row>
     <row r="627">
       <c r="A627" s="7" t="inlineStr">
@@ -47684,18 +47724,18 @@
           <t>Trace: Frameworks / Market Research · F-FLOW-007 covers Local-offline only</t>
         </is>
       </c>
-      <c r="N627" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O627" s="7" t="inlineStr"/>
+      <c r="N627" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O627" s="7" t="inlineStr">
+        <is>
+          <t>META: price[C] on offline/online competitor + brand children -&gt; competitor-average + 6 cross-feed averages to Unit Pricing cb_competitor_avg + summary aggregates (calc structure present).</t>
+        </is>
+      </c>
       <c r="P627" s="8" t="inlineStr"/>
-      <c r="Q627" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q627" s="7" t="inlineStr"/>
     </row>
     <row r="628">
       <c r="A628" s="7" t="inlineStr">
@@ -47760,18 +47800,18 @@
           <t>Trace: Frameworks / Market Research</t>
         </is>
       </c>
-      <c r="N628" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O628" s="7" t="inlineStr"/>
+      <c r="N628" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O628" s="7" t="inlineStr">
+        <is>
+          <t>META: price[C] on offline/online competitor + brand children -&gt; competitor-average + 6 cross-feed averages to Unit Pricing cb_competitor_avg + summary aggregates (calc structure present).</t>
+        </is>
+      </c>
       <c r="P628" s="8" t="inlineStr"/>
-      <c r="Q628" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q628" s="7" t="inlineStr"/>
     </row>
     <row r="629">
       <c r="A629" s="7" t="inlineStr">
@@ -47836,18 +47876,18 @@
           <t>Trace: Frameworks / Market Research · negative-price guard BRD-added</t>
         </is>
       </c>
-      <c r="N629" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O629" s="7" t="inlineStr"/>
+      <c r="N629" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O629" s="7" t="inlineStr">
+        <is>
+          <t>META: Competitor scope is reqd. NOTE: parent product and the Price&gt;=0 guard are not hard-enforced (no reqd / no min) in build meta.</t>
+        </is>
+      </c>
       <c r="P629" s="8" t="inlineStr"/>
-      <c r="Q629" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q629" s="7" t="inlineStr"/>
     </row>
     <row r="630">
       <c r="A630" s="7" t="inlineStr">
@@ -47988,18 +48028,18 @@
           <t>Trace: Frameworks / Customer Analysis · CA-001 picks a couple only</t>
         </is>
       </c>
-      <c r="N631" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O631" s="7" t="inlineStr"/>
+      <c r="N631" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O631" s="7" t="inlineStr">
+        <is>
+          <t>META: CA modelled as Product Block child (phase, product_name, market_readiness 4-opt, intervention_need, implementation_status). NOTE: the full demographic dropdown set (Age/Gender/Family Size/Occupation 25/Income/Education) is not in the captured CA meta - CA build is product-block centric.</t>
+        </is>
+      </c>
       <c r="P631" s="8" t="inlineStr"/>
-      <c r="Q631" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q631" s="7" t="inlineStr"/>
     </row>
     <row r="632">
       <c r="A632" s="7" t="inlineStr">
@@ -48596,18 +48636,18 @@
           <t>Trace: Frameworks / Customer Analysis · generic UI-CHIP-001 only</t>
         </is>
       </c>
-      <c r="N639" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O639" s="7" t="inlineStr"/>
+      <c r="N639" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O639" s="7" t="inlineStr">
+        <is>
+          <t>META: product_name[L]&gt;Product present. NOTE: product-required + no-duplicate-chip are not hard-enforced in build meta.</t>
+        </is>
+      </c>
       <c r="P639" s="8" t="inlineStr"/>
-      <c r="Q639" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q639" s="7" t="inlineStr"/>
     </row>
     <row r="640">
       <c r="A640" s="7" t="inlineStr">
@@ -48672,18 +48712,18 @@
           <t>Trace: Frameworks / Market Linkage</t>
         </is>
       </c>
-      <c r="N640" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O640" s="7" t="inlineStr"/>
+      <c r="N640" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O640" s="7" t="inlineStr">
+        <is>
+          <t>META: channel_type {Online|Offline} confirmed. NOTE: a separate Selling Mode (B2B/B2C/D2C/Exhibition) select was NOT located in the captured ML child meta - field may be absent or relabelled.</t>
+        </is>
+      </c>
       <c r="P640" s="8" t="inlineStr"/>
-      <c r="Q640" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q640" s="7" t="inlineStr"/>
     </row>
     <row r="641">
       <c r="A641" s="7" t="inlineStr">
@@ -48748,18 +48788,18 @@
           <t>Trace: Frameworks / Market Linkage</t>
         </is>
       </c>
-      <c r="N641" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O641" s="7" t="inlineStr"/>
+      <c r="N641" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O641" s="7" t="inlineStr">
+        <is>
+          <t>META: ML Existing/Recommended Channel location[L]&gt;Block; identified_by {Ground Team|Core Team|Entrepreneur}.</t>
+        </is>
+      </c>
       <c r="P641" s="8" t="inlineStr"/>
-      <c r="Q641" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q641" s="7" t="inlineStr"/>
     </row>
     <row r="642">
       <c r="A642" s="7" t="inlineStr">
@@ -48824,18 +48864,18 @@
           <t>Trace: Frameworks / Market Linkage</t>
         </is>
       </c>
-      <c r="N642" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O642" s="7" t="inlineStr"/>
+      <c r="N642" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O642" s="7" t="inlineStr">
+        <is>
+          <t>META: ML Channel Product product[L]&gt;Product, product_sku[L]&gt;Product SKU, implementation_status {Pending|In Progress|Completed|Not Feasible}.</t>
+        </is>
+      </c>
       <c r="P642" s="8" t="inlineStr"/>
-      <c r="Q642" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q642" s="7" t="inlineStr"/>
     </row>
     <row r="643">
       <c r="A643" s="7" t="inlineStr">
@@ -48900,18 +48940,18 @@
           <t>Trace: Frameworks / Market Linkage</t>
         </is>
       </c>
-      <c r="N643" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O643" s="7" t="inlineStr"/>
+      <c r="N643" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O643" s="7" t="inlineStr">
+        <is>
+          <t>META: product_sku is a Link to Product SKU; Product-then-SKU cascade is a link_filter (structure present).</t>
+        </is>
+      </c>
       <c r="P643" s="8" t="inlineStr"/>
-      <c r="Q643" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q643" s="7" t="inlineStr"/>
     </row>
     <row r="644">
       <c r="A644" s="7" t="inlineStr">
@@ -48976,18 +49016,18 @@
           <t>Trace: Frameworks / Market Linkage · F-CALC-022</t>
         </is>
       </c>
-      <c r="N644" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O644" s="7" t="inlineStr"/>
+      <c r="N644" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O644" s="7" t="inlineStr">
+        <is>
+          <t>META: Existing Channel price + avg_units_per_month -&gt; avg_revenue_per_month (ro), annual_revenue (ro), annual_total_revenue (ro). Calc fields present.</t>
+        </is>
+      </c>
       <c r="P644" s="8" t="inlineStr"/>
-      <c r="Q644" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q644" s="7" t="inlineStr"/>
     </row>
     <row r="645">
       <c r="A645" s="7" t="inlineStr">
@@ -49052,18 +49092,18 @@
           <t>Trace: Frameworks / Market Linkage · F-CALC-023; live: Revenue needs a priced Product (ML-001 blocked)</t>
         </is>
       </c>
-      <c r="N645" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O645" s="7" t="inlineStr"/>
+      <c r="N645" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O645" s="7" t="inlineStr">
+        <is>
+          <t>META: Sales Tracker Entry units + selling_price -&gt; revenue (read-only). Month/grand totals computed.</t>
+        </is>
+      </c>
       <c r="P645" s="8" t="inlineStr"/>
-      <c r="Q645" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q645" s="7" t="inlineStr"/>
     </row>
     <row r="646">
       <c r="A646" s="7" t="inlineStr">
@@ -49128,18 +49168,18 @@
           <t>Trace: Frameworks / Market Linkage</t>
         </is>
       </c>
-      <c r="N646" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O646" s="7" t="inlineStr"/>
+      <c r="N646" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O646" s="7" t="inlineStr">
+        <is>
+          <t>META: Recommended Channel status {Pending|In Progress|Completed|Not Feasible} + channel_type Online/Offline support status-chip rollup and online/offline summary aggregates.</t>
+        </is>
+      </c>
       <c r="P646" s="8" t="inlineStr"/>
-      <c r="Q646" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q646" s="7" t="inlineStr"/>
     </row>
     <row r="647">
       <c r="A647" s="7" t="inlineStr">
@@ -49204,18 +49244,18 @@
           <t>Trace: Frameworks / Market Linkage</t>
         </is>
       </c>
-      <c r="N647" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O647" s="7" t="inlineStr"/>
+      <c r="N647" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O647" s="7" t="inlineStr">
+        <is>
+          <t>META: Recommended Channel status {Pending|In Progress|Completed|Not Feasible} + channel_type Online/Offline support status-chip rollup and online/offline summary aggregates.</t>
+        </is>
+      </c>
       <c r="P647" s="8" t="inlineStr"/>
-      <c r="Q647" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q647" s="7" t="inlineStr"/>
     </row>
     <row r="648">
       <c r="A648" s="7" t="inlineStr">
@@ -49812,18 +49852,18 @@
           <t>Trace: Frameworks / Branding Identity · journey change; BRD captures clubbing</t>
         </is>
       </c>
-      <c r="N655" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O655" s="7" t="inlineStr"/>
+      <c r="N655" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O655" s="7" t="inlineStr">
+        <is>
+          <t>META: need_new_brand + need_new_logo + need_new_bizcard each with own designer/drafts/approvals - Brand/Logo/Card clubbed into one framework (3 tracks) confirmed.</t>
+        </is>
+      </c>
       <c r="P655" s="8" t="inlineStr"/>
-      <c r="Q655" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q655" s="7" t="inlineStr"/>
     </row>
     <row r="656">
       <c r="A656" s="7" t="inlineStr">
@@ -49888,18 +49928,18 @@
           <t>Trace: Frameworks / Branding Identity · BRAND-002 tests dual-approve, not the 3 values / Rejected path</t>
         </is>
       </c>
-      <c r="N656" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O656" s="7" t="inlineStr"/>
+      <c r="N656" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O656" s="7" t="inlineStr">
+        <is>
+          <t>META: brand/logo/bizcard _entrepreneur_approval + _core_team_approval each {Approved|Pending|Rejected} - confirmed incl. Rejected.</t>
+        </is>
+      </c>
       <c r="P656" s="8" t="inlineStr"/>
-      <c r="Q656" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q656" s="7" t="inlineStr"/>
     </row>
     <row r="657">
       <c r="A657" s="7" t="inlineStr">
@@ -50040,18 +50080,18 @@
           <t>Trace: Frameworks / Branding Identity · difference from Logo track untested</t>
         </is>
       </c>
-      <c r="N658" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O658" s="7" t="inlineStr"/>
+      <c r="N658" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O658" s="7" t="inlineStr">
+        <is>
+          <t>META: bizcard_assigned_designer is a User Link picker (not a fixed Designer A/B select); no AI-Generated option present - consistent with the no-AI claim.</t>
+        </is>
+      </c>
       <c r="P658" s="8" t="inlineStr"/>
-      <c r="Q658" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q658" s="7" t="inlineStr"/>
     </row>
     <row r="659">
       <c r="A659" s="7" t="inlineStr">
@@ -50116,18 +50156,18 @@
           <t>Trace: Frameworks / Branding Identity · Resources Type list missing from BRD · BRD reconcile pending</t>
         </is>
       </c>
-      <c r="N659" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O659" s="7" t="inlineStr"/>
+      <c r="N659" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O659" s="7" t="inlineStr">
+        <is>
+          <t>META: Resources Category/Type table not in captured Branding meta.</t>
+        </is>
+      </c>
       <c r="P659" s="8" t="inlineStr"/>
-      <c r="Q659" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q659" s="7" t="inlineStr"/>
     </row>
     <row r="660">
       <c r="A660" s="7" t="inlineStr">
@@ -50428,18 +50468,18 @@
           <t>Trace: Frameworks / Branding Identity · BRAND-001 uploads 3 but doesn't test sequential lock</t>
         </is>
       </c>
-      <c r="N663" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O663" s="7" t="inlineStr"/>
+      <c r="N663" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O663" s="7" t="inlineStr">
+        <is>
+          <t>META: Branding Draft Child status {Pending|Under Review|Redo|Approved|Not Approved} present. NOTE: sequential Draft 2/3 lock is row-based UI behaviour.</t>
+        </is>
+      </c>
       <c r="P663" s="8" t="inlineStr"/>
-      <c r="Q663" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q663" s="7" t="inlineStr"/>
     </row>
     <row r="664">
       <c r="A664" s="7" t="inlineStr">
@@ -50580,18 +50620,18 @@
           <t>Trace: Frameworks / Branding Identity · BRAND-002 happy-path only</t>
         </is>
       </c>
-      <c r="N665" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O665" s="7" t="inlineStr"/>
+      <c r="N665" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O665" s="7" t="inlineStr">
+        <is>
+          <t>META: logo/bizcard assigned_designer depends_on need_new_* (reveals, not reqd). NOTE: designer-before-draft / &gt;=1-draft-before-approval not hard-enforced.</t>
+        </is>
+      </c>
       <c r="P665" s="8" t="inlineStr"/>
-      <c r="Q665" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q665" s="7" t="inlineStr"/>
     </row>
     <row r="666">
       <c r="A666" s="7" t="inlineStr">
@@ -51036,18 +51076,18 @@
           <t>Trace: Frameworks / Marketing Brochure · BR-001 picks products, not the Type list</t>
         </is>
       </c>
-      <c r="N671" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O671" s="7" t="inlineStr"/>
+      <c r="N671" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O671" s="7" t="inlineStr">
+        <is>
+          <t>META: brochure_type {Single Product Brochure|Multi-Product Catalogue|Tri-fold Leaflet|Bi-fold Leaflet|Single-page Flyer} = 5 types. NOTE: single-select in build (test says multi-select).</t>
+        </is>
+      </c>
       <c r="P671" s="8" t="inlineStr"/>
-      <c r="Q671" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q671" s="7" t="inlineStr"/>
     </row>
     <row r="672">
       <c r="A672" s="7" t="inlineStr">
@@ -51652,18 +51692,18 @@
           <t>Trace: Frameworks / Marketing Brochure · journey change; price field removed</t>
         </is>
       </c>
-      <c r="N679" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O679" s="7" t="inlineStr"/>
+      <c r="N679" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O679" s="7" t="inlineStr">
+        <is>
+          <t>META: Brochure Product Child length_cm/breadth_cm/height_cm + volume_cm3 (ro) + retail_price (ro) + wholesale_price (ro) + minimum_order_quantity - dims/volume/MOQ/retail+wholesale all present.</t>
+        </is>
+      </c>
       <c r="P679" s="8" t="inlineStr"/>
-      <c r="Q679" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q679" s="7" t="inlineStr"/>
     </row>
     <row r="680">
       <c r="A680" s="7" t="inlineStr">
@@ -52032,18 +52072,18 @@
           <t>Trace: Frameworks / Pitch Deck · BRD lists a DIFFERENT set (Drafting/Review/Mentor Session/Mock Pitch/Investor Meeting) — fix BRD · BRD reconcile pending</t>
         </is>
       </c>
-      <c r="N684" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O684" s="7" t="inlineStr"/>
+      <c r="N684" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O684" s="7" t="inlineStr">
+        <is>
+          <t>META: Pitch Deck log uses shared Direct Log Book Child visit_type {Site Visit|Office Visit|Group Meeting} (3 generic), not the pitch-specific list (Pitch Rehearsal/Investor Meeting). BRD reconcile pending.</t>
+        </is>
+      </c>
       <c r="P684" s="8" t="inlineStr"/>
-      <c r="Q684" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q684" s="7" t="inlineStr"/>
     </row>
     <row r="685">
       <c r="A685" s="7" t="inlineStr">
@@ -52108,18 +52148,18 @@
           <t>Trace: Frameworks / Pitch Deck · 'Blocked' option missing from BRD · BRD reconcile pending</t>
         </is>
       </c>
-      <c r="N685" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O685" s="7" t="inlineStr"/>
+      <c r="N685" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O685" s="7" t="inlineStr">
+        <is>
+          <t>META: DF Pitch Deck implementation_status {Pending|In Progress|Implemented|Not Feasible} - no Blocked option (test/BRD reconcile pending).</t>
+        </is>
+      </c>
       <c r="P685" s="8" t="inlineStr"/>
-      <c r="Q685" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q685" s="7" t="inlineStr"/>
     </row>
     <row r="686">
       <c r="A686" s="7" t="inlineStr">
@@ -52488,18 +52528,18 @@
           <t>Trace: Frameworks / Pitch Deck · PD-001 phrases slide state as Drafted/Reviewed/Final, not fill-based · Was stale — realigned</t>
         </is>
       </c>
-      <c r="N690" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O690" s="7" t="inlineStr"/>
+      <c r="N690" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O690" s="7" t="inlineStr">
+        <is>
+          <t>META: Pitch Deck captured fields are intervention_need + implementation_status + log; slide-completion model realigned per BRD (final-deck, not 11-fill). Slide fields are non-enumerable (text/attach).</t>
+        </is>
+      </c>
       <c r="P690" s="8" t="inlineStr"/>
-      <c r="Q690" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q690" s="7" t="inlineStr"/>
     </row>
     <row r="691">
       <c r="A691" s="7" t="inlineStr">
@@ -52800,18 +52840,18 @@
           <t>Trace: Frameworks / Digital Literacy · DL-001 says '9 platforms' but lists none</t>
         </is>
       </c>
-      <c r="N694" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O694" s="7" t="inlineStr"/>
+      <c r="N694" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O694" s="7" t="inlineStr">
+        <is>
+          <t>META: Skill rows present (existing_level/target_level/intervention_required/implementation_status). NOTE: the Platform/Skill master Link (9 from master) is not in the captured Select/Link slice.</t>
+        </is>
+      </c>
       <c r="P694" s="8" t="inlineStr"/>
-      <c r="Q694" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q694" s="7" t="inlineStr"/>
     </row>
     <row r="695">
       <c r="A695" s="7" t="inlineStr">
@@ -52875,18 +52915,18 @@
           <t>Trace: Frameworks / Digital Literacy · DL-001 says '0-5' scale — wrong · Was stale — realigned</t>
         </is>
       </c>
-      <c r="N695" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O695" s="7" t="inlineStr"/>
+      <c r="N695" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O695" s="7" t="inlineStr">
+        <is>
+          <t>META: existing_level + target_level are Int (1-5 star) - not a 0-5 scale (DL-001 0-5 was stale, now realigned).</t>
+        </is>
+      </c>
       <c r="P695" s="8" t="inlineStr"/>
-      <c r="Q695" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q695" s="7" t="inlineStr"/>
     </row>
     <row r="696">
       <c r="A696" s="7" t="inlineStr">
@@ -52951,18 +52991,18 @@
           <t>Trace: Frameworks / Digital Literacy · DL-001 invents Readiness = avg x 20 = 100% + radar chart — not in spec · Was stale — realigned</t>
         </is>
       </c>
-      <c r="N696" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O696" s="7" t="inlineStr"/>
+      <c r="N696" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O696" s="7" t="inlineStr">
+        <is>
+          <t>META: Average Skill Level = sum of star levels / rated count computed from existing/target Int levels (0 excluded).</t>
+        </is>
+      </c>
       <c r="P696" s="8" t="inlineStr"/>
-      <c r="Q696" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q696" s="7" t="inlineStr"/>
     </row>
     <row r="697">
       <c r="A697" s="7" t="inlineStr">
@@ -53027,18 +53067,18 @@
           <t>Trace: Frameworks / Digital Literacy</t>
         </is>
       </c>
-      <c r="N697" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O697" s="7" t="inlineStr"/>
+      <c r="N697" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O697" s="7" t="inlineStr">
+        <is>
+          <t>META: existing_has_smartphone/laptop/internet (checks) + required_needs_* with status depends_on each need - has-device=No reveals required path.</t>
+        </is>
+      </c>
       <c r="P697" s="8" t="inlineStr"/>
-      <c r="Q697" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q697" s="7" t="inlineStr"/>
     </row>
     <row r="698">
       <c r="A698" s="7" t="inlineStr">
@@ -53103,18 +53143,18 @@
           <t>Trace: Frameworks / Digital Literacy</t>
         </is>
       </c>
-      <c r="N698" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O698" s="7" t="inlineStr"/>
+      <c r="N698" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O698" s="7" t="inlineStr">
+        <is>
+          <t>META: required_smartphone/laptop/internet_status {Pending|In Progress|Completed|Not Feasible} = 4-status per device.</t>
+        </is>
+      </c>
       <c r="P698" s="8" t="inlineStr"/>
-      <c r="Q698" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q698" s="7" t="inlineStr"/>
     </row>
     <row r="699">
       <c r="A699" s="7" t="inlineStr">
@@ -53179,18 +53219,18 @@
           <t>Trace: Frameworks / Digital Literacy</t>
         </is>
       </c>
-      <c r="N699" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O699" s="7" t="inlineStr"/>
+      <c r="N699" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O699" s="7" t="inlineStr">
+        <is>
+          <t>META: dual existing_skills + required_skills children = intervention bridge.</t>
+        </is>
+      </c>
       <c r="P699" s="8" t="inlineStr"/>
-      <c r="Q699" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q699" s="7" t="inlineStr"/>
     </row>
     <row r="700">
       <c r="A700" s="7" t="inlineStr">
@@ -53255,18 +53295,18 @@
           <t>Trace: Frameworks / Digital Literacy</t>
         </is>
       </c>
-      <c r="N700" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O700" s="7" t="inlineStr"/>
+      <c r="N700" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O700" s="7" t="inlineStr">
+        <is>
+          <t>META: existing_level + target_level -&gt; Skill Change = Target - Existing; device gap + summary aggregates computed.</t>
+        </is>
+      </c>
       <c r="P700" s="8" t="inlineStr"/>
-      <c r="Q700" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q700" s="7" t="inlineStr"/>
     </row>
     <row r="701">
       <c r="A701" s="7" t="inlineStr">
@@ -53331,18 +53371,18 @@
           <t>Trace: Frameworks / Digital Literacy</t>
         </is>
       </c>
-      <c r="N701" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O701" s="7" t="inlineStr"/>
+      <c r="N701" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O701" s="7" t="inlineStr">
+        <is>
+          <t>META: Log Book Activity uses shared 7-list; Task Log -&gt; DF Module Step Master (per-DL 10 not isolated).</t>
+        </is>
+      </c>
       <c r="P701" s="8" t="inlineStr"/>
-      <c r="Q701" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q701" s="7" t="inlineStr"/>
     </row>
     <row r="702">
       <c r="A702" s="7" t="inlineStr">
@@ -53407,18 +53447,18 @@
           <t>Trace: Frameworks / Capacity Building</t>
         </is>
       </c>
-      <c r="N702" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O702" s="7" t="inlineStr"/>
+      <c r="N702" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O702" s="7" t="inlineStr">
+        <is>
+          <t>META: Required Training skill_area present. NOTE: a separate Skill Type {Soft|Technical} mandatory select was not located in captured CB child meta.</t>
+        </is>
+      </c>
       <c r="P702" s="8" t="inlineStr"/>
-      <c r="Q702" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q702" s="7" t="inlineStr"/>
     </row>
     <row r="703">
       <c r="A703" s="7" t="inlineStr">
@@ -53483,18 +53523,18 @@
           <t>Trace: Frameworks / Capacity Building</t>
         </is>
       </c>
-      <c r="N703" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O703" s="7" t="inlineStr"/>
+      <c r="N703" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O703" s="7" t="inlineStr">
+        <is>
+          <t>META: skill_area is a flat 21-option list (Financial Literacy ... Other), NOT split Soft(8)/Technical(10).</t>
+        </is>
+      </c>
       <c r="P703" s="8" t="inlineStr"/>
-      <c r="Q703" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q703" s="7" t="inlineStr"/>
     </row>
     <row r="704">
       <c r="A704" s="7" t="inlineStr">
@@ -53559,18 +53599,18 @@
           <t>Trace: Frameworks / Capacity Building</t>
         </is>
       </c>
-      <c r="N704" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O704" s="7" t="inlineStr"/>
+      <c r="N704" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O704" s="7" t="inlineStr">
+        <is>
+          <t>META: Skill Type-&gt;Skill Area filter not confirmable (no skill_type field captured); skill_area present as flat list.</t>
+        </is>
+      </c>
       <c r="P704" s="8" t="inlineStr"/>
-      <c r="Q704" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q704" s="7" t="inlineStr"/>
     </row>
     <row r="705">
       <c r="A705" s="7" t="inlineStr">
@@ -53635,18 +53675,18 @@
           <t>Trace: Frameworks / Capacity Building</t>
         </is>
       </c>
-      <c r="N705" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O705" s="7" t="inlineStr"/>
+      <c r="N705" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O705" s="7" t="inlineStr">
+        <is>
+          <t>META: Past Training completion_status {In progress|Partial Completion|Completed} = 3 (test says 4). Training Format / Skill Retention fields not in captured meta.</t>
+        </is>
+      </c>
       <c r="P705" s="8" t="inlineStr"/>
-      <c r="Q705" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q705" s="7" t="inlineStr"/>
     </row>
     <row r="706">
       <c r="A706" s="7" t="inlineStr">
@@ -53711,18 +53751,18 @@
           <t>Trace: Frameworks / Capacity Building</t>
         </is>
       </c>
-      <c r="N706" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O706" s="7" t="inlineStr"/>
+      <c r="N706" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O706" s="7" t="inlineStr">
+        <is>
+          <t>META: Behaviour Change / Improvement Seen / Time Since / Gap selects not in captured CB child meta (likely on the scorecard child).</t>
+        </is>
+      </c>
       <c r="P706" s="8" t="inlineStr"/>
-      <c r="Q706" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q706" s="7" t="inlineStr"/>
     </row>
     <row r="707">
       <c r="A707" s="7" t="inlineStr">
@@ -53787,18 +53827,18 @@
           <t>Trace: Frameworks / Capacity Building</t>
         </is>
       </c>
-      <c r="N707" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O707" s="7" t="inlineStr"/>
+      <c r="N707" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O707" s="7" t="inlineStr">
+        <is>
+          <t>META: Required Training level_required {Beginner|Intermediate|Advance} = 3 (test says 4 skill levels); status (5), prime_team_member (User), attendance_status (3). Intervention Type/Impl Status differ from claim.</t>
+        </is>
+      </c>
       <c r="P707" s="8" t="inlineStr"/>
-      <c r="Q707" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q707" s="7" t="inlineStr"/>
     </row>
     <row r="708">
       <c r="A708" s="7" t="inlineStr">
@@ -53863,18 +53903,18 @@
           <t>Trace: Frameworks / Capacity Building</t>
         </is>
       </c>
-      <c r="N708" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O708" s="7" t="inlineStr"/>
+      <c r="N708" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O708" s="7" t="inlineStr">
+        <is>
+          <t>META: dual past_trainings + required_trainings children = re-training bridge structure.</t>
+        </is>
+      </c>
       <c r="P708" s="8" t="inlineStr"/>
-      <c r="Q708" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q708" s="7" t="inlineStr"/>
     </row>
     <row r="709">
       <c r="A709" s="7" t="inlineStr">
@@ -53938,18 +53978,18 @@
           <t>Trace: Frameworks / Capacity Building · CB-001 tests past-training only, not the 6-dim scorecard</t>
         </is>
       </c>
-      <c r="N709" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O709" s="7" t="inlineStr"/>
+      <c r="N709" s="16" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O709" s="7" t="inlineStr">
+        <is>
+          <t>Post-Training 6-dimension x 1-5 star scorecard is a Rating-widget child not in the Select/Link/Check meta slice; needs UI QA.</t>
+        </is>
+      </c>
       <c r="P709" s="8" t="inlineStr"/>
-      <c r="Q709" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q709" s="7" t="inlineStr"/>
     </row>
     <row r="710">
       <c r="A710" s="7" t="inlineStr">
@@ -54014,18 +54054,18 @@
           <t>Trace: Frameworks / Capacity Building</t>
         </is>
       </c>
-      <c r="N710" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O710" s="7" t="inlineStr"/>
+      <c r="N710" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O710" s="7" t="inlineStr">
+        <is>
+          <t>META: End/Start + Required/Current level fields present. NOTE: End&gt;=Start and Required&gt;=Current not hard-enforced in meta.</t>
+        </is>
+      </c>
       <c r="P710" s="8" t="inlineStr"/>
-      <c r="Q710" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q710" s="7" t="inlineStr"/>
     </row>
     <row r="711">
       <c r="A711" s="7" t="inlineStr">
@@ -54090,18 +54130,18 @@
           <t>Trace: Frameworks / Capacity Building</t>
         </is>
       </c>
-      <c r="N711" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O711" s="7" t="inlineStr"/>
+      <c r="N711" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O711" s="7" t="inlineStr">
+        <is>
+          <t>META: past/required children support Past/Required/Capacity/Status rollups + gap (computed).</t>
+        </is>
+      </c>
       <c r="P711" s="8" t="inlineStr"/>
-      <c r="Q711" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q711" s="7" t="inlineStr"/>
     </row>
     <row r="712">
       <c r="A712" s="7" t="inlineStr">
@@ -54166,18 +54206,18 @@
           <t>Trace: Frameworks / Business Plan Canvas · tested only generically (BPC-001)</t>
         </is>
       </c>
-      <c r="N712" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O712" s="7" t="inlineStr"/>
+      <c r="N712" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O712" s="7" t="inlineStr">
+        <is>
+          <t>META: 7 cross-module ref pills present; the 9 canvas text blocks are Long Text fields (non-enumerable, outside the Select/Link slice).</t>
+        </is>
+      </c>
       <c r="P712" s="8" t="inlineStr"/>
-      <c r="Q712" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q712" s="7" t="inlineStr"/>
     </row>
     <row r="713">
       <c r="A713" s="7" t="inlineStr">
@@ -54242,18 +54282,18 @@
           <t>Trace: Frameworks / Business Plan Canvas</t>
         </is>
       </c>
-      <c r="N713" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O713" s="7" t="inlineStr"/>
+      <c r="N713" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O713" s="7" t="inlineStr">
+        <is>
+          <t>META: quadrant grouping (UI layout) + completion% (filled/9) + Value-Prop-Set flag are computed/UI from the 9 blocks.</t>
+        </is>
+      </c>
       <c r="P713" s="8" t="inlineStr"/>
-      <c r="Q713" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q713" s="7" t="inlineStr"/>
     </row>
     <row r="714">
       <c r="A714" s="7" t="inlineStr">
@@ -54318,18 +54358,18 @@
           <t>Trace: Frameworks / Business Plan Canvas</t>
         </is>
       </c>
-      <c r="N714" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O714" s="7" t="inlineStr"/>
+      <c r="N714" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O714" s="7" t="inlineStr">
+        <is>
+          <t>META: quadrant grouping (UI layout) + completion% (filled/9) + Value-Prop-Set flag are computed/UI from the 9 blocks.</t>
+        </is>
+      </c>
       <c r="P714" s="8" t="inlineStr"/>
-      <c r="Q714" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q714" s="7" t="inlineStr"/>
     </row>
     <row r="715">
       <c r="A715" s="7" t="inlineStr">
@@ -54394,18 +54434,18 @@
           <t>Trace: Frameworks / Business Plan Canvas</t>
         </is>
       </c>
-      <c r="N715" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O715" s="7" t="inlineStr"/>
+      <c r="N715" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O715" s="7" t="inlineStr">
+        <is>
+          <t>META: quadrant grouping (UI layout) + completion% (filled/9) + Value-Prop-Set flag are computed/UI from the 9 blocks.</t>
+        </is>
+      </c>
       <c r="P715" s="8" t="inlineStr"/>
-      <c r="Q715" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q715" s="7" t="inlineStr"/>
     </row>
     <row r="716">
       <c r="A716" s="7" t="inlineStr">
@@ -54470,18 +54510,18 @@
           <t>Trace: Frameworks / Business Plan Canvas</t>
         </is>
       </c>
-      <c r="N716" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O716" s="7" t="inlineStr"/>
+      <c r="N716" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O716" s="7" t="inlineStr">
+        <is>
+          <t>META: Resources Category/Type + Task Log(17) not enumerated in captured BPC meta.</t>
+        </is>
+      </c>
       <c r="P716" s="8" t="inlineStr"/>
-      <c r="Q716" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q716" s="7" t="inlineStr"/>
     </row>
     <row r="717">
       <c r="A717" s="7" t="inlineStr">
@@ -54546,18 +54586,18 @@
           <t>Trace: Frameworks / Business Plan Canvas</t>
         </is>
       </c>
-      <c r="N717" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O717" s="7" t="inlineStr"/>
+      <c r="N717" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O717" s="7" t="inlineStr">
+        <is>
+          <t>META: at-least-one-resource-row not hard-enforced in meta.</t>
+        </is>
+      </c>
       <c r="P717" s="8" t="inlineStr"/>
-      <c r="Q717" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q717" s="7" t="inlineStr"/>
     </row>
     <row r="718">
       <c r="A718" s="7" t="inlineStr">
@@ -54622,18 +54662,18 @@
           <t>Trace: Frameworks / Business Plan Canvas</t>
         </is>
       </c>
-      <c r="N718" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O718" s="7" t="inlineStr"/>
+      <c r="N718" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O718" s="7" t="inlineStr">
+        <is>
+          <t>META: exactly 7 cross-module ref Links present - ref_key_partners&gt;DF Market Linkage, ref_key_activities&gt;DF Standardization, ref_key_resources&gt;DF Human Resource, ref_channels&gt;DF Promotional Marketing, ref_customer_segments&gt;DF Customer Analysis, ref_cost_structure&gt;DF Unit Pricing, ref_revenue_streams&gt;DF Financials.</t>
+        </is>
+      </c>
       <c r="P718" s="8" t="inlineStr"/>
-      <c r="Q718" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q718" s="7" t="inlineStr"/>
     </row>
     <row r="719">
       <c r="A719" s="7" t="inlineStr">
@@ -55913,18 +55953,18 @@
           <t>Trace: Product Form / Product Profile</t>
         </is>
       </c>
-      <c r="N735" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O735" s="7" t="inlineStr"/>
+      <c r="N735" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O735" s="7" t="inlineStr">
+        <is>
+          <t>META: product_status {New Product Developed|Existing Product}. NOTE: labels are fuller than bare New/Existing.</t>
+        </is>
+      </c>
       <c r="P735" s="8" t="inlineStr"/>
-      <c r="Q735" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q735" s="7" t="inlineStr"/>
     </row>
     <row r="736">
       <c r="A736" s="7" t="inlineStr">
@@ -55989,18 +56029,18 @@
           <t>Trace: Product Form / Product Profile</t>
         </is>
       </c>
-      <c r="N736" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O736" s="7" t="inlineStr"/>
+      <c r="N736" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O736" s="7" t="inlineStr">
+        <is>
+          <t>META: sector[L]&gt;Sector, master count 17 (test says 6) - seed/count drift (Link picker correct).</t>
+        </is>
+      </c>
       <c r="P736" s="8" t="inlineStr"/>
-      <c r="Q736" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q736" s="7" t="inlineStr"/>
     </row>
     <row r="737">
       <c r="A737" s="7" t="inlineStr">
@@ -56065,18 +56105,18 @@
           <t>Trace: Product Form / Product Profile</t>
         </is>
       </c>
-      <c r="N737" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O737" s="7" t="inlineStr"/>
+      <c r="N737" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O737" s="7" t="inlineStr">
+        <is>
+          <t>META: business_basket[L]&gt;Business Basket, master count 75 (test says 8) - seed/count drift.</t>
+        </is>
+      </c>
       <c r="P737" s="8" t="inlineStr"/>
-      <c r="Q737" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q737" s="7" t="inlineStr"/>
     </row>
     <row r="738">
       <c r="A738" s="7" t="inlineStr">
@@ -56141,18 +56181,18 @@
           <t>Trace: Product Form / Product Profile</t>
         </is>
       </c>
-      <c r="N738" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O738" s="7" t="inlineStr"/>
+      <c r="N738" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O738" s="7" t="inlineStr">
+        <is>
+          <t>META: product_type[L]&gt;Product Type, master count 97 (test says 7) - seed/count drift.</t>
+        </is>
+      </c>
       <c r="P738" s="8" t="inlineStr"/>
-      <c r="Q738" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q738" s="7" t="inlineStr"/>
     </row>
     <row r="739">
       <c r="A739" s="7" t="inlineStr">
@@ -56217,18 +56257,18 @@
           <t>Trace: Product Form / Product Profile · PR-002 treats it as free text + invents a duplicate-per-EP rule · Was stale — realigned</t>
         </is>
       </c>
-      <c r="N739" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O739" s="7" t="inlineStr"/>
+      <c r="N739" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O739" s="7" t="inlineStr">
+        <is>
+          <t>META: product_name[L]&gt;Product Master reqd - Product Name required + Link to Product Master (PR-002 free-text model was stale, now realigned).</t>
+        </is>
+      </c>
       <c r="P739" s="8" t="inlineStr"/>
-      <c r="Q739" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q739" s="7" t="inlineStr"/>
     </row>
     <row r="740">
       <c r="A740" s="7" t="inlineStr">
@@ -56293,18 +56333,18 @@
           <t>Trace: Product Form / Product Profile</t>
         </is>
       </c>
-      <c r="N740" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O740" s="7" t="inlineStr"/>
+      <c r="N740" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O740" s="7" t="inlineStr">
+        <is>
+          <t>META: entrepreneur_name[L]&gt;Enterprenur Profile - EP chip auto-fetched.</t>
+        </is>
+      </c>
       <c r="P740" s="8" t="inlineStr"/>
-      <c r="Q740" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q740" s="7" t="inlineStr"/>
     </row>
     <row r="741">
       <c r="A741" s="7" t="inlineStr">
@@ -56369,18 +56409,18 @@
           <t>Trace: Product Form / Product Profile · labelled 'Description' in PR-001</t>
         </is>
       </c>
-      <c r="N741" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O741" s="7" t="inlineStr"/>
+      <c r="N741" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O741" s="7" t="inlineStr">
+        <is>
+          <t>META: Product Snapshot / Product Image / USP are Text/Attach fields (present, outside the Select/Link enumerable slice).</t>
+        </is>
+      </c>
       <c r="P741" s="8" t="inlineStr"/>
-      <c r="Q741" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q741" s="7" t="inlineStr"/>
     </row>
     <row r="742">
       <c r="A742" s="7" t="inlineStr">
@@ -56445,18 +56485,18 @@
           <t>Trace: Product Form / Product Profile</t>
         </is>
       </c>
-      <c r="N742" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O742" s="7" t="inlineStr"/>
+      <c r="N742" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O742" s="7" t="inlineStr">
+        <is>
+          <t>META: Product Snapshot / Product Image / USP are Text/Attach fields (present, outside the Select/Link enumerable slice).</t>
+        </is>
+      </c>
       <c r="P742" s="8" t="inlineStr"/>
-      <c r="Q742" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q742" s="7" t="inlineStr"/>
     </row>
     <row r="743">
       <c r="A743" s="7" t="inlineStr">
@@ -56521,18 +56561,18 @@
           <t>Trace: Product Form / Product Profile · journey core rule; zero tests</t>
         </is>
       </c>
-      <c r="N743" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O743" s="7" t="inlineStr"/>
+      <c r="N743" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O743" s="7" t="inlineStr">
+        <is>
+          <t>META: product_raw_materials[T]&gt;Product Raw Material - Ingredients pills fetched from Raw Material framework.</t>
+        </is>
+      </c>
       <c r="P743" s="8" t="inlineStr"/>
-      <c r="Q743" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q743" s="7" t="inlineStr"/>
     </row>
     <row r="744">
       <c r="A744" s="7" t="inlineStr">
@@ -56597,18 +56637,18 @@
           <t>Trace: Product Form / Product Profile</t>
         </is>
       </c>
-      <c r="N744" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O744" s="7" t="inlineStr"/>
+      <c r="N744" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O744" s="7" t="inlineStr">
+        <is>
+          <t>META: Product Snapshot / Product Image / USP are Text/Attach fields (present, outside the Select/Link enumerable slice).</t>
+        </is>
+      </c>
       <c r="P744" s="8" t="inlineStr"/>
-      <c r="Q744" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q744" s="7" t="inlineStr"/>
     </row>
     <row r="745">
       <c r="A745" s="7" t="inlineStr">
@@ -56673,18 +56713,18 @@
           <t>Trace: Product Form / Product Profile</t>
         </is>
       </c>
-      <c r="N745" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O745" s="7" t="inlineStr"/>
+      <c r="N745" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O745" s="7" t="inlineStr">
+        <is>
+          <t>META: shelf_life_tested checkbox (Yes/No); frequency depends_on shelf_life_tested.</t>
+        </is>
+      </c>
       <c r="P745" s="8" t="inlineStr"/>
-      <c r="Q745" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q745" s="7" t="inlineStr"/>
     </row>
     <row r="746">
       <c r="A746" s="7" t="inlineStr">
@@ -56749,18 +56789,18 @@
           <t>Trace: Product Form / Product Profile · PR-008/014 use APIC-HHF-250G-001 master-expansion format · Was stale — realigned</t>
         </is>
       </c>
-      <c r="N746" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O746" s="7" t="inlineStr"/>
+      <c r="N746" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O746" s="7" t="inlineStr">
+        <is>
+          <t>META: sku_data[T]&gt;Sku Data child - SKU = VARIANT-SUBVARIANT-WEIGHT-UNIT (format realigned to APIC-HHF-250G-001 earlier).</t>
+        </is>
+      </c>
       <c r="P746" s="8" t="inlineStr"/>
-      <c r="Q746" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q746" s="7" t="inlineStr"/>
     </row>
     <row r="747">
       <c r="A747" s="7" t="inlineStr">
@@ -56825,18 +56865,18 @@
           <t>Trace: Product Form / Product Profile</t>
         </is>
       </c>
-      <c r="N747" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O747" s="7" t="inlineStr"/>
+      <c r="N747" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O747" s="7" t="inlineStr">
+        <is>
+          <t>META: Product SKU phase {Existing|Optimized}. NOTE: variant-status enum is Existing/Optimized, not Existing/New as test claims.</t>
+        </is>
+      </c>
       <c r="P747" s="8" t="inlineStr"/>
-      <c r="Q747" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q747" s="7" t="inlineStr"/>
     </row>
     <row r="748">
       <c r="A748" s="7" t="inlineStr">
@@ -56901,18 +56941,18 @@
           <t>Trace: Product Form / Product Profile</t>
         </is>
       </c>
-      <c r="N748" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O748" s="7" t="inlineStr"/>
+      <c r="N748" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O748" s="7" t="inlineStr">
+        <is>
+          <t>META: Sku Data child carries Variant Name / Sub Variant / Net Weight feeding the SKU. NOTE: not-empty / &gt;0 guards not hard-enforced in meta.</t>
+        </is>
+      </c>
       <c r="P748" s="8" t="inlineStr"/>
-      <c r="Q748" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q748" s="7" t="inlineStr"/>
     </row>
     <row r="749">
       <c r="A749" s="7" t="inlineStr">
@@ -56977,18 +57017,18 @@
           <t>Trace: Product Form / Product Profile</t>
         </is>
       </c>
-      <c r="N749" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O749" s="7" t="inlineStr"/>
+      <c r="N749" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O749" s="7" t="inlineStr">
+        <is>
+          <t>META: Sku Data child carries Variant Name / Sub Variant / Net Weight feeding the SKU. NOTE: not-empty / &gt;0 guards not hard-enforced in meta.</t>
+        </is>
+      </c>
       <c r="P749" s="8" t="inlineStr"/>
-      <c r="Q749" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q749" s="7" t="inlineStr"/>
     </row>
     <row r="750">
       <c r="A750" s="7" t="inlineStr">
@@ -57053,18 +57093,18 @@
           <t>Trace: Product Form / Product Profile</t>
         </is>
       </c>
-      <c r="N750" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O750" s="7" t="inlineStr"/>
+      <c r="N750" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O750" s="7" t="inlineStr">
+        <is>
+          <t>META: Sku Data child carries Variant Name / Sub Variant / Net Weight feeding the SKU. NOTE: not-empty / &gt;0 guards not hard-enforced in meta.</t>
+        </is>
+      </c>
       <c r="P750" s="8" t="inlineStr"/>
-      <c r="Q750" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q750" s="7" t="inlineStr"/>
     </row>
     <row r="751">
       <c r="A751" s="7" t="inlineStr">
@@ -57129,18 +57169,18 @@
           <t>Trace: Product Form / Product Profile</t>
         </is>
       </c>
-      <c r="N751" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O751" s="7" t="inlineStr"/>
+      <c r="N751" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O751" s="7" t="inlineStr">
+        <is>
+          <t>META: Product SKU unit[L]&gt;DF Module Unit Type + quantity_unit {gm|kg|ml|ltr|pcs|box|pack|bottle|pouch}.</t>
+        </is>
+      </c>
       <c r="P751" s="8" t="inlineStr"/>
-      <c r="Q751" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q751" s="7" t="inlineStr"/>
     </row>
     <row r="752">
       <c r="A752" s="7" t="inlineStr">
@@ -57205,18 +57245,18 @@
           <t>Trace: Product Form / Product Profile</t>
         </is>
       </c>
-      <c r="N752" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O752" s="7" t="inlineStr"/>
+      <c r="N752" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O752" s="7" t="inlineStr">
+        <is>
+          <t>META: Product SKU length/breadth/height (Float) + unit[L]&gt;DF Module Unit Type - dimensions L x B x H + unit.</t>
+        </is>
+      </c>
       <c r="P752" s="8" t="inlineStr"/>
-      <c r="Q752" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q752" s="7" t="inlineStr"/>
     </row>
     <row r="753">
       <c r="A753" s="7" t="inlineStr">
@@ -57281,18 +57321,18 @@
           <t>Trace: Product Form / Product Profile</t>
         </is>
       </c>
-      <c r="N753" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O753" s="7" t="inlineStr"/>
+      <c r="N753" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O753" s="7" t="inlineStr">
+        <is>
+          <t>META: Product SKU volume (Float, read-only) = L x B x H.</t>
+        </is>
+      </c>
       <c r="P753" s="8" t="inlineStr"/>
-      <c r="Q753" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q753" s="7" t="inlineStr"/>
     </row>
     <row r="754">
       <c r="A754" s="7" t="inlineStr">
@@ -57357,18 +57397,18 @@
           <t>Trace: Product Form / Product Profile</t>
         </is>
       </c>
-      <c r="N754" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O754" s="7" t="inlineStr"/>
+      <c r="N754" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O754" s="7" t="inlineStr">
+        <is>
+          <t>META: variant Retail Price fetch-from-Unit-Pricing not in the captured Product SKU fields - cross-module fetch not confirmed this pass.</t>
+        </is>
+      </c>
       <c r="P754" s="8" t="inlineStr"/>
-      <c r="Q754" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q754" s="7" t="inlineStr"/>
     </row>
     <row r="755">
       <c r="A755" s="7" t="inlineStr">
@@ -57433,18 +57473,18 @@
           <t>Trace: Product Form / Product Profile</t>
         </is>
       </c>
-      <c r="N755" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O755" s="7" t="inlineStr"/>
+      <c r="N755" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O755" s="7" t="inlineStr">
+        <is>
+          <t>META: process_flow_table[T]&gt;Process Flow Product Child present; Step Detail / Machine Status / Implemented? are child fields not in the captured slice.</t>
+        </is>
+      </c>
       <c r="P755" s="8" t="inlineStr"/>
-      <c r="Q755" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q755" s="7" t="inlineStr"/>
     </row>
     <row r="756">
       <c r="A756" s="7" t="inlineStr">
@@ -57509,18 +57549,18 @@
           <t>Trace: Product Form / Product Profile · journey: machines -&gt; Machinery; PR-007/RAWMAT-002 wrongly route machines -&gt; Raw Materials · Was stale — realigned</t>
         </is>
       </c>
-      <c r="N756" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O756" s="7" t="inlineStr"/>
+      <c r="N756" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O756" s="7" t="inlineStr">
+        <is>
+          <t>META: process_flow_table present; existing-machine -&gt; Machinery routing realigned (RAWMAT-002 RM mis-route was stale).</t>
+        </is>
+      </c>
       <c r="P756" s="8" t="inlineStr"/>
-      <c r="Q756" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q756" s="7" t="inlineStr"/>
     </row>
     <row r="757">
       <c r="A757" s="7" t="inlineStr">
@@ -57585,18 +57625,18 @@
           <t>Trace: Product Form / Product Profile</t>
         </is>
       </c>
-      <c r="N757" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O757" s="7" t="inlineStr"/>
+      <c r="N757" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O757" s="7" t="inlineStr">
+        <is>
+          <t>META: process_flow_table[T]&gt;Process Flow Product Child present; Step Detail / Machine Status / Implemented? are child fields not in the captured slice.</t>
+        </is>
+      </c>
       <c r="P757" s="8" t="inlineStr"/>
-      <c r="Q757" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q757" s="7" t="inlineStr"/>
     </row>
     <row r="758">
       <c r="A758" s="7" t="inlineStr">
@@ -57661,18 +57701,18 @@
           <t>Trace: Product Form / Product Profile</t>
         </is>
       </c>
-      <c r="N758" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O758" s="7" t="inlineStr"/>
+      <c r="N758" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O758" s="7" t="inlineStr">
+        <is>
+          <t>META: if_agri_bi_products (check); land_ownership + production_unit depends_on if_agri_bi_products - Agri block reveal/grey confirmed.</t>
+        </is>
+      </c>
       <c r="P758" s="8" t="inlineStr"/>
-      <c r="Q758" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q758" s="7" t="inlineStr"/>
     </row>
     <row r="759">
       <c r="A759" s="7" t="inlineStr">
@@ -57737,18 +57777,18 @@
           <t>Trace: Product Form / Product Profile</t>
         </is>
       </c>
-      <c r="N759" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O759" s="7" t="inlineStr"/>
+      <c r="N759" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O759" s="7" t="inlineStr">
+        <is>
+          <t>META: land_ownership {Own Land|Land on Lease} = 2 (test says 4); production_unit[L]&gt;DF Module Unit Type. Capacity Units via Unit Master.</t>
+        </is>
+      </c>
       <c r="P759" s="8" t="inlineStr"/>
-      <c r="Q759" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q759" s="7" t="inlineStr"/>
     </row>
     <row r="760">
       <c r="A760" s="7" t="inlineStr">
@@ -57813,18 +57853,18 @@
           <t>Trace: Product Form / Product Profile</t>
         </is>
       </c>
-      <c r="N760" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O760" s="7" t="inlineStr"/>
+      <c r="N760" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O760" s="7" t="inlineStr">
+        <is>
+          <t>META: average_existing/aspiring_production_capacity + Production Capacity table present. NOTE: Area&gt;0 / capacity&gt;=0 not hard-enforced.</t>
+        </is>
+      </c>
       <c r="P760" s="8" t="inlineStr"/>
-      <c r="Q760" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q760" s="7" t="inlineStr"/>
     </row>
     <row r="761">
       <c r="A761" s="7" t="inlineStr">
@@ -57889,18 +57929,18 @@
           <t>Trace: Product Form / Product Profile</t>
         </is>
       </c>
-      <c r="N761" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O761" s="7" t="inlineStr"/>
+      <c r="N761" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O761" s="7" t="inlineStr">
+        <is>
+          <t>META: available_months[T]&gt;Product Available Month Picker - month grid present.</t>
+        </is>
+      </c>
       <c r="P761" s="8" t="inlineStr"/>
-      <c r="Q761" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q761" s="7" t="inlineStr"/>
     </row>
     <row r="762">
       <c r="A762" s="7" t="inlineStr">
@@ -57965,18 +58005,18 @@
           <t>Trace: Product Form / Product Profile</t>
         </is>
       </c>
-      <c r="N762" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O762" s="7" t="inlineStr"/>
+      <c r="N762" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O762" s="7" t="inlineStr">
+        <is>
+          <t>META: available_months month-picker present; seasonal reveal driven via available_months (explicit Is-Seasonal toggle not isolated).</t>
+        </is>
+      </c>
       <c r="P762" s="8" t="inlineStr"/>
-      <c r="Q762" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q762" s="7" t="inlineStr"/>
     </row>
     <row r="763">
       <c r="A763" s="7" t="inlineStr">
@@ -58041,18 +58081,18 @@
           <t>Trace: Product Form / Product Profile</t>
         </is>
       </c>
-      <c r="N763" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O763" s="7" t="inlineStr"/>
+      <c r="N763" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O763" s="7" t="inlineStr">
+        <is>
+          <t>META: monthly_production_data[T]&gt;Monthly Production Entry - production tracker rows present.</t>
+        </is>
+      </c>
       <c r="P763" s="8" t="inlineStr"/>
-      <c r="Q763" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q763" s="7" t="inlineStr"/>
     </row>
     <row r="764">
       <c r="A764" s="7" t="inlineStr">
@@ -58117,18 +58157,18 @@
           <t>Trace: Product Form / Product Profile</t>
         </is>
       </c>
-      <c r="N764" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O764" s="7" t="inlineStr"/>
+      <c r="N764" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O764" s="7" t="inlineStr">
+        <is>
+          <t>META: Monthly Production Entry table present - Revenue = Qty x Selling Price; row + annual totals computed.</t>
+        </is>
+      </c>
       <c r="P764" s="8" t="inlineStr"/>
-      <c r="Q764" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q764" s="7" t="inlineStr"/>
     </row>
     <row r="765">
       <c r="A765" s="7" t="inlineStr">
@@ -58193,18 +58233,18 @@
           <t>Trace: Product Form / Product Profile</t>
         </is>
       </c>
-      <c r="N765" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O765" s="7" t="inlineStr"/>
+      <c r="N765" s="16" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O765" s="7" t="inlineStr">
+        <is>
+          <t>Calc-field formula display + fetched-field source link are UI-presentation claims; need visual QA.</t>
+        </is>
+      </c>
       <c r="P765" s="8" t="inlineStr"/>
-      <c r="Q765" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q765" s="7" t="inlineStr"/>
     </row>
     <row r="766">
       <c r="A766" s="7" t="inlineStr">
@@ -58269,18 +58309,18 @@
           <t>Trace: Product Form / Product Profile · BRD data-flow (~line 1735) wrongly routes process-flow machines into Raw Materials Existing · BRD reconcile pending</t>
         </is>
       </c>
-      <c r="N766" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O766" s="7" t="inlineStr"/>
+      <c r="N766" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O766" s="7" t="inlineStr">
+        <is>
+          <t>META: product_raw_materials + process_flow_table present. NOTE: BRD data-flow text (~line 1735) still wrongly routes process-flow machines into Raw Materials Existing (should route to Machinery) - BRD reconcile pending.</t>
+        </is>
+      </c>
       <c r="P766" s="8" t="inlineStr"/>
-      <c r="Q766" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q766" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:Q766"/>

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -1293,11 +1293,11 @@
         </is>
       </c>
       <c r="B85" s="5" t="n">
-        <v>391</v>
+        <v>406</v>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>51%</t>
+          <t>53%</t>
         </is>
       </c>
     </row>
@@ -1308,11 +1308,11 @@
         </is>
       </c>
       <c r="B86" s="5" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>9%</t>
         </is>
       </c>
     </row>
@@ -1338,11 +1338,11 @@
         </is>
       </c>
       <c r="B88" s="5" t="n">
-        <v>277</v>
+        <v>261</v>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>34%</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Executed (Pass+Fail): 456  |  Pass rate of executed: 86%</t>
+          <t>Executed (Pass+Fail): 472  |  Pass rate of executed: 86%</t>
         </is>
       </c>
     </row>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>0 / 0 / 0 / 16</t>
+          <t>15 / 1 / 0 / 0</t>
         </is>
       </c>
     </row>
@@ -54738,18 +54738,18 @@
           <t>Trace: Entrepreneur Profile / EP Profile · EP-021 'Final Selection blocked without attachment' — no such validation · Was stale — realigned</t>
         </is>
       </c>
-      <c r="N719" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O719" s="7" t="inlineStr"/>
+      <c r="N719" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O719" s="7" t="inlineStr">
+        <is>
+          <t>META: perm-leveled selection fields exist (rural_e_champ_score PL1, final_selection_status PL2). NOTE: a discrete Selection Attachment PL1 field was not identified - attachments live in documents_table; EP-021 block-without-attachment was stale and realigned.</t>
+        </is>
+      </c>
       <c r="P719" s="8" t="inlineStr"/>
-      <c r="Q719" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q719" s="7" t="inlineStr"/>
     </row>
     <row r="720">
       <c r="A720" s="7" t="inlineStr">
@@ -54814,18 +54814,18 @@
           <t>Trace: Entrepreneur Profile / EP Profile · real repo rule, undocumented + untested</t>
         </is>
       </c>
-      <c r="N720" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O720" s="7" t="inlineStr"/>
+      <c r="N720" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O720" s="7" t="inlineStr">
+        <is>
+          <t>META: rural_e_champ_score (PL1, Int) + final_selection_status (PL2, {Incubated|Supported}) both present. NOTE: final_selection-mandatory-once-score-entered is a server-side validation hook, not visible/enforced in field meta.</t>
+        </is>
+      </c>
       <c r="P720" s="8" t="inlineStr"/>
-      <c r="Q720" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q720" s="7" t="inlineStr"/>
     </row>
     <row r="721">
       <c r="A721" s="7" t="inlineStr">
@@ -54889,18 +54889,18 @@
           <t>Trace: Entrepreneur Profile / EP Profile</t>
         </is>
       </c>
-      <c r="N721" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O721" s="7" t="inlineStr"/>
+      <c r="N721" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O721" s="7" t="inlineStr">
+        <is>
+          <t>META: priority_table[T]&gt;Priority Table with framework_name[L]&gt;Diagnostic Framework Master + priority[I] - frameworks auto-listed with priority; reorder is UI on the priority column.</t>
+        </is>
+      </c>
       <c r="P721" s="8" t="inlineStr"/>
-      <c r="Q721" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q721" s="7" t="inlineStr"/>
     </row>
     <row r="722">
       <c r="A722" s="7" t="inlineStr">
@@ -54965,18 +54965,18 @@
           <t>Trace: Entrepreneur Profile / EP Profile · gating not explicitly tested</t>
         </is>
       </c>
-      <c r="N722" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O722" s="7" t="inlineStr"/>
+      <c r="N722" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O722" s="7" t="inlineStr">
+        <is>
+          <t>META: final_selection_status {Incubated|Supported} + priority_table present. NOTE: the Prioritisation-tab-only-when-Incubated/Supported gating is UI depends_on, needs visual confirmation.</t>
+        </is>
+      </c>
       <c r="P722" s="8" t="inlineStr"/>
-      <c r="Q722" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q722" s="7" t="inlineStr"/>
     </row>
     <row r="723">
       <c r="A723" s="7" t="inlineStr">
@@ -55041,18 +55041,18 @@
           <t>Trace: Entrepreneur Profile / EP Profile · dup-priority not in BRD/tests; EP-023 add-twice can't run</t>
         </is>
       </c>
-      <c r="N723" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O723" s="7" t="inlineStr"/>
+      <c r="N723" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O723" s="7" t="inlineStr">
+        <is>
+          <t>META: Priority Table framework_name + priority present. NOTE: no duplicate-framework / duplicate-priority unique constraint in child meta - not hard-enforced.</t>
+        </is>
+      </c>
       <c r="P723" s="8" t="inlineStr"/>
-      <c r="Q723" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q723" s="7" t="inlineStr"/>
     </row>
     <row r="724">
       <c r="A724" s="7" t="inlineStr">
@@ -55117,18 +55117,18 @@
           <t>Trace: Entrepreneur Profile / EP Profile</t>
         </is>
       </c>
-      <c r="N724" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O724" s="7" t="inlineStr"/>
+      <c r="N724" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O724" s="7" t="inlineStr">
+        <is>
+          <t>META: email is a plain Data field (no Email-format options flag) - email format validation not confirmed in meta.</t>
+        </is>
+      </c>
       <c r="P724" s="8" t="inlineStr"/>
-      <c r="Q724" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q724" s="7" t="inlineStr"/>
     </row>
     <row r="725">
       <c r="A725" s="7" t="inlineStr">
@@ -55193,18 +55193,18 @@
           <t>Trace: Entrepreneur Profile / EP Profile</t>
         </is>
       </c>
-      <c r="N725" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O725" s="7" t="inlineStr"/>
+      <c r="N725" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O725" s="7" t="inlineStr">
+        <is>
+          <t>META: block[L]&gt;Block and village[L]&gt;Village both carry link_filters - Block filtered by District, Village by Block confirmed.</t>
+        </is>
+      </c>
       <c r="P725" s="8" t="inlineStr"/>
-      <c r="Q725" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q725" s="7" t="inlineStr"/>
     </row>
     <row r="726">
       <c r="A726" s="7" t="inlineStr">
@@ -55269,18 +55269,18 @@
           <t>Trace: Entrepreneur Profile / EP Profile · journey-mandated; zero tests</t>
         </is>
       </c>
-      <c r="N726" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O726" s="7" t="inlineStr"/>
+      <c r="N726" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O726" s="7" t="inlineStr">
+        <is>
+          <t>META: table_product_profiling[T]&gt;Product Profiling present on EP. NOTE: the Raw-Materials-from-Product-Profile auto-fill into the Raw Material framework is a cross-doctype server hook, not a field-meta artifact.</t>
+        </is>
+      </c>
       <c r="P726" s="8" t="inlineStr"/>
-      <c r="Q726" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q726" s="7" t="inlineStr"/>
     </row>
     <row r="727">
       <c r="A727" s="7" t="inlineStr">
@@ -55345,18 +55345,18 @@
           <t>Trace: Entrepreneur Profile / EP Profile · journey-mandated; zero tests</t>
         </is>
       </c>
-      <c r="N727" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O727" s="7" t="inlineStr"/>
+      <c r="N727" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O727" s="7" t="inlineStr">
+        <is>
+          <t>META: machinery_flow[L]&gt;Machinery Flow + process_flow[L]&gt;Process Flow links present on EP - process/machinery existing-machine routing to Machinery framework wired.</t>
+        </is>
+      </c>
       <c r="P727" s="8" t="inlineStr"/>
-      <c r="Q727" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q727" s="7" t="inlineStr"/>
     </row>
     <row r="728">
       <c r="A728" s="7" t="inlineStr">
@@ -55421,18 +55421,18 @@
           <t>Trace: Entrepreneur Profile / EP Profile · repetition count + popup % not tested</t>
         </is>
       </c>
-      <c r="N728" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O728" s="7" t="inlineStr"/>
+      <c r="N728" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O728" s="7" t="inlineStr">
+        <is>
+          <t>META: framework-completion rollup is a dashboard calc (Product carries df_product_diag_frameworks_details + progress_percent). NOTE: the Not started / Completed xN repetition count + popup % need UI/dashboard QA.</t>
+        </is>
+      </c>
       <c r="P728" s="8" t="inlineStr"/>
-      <c r="Q728" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q728" s="7" t="inlineStr"/>
     </row>
     <row r="729">
       <c r="A729" s="7" t="inlineStr">
@@ -55497,18 +55497,18 @@
           <t>Trace: Entrepreneur Profile / EP Profile</t>
         </is>
       </c>
-      <c r="N729" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O729" s="7" t="inlineStr"/>
+      <c r="N729" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O729" s="7" t="inlineStr">
+        <is>
+          <t>META: Entrepreneur Introduction contact_type {Mentor|Network Contact} - exact match.</t>
+        </is>
+      </c>
       <c r="P729" s="8" t="inlineStr"/>
-      <c r="Q729" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q729" s="7" t="inlineStr"/>
     </row>
     <row r="730">
       <c r="A730" s="7" t="inlineStr">
@@ -55573,18 +55573,18 @@
           <t>Trace: Entrepreneur Profile / EP Profile · EP-035 uses 'Pending' — no such option · Was stale — realigned</t>
         </is>
       </c>
-      <c r="N730" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O730" s="7" t="inlineStr"/>
+      <c r="N730" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O730" s="7" t="inlineStr">
+        <is>
+          <t>META: Entrepreneur Introduction meeting_status {Not Yet Met|Awaiting Response|Scheduled|In Progress|Completed} - no Pending option (EP-035 Pending was stale, now realigned).</t>
+        </is>
+      </c>
       <c r="P730" s="8" t="inlineStr"/>
-      <c r="Q730" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q730" s="7" t="inlineStr"/>
     </row>
     <row r="731">
       <c r="A731" s="7" t="inlineStr">
@@ -55649,16 +55649,24 @@
           <t>Trace: Entrepreneur Profile / EP Profile · not in BRD or tests</t>
         </is>
       </c>
-      <c r="N731" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O731" s="7" t="inlineStr"/>
-      <c r="P731" s="8" t="inlineStr"/>
+      <c r="N731" s="15" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O731" s="7" t="inlineStr">
+        <is>
+          <t>META: Entrepreneur Introduction child has only mentor, contact_type, meeting_status, meeting_count - the Networking outcome controlled-vocabulary (7 values) field is NOT present in the build.</t>
+        </is>
+      </c>
+      <c r="P731" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="Q731" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Networking outcome vocab field missing.</t>
         </is>
       </c>
     </row>
@@ -55725,18 +55733,18 @@
           <t>Trace: Entrepreneur Profile / EP Profile · BRD says 'mean of 10'; repo = (total/max)*5*10 — mismatch, exact value untested</t>
         </is>
       </c>
-      <c r="N732" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O732" s="7" t="inlineStr"/>
+      <c r="N732" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O732" s="7" t="inlineStr">
+        <is>
+          <t>META: avg_rating is a read-only Data field on EP. NOTE: the 10-rating source child + repo 0-100 scaling are not in the captured meta - exact value not verified.</t>
+        </is>
+      </c>
       <c r="P732" s="8" t="inlineStr"/>
-      <c r="Q732" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q732" s="7" t="inlineStr"/>
     </row>
     <row r="733">
       <c r="A733" s="7" t="inlineStr">
@@ -55801,18 +55809,18 @@
           <t>Trace: Entrepreneur Profile / EP Profile</t>
         </is>
       </c>
-      <c r="N733" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O733" s="7" t="inlineStr"/>
+      <c r="N733" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O733" s="7" t="inlineStr">
+        <is>
+          <t>META: 18 needs_*_support checkboxes present (financial_bookkeeping, unit_pricing, raw_material_procurement, machinery, registration_licensing, product_testing, standardization, packaging, quality_control, market_linkage, branding_marketing, logistic, digital_literacy, training, infrastructure, pitch_deck, funding_schemes, other). NOTE: the dependent note-field reveal is depends_on on Text fields, outside the captured slice.</t>
+        </is>
+      </c>
       <c r="P733" s="8" t="inlineStr"/>
-      <c r="Q733" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q733" s="7" t="inlineStr"/>
     </row>
     <row r="734">
       <c r="A734" s="7" t="inlineStr">
@@ -55877,18 +55885,18 @@
           <t>Trace: Entrepreneur Profile / EP Profile · Business Basket / Product Name map filters not tested</t>
         </is>
       </c>
-      <c r="N734" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O734" s="7" t="inlineStr"/>
+      <c r="N734" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O734" s="7" t="inlineStr">
+        <is>
+          <t>META: EP carries district[L], block[L], cohort[L], sector[S] (3-opt on EP). NOTE: EP Landscape map filters (incl. Business Basket, Product Name) are a dashboard view - filter behaviour needs UI QA.</t>
+        </is>
+      </c>
       <c r="P734" s="8" t="inlineStr"/>
-      <c r="Q734" s="7" t="inlineStr">
-        <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
-        </is>
-      </c>
+      <c r="Q734" s="7" t="inlineStr"/>
     </row>
     <row r="735">
       <c r="A735" s="7" t="inlineStr">

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -1932,7 +1932,7 @@
       <c r="P3" s="8" t="inlineStr"/>
       <c r="Q3" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2013,7 @@
       <c r="P4" s="8" t="inlineStr"/>
       <c r="Q4" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       <c r="P7" s="8" t="inlineStr"/>
       <c r="Q7" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
       <c r="P9" s="8" t="inlineStr"/>
       <c r="Q9" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       <c r="P10" s="8" t="inlineStr"/>
       <c r="Q10" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       <c r="P11" s="8" t="inlineStr"/>
       <c r="Q11" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -2575,7 +2575,7 @@
       <c r="P12" s="8" t="inlineStr"/>
       <c r="Q12" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -2642,7 +2642,7 @@
       <c r="P13" s="8" t="inlineStr"/>
       <c r="Q13" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -2709,7 +2709,7 @@
       <c r="P14" s="8" t="inlineStr"/>
       <c r="Q14" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       <c r="P15" s="8" t="inlineStr"/>
       <c r="Q15" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -2843,7 +2843,7 @@
       <c r="P16" s="8" t="inlineStr"/>
       <c r="Q16" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       <c r="P17" s="8" t="inlineStr"/>
       <c r="Q17" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2979,7 @@
       <c r="P18" s="8" t="inlineStr"/>
       <c r="Q18" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -3047,7 +3047,7 @@
       <c r="P19" s="8" t="inlineStr"/>
       <c r="Q19" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       <c r="P20" s="8" t="inlineStr"/>
       <c r="Q20" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -3193,7 +3193,7 @@
       <c r="P21" s="8" t="inlineStr"/>
       <c r="Q21" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3261,7 @@
       <c r="P22" s="8" t="inlineStr"/>
       <c r="Q22" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -3329,7 +3329,7 @@
       <c r="P23" s="8" t="inlineStr"/>
       <c r="Q23" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -3396,7 +3396,7 @@
       <c r="P24" s="8" t="inlineStr"/>
       <c r="Q24" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -3463,7 +3463,7 @@
       <c r="P25" s="8" t="inlineStr"/>
       <c r="Q25" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3531,7 @@
       <c r="P26" s="8" t="inlineStr"/>
       <c r="Q26" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -3599,7 +3599,7 @@
       <c r="P27" s="8" t="inlineStr"/>
       <c r="Q27" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
       <c r="P28" s="8" t="inlineStr"/>
       <c r="Q28" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3735,7 @@
       <c r="P29" s="8" t="inlineStr"/>
       <c r="Q29" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       <c r="P30" s="8" t="inlineStr"/>
       <c r="Q30" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -3872,7 +3872,7 @@
       <c r="P31" s="8" t="inlineStr"/>
       <c r="Q31" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -4017,7 +4017,7 @@
       <c r="P33" s="8" t="inlineStr"/>
       <c r="Q33" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -4152,7 +4152,7 @@
       <c r="P35" s="8" t="inlineStr"/>
       <c r="Q35" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       <c r="P36" s="8" t="inlineStr"/>
       <c r="Q36" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -4436,7 +4436,7 @@
       <c r="P39" s="8" t="inlineStr"/>
       <c r="Q39" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       <c r="P40" s="8" t="inlineStr"/>
       <c r="Q40" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -4571,7 +4571,7 @@
       <c r="P41" s="8" t="inlineStr"/>
       <c r="Q41" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -4854,7 +4854,7 @@
       <c r="P45" s="8" t="inlineStr"/>
       <c r="Q45" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -5061,7 +5061,7 @@
       <c r="P48" s="8" t="inlineStr"/>
       <c r="Q48" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -5275,7 +5275,7 @@
       <c r="P51" s="8" t="inlineStr"/>
       <c r="Q51" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -5619,7 +5619,7 @@
       <c r="P56" s="8" t="inlineStr"/>
       <c r="Q56" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -5754,7 +5754,7 @@
       <c r="P58" s="8" t="inlineStr"/>
       <c r="Q58" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -5956,7 +5956,7 @@
       <c r="P61" s="8" t="inlineStr"/>
       <c r="Q61" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -6024,7 +6024,7 @@
       <c r="P62" s="8" t="inlineStr"/>
       <c r="Q62" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -6093,7 +6093,7 @@
       <c r="P63" s="8" t="inlineStr"/>
       <c r="Q63" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       <c r="P64" s="8" t="inlineStr"/>
       <c r="Q64" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -6227,7 +6227,7 @@
       <c r="P65" s="8" t="inlineStr"/>
       <c r="Q65" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       <c r="P66" s="8" t="inlineStr"/>
       <c r="Q66" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -6362,7 +6362,7 @@
       <c r="P67" s="8" t="inlineStr"/>
       <c r="Q67" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -6430,7 +6430,7 @@
       <c r="P68" s="8" t="inlineStr"/>
       <c r="Q68" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -6497,7 +6497,7 @@
       <c r="P69" s="8" t="inlineStr"/>
       <c r="Q69" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -6564,7 +6564,7 @@
       <c r="P70" s="8" t="inlineStr"/>
       <c r="Q70" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -6631,7 +6631,7 @@
       <c r="P71" s="8" t="inlineStr"/>
       <c r="Q71" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -6698,7 +6698,7 @@
       <c r="P72" s="8" t="inlineStr"/>
       <c r="Q72" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -6765,7 +6765,7 @@
       <c r="P73" s="8" t="inlineStr"/>
       <c r="Q73" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -6833,7 +6833,7 @@
       <c r="P74" s="8" t="inlineStr"/>
       <c r="Q74" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -6900,7 +6900,7 @@
       <c r="P75" s="8" t="inlineStr"/>
       <c r="Q75" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -6967,7 +6967,7 @@
       <c r="P76" s="8" t="inlineStr"/>
       <c r="Q76" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       <c r="P77" s="8" t="inlineStr"/>
       <c r="Q77" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -7101,7 +7101,7 @@
       <c r="P78" s="8" t="inlineStr"/>
       <c r="Q78" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -7168,7 +7168,7 @@
       <c r="P79" s="8" t="inlineStr"/>
       <c r="Q79" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -7236,7 +7236,7 @@
       <c r="P80" s="8" t="inlineStr"/>
       <c r="Q80" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -7304,7 +7304,7 @@
       <c r="P81" s="8" t="inlineStr"/>
       <c r="Q81" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -7447,7 +7447,7 @@
       <c r="P83" s="8" t="inlineStr"/>
       <c r="Q83" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -7515,7 +7515,7 @@
       <c r="P84" s="8" t="inlineStr"/>
       <c r="Q84" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -7582,7 +7582,7 @@
       <c r="P85" s="8" t="inlineStr"/>
       <c r="Q85" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -7649,7 +7649,7 @@
       <c r="P86" s="8" t="inlineStr"/>
       <c r="Q86" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -7716,7 +7716,7 @@
       <c r="P87" s="8" t="inlineStr"/>
       <c r="Q87" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7793,7 @@
       <c r="P88" s="8" t="inlineStr"/>
       <c r="Q88" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -7862,7 +7862,7 @@
       <c r="P89" s="8" t="inlineStr"/>
       <c r="Q89" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7931,7 @@
       <c r="P90" s="8" t="inlineStr"/>
       <c r="Q90" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       <c r="P91" s="8" t="inlineStr"/>
       <c r="Q91" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -8523,7 +8523,7 @@
       <c r="P98" s="8" t="inlineStr"/>
       <c r="Q98" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -8666,7 +8666,7 @@
       <c r="P100" s="8" t="inlineStr"/>
       <c r="Q100" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -8874,7 +8874,7 @@
       <c r="P103" s="8" t="inlineStr"/>
       <c r="Q103" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -8941,7 +8941,7 @@
       <c r="P104" s="8" t="inlineStr"/>
       <c r="Q104" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -9008,7 +9008,7 @@
       <c r="P105" s="8" t="inlineStr"/>
       <c r="Q105" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -9083,7 +9083,7 @@
       <c r="P106" s="8" t="inlineStr"/>
       <c r="Q106" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -9150,7 +9150,7 @@
       <c r="P107" s="8" t="inlineStr"/>
       <c r="Q107" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -9217,7 +9217,7 @@
       <c r="P108" s="8" t="inlineStr"/>
       <c r="Q108" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -9579,7 +9579,7 @@
       <c r="P113" s="8" t="inlineStr"/>
       <c r="Q113" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -9647,7 +9647,7 @@
       <c r="P114" s="8" t="inlineStr"/>
       <c r="Q114" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       <c r="P115" s="8" t="inlineStr"/>
       <c r="Q115" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9784,7 @@
       <c r="P116" s="8" t="inlineStr"/>
       <c r="Q116" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -10053,7 +10053,7 @@
       <c r="P120" s="8" t="inlineStr"/>
       <c r="Q120" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -10120,7 +10120,7 @@
       <c r="P121" s="8" t="inlineStr"/>
       <c r="Q121" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -10531,7 +10531,7 @@
       <c r="P127" s="8" t="inlineStr"/>
       <c r="Q127" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -10750,7 +10750,7 @@
       <c r="P130" s="8" t="inlineStr"/>
       <c r="Q130" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -11045,7 +11045,7 @@
       <c r="P134" s="8" t="inlineStr"/>
       <c r="Q134" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -11112,7 +11112,7 @@
       <c r="P135" s="8" t="inlineStr"/>
       <c r="Q135" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -11179,7 +11179,7 @@
       <c r="P136" s="8" t="inlineStr"/>
       <c r="Q136" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -11533,7 +11533,7 @@
       <c r="P141" s="8" t="inlineStr"/>
       <c r="Q141" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -11825,7 +11825,7 @@
       <c r="P145" s="8" t="inlineStr"/>
       <c r="Q145" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -11893,7 +11893,7 @@
       <c r="P146" s="8" t="inlineStr"/>
       <c r="Q146" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -12050,7 +12050,7 @@
       <c r="P148" s="8" t="inlineStr"/>
       <c r="Q148" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -12606,7 +12606,7 @@
       <c r="P156" s="8" t="inlineStr"/>
       <c r="Q156" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -12674,7 +12674,7 @@
       <c r="P157" s="8" t="inlineStr"/>
       <c r="Q157" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -12741,7 +12741,7 @@
       <c r="P158" s="8" t="inlineStr"/>
       <c r="Q158" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -12816,7 +12816,7 @@
       <c r="P159" s="8" t="inlineStr"/>
       <c r="Q159" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -12885,7 +12885,7 @@
       <c r="P160" s="8" t="inlineStr"/>
       <c r="Q160" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -12953,7 +12953,7 @@
       <c r="P161" s="8" t="inlineStr"/>
       <c r="Q161" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -13030,7 +13030,7 @@
       <c r="P162" s="8" t="inlineStr"/>
       <c r="Q162" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -13097,7 +13097,7 @@
       <c r="P163" s="8" t="inlineStr"/>
       <c r="Q163" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -13324,7 +13324,7 @@
       <c r="P166" s="8" t="inlineStr"/>
       <c r="Q166" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -13391,7 +13391,7 @@
       <c r="P167" s="8" t="inlineStr"/>
       <c r="Q167" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -13468,7 +13468,7 @@
       <c r="P168" s="8" t="inlineStr"/>
       <c r="Q168" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -13535,7 +13535,7 @@
       <c r="P169" s="8" t="inlineStr"/>
       <c r="Q169" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -13602,7 +13602,7 @@
       <c r="P170" s="8" t="inlineStr"/>
       <c r="Q170" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -13677,7 +13677,7 @@
       <c r="P171" s="8" t="inlineStr"/>
       <c r="Q171" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -13753,7 +13753,7 @@
       <c r="P172" s="8" t="inlineStr"/>
       <c r="Q172" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -13888,7 +13888,7 @@
       <c r="P174" s="8" t="inlineStr"/>
       <c r="Q174" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -13955,7 +13955,7 @@
       <c r="P175" s="8" t="inlineStr"/>
       <c r="Q175" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -14022,7 +14022,7 @@
       <c r="P176" s="8" t="inlineStr"/>
       <c r="Q176" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -14241,7 +14241,7 @@
       <c r="P179" s="8" t="inlineStr"/>
       <c r="Q179" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -14308,7 +14308,7 @@
       <c r="P180" s="8" t="inlineStr"/>
       <c r="Q180" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -14385,7 +14385,7 @@
       <c r="P181" s="8" t="inlineStr"/>
       <c r="Q181" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       <c r="P182" s="8" t="inlineStr"/>
       <c r="Q182" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -14521,7 +14521,7 @@
       <c r="P183" s="8" t="inlineStr"/>
       <c r="Q183" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -14597,7 +14597,7 @@
       <c r="P184" s="8" t="inlineStr"/>
       <c r="Q184" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -14815,7 +14815,7 @@
       <c r="P187" s="8" t="inlineStr"/>
       <c r="Q187" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -15017,7 +15017,7 @@
       <c r="P190" s="8" t="inlineStr"/>
       <c r="Q190" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -15296,7 +15296,7 @@
       <c r="P194" s="8" t="inlineStr"/>
       <c r="Q194" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -15371,7 +15371,7 @@
       <c r="P195" s="8" t="inlineStr"/>
       <c r="Q195" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -15449,7 +15449,7 @@
       <c r="P196" s="8" t="inlineStr"/>
       <c r="Q196" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -15516,7 +15516,7 @@
       <c r="P197" s="8" t="inlineStr"/>
       <c r="Q197" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -15593,7 +15593,7 @@
       <c r="P198" s="8" t="inlineStr"/>
       <c r="Q198" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -15670,7 +15670,7 @@
       <c r="P199" s="8" t="inlineStr"/>
       <c r="Q199" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -15737,7 +15737,7 @@
       <c r="P200" s="8" t="inlineStr"/>
       <c r="Q200" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -15879,7 +15879,7 @@
       <c r="P202" s="8" t="inlineStr"/>
       <c r="Q202" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       <c r="P203" s="8" t="inlineStr"/>
       <c r="Q203" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -16030,7 +16030,7 @@
       <c r="P204" s="8" t="inlineStr"/>
       <c r="Q204" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -16172,7 +16172,7 @@
       <c r="P206" s="8" t="inlineStr"/>
       <c r="Q206" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -16306,7 +16306,7 @@
       <c r="P208" s="8" t="inlineStr"/>
       <c r="Q208" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -16728,7 +16728,7 @@
       <c r="P214" s="8" t="inlineStr"/>
       <c r="Q214" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -16940,7 +16940,7 @@
       <c r="P217" s="8" t="inlineStr"/>
       <c r="Q217" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -17007,7 +17007,7 @@
       <c r="P218" s="8" t="inlineStr"/>
       <c r="Q218" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -17075,7 +17075,7 @@
       <c r="P219" s="8" t="inlineStr"/>
       <c r="Q219" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -17210,7 +17210,7 @@
       <c r="P221" s="8" t="inlineStr"/>
       <c r="Q221" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -17346,7 +17346,7 @@
       <c r="P223" s="8" t="inlineStr"/>
       <c r="Q223" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -17413,7 +17413,7 @@
       <c r="P224" s="8" t="inlineStr"/>
       <c r="Q224" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -17547,7 +17547,7 @@
       <c r="P226" s="8" t="inlineStr"/>
       <c r="Q226" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -17690,7 +17690,7 @@
       <c r="P228" s="8" t="inlineStr"/>
       <c r="Q228" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -17757,7 +17757,7 @@
       <c r="P229" s="8" t="inlineStr"/>
       <c r="Q229" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -17984,7 +17984,7 @@
       <c r="P232" s="8" t="inlineStr"/>
       <c r="Q232" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -18260,7 +18260,7 @@
       <c r="P236" s="8" t="inlineStr"/>
       <c r="Q236" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -18328,7 +18328,7 @@
       <c r="P237" s="8" t="inlineStr"/>
       <c r="Q237" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -18396,7 +18396,7 @@
       <c r="P238" s="8" t="inlineStr"/>
       <c r="Q238" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -18606,7 +18606,7 @@
       <c r="P241" s="8" t="inlineStr"/>
       <c r="Q241" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -18673,7 +18673,7 @@
       <c r="P242" s="8" t="inlineStr"/>
       <c r="Q242" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -18874,7 +18874,7 @@
       <c r="P245" s="8" t="inlineStr"/>
       <c r="Q245" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       <c r="P250" s="8" t="inlineStr"/>
       <c r="Q250" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -19282,7 +19282,7 @@
       <c r="P251" s="8" t="inlineStr"/>
       <c r="Q251" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -19349,7 +19349,7 @@
       <c r="P252" s="8" t="inlineStr"/>
       <c r="Q252" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -19416,7 +19416,7 @@
       <c r="P253" s="8" t="inlineStr"/>
       <c r="Q253" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -19483,7 +19483,7 @@
       <c r="P254" s="8" t="inlineStr"/>
       <c r="Q254" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -19751,7 +19751,7 @@
       <c r="P258" s="8" t="inlineStr"/>
       <c r="Q258" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -19983,7 +19983,7 @@
       <c r="P261" s="8" t="inlineStr"/>
       <c r="Q261" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -20050,7 +20050,7 @@
       <c r="P262" s="8" t="inlineStr"/>
       <c r="Q262" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -20117,7 +20117,7 @@
       <c r="P263" s="8" t="inlineStr"/>
       <c r="Q263" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -20185,7 +20185,7 @@
       <c r="P264" s="8" t="inlineStr"/>
       <c r="Q264" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -20550,7 +20550,7 @@
       <c r="P269" s="8" t="inlineStr"/>
       <c r="Q269" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -20769,7 +20769,7 @@
       <c r="P272" s="8" t="inlineStr"/>
       <c r="Q272" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -20903,7 +20903,7 @@
       <c r="P274" s="8" t="inlineStr"/>
       <c r="Q274" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -20970,7 +20970,7 @@
       <c r="P275" s="8" t="inlineStr"/>
       <c r="Q275" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -21560,7 +21560,7 @@
       <c r="P283" s="8" t="inlineStr"/>
       <c r="Q283" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -21871,7 +21871,7 @@
       <c r="P287" s="8" t="inlineStr"/>
       <c r="Q287" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -22022,7 +22022,7 @@
       <c r="P289" s="8" t="inlineStr"/>
       <c r="Q289" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -22097,7 +22097,7 @@
       <c r="P290" s="8" t="inlineStr"/>
       <c r="Q290" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -22173,7 +22173,7 @@
       <c r="P291" s="8" t="inlineStr"/>
       <c r="Q291" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -22315,7 +22315,7 @@
       <c r="P293" s="8" t="inlineStr"/>
       <c r="Q293" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -22382,7 +22382,7 @@
       <c r="P294" s="8" t="inlineStr"/>
       <c r="Q294" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -22449,7 +22449,7 @@
       <c r="P295" s="8" t="inlineStr"/>
       <c r="Q295" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -22517,7 +22517,7 @@
       <c r="P296" s="8" t="inlineStr"/>
       <c r="Q296" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -22726,7 +22726,7 @@
       <c r="P299" s="8" t="inlineStr"/>
       <c r="Q299" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -22928,7 +22928,7 @@
       <c r="P302" s="8" t="inlineStr"/>
       <c r="Q302" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -23330,7 +23330,7 @@
       <c r="P308" s="8" t="inlineStr"/>
       <c r="Q308" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -23397,7 +23397,7 @@
       <c r="P309" s="8" t="inlineStr"/>
       <c r="Q309" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -23736,7 +23736,7 @@
       <c r="P314" s="8" t="inlineStr"/>
       <c r="Q314" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -23874,7 +23874,7 @@
       <c r="P316" s="8" t="inlineStr"/>
       <c r="Q316" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -23941,7 +23941,7 @@
       <c r="P317" s="8" t="inlineStr"/>
       <c r="Q317" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -24231,7 +24231,7 @@
       <c r="P321" s="8" t="inlineStr"/>
       <c r="Q321" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -24681,7 +24681,7 @@
       <c r="P327" s="8" t="inlineStr"/>
       <c r="Q327" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -24748,7 +24748,7 @@
       <c r="P328" s="8" t="inlineStr"/>
       <c r="Q328" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -24882,7 +24882,7 @@
       <c r="P330" s="8" t="inlineStr"/>
       <c r="Q330" s="7" t="inlineStr">
         <is>
-          <t>No execution evidence in the current pass (Sessions 18-24).</t>
+          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
         </is>
       </c>
     </row>
@@ -26910,7 +26910,7 @@
       <c r="P355" s="8" t="inlineStr"/>
       <c r="Q355" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -26986,7 +26986,7 @@
       <c r="P356" s="8" t="inlineStr"/>
       <c r="Q356" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -27822,7 +27822,7 @@
       <c r="P367" s="8" t="inlineStr"/>
       <c r="Q367" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -27974,7 +27974,7 @@
       <c r="P369" s="8" t="inlineStr"/>
       <c r="Q369" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -28658,7 +28658,7 @@
       <c r="P378" s="8" t="inlineStr"/>
       <c r="Q378" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -29342,7 +29342,7 @@
       <c r="P387" s="8" t="inlineStr"/>
       <c r="Q387" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -29494,7 +29494,7 @@
       <c r="P389" s="8" t="inlineStr"/>
       <c r="Q389" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -30026,7 +30026,7 @@
       <c r="P396" s="8" t="inlineStr"/>
       <c r="Q396" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -30102,7 +30102,7 @@
       <c r="P397" s="8" t="inlineStr"/>
       <c r="Q397" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -30178,7 +30178,7 @@
       <c r="P398" s="8" t="inlineStr"/>
       <c r="Q398" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -30254,7 +30254,7 @@
       <c r="P399" s="8" t="inlineStr"/>
       <c r="Q399" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -30330,7 +30330,7 @@
       <c r="P400" s="8" t="inlineStr"/>
       <c r="Q400" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -30406,7 +30406,7 @@
       <c r="P401" s="8" t="inlineStr"/>
       <c r="Q401" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -30482,7 +30482,7 @@
       <c r="P402" s="8" t="inlineStr"/>
       <c r="Q402" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -30558,7 +30558,7 @@
       <c r="P403" s="8" t="inlineStr"/>
       <c r="Q403" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -33394,7 +33394,7 @@
       <c r="P440" s="8" t="inlineStr"/>
       <c r="Q440" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -34238,7 +34238,7 @@
       <c r="P451" s="8" t="inlineStr"/>
       <c r="Q451" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -34770,7 +34770,7 @@
       <c r="P458" s="8" t="inlineStr"/>
       <c r="Q458" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -35310,7 +35310,7 @@
       <c r="P465" s="8" t="inlineStr"/>
       <c r="Q465" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -35462,7 +35462,7 @@
       <c r="P467" s="8" t="inlineStr"/>
       <c r="Q467" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -35766,7 +35766,7 @@
       <c r="P471" s="8" t="inlineStr"/>
       <c r="Q471" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -35918,7 +35918,7 @@
       <c r="P473" s="8" t="inlineStr"/>
       <c r="Q473" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -36906,7 +36906,7 @@
       <c r="P486" s="8" t="inlineStr"/>
       <c r="Q486" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -36982,7 +36982,7 @@
       <c r="P487" s="8" t="inlineStr"/>
       <c r="Q487" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -37058,7 +37058,7 @@
       <c r="P488" s="8" t="inlineStr"/>
       <c r="Q488" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -37286,7 +37286,7 @@
       <c r="P491" s="8" t="inlineStr"/>
       <c r="Q491" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -37590,7 +37590,7 @@
       <c r="P495" s="8" t="inlineStr"/>
       <c r="Q495" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -38586,7 +38586,7 @@
       <c r="P508" s="8" t="inlineStr"/>
       <c r="Q508" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -39118,7 +39118,7 @@
       <c r="P515" s="8" t="inlineStr"/>
       <c r="Q515" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -39270,7 +39270,7 @@
       <c r="P517" s="8" t="inlineStr"/>
       <c r="Q517" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -39750,7 +39750,7 @@
       <c r="P523" s="8" t="inlineStr"/>
       <c r="Q523" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -39902,7 +39902,7 @@
       <c r="P525" s="8" t="inlineStr"/>
       <c r="Q525" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -40138,7 +40138,7 @@
       <c r="P528" s="8" t="inlineStr"/>
       <c r="Q528" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -40366,7 +40366,7 @@
       <c r="P531" s="8" t="inlineStr"/>
       <c r="Q531" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -41705,7 +41705,7 @@
       <c r="P548" s="8" t="inlineStr"/>
       <c r="Q548" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -41857,7 +41857,7 @@
       <c r="P550" s="8" t="inlineStr"/>
       <c r="Q550" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -42017,7 +42017,7 @@
       <c r="P552" s="8" t="inlineStr"/>
       <c r="Q552" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -42093,7 +42093,7 @@
       <c r="P553" s="8" t="inlineStr"/>
       <c r="Q553" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -42169,7 +42169,7 @@
       <c r="P554" s="8" t="inlineStr"/>
       <c r="Q554" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -42397,7 +42397,7 @@
       <c r="P557" s="8" t="inlineStr"/>
       <c r="Q557" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -43233,7 +43233,7 @@
       <c r="P568" s="8" t="inlineStr"/>
       <c r="Q568" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -43621,7 +43621,7 @@
       <c r="P573" s="8" t="inlineStr"/>
       <c r="Q573" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -43697,7 +43697,7 @@
       <c r="P574" s="8" t="inlineStr"/>
       <c r="Q574" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -43773,7 +43773,7 @@
       <c r="P575" s="8" t="inlineStr"/>
       <c r="Q575" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -43849,7 +43849,7 @@
       <c r="P576" s="8" t="inlineStr"/>
       <c r="Q576" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -43925,7 +43925,7 @@
       <c r="P577" s="8" t="inlineStr"/>
       <c r="Q577" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -44001,7 +44001,7 @@
       <c r="P578" s="8" t="inlineStr"/>
       <c r="Q578" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -44077,7 +44077,7 @@
       <c r="P579" s="8" t="inlineStr"/>
       <c r="Q579" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -44153,7 +44153,7 @@
       <c r="P580" s="8" t="inlineStr"/>
       <c r="Q580" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -44229,7 +44229,7 @@
       <c r="P581" s="8" t="inlineStr"/>
       <c r="Q581" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -44685,7 +44685,7 @@
       <c r="P587" s="8" t="inlineStr"/>
       <c r="Q587" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -44761,7 +44761,7 @@
       <c r="P588" s="8" t="inlineStr"/>
       <c r="Q588" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -44989,7 +44989,7 @@
       <c r="P591" s="8" t="inlineStr"/>
       <c r="Q591" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -45149,7 +45149,7 @@
       <c r="P593" s="8" t="inlineStr"/>
       <c r="Q593" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -45225,7 +45225,7 @@
       <c r="P594" s="8" t="inlineStr"/>
       <c r="Q594" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -45377,7 +45377,7 @@
       <c r="P596" s="8" t="inlineStr"/>
       <c r="Q596" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -45909,7 +45909,7 @@
       <c r="P603" s="8" t="inlineStr"/>
       <c r="Q603" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -45985,7 +45985,7 @@
       <c r="P604" s="8" t="inlineStr"/>
       <c r="Q604" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -46745,7 +46745,7 @@
       <c r="P614" s="8" t="inlineStr"/>
       <c r="Q614" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -48417,7 +48417,7 @@
       <c r="P636" s="8" t="inlineStr"/>
       <c r="Q636" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -48493,7 +48493,7 @@
       <c r="P637" s="8" t="inlineStr"/>
       <c r="Q637" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -49481,7 +49481,7 @@
       <c r="P650" s="8" t="inlineStr"/>
       <c r="Q650" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -49557,7 +49557,7 @@
       <c r="P651" s="8" t="inlineStr"/>
       <c r="Q651" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -49633,7 +49633,7 @@
       <c r="P652" s="8" t="inlineStr"/>
       <c r="Q652" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -49785,7 +49785,7 @@
       <c r="P654" s="8" t="inlineStr"/>
       <c r="Q654" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -50325,7 +50325,7 @@
       <c r="P661" s="8" t="inlineStr"/>
       <c r="Q661" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -50553,7 +50553,7 @@
       <c r="P664" s="8" t="inlineStr"/>
       <c r="Q664" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -50705,7 +50705,7 @@
       <c r="P666" s="8" t="inlineStr"/>
       <c r="Q666" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -50857,7 +50857,7 @@
       <c r="P668" s="8" t="inlineStr"/>
       <c r="Q668" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -50933,7 +50933,7 @@
       <c r="P669" s="8" t="inlineStr"/>
       <c r="Q669" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -51009,7 +51009,7 @@
       <c r="P670" s="8" t="inlineStr"/>
       <c r="Q670" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -51473,7 +51473,7 @@
       <c r="P676" s="8" t="inlineStr"/>
       <c r="Q676" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -51625,7 +51625,7 @@
       <c r="P678" s="8" t="inlineStr"/>
       <c r="Q678" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -51777,7 +51777,7 @@
       <c r="P680" s="8" t="inlineStr"/>
       <c r="Q680" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -51853,7 +51853,7 @@
       <c r="P681" s="8" t="inlineStr"/>
       <c r="Q681" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -51929,7 +51929,7 @@
       <c r="P682" s="8" t="inlineStr"/>
       <c r="Q682" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -52309,7 +52309,7 @@
       <c r="P687" s="8" t="inlineStr"/>
       <c r="Q687" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -52385,7 +52385,7 @@
       <c r="P688" s="8" t="inlineStr"/>
       <c r="Q688" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -52461,7 +52461,7 @@
       <c r="P689" s="8" t="inlineStr"/>
       <c r="Q689" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>
@@ -52613,7 +52613,7 @@
       <c r="P691" s="8" t="inlineStr"/>
       <c r="Q691" s="7" t="inlineStr">
         <is>
-          <t>Deferred to manual QA / dev calc-contract - deep field/calc/dropdown checks not driven in the MCP pass.</t>
+          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
         </is>
       </c>
     </row>

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -1293,11 +1293,11 @@
         </is>
       </c>
       <c r="B85" s="5" t="n">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>54%</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
         </is>
       </c>
       <c r="B86" s="5" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
@@ -1323,11 +1323,11 @@
         </is>
       </c>
       <c r="B87" s="5" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>5%</t>
         </is>
       </c>
     </row>
@@ -1338,11 +1338,11 @@
         </is>
       </c>
       <c r="B88" s="5" t="n">
-        <v>261</v>
+        <v>243</v>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>32%</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Executed (Pass+Fail): 472  |  Pass rate of executed: 86%</t>
+          <t>Executed (Pass+Fail): 485  |  Pass rate of executed: 85%</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>6 / 0 / 0 / 12</t>
+          <t>12 / 1 / 3 / 2</t>
         </is>
       </c>
     </row>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>6 / 4 / 5 / 8</t>
+          <t>8 / 8 / 7 / 0</t>
         </is>
       </c>
     </row>
@@ -15287,16 +15287,24 @@
       </c>
       <c r="L194" s="7" t="inlineStr"/>
       <c r="M194" s="7" t="inlineStr"/>
-      <c r="N194" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O194" s="7" t="inlineStr"/>
-      <c r="P194" s="8" t="inlineStr"/>
+      <c r="N194" s="15" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O194" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: Shelf Life Duration renders as a numeric spinbutton (+ Shelf Life Tested checkbox + frequency unit Days/Weeks/Months/Years per meta) - NOT a free-text field (e.g. "12 months") as the test expects.</t>
+        </is>
+      </c>
+      <c r="P194" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="Q194" s="7" t="inlineStr">
         <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
+          <t>Shelf-life is numeric+unit, not free text.</t>
         </is>
       </c>
     </row>
@@ -15362,18 +15370,18 @@
           <t>BRD: Available Months drive the Monthly Production Tracker (checkbox-table model, per wireframe).</t>
         </is>
       </c>
-      <c r="N195" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O195" s="7" t="inlineStr"/>
+      <c r="N195" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O195" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: Available Months is a 12-row Jan-Dec checkbox table (Month/State/Available?) with 0/12 counter + Select all/Clear all + helper text "These selections control which months appear in the Monthly Production Tracker" - exactly as specified.</t>
+        </is>
+      </c>
       <c r="P195" s="8" t="inlineStr"/>
-      <c r="Q195" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q195" s="7" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="7" t="inlineStr">
@@ -15440,18 +15448,18 @@
           <t>BRD: Process Flow drag-drop (bug fixed from QA bug tracker).</t>
         </is>
       </c>
-      <c r="N196" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O196" s="7" t="inlineStr"/>
+      <c r="N196" s="16" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O196" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: Process Flow tab present, but build-by-drag-from-palette and drag-handle reorder are drag-drop interactions that need manual interaction QA (not reliably scriptable via the automation driver).</t>
+        </is>
+      </c>
       <c r="P196" s="8" t="inlineStr"/>
-      <c r="Q196" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q196" s="7" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="7" t="inlineStr">
@@ -15507,18 +15515,18 @@
       </c>
       <c r="L197" s="7" t="inlineStr"/>
       <c r="M197" s="7" t="inlineStr"/>
-      <c r="N197" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O197" s="7" t="inlineStr"/>
+      <c r="N197" s="16" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O197" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: Process Flow tab present, but build-by-drag-from-palette and drag-handle reorder are drag-drop interactions that need manual interaction QA (not reliably scriptable via the automation driver).</t>
+        </is>
+      </c>
       <c r="P197" s="8" t="inlineStr"/>
-      <c r="Q197" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q197" s="7" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="7" t="inlineStr">
@@ -15584,18 +15592,18 @@
           <t>BRD: process-flow machines → Machinery Existing rows; Ingredients → Raw Material rows.</t>
         </is>
       </c>
-      <c r="N198" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O198" s="7" t="inlineStr"/>
+      <c r="N198" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O198" s="7" t="inlineStr">
+        <is>
+          <t>META+LIVE: Process Flow tab present; process_flow_table + machinery_flow links wired on the Product. NOTE: the existing-machine cross-fill into Machinery Existing is a server hook (needs a saved product+machine to observe live).</t>
+        </is>
+      </c>
       <c r="P198" s="8" t="inlineStr"/>
-      <c r="Q198" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q198" s="7" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="7" t="inlineStr">
@@ -15661,18 +15669,18 @@
           <t>BRD: SKU = Variant-SubVariant-Weight-Unit join (per wireframe).</t>
         </is>
       </c>
-      <c r="N199" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O199" s="7" t="inlineStr"/>
+      <c r="N199" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O199" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: Product Variants tab + Add Row gives a variant grid (Variant Status Existing/Required, Variant Name, Sub Variant, Net Weight, Unit, L/B/H); SKU auto-generates on save (verified live in RUN-7: sku_code "Wildflower Raw-250gram").</t>
+        </is>
+      </c>
       <c r="P199" s="8" t="inlineStr"/>
-      <c r="Q199" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q199" s="7" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="7" t="inlineStr">
@@ -15728,18 +15736,18 @@
       </c>
       <c r="L200" s="7" t="inlineStr"/>
       <c r="M200" s="7" t="inlineStr"/>
-      <c r="N200" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O200" s="7" t="inlineStr"/>
+      <c r="N200" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O200" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: the variant grid has no Retail Price column and Product SKU meta carries no retail_price - the read-only retail-price-fetched-from-Unit-Pricing is not surfaced on the variant row (consistent with RUN-10 CVR-0410).</t>
+        </is>
+      </c>
       <c r="P200" s="8" t="inlineStr"/>
-      <c r="Q200" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q200" s="7" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="7" t="inlineStr">
@@ -15870,18 +15878,18 @@
           <t>BRD Decision: Variants → Labels &amp; Packaging is dropdown selection, not auto-prepopulate.</t>
         </is>
       </c>
-      <c r="N202" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O202" s="7" t="inlineStr"/>
+      <c r="N202" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O202" s="7" t="inlineStr">
+        <is>
+          <t>META+LIVE: Packaging Child product_sku is a Link to Product SKU - variants/SKU act as the picker for downstream frameworks (Packaging confirmed; Labels gated by DF Labels 403).</t>
+        </is>
+      </c>
       <c r="P202" s="8" t="inlineStr"/>
-      <c r="Q202" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q202" s="7" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="7" t="inlineStr">
@@ -15946,18 +15954,18 @@
           <t>BRD QA fix: Production per month auto-fetched.</t>
         </is>
       </c>
-      <c r="N203" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O203" s="7" t="inlineStr"/>
+      <c r="N203" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O203" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: Production Capacity &amp; Revenue tab present with the monthly tracker (placeholder "Select months in Product Availability and add SKU variants to see the monthly production tracker") - tracker is gated on months+variants. NOTE: the Unit-Pricing monthly auto-fetch is a server/link hook, not driven live this pass.</t>
+        </is>
+      </c>
       <c r="P203" s="8" t="inlineStr"/>
-      <c r="Q203" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q203" s="7" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="7" t="inlineStr">
@@ -16297,18 +16305,18 @@
       </c>
       <c r="L208" s="7" t="inlineStr"/>
       <c r="M208" s="7" t="inlineStr"/>
-      <c r="N208" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O208" s="7" t="inlineStr"/>
+      <c r="N208" s="16" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O208" s="7" t="inlineStr">
+        <is>
+          <t>Variant-table render at 20+ rows is a bulk-render/perf check needing a loaded fixture or manual bulk entry; not driven this pass.</t>
+        </is>
+      </c>
       <c r="P208" s="8" t="inlineStr"/>
-      <c r="Q208" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q208" s="7" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="7" t="inlineStr">
@@ -20760,18 +20768,18 @@
       </c>
       <c r="L272" s="7" t="inlineStr"/>
       <c r="M272" s="7" t="inlineStr"/>
-      <c r="N272" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O272" s="7" t="inlineStr"/>
+      <c r="N272" s="16" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O272" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: the landscape API still exposes only the single status field (selection_status/engagement_status not deployed) - the MET/Incubated/Supported pill colour semantics depend on the not-yet-deployed two-field model; held until the full redeploy.</t>
+        </is>
+      </c>
       <c r="P272" s="8" t="inlineStr"/>
-      <c r="Q272" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q272" s="7" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" s="7" t="inlineStr">
@@ -20894,16 +20902,24 @@
       </c>
       <c r="L274" s="7" t="inlineStr"/>
       <c r="M274" s="7" t="inlineStr"/>
-      <c r="N274" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O274" s="7" t="inlineStr"/>
-      <c r="P274" s="8" t="inlineStr"/>
+      <c r="N274" s="15" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O274" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: no Sankey diagram present on the Entrepreneurial Landscape (the only analytics dashboard in CT-IT nav) - the dashboard is a Leaflet map + KPI cards. MET-&gt;Incubated/Supported-&gt;Sectors-&gt;Baskets Sankey not rendered. Verify vs BRD whether a Sankey is in scope.</t>
+        </is>
+      </c>
+      <c r="P274" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
       <c r="Q274" s="7" t="inlineStr">
         <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
+          <t>Sankey not rendered on dashboard.</t>
         </is>
       </c>
     </row>
@@ -20961,16 +20977,24 @@
       </c>
       <c r="L275" s="7" t="inlineStr"/>
       <c r="M275" s="7" t="inlineStr"/>
-      <c r="N275" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O275" s="7" t="inlineStr"/>
-      <c r="P275" s="8" t="inlineStr"/>
+      <c r="N275" s="15" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O275" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: no View-as-table toggle found (it depends on the Sankey, which is not present).</t>
+        </is>
+      </c>
+      <c r="P275" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="Q275" s="7" t="inlineStr">
         <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
+          <t>No view-as-table toggle.</t>
         </is>
       </c>
     </row>
@@ -21551,16 +21575,24 @@
           <t>BRD: District→Block cascade.</t>
         </is>
       </c>
-      <c r="N283" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O283" s="7" t="inlineStr"/>
-      <c r="P283" s="8" t="inlineStr"/>
+      <c r="N283" s="15" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O283" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: dashboard filter bar = Sector / Business Basket / Cohort / Stage / Status only - NO District or Block cascade filter present. Matches the S15 finding.</t>
+        </is>
+      </c>
+      <c r="P283" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
       <c r="Q283" s="7" t="inlineStr">
         <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
+          <t>No District/Block cascade filter on dashboard.</t>
         </is>
       </c>
     </row>
@@ -21862,18 +21894,18 @@
           <t>BRD: geo-tag capture.</t>
         </is>
       </c>
-      <c r="N287" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O287" s="7" t="inlineStr"/>
+      <c r="N287" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O287" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: get_landscape_entrepreneurs returns 20 EPs, 12 with non-null lat/lng; GPS Verified KPI shows 12 (60% located) - count cross-checks exactly.</t>
+        </is>
+      </c>
       <c r="P287" s="8" t="inlineStr"/>
-      <c r="Q287" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q287" s="7" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" s="7" t="inlineStr">
@@ -22013,16 +22045,24 @@
           <t>BRD: map boundaries.</t>
         </is>
       </c>
-      <c r="N289" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O289" s="7" t="inlineStr"/>
-      <c r="P289" s="8" t="inlineStr"/>
+      <c r="N289" s="15" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O289" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: Leaflet map renders OSM tiles + 12 markers but NO boundary polygon (overlay-pane path count = 0). No Meghalaya boundary overlay rendered.</t>
+        </is>
+      </c>
+      <c r="P289" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="Q289" s="7" t="inlineStr">
         <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
+          <t>No Meghalaya boundary overlay on map.</t>
         </is>
       </c>
     </row>
@@ -22088,18 +22128,18 @@
           <t>BRD: drill down to block level.</t>
         </is>
       </c>
-      <c r="N290" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O290" s="7" t="inlineStr"/>
+      <c r="N290" s="16" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O290" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: marker clustering is present in the DOM (Leaflet.markercluster), which normally zooms to block on cluster-click, but a clean isolated cluster-click drill-down could not be scripted reliably - needs manual map interaction QA.</t>
+        </is>
+      </c>
       <c r="P290" s="8" t="inlineStr"/>
-      <c r="Q290" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q290" s="7" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" s="7" t="inlineStr">
@@ -22164,18 +22204,18 @@
           <t>BRD: coordinate validation / map boundaries.</t>
         </is>
       </c>
-      <c r="N291" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O291" s="7" t="inlineStr"/>
+      <c r="N291" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O291" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: all 12 GPS coords fall within Meghalaya bounds (lat 25.0-26.2, lng 89.7-92.9); 0 outside. RESOLVES the S15 finding (coords were Mountain View / Delhi defaults) - now clean.</t>
+        </is>
+      </c>
       <c r="P291" s="8" t="inlineStr"/>
-      <c r="Q291" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q291" s="7" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" s="7" t="inlineStr">

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -106,7 +106,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FBF5E5"/>
+        <fgColor rgb="00EDE6D2"/>
       </patternFill>
     </fill>
     <fill>
@@ -116,7 +116,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EDE6D2"/>
+        <fgColor rgb="00FBF5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -1293,11 +1293,11 @@
         </is>
       </c>
       <c r="B85" s="5" t="n">
-        <v>414</v>
+        <v>431</v>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>56%</t>
         </is>
       </c>
     </row>
@@ -1308,11 +1308,11 @@
         </is>
       </c>
       <c r="B86" s="5" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>10%</t>
         </is>
       </c>
     </row>
@@ -1323,11 +1323,11 @@
         </is>
       </c>
       <c r="B87" s="5" t="n">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>11%</t>
         </is>
       </c>
     </row>
@@ -1338,11 +1338,11 @@
         </is>
       </c>
       <c r="B88" s="5" t="n">
-        <v>243</v>
+        <v>174</v>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>23%</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Executed (Pass+Fail): 485  |  Pass rate of executed: 85%</t>
+          <t>Executed (Pass+Fail): 505  |  Pass rate of executed: 85%</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>3 / 1 / 0 / 6</t>
+          <t>8 / 1 / 1 / 0</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>0 / 0 / 0 / 10</t>
+          <t>1 / 0 / 9 / 0</t>
         </is>
       </c>
     </row>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>0 / 0 / 0 / 10</t>
+          <t>3 / 2 / 5 / 0</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>4 / 0 / 7 / 9</t>
+          <t>6 / 1 / 13 / 0</t>
         </is>
       </c>
     </row>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>0 / 0 / 0 / 8</t>
+          <t>1 / 0 / 7 / 0</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>0 / 0 / 0 / 6</t>
+          <t>0 / 0 / 6 / 0</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>12 / 4 / 0 / 14</t>
+          <t>17 / 4 / 9 / 0</t>
         </is>
       </c>
     </row>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>8 / 0 / 0 / 3</t>
+          <t>8 / 0 / 3 / 0</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>2 / 0 / 5 / 3</t>
+          <t>2 / 0 / 8 / 0</t>
         </is>
       </c>
     </row>
@@ -1923,18 +1923,18 @@
           <t>BRD: PR-OV-003, PR-UJ-* (per-role journeys)</t>
         </is>
       </c>
-      <c r="N3" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O3" s="7" t="inlineStr"/>
+      <c r="N3" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O3" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: authenticated CT-IT hitting /primerural lands on the Entrepreneurial Landscape (the CT-IT role landing page).</t>
+        </is>
+      </c>
       <c r="P3" s="8" t="inlineStr"/>
-      <c r="Q3" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q3" s="7" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
@@ -2006,16 +2006,16 @@
       </c>
       <c r="N4" s="14" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O4" s="7" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O4" s="7" t="inlineStr">
+        <is>
+          <t>Deep-link-while-logged-out preserves-intent needs a logged-out session; no inline re-login credentials this pass (would terminate the live CT-IT session).</t>
+        </is>
+      </c>
       <c r="P4" s="8" t="inlineStr"/>
-      <c r="Q4" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q4" s="7" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -2207,18 +2207,18 @@
       </c>
       <c r="L7" s="7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
-      <c r="N7" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O7" s="7" t="inlineStr"/>
+      <c r="N7" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: SPA uses the History API; navigated across many routes (Landscape/Product/User/EP list) and browser back/forward works without full reloads.</t>
+        </is>
+      </c>
       <c r="P7" s="8" t="inlineStr"/>
-      <c r="Q7" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -2351,18 +2351,18 @@
       </c>
       <c r="L9" s="7" t="inlineStr"/>
       <c r="M9" s="7" t="inlineStr"/>
-      <c r="N9" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O9" s="7" t="inlineStr"/>
+      <c r="N9" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O9" s="7" t="inlineStr">
+        <is>
+          <t>Bad/edge routes resolve without a server traceback (RUN-8 bad-route 200-with-empty-state). NOTE: exhaustive trailing/double-slash/uppercase normalization not separately driven.</t>
+        </is>
+      </c>
       <c r="P9" s="8" t="inlineStr"/>
-      <c r="Q9" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -2419,18 +2419,18 @@
       </c>
       <c r="L10" s="7" t="inlineStr"/>
       <c r="M10" s="7" t="inlineStr"/>
-      <c r="N10" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O10" s="7" t="inlineStr"/>
+      <c r="N10" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O10" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: deep-page refresh (F5) reloads the correct route - SPA deep-linking works. NOTE: in-progress unsaved form state is not persisted across a hard refresh (expected).</t>
+        </is>
+      </c>
       <c r="P10" s="8" t="inlineStr"/>
-      <c r="Q10" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q10" s="7" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -2499,18 +2499,18 @@
           <t>OWASP: A01 Broken Access Control. BRD: PR-OV-003.</t>
         </is>
       </c>
-      <c r="N11" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O11" s="7" t="inlineStr"/>
+      <c r="N11" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O11" s="7" t="inlineStr">
+        <is>
+          <t>Manually editing a record name to a non-existent one returns a friendly not-found, no Python traceback (RUN-8). NOTE: a true cross-user 403 needs a record owned by another user + a restricted (non-admin) role.</t>
+        </is>
+      </c>
       <c r="P11" s="8" t="inlineStr"/>
-      <c r="Q11" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -2566,18 +2566,18 @@
       </c>
       <c r="L12" s="7" t="inlineStr"/>
       <c r="M12" s="7" t="inlineStr"/>
-      <c r="N12" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O12" s="7" t="inlineStr"/>
+      <c r="N12" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O12" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: the entire pass runs on the Chromium (Chrome) engine - app loads, login + all flows work.</t>
+        </is>
+      </c>
       <c r="P12" s="8" t="inlineStr"/>
-      <c r="Q12" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -2635,16 +2635,16 @@
       <c r="M13" s="7" t="inlineStr"/>
       <c r="N13" s="14" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O13" s="7" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t>Firefox / Edge / Safari / IE11 / old-Chrome require a real cross-browser matrix; the automation driver is single-engine (Chromium) - cannot certify other engines.</t>
+        </is>
+      </c>
       <c r="P13" s="8" t="inlineStr"/>
-      <c r="Q13" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -2702,16 +2702,16 @@
       <c r="M14" s="7" t="inlineStr"/>
       <c r="N14" s="14" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O14" s="7" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O14" s="7" t="inlineStr">
+        <is>
+          <t>Firefox / Edge / Safari / IE11 / old-Chrome require a real cross-browser matrix; the automation driver is single-engine (Chromium) - cannot certify other engines.</t>
+        </is>
+      </c>
       <c r="P14" s="8" t="inlineStr"/>
-      <c r="Q14" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -2769,16 +2769,16 @@
       <c r="M15" s="7" t="inlineStr"/>
       <c r="N15" s="14" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O15" s="7" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O15" s="7" t="inlineStr">
+        <is>
+          <t>Firefox / Edge / Safari / IE11 / old-Chrome require a real cross-browser matrix; the automation driver is single-engine (Chromium) - cannot certify other engines.</t>
+        </is>
+      </c>
       <c r="P15" s="8" t="inlineStr"/>
-      <c r="Q15" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -2836,16 +2836,16 @@
       <c r="M16" s="7" t="inlineStr"/>
       <c r="N16" s="14" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O16" s="7" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O16" s="7" t="inlineStr">
+        <is>
+          <t>Firefox / Edge / Safari / IE11 / old-Chrome require a real cross-browser matrix; the automation driver is single-engine (Chromium) - cannot certify other engines.</t>
+        </is>
+      </c>
       <c r="P16" s="8" t="inlineStr"/>
-      <c r="Q16" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q16" s="7" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
@@ -2903,16 +2903,16 @@
       <c r="M17" s="7" t="inlineStr"/>
       <c r="N17" s="14" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O17" s="7" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O17" s="7" t="inlineStr">
+        <is>
+          <t>Firefox / Edge / Safari / IE11 / old-Chrome require a real cross-browser matrix; the automation driver is single-engine (Chromium) - cannot certify other engines.</t>
+        </is>
+      </c>
       <c r="P17" s="8" t="inlineStr"/>
-      <c r="Q17" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
@@ -2972,16 +2972,16 @@
       <c r="M18" s="7" t="inlineStr"/>
       <c r="N18" s="14" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O18" s="7" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O18" s="7" t="inlineStr">
+        <is>
+          <t>Low-end hardware (4 GB RAM / integrated GPU) behaviour needs a real device - not emulatable here.</t>
+        </is>
+      </c>
       <c r="P18" s="8" t="inlineStr"/>
-      <c r="Q18" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q18" s="7" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
@@ -3040,16 +3040,16 @@
       <c r="M19" s="7" t="inlineStr"/>
       <c r="N19" s="14" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O19" s="7" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O19" s="7" t="inlineStr">
+        <is>
+          <t>Slow-3G throttle needs CDP network emulation not exposed through this driver.</t>
+        </is>
+      </c>
       <c r="P19" s="8" t="inlineStr"/>
-      <c r="Q19" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q19" s="7" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
@@ -3109,16 +3109,16 @@
       <c r="M20" s="7" t="inlineStr"/>
       <c r="N20" s="14" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O20" s="7" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O20" s="7" t="inlineStr">
+        <is>
+          <t>Network-drop-mid-save needs mid-flight connection interruption simulation - not available via this driver.</t>
+        </is>
+      </c>
       <c r="P20" s="8" t="inlineStr"/>
-      <c r="Q20" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q20" s="7" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -3186,16 +3186,16 @@
       </c>
       <c r="N21" s="14" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O21" s="7" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O21" s="7" t="inlineStr">
+        <is>
+          <t>Two-simultaneous-tabs-of-same-record concurrency needs two live tabs editing one record - not driven this pass.</t>
+        </is>
+      </c>
       <c r="P21" s="8" t="inlineStr"/>
-      <c r="Q21" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -3252,18 +3252,18 @@
       </c>
       <c r="L22" s="7" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
-      <c r="N22" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O22" s="7" t="inlineStr"/>
+      <c r="N22" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O22" s="7" t="inlineStr">
+        <is>
+          <t>LIVE at 1920: sidebar expanded (240px), no horizontal scroll. NOTE: main content fills the available width (1680px) and is NOT capped at 1280px centred on the list view - minor layout-spec deviation.</t>
+        </is>
+      </c>
       <c r="P22" s="8" t="inlineStr"/>
-      <c r="Q22" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q22" s="7" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
@@ -3320,18 +3320,18 @@
       </c>
       <c r="L23" s="7" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
-      <c r="N23" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O23" s="7" t="inlineStr"/>
+      <c r="N23" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O23" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: resized to 1024 and 800 wide - NO horizontal scroll at any width (scrollWidth==clientWidth); 1366x768 fits comfortably.</t>
+        </is>
+      </c>
       <c r="P23" s="8" t="inlineStr"/>
-      <c r="Q23" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q23" s="7" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
@@ -3387,16 +3387,24 @@
       </c>
       <c r="L24" s="7" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
-      <c r="N24" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O24" s="7" t="inlineStr"/>
-      <c r="P24" s="8" t="inlineStr"/>
+      <c r="N24" s="15" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O24" s="7" t="inlineStr">
+        <is>
+          <t>LIVE at 1024x768: the sidebar stays 240px expanded - it does NOT collapse to an icon rail. Confirms + reproduces the S15 finding.</t>
+        </is>
+      </c>
+      <c r="P24" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="Q24" s="7" t="inlineStr">
         <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
+          <t>Sidebar does not collapse to icon rail at 1024px.</t>
         </is>
       </c>
     </row>
@@ -3454,16 +3462,24 @@
       </c>
       <c r="L25" s="7" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
-      <c r="N25" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O25" s="7" t="inlineStr"/>
-      <c r="P25" s="8" t="inlineStr"/>
+      <c r="N25" s="15" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O25" s="7" t="inlineStr">
+        <is>
+          <t>LIVE at 800x600: the sidebar is still 240px and visible - it does NOT hide behind a toggle. The sidebar is non-responsive across 800-1920.</t>
+        </is>
+      </c>
+      <c r="P25" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="Q25" s="7" t="inlineStr">
         <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
+          <t>Sidebar does not hide at 800px.</t>
         </is>
       </c>
     </row>
@@ -3524,16 +3540,16 @@
       <c r="M26" s="7" t="inlineStr"/>
       <c r="N26" s="14" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O26" s="7" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O26" s="7" t="inlineStr">
+        <is>
+          <t>Browser zoom 50-200% needs page-zoom emulation (CDP Emulation.setPageScaleFactor) not exposed through this driver.</t>
+        </is>
+      </c>
       <c r="P26" s="8" t="inlineStr"/>
-      <c r="Q26" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q26" s="7" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
@@ -3592,16 +3608,16 @@
       <c r="M27" s="7" t="inlineStr"/>
       <c r="N27" s="14" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O27" s="7" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O27" s="7" t="inlineStr">
+        <is>
+          <t>Long-value field distortion not exhaustively driven this pass (needs systematic overflow entry across field types).</t>
+        </is>
+      </c>
       <c r="P27" s="8" t="inlineStr"/>
-      <c r="Q27" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q27" s="7" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
@@ -3660,16 +3676,16 @@
       <c r="M28" s="7" t="inlineStr"/>
       <c r="N28" s="14" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O28" s="7" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O28" s="7" t="inlineStr">
+        <is>
+          <t>Child-table 100+ rows render needs a loaded fixture - not built this pass.</t>
+        </is>
+      </c>
       <c r="P28" s="8" t="inlineStr"/>
-      <c r="Q28" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q28" s="7" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
@@ -3728,16 +3744,16 @@
       <c r="M29" s="7" t="inlineStr"/>
       <c r="N29" s="14" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O29" s="7" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O29" s="7" t="inlineStr">
+        <is>
+          <t>List-view 500+ records render needs a 500-record fixture; staging holds ~20 EPs.</t>
+        </is>
+      </c>
       <c r="P29" s="8" t="inlineStr"/>
-      <c r="Q29" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q29" s="7" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
@@ -3796,16 +3812,16 @@
       <c r="M30" s="7" t="inlineStr"/>
       <c r="N30" s="14" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O30" s="7" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O30" s="7" t="inlineStr">
+        <is>
+          <t>No 1000+-option combobox exists in the build (largest seen: Product Type ~97) - cannot exercise the 1000-option case.</t>
+        </is>
+      </c>
       <c r="P30" s="8" t="inlineStr"/>
-      <c r="Q30" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q30" s="7" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
@@ -3863,18 +3879,18 @@
       </c>
       <c r="L31" s="7" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
-      <c r="N31" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O31" s="7" t="inlineStr"/>
+      <c r="N31" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O31" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: empty-state renders cleanly - the User Manager list shows a tidy "No records found." state; the Landscape shows a "Loading data..." then data.</t>
+        </is>
+      </c>
       <c r="P31" s="8" t="inlineStr"/>
-      <c r="Q31" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q31" s="7" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
@@ -4008,18 +4024,18 @@
           <t>OWASP A07 Auth Failures (do not leak account existence).</t>
         </is>
       </c>
-      <c r="N33" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O33" s="7" t="inlineStr"/>
+      <c r="N33" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O33" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: a wrong-password login returns generic "Invalid login credentials" - does not reveal whether the email exists.</t>
+        </is>
+      </c>
       <c r="P33" s="8" t="inlineStr"/>
-      <c r="Q33" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q33" s="7" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
@@ -4145,16 +4161,16 @@
       <c r="M35" s="7" t="inlineStr"/>
       <c r="N35" s="14" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O35" s="7" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O35" s="7" t="inlineStr">
+        <is>
+          <t>Empty / malformed email client-side rejection happens on the login PAGE (logged-out) - not reachable while holding a live authenticated session.</t>
+        </is>
+      </c>
       <c r="P35" s="8" t="inlineStr"/>
-      <c r="Q35" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q35" s="7" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
@@ -4214,16 +4230,16 @@
       <c r="M36" s="7" t="inlineStr"/>
       <c r="N36" s="14" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O36" s="7" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O36" s="7" t="inlineStr">
+        <is>
+          <t>Empty / malformed email client-side rejection happens on the login PAGE (logged-out) - not reachable while holding a live authenticated session.</t>
+        </is>
+      </c>
       <c r="P36" s="8" t="inlineStr"/>
-      <c r="Q36" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q36" s="7" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
@@ -4287,7 +4303,7 @@
           <t>OWASP A07; Frappe default lockout settings.</t>
         </is>
       </c>
-      <c r="N37" s="16" t="inlineStr">
+      <c r="N37" s="14" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
@@ -4429,16 +4445,16 @@
       <c r="M39" s="7" t="inlineStr"/>
       <c r="N39" s="14" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O39" s="7" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O39" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: reset_password for a real email returned HTTP 502 (gateway / email-send error on staging - SMTP likely not configured) - cannot confirm a reset email is actually delivered.</t>
+        </is>
+      </c>
       <c r="P39" s="8" t="inlineStr"/>
-      <c r="Q39" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q39" s="7" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
@@ -4494,16 +4510,24 @@
       </c>
       <c r="L40" s="7" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
-      <c r="N40" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O40" s="7" t="inlineStr"/>
-      <c r="P40" s="8" t="inlineStr"/>
+      <c r="N40" s="15" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O40" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: reset_password for a NON-existent email returns HTTP 404 {message:not found}, while a real email returns a different response (502) - the differing responses allow user/email enumeration. Should return one generic banner for both.</t>
+        </is>
+      </c>
+      <c r="P40" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
       <c r="Q40" s="7" t="inlineStr">
         <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
+          <t>Password-reset reveals whether an email exists (enumeration).</t>
         </is>
       </c>
     </row>
@@ -4564,16 +4588,16 @@
       <c r="M41" s="7" t="inlineStr"/>
       <c r="N41" s="14" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O41" s="7" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O41" s="7" t="inlineStr">
+        <is>
+          <t>Reset-link-cannot-be-reused needs the emailed reset link (email delivery is 502 on staging) - not drivable.</t>
+        </is>
+      </c>
       <c r="P41" s="8" t="inlineStr"/>
-      <c r="Q41" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q41" s="7" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
@@ -4631,7 +4655,7 @@
       </c>
       <c r="L42" s="7" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
-      <c r="N42" s="16" t="inlineStr">
+      <c r="N42" s="14" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
@@ -4702,7 +4726,7 @@
       </c>
       <c r="L43" s="7" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
-      <c r="N43" s="16" t="inlineStr">
+      <c r="N43" s="14" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
@@ -4773,7 +4797,7 @@
       </c>
       <c r="L44" s="7" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
-      <c r="N44" s="16" t="inlineStr">
+      <c r="N44" s="14" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
@@ -4847,16 +4871,16 @@
       <c r="M45" s="7" t="inlineStr"/>
       <c r="N45" s="14" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O45" s="7" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O45" s="7" t="inlineStr">
+        <is>
+          <t>Logout-terminates-session would end the live CT-IT session and there are no inline re-login credentials this pass.</t>
+        </is>
+      </c>
       <c r="P45" s="8" t="inlineStr"/>
-      <c r="Q45" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q45" s="7" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
@@ -4913,7 +4937,7 @@
       </c>
       <c r="L46" s="7" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
-      <c r="N46" s="16" t="inlineStr">
+      <c r="N46" s="14" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
@@ -5052,18 +5076,18 @@
       </c>
       <c r="L48" s="7" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
-      <c r="N48" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O48" s="7" t="inlineStr"/>
+      <c r="N48" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O48" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: a state-changing POST (/api/resource/ToDo) WITHOUT the X-Frappe-CSRF-Token is rejected with HTTP 400 CSRFTokenError.</t>
+        </is>
+      </c>
       <c r="P48" s="8" t="inlineStr"/>
-      <c r="Q48" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q48" s="7" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
@@ -5122,7 +5146,7 @@
       </c>
       <c r="L49" s="7" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
-      <c r="N49" s="16" t="inlineStr">
+      <c r="N49" s="14" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
@@ -5195,7 +5219,7 @@
       </c>
       <c r="L50" s="7" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
-      <c r="N50" s="16" t="inlineStr">
+      <c r="N50" s="14" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
@@ -5268,16 +5292,16 @@
       <c r="M51" s="7" t="inlineStr"/>
       <c r="N51" s="14" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O51" s="7" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O51" s="7" t="inlineStr">
+        <is>
+          <t>Remember-me session extension is a login-page feature - not reachable while authenticated.</t>
+        </is>
+      </c>
       <c r="P51" s="8" t="inlineStr"/>
-      <c r="Q51" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q51" s="7" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
@@ -5610,7 +5634,7 @@
       </c>
       <c r="L56" s="7" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
-      <c r="N56" s="14" t="inlineStr">
+      <c r="N56" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -5745,7 +5769,7 @@
       </c>
       <c r="L58" s="7" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
-      <c r="N58" s="14" t="inlineStr">
+      <c r="N58" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -5947,7 +5971,7 @@
       </c>
       <c r="L61" s="7" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
-      <c r="N61" s="14" t="inlineStr">
+      <c r="N61" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -6017,16 +6041,16 @@
       <c r="M62" s="7" t="inlineStr"/>
       <c r="N62" s="14" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O62" s="7" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O62" s="7" t="inlineStr">
+        <is>
+          <t>WCAG keyboard-reachability / focus-trap / axe label rule / colour-contrast / chart aria / reduced-motion / SR route-announce need axe-core + a screen reader + automated a11y tooling - not available through this driver.</t>
+        </is>
+      </c>
       <c r="P62" s="8" t="inlineStr"/>
-      <c r="Q62" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q62" s="7" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
@@ -6086,16 +6110,16 @@
       <c r="M63" s="7" t="inlineStr"/>
       <c r="N63" s="14" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O63" s="7" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O63" s="7" t="inlineStr">
+        <is>
+          <t>WCAG keyboard-reachability / focus-trap / axe label rule / colour-contrast / chart aria / reduced-motion / SR route-announce need axe-core + a screen reader + automated a11y tooling - not available through this driver.</t>
+        </is>
+      </c>
       <c r="P63" s="8" t="inlineStr"/>
-      <c r="Q63" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q63" s="7" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
@@ -6153,16 +6177,16 @@
       <c r="M64" s="7" t="inlineStr"/>
       <c r="N64" s="14" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O64" s="7" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O64" s="7" t="inlineStr">
+        <is>
+          <t>WCAG keyboard-reachability / focus-trap / axe label rule / colour-contrast / chart aria / reduced-motion / SR route-announce need axe-core + a screen reader + automated a11y tooling - not available through this driver.</t>
+        </is>
+      </c>
       <c r="P64" s="8" t="inlineStr"/>
-      <c r="Q64" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q64" s="7" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
@@ -6220,16 +6244,16 @@
       <c r="M65" s="7" t="inlineStr"/>
       <c r="N65" s="14" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O65" s="7" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O65" s="7" t="inlineStr">
+        <is>
+          <t>WCAG keyboard-reachability / focus-trap / axe label rule / colour-contrast / chart aria / reduced-motion / SR route-announce need axe-core + a screen reader + automated a11y tooling - not available through this driver.</t>
+        </is>
+      </c>
       <c r="P65" s="8" t="inlineStr"/>
-      <c r="Q65" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q65" s="7" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
@@ -6287,16 +6311,16 @@
       <c r="M66" s="7" t="inlineStr"/>
       <c r="N66" s="14" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O66" s="7" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O66" s="7" t="inlineStr">
+        <is>
+          <t>WCAG keyboard-reachability / focus-trap / axe label rule / colour-contrast / chart aria / reduced-motion / SR route-announce need axe-core + a screen reader + automated a11y tooling - not available through this driver.</t>
+        </is>
+      </c>
       <c r="P66" s="8" t="inlineStr"/>
-      <c r="Q66" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q66" s="7" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
@@ -6355,16 +6379,16 @@
       <c r="M67" s="7" t="inlineStr"/>
       <c r="N67" s="14" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O67" s="7" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O67" s="7" t="inlineStr">
+        <is>
+          <t>WCAG keyboard-reachability / focus-trap / axe label rule / colour-contrast / chart aria / reduced-motion / SR route-announce need axe-core + a screen reader + automated a11y tooling - not available through this driver.</t>
+        </is>
+      </c>
       <c r="P67" s="8" t="inlineStr"/>
-      <c r="Q67" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q67" s="7" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
@@ -6423,16 +6447,16 @@
       <c r="M68" s="7" t="inlineStr"/>
       <c r="N68" s="14" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O68" s="7" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O68" s="7" t="inlineStr">
+        <is>
+          <t>WCAG keyboard-reachability / focus-trap / axe label rule / colour-contrast / chart aria / reduced-motion / SR route-announce need axe-core + a screen reader + automated a11y tooling - not available through this driver.</t>
+        </is>
+      </c>
       <c r="P68" s="8" t="inlineStr"/>
-      <c r="Q68" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q68" s="7" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
@@ -6488,18 +6512,18 @@
       </c>
       <c r="L69" s="7" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr"/>
-      <c r="N69" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O69" s="7" t="inlineStr"/>
+      <c r="N69" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O69" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: status/KPI elements carry text labels alongside colour (MET Entrepreneurs / GPS Verified / Districts Covered etc. all have visible text) - colour is not the only signal on the dashboard KPIs.</t>
+        </is>
+      </c>
       <c r="P69" s="8" t="inlineStr"/>
-      <c r="Q69" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q69" s="7" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
@@ -6557,16 +6581,16 @@
       <c r="M70" s="7" t="inlineStr"/>
       <c r="N70" s="14" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O70" s="7" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O70" s="7" t="inlineStr">
+        <is>
+          <t>FCP / load-time / save round-trip / filter-latency / 30-min memory-leak / N+1 baselines need Lighthouse + sustained perf instrumentation - not measurable reliably through this driver in a single pass.</t>
+        </is>
+      </c>
       <c r="P70" s="8" t="inlineStr"/>
-      <c r="Q70" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q70" s="7" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
@@ -6624,16 +6648,16 @@
       <c r="M71" s="7" t="inlineStr"/>
       <c r="N71" s="14" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O71" s="7" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O71" s="7" t="inlineStr">
+        <is>
+          <t>FCP / load-time / save round-trip / filter-latency / 30-min memory-leak / N+1 baselines need Lighthouse + sustained perf instrumentation - not measurable reliably through this driver in a single pass.</t>
+        </is>
+      </c>
       <c r="P71" s="8" t="inlineStr"/>
-      <c r="Q71" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q71" s="7" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
@@ -6691,16 +6715,16 @@
       <c r="M72" s="7" t="inlineStr"/>
       <c r="N72" s="14" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O72" s="7" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O72" s="7" t="inlineStr">
+        <is>
+          <t>FCP / load-time / save round-trip / filter-latency / 30-min memory-leak / N+1 baselines need Lighthouse + sustained perf instrumentation - not measurable reliably through this driver in a single pass.</t>
+        </is>
+      </c>
       <c r="P72" s="8" t="inlineStr"/>
-      <c r="Q72" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q72" s="7" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
@@ -6758,16 +6782,16 @@
       <c r="M73" s="7" t="inlineStr"/>
       <c r="N73" s="14" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O73" s="7" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O73" s="7" t="inlineStr">
+        <is>
+          <t>FCP / load-time / save round-trip / filter-latency / 30-min memory-leak / N+1 baselines need Lighthouse + sustained perf instrumentation - not measurable reliably through this driver in a single pass.</t>
+        </is>
+      </c>
       <c r="P73" s="8" t="inlineStr"/>
-      <c r="Q73" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q73" s="7" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
@@ -6826,16 +6850,16 @@
       <c r="M74" s="7" t="inlineStr"/>
       <c r="N74" s="14" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O74" s="7" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O74" s="7" t="inlineStr">
+        <is>
+          <t>FCP / load-time / save round-trip / filter-latency / 30-min memory-leak / N+1 baselines need Lighthouse + sustained perf instrumentation - not measurable reliably through this driver in a single pass.</t>
+        </is>
+      </c>
       <c r="P74" s="8" t="inlineStr"/>
-      <c r="Q74" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q74" s="7" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
@@ -6893,16 +6917,16 @@
       <c r="M75" s="7" t="inlineStr"/>
       <c r="N75" s="14" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O75" s="7" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O75" s="7" t="inlineStr">
+        <is>
+          <t>FCP / load-time / save round-trip / filter-latency / 30-min memory-leak / N+1 baselines need Lighthouse + sustained perf instrumentation - not measurable reliably through this driver in a single pass.</t>
+        </is>
+      </c>
       <c r="P75" s="8" t="inlineStr"/>
-      <c r="Q75" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q75" s="7" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
@@ -6958,7 +6982,7 @@
       </c>
       <c r="L76" s="7" t="inlineStr"/>
       <c r="M76" s="7" t="inlineStr"/>
-      <c r="N76" s="14" t="inlineStr">
+      <c r="N76" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -7025,7 +7049,7 @@
       </c>
       <c r="L77" s="7" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr"/>
-      <c r="N77" s="14" t="inlineStr">
+      <c r="N77" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -7092,7 +7116,7 @@
       </c>
       <c r="L78" s="7" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr"/>
-      <c r="N78" s="14" t="inlineStr">
+      <c r="N78" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -7159,7 +7183,7 @@
       </c>
       <c r="L79" s="7" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr"/>
-      <c r="N79" s="14" t="inlineStr">
+      <c r="N79" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -7227,7 +7251,7 @@
       </c>
       <c r="L80" s="7" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr"/>
-      <c r="N80" s="14" t="inlineStr">
+      <c r="N80" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -7295,7 +7319,7 @@
       </c>
       <c r="L81" s="7" t="inlineStr"/>
       <c r="M81" s="7" t="inlineStr"/>
-      <c r="N81" s="14" t="inlineStr">
+      <c r="N81" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -7438,7 +7462,7 @@
       </c>
       <c r="L83" s="7" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr"/>
-      <c r="N83" s="14" t="inlineStr">
+      <c r="N83" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -7506,7 +7530,7 @@
       </c>
       <c r="L84" s="7" t="inlineStr"/>
       <c r="M84" s="7" t="inlineStr"/>
-      <c r="N84" s="14" t="inlineStr">
+      <c r="N84" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -7573,7 +7597,7 @@
       </c>
       <c r="L85" s="7" t="inlineStr"/>
       <c r="M85" s="7" t="inlineStr"/>
-      <c r="N85" s="14" t="inlineStr">
+      <c r="N85" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -7640,7 +7664,7 @@
       </c>
       <c r="L86" s="7" t="inlineStr"/>
       <c r="M86" s="7" t="inlineStr"/>
-      <c r="N86" s="14" t="inlineStr">
+      <c r="N86" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -7707,7 +7731,7 @@
       </c>
       <c r="L87" s="7" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr"/>
-      <c r="N87" s="14" t="inlineStr">
+      <c r="N87" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -7784,7 +7808,7 @@
           <t>Verhoeff checksum required for compliance.</t>
         </is>
       </c>
-      <c r="N88" s="14" t="inlineStr">
+      <c r="N88" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -7853,7 +7877,7 @@
       </c>
       <c r="L89" s="7" t="inlineStr"/>
       <c r="M89" s="7" t="inlineStr"/>
-      <c r="N89" s="14" t="inlineStr">
+      <c r="N89" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -7922,7 +7946,7 @@
       </c>
       <c r="L90" s="7" t="inlineStr"/>
       <c r="M90" s="7" t="inlineStr"/>
-      <c r="N90" s="14" t="inlineStr">
+      <c r="N90" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -7991,7 +8015,7 @@
       </c>
       <c r="L91" s="7" t="inlineStr"/>
       <c r="M91" s="7" t="inlineStr"/>
-      <c r="N91" s="14" t="inlineStr">
+      <c r="N91" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -8514,18 +8538,18 @@
       </c>
       <c r="L98" s="7" t="inlineStr"/>
       <c r="M98" s="7" t="inlineStr"/>
-      <c r="N98" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O98" s="7" t="inlineStr"/>
+      <c r="N98" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O98" s="7" t="inlineStr">
+        <is>
+          <t>Frappe imposes no role-conflict rule - System Manager can coexist with any role; the build adds no such validation. NOTE: flag vs BRD whether conflicting-role prevention is actually required (would need a custom validate hook).</t>
+        </is>
+      </c>
       <c r="P98" s="8" t="inlineStr"/>
-      <c r="Q98" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q98" s="7" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
@@ -8657,18 +8681,18 @@
       </c>
       <c r="L100" s="7" t="inlineStr"/>
       <c r="M100" s="7" t="inlineStr"/>
-      <c r="N100" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O100" s="7" t="inlineStr"/>
+      <c r="N100" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O100" s="7" t="inlineStr">
+        <is>
+          <t>Frappe core lowercases + trims User.email on validate (framework behaviour). NOTE: scripted API create hit a custom server hook 500 (NoneType.strip), so the normalization was not independently re-driven this pass.</t>
+        </is>
+      </c>
       <c r="P100" s="8" t="inlineStr"/>
-      <c r="Q100" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q100" s="7" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="7" t="inlineStr">
@@ -8867,16 +8891,16 @@
       <c r="M103" s="7" t="inlineStr"/>
       <c r="N103" s="14" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O103" s="7" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O103" s="7" t="inlineStr">
+        <is>
+          <t>Session-revoke-within-60s of deactivation is a timing/infra check - needs two concurrent sessions + clock observation; not scriptable in this pass.</t>
+        </is>
+      </c>
       <c r="P103" s="8" t="inlineStr"/>
-      <c r="Q103" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q103" s="7" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="7" t="inlineStr">
@@ -8934,16 +8958,16 @@
       <c r="M104" s="7" t="inlineStr"/>
       <c r="N104" s="14" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O104" s="7" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O104" s="7" t="inlineStr">
+        <is>
+          <t>Deactivating the only System Manager is destructive (system-lock risk) - not safe to exercise on shared staging.</t>
+        </is>
+      </c>
       <c r="P104" s="8" t="inlineStr"/>
-      <c r="Q104" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q104" s="7" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="7" t="inlineStr">
@@ -9001,16 +9025,16 @@
       <c r="M105" s="7" t="inlineStr"/>
       <c r="N105" s="14" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O105" s="7" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O105" s="7" t="inlineStr">
+        <is>
+          <t>Deleting a record-owning user is destructive; needs a disposable owner-user fixture - not exercised to protect staging data.</t>
+        </is>
+      </c>
       <c r="P105" s="8" t="inlineStr"/>
-      <c r="Q105" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q105" s="7" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
@@ -9076,16 +9100,16 @@
       </c>
       <c r="N106" s="14" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O106" s="7" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O106" s="7" t="inlineStr">
+        <is>
+          <t>Password strength + password-not-equal-identity are zxcvbn policy rules held in System Settings, which CT-IT cannot read; the set-password page enforcement was not drivable as this role.</t>
+        </is>
+      </c>
       <c r="P106" s="8" t="inlineStr"/>
-      <c r="Q106" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q106" s="7" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="7" t="inlineStr">
@@ -9143,16 +9167,16 @@
       <c r="M107" s="7" t="inlineStr"/>
       <c r="N107" s="14" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O107" s="7" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O107" s="7" t="inlineStr">
+        <is>
+          <t>Password-reuse (last 5) history is not a stock Frappe feature; verifying it needs policy access + repeated resets - not drivable as CT-IT.</t>
+        </is>
+      </c>
       <c r="P107" s="8" t="inlineStr"/>
-      <c r="Q107" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q107" s="7" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="7" t="inlineStr">
@@ -9210,16 +9234,16 @@
       <c r="M108" s="7" t="inlineStr"/>
       <c r="N108" s="14" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O108" s="7" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O108" s="7" t="inlineStr">
+        <is>
+          <t>Password strength + password-not-equal-identity are zxcvbn policy rules held in System Settings, which CT-IT cannot read; the set-password page enforcement was not drivable as this role.</t>
+        </is>
+      </c>
       <c r="P108" s="8" t="inlineStr"/>
-      <c r="Q108" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q108" s="7" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="7" t="inlineStr">
@@ -9572,16 +9596,16 @@
       <c r="M113" s="7" t="inlineStr"/>
       <c r="N113" s="14" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O113" s="7" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O113" s="7" t="inlineStr">
+        <is>
+          <t>The SPA User form exposes only User Details / Settings tabs - no per-user Activity Log tab is surfaced in the SPA (desk-only); cannot verify here.</t>
+        </is>
+      </c>
       <c r="P113" s="8" t="inlineStr"/>
-      <c r="Q113" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q113" s="7" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="7" t="inlineStr">
@@ -9638,18 +9662,18 @@
       </c>
       <c r="L114" s="7" t="inlineStr"/>
       <c r="M114" s="7" t="inlineStr"/>
-      <c r="N114" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O114" s="7" t="inlineStr"/>
+      <c r="N114" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O114" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: one failed login (bad password) returns HTTP 401 with generic "Invalid login credentials"; Frappe core writes failed auth to Activity Log (framework-standard). My CT-IT session was unaffected.</t>
+        </is>
+      </c>
       <c r="P114" s="8" t="inlineStr"/>
-      <c r="Q114" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q114" s="7" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="7" t="inlineStr">
@@ -9708,16 +9732,16 @@
       <c r="M115" s="7" t="inlineStr"/>
       <c r="N115" s="14" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O115" s="7" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O115" s="7" t="inlineStr">
+        <is>
+          <t>The User Manager list has row multi-select, but bulk-disabling 5 users risks disabling real accounts on shared staging - not exercised (multi-select present).</t>
+        </is>
+      </c>
       <c r="P115" s="8" t="inlineStr"/>
-      <c r="Q115" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q115" s="7" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="7" t="inlineStr">
@@ -9777,16 +9801,16 @@
       <c r="M116" s="7" t="inlineStr"/>
       <c r="N116" s="14" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O116" s="7" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O116" s="7" t="inlineStr">
+        <is>
+          <t>No CSV bulk-import UI is exposed in the SPA User Management (Frappe Data Import is desk-only) - not drivable here.</t>
+        </is>
+      </c>
       <c r="P116" s="8" t="inlineStr"/>
-      <c r="Q116" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q116" s="7" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="7" t="inlineStr">
@@ -10044,18 +10068,18 @@
       </c>
       <c r="L120" s="7" t="inlineStr"/>
       <c r="M120" s="7" t="inlineStr"/>
-      <c r="N120" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O120" s="7" t="inlineStr"/>
+      <c r="N120" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O120" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: New User form has tabbed sections (User Details / Settings) + grouped field cards - fields are grouped into clear sections.</t>
+        </is>
+      </c>
       <c r="P120" s="8" t="inlineStr"/>
-      <c r="Q120" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q120" s="7" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="7" t="inlineStr">
@@ -10111,18 +10135,18 @@
       </c>
       <c r="L121" s="7" t="inlineStr"/>
       <c r="M121" s="7" t="inlineStr"/>
-      <c r="N121" s="14" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O121" s="7" t="inlineStr"/>
+      <c r="N121" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O121" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: the User create form exposes NO plaintext password field (pwField count 0) - password is set via the welcome-email / set-password link (masked input), never shown in the DOM.</t>
+        </is>
+      </c>
       <c r="P121" s="8" t="inlineStr"/>
-      <c r="Q121" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q121" s="7" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="7" t="inlineStr">
@@ -10522,7 +10546,7 @@
       </c>
       <c r="L127" s="7" t="inlineStr"/>
       <c r="M127" s="7" t="inlineStr"/>
-      <c r="N127" s="14" t="inlineStr">
+      <c r="N127" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -10741,7 +10765,7 @@
       </c>
       <c r="L130" s="7" t="inlineStr"/>
       <c r="M130" s="7" t="inlineStr"/>
-      <c r="N130" s="14" t="inlineStr">
+      <c r="N130" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11036,7 +11060,7 @@
           <t>BRD PR-XC-002b — "Other" handling.</t>
         </is>
       </c>
-      <c r="N134" s="14" t="inlineStr">
+      <c r="N134" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11103,7 +11127,7 @@
       </c>
       <c r="L135" s="7" t="inlineStr"/>
       <c r="M135" s="7" t="inlineStr"/>
-      <c r="N135" s="14" t="inlineStr">
+      <c r="N135" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11170,7 +11194,7 @@
       </c>
       <c r="L136" s="7" t="inlineStr"/>
       <c r="M136" s="7" t="inlineStr"/>
-      <c r="N136" s="14" t="inlineStr">
+      <c r="N136" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11524,7 +11548,7 @@
           <t>BRD m-schemes.</t>
         </is>
       </c>
-      <c r="N141" s="14" t="inlineStr">
+      <c r="N141" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11816,7 +11840,7 @@
       </c>
       <c r="L145" s="7" t="inlineStr"/>
       <c r="M145" s="7" t="inlineStr"/>
-      <c r="N145" s="14" t="inlineStr">
+      <c r="N145" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11884,7 +11908,7 @@
       </c>
       <c r="L146" s="7" t="inlineStr"/>
       <c r="M146" s="7" t="inlineStr"/>
-      <c r="N146" s="14" t="inlineStr">
+      <c r="N146" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12041,7 +12065,7 @@
       </c>
       <c r="L148" s="7" t="inlineStr"/>
       <c r="M148" s="7" t="inlineStr"/>
-      <c r="N148" s="14" t="inlineStr">
+      <c r="N148" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12109,7 +12133,7 @@
       </c>
       <c r="L149" s="7" t="inlineStr"/>
       <c r="M149" s="7" t="inlineStr"/>
-      <c r="N149" s="16" t="inlineStr">
+      <c r="N149" s="14" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
@@ -12180,7 +12204,7 @@
       </c>
       <c r="L150" s="7" t="inlineStr"/>
       <c r="M150" s="7" t="inlineStr"/>
-      <c r="N150" s="16" t="inlineStr">
+      <c r="N150" s="14" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
@@ -12597,7 +12621,7 @@
       </c>
       <c r="L156" s="7" t="inlineStr"/>
       <c r="M156" s="7" t="inlineStr"/>
-      <c r="N156" s="14" t="inlineStr">
+      <c r="N156" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12665,7 +12689,7 @@
       </c>
       <c r="L157" s="7" t="inlineStr"/>
       <c r="M157" s="7" t="inlineStr"/>
-      <c r="N157" s="14" t="inlineStr">
+      <c r="N157" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12732,7 +12756,7 @@
       </c>
       <c r="L158" s="7" t="inlineStr"/>
       <c r="M158" s="7" t="inlineStr"/>
-      <c r="N158" s="14" t="inlineStr">
+      <c r="N158" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12807,7 +12831,7 @@
           <t>OWASP A03 Injection / A05 Security Misconfig (file upload).</t>
         </is>
       </c>
-      <c r="N159" s="14" t="inlineStr">
+      <c r="N159" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12876,7 +12900,7 @@
       </c>
       <c r="L160" s="7" t="inlineStr"/>
       <c r="M160" s="7" t="inlineStr"/>
-      <c r="N160" s="14" t="inlineStr">
+      <c r="N160" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12944,7 +12968,7 @@
       </c>
       <c r="L161" s="7" t="inlineStr"/>
       <c r="M161" s="7" t="inlineStr"/>
-      <c r="N161" s="14" t="inlineStr">
+      <c r="N161" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13021,7 +13045,7 @@
           <t>BRD Decision: Fellow fills 10Q + Rural E-Champ during profiling.</t>
         </is>
       </c>
-      <c r="N162" s="14" t="inlineStr">
+      <c r="N162" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13088,7 +13112,7 @@
       </c>
       <c r="L163" s="7" t="inlineStr"/>
       <c r="M163" s="7" t="inlineStr"/>
-      <c r="N163" s="14" t="inlineStr">
+      <c r="N163" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13315,7 +13339,7 @@
           <t>BRD: 3-state model (MET / Incubated / Supported).</t>
         </is>
       </c>
-      <c r="N166" s="14" t="inlineStr">
+      <c r="N166" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13382,7 +13406,7 @@
       </c>
       <c r="L167" s="7" t="inlineStr"/>
       <c r="M167" s="7" t="inlineStr"/>
-      <c r="N167" s="14" t="inlineStr">
+      <c r="N167" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13459,7 +13483,7 @@
           <t>BRD: Decision — Framework Prioritisation by CTIT or Fellow.</t>
         </is>
       </c>
-      <c r="N168" s="14" t="inlineStr">
+      <c r="N168" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13526,7 +13550,7 @@
       </c>
       <c r="L169" s="7" t="inlineStr"/>
       <c r="M169" s="7" t="inlineStr"/>
-      <c r="N169" s="14" t="inlineStr">
+      <c r="N169" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13593,7 +13617,7 @@
       </c>
       <c r="L170" s="7" t="inlineStr"/>
       <c r="M170" s="7" t="inlineStr"/>
-      <c r="N170" s="14" t="inlineStr">
+      <c r="N170" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13668,7 +13692,7 @@
           <t>BRD: PR-EP-001 (EP Profile Dashboard).</t>
         </is>
       </c>
-      <c r="N171" s="14" t="inlineStr">
+      <c r="N171" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13744,7 +13768,7 @@
           <t>BRD: EP Profile Dashboard — "+ Add New Product" tile decision.</t>
         </is>
       </c>
-      <c r="N172" s="14" t="inlineStr">
+      <c r="N172" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13879,7 +13903,7 @@
       </c>
       <c r="L174" s="7" t="inlineStr"/>
       <c r="M174" s="7" t="inlineStr"/>
-      <c r="N174" s="14" t="inlineStr">
+      <c r="N174" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13946,7 +13970,7 @@
       </c>
       <c r="L175" s="7" t="inlineStr"/>
       <c r="M175" s="7" t="inlineStr"/>
-      <c r="N175" s="14" t="inlineStr">
+      <c r="N175" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -14013,7 +14037,7 @@
       </c>
       <c r="L176" s="7" t="inlineStr"/>
       <c r="M176" s="7" t="inlineStr"/>
-      <c r="N176" s="14" t="inlineStr">
+      <c r="N176" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -14232,7 +14256,7 @@
       </c>
       <c r="L179" s="7" t="inlineStr"/>
       <c r="M179" s="7" t="inlineStr"/>
-      <c r="N179" s="14" t="inlineStr">
+      <c r="N179" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -14299,7 +14323,7 @@
       </c>
       <c r="L180" s="7" t="inlineStr"/>
       <c r="M180" s="7" t="inlineStr"/>
-      <c r="N180" s="14" t="inlineStr">
+      <c r="N180" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -14376,7 +14400,7 @@
           <t>BRD: Networking &amp; Mentoring module.</t>
         </is>
       </c>
-      <c r="N181" s="14" t="inlineStr">
+      <c r="N181" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -14445,7 +14469,7 @@
       </c>
       <c r="L182" s="7" t="inlineStr"/>
       <c r="M182" s="7" t="inlineStr"/>
-      <c r="N182" s="14" t="inlineStr">
+      <c r="N182" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -14512,7 +14536,7 @@
       </c>
       <c r="L183" s="7" t="inlineStr"/>
       <c r="M183" s="7" t="inlineStr"/>
-      <c r="N183" s="14" t="inlineStr">
+      <c r="N183" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -14588,7 +14612,7 @@
           <t>BRD Rule 8: Log Book is per-framework but EP-level aggregate is the EP's Log Book.</t>
         </is>
       </c>
-      <c r="N184" s="14" t="inlineStr">
+      <c r="N184" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -14806,7 +14830,7 @@
       </c>
       <c r="L187" s="7" t="inlineStr"/>
       <c r="M187" s="7" t="inlineStr"/>
-      <c r="N187" s="14" t="inlineStr">
+      <c r="N187" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -15008,7 +15032,7 @@
       </c>
       <c r="L190" s="7" t="inlineStr"/>
       <c r="M190" s="7" t="inlineStr"/>
-      <c r="N190" s="14" t="inlineStr">
+      <c r="N190" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -15448,7 +15472,7 @@
           <t>BRD: Process Flow drag-drop (bug fixed from QA bug tracker).</t>
         </is>
       </c>
-      <c r="N196" s="16" t="inlineStr">
+      <c r="N196" s="14" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
@@ -15515,7 +15539,7 @@
       </c>
       <c r="L197" s="7" t="inlineStr"/>
       <c r="M197" s="7" t="inlineStr"/>
-      <c r="N197" s="16" t="inlineStr">
+      <c r="N197" s="14" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
@@ -16029,7 +16053,7 @@
           <t>BRD QA fix: currency symbol.</t>
         </is>
       </c>
-      <c r="N204" s="14" t="inlineStr">
+      <c r="N204" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -16171,7 +16195,7 @@
       </c>
       <c r="L206" s="7" t="inlineStr"/>
       <c r="M206" s="7" t="inlineStr"/>
-      <c r="N206" s="14" t="inlineStr">
+      <c r="N206" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -16305,7 +16329,7 @@
       </c>
       <c r="L208" s="7" t="inlineStr"/>
       <c r="M208" s="7" t="inlineStr"/>
-      <c r="N208" s="16" t="inlineStr">
+      <c r="N208" s="14" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
@@ -16727,7 +16751,7 @@
       </c>
       <c r="L214" s="7" t="inlineStr"/>
       <c r="M214" s="7" t="inlineStr"/>
-      <c r="N214" s="14" t="inlineStr">
+      <c r="N214" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -16939,7 +16963,7 @@
       </c>
       <c r="L217" s="7" t="inlineStr"/>
       <c r="M217" s="7" t="inlineStr"/>
-      <c r="N217" s="14" t="inlineStr">
+      <c r="N217" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -17006,7 +17030,7 @@
       </c>
       <c r="L218" s="7" t="inlineStr"/>
       <c r="M218" s="7" t="inlineStr"/>
-      <c r="N218" s="14" t="inlineStr">
+      <c r="N218" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -17074,7 +17098,7 @@
       </c>
       <c r="L219" s="7" t="inlineStr"/>
       <c r="M219" s="7" t="inlineStr"/>
-      <c r="N219" s="14" t="inlineStr">
+      <c r="N219" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -17209,7 +17233,7 @@
       </c>
       <c r="L221" s="7" t="inlineStr"/>
       <c r="M221" s="7" t="inlineStr"/>
-      <c r="N221" s="14" t="inlineStr">
+      <c r="N221" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -17345,7 +17369,7 @@
       </c>
       <c r="L223" s="7" t="inlineStr"/>
       <c r="M223" s="7" t="inlineStr"/>
-      <c r="N223" s="14" t="inlineStr">
+      <c r="N223" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -17412,7 +17436,7 @@
       </c>
       <c r="L224" s="7" t="inlineStr"/>
       <c r="M224" s="7" t="inlineStr"/>
-      <c r="N224" s="14" t="inlineStr">
+      <c r="N224" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -17546,7 +17570,7 @@
       </c>
       <c r="L226" s="7" t="inlineStr"/>
       <c r="M226" s="7" t="inlineStr"/>
-      <c r="N226" s="14" t="inlineStr">
+      <c r="N226" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -17689,7 +17713,7 @@
           <t>BRD Decision: Machinery Required → Infra EE: dropdown selection.</t>
         </is>
       </c>
-      <c r="N228" s="14" t="inlineStr">
+      <c r="N228" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -17756,7 +17780,7 @@
       </c>
       <c r="L229" s="7" t="inlineStr"/>
       <c r="M229" s="7" t="inlineStr"/>
-      <c r="N229" s="14" t="inlineStr">
+      <c r="N229" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -17983,7 +18007,7 @@
       </c>
       <c r="L232" s="7" t="inlineStr"/>
       <c r="M232" s="7" t="inlineStr"/>
-      <c r="N232" s="14" t="inlineStr">
+      <c r="N232" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -18050,7 +18074,7 @@
       </c>
       <c r="L233" s="7" t="inlineStr"/>
       <c r="M233" s="7" t="inlineStr"/>
-      <c r="N233" s="14" t="inlineStr">
+      <c r="N233" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -18192,7 +18216,7 @@
       </c>
       <c r="L235" s="7" t="inlineStr"/>
       <c r="M235" s="7" t="inlineStr"/>
-      <c r="N235" s="14" t="inlineStr">
+      <c r="N235" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -18259,7 +18283,7 @@
       </c>
       <c r="L236" s="7" t="inlineStr"/>
       <c r="M236" s="7" t="inlineStr"/>
-      <c r="N236" s="14" t="inlineStr">
+      <c r="N236" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -18327,7 +18351,7 @@
       </c>
       <c r="L237" s="7" t="inlineStr"/>
       <c r="M237" s="7" t="inlineStr"/>
-      <c r="N237" s="14" t="inlineStr">
+      <c r="N237" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -18395,7 +18419,7 @@
       </c>
       <c r="L238" s="7" t="inlineStr"/>
       <c r="M238" s="7" t="inlineStr"/>
-      <c r="N238" s="14" t="inlineStr">
+      <c r="N238" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -18605,7 +18629,7 @@
       </c>
       <c r="L241" s="7" t="inlineStr"/>
       <c r="M241" s="7" t="inlineStr"/>
-      <c r="N241" s="14" t="inlineStr">
+      <c r="N241" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -18672,7 +18696,7 @@
       </c>
       <c r="L242" s="7" t="inlineStr"/>
       <c r="M242" s="7" t="inlineStr"/>
-      <c r="N242" s="14" t="inlineStr">
+      <c r="N242" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -18873,7 +18897,7 @@
       </c>
       <c r="L245" s="7" t="inlineStr"/>
       <c r="M245" s="7" t="inlineStr"/>
-      <c r="N245" s="14" t="inlineStr">
+      <c r="N245" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -19213,7 +19237,7 @@
       </c>
       <c r="L250" s="7" t="inlineStr"/>
       <c r="M250" s="7" t="inlineStr"/>
-      <c r="N250" s="14" t="inlineStr">
+      <c r="N250" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -19281,7 +19305,7 @@
       </c>
       <c r="L251" s="7" t="inlineStr"/>
       <c r="M251" s="7" t="inlineStr"/>
-      <c r="N251" s="14" t="inlineStr">
+      <c r="N251" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -19348,7 +19372,7 @@
       </c>
       <c r="L252" s="7" t="inlineStr"/>
       <c r="M252" s="7" t="inlineStr"/>
-      <c r="N252" s="14" t="inlineStr">
+      <c r="N252" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -19415,7 +19439,7 @@
       </c>
       <c r="L253" s="7" t="inlineStr"/>
       <c r="M253" s="7" t="inlineStr"/>
-      <c r="N253" s="14" t="inlineStr">
+      <c r="N253" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -19482,7 +19506,7 @@
       </c>
       <c r="L254" s="7" t="inlineStr"/>
       <c r="M254" s="7" t="inlineStr"/>
-      <c r="N254" s="14" t="inlineStr">
+      <c r="N254" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -19750,7 +19774,7 @@
       </c>
       <c r="L258" s="7" t="inlineStr"/>
       <c r="M258" s="7" t="inlineStr"/>
-      <c r="N258" s="14" t="inlineStr">
+      <c r="N258" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -19982,7 +20006,7 @@
           <t>BRD PR-XC-002b.</t>
         </is>
       </c>
-      <c r="N261" s="14" t="inlineStr">
+      <c r="N261" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -20049,7 +20073,7 @@
       </c>
       <c r="L262" s="7" t="inlineStr"/>
       <c r="M262" s="7" t="inlineStr"/>
-      <c r="N262" s="14" t="inlineStr">
+      <c r="N262" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -20116,7 +20140,7 @@
       </c>
       <c r="L263" s="7" t="inlineStr"/>
       <c r="M263" s="7" t="inlineStr"/>
-      <c r="N263" s="14" t="inlineStr">
+      <c r="N263" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -20184,7 +20208,7 @@
       </c>
       <c r="L264" s="7" t="inlineStr"/>
       <c r="M264" s="7" t="inlineStr"/>
-      <c r="N264" s="14" t="inlineStr">
+      <c r="N264" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -20401,7 +20425,7 @@
           <t>BRD Decision: Activity Logger Board view = block-wise cards, descending log date.</t>
         </is>
       </c>
-      <c r="N267" s="16" t="inlineStr">
+      <c r="N267" s="14" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
@@ -20549,7 +20573,7 @@
       </c>
       <c r="L269" s="7" t="inlineStr"/>
       <c r="M269" s="7" t="inlineStr"/>
-      <c r="N269" s="14" t="inlineStr">
+      <c r="N269" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -20768,7 +20792,7 @@
       </c>
       <c r="L272" s="7" t="inlineStr"/>
       <c r="M272" s="7" t="inlineStr"/>
-      <c r="N272" s="16" t="inlineStr">
+      <c r="N272" s="14" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
@@ -21052,7 +21076,7 @@
       </c>
       <c r="L276" s="7" t="inlineStr"/>
       <c r="M276" s="7" t="inlineStr"/>
-      <c r="N276" s="16" t="inlineStr">
+      <c r="N276" s="14" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
@@ -21123,7 +21147,7 @@
       </c>
       <c r="L277" s="7" t="inlineStr"/>
       <c r="M277" s="7" t="inlineStr"/>
-      <c r="N277" s="16" t="inlineStr">
+      <c r="N277" s="14" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
@@ -21194,7 +21218,7 @@
       </c>
       <c r="L278" s="7" t="inlineStr"/>
       <c r="M278" s="7" t="inlineStr"/>
-      <c r="N278" s="16" t="inlineStr">
+      <c r="N278" s="14" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
@@ -21265,7 +21289,7 @@
       </c>
       <c r="L279" s="7" t="inlineStr"/>
       <c r="M279" s="7" t="inlineStr"/>
-      <c r="N279" s="16" t="inlineStr">
+      <c r="N279" s="14" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
@@ -21411,7 +21435,7 @@
       </c>
       <c r="L281" s="7" t="inlineStr"/>
       <c r="M281" s="7" t="inlineStr"/>
-      <c r="N281" s="16" t="inlineStr">
+      <c r="N281" s="14" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
@@ -22128,7 +22152,7 @@
           <t>BRD: drill down to block level.</t>
         </is>
       </c>
-      <c r="N290" s="16" t="inlineStr">
+      <c r="N290" s="14" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
@@ -22346,7 +22370,7 @@
       </c>
       <c r="L293" s="7" t="inlineStr"/>
       <c r="M293" s="7" t="inlineStr"/>
-      <c r="N293" s="14" t="inlineStr">
+      <c r="N293" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -22413,7 +22437,7 @@
       </c>
       <c r="L294" s="7" t="inlineStr"/>
       <c r="M294" s="7" t="inlineStr"/>
-      <c r="N294" s="14" t="inlineStr">
+      <c r="N294" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -22480,7 +22504,7 @@
       </c>
       <c r="L295" s="7" t="inlineStr"/>
       <c r="M295" s="7" t="inlineStr"/>
-      <c r="N295" s="14" t="inlineStr">
+      <c r="N295" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -22548,7 +22572,7 @@
       </c>
       <c r="L296" s="7" t="inlineStr"/>
       <c r="M296" s="7" t="inlineStr"/>
-      <c r="N296" s="14" t="inlineStr">
+      <c r="N296" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -22757,7 +22781,7 @@
           <t>BRD Decision: CTI receive-only on notifications.</t>
         </is>
       </c>
-      <c r="N299" s="14" t="inlineStr">
+      <c r="N299" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -22961,16 +22985,16 @@
       <c r="M302" s="7" t="inlineStr"/>
       <c r="N302" s="14" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O302" s="7" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O302" s="7" t="inlineStr">
+        <is>
+          <t>Disabled-user API-key rejection needs a disabled user plus that user API key/secret - cannot mint or test another users key safely.</t>
+        </is>
+      </c>
       <c r="P302" s="8" t="inlineStr"/>
-      <c r="Q302" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q302" s="7" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" s="7" t="inlineStr">
@@ -23363,16 +23387,16 @@
       <c r="M308" s="7" t="inlineStr"/>
       <c r="N308" s="14" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O308" s="7" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O308" s="7" t="inlineStr">
+        <is>
+          <t>1000-req/min rate-limit test would require hammering the server (abusive) - deliberately not run on shared staging.</t>
+        </is>
+      </c>
       <c r="P308" s="8" t="inlineStr"/>
-      <c r="Q308" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q308" s="7" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" s="7" t="inlineStr">
@@ -23430,16 +23454,16 @@
       <c r="M309" s="7" t="inlineStr"/>
       <c r="N309" s="14" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O309" s="7" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O309" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: POST to prime_rural.api.networking_mentoring.save_introduction returns HTTP 417 "Failed to get method for command" - the literal whitelisted path is not resolvable (the introduction-save likely runs through the doctype controller, per the entrepreneur_meeting_log sync). Needs dev to confirm the correct endpoint path.</t>
+        </is>
+      </c>
       <c r="P309" s="8" t="inlineStr"/>
-      <c r="Q309" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q309" s="7" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" s="7" t="inlineStr">
@@ -23696,7 +23720,7 @@
       </c>
       <c r="L313" s="7" t="inlineStr"/>
       <c r="M313" s="7" t="inlineStr"/>
-      <c r="N313" s="16" t="inlineStr">
+      <c r="N313" s="14" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
@@ -23769,16 +23793,16 @@
       <c r="M314" s="7" t="inlineStr"/>
       <c r="N314" s="14" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O314" s="7" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O314" s="7" t="inlineStr">
+        <is>
+          <t>Cascade-delete behaviour (deleting an EP must NOT cascade framework records) is destructive - needs a disposable EP with linked frameworks + a delete; not exercised to protect staging data.</t>
+        </is>
+      </c>
       <c r="P314" s="8" t="inlineStr"/>
-      <c r="Q314" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q314" s="7" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" s="7" t="inlineStr">
@@ -23834,7 +23858,7 @@
       </c>
       <c r="L315" s="7" t="inlineStr"/>
       <c r="M315" s="7" t="inlineStr"/>
-      <c r="N315" s="16" t="inlineStr">
+      <c r="N315" s="14" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
@@ -23907,16 +23931,16 @@
       <c r="M316" s="7" t="inlineStr"/>
       <c r="N316" s="14" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O316" s="7" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O316" s="7" t="inlineStr">
+        <is>
+          <t>DB charset (utf8mb4) and UTC-store/IST-display are storage-layer facts needing a DB shell - not inspectable through the app API as CT-IT.</t>
+        </is>
+      </c>
       <c r="P316" s="8" t="inlineStr"/>
-      <c r="Q316" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q316" s="7" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" s="7" t="inlineStr">
@@ -23974,16 +23998,16 @@
       <c r="M317" s="7" t="inlineStr"/>
       <c r="N317" s="14" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O317" s="7" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O317" s="7" t="inlineStr">
+        <is>
+          <t>DB charset (utf8mb4) and UTC-store/IST-display are storage-layer facts needing a DB shell - not inspectable through the app API as CT-IT.</t>
+        </is>
+      </c>
       <c r="P317" s="8" t="inlineStr"/>
-      <c r="Q317" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q317" s="7" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" s="7" t="inlineStr">
@@ -24039,7 +24063,7 @@
       </c>
       <c r="L318" s="7" t="inlineStr"/>
       <c r="M318" s="7" t="inlineStr"/>
-      <c r="N318" s="16" t="inlineStr">
+      <c r="N318" s="14" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
@@ -24110,7 +24134,7 @@
       </c>
       <c r="L319" s="7" t="inlineStr"/>
       <c r="M319" s="7" t="inlineStr"/>
-      <c r="N319" s="16" t="inlineStr">
+      <c r="N319" s="14" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
@@ -24182,7 +24206,7 @@
       </c>
       <c r="L320" s="7" t="inlineStr"/>
       <c r="M320" s="7" t="inlineStr"/>
-      <c r="N320" s="16" t="inlineStr">
+      <c r="N320" s="14" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
@@ -24262,7 +24286,7 @@
           <t>OWASP A03 Injection (XSS sub-category).</t>
         </is>
       </c>
-      <c r="N321" s="14" t="inlineStr">
+      <c r="N321" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -24712,7 +24736,7 @@
           <t>OWASP A01.</t>
         </is>
       </c>
-      <c r="N327" s="14" t="inlineStr">
+      <c r="N327" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -24779,7 +24803,7 @@
       </c>
       <c r="L328" s="7" t="inlineStr"/>
       <c r="M328" s="7" t="inlineStr"/>
-      <c r="N328" s="14" t="inlineStr">
+      <c r="N328" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -24913,7 +24937,7 @@
       </c>
       <c r="L330" s="7" t="inlineStr"/>
       <c r="M330" s="7" t="inlineStr"/>
-      <c r="N330" s="14" t="inlineStr">
+      <c r="N330" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -24988,7 +25012,7 @@
           <t>Solution Doc Assumption: VAPT is client responsibility.</t>
         </is>
       </c>
-      <c r="N331" s="16" t="inlineStr">
+      <c r="N331" s="14" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
@@ -26325,7 +26349,7 @@
           <t>Trace: Frameworks / — General (all forms)</t>
         </is>
       </c>
-      <c r="N347" s="16" t="inlineStr">
+      <c r="N347" s="14" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
@@ -26401,7 +26425,7 @@
           <t>Trace: Frameworks / — General (all forms)</t>
         </is>
       </c>
-      <c r="N348" s="16" t="inlineStr">
+      <c r="N348" s="14" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
@@ -26477,7 +26501,7 @@
           <t>Trace: Frameworks / — General (all forms)</t>
         </is>
       </c>
-      <c r="N349" s="16" t="inlineStr">
+      <c r="N349" s="14" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
@@ -26553,7 +26577,7 @@
           <t>Trace: Frameworks / — General (all forms)</t>
         </is>
       </c>
-      <c r="N350" s="16" t="inlineStr">
+      <c r="N350" s="14" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
@@ -26629,7 +26653,7 @@
           <t>Trace: Frameworks / — General (all forms)</t>
         </is>
       </c>
-      <c r="N351" s="16" t="inlineStr">
+      <c r="N351" s="14" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
@@ -26705,7 +26729,7 @@
           <t>Trace: Frameworks / — General (all forms)</t>
         </is>
       </c>
-      <c r="N352" s="16" t="inlineStr">
+      <c r="N352" s="14" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
@@ -26941,7 +26965,7 @@
           <t>Trace: Frameworks / Financials / BMC</t>
         </is>
       </c>
-      <c r="N355" s="14" t="inlineStr">
+      <c r="N355" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -27017,7 +27041,7 @@
           <t>Trace: Frameworks / Financials / BMC</t>
         </is>
       </c>
-      <c r="N356" s="14" t="inlineStr">
+      <c r="N356" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -27853,7 +27877,7 @@
           <t>Trace: Frameworks / Financials / BMC</t>
         </is>
       </c>
-      <c r="N367" s="14" t="inlineStr">
+      <c r="N367" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -28005,7 +28029,7 @@
           <t>Trace: Frameworks / Financials / BMC</t>
         </is>
       </c>
-      <c r="N369" s="14" t="inlineStr">
+      <c r="N369" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -28689,7 +28713,7 @@
           <t>Trace: Frameworks / Unit Pricing</t>
         </is>
       </c>
-      <c r="N378" s="14" t="inlineStr">
+      <c r="N378" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -29373,7 +29397,7 @@
           <t>Trace: Frameworks / Unit Pricing</t>
         </is>
       </c>
-      <c r="N387" s="14" t="inlineStr">
+      <c r="N387" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -29525,7 +29549,7 @@
           <t>Trace: Frameworks / Unit Pricing</t>
         </is>
       </c>
-      <c r="N389" s="14" t="inlineStr">
+      <c r="N389" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -30057,7 +30081,7 @@
           <t>Trace: Frameworks / Schemes &amp; Funding</t>
         </is>
       </c>
-      <c r="N396" s="14" t="inlineStr">
+      <c r="N396" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -30133,7 +30157,7 @@
           <t>Trace: Frameworks / Schemes &amp; Funding</t>
         </is>
       </c>
-      <c r="N397" s="14" t="inlineStr">
+      <c r="N397" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -30209,7 +30233,7 @@
           <t>Trace: Frameworks / Schemes &amp; Funding</t>
         </is>
       </c>
-      <c r="N398" s="14" t="inlineStr">
+      <c r="N398" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -30285,7 +30309,7 @@
           <t>Trace: Frameworks / Schemes &amp; Funding</t>
         </is>
       </c>
-      <c r="N399" s="14" t="inlineStr">
+      <c r="N399" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -30361,7 +30385,7 @@
           <t>Trace: Frameworks / Schemes &amp; Funding</t>
         </is>
       </c>
-      <c r="N400" s="14" t="inlineStr">
+      <c r="N400" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -30437,7 +30461,7 @@
           <t>Trace: Frameworks / Schemes &amp; Funding</t>
         </is>
       </c>
-      <c r="N401" s="14" t="inlineStr">
+      <c r="N401" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -30513,7 +30537,7 @@
           <t>Trace: Frameworks / Schemes &amp; Funding</t>
         </is>
       </c>
-      <c r="N402" s="14" t="inlineStr">
+      <c r="N402" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -30589,7 +30613,7 @@
           <t>Trace: Frameworks / Schemes &amp; Funding</t>
         </is>
       </c>
-      <c r="N403" s="14" t="inlineStr">
+      <c r="N403" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -33425,7 +33449,7 @@
           <t>Trace: Frameworks / Machinery</t>
         </is>
       </c>
-      <c r="N440" s="14" t="inlineStr">
+      <c r="N440" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -34269,7 +34293,7 @@
           <t>Trace: Frameworks / Machinery</t>
         </is>
       </c>
-      <c r="N451" s="14" t="inlineStr">
+      <c r="N451" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -34801,7 +34825,7 @@
           <t>Trace: Frameworks / Human Resource</t>
         </is>
       </c>
-      <c r="N458" s="14" t="inlineStr">
+      <c r="N458" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -35341,7 +35365,7 @@
           <t>Trace: Frameworks / Human Resource</t>
         </is>
       </c>
-      <c r="N465" s="14" t="inlineStr">
+      <c r="N465" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -35493,7 +35517,7 @@
           <t>Trace: Frameworks / Human Resource</t>
         </is>
       </c>
-      <c r="N467" s="14" t="inlineStr">
+      <c r="N467" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -35797,7 +35821,7 @@
           <t>Trace: Frameworks / Infrastructure</t>
         </is>
       </c>
-      <c r="N471" s="14" t="inlineStr">
+      <c r="N471" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -35949,7 +35973,7 @@
           <t>Trace: Frameworks / Infrastructure</t>
         </is>
       </c>
-      <c r="N473" s="14" t="inlineStr">
+      <c r="N473" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -36937,7 +36961,7 @@
           <t>Trace: Frameworks / Infrastructure</t>
         </is>
       </c>
-      <c r="N486" s="14" t="inlineStr">
+      <c r="N486" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -37013,7 +37037,7 @@
           <t>Trace: Frameworks / Infrastructure</t>
         </is>
       </c>
-      <c r="N487" s="14" t="inlineStr">
+      <c r="N487" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -37089,7 +37113,7 @@
           <t>Trace: Frameworks / Infrastructure</t>
         </is>
       </c>
-      <c r="N488" s="14" t="inlineStr">
+      <c r="N488" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -37317,7 +37341,7 @@
           <t>Trace: Frameworks / Infrastructure</t>
         </is>
       </c>
-      <c r="N491" s="14" t="inlineStr">
+      <c r="N491" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -37621,7 +37645,7 @@
           <t>Trace: Frameworks / Infrastructure</t>
         </is>
       </c>
-      <c r="N495" s="14" t="inlineStr">
+      <c r="N495" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -38617,7 +38641,7 @@
           <t>Trace: Frameworks / Infrastructure</t>
         </is>
       </c>
-      <c r="N508" s="14" t="inlineStr">
+      <c r="N508" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -39149,7 +39173,7 @@
           <t>Trace: Frameworks / Product Testing</t>
         </is>
       </c>
-      <c r="N515" s="14" t="inlineStr">
+      <c r="N515" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -39301,7 +39325,7 @@
           <t>Trace: Frameworks / Product Testing</t>
         </is>
       </c>
-      <c r="N517" s="14" t="inlineStr">
+      <c r="N517" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -39781,7 +39805,7 @@
           <t>Trace: Frameworks / Product Testing</t>
         </is>
       </c>
-      <c r="N523" s="14" t="inlineStr">
+      <c r="N523" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -39933,7 +39957,7 @@
           <t>Trace: Frameworks / Standardization</t>
         </is>
       </c>
-      <c r="N525" s="14" t="inlineStr">
+      <c r="N525" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -40169,7 +40193,7 @@
           <t>Trace: Frameworks / Standardization</t>
         </is>
       </c>
-      <c r="N528" s="14" t="inlineStr">
+      <c r="N528" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -40397,7 +40421,7 @@
           <t>Trace: Frameworks / Standardization</t>
         </is>
       </c>
-      <c r="N531" s="14" t="inlineStr">
+      <c r="N531" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -41736,7 +41760,7 @@
           <t>Trace: Frameworks / Business Registration</t>
         </is>
       </c>
-      <c r="N548" s="14" t="inlineStr">
+      <c r="N548" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -41888,7 +41912,7 @@
           <t>Trace: Frameworks / Business Registration</t>
         </is>
       </c>
-      <c r="N550" s="14" t="inlineStr">
+      <c r="N550" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -42048,7 +42072,7 @@
           <t>Trace: Frameworks / Business Registration</t>
         </is>
       </c>
-      <c r="N552" s="14" t="inlineStr">
+      <c r="N552" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -42124,7 +42148,7 @@
           <t>Trace: Frameworks / Business Registration</t>
         </is>
       </c>
-      <c r="N553" s="14" t="inlineStr">
+      <c r="N553" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -42200,7 +42224,7 @@
           <t>Trace: Frameworks / Business Registration</t>
         </is>
       </c>
-      <c r="N554" s="14" t="inlineStr">
+      <c r="N554" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -42352,7 +42376,7 @@
           <t>Trace: Frameworks / Business Registration · NT-004 is a 60/30/7-day notify, different rule</t>
         </is>
       </c>
-      <c r="N556" s="16" t="inlineStr">
+      <c r="N556" s="14" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
@@ -42428,7 +42452,7 @@
           <t>Trace: Frameworks / Business Registration</t>
         </is>
       </c>
-      <c r="N557" s="14" t="inlineStr">
+      <c r="N557" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -43036,7 +43060,7 @@
           <t>Trace: Frameworks / Product Compliance</t>
         </is>
       </c>
-      <c r="N565" s="16" t="inlineStr">
+      <c r="N565" s="14" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
@@ -43188,7 +43212,7 @@
           <t>Trace: Frameworks / Product Compliance · only 60/30/7-day notify (NT-004) exists</t>
         </is>
       </c>
-      <c r="N567" s="16" t="inlineStr">
+      <c r="N567" s="14" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
@@ -43264,7 +43288,7 @@
           <t>Trace: Frameworks / Labels · design decision noted at 4774; no Labels exec steps</t>
         </is>
       </c>
-      <c r="N568" s="14" t="inlineStr">
+      <c r="N568" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -43652,7 +43676,7 @@
           <t>Trace: Frameworks / Labels · LBL-001 cites a 'pregnancy warning' field; actual is a fixed 2-line banner + ABV · Was stale — realigned</t>
         </is>
       </c>
-      <c r="N573" s="14" t="inlineStr">
+      <c r="N573" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -43728,7 +43752,7 @@
           <t>Trace: Frameworks / Labels · wireframe shows field but no hard JS enforcement</t>
         </is>
       </c>
-      <c r="N574" s="14" t="inlineStr">
+      <c r="N574" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -43804,7 +43828,7 @@
           <t>Trace: Frameworks / Labels · only test cites wrong text</t>
         </is>
       </c>
-      <c r="N575" s="14" t="inlineStr">
+      <c r="N575" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -43880,7 +43904,7 @@
           <t>Trace: Frameworks / Labels</t>
         </is>
       </c>
-      <c r="N576" s="14" t="inlineStr">
+      <c r="N576" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -43956,7 +43980,7 @@
           <t>Trace: Frameworks / Labels</t>
         </is>
       </c>
-      <c r="N577" s="14" t="inlineStr">
+      <c r="N577" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -44032,7 +44056,7 @@
           <t>Trace: Frameworks / Labels</t>
         </is>
       </c>
-      <c r="N578" s="14" t="inlineStr">
+      <c r="N578" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -44108,7 +44132,7 @@
           <t>Trace: Frameworks / Labels</t>
         </is>
       </c>
-      <c r="N579" s="14" t="inlineStr">
+      <c r="N579" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -44184,7 +44208,7 @@
           <t>Trace: Frameworks / Labels · AI-generate untested; FSSAI-format validation BRD-added</t>
         </is>
       </c>
-      <c r="N580" s="14" t="inlineStr">
+      <c r="N580" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -44260,7 +44284,7 @@
           <t>Trace: Frameworks / Labels · none tested</t>
         </is>
       </c>
-      <c r="N581" s="14" t="inlineStr">
+      <c r="N581" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -44716,7 +44740,7 @@
           <t>Trace: Frameworks / Packaging</t>
         </is>
       </c>
-      <c r="N587" s="14" t="inlineStr">
+      <c r="N587" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -44792,7 +44816,7 @@
           <t>Trace: Frameworks / Packaging</t>
         </is>
       </c>
-      <c r="N588" s="14" t="inlineStr">
+      <c r="N588" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -45020,7 +45044,7 @@
           <t>Trace: Frameworks / Packaging</t>
         </is>
       </c>
-      <c r="N591" s="14" t="inlineStr">
+      <c r="N591" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -45180,7 +45204,7 @@
           <t>Trace: Frameworks / Packaging</t>
         </is>
       </c>
-      <c r="N593" s="14" t="inlineStr">
+      <c r="N593" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -45256,7 +45280,7 @@
           <t>Trace: Frameworks / Packaging</t>
         </is>
       </c>
-      <c r="N594" s="14" t="inlineStr">
+      <c r="N594" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -45408,7 +45432,7 @@
           <t>Trace: Frameworks / Packaging</t>
         </is>
       </c>
-      <c r="N596" s="14" t="inlineStr">
+      <c r="N596" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -45940,7 +45964,7 @@
           <t>Trace: Frameworks / Logistic Packing</t>
         </is>
       </c>
-      <c r="N603" s="14" t="inlineStr">
+      <c r="N603" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -46016,7 +46040,7 @@
           <t>Trace: Frameworks / Logistic Packing</t>
         </is>
       </c>
-      <c r="N604" s="14" t="inlineStr">
+      <c r="N604" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -46776,7 +46800,7 @@
           <t>Trace: Frameworks / Logistic Service</t>
         </is>
       </c>
-      <c r="N614" s="14" t="inlineStr">
+      <c r="N614" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -48448,7 +48472,7 @@
           <t>Trace: Frameworks / Customer Analysis</t>
         </is>
       </c>
-      <c r="N636" s="14" t="inlineStr">
+      <c r="N636" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -48524,7 +48548,7 @@
           <t>Trace: Frameworks / Customer Analysis</t>
         </is>
       </c>
-      <c r="N637" s="14" t="inlineStr">
+      <c r="N637" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -49512,7 +49536,7 @@
           <t>Trace: Frameworks / Promotions</t>
         </is>
       </c>
-      <c r="N650" s="14" t="inlineStr">
+      <c r="N650" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -49588,7 +49612,7 @@
           <t>Trace: Frameworks / Promotions</t>
         </is>
       </c>
-      <c r="N651" s="14" t="inlineStr">
+      <c r="N651" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -49664,7 +49688,7 @@
           <t>Trace: Frameworks / Promotions · BRD over-specifies a richer doctype not in wireframe</t>
         </is>
       </c>
-      <c r="N652" s="14" t="inlineStr">
+      <c r="N652" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -49816,7 +49840,7 @@
           <t>Trace: Frameworks / Promotions</t>
         </is>
       </c>
-      <c r="N654" s="14" t="inlineStr">
+      <c r="N654" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -50356,7 +50380,7 @@
           <t>Trace: Frameworks / Branding Identity</t>
         </is>
       </c>
-      <c r="N661" s="14" t="inlineStr">
+      <c r="N661" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -50584,7 +50608,7 @@
           <t>Trace: Frameworks / Branding Identity</t>
         </is>
       </c>
-      <c r="N664" s="14" t="inlineStr">
+      <c r="N664" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -50736,7 +50760,7 @@
           <t>Trace: Frameworks / Branding Identity</t>
         </is>
       </c>
-      <c r="N666" s="14" t="inlineStr">
+      <c r="N666" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -50888,7 +50912,7 @@
           <t>Trace: Frameworks / Branding Identity</t>
         </is>
       </c>
-      <c r="N668" s="14" t="inlineStr">
+      <c r="N668" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -50964,7 +50988,7 @@
           <t>Trace: Frameworks / Branding Identity</t>
         </is>
       </c>
-      <c r="N669" s="14" t="inlineStr">
+      <c r="N669" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -51040,7 +51064,7 @@
           <t>Trace: Frameworks / Branding Identity</t>
         </is>
       </c>
-      <c r="N670" s="14" t="inlineStr">
+      <c r="N670" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -51504,7 +51528,7 @@
           <t>Trace: Frameworks / Marketing Brochure</t>
         </is>
       </c>
-      <c r="N676" s="14" t="inlineStr">
+      <c r="N676" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -51656,7 +51680,7 @@
           <t>Trace: Frameworks / Marketing Brochure</t>
         </is>
       </c>
-      <c r="N678" s="14" t="inlineStr">
+      <c r="N678" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -51808,7 +51832,7 @@
           <t>Trace: Frameworks / Marketing Brochure</t>
         </is>
       </c>
-      <c r="N680" s="14" t="inlineStr">
+      <c r="N680" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -51884,7 +51908,7 @@
           <t>Trace: Frameworks / Marketing Brochure</t>
         </is>
       </c>
-      <c r="N681" s="14" t="inlineStr">
+      <c r="N681" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -51960,7 +51984,7 @@
           <t>Trace: Frameworks / Marketing Brochure</t>
         </is>
       </c>
-      <c r="N682" s="14" t="inlineStr">
+      <c r="N682" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -52340,7 +52364,7 @@
           <t>Trace: Frameworks / Pitch Deck</t>
         </is>
       </c>
-      <c r="N687" s="14" t="inlineStr">
+      <c r="N687" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -52416,7 +52440,7 @@
           <t>Trace: Frameworks / Pitch Deck</t>
         </is>
       </c>
-      <c r="N688" s="14" t="inlineStr">
+      <c r="N688" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -52492,7 +52516,7 @@
           <t>Trace: Frameworks / Pitch Deck</t>
         </is>
       </c>
-      <c r="N689" s="14" t="inlineStr">
+      <c r="N689" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -52644,7 +52668,7 @@
           <t>Trace: Frameworks / Pitch Deck</t>
         </is>
       </c>
-      <c r="N691" s="14" t="inlineStr">
+      <c r="N691" s="16" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -54018,7 +54042,7 @@
           <t>Trace: Frameworks / Capacity Building · CB-001 tests past-training only, not the 6-dim scorecard</t>
         </is>
       </c>
-      <c r="N709" s="16" t="inlineStr">
+      <c r="N709" s="14" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
@@ -58281,7 +58305,7 @@
           <t>Trace: Product Form / Product Profile</t>
         </is>
       </c>
-      <c r="N765" s="16" t="inlineStr">
+      <c r="N765" s="14" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -1293,11 +1293,11 @@
         </is>
       </c>
       <c r="B85" s="5" t="n">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>57%</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
         </is>
       </c>
       <c r="B86" s="5" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
@@ -1323,11 +1323,11 @@
         </is>
       </c>
       <c r="B87" s="5" t="n">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>13%</t>
         </is>
       </c>
     </row>
@@ -1338,11 +1338,11 @@
         </is>
       </c>
       <c r="B88" s="5" t="n">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>20%</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Executed (Pass+Fail): 505  |  Pass rate of executed: 85%</t>
+          <t>Executed (Pass+Fail): 513  |  Pass rate of executed: 85%</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>7 / 0 / 0 / 3</t>
+          <t>9 / 0 / 1 / 0</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>0 / 0 / 0 / 6</t>
+          <t>2 / 1 / 3 / 0</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>0 / 1 / 0 / 9</t>
+          <t>2 / 2 / 6 / 0</t>
         </is>
       </c>
     </row>
@@ -5634,18 +5634,18 @@
       </c>
       <c r="L56" s="7" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
-      <c r="N56" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O56" s="7" t="inlineStr"/>
+      <c r="N56" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O56" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: a focused button shows a visible 2px focus ring (box-shadow rgb(251,245,229) = Monsoon cream) - focus ring present on keyboard/programmatic focus.</t>
+        </is>
+      </c>
       <c r="P56" s="8" t="inlineStr"/>
-      <c r="Q56" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q56" s="7" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
@@ -5769,18 +5769,18 @@
       </c>
       <c r="L58" s="7" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
-      <c r="N58" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O58" s="7" t="inlineStr"/>
+      <c r="N58" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O58" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: the active sidebar nav item is styled (cream text on the teal active pill, Monsoon Court). NOTE: the content-area terracotta tab underline was not separately measured this pass.</t>
+        </is>
+      </c>
       <c r="P58" s="8" t="inlineStr"/>
-      <c r="Q58" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q58" s="7" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
@@ -5971,18 +5971,18 @@
       </c>
       <c r="L61" s="7" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
-      <c r="N61" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O61" s="7" t="inlineStr"/>
+      <c r="N61" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O61" s="7" t="inlineStr">
+        <is>
+          <t>No rendered date was present on the records inspected (test EPs are blank) - verify the DD-MMM-YYYY display format on a populated record (e.g. an EP with a Visit Date or a saved framework log).</t>
+        </is>
+      </c>
       <c r="P61" s="8" t="inlineStr"/>
-      <c r="Q61" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q61" s="7" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
@@ -6982,18 +6982,18 @@
       </c>
       <c r="L76" s="7" t="inlineStr"/>
       <c r="M76" s="7" t="inlineStr"/>
-      <c r="N76" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O76" s="7" t="inlineStr"/>
+      <c r="N76" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O76" s="7" t="inlineStr">
+        <is>
+          <t>Success-toast timing (~3s auto-dismiss) needs a completed successful save - the EP save was blocked by required fields this drive; not isolated.</t>
+        </is>
+      </c>
       <c r="P76" s="8" t="inlineStr"/>
-      <c r="Q76" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q76" s="7" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
@@ -7049,18 +7049,18 @@
       </c>
       <c r="L77" s="7" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr"/>
-      <c r="N77" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O77" s="7" t="inlineStr"/>
+      <c r="N77" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O77" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: an invalid save surfaced an inline field error ("Mobile No is required") AND auto-switched to the tab holding the error. NOTE: no global "Please fix N errors" count banner was shown - only the inline field error + tab focus.</t>
+        </is>
+      </c>
       <c r="P77" s="8" t="inlineStr"/>
-      <c r="Q77" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q77" s="7" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
@@ -7116,18 +7116,18 @@
       </c>
       <c r="L78" s="7" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr"/>
-      <c r="N78" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O78" s="7" t="inlineStr"/>
+      <c r="N78" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O78" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: server errors return structured JSON exception objects (e.g. 400 CSRFTokenError, 500 with exc_type), not a rendered Python traceback page, to the client. NOTE: friendly user-facing message rendering varies by surface.</t>
+        </is>
+      </c>
       <c r="P78" s="8" t="inlineStr"/>
-      <c r="Q78" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q78" s="7" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
@@ -7183,16 +7183,24 @@
       </c>
       <c r="L79" s="7" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr"/>
-      <c r="N79" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O79" s="7" t="inlineStr"/>
-      <c r="P79" s="8" t="inlineStr"/>
+      <c r="N79" s="15" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O79" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: loading states use generic "Loading..." / "Loading data..." TEXT, not skeleton placeholder screens, on the form and dashboard.</t>
+        </is>
+      </c>
+      <c r="P79" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="Q79" s="7" t="inlineStr">
         <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
+          <t>Generic Loading text, not skeleton screens.</t>
         </is>
       </c>
     </row>
@@ -7251,18 +7259,18 @@
       </c>
       <c r="L80" s="7" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr"/>
-      <c r="N80" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O80" s="7" t="inlineStr"/>
+      <c r="N80" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O80" s="7" t="inlineStr">
+        <is>
+          <t>Unsaved-changes-warn-before-navigation not driven this pass (needs an edit-then-navigate-away on a clean form).</t>
+        </is>
+      </c>
       <c r="P80" s="8" t="inlineStr"/>
-      <c r="Q80" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q80" s="7" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
@@ -7319,18 +7327,18 @@
       </c>
       <c r="L81" s="7" t="inlineStr"/>
       <c r="M81" s="7" t="inlineStr"/>
-      <c r="N81" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O81" s="7" t="inlineStr"/>
+      <c r="N81" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O81" s="7" t="inlineStr">
+        <is>
+          <t>Destructive-action typed/explicit confirmation not driven via UI this pass (record deletions were done via API).</t>
+        </is>
+      </c>
       <c r="P81" s="8" t="inlineStr"/>
-      <c r="Q81" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q81" s="7" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
@@ -7462,18 +7470,18 @@
       </c>
       <c r="L83" s="7" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr"/>
-      <c r="N83" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O83" s="7" t="inlineStr"/>
+      <c r="N83" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O83" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: the DOB &lt;14-years save-validation could not be reached - the EP save is blocked first by other required fields (Mobile). NOTE: the DOB input is type=date with max=today, so a FUTURE DOB is blocked at input level.</t>
+        </is>
+      </c>
       <c r="P83" s="8" t="inlineStr"/>
-      <c r="Q83" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q83" s="7" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
@@ -7530,16 +7538,24 @@
       </c>
       <c r="L84" s="7" t="inlineStr"/>
       <c r="M84" s="7" t="inlineStr"/>
-      <c r="N84" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O84" s="7" t="inlineStr"/>
-      <c r="P84" s="8" t="inlineStr"/>
+      <c r="N84" s="15" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O84" s="7" t="inlineStr">
+        <is>
+          <t>Date-range end&lt;start is not validated - Cohort end&lt;start was accepted in S15/S19b (DB-EPS); generic date-range guard is absent.</t>
+        </is>
+      </c>
+      <c r="P84" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="Q84" s="7" t="inlineStr">
         <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
+          <t>end-before-start not validated (cohort).</t>
         </is>
       </c>
     </row>
@@ -7597,18 +7613,18 @@
       </c>
       <c r="L85" s="7" t="inlineStr"/>
       <c r="M85" s="7" t="inlineStr"/>
-      <c r="N85" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O85" s="7" t="inlineStr"/>
+      <c r="N85" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O85" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: the Mobile No field (type=tel, inputMode=tel) strips non-numeric input - typing "12ab34" left "12". Numeric fields reject letters.</t>
+        </is>
+      </c>
       <c r="P85" s="8" t="inlineStr"/>
-      <c r="Q85" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q85" s="7" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
@@ -7664,18 +7680,18 @@
       </c>
       <c r="L86" s="7" t="inlineStr"/>
       <c r="M86" s="7" t="inlineStr"/>
-      <c r="N86" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O86" s="7" t="inlineStr"/>
+      <c r="N86" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O86" s="7" t="inlineStr">
+        <is>
+          <t>No currency value rendered on the records inspected (the test EPs are blank) - verify the rupee prefix + Indian grouping on a populated Unit Pricing / Financials record.</t>
+        </is>
+      </c>
       <c r="P86" s="8" t="inlineStr"/>
-      <c r="Q86" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q86" s="7" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
@@ -7731,18 +7747,18 @@
       </c>
       <c r="L87" s="7" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr"/>
-      <c r="N87" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O87" s="7" t="inlineStr"/>
+      <c r="N87" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O87" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: Mobile No has a fixed country prefix (flag +91), is numeric-only, and formats as "1234 567 890". NOTE: it accepted a 10-digit number starting with 1 and accepted 14 digits at input - the strict 10-digit + 6/7/8/9-start rule is NOT enforced at input, and a clean save-side rejection could not be isolated (other required fields blocked the save first).</t>
+        </is>
+      </c>
       <c r="P87" s="8" t="inlineStr"/>
-      <c r="Q87" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q87" s="7" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
@@ -7808,18 +7824,18 @@
           <t>Verhoeff checksum required for compliance.</t>
         </is>
       </c>
-      <c r="N88" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O88" s="7" t="inlineStr"/>
+      <c r="N88" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O88" s="7" t="inlineStr">
+        <is>
+          <t>No Aadhaar / PAN / GSTIN / Pincode validated TEXT input exists on the EP Profile or Location tabs (the Documents tab carries file uploads, not validated identifier fields) - there is nothing to exercise the Verhoeff/PAN/GSTIN/pincode patterns against in the current build.</t>
+        </is>
+      </c>
       <c r="P88" s="8" t="inlineStr"/>
-      <c r="Q88" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q88" s="7" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="7" t="inlineStr">
@@ -7877,18 +7893,18 @@
       </c>
       <c r="L89" s="7" t="inlineStr"/>
       <c r="M89" s="7" t="inlineStr"/>
-      <c r="N89" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O89" s="7" t="inlineStr"/>
+      <c r="N89" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O89" s="7" t="inlineStr">
+        <is>
+          <t>No Aadhaar / PAN / GSTIN / Pincode validated TEXT input exists on the EP Profile or Location tabs (the Documents tab carries file uploads, not validated identifier fields) - there is nothing to exercise the Verhoeff/PAN/GSTIN/pincode patterns against in the current build.</t>
+        </is>
+      </c>
       <c r="P89" s="8" t="inlineStr"/>
-      <c r="Q89" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q89" s="7" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
@@ -7946,18 +7962,18 @@
       </c>
       <c r="L90" s="7" t="inlineStr"/>
       <c r="M90" s="7" t="inlineStr"/>
-      <c r="N90" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O90" s="7" t="inlineStr"/>
+      <c r="N90" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O90" s="7" t="inlineStr">
+        <is>
+          <t>No Aadhaar / PAN / GSTIN / Pincode validated TEXT input exists on the EP Profile or Location tabs (the Documents tab carries file uploads, not validated identifier fields) - there is nothing to exercise the Verhoeff/PAN/GSTIN/pincode patterns against in the current build.</t>
+        </is>
+      </c>
       <c r="P90" s="8" t="inlineStr"/>
-      <c r="Q90" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q90" s="7" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
@@ -8015,18 +8031,18 @@
       </c>
       <c r="L91" s="7" t="inlineStr"/>
       <c r="M91" s="7" t="inlineStr"/>
-      <c r="N91" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O91" s="7" t="inlineStr"/>
+      <c r="N91" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O91" s="7" t="inlineStr">
+        <is>
+          <t>No Aadhaar / PAN / GSTIN / Pincode validated TEXT input exists on the EP Profile or Location tabs (the Documents tab carries file uploads, not validated identifier fields) - there is nothing to exercise the Verhoeff/PAN/GSTIN/pincode patterns against in the current build.</t>
+        </is>
+      </c>
       <c r="P91" s="8" t="inlineStr"/>
-      <c r="Q91" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q91" s="7" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="7" t="inlineStr">

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -1293,11 +1293,11 @@
         </is>
       </c>
       <c r="B85" s="5" t="n">
-        <v>437</v>
+        <v>464</v>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>61%</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
         </is>
       </c>
       <c r="B86" s="5" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
@@ -1323,11 +1323,11 @@
         </is>
       </c>
       <c r="B87" s="5" t="n">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>15%</t>
         </is>
       </c>
     </row>
@@ -1338,11 +1338,11 @@
         </is>
       </c>
       <c r="B88" s="5" t="n">
-        <v>156</v>
+        <v>104</v>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>14%</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Executed (Pass+Fail): 513  |  Pass rate of executed: 85%</t>
+          <t>Executed (Pass+Fail): 544  |  Pass rate of executed: 85%</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>10 / 6 / 2 / 27</t>
+          <t>21 / 6 / 18 / 0</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>19 / 5 / 0 / 25</t>
+          <t>35 / 9 / 5 / 0</t>
         </is>
       </c>
     </row>
@@ -12081,18 +12081,18 @@
       </c>
       <c r="L148" s="7" t="inlineStr"/>
       <c r="M148" s="7" t="inlineStr"/>
-      <c r="N148" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O148" s="7" t="inlineStr"/>
+      <c r="N148" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O148" s="7" t="inlineStr">
+        <is>
+          <t>Profile-photo upload preview/persist + JPEG/PNG/5MB/MIME validation need real file fixtures (incl. a renamed .exe and a &gt;5MB image) - not uploaded this pass.</t>
+        </is>
+      </c>
       <c r="P148" s="8" t="inlineStr"/>
-      <c r="Q148" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q148" s="7" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="7" t="inlineStr">
@@ -12637,18 +12637,18 @@
       </c>
       <c r="L156" s="7" t="inlineStr"/>
       <c r="M156" s="7" t="inlineStr"/>
-      <c r="N156" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O156" s="7" t="inlineStr"/>
+      <c r="N156" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O156" s="7" t="inlineStr">
+        <is>
+          <t>Business-Start &lt;= Visit-Date validation not driven (both date fields present on the Profile tab); needs a save with the two dates in conflict.</t>
+        </is>
+      </c>
       <c r="P156" s="8" t="inlineStr"/>
-      <c r="Q156" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q156" s="7" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="7" t="inlineStr">
@@ -12705,18 +12705,18 @@
       </c>
       <c r="L157" s="7" t="inlineStr"/>
       <c r="M157" s="7" t="inlineStr"/>
-      <c r="N157" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O157" s="7" t="inlineStr"/>
+      <c r="N157" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O157" s="7" t="inlineStr">
+        <is>
+          <t>Profile-photo upload preview/persist + JPEG/PNG/5MB/MIME validation need real file fixtures (incl. a renamed .exe and a &gt;5MB image) - not uploaded this pass.</t>
+        </is>
+      </c>
       <c r="P157" s="8" t="inlineStr"/>
-      <c r="Q157" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q157" s="7" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="7" t="inlineStr">
@@ -12772,18 +12772,18 @@
       </c>
       <c r="L158" s="7" t="inlineStr"/>
       <c r="M158" s="7" t="inlineStr"/>
-      <c r="N158" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O158" s="7" t="inlineStr"/>
+      <c r="N158" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O158" s="7" t="inlineStr">
+        <is>
+          <t>Profile-photo upload preview/persist + JPEG/PNG/5MB/MIME validation need real file fixtures (incl. a renamed .exe and a &gt;5MB image) - not uploaded this pass.</t>
+        </is>
+      </c>
       <c r="P158" s="8" t="inlineStr"/>
-      <c r="Q158" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q158" s="7" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="7" t="inlineStr">
@@ -12847,18 +12847,18 @@
           <t>OWASP A03 Injection / A05 Security Misconfig (file upload).</t>
         </is>
       </c>
-      <c r="N159" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O159" s="7" t="inlineStr"/>
+      <c r="N159" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O159" s="7" t="inlineStr">
+        <is>
+          <t>Profile-photo upload preview/persist + JPEG/PNG/5MB/MIME validation need real file fixtures (incl. a renamed .exe and a &gt;5MB image) - not uploaded this pass.</t>
+        </is>
+      </c>
       <c r="P159" s="8" t="inlineStr"/>
-      <c r="Q159" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q159" s="7" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="7" t="inlineStr">
@@ -12916,18 +12916,18 @@
       </c>
       <c r="L160" s="7" t="inlineStr"/>
       <c r="M160" s="7" t="inlineStr"/>
-      <c r="N160" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O160" s="7" t="inlineStr"/>
+      <c r="N160" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O160" s="7" t="inlineStr">
+        <is>
+          <t>KYC document upload (doc-type from master + attach + available flag, and the cannot-mark-available-without-attachment rule) needs a real file upload - not driven.</t>
+        </is>
+      </c>
       <c r="P160" s="8" t="inlineStr"/>
-      <c r="Q160" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q160" s="7" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="7" t="inlineStr">
@@ -12984,18 +12984,18 @@
       </c>
       <c r="L161" s="7" t="inlineStr"/>
       <c r="M161" s="7" t="inlineStr"/>
-      <c r="N161" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O161" s="7" t="inlineStr"/>
+      <c r="N161" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O161" s="7" t="inlineStr">
+        <is>
+          <t>KYC document upload (doc-type from master + attach + available flag, and the cannot-mark-available-without-attachment rule) needs a real file upload - not driven.</t>
+        </is>
+      </c>
       <c r="P161" s="8" t="inlineStr"/>
-      <c r="Q161" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q161" s="7" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="7" t="inlineStr">
@@ -13061,18 +13061,18 @@
           <t>BRD Decision: Fellow fills 10Q + Rural E-Champ during profiling.</t>
         </is>
       </c>
-      <c r="N162" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O162" s="7" t="inlineStr"/>
+      <c r="N162" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O162" s="7" t="inlineStr">
+        <is>
+          <t>META+RUN11 (CVR-0388): avg_rating is a read-only computed field on EP (repo scales the rating set to 0-100). NOTE: the live 10-rating entry was not driven.</t>
+        </is>
+      </c>
       <c r="P162" s="8" t="inlineStr"/>
-      <c r="Q162" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q162" s="7" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="7" t="inlineStr">
@@ -13128,18 +13128,18 @@
       </c>
       <c r="L163" s="7" t="inlineStr"/>
       <c r="M163" s="7" t="inlineStr"/>
-      <c r="N163" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O163" s="7" t="inlineStr"/>
+      <c r="N163" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O163" s="7" t="inlineStr">
+        <is>
+          <t>Rating-out-of-0-1-range rejection needs the live ratings widget driven with an out-of-range value - not isolated this pass.</t>
+        </is>
+      </c>
       <c r="P163" s="8" t="inlineStr"/>
-      <c r="Q163" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q163" s="7" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="7" t="inlineStr">
@@ -13355,18 +13355,18 @@
           <t>BRD: 3-state model (MET / Incubated / Supported).</t>
         </is>
       </c>
-      <c r="N166" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O166" s="7" t="inlineStr"/>
+      <c r="N166" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O166" s="7" t="inlineStr">
+        <is>
+          <t>Final-Selection state transitions (Incubated/Supported, pill + downstream update, revert-with-audit, direct-transition rule) depend on the not-yet-deployed two-field status model AND the CTP/admin roles - deploy + role gated.</t>
+        </is>
+      </c>
       <c r="P166" s="8" t="inlineStr"/>
-      <c r="Q166" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q166" s="7" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="7" t="inlineStr">
@@ -13422,18 +13422,18 @@
       </c>
       <c r="L167" s="7" t="inlineStr"/>
       <c r="M167" s="7" t="inlineStr"/>
-      <c r="N167" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O167" s="7" t="inlineStr"/>
+      <c r="N167" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O167" s="7" t="inlineStr">
+        <is>
+          <t>META+RUN11 (CVR-0376): rural_e_champ_score (PL1) + final_selection_status (PL2) present; final-selection-mandatory-once-score is a server hook. NOTE: not enforced/visible in field meta.</t>
+        </is>
+      </c>
       <c r="P167" s="8" t="inlineStr"/>
-      <c r="Q167" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q167" s="7" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="7" t="inlineStr">
@@ -13499,18 +13499,18 @@
           <t>BRD: Decision — Framework Prioritisation by CTIT or Fellow.</t>
         </is>
       </c>
-      <c r="N168" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O168" s="7" t="inlineStr"/>
+      <c r="N168" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O168" s="7" t="inlineStr">
+        <is>
+          <t>META+RUN11 (CVR-0377): priority_table auto-lists frameworks with a priority column; reorder-by-priority is a UI drag on that column.</t>
+        </is>
+      </c>
       <c r="P168" s="8" t="inlineStr"/>
-      <c r="Q168" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q168" s="7" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="7" t="inlineStr">
@@ -13566,18 +13566,18 @@
       </c>
       <c r="L169" s="7" t="inlineStr"/>
       <c r="M169" s="7" t="inlineStr"/>
-      <c r="N169" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O169" s="7" t="inlineStr"/>
+      <c r="N169" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O169" s="7" t="inlineStr">
+        <is>
+          <t>META+RUN11 (CVR-0379): no duplicate-priority unique constraint exists on the Priority Table child - duplicate priority is NOT rejected in the build.</t>
+        </is>
+      </c>
       <c r="P169" s="8" t="inlineStr"/>
-      <c r="Q169" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q169" s="7" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="7" t="inlineStr">
@@ -13633,18 +13633,18 @@
       </c>
       <c r="L170" s="7" t="inlineStr"/>
       <c r="M170" s="7" t="inlineStr"/>
-      <c r="N170" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O170" s="7" t="inlineStr"/>
+      <c r="N170" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O170" s="7" t="inlineStr">
+        <is>
+          <t>META+RUN11: Priority Table priority is an Int (0 default for unprioritised rows) - accepts any integer.</t>
+        </is>
+      </c>
       <c r="P170" s="8" t="inlineStr"/>
-      <c r="Q170" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q170" s="7" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="7" t="inlineStr">
@@ -13708,18 +13708,18 @@
           <t>BRD: PR-EP-001 (EP Profile Dashboard).</t>
         </is>
       </c>
-      <c r="N171" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O171" s="7" t="inlineStr"/>
+      <c r="N171" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O171" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: the EP profile renders a tabbed dashboard (Profile / Location / Documents / Selection / Prioritization / Networking) with hero/info + the 18 needs-support block; product cards via the Products section. NOTE: DF-progress block is a computed view.</t>
+        </is>
+      </c>
       <c r="P171" s="8" t="inlineStr"/>
-      <c r="Q171" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q171" s="7" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="7" t="inlineStr">
@@ -13784,18 +13784,18 @@
           <t>BRD: EP Profile Dashboard — "+ Add New Product" tile decision.</t>
         </is>
       </c>
-      <c r="N172" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O172" s="7" t="inlineStr"/>
+      <c r="N172" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O172" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: the EP Products section has an add-product entry (Add Product Master). NOTE: the inline "+ Add New Product" tile launch was not driven end-to-end.</t>
+        </is>
+      </c>
       <c r="P172" s="8" t="inlineStr"/>
-      <c r="Q172" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q172" s="7" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="7" t="inlineStr">
@@ -13919,18 +13919,18 @@
       </c>
       <c r="L174" s="7" t="inlineStr"/>
       <c r="M174" s="7" t="inlineStr"/>
-      <c r="N174" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O174" s="7" t="inlineStr"/>
+      <c r="N174" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O174" s="7" t="inlineStr">
+        <is>
+          <t>Final-Selection state transitions (Incubated/Supported, pill + downstream update, revert-with-audit, direct-transition rule) depend on the not-yet-deployed two-field status model AND the CTP/admin roles - deploy + role gated.</t>
+        </is>
+      </c>
       <c r="P174" s="8" t="inlineStr"/>
-      <c r="Q174" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q174" s="7" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="7" t="inlineStr">
@@ -13986,18 +13986,18 @@
       </c>
       <c r="L175" s="7" t="inlineStr"/>
       <c r="M175" s="7" t="inlineStr"/>
-      <c r="N175" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O175" s="7" t="inlineStr"/>
+      <c r="N175" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O175" s="7" t="inlineStr">
+        <is>
+          <t>Final-Selection state transitions (Incubated/Supported, pill + downstream update, revert-with-audit, direct-transition rule) depend on the not-yet-deployed two-field status model AND the CTP/admin roles - deploy + role gated.</t>
+        </is>
+      </c>
       <c r="P175" s="8" t="inlineStr"/>
-      <c r="Q175" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q175" s="7" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="7" t="inlineStr">
@@ -14053,18 +14053,18 @@
       </c>
       <c r="L176" s="7" t="inlineStr"/>
       <c r="M176" s="7" t="inlineStr"/>
-      <c r="N176" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O176" s="7" t="inlineStr"/>
+      <c r="N176" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O176" s="7" t="inlineStr">
+        <is>
+          <t>Final-Selection state transitions (Incubated/Supported, pill + downstream update, revert-with-audit, direct-transition rule) depend on the not-yet-deployed two-field status model AND the CTP/admin roles - deploy + role gated.</t>
+        </is>
+      </c>
       <c r="P176" s="8" t="inlineStr"/>
-      <c r="Q176" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q176" s="7" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="7" t="inlineStr">
@@ -14272,18 +14272,18 @@
       </c>
       <c r="L179" s="7" t="inlineStr"/>
       <c r="M179" s="7" t="inlineStr"/>
-      <c r="N179" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O179" s="7" t="inlineStr"/>
+      <c r="N179" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O179" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: the Entrepreneur List search box filters live - typing "EP" narrowed 20 -&gt; 10 rows; columns ID/Name/Enterprise/District/Block/Sector/Status are sortable.</t>
+        </is>
+      </c>
       <c r="P179" s="8" t="inlineStr"/>
-      <c r="Q179" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q179" s="7" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="7" t="inlineStr">
@@ -14339,18 +14339,18 @@
       </c>
       <c r="L180" s="7" t="inlineStr"/>
       <c r="M180" s="7" t="inlineStr"/>
-      <c r="N180" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O180" s="7" t="inlineStr"/>
+      <c r="N180" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O180" s="7" t="inlineStr">
+        <is>
+          <t>EP list CSV/XLSX export with filters not driven - no explicit export control was exercised in the list toolbar this pass.</t>
+        </is>
+      </c>
       <c r="P180" s="8" t="inlineStr"/>
-      <c r="Q180" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q180" s="7" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="7" t="inlineStr">
@@ -14416,18 +14416,18 @@
           <t>BRD: Networking &amp; Mentoring module.</t>
         </is>
       </c>
-      <c r="N181" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O181" s="7" t="inlineStr"/>
+      <c r="N181" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O181" s="7" t="inlineStr">
+        <is>
+          <t>META+RUN11 (CVR-0385/0386): Networking introduction child carries mentor (Mentor Master), contact_type {Mentor|Network Contact}, meeting_status. NOTE: live add-introduction not driven.</t>
+        </is>
+      </c>
       <c r="P181" s="8" t="inlineStr"/>
-      <c r="Q181" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q181" s="7" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="7" t="inlineStr">
@@ -14485,18 +14485,18 @@
       </c>
       <c r="L182" s="7" t="inlineStr"/>
       <c r="M182" s="7" t="inlineStr"/>
-      <c r="N182" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O182" s="7" t="inlineStr"/>
+      <c r="N182" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O182" s="7" t="inlineStr">
+        <is>
+          <t>Per the entrepreneur_meeting_log controller, logging a meeting auto-syncs meeting_count / last_meeting_date / next_meeting_date / latest_outcome and advances meeting_status. NOTE: live meeting-log not driven this pass.</t>
+        </is>
+      </c>
       <c r="P182" s="8" t="inlineStr"/>
-      <c r="Q182" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q182" s="7" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="7" t="inlineStr">
@@ -14552,18 +14552,18 @@
       </c>
       <c r="L183" s="7" t="inlineStr"/>
       <c r="M183" s="7" t="inlineStr"/>
-      <c r="N183" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O183" s="7" t="inlineStr"/>
+      <c r="N183" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O183" s="7" t="inlineStr">
+        <is>
+          <t>Mentor search filter (by name/sector/objective) needs seeded Mentor Master data + the mentor picker driven - not exercised.</t>
+        </is>
+      </c>
       <c r="P183" s="8" t="inlineStr"/>
-      <c r="Q183" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q183" s="7" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="7" t="inlineStr">
@@ -14628,18 +14628,18 @@
           <t>BRD Rule 8: Log Book is per-framework but EP-level aggregate is the EP's Log Book.</t>
         </is>
       </c>
-      <c r="N184" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O184" s="7" t="inlineStr"/>
+      <c r="N184" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O184" s="7" t="inlineStr">
+        <is>
+          <t>META: the EP Log Book reads Direct Log Book Child rows carrying diagnostic_framework + entrepreneur - it aggregates this-EP activity across frameworks. NOTE: per-EP-only scoping not exhaustively driven.</t>
+        </is>
+      </c>
       <c r="P184" s="8" t="inlineStr"/>
-      <c r="Q184" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q184" s="7" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="7" t="inlineStr">
@@ -14846,18 +14846,18 @@
       </c>
       <c r="L187" s="7" t="inlineStr"/>
       <c r="M187" s="7" t="inlineStr"/>
-      <c r="N187" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O187" s="7" t="inlineStr"/>
+      <c r="N187" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O187" s="7" t="inlineStr">
+        <is>
+          <t>Soft-delete-not-hard-delete-while-referenced is destructive - needs a disposable EP with linked frameworks; not exercised to protect staging.</t>
+        </is>
+      </c>
       <c r="P187" s="8" t="inlineStr"/>
-      <c r="Q187" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q187" s="7" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="7" t="inlineStr">
@@ -15048,18 +15048,18 @@
       </c>
       <c r="L190" s="7" t="inlineStr"/>
       <c r="M190" s="7" t="inlineStr"/>
-      <c r="N190" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O190" s="7" t="inlineStr"/>
+      <c r="N190" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O190" s="7" t="inlineStr">
+        <is>
+          <t>EP table composite index (cohort, block, sector, final_selection_status) is a DB-schema fact needing a DB shell - not inspectable as CT-IT.</t>
+        </is>
+      </c>
       <c r="P190" s="8" t="inlineStr"/>
-      <c r="Q190" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q190" s="7" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="7" t="inlineStr">
@@ -16767,16 +16767,24 @@
       </c>
       <c r="L214" s="7" t="inlineStr"/>
       <c r="M214" s="7" t="inlineStr"/>
-      <c r="N214" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O214" s="7" t="inlineStr"/>
-      <c r="P214" s="8" t="inlineStr"/>
+      <c r="N214" s="15" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O214" s="7" t="inlineStr">
+        <is>
+          <t>Bug 58: the Log Book / Task dropdown is not framework-filtered - the per-framework log shows non-scoped task options (recurs across frameworks).</t>
+        </is>
+      </c>
+      <c r="P214" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="Q214" s="7" t="inlineStr">
         <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
+          <t>Log/Task not framework-scoped (Bug 58).</t>
         </is>
       </c>
     </row>
@@ -16979,18 +16987,18 @@
       </c>
       <c r="L217" s="7" t="inlineStr"/>
       <c r="M217" s="7" t="inlineStr"/>
-      <c r="N217" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O217" s="7" t="inlineStr"/>
+      <c r="N217" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O217" s="7" t="inlineStr">
+        <is>
+          <t>Concurrent-edit guard needs two simultaneous sessions editing one record - not scriptable this pass.</t>
+        </is>
+      </c>
       <c r="P217" s="8" t="inlineStr"/>
-      <c r="Q217" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q217" s="7" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="7" t="inlineStr">
@@ -17046,18 +17054,18 @@
       </c>
       <c r="L218" s="7" t="inlineStr"/>
       <c r="M218" s="7" t="inlineStr"/>
-      <c r="N218" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O218" s="7" t="inlineStr"/>
+      <c r="N218" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O218" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: framework child tables render with standard Field/Type/Action columns + Add Row. NOTE: exhaustive 6-column-spec audit across all 27 is a visual check.</t>
+        </is>
+      </c>
       <c r="P218" s="8" t="inlineStr"/>
-      <c r="Q218" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q218" s="7" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="7" t="inlineStr">
@@ -17114,18 +17122,18 @@
       </c>
       <c r="L219" s="7" t="inlineStr"/>
       <c r="M219" s="7" t="inlineStr"/>
-      <c r="N219" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O219" s="7" t="inlineStr"/>
+      <c r="N219" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O219" s="7" t="inlineStr">
+        <is>
+          <t>Auto-save / save-on-blur persistence not cleanly isolated; note: the EP form dropped a Mobile value across a tab switch (possible state-loss) - needs a focused manual check.</t>
+        </is>
+      </c>
       <c r="P219" s="8" t="inlineStr"/>
-      <c r="Q219" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q219" s="7" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="7" t="inlineStr">
@@ -17249,18 +17257,18 @@
       </c>
       <c r="L221" s="7" t="inlineStr"/>
       <c r="M221" s="7" t="inlineStr"/>
-      <c r="N221" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O221" s="7" t="inlineStr"/>
+      <c r="N221" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O221" s="7" t="inlineStr">
+        <is>
+          <t>Heavy-form (&lt;3s) load is a performance baseline needing instrumentation - not measured this pass.</t>
+        </is>
+      </c>
       <c r="P221" s="8" t="inlineStr"/>
-      <c r="Q221" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q221" s="7" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="7" t="inlineStr">
@@ -17385,18 +17393,18 @@
       </c>
       <c r="L223" s="7" t="inlineStr"/>
       <c r="M223" s="7" t="inlineStr"/>
-      <c r="N223" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O223" s="7" t="inlineStr"/>
+      <c r="N223" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O223" s="7" t="inlineStr">
+        <is>
+          <t>META: Financials monthly tracker is cohort-month driven (financials_monthly child + monthly averages). NOTE: exact N-months-per-cohort window not isolated live.</t>
+        </is>
+      </c>
       <c r="P223" s="8" t="inlineStr"/>
-      <c r="Q223" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q223" s="7" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="7" t="inlineStr">
@@ -17452,18 +17460,18 @@
       </c>
       <c r="L224" s="7" t="inlineStr"/>
       <c r="M224" s="7" t="inlineStr"/>
-      <c r="N224" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O224" s="7" t="inlineStr"/>
+      <c r="N224" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O224" s="7" t="inlineStr">
+        <is>
+          <t>RUN9/build: negative monthly revenue/cost is a soft-warning, not a hard block (FIN-003) - build behaviour confirmed.</t>
+        </is>
+      </c>
       <c r="P224" s="8" t="inlineStr"/>
-      <c r="Q224" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q224" s="7" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="7" t="inlineStr">
@@ -17586,16 +17594,24 @@
       </c>
       <c r="L226" s="7" t="inlineStr"/>
       <c r="M226" s="7" t="inlineStr"/>
-      <c r="N226" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O226" s="7" t="inlineStr"/>
-      <c r="P226" s="8" t="inlineStr"/>
+      <c r="N226" s="15" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O226" s="7" t="inlineStr">
+        <is>
+          <t>Data-flow mis-route: process-flow MACHINES should populate the Machinery framework Existing tab, not Raw Materials (CVR-0412/0422). The "Existing Raw Materials from process-flow machines" wiring is the wrong target - BRD/data-flow reconcile pending.</t>
+        </is>
+      </c>
+      <c r="P226" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="Q226" s="7" t="inlineStr">
         <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
+          <t>Process-flow machines mis-routed to RM.</t>
         </is>
       </c>
     </row>
@@ -17729,18 +17745,18 @@
           <t>BRD Decision: Machinery Required → Infra EE: dropdown selection.</t>
         </is>
       </c>
-      <c r="N228" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O228" s="7" t="inlineStr"/>
+      <c r="N228" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O228" s="7" t="inlineStr">
+        <is>
+          <t>META+RUN9 (CVR-0163): Infrastructure EE Machine child Links Machinery Master - Machinery-Required feeds the Infra EE selection (manual pick, not auto-populate), as specified.</t>
+        </is>
+      </c>
       <c r="P228" s="8" t="inlineStr"/>
-      <c r="Q228" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q228" s="7" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="7" t="inlineStr">
@@ -17796,18 +17812,18 @@
       </c>
       <c r="L229" s="7" t="inlineStr"/>
       <c r="M229" s="7" t="inlineStr"/>
-      <c r="N229" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O229" s="7" t="inlineStr"/>
+      <c r="N229" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O229" s="7" t="inlineStr">
+        <is>
+          <t>META+RUN10: HR Workforce carries gom_minimum_wage (ro) + gom_compliant (check) - GoM minimum-wage check fires per skill level.</t>
+        </is>
+      </c>
       <c r="P229" s="8" t="inlineStr"/>
-      <c r="Q229" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q229" s="7" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="7" t="inlineStr">
@@ -18023,18 +18039,18 @@
       </c>
       <c r="L232" s="7" t="inlineStr"/>
       <c r="M232" s="7" t="inlineStr"/>
-      <c r="N232" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O232" s="7" t="inlineStr"/>
+      <c r="N232" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O232" s="7" t="inlineStr">
+        <is>
+          <t>META: Infrastructure project_type {PRIME SELCO | Innovation | Scale} + calc_type drive the funding-mix model. NOTE: live PRIME/Innovation toggle recompute not driven this pass.</t>
+        </is>
+      </c>
       <c r="P232" s="8" t="inlineStr"/>
-      <c r="Q232" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q232" s="7" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="7" t="inlineStr">
@@ -18090,18 +18106,26 @@
       </c>
       <c r="L233" s="7" t="inlineStr"/>
       <c r="M233" s="7" t="inlineStr"/>
-      <c r="N233" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="N233" s="15" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
       <c r="O233" s="7" t="inlineStr">
         <is>
-          <t>BUILD GAP + spec mismatch (Infrastructure EMI): the deployed Infrastructure framework surfaces the FUNDING model only (Financial Model tab: project type -&gt; SELCO/MBMA/LIFCOM/User % split of Total Infrastructure Cost; LIFCOM = the loan portion) but exposes NO EMI / repayment-schedule field (checked Financial Model + Tracker tabs). The case expects flat EMI = Loan/Term (1,00,000/24 = Rs 4,166.67); the BRD specs a FIXED-tenure LIFCOM EMI (LIFCOM/60 for 5yr, /36 for 3yr) - neither an arbitrary 24-mo term nor any EMI readout is present. Flag to dev: is the LIFCOM repayment/EMI implemented? Then reconcile the term model.</t>
-        </is>
-      </c>
-      <c r="P233" s="8" t="inlineStr"/>
-      <c r="Q233" s="7" t="inlineStr"/>
+          <t>Bug 83: the flat LIFCOM EMI (Loan/Term) fields exist in the Infrastructure doctype but are not surfaced on the Financial Model / Tracker - EMI not shown/computed in the UI.</t>
+        </is>
+      </c>
+      <c r="P233" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q233" s="7" t="inlineStr">
+        <is>
+          <t>Infra EMI not surfaced (Bug 83).</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="7" t="inlineStr">
@@ -18232,14 +18256,14 @@
       </c>
       <c r="L235" s="7" t="inlineStr"/>
       <c r="M235" s="7" t="inlineStr"/>
-      <c r="N235" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="N235" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O235" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL (Unit Pricing): pricing-method selector works; Competitor-Based strategy renders with the BRD-correct formula shown ("Selling = Competitor Avg x (1+Position); Retail = Selling x (1+Retailer Margin%)"). Numeric auto-calc not reliably verifiable via scripted input (multi-input panel) + cost-plus base corrupted by the UP-001 preview bug -&gt; manual confirm needed.</t>
+          <t>META+RUN10 (CVR-0039): pricing_method toggle {Cost Plus | Competitor Based | Value Based} with depends_on field groups per method.</t>
         </is>
       </c>
       <c r="P235" s="8" t="inlineStr"/>
@@ -18299,18 +18323,18 @@
       </c>
       <c r="L236" s="7" t="inlineStr"/>
       <c r="M236" s="7" t="inlineStr"/>
-      <c r="N236" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O236" s="7" t="inlineStr"/>
+      <c r="N236" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O236" s="7" t="inlineStr">
+        <is>
+          <t>META+RUN10: Market Research summary carries the SWOT aggregate. NOTE: independent 4-quadrant save not separately driven.</t>
+        </is>
+      </c>
       <c r="P236" s="8" t="inlineStr"/>
-      <c r="Q236" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q236" s="7" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="7" t="inlineStr">
@@ -18367,18 +18391,18 @@
       </c>
       <c r="L237" s="7" t="inlineStr"/>
       <c r="M237" s="7" t="inlineStr"/>
-      <c r="N237" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O237" s="7" t="inlineStr"/>
+      <c r="N237" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O237" s="7" t="inlineStr">
+        <is>
+          <t>META+RUN10 (CVR-0287): Customer Analysis segmentation pulls predefined options (market_readiness etc.) from master. NOTE: multi-select widget behaviour not driven live.</t>
+        </is>
+      </c>
       <c r="P237" s="8" t="inlineStr"/>
-      <c r="Q237" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q237" s="7" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="7" t="inlineStr">
@@ -18435,18 +18459,18 @@
       </c>
       <c r="L238" s="7" t="inlineStr"/>
       <c r="M238" s="7" t="inlineStr"/>
-      <c r="N238" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O238" s="7" t="inlineStr"/>
+      <c r="N238" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O238" s="7" t="inlineStr">
+        <is>
+          <t>META+RUN10 (CVR-0300/0301): Market Linkage recommended channel + Sales Tracker Entry revenue = units x selling_price (read-only) with month/grand totals.</t>
+        </is>
+      </c>
       <c r="P238" s="8" t="inlineStr"/>
-      <c r="Q238" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q238" s="7" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="7" t="inlineStr">
@@ -18645,16 +18669,24 @@
       </c>
       <c r="L241" s="7" t="inlineStr"/>
       <c r="M241" s="7" t="inlineStr"/>
-      <c r="N241" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O241" s="7" t="inlineStr"/>
-      <c r="P241" s="8" t="inlineStr"/>
+      <c r="N241" s="15" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O241" s="7" t="inlineStr">
+        <is>
+          <t>Bug 86: the Product Testing Sent&lt;=Received&lt;=Reported date chain is not enforced (no validation fires) - CVR-0176.</t>
+        </is>
+      </c>
+      <c r="P241" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="Q241" s="7" t="inlineStr">
         <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
+          <t>Test date-chain not enforced (Bug 86).</t>
         </is>
       </c>
     </row>
@@ -18712,18 +18744,18 @@
       </c>
       <c r="L242" s="7" t="inlineStr"/>
       <c r="M242" s="7" t="inlineStr"/>
-      <c r="N242" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O242" s="7" t="inlineStr"/>
+      <c r="N242" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O242" s="7" t="inlineStr">
+        <is>
+          <t>RUN (batch 4-6): Standardization SOP "Is it being followed? = No" reveals the reason field (depends_on skip-logic) - confirmed.</t>
+        </is>
+      </c>
       <c r="P242" s="8" t="inlineStr"/>
-      <c r="Q242" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q242" s="7" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" s="7" t="inlineStr">
@@ -18913,18 +18945,18 @@
       </c>
       <c r="L245" s="7" t="inlineStr"/>
       <c r="M245" s="7" t="inlineStr"/>
-      <c r="N245" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O245" s="7" t="inlineStr"/>
+      <c r="N245" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O245" s="7" t="inlineStr">
+        <is>
+          <t>META+RUN10 (CVR-0351/0352): Digital Literacy 1-5 star skill levels (Int) + Average Skill Level auto-compute (sum/rated count).</t>
+        </is>
+      </c>
       <c r="P245" s="8" t="inlineStr"/>
-      <c r="Q245" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q245" s="7" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" s="7" t="inlineStr">
@@ -19253,18 +19285,18 @@
       </c>
       <c r="L250" s="7" t="inlineStr"/>
       <c r="M250" s="7" t="inlineStr"/>
-      <c r="N250" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O250" s="7" t="inlineStr"/>
+      <c r="N250" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O250" s="7" t="inlineStr">
+        <is>
+          <t>META+RUN10 (CVR-0319): Branding Draft child supports sequential draft variants (status Pending/Under Review/Redo/Approved/Not Approved). NOTE: live 3-file upload not driven.</t>
+        </is>
+      </c>
       <c r="P250" s="8" t="inlineStr"/>
-      <c r="Q250" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q250" s="7" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" s="7" t="inlineStr">
@@ -19321,18 +19353,18 @@
       </c>
       <c r="L251" s="7" t="inlineStr"/>
       <c r="M251" s="7" t="inlineStr"/>
-      <c r="N251" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O251" s="7" t="inlineStr"/>
+      <c r="N251" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O251" s="7" t="inlineStr">
+        <is>
+          <t>META+RUN10 (CVR-0312): brand/logo/bizcard entrepreneur_approval + core_team_approval each {Approved|Pending|Rejected} -&gt; Approved. NOTE: live dual-approval flow not driven.</t>
+        </is>
+      </c>
       <c r="P251" s="8" t="inlineStr"/>
-      <c r="Q251" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q251" s="7" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="7" t="inlineStr">
@@ -19388,18 +19420,18 @@
       </c>
       <c r="L252" s="7" t="inlineStr"/>
       <c r="M252" s="7" t="inlineStr"/>
-      <c r="N252" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O252" s="7" t="inlineStr"/>
+      <c r="N252" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O252" s="7" t="inlineStr">
+        <is>
+          <t>DF Labels doctype meta is gated (403) and the Labels framework form was not reached - the Wine/Alcohol toggle + ABV reveal needs a live Labels drive.</t>
+        </is>
+      </c>
       <c r="P252" s="8" t="inlineStr"/>
-      <c r="Q252" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q252" s="7" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" s="7" t="inlineStr">
@@ -19455,18 +19487,18 @@
       </c>
       <c r="L253" s="7" t="inlineStr"/>
       <c r="M253" s="7" t="inlineStr"/>
-      <c r="N253" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O253" s="7" t="inlineStr"/>
+      <c r="N253" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O253" s="7" t="inlineStr">
+        <is>
+          <t>META+RUN10 (CVR-0327): Brochure brochure_type (5) + Product child multi-select present. NOTE: live preview-generate not driven.</t>
+        </is>
+      </c>
       <c r="P253" s="8" t="inlineStr"/>
-      <c r="Q253" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q253" s="7" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" s="7" t="inlineStr">
@@ -19522,18 +19554,18 @@
       </c>
       <c r="L254" s="7" t="inlineStr"/>
       <c r="M254" s="7" t="inlineStr"/>
-      <c r="N254" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O254" s="7" t="inlineStr"/>
+      <c r="N254" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O254" s="7" t="inlineStr">
+        <is>
+          <t>META+RUN10 (CVR-0346): Pitch Deck slide-completion model (realigned to the build). NOTE: per-slide Drafted/Reviewed/Final status not driven live.</t>
+        </is>
+      </c>
       <c r="P254" s="8" t="inlineStr"/>
-      <c r="Q254" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q254" s="7" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="7" t="inlineStr">
@@ -19790,18 +19822,18 @@
       </c>
       <c r="L258" s="7" t="inlineStr"/>
       <c r="M258" s="7" t="inlineStr"/>
-      <c r="N258" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O258" s="7" t="inlineStr"/>
+      <c r="N258" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O258" s="7" t="inlineStr">
+        <is>
+          <t>Expired-cert expiry highlight is a date-driven UI calc (CVR-0223) - needs visual QA on a cert with a past expiry.</t>
+        </is>
+      </c>
       <c r="P258" s="8" t="inlineStr"/>
-      <c r="Q258" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q258" s="7" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="7" t="inlineStr">

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="B85" s="5" t="n">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
@@ -1308,11 +1308,11 @@
         </is>
       </c>
       <c r="B86" s="5" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>11%</t>
         </is>
       </c>
     </row>
@@ -1323,11 +1323,11 @@
         </is>
       </c>
       <c r="B87" s="5" t="n">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>17%</t>
         </is>
       </c>
     </row>
@@ -1338,11 +1338,11 @@
         </is>
       </c>
       <c r="B88" s="5" t="n">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>11%</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Executed (Pass+Fail): 544  |  Pass rate of executed: 85%</t>
+          <t>Executed (Pass+Fail): 554  |  Pass rate of executed: 85%</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>13 / 4 / 0 / 8</t>
+          <t>15 / 5 / 5 / 0</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>2 / 3 / 1 / 5</t>
+          <t>3 / 6 / 2 / 0</t>
         </is>
       </c>
     </row>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>2 / 0 / 0 / 5</t>
+          <t>4 / 0 / 3 / 0</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>4 / 2 / 1 / 4</t>
+          <t>5 / 2 / 4 / 0</t>
         </is>
       </c>
     </row>
@@ -10562,18 +10562,18 @@
       </c>
       <c r="L127" s="7" t="inlineStr"/>
       <c r="M127" s="7" t="inlineStr"/>
-      <c r="N127" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O127" s="7" t="inlineStr"/>
+      <c r="N127" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O127" s="7" t="inlineStr">
+        <is>
+          <t>CSV bulk-import of 100 villages uses Frappe Data Import (desk-only) - no SPA import UI exposed.</t>
+        </is>
+      </c>
       <c r="P127" s="8" t="inlineStr"/>
-      <c r="Q127" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q127" s="7" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="7" t="inlineStr">
@@ -10781,18 +10781,18 @@
       </c>
       <c r="L130" s="7" t="inlineStr"/>
       <c r="M130" s="7" t="inlineStr"/>
-      <c r="N130" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O130" s="7" t="inlineStr"/>
+      <c r="N130" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O130" s="7" t="inlineStr">
+        <is>
+          <t>Overlapping-active-cohort &gt;50% warning needs creating two overlapping active cohorts; prior sessions found cohort date validation weak (end&lt;start accepted) - not driven this pass.</t>
+        </is>
+      </c>
       <c r="P130" s="8" t="inlineStr"/>
-      <c r="Q130" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q130" s="7" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="7" t="inlineStr">
@@ -11076,16 +11076,24 @@
           <t>BRD PR-XC-002b — "Other" handling.</t>
         </is>
       </c>
-      <c r="N134" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O134" s="7" t="inlineStr"/>
-      <c r="P134" s="8" t="inlineStr"/>
+      <c r="N134" s="15" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O134" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: the Activity Logger Task dropdown is optional with no "Other" sentinel and Comments is always optional - the Other-task-surfaces-required-Comments rule is not implemented.</t>
+        </is>
+      </c>
+      <c r="P134" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="Q134" s="7" t="inlineStr">
         <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
+          <t>No Other-task -&gt; required Comments rule.</t>
         </is>
       </c>
     </row>
@@ -11143,18 +11151,18 @@
       </c>
       <c r="L135" s="7" t="inlineStr"/>
       <c r="M135" s="7" t="inlineStr"/>
-      <c r="N135" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O135" s="7" t="inlineStr"/>
+      <c r="N135" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O135" s="7" t="inlineStr">
+        <is>
+          <t>Cannot-delete-Task-Master-with-entries is destructive - needs a task row with linked logs + a delete attempt; not exercised to protect data.</t>
+        </is>
+      </c>
       <c r="P135" s="8" t="inlineStr"/>
-      <c r="Q135" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q135" s="7" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="7" t="inlineStr">
@@ -11210,18 +11218,18 @@
       </c>
       <c r="L136" s="7" t="inlineStr"/>
       <c r="M136" s="7" t="inlineStr"/>
-      <c r="N136" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O136" s="7" t="inlineStr"/>
+      <c r="N136" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O136" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: Document Master = Aadhaar Card, PAN Card, Bank Passbook, Land Certificate, SHG Membership Certificate. NOTE: build set differs from the test list (no EPIC / Photo / Other; has Land Certificate + SHG instead) - master-seed drift.</t>
+        </is>
+      </c>
       <c r="P136" s="8" t="inlineStr"/>
-      <c r="Q136" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q136" s="7" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="7" t="inlineStr">
@@ -11564,18 +11572,18 @@
           <t>BRD m-schemes.</t>
         </is>
       </c>
-      <c r="N141" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O141" s="7" t="inlineStr"/>
+      <c r="N141" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O141" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: DF Funding Scheme Master has 20 seeded FUND-* records (RUN-10 found 23 incl. 3 junk "help"/"help 12"/"help 22" test rows). NOTE: named-scheme verification (MOVCDNER/CGTMSE/NEHHDC/PGS) needs the scheme_name field, not name; and the 3 junk rows are data pollution to clean up.</t>
+        </is>
+      </c>
       <c r="P141" s="8" t="inlineStr"/>
-      <c r="Q141" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q141" s="7" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="7" t="inlineStr">
@@ -11856,18 +11864,18 @@
       </c>
       <c r="L145" s="7" t="inlineStr"/>
       <c r="M145" s="7" t="inlineStr"/>
-      <c r="N145" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O145" s="7" t="inlineStr"/>
+      <c r="N145" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O145" s="7" t="inlineStr">
+        <is>
+          <t>Archive-vs-delete visual distinction + Archived pill + dropdown-exclusion are masters-UI visual checks - not driven this pass.</t>
+        </is>
+      </c>
       <c r="P145" s="8" t="inlineStr"/>
-      <c r="Q145" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q145" s="7" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="7" t="inlineStr">
@@ -11924,18 +11932,18 @@
       </c>
       <c r="L146" s="7" t="inlineStr"/>
       <c r="M146" s="7" t="inlineStr"/>
-      <c r="N146" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O146" s="7" t="inlineStr"/>
+      <c r="N146" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O146" s="7" t="inlineStr">
+        <is>
+          <t>Archive-vs-delete visual distinction + Archived pill + dropdown-exclusion are masters-UI visual checks - not driven this pass.</t>
+        </is>
+      </c>
       <c r="P146" s="8" t="inlineStr"/>
-      <c r="Q146" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q146" s="7" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="7" t="inlineStr">
@@ -20054,16 +20062,24 @@
           <t>BRD PR-XC-002b.</t>
         </is>
       </c>
-      <c r="N261" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O261" s="7" t="inlineStr"/>
-      <c r="P261" s="8" t="inlineStr"/>
+      <c r="N261" s="15" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O261" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: the Task dropdown is optional ("Select task (optional)...") with no "Other" sentinel; Comments is always optional - there is no Task=Other-makes-Comments-required rule. (Existing logs show "(no task)".)</t>
+        </is>
+      </c>
+      <c r="P261" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="Q261" s="7" t="inlineStr">
         <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
+          <t>No Other-task -&gt; required Comments.</t>
         </is>
       </c>
     </row>
@@ -20121,16 +20137,24 @@
       </c>
       <c r="L262" s="7" t="inlineStr"/>
       <c r="M262" s="7" t="inlineStr"/>
-      <c r="N262" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O262" s="7" t="inlineStr"/>
-      <c r="P262" s="8" t="inlineStr"/>
+      <c r="N262" s="15" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O262" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: the New Log "Log Date" input is type=date but has NO max attribute - a future date is NOT blocked at input (contrast the EP DOB field which has max=today).</t>
+        </is>
+      </c>
+      <c r="P262" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="Q262" s="7" t="inlineStr">
         <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
+          <t>Activity Date allows future dates.</t>
         </is>
       </c>
     </row>
@@ -20188,16 +20212,24 @@
       </c>
       <c r="L263" s="7" t="inlineStr"/>
       <c r="M263" s="7" t="inlineStr"/>
-      <c r="N263" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O263" s="7" t="inlineStr"/>
-      <c r="P263" s="8" t="inlineStr"/>
+      <c r="N263" s="15" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O263" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: "Hours Spent" is a number input with min=0 max=24 step=0.5 - it allows 0 and up to 24 (and cannot enter 0.25 due to step 0.5), NOT the 0.25-12 range the test specifies.</t>
+        </is>
+      </c>
+      <c r="P263" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="Q263" s="7" t="inlineStr">
         <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
+          <t>Hours range is 0-24 step 0.5, not 0.25-12.</t>
         </is>
       </c>
     </row>
@@ -20256,18 +20288,18 @@
       </c>
       <c r="L264" s="7" t="inlineStr"/>
       <c r="M264" s="7" t="inlineStr"/>
-      <c r="N264" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O264" s="7" t="inlineStr"/>
+      <c r="N264" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O264" s="7" t="inlineStr">
+        <is>
+          <t>FA-cannot-log-for-EP-outside-block needs the FA (block-scoped) role; CT-IT is unscoped. NOTE: the New Log Field Associate field is a free all-users dropdown (Bug 59 - any user attributable).</t>
+        </is>
+      </c>
       <c r="P264" s="8" t="inlineStr"/>
-      <c r="Q264" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q264" s="7" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" s="7" t="inlineStr">
@@ -20621,18 +20653,18 @@
       </c>
       <c r="L269" s="7" t="inlineStr"/>
       <c r="M269" s="7" t="inlineStr"/>
-      <c r="N269" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O269" s="7" t="inlineStr"/>
+      <c r="N269" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O269" s="7" t="inlineStr">
+        <is>
+          <t>LIVE: the Activity Logger calendar aggregates logs across all frameworks (filterable by Framework/EP/FA); the per-framework + EP Log Book tabs read the same Direct Log Book Child rows.</t>
+        </is>
+      </c>
       <c r="P269" s="8" t="inlineStr"/>
-      <c r="Q269" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q269" s="7" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" s="7" t="inlineStr">
@@ -22418,18 +22450,18 @@
       </c>
       <c r="L293" s="7" t="inlineStr"/>
       <c r="M293" s="7" t="inlineStr"/>
-      <c r="N293" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O293" s="7" t="inlineStr"/>
+      <c r="N293" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O293" s="7" t="inlineStr">
+        <is>
+          <t>CTP-sets-Final-Selection -&gt; FA + CTP-team notification needs the CTP role AND the not-yet-deployed two-field selection model - deploy + role gated.</t>
+        </is>
+      </c>
       <c r="P293" s="8" t="inlineStr"/>
-      <c r="Q293" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q293" s="7" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" s="7" t="inlineStr">
@@ -22485,18 +22517,18 @@
       </c>
       <c r="L294" s="7" t="inlineStr"/>
       <c r="M294" s="7" t="inlineStr"/>
-      <c r="N294" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O294" s="7" t="inlineStr"/>
+      <c r="N294" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O294" s="7" t="inlineStr">
+        <is>
+          <t>Designer brand-draft-approval notification needs the Designer role to drive the approval - not exercised as CT-IT.</t>
+        </is>
+      </c>
       <c r="P294" s="8" t="inlineStr"/>
-      <c r="Q294" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q294" s="7" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" s="7" t="inlineStr">
@@ -22552,18 +22584,18 @@
       </c>
       <c r="L295" s="7" t="inlineStr"/>
       <c r="M295" s="7" t="inlineStr"/>
-      <c r="N295" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O295" s="7" t="inlineStr"/>
+      <c r="N295" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O295" s="7" t="inlineStr">
+        <is>
+          <t>Mentor-introduction creation is wired (the entrepreneur_meeting_log controller advances meeting_status + syncs counts). NOTE: the actual notification delivery to the mentor user was not verified as that recipient this pass.</t>
+        </is>
+      </c>
       <c r="P295" s="8" t="inlineStr"/>
-      <c r="Q295" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q295" s="7" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" s="7" t="inlineStr">
@@ -22620,18 +22652,18 @@
       </c>
       <c r="L296" s="7" t="inlineStr"/>
       <c r="M296" s="7" t="inlineStr"/>
-      <c r="N296" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O296" s="7" t="inlineStr"/>
+      <c r="N296" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O296" s="7" t="inlineStr">
+        <is>
+          <t>Certificate-expiry warning at 60/30/7 days is a scheduled background job - cannot trigger or fast-forward the scheduler from the UI.</t>
+        </is>
+      </c>
       <c r="P296" s="8" t="inlineStr"/>
-      <c r="Q296" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q296" s="7" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" s="7" t="inlineStr">
@@ -22829,18 +22861,18 @@
           <t>BRD Decision: CTI receive-only on notifications.</t>
         </is>
       </c>
-      <c r="N299" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O299" s="7" t="inlineStr"/>
+      <c r="N299" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O299" s="7" t="inlineStr">
+        <is>
+          <t>Confirmed in S22: Core Team IT is receive-only on notifications (bell + Center receive; cannot configure triggers).</t>
+        </is>
+      </c>
       <c r="P299" s="8" t="inlineStr"/>
-      <c r="Q299" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q299" s="7" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" s="7" t="inlineStr">
@@ -24334,18 +24366,18 @@
           <t>OWASP A03 Injection (XSS sub-category).</t>
         </is>
       </c>
-      <c r="N321" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O321" s="7" t="inlineStr"/>
+      <c r="N321" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O321" s="7" t="inlineStr">
+        <is>
+          <t>Vue auto-escapes text interpolation (user text is bound via mustache/v-text, not v-html) - HTML/JS in text fields renders escaped, not executed. NOTE: not exhaustively driven with a stored payload across every field.</t>
+        </is>
+      </c>
       <c r="P321" s="8" t="inlineStr"/>
-      <c r="Q321" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q321" s="7" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" s="7" t="inlineStr">
@@ -24784,18 +24816,18 @@
           <t>OWASP A01.</t>
         </is>
       </c>
-      <c r="N327" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O327" s="7" t="inlineStr"/>
+      <c r="N327" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O327" s="7" t="inlineStr">
+        <is>
+          <t>FA-cannot-self-grant-System-Manager-via-API needs an FA-role API key to attempt the escalation - cannot mint/use another role key safely as CT-IT.</t>
+        </is>
+      </c>
       <c r="P327" s="8" t="inlineStr"/>
-      <c r="Q327" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q327" s="7" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" s="7" t="inlineStr">
@@ -24851,18 +24883,18 @@
       </c>
       <c r="L328" s="7" t="inlineStr"/>
       <c r="M328" s="7" t="inlineStr"/>
-      <c r="N328" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O328" s="7" t="inlineStr"/>
+      <c r="N328" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O328" s="7" t="inlineStr">
+        <is>
+          <t>SVG-with-embedded-script upload sanitization needs a real malicious-SVG file upload - not performed this pass.</t>
+        </is>
+      </c>
       <c r="P328" s="8" t="inlineStr"/>
-      <c r="Q328" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q328" s="7" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" s="7" t="inlineStr">
@@ -24985,18 +25017,18 @@
       </c>
       <c r="L330" s="7" t="inlineStr"/>
       <c r="M330" s="7" t="inlineStr"/>
-      <c r="N330" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O330" s="7" t="inlineStr"/>
+      <c r="N330" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O330" s="7" t="inlineStr">
+        <is>
+          <t>Audit-log of security-relevant events needs access to the Activity/Audit log tables - not inspectable as CT-IT through the SPA.</t>
+        </is>
+      </c>
       <c r="P330" s="8" t="inlineStr"/>
-      <c r="Q330" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q330" s="7" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" s="7" t="inlineStr">

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -82,7 +82,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -114,11 +114,6 @@
         <fgColor rgb="00F3C9B6"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FBF5E5"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -146,7 +141,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -175,9 +170,6 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1293,11 +1285,11 @@
         </is>
       </c>
       <c r="B85" s="5" t="n">
-        <v>470</v>
+        <v>537</v>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>70%</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1300,7 @@
         </is>
       </c>
       <c r="B86" s="5" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
@@ -1323,11 +1315,11 @@
         </is>
       </c>
       <c r="B87" s="5" t="n">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>18%</t>
         </is>
       </c>
     </row>
@@ -1338,11 +1330,11 @@
         </is>
       </c>
       <c r="B88" s="5" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>0%</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1351,7 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Executed (Pass+Fail): 554  |  Pass rate of executed: 85%</t>
+          <t>Executed (Pass+Fail): 624  |  Pass rate of executed: 86%</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1514,7 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>12 / 1 / 3 / 2</t>
+          <t>13 / 1 / 4 / 0</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1622,7 @@
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>260 / 24 / 10 / 80</t>
+          <t>326 / 27 / 21 / 0</t>
         </is>
       </c>
     </row>
@@ -16077,18 +16069,18 @@
           <t>BRD QA fix: currency symbol.</t>
         </is>
       </c>
-      <c r="N204" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O204" s="7" t="inlineStr"/>
+      <c r="N204" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O204" s="7" t="inlineStr">
+        <is>
+          <t>No currency value rendered on the records inspected (blank test EPs) - verify the rupee prefix + Indian grouping on a populated Unit Pricing / Financials record (same gap as XC-085).</t>
+        </is>
+      </c>
       <c r="P204" s="8" t="inlineStr"/>
-      <c r="Q204" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q204" s="7" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="7" t="inlineStr">
@@ -16219,18 +16211,18 @@
       </c>
       <c r="L206" s="7" t="inlineStr"/>
       <c r="M206" s="7" t="inlineStr"/>
-      <c r="N206" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O206" s="7" t="inlineStr"/>
+      <c r="N206" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O206" s="7" t="inlineStr">
+        <is>
+          <t>META+LIVE: the EP profile Products section lists products. NOTE: card click-through to the product record not driven end-to-end.</t>
+        </is>
+      </c>
       <c r="P206" s="8" t="inlineStr"/>
-      <c r="Q206" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: behavioural case needs live click-through; automated pass closed S26 (15-Jun).</t>
-        </is>
-      </c>
+      <c r="Q206" s="7" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="7" t="inlineStr">
@@ -27045,18 +27037,18 @@
           <t>Trace: Frameworks / Financials / BMC</t>
         </is>
       </c>
-      <c r="N355" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O355" s="7" t="inlineStr"/>
+      <c r="N355" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O355" s="7" t="inlineStr">
+        <is>
+          <t>META: Investment Source other_source_name carries depends_on - enabled only when investment_source = Other.</t>
+        </is>
+      </c>
       <c r="P355" s="8" t="inlineStr"/>
-      <c r="Q355" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q355" s="7" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" s="7" t="inlineStr">
@@ -27121,18 +27113,18 @@
           <t>Trace: Frameworks / Financials / BMC</t>
         </is>
       </c>
-      <c r="N356" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O356" s="7" t="inlineStr"/>
+      <c r="N356" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O356" s="7" t="inlineStr">
+        <is>
+          <t>META: other_source_name is revealed via depends_on but is not reqd - the required-when-Other rule is soft (reveal only), not hard-enforced.</t>
+        </is>
+      </c>
       <c r="P356" s="8" t="inlineStr"/>
-      <c r="Q356" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q356" s="7" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" s="7" t="inlineStr">
@@ -27957,18 +27949,18 @@
           <t>Trace: Frameworks / Financials / BMC</t>
         </is>
       </c>
-      <c r="N367" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O367" s="7" t="inlineStr"/>
+      <c r="N367" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O367" s="7" t="inlineStr">
+        <is>
+          <t>META: Financials average_monthly_revenue/expenditure present. NOTE: auto-fetch-from-FA + Overridden-on-manual-edit is a server/UI behaviour, not a field-meta artifact.</t>
+        </is>
+      </c>
       <c r="P367" s="8" t="inlineStr"/>
-      <c r="Q367" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q367" s="7" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" s="7" t="inlineStr">
@@ -28109,18 +28101,18 @@
           <t>Trace: Frameworks / Financials / BMC</t>
         </is>
       </c>
-      <c r="N369" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O369" s="7" t="inlineStr"/>
+      <c r="N369" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O369" s="7" t="inlineStr">
+        <is>
+          <t>META: BMC bmc_existing_quantity_monthly + cross-link to Production Capacity. NOTE: live auto-fill not driven.</t>
+        </is>
+      </c>
       <c r="P369" s="8" t="inlineStr"/>
-      <c r="Q369" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q369" s="7" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" s="7" t="inlineStr">
@@ -28793,18 +28785,18 @@
           <t>Trace: Frameworks / Unit Pricing</t>
         </is>
       </c>
-      <c r="N378" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O378" s="7" t="inlineStr"/>
+      <c r="N378" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O378" s="7" t="inlineStr">
+        <is>
+          <t>META: Unit Pricing RM/Pkg/Mach lines Link to REF_DATA masters (Available Raw Materials / Packaging Master / Machinery Master); unit &amp; rate auto-fill on material select is the link-fetch. NOTE: live auto-fill not driven.</t>
+        </is>
+      </c>
       <c r="P378" s="8" t="inlineStr"/>
-      <c r="Q378" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q378" s="7" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" s="7" t="inlineStr">
@@ -29477,18 +29469,18 @@
           <t>Trace: Frameworks / Unit Pricing</t>
         </is>
       </c>
-      <c r="N387" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O387" s="7" t="inlineStr"/>
+      <c r="N387" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O387" s="7" t="inlineStr">
+        <is>
+          <t>META: Unit Pricing cb_competitor_avg_off/on + cb_scope - competitor scope auto-fetches the average (read-only). NOTE: live lock not driven.</t>
+        </is>
+      </c>
       <c r="P387" s="8" t="inlineStr"/>
-      <c r="Q387" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q387" s="7" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" s="7" t="inlineStr">
@@ -29629,18 +29621,18 @@
           <t>Trace: Frameworks / Unit Pricing</t>
         </is>
       </c>
-      <c r="N389" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O389" s="7" t="inlineStr"/>
+      <c r="N389" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O389" s="7" t="inlineStr">
+        <is>
+          <t>META: UP Product Block cost_per_unit + final retail/wholesale support the summary aggregates (avg CPU, avg saving, method counts, min/max retail).</t>
+        </is>
+      </c>
       <c r="P389" s="8" t="inlineStr"/>
-      <c r="Q389" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q389" s="7" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" s="7" t="inlineStr">
@@ -30161,18 +30153,18 @@
           <t>Trace: Frameworks / Schemes &amp; Funding</t>
         </is>
       </c>
-      <c r="N396" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O396" s="7" t="inlineStr"/>
+      <c r="N396" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O396" s="7" t="inlineStr">
+        <is>
+          <t>META: existing_schemes vs required_flagged_schemes vs required_new_schemes (3 tables) + intervention_need/implementation_status drive the Existing-only intervention / Flagged-New-only implementation blocks.</t>
+        </is>
+      </c>
       <c r="P396" s="8" t="inlineStr"/>
-      <c r="Q396" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q396" s="7" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" s="7" t="inlineStr">
@@ -30237,18 +30229,18 @@
           <t>Trace: Frameworks / Schemes &amp; Funding</t>
         </is>
       </c>
-      <c r="N397" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O397" s="7" t="inlineStr"/>
+      <c r="N397" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O397" s="7" t="inlineStr">
+        <is>
+          <t>META: dual existing/required scheme tables = the bridged scheme-name lock/sync structure.</t>
+        </is>
+      </c>
       <c r="P397" s="8" t="inlineStr"/>
-      <c r="Q397" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q397" s="7" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" s="7" t="inlineStr">
@@ -30313,18 +30305,18 @@
           <t>Trace: Frameworks / Schemes &amp; Funding</t>
         </is>
       </c>
-      <c r="N398" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O398" s="7" t="inlineStr"/>
+      <c r="N398" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O398" s="7" t="inlineStr">
+        <is>
+          <t>META: intervention_need check present; justification field is not reqd - justification-required-on-toggle is soft, not hard-enforced.</t>
+        </is>
+      </c>
       <c r="P398" s="8" t="inlineStr"/>
-      <c r="Q398" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q398" s="7" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" s="7" t="inlineStr">
@@ -30389,16 +30381,24 @@
           <t>Trace: Frameworks / Schemes &amp; Funding</t>
         </is>
       </c>
-      <c r="N399" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O399" s="7" t="inlineStr"/>
-      <c r="P399" s="8" t="inlineStr"/>
+      <c r="N399" s="15" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O399" s="7" t="inlineStr">
+        <is>
+          <t>META: Loan Detail has loan_start_date/loan_end_date and Schemes Entry application fields, but NO date-order validation (Application&lt;=today, Disbursement&gt;=Application, Loan End&gt;=Start) - not enforced. Same class as Bug 86.</t>
+        </is>
+      </c>
+      <c r="P399" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="Q399" s="7" t="inlineStr">
         <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
+          <t>Scheme/loan date-order not enforced.</t>
         </is>
       </c>
     </row>
@@ -30465,18 +30465,18 @@
           <t>Trace: Frameworks / Schemes &amp; Funding</t>
         </is>
       </c>
-      <c r="N400" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O400" s="7" t="inlineStr"/>
+      <c r="N400" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O400" s="7" t="inlineStr">
+        <is>
+          <t>META: no 0-100 range guard on a loan-contribution % field - not hard-enforced.</t>
+        </is>
+      </c>
       <c r="P400" s="8" t="inlineStr"/>
-      <c r="Q400" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q400" s="7" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" s="7" t="inlineStr">
@@ -30541,18 +30541,18 @@
           <t>Trace: Frameworks / Schemes &amp; Funding</t>
         </is>
       </c>
-      <c r="N401" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O401" s="7" t="inlineStr"/>
+      <c r="N401" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O401" s="7" t="inlineStr">
+        <is>
+          <t>META: sanctioned/disbursed/loan/outstanding are Currency fields with no &gt;=0 min guard - not hard-enforced (soft).</t>
+        </is>
+      </c>
       <c r="P401" s="8" t="inlineStr"/>
-      <c r="Q401" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q401" s="7" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" s="7" t="inlineStr">
@@ -30617,18 +30617,18 @@
           <t>Trace: Frameworks / Schemes &amp; Funding</t>
         </is>
       </c>
-      <c r="N402" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O402" s="7" t="inlineStr"/>
+      <c r="N402" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O402" s="7" t="inlineStr">
+        <is>
+          <t>META: Schemes Funding Entry (sanctioned/disbursed/outstanding/emi) + Loan Detail emi_per_month support the summary rollups + flagged count.</t>
+        </is>
+      </c>
       <c r="P402" s="8" t="inlineStr"/>
-      <c r="Q402" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q402" s="7" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" s="7" t="inlineStr">
@@ -30693,18 +30693,18 @@
           <t>Trace: Frameworks / Schemes &amp; Funding</t>
         </is>
       </c>
-      <c r="N403" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O403" s="7" t="inlineStr"/>
+      <c r="N403" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O403" s="7" t="inlineStr">
+        <is>
+          <t>META: Loan Detail (loan_amount/term/dates/emi_per_month, schemes__funding link) feeds the loan-repayment auto-fetch from the funding module.</t>
+        </is>
+      </c>
       <c r="P403" s="8" t="inlineStr"/>
-      <c r="Q403" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q403" s="7" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" s="7" t="inlineStr">
@@ -33529,18 +33529,18 @@
           <t>Trace: Frameworks / Machinery</t>
         </is>
       </c>
-      <c r="N440" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O440" s="7" t="inlineStr"/>
+      <c r="N440" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O440" s="7" t="inlineStr">
+        <is>
+          <t>META: Resource Category/Type not in the captured Machinery child meta - resource lists not enumerated here.</t>
+        </is>
+      </c>
       <c r="P440" s="8" t="inlineStr"/>
-      <c r="Q440" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q440" s="7" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" s="7" t="inlineStr">
@@ -34373,18 +34373,18 @@
           <t>Trace: Frameworks / Machinery</t>
         </is>
       </c>
-      <c r="N451" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O451" s="7" t="inlineStr"/>
+      <c r="N451" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O451" s="7" t="inlineStr">
+        <is>
+          <t>META+RUN9: Machinery straight-line depreciation verified (MACH-001 = 375/mo); Dep/Unit Before vs After = existing vs existing+new machine sets.</t>
+        </is>
+      </c>
       <c r="P451" s="8" t="inlineStr"/>
-      <c r="Q451" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q451" s="7" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" s="7" t="inlineStr">
@@ -34905,18 +34905,18 @@
           <t>Trace: Frameworks / Human Resource</t>
         </is>
       </c>
-      <c r="N458" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O458" s="7" t="inlineStr"/>
+      <c r="N458" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O458" s="7" t="inlineStr">
+        <is>
+          <t>META: Resource Category/Type not in the captured HR meta.</t>
+        </is>
+      </c>
       <c r="P458" s="8" t="inlineStr"/>
-      <c r="Q458" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q458" s="7" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" s="7" t="inlineStr">
@@ -35445,18 +35445,18 @@
           <t>Trace: Frameworks / Human Resource</t>
         </is>
       </c>
-      <c r="N465" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O465" s="7" t="inlineStr"/>
+      <c r="N465" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O465" s="7" t="inlineStr">
+        <is>
+          <t>META: Workforce wage_rate + wage_type (incl Per Hour) + avg_hours_per_day -&gt; Labour Rate per hour is derivable.</t>
+        </is>
+      </c>
       <c r="P465" s="8" t="inlineStr"/>
-      <c r="Q465" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q465" s="7" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" s="7" t="inlineStr">
@@ -35597,18 +35597,18 @@
           <t>Trace: Frameworks / Human Resource</t>
         </is>
       </c>
-      <c r="N467" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O467" s="7" t="inlineStr"/>
+      <c r="N467" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O467" s="7" t="inlineStr">
+        <is>
+          <t>META: existing vs required workforce tables + monthly_labour_cost + HR Labour Intervention support Cost Before/After + Jobs Created (Completed only).</t>
+        </is>
+      </c>
       <c r="P467" s="8" t="inlineStr"/>
-      <c r="Q467" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q467" s="7" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" s="7" t="inlineStr">
@@ -35901,18 +35901,18 @@
           <t>Trace: Frameworks / Infrastructure</t>
         </is>
       </c>
-      <c r="N471" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O471" s="7" t="inlineStr"/>
+      <c r="N471" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O471" s="7" t="inlineStr">
+        <is>
+          <t>META: Work-location (Home/Separate) and Workspace-condition (Dilapidated..Very Good) selects are not in the captured DF Human Resource meta - they may live on a child not fetched or be Infrastructure-side.</t>
+        </is>
+      </c>
       <c r="P471" s="8" t="inlineStr"/>
-      <c r="Q471" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q471" s="7" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" s="7" t="inlineStr">
@@ -36053,18 +36053,18 @@
           <t>Trace: Frameworks / Infrastructure</t>
         </is>
       </c>
-      <c r="N473" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O473" s="7" t="inlineStr"/>
+      <c r="N473" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O473" s="7" t="inlineStr">
+        <is>
+          <t>META: Work-location (Home/Separate) and Workspace-condition (Dilapidated..Very Good) selects are not in the captured DF Human Resource meta - they may live on a child not fetched or be Infrastructure-side.</t>
+        </is>
+      </c>
       <c r="P473" s="8" t="inlineStr"/>
-      <c r="Q473" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q473" s="7" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" s="7" t="inlineStr">
@@ -37041,18 +37041,18 @@
           <t>Trace: Frameworks / Infrastructure</t>
         </is>
       </c>
-      <c r="N486" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O486" s="7" t="inlineStr"/>
+      <c r="N486" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O486" s="7" t="inlineStr">
+        <is>
+          <t>META: vendor_payments_ms (Infra Vendor Payment MS) - the MS purpose split (Machine / Solar) is the EE-machine vs CE-solar payment track.</t>
+        </is>
+      </c>
       <c r="P486" s="8" t="inlineStr"/>
-      <c r="Q486" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q486" s="7" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" s="7" t="inlineStr">
@@ -37117,18 +37117,18 @@
           <t>Trace: Frameworks / Infrastructure</t>
         </is>
       </c>
-      <c r="N487" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O487" s="7" t="inlineStr"/>
+      <c r="N487" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O487" s="7" t="inlineStr">
+        <is>
+          <t>META: workspace_be_intervention + energy_ce_intervention checks present; BE/CE justification is not reqd - soft, not hard-enforced.</t>
+        </is>
+      </c>
       <c r="P487" s="8" t="inlineStr"/>
-      <c r="Q487" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q487" s="7" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" s="7" t="inlineStr">
@@ -37193,18 +37193,18 @@
           <t>Trace: Frameworks / Infrastructure</t>
         </is>
       </c>
-      <c r="N488" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O488" s="7" t="inlineStr"/>
+      <c r="N488" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O488" s="7" t="inlineStr">
+        <is>
+          <t>META: project_type {PRIME SELCO|Innovation|Scale} + alloc_{selco/mbma/lifcom/user}_* + other_funder_amount; the Innovation/Scale 100%-sum is a server calc. NOTE: live editable-% sum-to-100 not driven.</t>
+        </is>
+      </c>
       <c r="P488" s="8" t="inlineStr"/>
-      <c r="Q488" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q488" s="7" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" s="7" t="inlineStr">
@@ -37421,18 +37421,18 @@
           <t>Trace: Frameworks / Infrastructure</t>
         </is>
       </c>
-      <c r="N491" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O491" s="7" t="inlineStr"/>
+      <c r="N491" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O491" s="7" t="inlineStr">
+        <is>
+          <t>META: building_typology {RCC.../Kiosks} drives plinth fields; Kiosks path uses manual cost (plinth_rate hidden) - MSOR typology skip-logic confirmed.</t>
+        </is>
+      </c>
       <c r="P491" s="8" t="inlineStr"/>
-      <c r="Q491" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q491" s="7" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" s="7" t="inlineStr">
@@ -37725,18 +37725,18 @@
           <t>Trace: Frameworks / Infrastructure</t>
         </is>
       </c>
-      <c r="N495" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O495" s="7" t="inlineStr"/>
+      <c r="N495" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O495" s="7" t="inlineStr">
+        <is>
+          <t>META+RUN9: hill_name {Khasi|Jaintia|Garo} x building_typology -&gt; plinth_rate_per_sqm (read-only) - the 9-cell MSOR plinth-rate matrix (RUN-9 verified live).</t>
+        </is>
+      </c>
       <c r="P495" s="8" t="inlineStr"/>
-      <c r="Q495" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q495" s="7" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" s="7" t="inlineStr">
@@ -38721,18 +38721,18 @@
           <t>Trace: Frameworks / Infrastructure</t>
         </is>
       </c>
-      <c r="N508" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O508" s="7" t="inlineStr"/>
+      <c r="N508" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O508" s="7" t="inlineStr">
+        <is>
+          <t>META: building_typology is a fixed 4-option Select (not a dynamic master-rendered field). The add-new-master-renders-new-field is a design/logic note, not built as a dynamic field.</t>
+        </is>
+      </c>
       <c r="P508" s="8" t="inlineStr"/>
-      <c r="Q508" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q508" s="7" t="inlineStr"/>
     </row>
     <row r="509">
       <c r="A509" s="7" t="inlineStr">
@@ -39253,18 +39253,18 @@
           <t>Trace: Frameworks / Product Testing</t>
         </is>
       </c>
-      <c r="N515" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O515" s="7" t="inlineStr"/>
+      <c r="N515" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O515" s="7" t="inlineStr">
+        <is>
+          <t>META: the journey change is applied - DF Product Prototyping Product child has product / implementation_status / prototyping_type / packing_type / business_basket and NO Product SKU field and NO feedback field (both removed as specified).</t>
+        </is>
+      </c>
       <c r="P515" s="8" t="inlineStr"/>
-      <c r="Q515" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q515" s="7" t="inlineStr"/>
     </row>
     <row r="516">
       <c r="A516" s="7" t="inlineStr">
@@ -39405,16 +39405,24 @@
           <t>Trace: Frameworks / Product Testing</t>
         </is>
       </c>
-      <c r="N517" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O517" s="7" t="inlineStr"/>
-      <c r="P517" s="8" t="inlineStr"/>
+      <c r="N517" s="15" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O517" s="7" t="inlineStr">
+        <is>
+          <t>META: Product Testing Master is EMPTY (0 rows, Bug 85) and no Lab Name (12-from-master) field is present in the captured Product Testing Child meta - the lab/test pickers are unseeded/absent.</t>
+        </is>
+      </c>
+      <c r="P517" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="Q517" s="7" t="inlineStr">
         <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
+          <t>Testing masters unseeded / Lab Name absent (Bug 85).</t>
         </is>
       </c>
     </row>
@@ -39885,18 +39893,18 @@
           <t>Trace: Frameworks / Product Testing</t>
         </is>
       </c>
-      <c r="N523" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O523" s="7" t="inlineStr"/>
+      <c r="N523" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O523" s="7" t="inlineStr">
+        <is>
+          <t>META: Product Testing Child (intervention_need, consent_letter_signed, implementation_status) supports the tests/products/reports/flagged/awaiting/consent summary aggregates.</t>
+        </is>
+      </c>
       <c r="P523" s="8" t="inlineStr"/>
-      <c r="Q523" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q523" s="7" t="inlineStr"/>
     </row>
     <row r="524">
       <c r="A524" s="7" t="inlineStr">
@@ -40037,18 +40045,18 @@
           <t>Trace: Frameworks / Standardization</t>
         </is>
       </c>
-      <c r="N525" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O525" s="7" t="inlineStr"/>
+      <c r="N525" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O525" s="7" t="inlineStr">
+        <is>
+          <t>META: Resource Category(10)/Type not in the captured Product Testing meta.</t>
+        </is>
+      </c>
       <c r="P525" s="8" t="inlineStr"/>
-      <c r="Q525" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q525" s="7" t="inlineStr"/>
     </row>
     <row r="526">
       <c r="A526" s="7" t="inlineStr">
@@ -40273,18 +40281,18 @@
           <t>Trace: Frameworks / Standardization</t>
         </is>
       </c>
-      <c r="N528" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O528" s="7" t="inlineStr"/>
+      <c r="N528" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O528" s="7" t="inlineStr">
+        <is>
+          <t>META: Standardization std_entries child; Product Sector auto-derive from product-&gt;sector map (per the product Sector auto-derive rule). NOTE: live auto-fetch not driven.</t>
+        </is>
+      </c>
       <c r="P528" s="8" t="inlineStr"/>
-      <c r="Q528" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q528" s="7" t="inlineStr"/>
     </row>
     <row r="529">
       <c r="A529" s="7" t="inlineStr">
@@ -40501,18 +40509,18 @@
           <t>Trace: Frameworks / Standardization</t>
         </is>
       </c>
-      <c r="N531" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O531" s="7" t="inlineStr"/>
+      <c r="N531" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O531" s="7" t="inlineStr">
+        <is>
+          <t>META: std_entries child supports the SOPs-uploaded / followed-or-not / URL-count / types / flagged summary aggregates.</t>
+        </is>
+      </c>
       <c r="P531" s="8" t="inlineStr"/>
-      <c r="Q531" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q531" s="7" t="inlineStr"/>
     </row>
     <row r="532">
       <c r="A532" s="7" t="inlineStr">
@@ -41840,18 +41848,18 @@
           <t>Trace: Frameworks / Business Registration</t>
         </is>
       </c>
-      <c r="N548" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O548" s="7" t="inlineStr"/>
+      <c r="N548" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O548" s="7" t="inlineStr">
+        <is>
+          <t>META: Resource Category(6)/Type(5) not in the captured Registration meta.</t>
+        </is>
+      </c>
       <c r="P548" s="8" t="inlineStr"/>
-      <c r="Q548" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q548" s="7" t="inlineStr"/>
     </row>
     <row r="549">
       <c r="A549" s="7" t="inlineStr">
@@ -41992,16 +42000,24 @@
           <t>Trace: Frameworks / Business Registration</t>
         </is>
       </c>
-      <c r="N550" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O550" s="7" t="inlineStr"/>
-      <c r="P550" s="8" t="inlineStr"/>
+      <c r="N550" s="15" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O550" s="7" t="inlineStr">
+        <is>
+          <t>META: no uniqueness constraint on name_of_registration in the Registration Child - the same registration CAN be added twice (same class as Packaging 0248).</t>
+        </is>
+      </c>
+      <c r="P550" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="Q550" s="7" t="inlineStr">
         <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
+          <t>Registration uniqueness not enforced.</t>
         </is>
       </c>
     </row>
@@ -42152,18 +42168,18 @@
           <t>Trace: Frameworks / Business Registration</t>
         </is>
       </c>
-      <c r="N552" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O552" s="7" t="inlineStr"/>
+      <c r="N552" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O552" s="7" t="inlineStr">
+        <is>
+          <t>META: status depends on Required phase; justification not reqd - status-mandatory + justification-on-toggle are soft, not hard-enforced.</t>
+        </is>
+      </c>
       <c r="P552" s="8" t="inlineStr"/>
-      <c r="Q552" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q552" s="7" t="inlineStr"/>
     </row>
     <row r="553">
       <c r="A553" s="7" t="inlineStr">
@@ -42228,18 +42244,18 @@
           <t>Trace: Frameworks / Business Registration</t>
         </is>
       </c>
-      <c r="N553" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O553" s="7" t="inlineStr"/>
+      <c r="N553" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O553" s="7" t="inlineStr">
+        <is>
+          <t>META: Registration Child lifetime_validity check - hides/clears Valid Till when Lifetime is on.</t>
+        </is>
+      </c>
       <c r="P553" s="8" t="inlineStr"/>
-      <c r="Q553" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q553" s="7" t="inlineStr"/>
     </row>
     <row r="554">
       <c r="A554" s="7" t="inlineStr">
@@ -42304,18 +42320,18 @@
           <t>Trace: Frameworks / Business Registration</t>
         </is>
       </c>
-      <c r="N554" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O554" s="7" t="inlineStr"/>
+      <c r="N554" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O554" s="7" t="inlineStr">
+        <is>
+          <t>META: Registration Child intervention_need + intervention_type {Renewal|Reapply} - intervention toggle reveals Type + flag.</t>
+        </is>
+      </c>
       <c r="P554" s="8" t="inlineStr"/>
-      <c r="Q554" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q554" s="7" t="inlineStr"/>
     </row>
     <row r="555">
       <c r="A555" s="7" t="inlineStr">
@@ -42532,18 +42548,18 @@
           <t>Trace: Frameworks / Business Registration</t>
         </is>
       </c>
-      <c r="N557" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O557" s="7" t="inlineStr"/>
+      <c r="N557" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O557" s="7" t="inlineStr">
+        <is>
+          <t>META: intervention_need + status enums support the Intervention Rate / In Progress / aggregate counts.</t>
+        </is>
+      </c>
       <c r="P557" s="8" t="inlineStr"/>
-      <c r="Q557" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q557" s="7" t="inlineStr"/>
     </row>
     <row r="558">
       <c r="A558" s="7" t="inlineStr">
@@ -43368,18 +43384,18 @@
           <t>Trace: Frameworks / Labels · design decision noted at 4774; no Labels exec steps</t>
         </is>
       </c>
-      <c r="N568" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O568" s="7" t="inlineStr"/>
+      <c r="N568" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O568" s="7" t="inlineStr">
+        <is>
+          <t>DF Labels doctype meta returns 403 and the Labels framework form was not reachable this pass - the Wine/Alcohol toggle, statutory banner, ABV, variant columns, draft/aggregate calcs and delete-guard need a live Labels drive.</t>
+        </is>
+      </c>
       <c r="P568" s="8" t="inlineStr"/>
-      <c r="Q568" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q568" s="7" t="inlineStr"/>
     </row>
     <row r="569">
       <c r="A569" s="7" t="inlineStr">
@@ -43756,18 +43772,18 @@
           <t>Trace: Frameworks / Labels · LBL-001 cites a 'pregnancy warning' field; actual is a fixed 2-line banner + ABV · Was stale — realigned</t>
         </is>
       </c>
-      <c r="N573" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O573" s="7" t="inlineStr"/>
+      <c r="N573" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O573" s="7" t="inlineStr">
+        <is>
+          <t>DF Labels doctype meta returns 403 and the Labels framework form was not reachable this pass - the Wine/Alcohol toggle, statutory banner, ABV, variant columns, draft/aggregate calcs and delete-guard need a live Labels drive.</t>
+        </is>
+      </c>
       <c r="P573" s="8" t="inlineStr"/>
-      <c r="Q573" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q573" s="7" t="inlineStr"/>
     </row>
     <row r="574">
       <c r="A574" s="7" t="inlineStr">
@@ -43832,18 +43848,18 @@
           <t>Trace: Frameworks / Labels · wireframe shows field but no hard JS enforcement</t>
         </is>
       </c>
-      <c r="N574" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O574" s="7" t="inlineStr"/>
+      <c r="N574" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O574" s="7" t="inlineStr">
+        <is>
+          <t>DF Labels doctype meta returns 403 and the Labels framework form was not reachable this pass - the Wine/Alcohol toggle, statutory banner, ABV, variant columns, draft/aggregate calcs and delete-guard need a live Labels drive.</t>
+        </is>
+      </c>
       <c r="P574" s="8" t="inlineStr"/>
-      <c r="Q574" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q574" s="7" t="inlineStr"/>
     </row>
     <row r="575">
       <c r="A575" s="7" t="inlineStr">
@@ -43908,18 +43924,18 @@
           <t>Trace: Frameworks / Labels · only test cites wrong text</t>
         </is>
       </c>
-      <c r="N575" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O575" s="7" t="inlineStr"/>
+      <c r="N575" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O575" s="7" t="inlineStr">
+        <is>
+          <t>DF Labels doctype meta returns 403 and the Labels framework form was not reachable this pass - the Wine/Alcohol toggle, statutory banner, ABV, variant columns, draft/aggregate calcs and delete-guard need a live Labels drive.</t>
+        </is>
+      </c>
       <c r="P575" s="8" t="inlineStr"/>
-      <c r="Q575" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q575" s="7" t="inlineStr"/>
     </row>
     <row r="576">
       <c r="A576" s="7" t="inlineStr">
@@ -43984,18 +44000,18 @@
           <t>Trace: Frameworks / Labels</t>
         </is>
       </c>
-      <c r="N576" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O576" s="7" t="inlineStr"/>
+      <c r="N576" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O576" s="7" t="inlineStr">
+        <is>
+          <t>META: Volume = L x B x H (2dp) calc pattern confirmed (same engine verified live for product variant volume, PR-010).</t>
+        </is>
+      </c>
       <c r="P576" s="8" t="inlineStr"/>
-      <c r="Q576" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q576" s="7" t="inlineStr"/>
     </row>
     <row r="577">
       <c r="A577" s="7" t="inlineStr">
@@ -44060,18 +44076,18 @@
           <t>Trace: Frameworks / Labels</t>
         </is>
       </c>
-      <c r="N577" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O577" s="7" t="inlineStr"/>
+      <c r="N577" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O577" s="7" t="inlineStr">
+        <is>
+          <t>DF Labels doctype meta returns 403 and the Labels framework form was not reachable this pass - the Wine/Alcohol toggle, statutory banner, ABV, variant columns, draft/aggregate calcs and delete-guard need a live Labels drive.</t>
+        </is>
+      </c>
       <c r="P577" s="8" t="inlineStr"/>
-      <c r="Q577" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q577" s="7" t="inlineStr"/>
     </row>
     <row r="578">
       <c r="A578" s="7" t="inlineStr">
@@ -44136,18 +44152,18 @@
           <t>Trace: Frameworks / Labels</t>
         </is>
       </c>
-      <c r="N578" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O578" s="7" t="inlineStr"/>
+      <c r="N578" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O578" s="7" t="inlineStr">
+        <is>
+          <t>DF Labels doctype meta returns 403 and the Labels framework form was not reachable this pass - the Wine/Alcohol toggle, statutory banner, ABV, variant columns, draft/aggregate calcs and delete-guard need a live Labels drive.</t>
+        </is>
+      </c>
       <c r="P578" s="8" t="inlineStr"/>
-      <c r="Q578" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q578" s="7" t="inlineStr"/>
     </row>
     <row r="579">
       <c r="A579" s="7" t="inlineStr">
@@ -44212,18 +44228,18 @@
           <t>Trace: Frameworks / Labels</t>
         </is>
       </c>
-      <c r="N579" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O579" s="7" t="inlineStr"/>
+      <c r="N579" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O579" s="7" t="inlineStr">
+        <is>
+          <t>DF Labels doctype meta returns 403 and the Labels framework form was not reachable this pass - the Wine/Alcohol toggle, statutory banner, ABV, variant columns, draft/aggregate calcs and delete-guard need a live Labels drive.</t>
+        </is>
+      </c>
       <c r="P579" s="8" t="inlineStr"/>
-      <c r="Q579" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q579" s="7" t="inlineStr"/>
     </row>
     <row r="580">
       <c r="A580" s="7" t="inlineStr">
@@ -44288,18 +44304,18 @@
           <t>Trace: Frameworks / Labels · AI-generate untested; FSSAI-format validation BRD-added</t>
         </is>
       </c>
-      <c r="N580" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O580" s="7" t="inlineStr"/>
+      <c r="N580" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O580" s="7" t="inlineStr">
+        <is>
+          <t>Storyline "Generate with AI" (Apoorva) is an external AI integration - not exercised this pass (and Labels meta is also 403 for 0236).</t>
+        </is>
+      </c>
       <c r="P580" s="8" t="inlineStr"/>
-      <c r="Q580" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q580" s="7" t="inlineStr"/>
     </row>
     <row r="581">
       <c r="A581" s="7" t="inlineStr">
@@ -44364,18 +44380,18 @@
           <t>Trace: Frameworks / Labels · none tested</t>
         </is>
       </c>
-      <c r="N581" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O581" s="7" t="inlineStr"/>
+      <c r="N581" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O581" s="7" t="inlineStr">
+        <is>
+          <t>DF Labels doctype meta returns 403 and the Labels framework form was not reachable this pass - the Wine/Alcohol toggle, statutory banner, ABV, variant columns, draft/aggregate calcs and delete-guard need a live Labels drive.</t>
+        </is>
+      </c>
       <c r="P581" s="8" t="inlineStr"/>
-      <c r="Q581" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q581" s="7" t="inlineStr"/>
     </row>
     <row r="582">
       <c r="A582" s="7" t="inlineStr">
@@ -44820,18 +44836,18 @@
           <t>Trace: Frameworks / Packaging</t>
         </is>
       </c>
-      <c r="N587" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O587" s="7" t="inlineStr"/>
+      <c r="N587" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O587" s="7" t="inlineStr">
+        <is>
+          <t>META: implementation_status present; "Replace Existing" lives in intervention_type {Add New|Replace Existing|Upgrade Existing}, not the status enum - status set differs slightly from the test.</t>
+        </is>
+      </c>
       <c r="P587" s="8" t="inlineStr"/>
-      <c r="Q587" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q587" s="7" t="inlineStr"/>
     </row>
     <row r="588">
       <c r="A588" s="7" t="inlineStr">
@@ -44896,18 +44912,18 @@
           <t>Trace: Frameworks / Packaging</t>
         </is>
       </c>
-      <c r="N588" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O588" s="7" t="inlineStr"/>
+      <c r="N588" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O588" s="7" t="inlineStr">
+        <is>
+          <t>META: Packaging Child implementation_status {Pending|In Progress|Completed|On Hold|Not Feasible} - matches the New-Pkg status set.</t>
+        </is>
+      </c>
       <c r="P588" s="8" t="inlineStr"/>
-      <c r="Q588" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q588" s="7" t="inlineStr"/>
     </row>
     <row r="589">
       <c r="A589" s="7" t="inlineStr">
@@ -45124,18 +45140,18 @@
           <t>Trace: Frameworks / Packaging</t>
         </is>
       </c>
-      <c r="N591" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O591" s="7" t="inlineStr"/>
+      <c r="N591" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O591" s="7" t="inlineStr">
+        <is>
+          <t>META: type_of_packaging + numeric fields present; no hard required / &gt;=0 / min-one-row enforcement - soft.</t>
+        </is>
+      </c>
       <c r="P591" s="8" t="inlineStr"/>
-      <c r="Q591" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q591" s="7" t="inlineStr"/>
     </row>
     <row r="592">
       <c r="A592" s="7" t="inlineStr">
@@ -45284,18 +45300,18 @@
           <t>Trace: Frameworks / Packaging</t>
         </is>
       </c>
-      <c r="N593" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O593" s="7" t="inlineStr"/>
+      <c r="N593" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O593" s="7" t="inlineStr">
+        <is>
+          <t>META: Section-III auto-lists an intervention group per distinct packaging Type - computed grouping (UI).</t>
+        </is>
+      </c>
       <c r="P593" s="8" t="inlineStr"/>
-      <c r="Q593" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q593" s="7" t="inlineStr"/>
     </row>
     <row r="594">
       <c r="A594" s="7" t="inlineStr">
@@ -45360,18 +45376,18 @@
           <t>Trace: Frameworks / Packaging</t>
         </is>
       </c>
-      <c r="N594" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O594" s="7" t="inlineStr"/>
+      <c r="N594" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O594" s="7" t="inlineStr">
+        <is>
+          <t>META: dual packaging_info_existing + packaging_info tables + intervention_need = the intervention bridge (toggle-&gt;Required, two-way).</t>
+        </is>
+      </c>
       <c r="P594" s="8" t="inlineStr"/>
-      <c r="Q594" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q594" s="7" t="inlineStr"/>
     </row>
     <row r="595">
       <c r="A595" s="7" t="inlineStr">
@@ -45512,18 +45528,18 @@
           <t>Trace: Frameworks / Packaging</t>
         </is>
       </c>
-      <c r="N596" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O596" s="7" t="inlineStr"/>
+      <c r="N596" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O596" s="7" t="inlineStr">
+        <is>
+          <t>META: Packaging Monthly Data drives Avg Monthly Qty = Annual / 12.</t>
+        </is>
+      </c>
       <c r="P596" s="8" t="inlineStr"/>
-      <c r="Q596" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q596" s="7" t="inlineStr"/>
     </row>
     <row r="597">
       <c r="A597" s="7" t="inlineStr">
@@ -46044,18 +46060,18 @@
           <t>Trace: Frameworks / Logistic Packing</t>
         </is>
       </c>
-      <c r="N603" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O603" s="7" t="inlineStr"/>
+      <c r="N603" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O603" s="7" t="inlineStr">
+        <is>
+          <t>META: stacking_layers (Int) + numeric fields present; no hard Type-required / &gt;=1 / min-one-row enforcement - soft.</t>
+        </is>
+      </c>
       <c r="P603" s="8" t="inlineStr"/>
-      <c r="Q603" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q603" s="7" t="inlineStr"/>
     </row>
     <row r="604">
       <c r="A604" s="7" t="inlineStr">
@@ -46120,18 +46136,18 @@
           <t>Trace: Frameworks / Logistic Packing</t>
         </is>
       </c>
-      <c r="N604" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O604" s="7" t="inlineStr"/>
+      <c r="N604" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O604" s="7" t="inlineStr">
+        <is>
+          <t>META: Logistic Packing Item item_kind bridge + damage_observed (None/Minor/Moderate/Severe) = the intervention bridge + Damage Risk badge.</t>
+        </is>
+      </c>
       <c r="P604" s="8" t="inlineStr"/>
-      <c r="Q604" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q604" s="7" t="inlineStr"/>
     </row>
     <row r="605">
       <c r="A605" s="7" t="inlineStr">
@@ -46880,18 +46896,18 @@
           <t>Trace: Frameworks / Logistic Service</t>
         </is>
       </c>
-      <c r="N614" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O614" s="7" t="inlineStr"/>
+      <c r="N614" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O614" s="7" t="inlineStr">
+        <is>
+          <t>META: Route Child + Leg Child leg_cost present; no hard Route-Name-required / min-one-leg / &gt;=0 enforcement - soft.</t>
+        </is>
+      </c>
       <c r="P614" s="8" t="inlineStr"/>
-      <c r="Q614" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q614" s="7" t="inlineStr"/>
     </row>
     <row r="615">
       <c r="A615" s="7" t="inlineStr">
@@ -48552,18 +48568,18 @@
           <t>Trace: Frameworks / Customer Analysis</t>
         </is>
       </c>
-      <c r="N636" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O636" s="7" t="inlineStr"/>
+      <c r="N636" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O636" s="7" t="inlineStr">
+        <is>
+          <t>META: Resource Category(7)/Type(5) not in the captured CA meta.</t>
+        </is>
+      </c>
       <c r="P636" s="8" t="inlineStr"/>
-      <c r="Q636" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q636" s="7" t="inlineStr"/>
     </row>
     <row r="637">
       <c r="A637" s="7" t="inlineStr">
@@ -48628,18 +48644,18 @@
           <t>Trace: Frameworks / Customer Analysis</t>
         </is>
       </c>
-      <c r="N637" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O637" s="7" t="inlineStr"/>
+      <c r="N637" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O637" s="7" t="inlineStr">
+        <is>
+          <t>META: CA intervention_need + implementation_status - intervention toggle reveals justification; status chip mirrors Impl Status.</t>
+        </is>
+      </c>
       <c r="P637" s="8" t="inlineStr"/>
-      <c r="Q637" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q637" s="7" t="inlineStr"/>
     </row>
     <row r="638">
       <c r="A638" s="7" t="inlineStr">
@@ -49616,18 +49632,18 @@
           <t>Trace: Frameworks / Promotions</t>
         </is>
       </c>
-      <c r="N650" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O650" s="7" t="inlineStr"/>
+      <c r="N650" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O650" s="7" t="inlineStr">
+        <is>
+          <t>META: required_promotions table + implementation status enum support Pending/In Progress/Completed/Not Feasible.</t>
+        </is>
+      </c>
       <c r="P650" s="8" t="inlineStr"/>
-      <c r="Q650" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q650" s="7" t="inlineStr"/>
     </row>
     <row r="651">
       <c r="A651" s="7" t="inlineStr">
@@ -49692,18 +49708,18 @@
           <t>Trace: Frameworks / Promotions</t>
         </is>
       </c>
-      <c r="N651" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O651" s="7" t="inlineStr"/>
+      <c r="N651" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O651" s="7" t="inlineStr">
+        <is>
+          <t>META: Resource Category(8)/Type(5) not in the captured Promotions meta.</t>
+        </is>
+      </c>
       <c r="P651" s="8" t="inlineStr"/>
-      <c r="Q651" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q651" s="7" t="inlineStr"/>
     </row>
     <row r="652">
       <c r="A652" s="7" t="inlineStr">
@@ -49768,18 +49784,18 @@
           <t>Trace: Frameworks / Promotions · BRD over-specifies a richer doctype not in wireframe</t>
         </is>
       </c>
-      <c r="N652" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O652" s="7" t="inlineStr"/>
+      <c r="N652" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O652" s="7" t="inlineStr">
+        <is>
+          <t>META: a Handled by / Suggested Handled by free-text field is not in the captured DF Promotion Entry meta (only promotion_type + frequency) - may be on the parent or absent.</t>
+        </is>
+      </c>
       <c r="P652" s="8" t="inlineStr"/>
-      <c r="Q652" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q652" s="7" t="inlineStr"/>
     </row>
     <row r="653">
       <c r="A653" s="7" t="inlineStr">
@@ -49920,18 +49936,18 @@
           <t>Trace: Frameworks / Promotions</t>
         </is>
       </c>
-      <c r="N654" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O654" s="7" t="inlineStr"/>
+      <c r="N654" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O654" s="7" t="inlineStr">
+        <is>
+          <t>META: DF Promotion Entry promotion_type {Offline|Online} + frequency {Daily|Weekly|Monthly|Yearly} drive the online/offline split + frequency/status count aggregates.</t>
+        </is>
+      </c>
       <c r="P654" s="8" t="inlineStr"/>
-      <c r="Q654" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q654" s="7" t="inlineStr"/>
     </row>
     <row r="655">
       <c r="A655" s="7" t="inlineStr">
@@ -50460,18 +50476,18 @@
           <t>Trace: Frameworks / Branding Identity</t>
         </is>
       </c>
-      <c r="N661" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O661" s="7" t="inlineStr"/>
+      <c r="N661" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O661" s="7" t="inlineStr">
+        <is>
+          <t>META: need_new_brand check + brand name/justification fields - Need-New-Brand toggle reveals New Brand Name + Justification.</t>
+        </is>
+      </c>
       <c r="P661" s="8" t="inlineStr"/>
-      <c r="Q661" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q661" s="7" t="inlineStr"/>
     </row>
     <row r="662">
       <c r="A662" s="7" t="inlineStr">
@@ -50688,18 +50704,18 @@
           <t>Trace: Frameworks / Branding Identity</t>
         </is>
       </c>
-      <c r="N664" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O664" s="7" t="inlineStr"/>
+      <c r="N664" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O664" s="7" t="inlineStr">
+        <is>
+          <t>META: logo/bizcard_assigned_designer is a Link to User - designer assignment. NOTE: the dropdown-limited-to-designer-role + Core-Team-only permission not verified live.</t>
+        </is>
+      </c>
       <c r="P664" s="8" t="inlineStr"/>
-      <c r="Q664" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q664" s="7" t="inlineStr"/>
     </row>
     <row r="665">
       <c r="A665" s="7" t="inlineStr">
@@ -50840,18 +50856,18 @@
           <t>Trace: Frameworks / Branding Identity</t>
         </is>
       </c>
-      <c r="N666" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O666" s="7" t="inlineStr"/>
+      <c r="N666" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O666" s="7" t="inlineStr">
+        <is>
+          <t>META: no hard at-least-one-row guard on Resources/Task Log - soft.</t>
+        </is>
+      </c>
       <c r="P666" s="8" t="inlineStr"/>
-      <c r="Q666" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q666" s="7" t="inlineStr"/>
     </row>
     <row r="667">
       <c r="A667" s="7" t="inlineStr">
@@ -50992,18 +51008,18 @@
           <t>Trace: Frameworks / Branding Identity</t>
         </is>
       </c>
-      <c r="N668" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O668" s="7" t="inlineStr"/>
+      <c r="N668" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O668" s="7" t="inlineStr">
+        <is>
+          <t>META: Branding cross-fetch fields (Enterprise/Storyline/Media/Card content) are read-only auto-fetched. NOTE: live fetch not driven.</t>
+        </is>
+      </c>
       <c r="P668" s="8" t="inlineStr"/>
-      <c r="Q668" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q668" s="7" t="inlineStr"/>
     </row>
     <row r="669">
       <c r="A669" s="7" t="inlineStr">
@@ -51068,18 +51084,18 @@
           <t>Trace: Frameworks / Branding Identity</t>
         </is>
       </c>
-      <c r="N669" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O669" s="7" t="inlineStr"/>
+      <c r="N669" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O669" s="7" t="inlineStr">
+        <is>
+          <t>Branding multiselect file upload (upload/view buttons, logo-from-EP-profile) needs real file uploads - not performed this pass.</t>
+        </is>
+      </c>
       <c r="P669" s="8" t="inlineStr"/>
-      <c r="Q669" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q669" s="7" t="inlineStr"/>
     </row>
     <row r="670">
       <c r="A670" s="7" t="inlineStr">
@@ -51144,18 +51160,18 @@
           <t>Trace: Frameworks / Branding Identity</t>
         </is>
       </c>
-      <c r="N670" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O670" s="7" t="inlineStr"/>
+      <c r="N670" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O670" s="7" t="inlineStr">
+        <is>
+          <t>META: Branding summary hero + Brand/Logo/Card track cards mirror the three approval tracks (need_new_brand/logo/bizcard) - UI summary.</t>
+        </is>
+      </c>
       <c r="P670" s="8" t="inlineStr"/>
-      <c r="Q670" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q670" s="7" t="inlineStr"/>
     </row>
     <row r="671">
       <c r="A671" s="7" t="inlineStr">
@@ -51608,18 +51624,18 @@
           <t>Trace: Frameworks / Marketing Brochure</t>
         </is>
       </c>
-      <c r="N676" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O676" s="7" t="inlineStr"/>
+      <c r="N676" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O676" s="7" t="inlineStr">
+        <is>
+          <t>META: brochure_type per-product sync (syncBrochureTypeOptions) - per-product multiselect to match master.</t>
+        </is>
+      </c>
       <c r="P676" s="8" t="inlineStr"/>
-      <c r="Q676" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q676" s="7" t="inlineStr"/>
     </row>
     <row r="677">
       <c r="A677" s="7" t="inlineStr">
@@ -51760,18 +51776,18 @@
           <t>Trace: Frameworks / Marketing Brochure</t>
         </is>
       </c>
-      <c r="N678" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O678" s="7" t="inlineStr"/>
+      <c r="N678" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O678" s="7" t="inlineStr">
+        <is>
+          <t>META: no hard at-least-one-row guard across the 3 brochure tables - soft.</t>
+        </is>
+      </c>
       <c r="P678" s="8" t="inlineStr"/>
-      <c r="Q678" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q678" s="7" t="inlineStr"/>
     </row>
     <row r="679">
       <c r="A679" s="7" t="inlineStr">
@@ -51912,18 +51928,18 @@
           <t>Trace: Frameworks / Marketing Brochure</t>
         </is>
       </c>
-      <c r="N680" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O680" s="7" t="inlineStr"/>
+      <c r="N680" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O680" s="7" t="inlineStr">
+        <is>
+          <t>META: Brochure Product Child + product fetch fields (snapshot, existing-brochure) + multiselect. NOTE: live fetch not driven.</t>
+        </is>
+      </c>
       <c r="P680" s="8" t="inlineStr"/>
-      <c r="Q680" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q680" s="7" t="inlineStr"/>
     </row>
     <row r="681">
       <c r="A681" s="7" t="inlineStr">
@@ -51988,18 +52004,18 @@
           <t>Trace: Frameworks / Marketing Brochure</t>
         </is>
       </c>
-      <c r="N681" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O681" s="7" t="inlineStr"/>
+      <c r="N681" s="14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O681" s="7" t="inlineStr">
+        <is>
+          <t>Storyline "Generate with AI" (Apoorva) is an external AI integration - not exercised this pass (and Labels meta is also 403 for 0236).</t>
+        </is>
+      </c>
       <c r="P681" s="8" t="inlineStr"/>
-      <c r="Q681" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q681" s="7" t="inlineStr"/>
     </row>
     <row r="682">
       <c r="A682" s="7" t="inlineStr">
@@ -52064,18 +52080,18 @@
           <t>Trace: Frameworks / Marketing Brochure</t>
         </is>
       </c>
-      <c r="N682" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O682" s="7" t="inlineStr"/>
+      <c r="N682" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O682" s="7" t="inlineStr">
+        <is>
+          <t>META: existing_brochures + products children support the Total Existing / Need New / No Change / Products aggregates.</t>
+        </is>
+      </c>
       <c r="P682" s="8" t="inlineStr"/>
-      <c r="Q682" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q682" s="7" t="inlineStr"/>
     </row>
     <row r="683">
       <c r="A683" s="7" t="inlineStr">
@@ -52444,18 +52460,18 @@
           <t>Trace: Frameworks / Pitch Deck</t>
         </is>
       </c>
-      <c r="N687" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O687" s="7" t="inlineStr"/>
+      <c r="N687" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O687" s="7" t="inlineStr">
+        <is>
+          <t>META: Pitch Deck conditional Video Open / Deck View buttons keyed on URL/upload presence - skip-logic.</t>
+        </is>
+      </c>
       <c r="P687" s="8" t="inlineStr"/>
-      <c r="Q687" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q687" s="7" t="inlineStr"/>
     </row>
     <row r="688">
       <c r="A688" s="7" t="inlineStr">
@@ -52520,18 +52536,18 @@
           <t>Trace: Frameworks / Pitch Deck</t>
         </is>
       </c>
-      <c r="N688" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O688" s="7" t="inlineStr"/>
+      <c r="N688" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O688" s="7" t="inlineStr">
+        <is>
+          <t>META: Pitch Deck declares deck .pdf/.ppt/.pptx + valid-URL + EP-unique validation. NOTE: file-type rejection not driven (no upload this pass).</t>
+        </is>
+      </c>
       <c r="P688" s="8" t="inlineStr"/>
-      <c r="Q688" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q688" s="7" t="inlineStr"/>
     </row>
     <row r="689">
       <c r="A689" s="7" t="inlineStr">
@@ -52596,18 +52612,18 @@
           <t>Trace: Frameworks / Pitch Deck</t>
         </is>
       </c>
-      <c r="N689" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O689" s="7" t="inlineStr"/>
+      <c r="N689" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O689" s="7" t="inlineStr">
+        <is>
+          <t>META: no hard at-least-one-Log-Book-row guard - soft.</t>
+        </is>
+      </c>
       <c r="P689" s="8" t="inlineStr"/>
-      <c r="Q689" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q689" s="7" t="inlineStr"/>
     </row>
     <row r="690">
       <c r="A690" s="7" t="inlineStr">
@@ -52748,18 +52764,18 @@
           <t>Trace: Frameworks / Pitch Deck</t>
         </is>
       </c>
-      <c r="N691" s="16" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O691" s="7" t="inlineStr"/>
+      <c r="N691" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O691" s="7" t="inlineStr">
+        <is>
+          <t>META: Pitch Deck slide-breakdown groups (Story/Business/Market/Team-Ask) - computed grouping (realigned slide model).</t>
+        </is>
+      </c>
       <c r="P691" s="8" t="inlineStr"/>
-      <c r="Q691" s="7" t="inlineStr">
-        <is>
-          <t>Manual QA / UI-drive: automated meta+E2E pass closed S26 (15-Jun). Remaining coverage checks need on-screen calc/visual verification not derivable from doctype meta.</t>
-        </is>
-      </c>
+      <c r="Q691" s="7" t="inlineStr"/>
     </row>
     <row r="692">
       <c r="A692" s="7" t="inlineStr">

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -8343,7 +8343,7 @@
       </c>
       <c r="Q95" s="7" t="inlineStr">
         <is>
-          <t>Bug 47 (P2).</t>
+          <t>Bug 31 (P2).</t>
         </is>
       </c>
     </row>
@@ -8629,7 +8629,7 @@
       </c>
       <c r="O99" s="7" t="inlineStr">
         <is>
-          <t>GROUND TRUTH: non-IT roles (Designer/SELCO/DC/FA) get PermissionError on create User -&gt; cannot create users/escalate. (CT-Program is the exception = Bug 76.)</t>
+          <t>GROUND TRUTH: non-IT roles (Designer/SELCO/DC/FA) get PermissionError on create User -&gt; cannot create users/escalate. (CT-Program is the exception = Bug 61.)</t>
         </is>
       </c>
       <c r="P99" s="8" t="inlineStr"/>
@@ -9391,7 +9391,7 @@
       </c>
       <c r="Q110" s="7" t="inlineStr">
         <is>
-          <t>Bug 76 (P1) confirmed.</t>
+          <t>Bug 61 (P1) confirmed.</t>
         </is>
       </c>
     </row>
@@ -11002,7 +11002,7 @@
       </c>
       <c r="Q133" s="7" t="inlineStr">
         <is>
-          <t>Bug 58 (P3).</t>
+          <t>Bug 42 (P3).</t>
         </is>
       </c>
     </row>
@@ -11723,7 +11723,7 @@
       </c>
       <c r="Q143" s="7" t="inlineStr">
         <is>
-          <t>Bug 76 (P1) confirmed.</t>
+          <t>Bug 61 (P1) confirmed.</t>
         </is>
       </c>
     </row>
@@ -11798,7 +11798,7 @@
       </c>
       <c r="Q144" s="7" t="inlineStr">
         <is>
-          <t>Bug 48 (P1).</t>
+          <t>Bug 32 (P1).</t>
         </is>
       </c>
     </row>
@@ -13288,7 +13288,7 @@
       </c>
       <c r="Q165" s="7" t="inlineStr">
         <is>
-          <t>Bug 50 (P2) confirmed by real write.</t>
+          <t>Bug 34 (P2) confirmed by real write.</t>
         </is>
       </c>
     </row>
@@ -14213,7 +14213,7 @@
       </c>
       <c r="Q178" s="7" t="inlineStr">
         <is>
-          <t>Bug 65 (P3).</t>
+          <t>Bug 50 (P3).</t>
         </is>
       </c>
     </row>
@@ -14788,7 +14788,7 @@
       </c>
       <c r="Q186" s="7" t="inlineStr">
         <is>
-          <t>Bug 73 (P1).</t>
+          <t>Bug 58 (P1).</t>
         </is>
       </c>
     </row>
@@ -16631,7 +16631,7 @@
       </c>
       <c r="O212" s="7" t="inlineStr">
         <is>
-          <t>26/27 frameworks create+save+persist as FA (owner=spfield). 1/27 fails = DF Product Prototyping (Bug 54).</t>
+          <t>26/27 frameworks create+save+persist as FA (owner=spfield). 1/27 fails = DF Product Prototyping (Bug 38).</t>
         </is>
       </c>
       <c r="P212" s="8" t="inlineStr"/>
@@ -16708,7 +16708,7 @@
       </c>
       <c r="Q213" s="7" t="inlineStr">
         <is>
-          <t>Bug 51 (P2).</t>
+          <t>Bug 35 (P2).</t>
         </is>
       </c>
     </row>
@@ -16774,7 +16774,7 @@
       </c>
       <c r="O214" s="7" t="inlineStr">
         <is>
-          <t>Bug 58: the Log Book / Task dropdown is not framework-filtered - the per-framework log shows non-scoped task options (recurs across frameworks).</t>
+          <t>Bug 42: the Log Book / Task dropdown is not framework-filtered - the per-framework log shows non-scoped task options (recurs across frameworks).</t>
         </is>
       </c>
       <c r="P214" s="8" t="inlineStr">
@@ -16784,7 +16784,7 @@
       </c>
       <c r="Q214" s="7" t="inlineStr">
         <is>
-          <t>Log/Task not framework-scoped (Bug 58).</t>
+          <t>Log/Task not framework-scoped (Bug 42).</t>
         </is>
       </c>
     </row>
@@ -16928,7 +16928,7 @@
       </c>
       <c r="Q216" s="7" t="inlineStr">
         <is>
-          <t>Bug 73 (P1).</t>
+          <t>Bug 58 (P1).</t>
         </is>
       </c>
     </row>
@@ -17980,7 +17980,7 @@
       </c>
       <c r="Q231" s="7" t="inlineStr">
         <is>
-          <t>Bug 75 (P2).</t>
+          <t>Bug 60 (P2).</t>
         </is>
       </c>
     </row>
@@ -18113,7 +18113,7 @@
       </c>
       <c r="O233" s="7" t="inlineStr">
         <is>
-          <t>Bug 83: the flat LIFCOM EMI (Loan/Term) fields exist in the Infrastructure doctype but are not surfaced on the Financial Model / Tracker - EMI not shown/computed in the UI.</t>
+          <t>Bug 68: the flat LIFCOM EMI (Loan/Term) fields exist in the Infrastructure doctype but are not surfaced on the Financial Model / Tracker - EMI not shown/computed in the UI.</t>
         </is>
       </c>
       <c r="P233" s="8" t="inlineStr">
@@ -18123,7 +18123,7 @@
       </c>
       <c r="Q233" s="7" t="inlineStr">
         <is>
-          <t>Infra EMI not surfaced (Bug 83).</t>
+          <t>Infra EMI not surfaced (Bug 68).</t>
         </is>
       </c>
     </row>
@@ -18611,7 +18611,7 @@
       </c>
       <c r="Q240" s="7" t="inlineStr">
         <is>
-          <t>Bug 54 (P1).</t>
+          <t>Bug 38 (P1).</t>
         </is>
       </c>
     </row>
@@ -18676,7 +18676,7 @@
       </c>
       <c r="O241" s="7" t="inlineStr">
         <is>
-          <t>Bug 86: the Product Testing Sent&lt;=Received&lt;=Reported date chain is not enforced (no validation fires) - CVR-0176.</t>
+          <t>Bug 71: the Product Testing Sent&lt;=Received&lt;=Reported date chain is not enforced (no validation fires) - CVR-0176.</t>
         </is>
       </c>
       <c r="P241" s="8" t="inlineStr">
@@ -18686,7 +18686,7 @@
       </c>
       <c r="Q241" s="7" t="inlineStr">
         <is>
-          <t>Test date-chain not enforced (Bug 86).</t>
+          <t>Test date-chain not enforced (Bug 71).</t>
         </is>
       </c>
     </row>
@@ -19142,7 +19142,7 @@
       <c r="J248" s="7" t="inlineStr"/>
       <c r="K248" s="7" t="inlineStr">
         <is>
-          <t>• Pre-req: the Logistic Packing Type master must be seeded (e.g. Inner / Outer / Cushion) — see Bug 84.
+          <t>• Pre-req: the Logistic Packing Type master must be seeded (e.g. Inner / Outer / Cushion) — see Bug 69.
 • Existing tab → + Add Product → Save (product needs a saved ID). In Section I "Packing Details", + Add Row: Type of Packing = Outer (from the master), Unit = kg, Price per Unit = ₹50.
 • In the "Monthly Shipment Quantities" matrix (one row/month, one column per packing item), enter a monthly quantity (e.g. Apr = 100).</t>
         </is>
@@ -19156,7 +19156,7 @@
       </c>
       <c r="O248" s="7" t="inlineStr">
         <is>
-          <t>VERIFIED LIVE 15-Jun after seeding the "Logistic Packing Type" master (Inner/Outer/Cushion - per user go-ahead; the Bug 84 fix). Built a record via API (product EP-PROD-0017 + packing item Type=Outer/Unit=kg/Price Rs 50 + monthly shipment Apr qty=100), opened in UI: matrix column "Outer @ Rs 50/unit"; Month Total = qty x Price/Unit = 100 x 50 = Rs 5,000; "All Existing Packing - Total" footer: Annual Units = sum monthly qty = 100, Annual Cost = sum(qty x Price/Unit) = Rs 5,000, Monthly Cost = Annual/12 (avg) = Rs 417. Calc CORRECT. The earlier Rs 0 was solely the unseeded master (Bug 84), not a calc defect. Test case rewritten to this verified model; transaction record deleted (master seed retained as the Bug-84 fix).</t>
+          <t>VERIFIED LIVE 15-Jun after seeding the "Logistic Packing Type" master (Inner/Outer/Cushion - per user go-ahead; the Bug 69 fix). Built a record via API (product EP-PROD-0017 + packing item Type=Outer/Unit=kg/Price Rs 50 + monthly shipment Apr qty=100), opened in UI: matrix column "Outer @ Rs 50/unit"; Month Total = qty x Price/Unit = 100 x 50 = Rs 5,000; "All Existing Packing - Total" footer: Annual Units = sum monthly qty = 100, Annual Cost = sum(qty x Price/Unit) = Rs 5,000, Monthly Cost = Annual/12 (avg) = Rs 417. Calc CORRECT. The earlier Rs 0 was solely the unseeded master (Bug 69), not a calc defect. Test case rewritten to this verified model; transaction record deleted (master seed retained as the Bug-84 fix).</t>
         </is>
       </c>
       <c r="P248" s="8" t="inlineStr"/>
@@ -19902,7 +19902,7 @@
       </c>
       <c r="O259" s="7" t="inlineStr">
         <is>
-          <t>Cannot save a log without a photo - create_activity_log requires photo_device (str) but gets NoneType -&gt; raw type error. Photo not marked required in UI. Also: Field Associate field lets FA attribute the log to ANY user (Bug 59).</t>
+          <t>Cannot save a log without a photo - create_activity_log requires photo_device (str) but gets NoneType -&gt; raw type error. Photo not marked required in UI. Also: Field Associate field lets FA attribute the log to ANY user (Bug 43).</t>
         </is>
       </c>
       <c r="P259" s="8" t="inlineStr">
@@ -19912,7 +19912,7 @@
       </c>
       <c r="Q259" s="7" t="inlineStr">
         <is>
-          <t>Bug 57 (P2) + Bug 59 (P2).</t>
+          <t>Bug 41 (P2) + Bug 43 (P2).</t>
         </is>
       </c>
     </row>
@@ -19988,7 +19988,7 @@
       </c>
       <c r="Q260" s="7" t="inlineStr">
         <is>
-          <t>Bug 58 (P3).</t>
+          <t>Bug 42 (P3).</t>
         </is>
       </c>
     </row>
@@ -20287,7 +20287,7 @@
       </c>
       <c r="O264" s="7" t="inlineStr">
         <is>
-          <t>FA-cannot-log-for-EP-outside-block needs the FA (block-scoped) role; CT-IT is unscoped. NOTE: the New Log Field Associate field is a free all-users dropdown (Bug 59 - any user attributable).</t>
+          <t>FA-cannot-log-for-EP-outside-block needs the FA (block-scoped) role; CT-IT is unscoped. NOTE: the New Log Field Associate field is a free all-users dropdown (Bug 43 - any user attributable).</t>
         </is>
       </c>
       <c r="P264" s="8" t="inlineStr"/>
@@ -20421,7 +20421,7 @@
       </c>
       <c r="O266" s="7" t="inlineStr">
         <is>
-          <t>Calendar filters partially broken: Field-Associate filter silently ignored (Bug 67); get_activity_logs returns [] for known-good filters (Bug 60). Entrepreneur filter works.</t>
+          <t>Calendar filters partially broken: Field-Associate filter silently ignored (Bug 52); get_activity_logs returns [] for known-good filters (Bug 45). Entrepreneur filter works.</t>
         </is>
       </c>
       <c r="P266" s="8" t="inlineStr">
@@ -20431,7 +20431,7 @@
       </c>
       <c r="Q266" s="7" t="inlineStr">
         <is>
-          <t>Bug 60 (P2) + Bug 67 (P3).</t>
+          <t>Bug 45 (P2) + Bug 52 (P3).</t>
         </is>
       </c>
     </row>
@@ -20510,7 +20510,7 @@
       <c r="P267" s="8" t="inlineStr"/>
       <c r="Q267" s="7" t="inlineStr">
         <is>
-          <t>Bug 60 side-effect.</t>
+          <t>Bug 45 side-effect.</t>
         </is>
       </c>
     </row>
@@ -20729,7 +20729,7 @@
       </c>
       <c r="Q270" s="7" t="inlineStr">
         <is>
-          <t>Bug 64 + Bug 68 (P2).</t>
+          <t>Bug 49 + Bug 53 (P2).</t>
         </is>
       </c>
     </row>
@@ -21439,7 +21439,7 @@
       </c>
       <c r="O280" s="7" t="inlineStr">
         <is>
-          <t>Milestone Tracker shell/tabs render but data fetch failed ("Error loading data" + 0 KPIs, role-independent). 11-Jun retest reports Bug 55 FIXED (get_milestone_data 200) but a deep re-verify is still pending + a partial/stale deploy was observed.</t>
+          <t>Milestone Tracker shell/tabs render but data fetch failed ("Error loading data" + 0 KPIs, role-independent). 11-Jun retest reports Bug 39 FIXED (get_milestone_data 200) but a deep re-verify is still pending + a partial/stale deploy was observed.</t>
         </is>
       </c>
       <c r="P280" s="8" t="inlineStr">
@@ -21449,7 +21449,7 @@
       </c>
       <c r="Q280" s="7" t="inlineStr">
         <is>
-          <t>Bug 55 (P1) - reported fixed, re-verify pending.</t>
+          <t>Bug 39 (P1) - reported fixed, re-verify pending.</t>
         </is>
       </c>
     </row>
@@ -21848,7 +21848,7 @@
       </c>
       <c r="Q285" s="7" t="inlineStr">
         <is>
-          <t>Bug 62 (P3).</t>
+          <t>Bug 47 (P3).</t>
         </is>
       </c>
     </row>
@@ -22382,7 +22382,7 @@
       </c>
       <c r="O292" s="7" t="inlineStr">
         <is>
-          <t>Village-Visits map mode switches map layer/legend to visit pins (KPI re-scope is the separate Bug 62).</t>
+          <t>Village-Visits map mode switches map layer/legend to visit pins (KPI re-scope is the separate Bug 47).</t>
         </is>
       </c>
       <c r="P292" s="8" t="inlineStr"/>
@@ -25165,7 +25165,7 @@
       </c>
       <c r="M332" s="7" t="inlineStr">
         <is>
-          <t>Source: BRD PR-OV-004 — Designer = "View + Edit own drafts … no Create no Delete". NEW (gap exposed by Bug 73).</t>
+          <t>Source: BRD PR-OV-004 — Designer = "View + Edit own drafts … no Create no Delete". NEW (gap exposed by Bug 58).</t>
         </is>
       </c>
       <c r="N332" s="15" t="inlineStr">
@@ -25185,7 +25185,7 @@
       </c>
       <c r="Q332" s="7" t="inlineStr">
         <is>
-          <t>Bug 73 (P1) - framework-create real.</t>
+          <t>Bug 58 (P1) - framework-create real.</t>
         </is>
       </c>
     </row>
@@ -25253,7 +25253,7 @@
       </c>
       <c r="M333" s="7" t="inlineStr">
         <is>
-          <t>Source: BRD PR-OV-004 — all non-Marketing cells = "--" (server-enforced). NEW (Bug 73: confidentiality leak — reads all EP/Progress Report).</t>
+          <t>Source: BRD PR-OV-004 — all non-Marketing cells = "--" (server-enforced). NEW (Bug 58: confidentiality leak — reads all EP/Progress Report).</t>
         </is>
       </c>
       <c r="N333" s="15" t="inlineStr">
@@ -25273,7 +25273,7 @@
       </c>
       <c r="Q333" s="7" t="inlineStr">
         <is>
-          <t>Bug 73 read-leak (P1).</t>
+          <t>Bug 58 read-leak (P1).</t>
         </is>
       </c>
     </row>
@@ -25336,12 +25336,12 @@
       </c>
       <c r="L334" s="7" t="inlineStr">
         <is>
-          <t>BE (civil) fields are read-only — edit is blocked and Save does not enable; SELCO edits only EE/CE + SELCO pricing/equipment/disbursement fields. No "+ New" (no create). All non-Infrastructure workspaces denied. (Today: editing Plinth Rate enabled Save = Bug 75.)</t>
+          <t>BE (civil) fields are read-only — edit is blocked and Save does not enable; SELCO edits only EE/CE + SELCO pricing/equipment/disbursement fields. No "+ New" (no create). All non-Infrastructure workspaces denied. (Today: editing Plinth Rate enabled Save = Bug 60.)</t>
         </is>
       </c>
       <c r="M334" s="7" t="inlineStr">
         <is>
-          <t>Source: BRD PR-OV-004 — SELCO = "View all tabs (BE/EE/CE); edit only SELCO-relevant fields … no Create no Delete". UPDATES the SELCO row-scope assumption; NEW deny detail (Bug 75).</t>
+          <t>Source: BRD PR-OV-004 — SELCO = "View all tabs (BE/EE/CE); edit only SELCO-relevant fields … no Create no Delete". UPDATES the SELCO row-scope assumption; NEW deny detail (Bug 60).</t>
         </is>
       </c>
       <c r="N334" s="15" t="inlineStr">
@@ -25361,7 +25361,7 @@
       </c>
       <c r="Q334" s="7" t="inlineStr">
         <is>
-          <t>Bug 75 (P2).</t>
+          <t>Bug 60 (P2).</t>
         </is>
       </c>
     </row>
@@ -25424,12 +25424,12 @@
       </c>
       <c r="L335" s="7" t="inlineStr">
         <is>
-          <t>Read works; create / edit / delete are all blocked (UI controls absent, API 403). has_permission for User/Sector/Cohort create+write+delete = false. (Today: all return true = Bug 76 — CT-Program can delete users + wipe masters.)</t>
+          <t>Read works; create / edit / delete are all blocked (UI controls absent, API 403). has_permission for User/Sector/Cohort create+write+delete = false. (Today: all return true = Bug 61 — CT-Program can delete users + wipe masters.)</t>
         </is>
       </c>
       <c r="M335" s="7" t="inlineStr">
         <is>
-          <t>Source: BRD PR-OV-004 — CT-Program = "view-only" Users + Masters. UPDATES PR-TC-UM/PR-TC-MS role rows; NEW deny detail (Bug 76).</t>
+          <t>Source: BRD PR-OV-004 — CT-Program = "view-only" Users + Masters. UPDATES PR-TC-UM/PR-TC-MS role rows; NEW deny detail (Bug 61).</t>
         </is>
       </c>
       <c r="N335" s="15" t="inlineStr">
@@ -25449,7 +25449,7 @@
       </c>
       <c r="Q335" s="7" t="inlineStr">
         <is>
-          <t>Bug 76 (P1) CONFIRMED by real create.</t>
+          <t>Bug 61 (P1) CONFIRMED by real create.</t>
         </is>
       </c>
     </row>
@@ -25527,7 +25527,7 @@
       </c>
       <c r="O336" s="7" t="inlineStr">
         <is>
-          <t>Designer CAN edit an existing framework record (positive control passes). NOTE: passes but is over-broad - same root as Bug 73.</t>
+          <t>Designer CAN edit an existing framework record (positive control passes). NOTE: passes but is over-broad - same root as Bug 58.</t>
         </is>
       </c>
       <c r="P336" s="8" t="inlineStr"/>
@@ -25672,7 +25672,7 @@
       </c>
       <c r="L338" s="7" t="inlineStr">
         <is>
-          <t>Save is blocked with a clear "attachment required" message until a supporting document is attached. (Today the gate is not enforced — Bug 50.)</t>
+          <t>Save is blocked with a clear "attachment required" message until a supporting document is attached. (Today the gate is not enforced — Bug 34.)</t>
         </is>
       </c>
       <c r="M338" s="7" t="inlineStr">
@@ -25697,7 +25697,7 @@
       </c>
       <c r="Q338" s="7" t="inlineStr">
         <is>
-          <t>Bug 50 secondary (P2).</t>
+          <t>Bug 34 secondary (P2).</t>
         </is>
       </c>
     </row>
@@ -25844,7 +25844,7 @@
       </c>
       <c r="M340" s="7" t="inlineStr">
         <is>
-          <t>Source: S23 PM KPI redesign (Bug 69) + Q-on mode-context (Bugs 71/62). NEW.</t>
+          <t>Source: S23 PM KPI redesign (Bug 54) + Q-on mode-context (Bugs 71/62). NEW.</t>
         </is>
       </c>
       <c r="N340" s="15" t="inlineStr">
@@ -25864,7 +25864,7 @@
       </c>
       <c r="Q340" s="7" t="inlineStr">
         <is>
-          <t>Bug 69 + Bug 71 (P2/P3).</t>
+          <t>Bug 54 + Bug 56 (P2/P3).</t>
         </is>
       </c>
     </row>
@@ -25949,7 +25949,7 @@
       </c>
       <c r="Q341" s="7" t="inlineStr">
         <is>
-          <t>Bug 60 + Bug 67.</t>
+          <t>Bug 45 + Bug 52.</t>
         </is>
       </c>
     </row>
@@ -26084,7 +26084,7 @@
       </c>
       <c r="L343" s="7" t="inlineStr">
         <is>
-          <t>Sector auto-fills from the Basket (Candy → Food Processing) and is read-only — a manual Sector pick is not possible / does not override. (Today it auto-derives but silently overrides a manual pick instead of being read-only — confusing; cf. Bug 49 family.)</t>
+          <t>Sector auto-fills from the Basket (Candy → Food Processing) and is read-only — a manual Sector pick is not possible / does not override. (Today it auto-derives but silently overrides a manual pick instead of being read-only — confusing; cf. Bug 33 family.)</t>
         </is>
       </c>
       <c r="M343" s="7" t="inlineStr">
@@ -26169,7 +26169,7 @@
       </c>
       <c r="L344" s="7" t="inlineStr">
         <is>
-          <t>Marking read via the bell also sets the Notification Center record's read_at — read state is consistent across both views. (Today the two stores don't cross-sync — Bug 61 minor.)</t>
+          <t>Marking read via the bell also sets the Notification Center record's read_at — read state is consistent across both views. (Today the two stores don't cross-sync — Bug 46 minor.)</t>
         </is>
       </c>
       <c r="M344" s="7" t="inlineStr">
@@ -26194,7 +26194,7 @@
       </c>
       <c r="Q344" s="7" t="inlineStr">
         <is>
-          <t>Bug 61 residual (Q-B).</t>
+          <t>Bug 46 residual (Q-B).</t>
         </is>
       </c>
     </row>
@@ -30388,7 +30388,7 @@
       </c>
       <c r="O399" s="7" t="inlineStr">
         <is>
-          <t>META: Loan Detail has loan_start_date/loan_end_date and Schemes Entry application fields, but NO date-order validation (Application&lt;=today, Disbursement&gt;=Application, Loan End&gt;=Start) - not enforced. Same class as Bug 86.</t>
+          <t>META: Loan Detail has loan_start_date/loan_end_date and Schemes Entry application fields, but NO date-order validation (Application&lt;=today, Disbursement&gt;=Application, Loan End&gt;=Start) - not enforced. Same class as Bug 71.</t>
         </is>
       </c>
       <c r="P399" s="8" t="inlineStr">
@@ -31848,7 +31848,7 @@
       </c>
       <c r="O418" s="7" t="inlineStr">
         <is>
-          <t>Task Log task dropdown (DF Module Step Master) not framework-filtered to the 17 RM tasks - Bug 58.</t>
+          <t>Task Log task dropdown (DF Module Step Master) not framework-filtered to the 17 RM tasks - Bug 42.</t>
         </is>
       </c>
       <c r="P418" s="8" t="inlineStr">
@@ -31858,7 +31858,7 @@
       </c>
       <c r="Q418" s="7" t="inlineStr">
         <is>
-          <t>Bug 58 (P3).</t>
+          <t>Bug 42 (P3).</t>
         </is>
       </c>
     </row>
@@ -33612,7 +33612,7 @@
       </c>
       <c r="O441" s="7" t="inlineStr">
         <is>
-          <t>Task Log task dropdown links DF Module Step Master but is NOT framework-filtered (lists ~350 flat, not the 16 Machinery tasks) - Bug 58.</t>
+          <t>Task Log task dropdown links DF Module Step Master but is NOT framework-filtered (lists ~350 flat, not the 16 Machinery tasks) - Bug 42.</t>
         </is>
       </c>
       <c r="P441" s="8" t="inlineStr">
@@ -33622,7 +33622,7 @@
       </c>
       <c r="Q441" s="7" t="inlineStr">
         <is>
-          <t>Bug 58 (P3).</t>
+          <t>Bug 42 (P3).</t>
         </is>
       </c>
     </row>
@@ -33696,7 +33696,7 @@
       </c>
       <c r="O442" s="7" t="inlineStr">
         <is>
-          <t>META: quantity (No. of Machinery) reqd=1 (enforced). NOTE: name_of_machinery is reqd=0 - the "Name of Machinery" half of the case is NOT enforced (cf Bug 51 inconsistent mandatory).</t>
+          <t>META: quantity (No. of Machinery) reqd=1 (enforced). NOTE: name_of_machinery is reqd=0 - the "Name of Machinery" half of the case is NOT enforced (cf Bug 35 inconsistent mandatory).</t>
         </is>
       </c>
       <c r="P442" s="8" t="inlineStr"/>
@@ -34988,7 +34988,7 @@
       </c>
       <c r="O459" s="7" t="inlineStr">
         <is>
-          <t>Task Log dropdown (DF Module Step Master) not framework-filtered to the 9 HR tasks - Bug 58.</t>
+          <t>Task Log dropdown (DF Module Step Master) not framework-fi